--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-19.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-19.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB40"/>
+  <dimension ref="A1:CB46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -869,7 +869,7 @@
         <v>2.16</v>
       </c>
       <c r="J2" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K2" t="n">
         <v>3.85</v>
@@ -962,7 +962,7 @@
         <v>50</v>
       </c>
       <c r="AO2" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AP2" t="n">
         <v>12.5</v>
@@ -1013,7 +1013,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BF2" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BG2" t="n">
         <v>11</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-17 01:48:55</t>
+          <t>2026-07-17 04:10:01</t>
         </is>
       </c>
     </row>
@@ -1114,16 +1114,16 @@
         <v>1.63</v>
       </c>
       <c r="G3" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="H3" t="n">
         <v>6.4</v>
       </c>
       <c r="I3" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="J3" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="K3" t="n">
         <v>4.2</v>
@@ -1144,7 +1144,7 @@
         <v>1.71</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-17 01:48:55</t>
+          <t>2026-07-17 04:10:01</t>
         </is>
       </c>
     </row>
@@ -1368,16 +1368,16 @@
         <v>5.3</v>
       </c>
       <c r="G4" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="H4" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="I4" t="n">
         <v>1.81</v>
       </c>
       <c r="J4" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K4" t="n">
         <v>3.8</v>
@@ -1398,7 +1398,7 @@
         <v>1.72</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.2</v>
+        <v>2.04</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-17 01:48:55</t>
+          <t>2026-07-17 04:10:01</t>
         </is>
       </c>
     </row>
@@ -1628,10 +1628,10 @@
         <v>4.6</v>
       </c>
       <c r="I5" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="J5" t="n">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="K5" t="n">
         <v>4.5</v>
@@ -1649,10 +1649,10 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.96</v>
+        <v>1.85</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-17 01:48:55</t>
+          <t>2026-07-17 04:10:01</t>
         </is>
       </c>
     </row>
@@ -1873,7 +1873,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="G6" t="n">
         <v>3.2</v>
@@ -1885,10 +1885,10 @@
         <v>2.84</v>
       </c>
       <c r="J6" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K6" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-17 01:48:55</t>
+          <t>2026-07-17 04:10:01</t>
         </is>
       </c>
     </row>
@@ -2130,16 +2130,16 @@
         <v>2.96</v>
       </c>
       <c r="G7" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="H7" t="n">
         <v>2.4</v>
       </c>
       <c r="I7" t="n">
-        <v>2.68</v>
+        <v>2.74</v>
       </c>
       <c r="J7" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K7" t="n">
         <v>4.1</v>
@@ -2160,7 +2160,7 @@
         <v>1.82</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-17 01:48:55</t>
+          <t>2026-07-17 04:10:01</t>
         </is>
       </c>
     </row>
@@ -2390,7 +2390,7 @@
         <v>7.8</v>
       </c>
       <c r="I8" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="J8" t="n">
         <v>4.9</v>
@@ -2604,14 +2604,14 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-17 01:48:55</t>
+          <t>2026-07-17 04:10:01</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Swedish Superettan</t>
+          <t>Chinese League 2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2626,31 +2626,31 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Norrkoping</t>
+          <t>Dalian Yingbo II</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sandvikens IF</t>
+          <t>Xian Chongde Ronghai</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.57</v>
+        <v>1.04</v>
       </c>
       <c r="G9" t="n">
-        <v>1.65</v>
+        <v>1000</v>
       </c>
       <c r="H9" t="n">
-        <v>5.4</v>
+        <v>1.04</v>
       </c>
       <c r="I9" t="n">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="J9" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="K9" t="n">
-        <v>5.2</v>
+        <v>410</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -2665,10 +2665,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2.72</v>
+        <v>1.24</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.5</v>
+        <v>1.01</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -2858,14 +2858,14 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-17 01:48:55</t>
+          <t>2026-07-17 04:10:01</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Kazakhstan Premier League</t>
+          <t>Swedish Superettan</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2875,36 +2875,36 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>09:00:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>FK Altay</t>
+          <t>Norrkoping</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>FK Aktobe</t>
+          <t>Sandvikens IF</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.04</v>
+        <v>1.57</v>
       </c>
       <c r="G10" t="n">
-        <v>1000</v>
+        <v>1.64</v>
       </c>
       <c r="H10" t="n">
-        <v>1.04</v>
+        <v>5.1</v>
       </c>
       <c r="I10" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="J10" t="n">
-        <v>1.02</v>
+        <v>4.6</v>
       </c>
       <c r="K10" t="n">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -2919,10 +2919,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1.24</v>
+        <v>2.72</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -3112,14 +3112,14 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-17 01:48:55</t>
+          <t>2026-07-17 04:10:01</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Swedish Superettan</t>
+          <t>Chinese League 2</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3129,36 +3129,36 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>United IK Nordic</t>
+          <t>Taian Tiankuang</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Orebro</t>
+          <t>Qingdao Red Lions</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.85</v>
+        <v>1.04</v>
       </c>
       <c r="G11" t="n">
-        <v>2</v>
+        <v>1000</v>
       </c>
       <c r="H11" t="n">
-        <v>4</v>
+        <v>1.04</v>
       </c>
       <c r="I11" t="n">
-        <v>4.6</v>
+        <v>1000</v>
       </c>
       <c r="J11" t="n">
-        <v>3.7</v>
+        <v>1.01</v>
       </c>
       <c r="K11" t="n">
-        <v>4.3</v>
+        <v>440</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -3173,10 +3173,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>2.2</v>
+        <v>1.24</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.73</v>
+        <v>1.01</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -3366,14 +3366,14 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-17 01:48:55</t>
+          <t>2026-07-17 04:10:01</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Swedish Superettan</t>
+          <t>Chinese League 2</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3383,36 +3383,36 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>08:30:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Varnamo</t>
+          <t>Jiangxi Lushan</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Guangdong Mingtu</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.74</v>
+        <v>1.04</v>
       </c>
       <c r="G12" t="n">
-        <v>3.1</v>
+        <v>1000</v>
       </c>
       <c r="H12" t="n">
-        <v>2.44</v>
+        <v>1.04</v>
       </c>
       <c r="I12" t="n">
-        <v>2.74</v>
+        <v>1000</v>
       </c>
       <c r="J12" t="n">
-        <v>3.6</v>
+        <v>1.01</v>
       </c>
       <c r="K12" t="n">
-        <v>4</v>
+        <v>510</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -3427,10 +3427,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.12</v>
+        <v>1.24</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.71</v>
+        <v>1.01</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -3620,14 +3620,14 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-17 01:48:55</t>
+          <t>2026-07-17 04:10:01</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Chinese League 2</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3637,36 +3637,36 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>08:30:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Central Espanol</t>
+          <t>Hangzhou Linping Wuyue</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Cerro Largo FC</t>
+          <t>Chengdu Rongcheng II</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.84</v>
+        <v>1.04</v>
       </c>
       <c r="G13" t="n">
-        <v>3.45</v>
+        <v>1000</v>
       </c>
       <c r="H13" t="n">
-        <v>2.72</v>
+        <v>1.04</v>
       </c>
       <c r="I13" t="n">
-        <v>3.25</v>
+        <v>1000</v>
       </c>
       <c r="J13" t="n">
-        <v>2.94</v>
+        <v>1.01</v>
       </c>
       <c r="K13" t="n">
-        <v>3.55</v>
+        <v>490</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -3681,10 +3681,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1.52</v>
+        <v>1.24</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.56</v>
+        <v>1.01</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -3874,14 +3874,14 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-17 01:48:55</t>
+          <t>2026-07-17 04:10:01</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Estonian Premier League</t>
+          <t>Chinese League 2</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3891,17 +3891,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>11:00:00</t>
+          <t>08:30:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Wuhan Three Towns II</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Nomme Kalju</t>
+          <t>Guizhou Zhucheng Athletic</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -3920,7 +3920,7 @@
         <v>1.01</v>
       </c>
       <c r="K14" t="n">
-        <v>1000</v>
+        <v>550</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -4128,14 +4128,14 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-17 01:48:55</t>
+          <t>2026-07-17 04:10:01</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Icelandic Urvalsdeild</t>
+          <t>Chinese League 2</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -4145,36 +4145,36 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>11:00:00</t>
+          <t>08:30:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>IBV</t>
+          <t>Haimen Codion</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>KA Akureyri</t>
+          <t>Lanzhou Longyuan Athletic</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>470</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-17 01:48:55</t>
+          <t>2026-07-17 04:10:01</t>
         </is>
       </c>
     </row>
@@ -4399,17 +4399,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>11:00:00</t>
+          <t>09:00:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Irtysh Pavlodar</t>
+          <t>FK Altay</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>FC Astana</t>
+          <t>FK Aktobe</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -4636,14 +4636,14 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-17 01:48:55</t>
+          <t>2026-07-17 04:10:01</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Latvian Virsliga</t>
+          <t>Swedish Superettan</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -4653,36 +4653,36 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>11:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>United IK Nordic</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Orebro</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.04</v>
+        <v>1.85</v>
       </c>
       <c r="G17" t="n">
-        <v>1000</v>
+        <v>2</v>
       </c>
       <c r="H17" t="n">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="I17" t="n">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="J17" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="K17" t="n">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -4697,10 +4697,10 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>1.24</v>
+        <v>2.2</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.01</v>
+        <v>1.71</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -4890,14 +4890,14 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-17 01:48:55</t>
+          <t>2026-07-17 04:10:01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Romanian Liga I</t>
+          <t>Swedish Superettan</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -4907,36 +4907,36 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>11:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Varnamo</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Farul Constanta</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.08</v>
+        <v>2.74</v>
       </c>
       <c r="G18" t="n">
-        <v>2.18</v>
+        <v>3.1</v>
       </c>
       <c r="H18" t="n">
-        <v>3.75</v>
+        <v>2.44</v>
       </c>
       <c r="I18" t="n">
-        <v>4.2</v>
+        <v>2.74</v>
       </c>
       <c r="J18" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K18" t="n">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -4951,10 +4951,10 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>1.89</v>
+        <v>2.14</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.98</v>
+        <v>1.73</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -5144,14 +5144,14 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-17 01:48:55</t>
+          <t>2026-07-17 04:10:01</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Swedish Allsvenskan</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -5161,36 +5161,36 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>11:30:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Central Espanol</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Cerro Largo FC</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>3.65</v>
+        <v>2.82</v>
       </c>
       <c r="G19" t="n">
-        <v>3.85</v>
+        <v>3.3</v>
       </c>
       <c r="H19" t="n">
-        <v>2.04</v>
+        <v>2.7</v>
       </c>
       <c r="I19" t="n">
-        <v>2.12</v>
+        <v>3.15</v>
       </c>
       <c r="J19" t="n">
-        <v>3.9</v>
+        <v>2.94</v>
       </c>
       <c r="K19" t="n">
-        <v>4</v>
+        <v>3.55</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -5205,10 +5205,10 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.32</v>
+        <v>1.52</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -5398,14 +5398,14 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-17 01:48:55</t>
+          <t>2026-07-17 04:10:01</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Swedish Allsvenskan</t>
+          <t>Latvian Virsliga</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -5415,36 +5415,36 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>11:30:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.27</v>
+        <v>1.04</v>
       </c>
       <c r="G20" t="n">
-        <v>1.31</v>
+        <v>1000</v>
       </c>
       <c r="H20" t="n">
-        <v>12</v>
+        <v>1.04</v>
       </c>
       <c r="I20" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="J20" t="n">
-        <v>6</v>
+        <v>1.02</v>
       </c>
       <c r="K20" t="n">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -5459,10 +5459,10 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>2.5</v>
+        <v>1.24</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.54</v>
+        <v>1.01</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -5652,14 +5652,14 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-17 01:48:55</t>
+          <t>2026-07-17 04:10:01</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Swedish Allsvenskan</t>
+          <t>Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -5669,36 +5669,36 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>11:30:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Halmstads</t>
+          <t>Irtysh Pavlodar</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Hacken</t>
+          <t>FC Astana</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>5.4</v>
+        <v>1.04</v>
       </c>
       <c r="G21" t="n">
-        <v>5.8</v>
+        <v>1000</v>
       </c>
       <c r="H21" t="n">
-        <v>1.62</v>
+        <v>1.04</v>
       </c>
       <c r="I21" t="n">
-        <v>1.64</v>
+        <v>1000</v>
       </c>
       <c r="J21" t="n">
-        <v>4.7</v>
+        <v>1.02</v>
       </c>
       <c r="K21" t="n">
-        <v>4.9</v>
+        <v>1000</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -5713,10 +5713,10 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>2.64</v>
+        <v>1.24</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.53</v>
+        <v>1.01</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -5906,14 +5906,14 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-07-17 01:48:55</t>
+          <t>2026-07-17 04:10:01</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Bolivian Liga de Futbol Profesional</t>
+          <t>Romanian Liga I</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -5923,36 +5923,36 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>12:00:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>CD Gualberto Villarroel</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Farul Constanta</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.04</v>
+        <v>2.02</v>
       </c>
       <c r="G22" t="n">
-        <v>1000</v>
+        <v>2.18</v>
       </c>
       <c r="H22" t="n">
-        <v>1.04</v>
+        <v>3.85</v>
       </c>
       <c r="I22" t="n">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="J22" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="K22" t="n">
-        <v>1000</v>
+        <v>3.8</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -5967,10 +5967,10 @@
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>1.24</v>
+        <v>1.91</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.01</v>
+        <v>1.93</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
@@ -6160,14 +6160,14 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-07-17 01:48:55</t>
+          <t>2026-07-17 04:10:01</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Kazakhstan Premier League</t>
+          <t>Estonian Premier League</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -6177,33 +6177,33 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>12:00:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>FC Ordabasy</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Elimai FC</t>
+          <t>Nomme Kalju</t>
         </is>
       </c>
       <c r="F23" t="n">
         <v>1.04</v>
       </c>
       <c r="G23" t="n">
-        <v>1.79</v>
+        <v>1000</v>
       </c>
       <c r="H23" t="n">
-        <v>2.3</v>
+        <v>1.04</v>
       </c>
       <c r="I23" t="n">
         <v>1000</v>
       </c>
       <c r="J23" t="n">
-        <v>2.3</v>
+        <v>1.02</v>
       </c>
       <c r="K23" t="n">
         <v>1000</v>
@@ -6414,14 +6414,14 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-07-17 01:48:55</t>
+          <t>2026-07-17 04:10:01</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Finnish Veikkausliiga</t>
+          <t>Icelandic Urvalsdeild</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -6431,36 +6431,36 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>12:30:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>IBV</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>FC Inter</t>
+          <t>KA Akureyri</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -6475,10 +6475,10 @@
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>1.97</v>
+        <v>1.24</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.61</v>
+        <v>1.01</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -6668,14 +6668,14 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-07-17 01:48:55</t>
+          <t>2026-07-17 04:10:01</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Lithuanian A Lyga</t>
+          <t>Swedish Allsvenskan</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -6685,36 +6685,36 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>12:45:00</t>
+          <t>11:30:00</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>FC Dziugas</t>
+          <t>Halmstads</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>FK Banga Gargzdu</t>
+          <t>Hacken</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.04</v>
+        <v>5.7</v>
       </c>
       <c r="G25" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="H25" t="n">
-        <v>1.04</v>
+        <v>1.6</v>
       </c>
       <c r="I25" t="n">
-        <v>1000</v>
+        <v>1.62</v>
       </c>
       <c r="J25" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="K25" t="n">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -6729,10 +6729,10 @@
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>1.24</v>
+        <v>2.64</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -6922,14 +6922,14 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-07-17 01:48:55</t>
+          <t>2026-07-17 04:10:01</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Peruvian Primera Division</t>
+          <t>Swedish Allsvenskan</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -6939,36 +6939,36 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>11:30:00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>CD Los Chankas</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sport Boys (Per)</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -6983,10 +6983,10 @@
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>1.24</v>
+        <v>2.32</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.01</v>
+        <v>1.6</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -7176,14 +7176,14 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-07-17 01:48:55</t>
+          <t>2026-07-17 04:10:01</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Swedish Allsvenskan</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -7193,42 +7193,42 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>11:30:00</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Cerro</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Racing Club (Uru)</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>6</v>
+        <v>1.28</v>
       </c>
       <c r="G27" t="n">
-        <v>6.6</v>
+        <v>1.33</v>
       </c>
       <c r="H27" t="n">
-        <v>1.78</v>
+        <v>11.5</v>
       </c>
       <c r="I27" t="n">
-        <v>1.83</v>
+        <v>14</v>
       </c>
       <c r="J27" t="n">
-        <v>3.5</v>
+        <v>6.2</v>
       </c>
       <c r="K27" t="n">
-        <v>3.55</v>
+        <v>7</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
         <v>0</v>
@@ -7237,10 +7237,10 @@
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>1.5</v>
+        <v>2.52</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.7</v>
+        <v>1.54</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -7261,112 +7261,112 @@
         <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="AF27" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="AG27" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="AI27" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="AJ27" t="n">
-        <v>280</v>
+        <v>0</v>
       </c>
       <c r="AK27" t="n">
-        <v>170</v>
+        <v>0</v>
       </c>
       <c r="AL27" t="n">
-        <v>190</v>
+        <v>0</v>
       </c>
       <c r="AM27" t="n">
-        <v>340</v>
+        <v>0</v>
       </c>
       <c r="AN27" t="n">
-        <v>330</v>
+        <v>0</v>
       </c>
       <c r="AO27" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="AP27" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="AQ27" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AR27" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="AS27" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="AT27" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AU27" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="AV27" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AW27" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AX27" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="AY27" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AZ27" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="BA27" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BB27" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="BC27" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="BD27" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="BE27" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="BF27" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="BG27" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="BH27" t="n">
         <v>0</v>
@@ -7430,14 +7430,14 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-07-17 01:48:55</t>
+          <t>2026-07-17 04:10:01</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Slovenian Premier League</t>
+          <t>Bolivian Liga de Futbol Profesional</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -7447,36 +7447,36 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NK Aluminij</t>
+          <t>CD Gualberto Villarroel</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>NK Maribor</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>4.3</v>
+        <v>1.04</v>
       </c>
       <c r="G28" t="n">
-        <v>5.1</v>
+        <v>1000</v>
       </c>
       <c r="H28" t="n">
-        <v>1.68</v>
+        <v>1.04</v>
       </c>
       <c r="I28" t="n">
-        <v>1.84</v>
+        <v>1000</v>
       </c>
       <c r="J28" t="n">
-        <v>4.2</v>
+        <v>1.02</v>
       </c>
       <c r="K28" t="n">
-        <v>5.1</v>
+        <v>1000</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -7491,10 +7491,10 @@
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>2.62</v>
+        <v>1.24</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.48</v>
+        <v>1.01</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
@@ -7684,14 +7684,14 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-07-17 01:48:55</t>
+          <t>2026-07-17 04:10:01</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Lithuanian A Lyga</t>
+          <t>Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -7701,33 +7701,33 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VMFD Zalgiris</t>
+          <t>FC Ordabasy</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Elimai FC</t>
         </is>
       </c>
       <c r="F29" t="n">
         <v>1.04</v>
       </c>
       <c r="G29" t="n">
-        <v>1000</v>
+        <v>1.79</v>
       </c>
       <c r="H29" t="n">
-        <v>1.04</v>
+        <v>2.3</v>
       </c>
       <c r="I29" t="n">
         <v>1000</v>
       </c>
       <c r="J29" t="n">
-        <v>1.01</v>
+        <v>2.3</v>
       </c>
       <c r="K29" t="n">
         <v>1000</v>
@@ -7938,14 +7938,14 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-07-17 01:48:55</t>
+          <t>2026-07-17 04:10:01</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Latvian Virsliga</t>
+          <t>Finnish Veikkausliiga</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -7955,36 +7955,36 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>12:30:00</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>FK Auda</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Liepajas Metalurgs</t>
+          <t>FC Inter</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="G30" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="H30" t="n">
-        <v>1.04</v>
+        <v>1.54</v>
       </c>
       <c r="I30" t="n">
-        <v>1000</v>
+        <v>1.66</v>
       </c>
       <c r="J30" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="K30" t="n">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
@@ -7999,10 +7999,10 @@
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>1.07</v>
+        <v>2.14</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.01</v>
+        <v>1.69</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -8192,14 +8192,14 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-07-17 01:48:55</t>
+          <t>2026-07-17 04:10:01</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Icelandic Urvalsdeild</t>
+          <t>Lithuanian A Lyga</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -8209,36 +8209,36 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>12:45:00</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>KR Reykjavik</t>
+          <t>FC Dziugas</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>FK Banga Gargzdu</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="I31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="K31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -8446,14 +8446,14 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-07-17 01:48:55</t>
+          <t>2026-07-17 04:10:01</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Estonian Premier League</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -8468,38 +8468,38 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Harju JK Laagri</t>
+          <t>Cerro</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Paide Linnameeskond</t>
+          <t>Racing Club (Uru)</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1.04</v>
+        <v>5.8</v>
       </c>
       <c r="G32" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="H32" t="n">
-        <v>1.04</v>
+        <v>1.76</v>
       </c>
       <c r="I32" t="n">
-        <v>1000</v>
+        <v>1.85</v>
       </c>
       <c r="J32" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K32" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
         <v>1.01</v>
       </c>
-      <c r="K32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L32" t="n">
-        <v>0</v>
-      </c>
-      <c r="M32" t="n">
-        <v>0</v>
-      </c>
       <c r="N32" t="n">
         <v>0</v>
       </c>
@@ -8507,10 +8507,10 @@
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>1.24</v>
+        <v>1.53</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.01</v>
+        <v>2.68</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -8531,112 +8531,112 @@
         <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AI32" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="AK32" t="n">
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="AL32" t="n">
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="AM32" t="n">
-        <v>0</v>
+        <v>340</v>
       </c>
       <c r="AN32" t="n">
-        <v>0</v>
+        <v>320</v>
       </c>
       <c r="AO32" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AP32" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AR32" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AS32" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AT32" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AU32" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AV32" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AW32" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AX32" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AY32" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AZ32" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="BA32" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="BB32" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="BC32" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="BD32" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="BE32" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="BF32" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="BG32" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BH32" t="n">
         <v>0</v>
@@ -8700,14 +8700,14 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-07-17 01:48:55</t>
+          <t>2026-07-17 04:10:01</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Bulgarian A League</t>
+          <t>Slovenian Premier League</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -8717,36 +8717,36 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>13:30:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>NK Aluminij</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>NK Maribor</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>2.8</v>
+        <v>4.3</v>
       </c>
       <c r="G33" t="n">
-        <v>3.1</v>
+        <v>5.8</v>
       </c>
       <c r="H33" t="n">
-        <v>2.86</v>
+        <v>1.67</v>
       </c>
       <c r="I33" t="n">
-        <v>3.25</v>
+        <v>1.89</v>
       </c>
       <c r="J33" t="n">
-        <v>2.78</v>
+        <v>4.2</v>
       </c>
       <c r="K33" t="n">
-        <v>3.25</v>
+        <v>5.1</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
@@ -8761,10 +8761,10 @@
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>1.42</v>
+        <v>2.64</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.36</v>
+        <v>1.48</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
@@ -8954,14 +8954,14 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-07-17 01:48:55</t>
+          <t>2026-07-17 04:10:01</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Romanian Liga I</t>
+          <t>Peruvian Primera Division</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -8971,36 +8971,36 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>13:30:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>ACS Petrolul 52</t>
+          <t>CD Los Chankas</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Dinamo Bucharest</t>
+          <t>Sport Boys (Per)</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
@@ -9015,10 +9015,10 @@
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>1.66</v>
+        <v>1.24</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.28</v>
+        <v>1.01</v>
       </c>
       <c r="R34" t="n">
         <v>0</v>
@@ -9208,14 +9208,14 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-07-17 01:48:55</t>
+          <t>2026-07-17 04:10:01</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>Latvian Virsliga</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -9225,36 +9225,36 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>13:45:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Tecnico Universitario</t>
+          <t>FK Auda</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Aucas</t>
+          <t>Liepajas Metalurgs</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>2.9</v>
+        <v>1.04</v>
       </c>
       <c r="G35" t="n">
-        <v>4.6</v>
+        <v>1000</v>
       </c>
       <c r="H35" t="n">
-        <v>2.14</v>
+        <v>1.04</v>
       </c>
       <c r="I35" t="n">
-        <v>2.88</v>
+        <v>1000</v>
       </c>
       <c r="J35" t="n">
-        <v>2.28</v>
+        <v>1.02</v>
       </c>
       <c r="K35" t="n">
-        <v>5.4</v>
+        <v>1000</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
@@ -9269,10 +9269,10 @@
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>1.53</v>
+        <v>1.07</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.22</v>
+        <v>1.01</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -9462,14 +9462,14 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-07-17 01:48:55</t>
+          <t>2026-07-17 04:10:01</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Serbian Super League</t>
+          <t>Icelandic Urvalsdeild</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -9479,36 +9479,36 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Cukaricki</t>
+          <t>KR Reykjavik</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>FK IMT Novi Beograd</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
@@ -9523,7 +9523,7 @@
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>1.07</v>
+        <v>1.24</v>
       </c>
       <c r="Q36" t="n">
         <v>1.01</v>
@@ -9716,14 +9716,14 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-07-17 01:48:55</t>
+          <t>2026-07-17 04:10:01</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Serbian Super League</t>
+          <t>Estonian Premier League</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -9733,33 +9733,33 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Harju JK Laagri</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Paide Linnameeskond</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>1.49</v>
+        <v>1.04</v>
       </c>
       <c r="G37" t="n">
-        <v>1.88</v>
+        <v>1000</v>
       </c>
       <c r="H37" t="n">
-        <v>2.14</v>
+        <v>1.04</v>
       </c>
       <c r="I37" t="n">
         <v>1000</v>
       </c>
       <c r="J37" t="n">
-        <v>2.14</v>
+        <v>1.02</v>
       </c>
       <c r="K37" t="n">
         <v>1000</v>
@@ -9777,10 +9777,10 @@
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>1.96</v>
+        <v>1.24</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.58</v>
+        <v>1.01</v>
       </c>
       <c r="R37" t="n">
         <v>0</v>
@@ -9970,14 +9970,14 @@
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-07-17 01:48:55</t>
+          <t>2026-07-17 04:10:01</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Serbian Super League</t>
+          <t>Lithuanian A Lyga</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -9987,36 +9987,36 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>VMFD Zalgiris</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Mladost Lucani</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>1.77</v>
+        <v>1.04</v>
       </c>
       <c r="G38" t="n">
-        <v>2.32</v>
+        <v>1000</v>
       </c>
       <c r="H38" t="n">
-        <v>3.3</v>
+        <v>1.04</v>
       </c>
       <c r="I38" t="n">
         <v>1000</v>
       </c>
       <c r="J38" t="n">
-        <v>3.15</v>
+        <v>1.02</v>
       </c>
       <c r="K38" t="n">
-        <v>3.7</v>
+        <v>1000</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
@@ -10031,10 +10031,10 @@
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>1.57</v>
+        <v>1.24</v>
       </c>
       <c r="Q38" t="n">
-        <v>2</v>
+        <v>1.01</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
@@ -10224,14 +10224,14 @@
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-07-17 01:48:55</t>
+          <t>2026-07-17 04:10:01</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>Bulgarian A League</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -10241,36 +10241,36 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>18:45:00</t>
+          <t>13:30:00</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Guayaquil City</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>2.06</v>
+        <v>2.8</v>
       </c>
       <c r="G39" t="n">
-        <v>2.68</v>
+        <v>3.1</v>
       </c>
       <c r="H39" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="I39" t="n">
-        <v>4.9</v>
+        <v>3.25</v>
       </c>
       <c r="J39" t="n">
-        <v>2.36</v>
+        <v>2.78</v>
       </c>
       <c r="K39" t="n">
-        <v>5.3</v>
+        <v>3.25</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
@@ -10285,10 +10285,10 @@
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.2</v>
+        <v>2.58</v>
       </c>
       <c r="R39" t="n">
         <v>0</v>
@@ -10478,261 +10478,1785 @@
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-07-17 01:48:55</t>
+          <t>2026-07-17 04:10:01</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
+          <t>Romanian Liga I</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>13:30:00</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>ACS Petrolul 52</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Dinamo Bucharest</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="G40" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H40" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="I40" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="J40" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K40" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="R40" t="n">
+        <v>0</v>
+      </c>
+      <c r="S40" t="n">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>0</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
+      </c>
+      <c r="V40" t="n">
+        <v>0</v>
+      </c>
+      <c r="W40" t="n">
+        <v>0</v>
+      </c>
+      <c r="X40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ40" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA40" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB40" t="inlineStr">
+        <is>
+          <t>2026-07-17 04:10:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Ecuadorian Serie A</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>13:45:00</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Tecnico Universitario</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Aucas</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="G41" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H41" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="I41" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="J41" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="K41" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="R41" t="n">
+        <v>0</v>
+      </c>
+      <c r="S41" t="n">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>0</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
+      </c>
+      <c r="V41" t="n">
+        <v>0</v>
+      </c>
+      <c r="W41" t="n">
+        <v>0</v>
+      </c>
+      <c r="X41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ41" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA41" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB41" t="inlineStr">
+        <is>
+          <t>2026-07-17 04:10:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Serbian Super League</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Cukaricki</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>FK IMT Novi Beograd</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G42" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H42" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I42" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J42" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="K42" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R42" t="n">
+        <v>0</v>
+      </c>
+      <c r="S42" t="n">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>0</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
+      </c>
+      <c r="V42" t="n">
+        <v>0</v>
+      </c>
+      <c r="W42" t="n">
+        <v>0</v>
+      </c>
+      <c r="X42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ42" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA42" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB42" t="inlineStr">
+        <is>
+          <t>2026-07-17 04:10:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Serbian Super League</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Vojvodina</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>OFK Beograd</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="G43" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="H43" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="I43" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J43" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="K43" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" t="n">
+        <v>0</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P43" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="R43" t="n">
+        <v>0</v>
+      </c>
+      <c r="S43" t="n">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>0</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
+      </c>
+      <c r="V43" t="n">
+        <v>0</v>
+      </c>
+      <c r="W43" t="n">
+        <v>0</v>
+      </c>
+      <c r="X43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ43" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA43" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB43" t="inlineStr">
+        <is>
+          <t>2026-07-17 04:10:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Serbian Super League</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Radnik Surdulica</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Mladost Lucani</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="G44" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="H44" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I44" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="J44" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="K44" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" t="n">
+        <v>0</v>
+      </c>
+      <c r="O44" t="n">
+        <v>0</v>
+      </c>
+      <c r="P44" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="R44" t="n">
+        <v>0</v>
+      </c>
+      <c r="S44" t="n">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>0</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
+      </c>
+      <c r="V44" t="n">
+        <v>0</v>
+      </c>
+      <c r="W44" t="n">
+        <v>0</v>
+      </c>
+      <c r="X44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ44" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA44" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB44" t="inlineStr">
+        <is>
+          <t>2026-07-17 04:10:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Ecuadorian Serie A</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>18:45:00</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Guayaquil City</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Manta FC</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="G45" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="H45" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="I45" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J45" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="K45" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" t="n">
+        <v>0</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0</v>
+      </c>
+      <c r="P45" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R45" t="n">
+        <v>0</v>
+      </c>
+      <c r="S45" t="n">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>0</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
+      </c>
+      <c r="V45" t="n">
+        <v>0</v>
+      </c>
+      <c r="W45" t="n">
+        <v>0</v>
+      </c>
+      <c r="X45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ45" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA45" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB45" t="inlineStr">
+        <is>
+          <t>2026-07-17 04:10:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
           <t>Brazilian Serie D</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B46" t="inlineStr">
         <is>
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C46" t="inlineStr">
         <is>
           <t>19:00:00</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="D46" t="inlineStr">
         <is>
           <t>America RN</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="E46" t="inlineStr">
         <is>
           <t>Gama</t>
         </is>
       </c>
-      <c r="F40" t="n">
+      <c r="F46" t="n">
         <v>1.02</v>
       </c>
-      <c r="G40" t="n">
+      <c r="G46" t="n">
         <v>1000</v>
       </c>
-      <c r="H40" t="n">
+      <c r="H46" t="n">
         <v>1.02</v>
       </c>
-      <c r="I40" t="n">
+      <c r="I46" t="n">
         <v>1000</v>
       </c>
-      <c r="J40" t="n">
+      <c r="J46" t="n">
         <v>1.02</v>
       </c>
-      <c r="K40" t="n">
+      <c r="K46" t="n">
         <v>1000</v>
       </c>
-      <c r="L40" t="n">
-        <v>0</v>
-      </c>
-      <c r="M40" t="n">
-        <v>0</v>
-      </c>
-      <c r="N40" t="n">
-        <v>0</v>
-      </c>
-      <c r="O40" t="n">
-        <v>0</v>
-      </c>
-      <c r="P40" t="n">
+      <c r="L46" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" t="n">
         <v>1.24</v>
       </c>
-      <c r="Q40" t="n">
+      <c r="Q46" t="n">
         <v>1.01</v>
       </c>
-      <c r="R40" t="n">
-        <v>0</v>
-      </c>
-      <c r="S40" t="n">
-        <v>0</v>
-      </c>
-      <c r="T40" t="n">
-        <v>0</v>
-      </c>
-      <c r="U40" t="n">
-        <v>0</v>
-      </c>
-      <c r="V40" t="n">
-        <v>0</v>
-      </c>
-      <c r="W40" t="n">
-        <v>0</v>
-      </c>
-      <c r="X40" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ40" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA40" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB40" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC40" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD40" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE40" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF40" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG40" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH40" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI40" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ40" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK40" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL40" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM40" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN40" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO40" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP40" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ40" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR40" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS40" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT40" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU40" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV40" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW40" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX40" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY40" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ40" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA40" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB40" t="inlineStr">
-        <is>
-          <t>2026-07-17 01:48:55</t>
+      <c r="R46" t="n">
+        <v>0</v>
+      </c>
+      <c r="S46" t="n">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>0</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
+      </c>
+      <c r="V46" t="n">
+        <v>0</v>
+      </c>
+      <c r="W46" t="n">
+        <v>0</v>
+      </c>
+      <c r="X46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ46" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA46" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB46" t="inlineStr">
+        <is>
+          <t>2026-07-17 04:10:01</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-19.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-19.xlsx
@@ -869,10 +869,10 @@
         <v>2.16</v>
       </c>
       <c r="J2" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K2" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L2" t="n">
         <v>1.35</v>
@@ -920,7 +920,7 @@
         <v>14</v>
       </c>
       <c r="AA2" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AB2" t="n">
         <v>15.5</v>
@@ -1001,7 +1001,7 @@
         <v>25</v>
       </c>
       <c r="BB2" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC2" t="n">
         <v>30</v>
@@ -1010,7 +1010,7 @@
         <v>36</v>
       </c>
       <c r="BE2" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BF2" t="n">
         <v>7.6</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-17 04:10:01</t>
+          <t>2026-07-17 06:31:26</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
         <v>1.63</v>
       </c>
       <c r="G3" t="n">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="H3" t="n">
         <v>6.4</v>
@@ -1123,7 +1123,7 @@
         <v>7.4</v>
       </c>
       <c r="J3" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="K3" t="n">
         <v>4.2</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-17 04:10:01</t>
+          <t>2026-07-17 06:31:26</t>
         </is>
       </c>
     </row>
@@ -1380,7 +1380,7 @@
         <v>3.6</v>
       </c>
       <c r="K4" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-17 04:10:01</t>
+          <t>2026-07-17 06:31:26</t>
         </is>
       </c>
     </row>
@@ -1628,7 +1628,7 @@
         <v>4.6</v>
       </c>
       <c r="I5" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="J5" t="n">
         <v>3.55</v>
@@ -1652,7 +1652,7 @@
         <v>1.87</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-17 04:10:01</t>
+          <t>2026-07-17 06:31:26</t>
         </is>
       </c>
     </row>
@@ -1888,7 +1888,7 @@
         <v>3.3</v>
       </c>
       <c r="K6" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-17 04:10:01</t>
+          <t>2026-07-17 06:31:26</t>
         </is>
       </c>
     </row>
@@ -2130,16 +2130,16 @@
         <v>2.96</v>
       </c>
       <c r="G7" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="H7" t="n">
         <v>2.4</v>
       </c>
       <c r="I7" t="n">
-        <v>2.74</v>
+        <v>2.68</v>
       </c>
       <c r="J7" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K7" t="n">
         <v>4.1</v>
@@ -2160,7 +2160,7 @@
         <v>1.82</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-17 04:10:01</t>
+          <t>2026-07-17 06:31:26</t>
         </is>
       </c>
     </row>
@@ -2390,7 +2390,7 @@
         <v>7.8</v>
       </c>
       <c r="I8" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="J8" t="n">
         <v>4.9</v>
@@ -2414,7 +2414,7 @@
         <v>2.12</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.72</v>
+        <v>1.61</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-17 04:10:01</t>
+          <t>2026-07-17 06:31:26</t>
         </is>
       </c>
     </row>
@@ -2650,7 +2650,7 @@
         <v>1.01</v>
       </c>
       <c r="K9" t="n">
-        <v>410</v>
+        <v>1000</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-17 04:10:01</t>
+          <t>2026-07-17 06:31:26</t>
         </is>
       </c>
     </row>
@@ -2892,7 +2892,7 @@
         <v>1.57</v>
       </c>
       <c r="G10" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="H10" t="n">
         <v>5.1</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-17 04:10:01</t>
+          <t>2026-07-17 06:31:26</t>
         </is>
       </c>
     </row>
@@ -3158,7 +3158,7 @@
         <v>1.01</v>
       </c>
       <c r="K11" t="n">
-        <v>440</v>
+        <v>1000</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-17 04:10:01</t>
+          <t>2026-07-17 06:31:26</t>
         </is>
       </c>
     </row>
@@ -3412,7 +3412,7 @@
         <v>1.01</v>
       </c>
       <c r="K12" t="n">
-        <v>510</v>
+        <v>1000</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-17 04:10:01</t>
+          <t>2026-07-17 06:31:26</t>
         </is>
       </c>
     </row>
@@ -3666,7 +3666,7 @@
         <v>1.01</v>
       </c>
       <c r="K13" t="n">
-        <v>490</v>
+        <v>1000</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-17 04:10:01</t>
+          <t>2026-07-17 06:31:26</t>
         </is>
       </c>
     </row>
@@ -3920,7 +3920,7 @@
         <v>1.01</v>
       </c>
       <c r="K14" t="n">
-        <v>550</v>
+        <v>1000</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-17 04:10:01</t>
+          <t>2026-07-17 06:31:26</t>
         </is>
       </c>
     </row>
@@ -4174,7 +4174,7 @@
         <v>1.01</v>
       </c>
       <c r="K15" t="n">
-        <v>470</v>
+        <v>1000</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-17 04:10:01</t>
+          <t>2026-07-17 06:31:26</t>
         </is>
       </c>
     </row>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-17 04:10:01</t>
+          <t>2026-07-17 06:31:26</t>
         </is>
       </c>
     </row>
@@ -4697,10 +4697,10 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-17 04:10:01</t>
+          <t>2026-07-17 06:31:26</t>
         </is>
       </c>
     </row>
@@ -4951,10 +4951,10 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-17 04:10:01</t>
+          <t>2026-07-17 06:31:26</t>
         </is>
       </c>
     </row>
@@ -5208,7 +5208,7 @@
         <v>1.52</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.4</v>
+        <v>2.54</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-17 04:10:01</t>
+          <t>2026-07-17 06:31:26</t>
         </is>
       </c>
     </row>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-17 04:10:01</t>
+          <t>2026-07-17 06:31:26</t>
         </is>
       </c>
     </row>
@@ -5683,22 +5683,22 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -5713,10 +5713,10 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-07-17 04:10:01</t>
+          <t>2026-07-17 06:31:26</t>
         </is>
       </c>
     </row>
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="G22" t="n">
         <v>2.18</v>
@@ -5949,7 +5949,7 @@
         <v>4.4</v>
       </c>
       <c r="J22" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="K22" t="n">
         <v>3.8</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-07-17 04:10:01</t>
+          <t>2026-07-17 06:31:26</t>
         </is>
       </c>
     </row>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-07-17 04:10:01</t>
+          <t>2026-07-17 06:31:26</t>
         </is>
       </c>
     </row>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-07-17 04:10:01</t>
+          <t>2026-07-17 06:31:26</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-07-17 04:10:01</t>
+          <t>2026-07-17 06:31:26</t>
         </is>
       </c>
     </row>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-07-17 04:10:01</t>
+          <t>2026-07-17 06:31:26</t>
         </is>
       </c>
     </row>
@@ -7219,7 +7219,7 @@
         <v>14</v>
       </c>
       <c r="J27" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="K27" t="n">
         <v>7</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-07-17 04:10:01</t>
+          <t>2026-07-17 06:31:26</t>
         </is>
       </c>
     </row>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-07-17 04:10:01</t>
+          <t>2026-07-17 06:31:26</t>
         </is>
       </c>
     </row>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-07-17 04:10:01</t>
+          <t>2026-07-17 06:31:26</t>
         </is>
       </c>
     </row>
@@ -7972,10 +7972,10 @@
         <v>6</v>
       </c>
       <c r="G30" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="H30" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="I30" t="n">
         <v>1.66</v>
@@ -7984,7 +7984,7 @@
         <v>4.2</v>
       </c>
       <c r="K30" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
@@ -7999,10 +7999,10 @@
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-07-17 04:10:01</t>
+          <t>2026-07-17 06:31:26</t>
         </is>
       </c>
     </row>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-07-17 04:10:01</t>
+          <t>2026-07-17 06:31:26</t>
         </is>
       </c>
     </row>
@@ -8477,13 +8477,13 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="G32" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="H32" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="I32" t="n">
         <v>1.85</v>
@@ -8492,13 +8492,13 @@
         <v>3.5</v>
       </c>
       <c r="K32" t="n">
-        <v>3.9</v>
+        <v>3.65</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="N32" t="n">
         <v>0</v>
@@ -8507,7 +8507,7 @@
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="Q32" t="n">
         <v>2.68</v>
@@ -8534,16 +8534,16 @@
         <v>10.5</v>
       </c>
       <c r="Y32" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="Z32" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AA32" t="n">
         <v>25</v>
       </c>
       <c r="AB32" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AC32" t="n">
         <v>8.4</v>
@@ -8582,10 +8582,10 @@
         <v>320</v>
       </c>
       <c r="AO32" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AP32" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AQ32" t="n">
         <v>4.5</v>
@@ -8600,7 +8600,7 @@
         <v>10.5</v>
       </c>
       <c r="AU32" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AV32" t="n">
         <v>8.199999999999999</v>
@@ -8609,31 +8609,31 @@
         <v>19</v>
       </c>
       <c r="AX32" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="AY32" t="n">
         <v>19</v>
       </c>
       <c r="AZ32" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BA32" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BB32" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BC32" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="BD32" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="BE32" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BF32" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BG32" t="n">
         <v>16</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-07-17 04:10:01</t>
+          <t>2026-07-17 06:31:26</t>
         </is>
       </c>
     </row>
@@ -8734,13 +8734,13 @@
         <v>4.3</v>
       </c>
       <c r="G33" t="n">
-        <v>5.8</v>
+        <v>5.1</v>
       </c>
       <c r="H33" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="I33" t="n">
-        <v>1.89</v>
+        <v>1.84</v>
       </c>
       <c r="J33" t="n">
         <v>4.2</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-07-17 04:10:01</t>
+          <t>2026-07-17 06:31:26</t>
         </is>
       </c>
     </row>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-07-17 04:10:01</t>
+          <t>2026-07-17 06:31:26</t>
         </is>
       </c>
     </row>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-07-17 04:10:01</t>
+          <t>2026-07-17 06:31:26</t>
         </is>
       </c>
     </row>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-07-17 04:10:01</t>
+          <t>2026-07-17 06:31:26</t>
         </is>
       </c>
     </row>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-07-17 04:10:01</t>
+          <t>2026-07-17 06:31:26</t>
         </is>
       </c>
     </row>
@@ -10224,7 +10224,7 @@
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-07-17 04:10:01</t>
+          <t>2026-07-17 06:31:26</t>
         </is>
       </c>
     </row>
@@ -10255,10 +10255,10 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="G39" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="H39" t="n">
         <v>2.88</v>
@@ -10288,7 +10288,7 @@
         <v>1.5</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="R39" t="n">
         <v>0</v>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-07-17 04:10:01</t>
+          <t>2026-07-17 06:31:26</t>
         </is>
       </c>
     </row>
@@ -10539,7 +10539,7 @@
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="Q40" t="n">
         <v>2.24</v>
@@ -10732,7 +10732,7 @@
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-07-17 04:10:01</t>
+          <t>2026-07-17 06:31:26</t>
         </is>
       </c>
     </row>
@@ -10763,22 +10763,22 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="G41" t="n">
         <v>4.6</v>
       </c>
       <c r="H41" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="I41" t="n">
-        <v>2.88</v>
+        <v>2.96</v>
       </c>
       <c r="J41" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="K41" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
@@ -10793,10 +10793,10 @@
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -10986,7 +10986,7 @@
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-07-17 04:10:01</t>
+          <t>2026-07-17 06:31:26</t>
         </is>
       </c>
     </row>
@@ -11240,7 +11240,7 @@
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-07-17 04:10:01</t>
+          <t>2026-07-17 06:31:26</t>
         </is>
       </c>
     </row>
@@ -11494,7 +11494,7 @@
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-07-17 04:10:01</t>
+          <t>2026-07-17 06:31:26</t>
         </is>
       </c>
     </row>
@@ -11748,7 +11748,7 @@
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-07-17 04:10:01</t>
+          <t>2026-07-17 06:31:26</t>
         </is>
       </c>
     </row>
@@ -11779,13 +11779,13 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="G45" t="n">
         <v>2.68</v>
       </c>
       <c r="H45" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="I45" t="n">
         <v>4.9</v>
@@ -11794,7 +11794,7 @@
         <v>2.36</v>
       </c>
       <c r="K45" t="n">
-        <v>5.3</v>
+        <v>4.8</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
@@ -11812,7 +11812,7 @@
         <v>1.45</v>
       </c>
       <c r="Q45" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="R45" t="n">
         <v>0</v>
@@ -12002,7 +12002,7 @@
       </c>
       <c r="CB45" t="inlineStr">
         <is>
-          <t>2026-07-17 04:10:01</t>
+          <t>2026-07-17 06:31:26</t>
         </is>
       </c>
     </row>
@@ -12256,7 +12256,7 @@
       </c>
       <c r="CB46" t="inlineStr">
         <is>
-          <t>2026-07-17 04:10:01</t>
+          <t>2026-07-17 06:31:26</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-19.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-19.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB46"/>
+  <dimension ref="A1:CB44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -869,13 +869,13 @@
         <v>2.16</v>
       </c>
       <c r="J2" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="K2" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L2" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="M2" t="n">
         <v>1.07</v>
@@ -884,13 +884,13 @@
         <v>3.85</v>
       </c>
       <c r="O2" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="P2" t="n">
         <v>1.96</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="R2" t="n">
         <v>1.36</v>
@@ -899,16 +899,16 @@
         <v>3.2</v>
       </c>
       <c r="T2" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="U2" t="n">
-        <v>2.12</v>
+        <v>1.93</v>
       </c>
       <c r="V2" t="n">
         <v>1.86</v>
       </c>
       <c r="W2" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="X2" t="n">
         <v>16</v>
@@ -935,10 +935,10 @@
         <v>23</v>
       </c>
       <c r="AF2" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AG2" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AH2" t="n">
         <v>18.5</v>
@@ -953,7 +953,7 @@
         <v>50</v>
       </c>
       <c r="AL2" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AM2" t="n">
         <v>120</v>
@@ -1001,7 +1001,7 @@
         <v>25</v>
       </c>
       <c r="BB2" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BC2" t="n">
         <v>30</v>
@@ -1010,77 +1010,77 @@
         <v>36</v>
       </c>
       <c r="BE2" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF2" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BG2" t="n">
         <v>11</v>
       </c>
       <c r="BH2" t="n">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="BI2" t="n">
-        <v>1.01</v>
+        <v>2.78</v>
       </c>
       <c r="BJ2" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK2" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BL2" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="BM2" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BN2" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BP2" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BQ2" t="n">
-        <v>1.01</v>
+        <v>23</v>
       </c>
       <c r="BR2" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BS2" t="n">
-        <v>1.01</v>
+        <v>29</v>
       </c>
       <c r="BT2" t="n">
-        <v>1000</v>
+        <v>5.7</v>
       </c>
       <c r="BU2" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BV2" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="BW2" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BX2" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BZ2" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="CA2" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-17 06:31:26</t>
+          <t>2026-07-17 08:55:20</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
         <v>1.63</v>
       </c>
       <c r="G3" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="H3" t="n">
         <v>6.4</v>
@@ -1129,212 +1129,212 @@
         <v>4.2</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="P3" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>280</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>230</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AO3" t="n">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BG3" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="BH3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-17 06:31:26</t>
+          <t>2026-07-17 08:55:20</t>
         </is>
       </c>
     </row>
@@ -1383,212 +1383,212 @@
         <v>3.9</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="P4" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.04</v>
+        <v>2.2</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="AO4" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AP4" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AU4" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AV4" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW4" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AX4" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AY4" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="BA4" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="BG4" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="BH4" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="BI4" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BK4" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="BL4" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="BM4" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BN4" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BO4" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="BP4" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BR4" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="BS4" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BT4" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BU4" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="BV4" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BW4" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX4" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BY4" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="CA4" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-17 06:31:26</t>
+          <t>2026-07-17 08:55:20</t>
         </is>
       </c>
     </row>
@@ -1628,7 +1628,7 @@
         <v>4.6</v>
       </c>
       <c r="I5" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="J5" t="n">
         <v>3.55</v>
@@ -1637,16 +1637,16 @@
         <v>4.5</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="P5" t="n">
         <v>1.87</v>
@@ -1655,184 +1655,184 @@
         <v>1.95</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AO5" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AU5" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AW5" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AX5" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AY5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BA5" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BD5" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="BF5" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BG5" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="BH5" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="BI5" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BK5" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="BL5" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="BM5" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BN5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BO5" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BP5" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BR5" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BS5" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BT5" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="BU5" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BV5" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BW5" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BX5" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="BY5" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BZ5" t="n">
         <v>0</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-17 06:31:26</t>
+          <t>2026-07-17 08:55:20</t>
         </is>
       </c>
     </row>
@@ -1891,16 +1891,16 @@
         <v>4.2</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="P6" t="n">
         <v>1.87</v>
@@ -1909,184 +1909,184 @@
         <v>1.93</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AN6" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AO6" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AP6" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AS6" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU6" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AV6" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AW6" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AX6" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AY6" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BA6" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BC6" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="BD6" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BE6" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="BF6" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BG6" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="BH6" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="BI6" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BK6" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="BL6" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="BM6" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BN6" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="BO6" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BP6" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="BQ6" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="BR6" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BS6" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="BT6" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BU6" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BV6" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="BW6" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BX6" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BY6" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="BZ6" t="n">
         <v>0</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-17 06:31:26</t>
+          <t>2026-07-17 08:55:20</t>
         </is>
       </c>
     </row>
@@ -2142,19 +2142,19 @@
         <v>3.3</v>
       </c>
       <c r="K7" t="n">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="P7" t="n">
         <v>1.82</v>
@@ -2163,184 +2163,184 @@
         <v>1.98</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AO7" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AP7" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AS7" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AT7" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU7" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AV7" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW7" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AX7" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AY7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="BD7" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BE7" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="BF7" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="BG7" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="BH7" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="BI7" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="BK7" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BL7" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="BM7" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BN7" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="BO7" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BP7" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="BQ7" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="BR7" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="BS7" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="BT7" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BU7" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BV7" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="BW7" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BX7" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BY7" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="BZ7" t="n">
         <v>0</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-17 06:31:26</t>
+          <t>2026-07-17 08:55:20</t>
         </is>
       </c>
     </row>
@@ -2399,16 +2399,16 @@
         <v>6.2</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="P8" t="n">
         <v>2.12</v>
@@ -2417,184 +2417,184 @@
         <v>1.61</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AO8" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="AP8" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AR8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT8" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AU8" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX8" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AY8" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="BA8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BD8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF8" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BG8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH8" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BI8" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BK8" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BL8" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="BM8" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BN8" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BO8" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BP8" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BQ8" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BR8" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="BS8" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="BT8" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BU8" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="BV8" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="BW8" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BX8" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="BY8" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="BZ8" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-17 06:31:26</t>
+          <t>2026-07-17 08:55:20</t>
         </is>
       </c>
     </row>
@@ -2653,212 +2653,212 @@
         <v>1000</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P9" t="n">
         <v>1.24</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-17 06:31:26</t>
+          <t>2026-07-17 08:55:20</t>
         </is>
       </c>
     </row>
@@ -2895,7 +2895,7 @@
         <v>1.65</v>
       </c>
       <c r="H10" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="I10" t="n">
         <v>6.2</v>
@@ -2907,212 +2907,212 @@
         <v>5.2</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="P10" t="n">
         <v>2.72</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AL10" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AN10" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AO10" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AP10" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AR10" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AS10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AT10" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AU10" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV10" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AW10" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AX10" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY10" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BB10" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BC10" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="BD10" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="BE10" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BF10" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BG10" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BH10" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="BI10" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BK10" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="BL10" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="BM10" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BN10" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="BO10" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="BP10" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BQ10" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="BR10" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BS10" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="BT10" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BU10" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="BV10" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="BW10" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="BX10" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="BY10" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="BZ10" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="CA10" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-17 06:31:26</t>
+          <t>2026-07-17 08:55:20</t>
         </is>
       </c>
     </row>
@@ -3161,212 +3161,212 @@
         <v>1000</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P11" t="n">
         <v>1.24</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-17 06:31:26</t>
+          <t>2026-07-17 08:55:20</t>
         </is>
       </c>
     </row>
@@ -3415,212 +3415,212 @@
         <v>1000</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P12" t="n">
         <v>1.24</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-17 06:31:26</t>
+          <t>2026-07-17 08:55:20</t>
         </is>
       </c>
     </row>
@@ -3669,212 +3669,212 @@
         <v>1000</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P13" t="n">
         <v>1.24</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-17 06:31:26</t>
+          <t>2026-07-17 08:55:20</t>
         </is>
       </c>
     </row>
@@ -3923,212 +3923,212 @@
         <v>1000</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P14" t="n">
         <v>1.24</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-17 06:31:26</t>
+          <t>2026-07-17 08:55:20</t>
         </is>
       </c>
     </row>
@@ -4177,212 +4177,212 @@
         <v>1000</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P15" t="n">
         <v>1.24</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-17 06:31:26</t>
+          <t>2026-07-17 08:55:20</t>
         </is>
       </c>
     </row>
@@ -4636,14 +4636,14 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-17 06:31:26</t>
+          <t>2026-07-17 08:55:20</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Swedish Superettan</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -4658,31 +4658,31 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>United IK Nordic</t>
+          <t>Central Espanol</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Orebro</t>
+          <t>Cerro Largo FC</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.85</v>
+        <v>2.84</v>
       </c>
       <c r="G17" t="n">
-        <v>2</v>
+        <v>3.3</v>
       </c>
       <c r="H17" t="n">
-        <v>4</v>
+        <v>2.7</v>
       </c>
       <c r="I17" t="n">
-        <v>4.6</v>
+        <v>3.15</v>
       </c>
       <c r="J17" t="n">
-        <v>3.7</v>
+        <v>2.96</v>
       </c>
       <c r="K17" t="n">
-        <v>4.3</v>
+        <v>3.55</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -4697,10 +4697,10 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2.18</v>
+        <v>1.52</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.73</v>
+        <v>2.36</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-17 06:31:26</t>
+          <t>2026-07-17 08:55:20</t>
         </is>
       </c>
     </row>
@@ -4912,31 +4912,31 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Varnamo</t>
+          <t>United IK Nordic</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Orebro</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.74</v>
+        <v>1.85</v>
       </c>
       <c r="G18" t="n">
-        <v>3.1</v>
+        <v>2</v>
       </c>
       <c r="H18" t="n">
-        <v>2.44</v>
+        <v>4</v>
       </c>
       <c r="I18" t="n">
-        <v>2.74</v>
+        <v>4.6</v>
       </c>
       <c r="J18" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="K18" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -4951,10 +4951,10 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -5144,14 +5144,14 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-17 06:31:26</t>
+          <t>2026-07-17 08:55:20</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Swedish Superettan</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -5166,31 +5166,31 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Central Espanol</t>
+          <t>Varnamo</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Cerro Largo FC</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.82</v>
+        <v>2.74</v>
       </c>
       <c r="G19" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="H19" t="n">
-        <v>2.7</v>
+        <v>2.44</v>
       </c>
       <c r="I19" t="n">
-        <v>3.15</v>
+        <v>2.74</v>
       </c>
       <c r="J19" t="n">
-        <v>2.94</v>
+        <v>3.6</v>
       </c>
       <c r="K19" t="n">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -5205,10 +5205,10 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>1.52</v>
+        <v>2.12</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.54</v>
+        <v>1.71</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-17 06:31:26</t>
+          <t>2026-07-17 08:55:20</t>
         </is>
       </c>
     </row>
@@ -5652,14 +5652,14 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-17 06:31:26</t>
+          <t>2026-07-17 08:55:20</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Kazakhstan Premier League</t>
+          <t>Romanian Liga I</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -5674,31 +5674,31 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Irtysh Pavlodar</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>FC Astana</t>
+          <t>Farul Constanta</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -5713,10 +5713,10 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -5906,14 +5906,14 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-07-17 06:31:26</t>
+          <t>2026-07-17 08:55:20</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Romanian Liga I</t>
+          <t>Estonian Premier League</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -5928,31 +5928,31 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Farul Constanta</t>
+          <t>Nomme Kalju</t>
         </is>
       </c>
       <c r="F22" t="n">
         <v>2.06</v>
       </c>
       <c r="G22" t="n">
-        <v>2.18</v>
+        <v>1000</v>
       </c>
       <c r="H22" t="n">
-        <v>3.85</v>
+        <v>1.04</v>
       </c>
       <c r="I22" t="n">
-        <v>4.4</v>
+        <v>1.98</v>
       </c>
       <c r="J22" t="n">
-        <v>3.5</v>
+        <v>2.06</v>
       </c>
       <c r="K22" t="n">
-        <v>3.8</v>
+        <v>1000</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -5967,10 +5967,10 @@
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>1.91</v>
+        <v>1.24</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.93</v>
+        <v>1.01</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
@@ -6160,14 +6160,14 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-07-17 06:31:26</t>
+          <t>2026-07-17 08:55:20</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Estonian Premier League</t>
+          <t>Icelandic Urvalsdeild</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -6182,31 +6182,31 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>IBV</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Nomme Kalju</t>
+          <t>KA Akureyri</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -6414,14 +6414,14 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-07-17 06:31:26</t>
+          <t>2026-07-17 08:55:20</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Icelandic Urvalsdeild</t>
+          <t>Swedish Allsvenskan</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -6431,36 +6431,36 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>11:00:00</t>
+          <t>11:30:00</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>IBV</t>
+          <t>Halmstads</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>KA Akureyri</t>
+          <t>Hacken</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -6475,10 +6475,10 @@
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>1.24</v>
+        <v>2.64</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-07-17 06:31:26</t>
+          <t>2026-07-17 08:55:20</t>
         </is>
       </c>
     </row>
@@ -6690,50 +6690,50 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Halmstads</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Hacken</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>5.7</v>
+        <v>3.7</v>
       </c>
       <c r="G25" t="n">
-        <v>6.2</v>
+        <v>3.85</v>
       </c>
       <c r="H25" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="I25" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J25" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K25" t="n">
+        <v>4</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="Q25" t="n">
         <v>1.6</v>
       </c>
-      <c r="I25" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="J25" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="K25" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>1.52</v>
-      </c>
       <c r="R25" t="n">
         <v>0</v>
       </c>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-07-17 06:31:26</t>
+          <t>2026-07-17 08:55:20</t>
         </is>
       </c>
     </row>
@@ -6944,31 +6944,31 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>3.65</v>
+        <v>1.28</v>
       </c>
       <c r="G26" t="n">
-        <v>3.85</v>
+        <v>1.33</v>
       </c>
       <c r="H26" t="n">
-        <v>2.04</v>
+        <v>11.5</v>
       </c>
       <c r="I26" t="n">
-        <v>2.1</v>
+        <v>14</v>
       </c>
       <c r="J26" t="n">
-        <v>3.9</v>
+        <v>6.4</v>
       </c>
       <c r="K26" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -6983,10 +6983,10 @@
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>2.32</v>
+        <v>2.52</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.6</v>
+        <v>1.54</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -7176,14 +7176,14 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-07-17 06:31:26</t>
+          <t>2026-07-17 08:55:20</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Swedish Allsvenskan</t>
+          <t>Bolivian Liga de Futbol Profesional</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -7193,36 +7193,36 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>11:30:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>CD Gualberto Villarroel</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.28</v>
+        <v>1.85</v>
       </c>
       <c r="G27" t="n">
-        <v>1.33</v>
+        <v>1000</v>
       </c>
       <c r="H27" t="n">
-        <v>11.5</v>
+        <v>1.04</v>
       </c>
       <c r="I27" t="n">
-        <v>14</v>
+        <v>2.22</v>
       </c>
       <c r="J27" t="n">
-        <v>6.4</v>
+        <v>1.85</v>
       </c>
       <c r="K27" t="n">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -7237,10 +7237,10 @@
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>2.52</v>
+        <v>1.24</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.54</v>
+        <v>1.01</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -7430,14 +7430,14 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-07-17 06:31:26</t>
+          <t>2026-07-17 08:55:20</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Bolivian Liga de Futbol Profesional</t>
+          <t>Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -7452,28 +7452,28 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>CD Gualberto Villarroel</t>
+          <t>FC Ordabasy</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Elimai FC</t>
         </is>
       </c>
       <c r="F28" t="n">
         <v>1.04</v>
       </c>
       <c r="G28" t="n">
-        <v>1000</v>
+        <v>1.79</v>
       </c>
       <c r="H28" t="n">
-        <v>1.04</v>
+        <v>2.3</v>
       </c>
       <c r="I28" t="n">
         <v>1000</v>
       </c>
       <c r="J28" t="n">
-        <v>1.02</v>
+        <v>2.3</v>
       </c>
       <c r="K28" t="n">
         <v>1000</v>
@@ -7684,14 +7684,14 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-07-17 06:31:26</t>
+          <t>2026-07-17 08:55:20</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Kazakhstan Premier League</t>
+          <t>Finnish Veikkausliiga</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -7701,36 +7701,36 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>12:00:00</t>
+          <t>12:30:00</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>FC Ordabasy</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Elimai FC</t>
+          <t>FC Inter</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="G29" t="n">
-        <v>1.79</v>
+        <v>7</v>
       </c>
       <c r="H29" t="n">
-        <v>2.3</v>
+        <v>1.55</v>
       </c>
       <c r="I29" t="n">
-        <v>1000</v>
+        <v>1.66</v>
       </c>
       <c r="J29" t="n">
-        <v>2.3</v>
+        <v>4.2</v>
       </c>
       <c r="K29" t="n">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -7745,10 +7745,10 @@
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>1.24</v>
+        <v>2.18</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.01</v>
+        <v>1.71</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -7938,14 +7938,14 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-07-17 06:31:26</t>
+          <t>2026-07-17 08:55:20</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Finnish Veikkausliiga</t>
+          <t>Lithuanian A Lyga</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -7955,36 +7955,36 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>12:30:00</t>
+          <t>12:45:00</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>FC Dziugas</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>FC Inter</t>
+          <t>FK Banga Gargzdu</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>6</v>
+        <v>1.04</v>
       </c>
       <c r="G30" t="n">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="H30" t="n">
-        <v>1.55</v>
+        <v>1.04</v>
       </c>
       <c r="I30" t="n">
-        <v>1.66</v>
+        <v>1000</v>
       </c>
       <c r="J30" t="n">
-        <v>4.2</v>
+        <v>1.02</v>
       </c>
       <c r="K30" t="n">
-        <v>4.8</v>
+        <v>1000</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
@@ -7999,10 +7999,10 @@
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>2.18</v>
+        <v>1.24</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.71</v>
+        <v>1.01</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -8192,14 +8192,14 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-07-17 06:31:26</t>
+          <t>2026-07-17 08:55:20</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lithuanian A Lyga</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -8209,42 +8209,42 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>12:45:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>FC Dziugas</t>
+          <t>Cerro</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>FK Banga Gargzdu</t>
+          <t>Racing Club (Uru)</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="G31" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="H31" t="n">
-        <v>1.04</v>
+        <v>1.76</v>
       </c>
       <c r="I31" t="n">
-        <v>1000</v>
+        <v>1.82</v>
       </c>
       <c r="J31" t="n">
-        <v>1.02</v>
+        <v>3.5</v>
       </c>
       <c r="K31" t="n">
-        <v>1000</v>
+        <v>3.65</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="N31" t="n">
         <v>0</v>
@@ -8253,10 +8253,10 @@
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>1.24</v>
+        <v>1.52</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.01</v>
+        <v>2.68</v>
       </c>
       <c r="R31" t="n">
         <v>0</v>
@@ -8277,112 +8277,112 @@
         <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AI31" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0</v>
+        <v>280</v>
       </c>
       <c r="AK31" t="n">
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="AL31" t="n">
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="AM31" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="AN31" t="n">
-        <v>0</v>
+        <v>330</v>
       </c>
       <c r="AO31" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AP31" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AR31" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AS31" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AT31" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AU31" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AV31" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AW31" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AX31" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AY31" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AZ31" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="BA31" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BB31" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BC31" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BD31" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BE31" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BF31" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BG31" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BH31" t="n">
         <v>0</v>
@@ -8446,14 +8446,14 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-07-17 06:31:26</t>
+          <t>2026-07-17 08:55:20</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Slovenian Premier League</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -8468,37 +8468,37 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Cerro</t>
+          <t>NK Aluminij</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Racing Club (Uru)</t>
+          <t>NK Maribor</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>5.7</v>
+        <v>4.3</v>
       </c>
       <c r="G32" t="n">
-        <v>6.6</v>
+        <v>5.1</v>
       </c>
       <c r="H32" t="n">
-        <v>1.77</v>
+        <v>1.69</v>
       </c>
       <c r="I32" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="J32" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="K32" t="n">
-        <v>3.65</v>
+        <v>5.1</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
         <v>0</v>
@@ -8507,10 +8507,10 @@
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>1.52</v>
+        <v>2.64</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.68</v>
+        <v>1.48</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -8531,112 +8531,112 @@
         <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="AF32" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="AG32" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AH32" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AI32" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="AJ32" t="n">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="AK32" t="n">
-        <v>170</v>
+        <v>0</v>
       </c>
       <c r="AL32" t="n">
-        <v>190</v>
+        <v>0</v>
       </c>
       <c r="AM32" t="n">
-        <v>340</v>
+        <v>0</v>
       </c>
       <c r="AN32" t="n">
-        <v>320</v>
+        <v>0</v>
       </c>
       <c r="AO32" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="AP32" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="AQ32" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AR32" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="AS32" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AT32" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AU32" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="AV32" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AW32" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="AX32" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AY32" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="AZ32" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="BA32" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="BB32" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="BC32" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="BD32" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="BE32" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="BF32" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="BG32" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="BH32" t="n">
         <v>0</v>
@@ -8700,14 +8700,14 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-07-17 06:31:26</t>
+          <t>2026-07-17 08:55:20</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Slovenian Premier League</t>
+          <t>Peruvian Primera Division</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -8722,31 +8722,31 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NK Aluminij</t>
+          <t>CD Los Chankas</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>NK Maribor</t>
+          <t>Sport Boys (Per)</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
@@ -8761,10 +8761,10 @@
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>2.64</v>
+        <v>1.24</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.48</v>
+        <v>1.01</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
@@ -8954,14 +8954,14 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-07-17 06:31:26</t>
+          <t>2026-07-17 08:55:20</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Peruvian Primera Division</t>
+          <t>Lithuanian A Lyga</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -8976,31 +8976,31 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>CD Los Chankas</t>
+          <t>VMFD Zalgiris</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Sport Boys (Per)</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="I34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="K34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
@@ -9208,14 +9208,14 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-07-17 06:31:26</t>
+          <t>2026-07-17 08:55:20</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Latvian Virsliga</t>
+          <t>Estonian Premier League</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -9230,12 +9230,12 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>FK Auda</t>
+          <t>Harju JK Laagri</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Liepajas Metalurgs</t>
+          <t>Paide Linnameeskond</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -9269,7 +9269,7 @@
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>1.07</v>
+        <v>1.24</v>
       </c>
       <c r="Q35" t="n">
         <v>1.01</v>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-07-17 06:31:26</t>
+          <t>2026-07-17 08:55:20</t>
         </is>
       </c>
     </row>
@@ -9716,14 +9716,14 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-07-17 06:31:26</t>
+          <t>2026-07-17 08:55:20</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Estonian Premier League</t>
+          <t>Bulgarian A League</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -9733,36 +9733,36 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>13:30:00</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Harju JK Laagri</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Paide Linnameeskond</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>1.04</v>
+        <v>2.78</v>
       </c>
       <c r="G37" t="n">
-        <v>1000</v>
+        <v>3.1</v>
       </c>
       <c r="H37" t="n">
-        <v>1.04</v>
+        <v>2.9</v>
       </c>
       <c r="I37" t="n">
-        <v>1000</v>
+        <v>3.25</v>
       </c>
       <c r="J37" t="n">
-        <v>1.02</v>
+        <v>2.8</v>
       </c>
       <c r="K37" t="n">
-        <v>1000</v>
+        <v>3.25</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
@@ -9777,10 +9777,10 @@
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>1.24</v>
+        <v>1.5</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.01</v>
+        <v>2.6</v>
       </c>
       <c r="R37" t="n">
         <v>0</v>
@@ -9970,14 +9970,14 @@
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-07-17 06:31:26</t>
+          <t>2026-07-17 08:55:20</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Lithuanian A Lyga</t>
+          <t>Romanian Liga I</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -9987,36 +9987,36 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>13:30:00</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VMFD Zalgiris</t>
+          <t>ACS Petrolul 52</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Dinamo Bucharest</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>1.04</v>
+        <v>3.9</v>
       </c>
       <c r="G38" t="n">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="H38" t="n">
-        <v>1.04</v>
+        <v>2.08</v>
       </c>
       <c r="I38" t="n">
-        <v>1000</v>
+        <v>2.18</v>
       </c>
       <c r="J38" t="n">
-        <v>1.02</v>
+        <v>3.15</v>
       </c>
       <c r="K38" t="n">
-        <v>1000</v>
+        <v>3.5</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
@@ -10031,10 +10031,10 @@
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>1.24</v>
+        <v>1.65</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.01</v>
+        <v>2.24</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
@@ -10224,14 +10224,14 @@
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-07-17 06:31:26</t>
+          <t>2026-07-17 08:55:20</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Bulgarian A League</t>
+          <t>Ecuadorian Serie A</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -10241,36 +10241,36 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>13:30:00</t>
+          <t>13:45:00</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Tecnico Universitario</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Aucas</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>2.76</v>
+        <v>2.96</v>
       </c>
       <c r="G39" t="n">
-        <v>3.15</v>
+        <v>4.6</v>
       </c>
       <c r="H39" t="n">
-        <v>2.88</v>
+        <v>2.32</v>
       </c>
       <c r="I39" t="n">
-        <v>3.25</v>
+        <v>2.96</v>
       </c>
       <c r="J39" t="n">
-        <v>2.78</v>
+        <v>2.24</v>
       </c>
       <c r="K39" t="n">
-        <v>3.25</v>
+        <v>4.4</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
@@ -10285,10 +10285,10 @@
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.6</v>
+        <v>2.26</v>
       </c>
       <c r="R39" t="n">
         <v>0</v>
@@ -10478,14 +10478,14 @@
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-07-17 06:31:26</t>
+          <t>2026-07-17 08:55:20</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Romanian Liga I</t>
+          <t>Serbian Super League</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -10495,36 +10495,36 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>13:30:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>ACS Petrolul 52</t>
+          <t>Cukaricki</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Dinamo Bucharest</t>
+          <t>FK IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>3.85</v>
+        <v>1.04</v>
       </c>
       <c r="G40" t="n">
-        <v>4.5</v>
+        <v>1000</v>
       </c>
       <c r="H40" t="n">
-        <v>2.08</v>
+        <v>1.04</v>
       </c>
       <c r="I40" t="n">
-        <v>2.28</v>
+        <v>1000</v>
       </c>
       <c r="J40" t="n">
-        <v>3.1</v>
+        <v>1.02</v>
       </c>
       <c r="K40" t="n">
-        <v>3.5</v>
+        <v>1000</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
@@ -10539,10 +10539,10 @@
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>1.65</v>
+        <v>1.07</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.24</v>
+        <v>1.01</v>
       </c>
       <c r="R40" t="n">
         <v>0</v>
@@ -10732,14 +10732,14 @@
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-07-17 06:31:26</t>
+          <t>2026-07-17 08:55:20</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>Serbian Super League</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -10749,36 +10749,36 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>13:45:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Tecnico Universitario</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Aucas</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>2.94</v>
+        <v>1.49</v>
       </c>
       <c r="G41" t="n">
-        <v>4.6</v>
+        <v>1.88</v>
       </c>
       <c r="H41" t="n">
-        <v>2.32</v>
+        <v>2.18</v>
       </c>
       <c r="I41" t="n">
-        <v>2.96</v>
+        <v>1000</v>
       </c>
       <c r="J41" t="n">
-        <v>2.24</v>
+        <v>2.18</v>
       </c>
       <c r="K41" t="n">
-        <v>4.4</v>
+        <v>1000</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
@@ -10793,10 +10793,10 @@
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>1.51</v>
+        <v>1.96</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.26</v>
+        <v>1.58</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -10986,7 +10986,7 @@
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-07-17 06:31:26</t>
+          <t>2026-07-17 08:55:20</t>
         </is>
       </c>
     </row>
@@ -11008,31 +11008,31 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Cukaricki</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>FK IMT Novi Beograd</t>
+          <t>Mladost Lucani</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>1.04</v>
+        <v>1.9</v>
       </c>
       <c r="G42" t="n">
-        <v>1000</v>
+        <v>2.14</v>
       </c>
       <c r="H42" t="n">
-        <v>1.04</v>
+        <v>3.8</v>
       </c>
       <c r="I42" t="n">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="J42" t="n">
-        <v>1.02</v>
+        <v>3.15</v>
       </c>
       <c r="K42" t="n">
-        <v>1000</v>
+        <v>3.7</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
@@ -11047,10 +11047,10 @@
         <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>1.07</v>
+        <v>1.68</v>
       </c>
       <c r="Q42" t="n">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="R42" t="n">
         <v>0</v>
@@ -11240,14 +11240,14 @@
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-07-17 06:31:26</t>
+          <t>2026-07-17 08:55:20</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Serbian Super League</t>
+          <t>Ecuadorian Serie A</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -11257,36 +11257,36 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>18:45:00</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Guayaquil City</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>1.49</v>
+        <v>2.1</v>
       </c>
       <c r="G43" t="n">
-        <v>1.88</v>
+        <v>2.68</v>
       </c>
       <c r="H43" t="n">
-        <v>2.18</v>
+        <v>3.2</v>
       </c>
       <c r="I43" t="n">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="J43" t="n">
-        <v>2.18</v>
+        <v>2.36</v>
       </c>
       <c r="K43" t="n">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
@@ -11301,10 +11301,10 @@
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>1.96</v>
+        <v>1.45</v>
       </c>
       <c r="Q43" t="n">
-        <v>1.58</v>
+        <v>2.22</v>
       </c>
       <c r="R43" t="n">
         <v>0</v>
@@ -11494,14 +11494,14 @@
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-07-17 06:31:26</t>
+          <t>2026-07-17 08:55:20</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Serbian Super League</t>
+          <t>Brazilian Serie D</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -11511,36 +11511,36 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>America RN</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Mladost Lucani</t>
+          <t>Gama</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>1.9</v>
+        <v>1.02</v>
       </c>
       <c r="G44" t="n">
-        <v>2.14</v>
+        <v>1000</v>
       </c>
       <c r="H44" t="n">
-        <v>3.8</v>
+        <v>1.02</v>
       </c>
       <c r="I44" t="n">
-        <v>5.6</v>
+        <v>1000</v>
       </c>
       <c r="J44" t="n">
-        <v>3.15</v>
+        <v>1.02</v>
       </c>
       <c r="K44" t="n">
-        <v>3.7</v>
+        <v>1000</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
@@ -11555,10 +11555,10 @@
         <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>1.68</v>
+        <v>1.24</v>
       </c>
       <c r="Q44" t="n">
-        <v>2.04</v>
+        <v>1.01</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
@@ -11748,515 +11748,7 @@
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-07-17 06:31:26</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Ecuadorian Serie A</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>18:45:00</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>Guayaquil City</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>Manta FC</t>
-        </is>
-      </c>
-      <c r="F45" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="G45" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="H45" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="I45" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="J45" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="K45" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="L45" t="n">
-        <v>0</v>
-      </c>
-      <c r="M45" t="n">
-        <v>0</v>
-      </c>
-      <c r="N45" t="n">
-        <v>0</v>
-      </c>
-      <c r="O45" t="n">
-        <v>0</v>
-      </c>
-      <c r="P45" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="R45" t="n">
-        <v>0</v>
-      </c>
-      <c r="S45" t="n">
-        <v>0</v>
-      </c>
-      <c r="T45" t="n">
-        <v>0</v>
-      </c>
-      <c r="U45" t="n">
-        <v>0</v>
-      </c>
-      <c r="V45" t="n">
-        <v>0</v>
-      </c>
-      <c r="W45" t="n">
-        <v>0</v>
-      </c>
-      <c r="X45" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y45" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ45" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA45" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB45" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC45" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD45" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE45" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF45" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG45" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH45" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI45" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ45" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK45" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL45" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM45" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN45" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO45" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP45" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ45" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR45" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS45" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT45" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU45" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV45" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW45" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX45" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY45" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ45" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA45" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB45" t="inlineStr">
-        <is>
-          <t>2026-07-17 06:31:26</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Brazilian Serie D</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>19:00:00</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>America RN</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>Gama</t>
-        </is>
-      </c>
-      <c r="F46" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="G46" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H46" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="I46" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J46" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="K46" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L46" t="n">
-        <v>0</v>
-      </c>
-      <c r="M46" t="n">
-        <v>0</v>
-      </c>
-      <c r="N46" t="n">
-        <v>0</v>
-      </c>
-      <c r="O46" t="n">
-        <v>0</v>
-      </c>
-      <c r="P46" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R46" t="n">
-        <v>0</v>
-      </c>
-      <c r="S46" t="n">
-        <v>0</v>
-      </c>
-      <c r="T46" t="n">
-        <v>0</v>
-      </c>
-      <c r="U46" t="n">
-        <v>0</v>
-      </c>
-      <c r="V46" t="n">
-        <v>0</v>
-      </c>
-      <c r="W46" t="n">
-        <v>0</v>
-      </c>
-      <c r="X46" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y46" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ46" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA46" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB46" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC46" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD46" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE46" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF46" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG46" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH46" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI46" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ46" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK46" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL46" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM46" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN46" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO46" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP46" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ46" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR46" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS46" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT46" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU46" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV46" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW46" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX46" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY46" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ46" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA46" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB46" t="inlineStr">
-        <is>
-          <t>2026-07-17 06:31:26</t>
+          <t>2026-07-17 08:55:20</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-19.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-19.xlsx
@@ -866,7 +866,7 @@
         <v>2.02</v>
       </c>
       <c r="I2" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="J2" t="n">
         <v>3.55</v>
@@ -896,13 +896,13 @@
         <v>1.36</v>
       </c>
       <c r="S2" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="T2" t="n">
         <v>1.74</v>
       </c>
       <c r="U2" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="V2" t="n">
         <v>1.86</v>
@@ -1022,7 +1022,7 @@
         <v>4.1</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.78</v>
+        <v>3.05</v>
       </c>
       <c r="BJ2" t="n">
         <v>11.5</v>
@@ -1043,7 +1043,7 @@
         <v>5.5</v>
       </c>
       <c r="BP2" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="BQ2" t="n">
         <v>23</v>
@@ -1055,7 +1055,7 @@
         <v>29</v>
       </c>
       <c r="BT2" t="n">
-        <v>5.7</v>
+        <v>5.1</v>
       </c>
       <c r="BU2" t="n">
         <v>3.75</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-17 08:55:20</t>
+          <t>2026-07-17 11:19:35</t>
         </is>
       </c>
     </row>
@@ -1111,28 +1111,28 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="G3" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="H3" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="I3" t="n">
         <v>7.4</v>
       </c>
       <c r="J3" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K3" t="n">
         <v>4.2</v>
       </c>
       <c r="L3" t="n">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="M3" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N3" t="n">
         <v>3.15</v>
@@ -1141,10 +1141,10 @@
         <v>1.41</v>
       </c>
       <c r="P3" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="R3" t="n">
         <v>1.26</v>
@@ -1156,22 +1156,22 @@
         <v>2.12</v>
       </c>
       <c r="U3" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="V3" t="n">
         <v>1.16</v>
       </c>
       <c r="W3" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="X3" t="n">
         <v>12.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Z3" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AA3" t="n">
         <v>280</v>
@@ -1180,7 +1180,7 @@
         <v>7</v>
       </c>
       <c r="AC3" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD3" t="n">
         <v>32</v>
@@ -1225,10 +1225,10 @@
         <v>15</v>
       </c>
       <c r="AR3" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AS3" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AT3" t="n">
         <v>6</v>
@@ -1240,7 +1240,7 @@
         <v>19</v>
       </c>
       <c r="AW3" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AX3" t="n">
         <v>7.8</v>
@@ -1252,25 +1252,25 @@
         <v>18.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BB3" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BC3" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BD3" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BE3" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BF3" t="n">
         <v>11</v>
       </c>
       <c r="BG3" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BH3" t="n">
         <v>1000</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-17 08:55:20</t>
+          <t>2026-07-17 11:19:35</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
         <v>3.9</v>
       </c>
       <c r="L4" t="n">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="M4" t="n">
         <v>1.09</v>
@@ -1395,7 +1395,7 @@
         <v>1.41</v>
       </c>
       <c r="P4" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="Q4" t="n">
         <v>2.2</v>
@@ -1437,7 +1437,7 @@
         <v>9.6</v>
       </c>
       <c r="AD4" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AE4" t="n">
         <v>25</v>
@@ -1473,25 +1473,25 @@
         <v>17.5</v>
       </c>
       <c r="AP4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AQ4" t="n">
         <v>6.4</v>
       </c>
       <c r="AR4" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS4" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AT4" t="n">
         <v>12</v>
       </c>
       <c r="AU4" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AV4" t="n">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AW4" t="n">
         <v>16.5</v>
@@ -1500,31 +1500,31 @@
         <v>4.9</v>
       </c>
       <c r="AY4" t="n">
-        <v>19.5</v>
+        <v>16.5</v>
       </c>
       <c r="AZ4" t="n">
         <v>18</v>
       </c>
       <c r="BA4" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BB4" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BC4" t="n">
         <v>5.2</v>
       </c>
-      <c r="BC4" t="n">
-        <v>5.1</v>
-      </c>
       <c r="BD4" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BE4" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BF4" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BG4" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BH4" t="n">
         <v>3.45</v>
@@ -1536,31 +1536,31 @@
         <v>13</v>
       </c>
       <c r="BK4" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="BL4" t="n">
         <v>210</v>
       </c>
       <c r="BM4" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BN4" t="n">
         <v>10.5</v>
       </c>
       <c r="BO4" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BP4" t="n">
         <v>65</v>
       </c>
       <c r="BQ4" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BR4" t="n">
         <v>80</v>
       </c>
       <c r="BS4" t="n">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="BT4" t="n">
         <v>4.7</v>
@@ -1572,23 +1572,23 @@
         <v>15</v>
       </c>
       <c r="BW4" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BX4" t="n">
         <v>38</v>
       </c>
       <c r="BY4" t="n">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="BZ4" t="n">
         <v>34</v>
       </c>
       <c r="CA4" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-17 08:55:20</t>
+          <t>2026-07-17 11:19:35</t>
         </is>
       </c>
     </row>
@@ -1619,7 +1619,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="G5" t="n">
         <v>1.94</v>
@@ -1631,16 +1631,16 @@
         <v>5.5</v>
       </c>
       <c r="J5" t="n">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="K5" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="L5" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="M5" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N5" t="n">
         <v>3.5</v>
@@ -1733,10 +1733,10 @@
         <v>12.5</v>
       </c>
       <c r="AR5" t="n">
-        <v>28</v>
+        <v>1.01</v>
       </c>
       <c r="AS5" t="n">
-        <v>90</v>
+        <v>1.01</v>
       </c>
       <c r="AT5" t="n">
         <v>6.6</v>
@@ -1748,7 +1748,7 @@
         <v>15</v>
       </c>
       <c r="AW5" t="n">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="AX5" t="n">
         <v>8.6</v>
@@ -1760,7 +1760,7 @@
         <v>15</v>
       </c>
       <c r="BA5" t="n">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="BB5" t="n">
         <v>15.5</v>
@@ -1769,16 +1769,16 @@
         <v>15.5</v>
       </c>
       <c r="BD5" t="n">
-        <v>29</v>
+        <v>1.01</v>
       </c>
       <c r="BE5" t="n">
-        <v>85</v>
+        <v>1.01</v>
       </c>
       <c r="BF5" t="n">
         <v>10</v>
       </c>
       <c r="BG5" t="n">
-        <v>60</v>
+        <v>1.01</v>
       </c>
       <c r="BH5" t="n">
         <v>3.75</v>
@@ -1790,16 +1790,16 @@
         <v>12</v>
       </c>
       <c r="BK5" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="BL5" t="n">
         <v>160</v>
       </c>
       <c r="BM5" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BN5" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BO5" t="n">
         <v>3.6</v>
@@ -1808,31 +1808,31 @@
         <v>15</v>
       </c>
       <c r="BQ5" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BR5" t="n">
         <v>34</v>
       </c>
       <c r="BS5" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BT5" t="n">
         <v>9.4</v>
       </c>
       <c r="BU5" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BV5" t="n">
         <v>50</v>
       </c>
       <c r="BW5" t="n">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="BX5" t="n">
         <v>60</v>
       </c>
       <c r="BY5" t="n">
-        <v>38</v>
+        <v>1.01</v>
       </c>
       <c r="BZ5" t="n">
         <v>0</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-17 08:55:20</t>
+          <t>2026-07-17 11:19:35</t>
         </is>
       </c>
     </row>
@@ -1873,7 +1873,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="G6" t="n">
         <v>3.2</v>
@@ -1885,10 +1885,10 @@
         <v>2.84</v>
       </c>
       <c r="J6" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K6" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="L6" t="n">
         <v>1.36</v>
@@ -1900,13 +1900,13 @@
         <v>3.55</v>
       </c>
       <c r="O6" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="P6" t="n">
         <v>1.87</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="R6" t="n">
         <v>1.33</v>
@@ -1987,10 +1987,10 @@
         <v>8.4</v>
       </c>
       <c r="AR6" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AS6" t="n">
-        <v>29</v>
+        <v>1.01</v>
       </c>
       <c r="AT6" t="n">
         <v>9.199999999999999</v>
@@ -2002,7 +2002,7 @@
         <v>9.4</v>
       </c>
       <c r="AW6" t="n">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="AX6" t="n">
         <v>15.5</v>
@@ -2014,43 +2014,43 @@
         <v>13</v>
       </c>
       <c r="BA6" t="n">
-        <v>30</v>
+        <v>1.01</v>
       </c>
       <c r="BB6" t="n">
-        <v>34</v>
+        <v>1.01</v>
       </c>
       <c r="BC6" t="n">
-        <v>25</v>
+        <v>1.01</v>
       </c>
       <c r="BD6" t="n">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="BE6" t="n">
-        <v>65</v>
+        <v>1.01</v>
       </c>
       <c r="BF6" t="n">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="BG6" t="n">
         <v>18.5</v>
       </c>
       <c r="BH6" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="BJ6" t="n">
         <v>11</v>
       </c>
       <c r="BK6" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="BL6" t="n">
         <v>140</v>
       </c>
       <c r="BM6" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BN6" t="n">
         <v>6.8</v>
@@ -2062,16 +2062,16 @@
         <v>26</v>
       </c>
       <c r="BQ6" t="n">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="BR6" t="n">
         <v>40</v>
       </c>
       <c r="BS6" t="n">
-        <v>26</v>
+        <v>1.01</v>
       </c>
       <c r="BT6" t="n">
-        <v>6.4</v>
+        <v>5.8</v>
       </c>
       <c r="BU6" t="n">
         <v>4.4</v>
@@ -2080,13 +2080,13 @@
         <v>23</v>
       </c>
       <c r="BW6" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="BX6" t="n">
         <v>38</v>
       </c>
       <c r="BY6" t="n">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="BZ6" t="n">
         <v>0</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-17 08:55:20</t>
+          <t>2026-07-17 11:19:35</t>
         </is>
       </c>
     </row>
@@ -2130,7 +2130,7 @@
         <v>2.96</v>
       </c>
       <c r="G7" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="H7" t="n">
         <v>2.4</v>
@@ -2142,13 +2142,13 @@
         <v>3.3</v>
       </c>
       <c r="K7" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="L7" t="n">
         <v>1.35</v>
       </c>
       <c r="M7" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N7" t="n">
         <v>3.4</v>
@@ -2235,7 +2235,7 @@
         <v>29</v>
       </c>
       <c r="AP7" t="n">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ7" t="n">
         <v>7.6</v>
@@ -2244,7 +2244,7 @@
         <v>12</v>
       </c>
       <c r="AS7" t="n">
-        <v>26</v>
+        <v>1.01</v>
       </c>
       <c r="AT7" t="n">
         <v>8.800000000000001</v>
@@ -2268,28 +2268,28 @@
         <v>12.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>30</v>
+        <v>1.01</v>
       </c>
       <c r="BB7" t="n">
-        <v>38</v>
+        <v>1.01</v>
       </c>
       <c r="BC7" t="n">
-        <v>27</v>
+        <v>1.01</v>
       </c>
       <c r="BD7" t="n">
-        <v>34</v>
+        <v>1.01</v>
       </c>
       <c r="BE7" t="n">
-        <v>65</v>
+        <v>1.01</v>
       </c>
       <c r="BF7" t="n">
-        <v>25</v>
+        <v>1.01</v>
       </c>
       <c r="BG7" t="n">
         <v>17</v>
       </c>
       <c r="BH7" t="n">
-        <v>3.85</v>
+        <v>3.4</v>
       </c>
       <c r="BI7" t="n">
         <v>2.66</v>
@@ -2298,13 +2298,13 @@
         <v>11.5</v>
       </c>
       <c r="BK7" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BL7" t="n">
         <v>150</v>
       </c>
       <c r="BM7" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BN7" t="n">
         <v>7.4</v>
@@ -2316,13 +2316,13 @@
         <v>30</v>
       </c>
       <c r="BQ7" t="n">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="BR7" t="n">
         <v>46</v>
       </c>
       <c r="BS7" t="n">
-        <v>27</v>
+        <v>1.01</v>
       </c>
       <c r="BT7" t="n">
         <v>6.4</v>
@@ -2334,13 +2334,13 @@
         <v>23</v>
       </c>
       <c r="BW7" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="BX7" t="n">
         <v>40</v>
       </c>
       <c r="BY7" t="n">
-        <v>23</v>
+        <v>1.01</v>
       </c>
       <c r="BZ7" t="n">
         <v>0</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-17 08:55:20</t>
+          <t>2026-07-17 11:19:35</t>
         </is>
       </c>
     </row>
@@ -2390,13 +2390,13 @@
         <v>7.8</v>
       </c>
       <c r="I8" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="J8" t="n">
         <v>4.9</v>
       </c>
       <c r="K8" t="n">
-        <v>6.2</v>
+        <v>5.6</v>
       </c>
       <c r="L8" t="n">
         <v>1.28</v>
@@ -2429,7 +2429,7 @@
         <v>1.73</v>
       </c>
       <c r="V8" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="W8" t="n">
         <v>3</v>
@@ -2483,7 +2483,7 @@
         <v>170</v>
       </c>
       <c r="AN8" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AO8" t="n">
         <v>210</v>
@@ -2552,13 +2552,13 @@
         <v>13.5</v>
       </c>
       <c r="BK8" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BL8" t="n">
         <v>180</v>
       </c>
       <c r="BM8" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BN8" t="n">
         <v>4.6</v>
@@ -2570,31 +2570,31 @@
         <v>10.5</v>
       </c>
       <c r="BQ8" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BR8" t="n">
         <v>29</v>
       </c>
       <c r="BS8" t="n">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="BT8" t="n">
         <v>14</v>
       </c>
       <c r="BU8" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="BV8" t="n">
         <v>90</v>
       </c>
       <c r="BW8" t="n">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="BX8" t="n">
         <v>85</v>
       </c>
       <c r="BY8" t="n">
-        <v>48</v>
+        <v>1.01</v>
       </c>
       <c r="BZ8" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-17 08:55:20</t>
+          <t>2026-07-17 11:19:35</t>
         </is>
       </c>
     </row>
@@ -2647,7 +2647,7 @@
         <v>1000</v>
       </c>
       <c r="J9" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K9" t="n">
         <v>1000</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-17 08:55:20</t>
+          <t>2026-07-17 11:19:35</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
         <v>1.7</v>
       </c>
       <c r="S10" t="n">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="T10" t="n">
         <v>1.54</v>
@@ -2979,7 +2979,7 @@
         <v>65</v>
       </c>
       <c r="AJ10" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AK10" t="n">
         <v>17.5</v>
@@ -2991,22 +2991,22 @@
         <v>80</v>
       </c>
       <c r="AN10" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AO10" t="n">
         <v>60</v>
       </c>
       <c r="AP10" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="AQ10" t="n">
         <v>21</v>
       </c>
       <c r="AR10" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="AS10" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="AT10" t="n">
         <v>10</v>
@@ -3018,7 +3018,7 @@
         <v>17</v>
       </c>
       <c r="AW10" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="AX10" t="n">
         <v>9.800000000000001</v>
@@ -3027,10 +3027,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AZ10" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="BB10" t="n">
         <v>12.5</v>
@@ -3042,13 +3042,13 @@
         <v>19.5</v>
       </c>
       <c r="BE10" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BF10" t="n">
         <v>4.6</v>
       </c>
       <c r="BG10" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BH10" t="n">
         <v>5.4</v>
@@ -3060,13 +3060,13 @@
         <v>11</v>
       </c>
       <c r="BK10" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="BL10" t="n">
         <v>95</v>
       </c>
       <c r="BM10" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BN10" t="n">
         <v>5.3</v>
@@ -3078,41 +3078,41 @@
         <v>11</v>
       </c>
       <c r="BQ10" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BR10" t="n">
         <v>22</v>
       </c>
       <c r="BS10" t="n">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="BT10" t="n">
         <v>11</v>
       </c>
       <c r="BU10" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BV10" t="n">
         <v>46</v>
       </c>
       <c r="BW10" t="n">
-        <v>29</v>
+        <v>1.01</v>
       </c>
       <c r="BX10" t="n">
         <v>46</v>
       </c>
       <c r="BY10" t="n">
-        <v>29</v>
+        <v>1.01</v>
       </c>
       <c r="BZ10" t="n">
         <v>13.5</v>
       </c>
       <c r="CA10" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-17 08:55:20</t>
+          <t>2026-07-17 11:19:35</t>
         </is>
       </c>
     </row>
@@ -3155,7 +3155,7 @@
         <v>1000</v>
       </c>
       <c r="J11" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K11" t="n">
         <v>1000</v>
@@ -3191,10 +3191,10 @@
         <v>1.01</v>
       </c>
       <c r="V11" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W11" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X11" t="n">
         <v>1000</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-17 08:55:20</t>
+          <t>2026-07-17 11:19:35</t>
         </is>
       </c>
     </row>
@@ -3409,7 +3409,7 @@
         <v>1000</v>
       </c>
       <c r="J12" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K12" t="n">
         <v>1000</v>
@@ -3430,25 +3430,25 @@
         <v>1.24</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.02</v>
+        <v>1.42</v>
       </c>
       <c r="R12" t="n">
         <v>1.18</v>
       </c>
       <c r="S12" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V12" t="n">
         <v>1.02</v>
       </c>
-      <c r="T12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.01</v>
-      </c>
       <c r="W12" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X12" t="n">
         <v>1000</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-17 08:55:20</t>
+          <t>2026-07-17 11:19:35</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
         <v>1000</v>
       </c>
       <c r="J13" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K13" t="n">
         <v>1000</v>
@@ -3684,25 +3684,25 @@
         <v>1.24</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="R13" t="n">
         <v>1.18</v>
       </c>
       <c r="S13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V13" t="n">
         <v>1.02</v>
       </c>
-      <c r="T13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.01</v>
-      </c>
       <c r="W13" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X13" t="n">
         <v>1000</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-17 08:55:20</t>
+          <t>2026-07-17 11:19:35</t>
         </is>
       </c>
     </row>
@@ -3917,7 +3917,7 @@
         <v>1000</v>
       </c>
       <c r="J14" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K14" t="n">
         <v>1000</v>
@@ -3944,19 +3944,19 @@
         <v>1.18</v>
       </c>
       <c r="S14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V14" t="n">
         <v>1.02</v>
       </c>
-      <c r="T14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.01</v>
-      </c>
       <c r="W14" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X14" t="n">
         <v>1000</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-17 08:55:20</t>
+          <t>2026-07-17 11:19:35</t>
         </is>
       </c>
     </row>
@@ -4171,7 +4171,7 @@
         <v>1000</v>
       </c>
       <c r="J15" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K15" t="n">
         <v>1000</v>
@@ -4207,10 +4207,10 @@
         <v>1.01</v>
       </c>
       <c r="V15" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W15" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X15" t="n">
         <v>1000</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-17 08:55:20</t>
+          <t>2026-07-17 11:19:35</t>
         </is>
       </c>
     </row>
@@ -4425,218 +4425,218 @@
         <v>1000</v>
       </c>
       <c r="J16" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="K16" t="n">
         <v>1000</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P16" t="n">
         <v>1.24</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-17 08:55:20</t>
+          <t>2026-07-17 11:19:35</t>
         </is>
       </c>
     </row>
@@ -4667,7 +4667,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="G17" t="n">
         <v>3.3</v>
@@ -4685,202 +4685,202 @@
         <v>3.55</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="P17" t="n">
         <v>1.52</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.36</v>
+        <v>2.44</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AL17" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AM17" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="AN17" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AO17" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AP17" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AR17" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AS17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT17" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AU17" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AV17" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AW17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX17" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AY17" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BA17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ17" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-17 08:55:20</t>
+          <t>2026-07-17 11:19:35</t>
         </is>
       </c>
     </row>
@@ -4924,7 +4924,7 @@
         <v>1.85</v>
       </c>
       <c r="G18" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="H18" t="n">
         <v>4</v>
@@ -4939,212 +4939,212 @@
         <v>4.3</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="P18" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="Q18" t="n">
         <v>1.73</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AL18" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AM18" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AN18" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AO18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP18" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AR18" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AS18" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AT18" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AU18" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AV18" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AW18" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AX18" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY18" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="BA18" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="BB18" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BC18" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="BD18" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="BE18" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="BF18" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="BG18" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="BH18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-17 08:55:20</t>
+          <t>2026-07-17 11:19:35</t>
         </is>
       </c>
     </row>
@@ -5175,34 +5175,34 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="G19" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="H19" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="I19" t="n">
-        <v>2.74</v>
+        <v>2.68</v>
       </c>
       <c r="J19" t="n">
         <v>3.6</v>
       </c>
       <c r="K19" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="P19" t="n">
         <v>2.12</v>
@@ -5211,194 +5211,194 @@
         <v>1.71</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AL19" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AM19" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AN19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP19" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AR19" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AS19" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AT19" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AU19" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AV19" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AW19" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AX19" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AY19" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="BA19" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="BB19" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="BC19" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BD19" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="BE19" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="BF19" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="BG19" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="BH19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-17 08:55:20</t>
+          <t>2026-07-17 11:19:35</t>
         </is>
       </c>
     </row>
@@ -5447,212 +5447,212 @@
         <v>1000</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="P20" t="n">
         <v>1.24</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-17 08:55:20</t>
+          <t>2026-07-17 11:19:35</t>
         </is>
       </c>
     </row>
@@ -5686,227 +5686,227 @@
         <v>2.06</v>
       </c>
       <c r="G21" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="H21" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="I21" t="n">
         <v>4.4</v>
       </c>
       <c r="J21" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K21" t="n">
         <v>3.8</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="P21" t="n">
         <v>1.91</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AL21" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AM21" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AN21" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AO21" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AP21" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AR21" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AS21" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AT21" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AU21" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AV21" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AW21" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AX21" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AY21" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BA21" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="BB21" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="BC21" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="BD21" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BE21" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BF21" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="BG21" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BH21" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="BI21" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="BJ21" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BK21" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="BL21" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="BM21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN21" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="BO21" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="BP21" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BQ21" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BR21" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BS21" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BT21" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="BU21" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="BV21" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BW21" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="BX21" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BY21" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BZ21" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="CA21" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-07-17 08:55:20</t>
+          <t>2026-07-17 11:19:35</t>
         </is>
       </c>
     </row>
@@ -5955,202 +5955,202 @@
         <v>1000</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="P22" t="n">
         <v>1.24</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ22" t="n">
         <v>0</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-07-17 08:55:20</t>
+          <t>2026-07-17 11:19:35</t>
         </is>
       </c>
     </row>
@@ -6209,212 +6209,212 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="P23" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-07-17 08:55:20</t>
+          <t>2026-07-17 11:19:35</t>
         </is>
       </c>
     </row>
@@ -6457,7 +6457,7 @@
         <v>1.64</v>
       </c>
       <c r="J24" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="K24" t="n">
         <v>4.8</v>
@@ -6475,10 +6475,10 @@
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-07-17 08:55:20</t>
+          <t>2026-07-17 11:19:35</t>
         </is>
       </c>
     </row>
@@ -6714,7 +6714,7 @@
         <v>3.9</v>
       </c>
       <c r="K25" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -6732,7 +6732,7 @@
         <v>2.34</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-07-17 08:55:20</t>
+          <t>2026-07-17 11:19:35</t>
         </is>
       </c>
     </row>
@@ -6956,7 +6956,7 @@
         <v>1.28</v>
       </c>
       <c r="G26" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="H26" t="n">
         <v>11.5</v>
@@ -6986,7 +6986,7 @@
         <v>2.52</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-07-17 08:55:20</t>
+          <t>2026-07-17 11:19:35</t>
         </is>
       </c>
     </row>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-07-17 08:55:20</t>
+          <t>2026-07-17 11:19:35</t>
         </is>
       </c>
     </row>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-07-17 08:55:20</t>
+          <t>2026-07-17 11:19:35</t>
         </is>
       </c>
     </row>
@@ -7718,7 +7718,7 @@
         <v>6</v>
       </c>
       <c r="G29" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="H29" t="n">
         <v>1.55</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-07-17 08:55:20</t>
+          <t>2026-07-17 11:19:35</t>
         </is>
       </c>
     </row>
@@ -7969,22 +7969,22 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.04</v>
+        <v>2.72</v>
       </c>
       <c r="G30" t="n">
-        <v>1000</v>
+        <v>3.3</v>
       </c>
       <c r="H30" t="n">
-        <v>1.04</v>
+        <v>2.7</v>
       </c>
       <c r="I30" t="n">
-        <v>1000</v>
+        <v>3.3</v>
       </c>
       <c r="J30" t="n">
-        <v>1.02</v>
+        <v>2.52</v>
       </c>
       <c r="K30" t="n">
-        <v>1000</v>
+        <v>3.8</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
@@ -7999,10 +7999,10 @@
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>1.24</v>
+        <v>1.67</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.01</v>
+        <v>2.2</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-07-17 08:55:20</t>
+          <t>2026-07-17 11:19:35</t>
         </is>
       </c>
     </row>
@@ -8223,16 +8223,16 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="G31" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="H31" t="n">
         <v>1.76</v>
       </c>
       <c r="I31" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="J31" t="n">
         <v>3.5</v>
@@ -8244,7 +8244,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="N31" t="n">
         <v>0</v>
@@ -8256,7 +8256,7 @@
         <v>1.52</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="R31" t="n">
         <v>0</v>
@@ -8277,13 +8277,13 @@
         <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Y31" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="Z31" t="n">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="AA31" t="n">
         <v>25</v>
@@ -8292,7 +8292,7 @@
         <v>17.5</v>
       </c>
       <c r="AC31" t="n">
-        <v>10.5</v>
+        <v>8.6</v>
       </c>
       <c r="AD31" t="n">
         <v>13.5</v>
@@ -8313,7 +8313,7 @@
         <v>80</v>
       </c>
       <c r="AJ31" t="n">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="AK31" t="n">
         <v>170</v>
@@ -8322,68 +8322,68 @@
         <v>190</v>
       </c>
       <c r="AM31" t="n">
-        <v>350</v>
+        <v>360</v>
       </c>
       <c r="AN31" t="n">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="AO31" t="n">
         <v>26</v>
       </c>
       <c r="AP31" t="n">
-        <v>6.6</v>
+        <v>3.5</v>
       </c>
       <c r="AQ31" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BB31" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BC31" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BD31" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BE31" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BF31" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BG31" t="n">
         <v>4.4</v>
       </c>
-      <c r="AR31" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AS31" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AT31" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AU31" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV31" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AW31" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AX31" t="n">
-        <v>4</v>
-      </c>
-      <c r="AY31" t="n">
-        <v>19</v>
-      </c>
-      <c r="AZ31" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BA31" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB31" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BC31" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BD31" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BE31" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BF31" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BG31" t="n">
-        <v>15</v>
-      </c>
       <c r="BH31" t="n">
         <v>0</v>
       </c>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-07-17 08:55:20</t>
+          <t>2026-07-17 11:19:35</t>
         </is>
       </c>
     </row>
@@ -8477,22 +8477,22 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="G32" t="n">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="H32" t="n">
-        <v>1.69</v>
+        <v>1.59</v>
       </c>
       <c r="I32" t="n">
-        <v>1.84</v>
+        <v>1.74</v>
       </c>
       <c r="J32" t="n">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="K32" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
@@ -8507,7 +8507,7 @@
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="Q32" t="n">
         <v>1.48</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-07-17 08:55:20</t>
+          <t>2026-07-17 11:19:35</t>
         </is>
       </c>
     </row>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-07-17 08:55:20</t>
+          <t>2026-07-17 11:19:35</t>
         </is>
       </c>
     </row>
@@ -8985,22 +8985,22 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1.04</v>
+        <v>2.06</v>
       </c>
       <c r="G34" t="n">
-        <v>1000</v>
+        <v>2.32</v>
       </c>
       <c r="H34" t="n">
-        <v>1.04</v>
+        <v>2.88</v>
       </c>
       <c r="I34" t="n">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="J34" t="n">
-        <v>1.02</v>
+        <v>3.05</v>
       </c>
       <c r="K34" t="n">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
@@ -9015,10 +9015,10 @@
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>1.24</v>
+        <v>2.06</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.01</v>
+        <v>1.66</v>
       </c>
       <c r="R34" t="n">
         <v>0</v>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-07-17 08:55:20</t>
+          <t>2026-07-17 11:19:35</t>
         </is>
       </c>
     </row>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-07-17 08:55:20</t>
+          <t>2026-07-17 11:19:35</t>
         </is>
       </c>
     </row>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-07-17 08:55:20</t>
+          <t>2026-07-17 11:19:35</t>
         </is>
       </c>
     </row>
@@ -9747,16 +9747,16 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="G37" t="n">
         <v>3.1</v>
       </c>
       <c r="H37" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="I37" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="J37" t="n">
         <v>2.8</v>
@@ -9780,7 +9780,7 @@
         <v>1.5</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="R37" t="n">
         <v>0</v>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-07-17 08:55:20</t>
+          <t>2026-07-17 11:19:35</t>
         </is>
       </c>
     </row>
@@ -10013,7 +10013,7 @@
         <v>2.18</v>
       </c>
       <c r="J38" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K38" t="n">
         <v>3.5</v>
@@ -10034,7 +10034,7 @@
         <v>1.65</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
@@ -10224,7 +10224,7 @@
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-07-17 08:55:20</t>
+          <t>2026-07-17 11:19:35</t>
         </is>
       </c>
     </row>
@@ -10255,22 +10255,22 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>2.96</v>
+        <v>3.25</v>
       </c>
       <c r="G39" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="H39" t="n">
         <v>2.32</v>
       </c>
       <c r="I39" t="n">
-        <v>2.96</v>
+        <v>2.62</v>
       </c>
       <c r="J39" t="n">
-        <v>2.24</v>
+        <v>3</v>
       </c>
       <c r="K39" t="n">
-        <v>4.4</v>
+        <v>3.8</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
@@ -10285,10 +10285,10 @@
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>1.51</v>
+        <v>1.62</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="R39" t="n">
         <v>0</v>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-07-17 08:55:20</t>
+          <t>2026-07-17 11:19:35</t>
         </is>
       </c>
     </row>
@@ -10732,7 +10732,7 @@
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-07-17 08:55:20</t>
+          <t>2026-07-17 11:19:35</t>
         </is>
       </c>
     </row>
@@ -10763,22 +10763,22 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1.49</v>
+        <v>1.58</v>
       </c>
       <c r="G41" t="n">
-        <v>1.88</v>
+        <v>1.74</v>
       </c>
       <c r="H41" t="n">
-        <v>2.18</v>
+        <v>4.1</v>
       </c>
       <c r="I41" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="J41" t="n">
-        <v>2.18</v>
+        <v>3.65</v>
       </c>
       <c r="K41" t="n">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
@@ -10793,10 +10793,10 @@
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="Q41" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -10986,7 +10986,7 @@
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-07-17 08:55:20</t>
+          <t>2026-07-17 11:19:35</t>
         </is>
       </c>
     </row>
@@ -11240,7 +11240,7 @@
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-07-17 08:55:20</t>
+          <t>2026-07-17 11:19:35</t>
         </is>
       </c>
     </row>
@@ -11271,22 +11271,22 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="G43" t="n">
-        <v>2.68</v>
+        <v>2.62</v>
       </c>
       <c r="H43" t="n">
-        <v>3.2</v>
+        <v>2.92</v>
       </c>
       <c r="I43" t="n">
-        <v>4.9</v>
+        <v>4.3</v>
       </c>
       <c r="J43" t="n">
-        <v>2.36</v>
+        <v>2.94</v>
       </c>
       <c r="K43" t="n">
-        <v>4.8</v>
+        <v>3.4</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
@@ -11301,10 +11301,10 @@
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>1.45</v>
+        <v>1.54</v>
       </c>
       <c r="Q43" t="n">
-        <v>2.22</v>
+        <v>2.46</v>
       </c>
       <c r="R43" t="n">
         <v>0</v>
@@ -11494,7 +11494,7 @@
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-07-17 08:55:20</t>
+          <t>2026-07-17 11:19:35</t>
         </is>
       </c>
     </row>
@@ -11748,7 +11748,7 @@
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-07-17 08:55:20</t>
+          <t>2026-07-17 11:19:35</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-19.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-19.xlsx
@@ -866,13 +866,13 @@
         <v>2.02</v>
       </c>
       <c r="I2" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="J2" t="n">
         <v>3.55</v>
       </c>
       <c r="K2" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L2" t="n">
         <v>1.38</v>
@@ -887,13 +887,13 @@
         <v>1.31</v>
       </c>
       <c r="P2" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="Q2" t="n">
         <v>1.9</v>
       </c>
       <c r="R2" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="S2" t="n">
         <v>3.3</v>
@@ -1022,7 +1022,7 @@
         <v>4.1</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.05</v>
+        <v>2.78</v>
       </c>
       <c r="BJ2" t="n">
         <v>11.5</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-17 11:19:35</t>
+          <t>2026-07-17 13:44:14</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
         <v>1.64</v>
       </c>
       <c r="G3" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="H3" t="n">
         <v>6.2</v>
@@ -1123,7 +1123,7 @@
         <v>7.4</v>
       </c>
       <c r="J3" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="K3" t="n">
         <v>4.2</v>
@@ -1132,7 +1132,7 @@
         <v>1.44</v>
       </c>
       <c r="M3" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N3" t="n">
         <v>3.15</v>
@@ -1144,7 +1144,7 @@
         <v>1.75</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="R3" t="n">
         <v>1.26</v>
@@ -1156,13 +1156,13 @@
         <v>2.12</v>
       </c>
       <c r="U3" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="V3" t="n">
         <v>1.16</v>
       </c>
       <c r="W3" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="X3" t="n">
         <v>12.5</v>
@@ -1183,7 +1183,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AD3" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
         <v>150</v>
@@ -1225,10 +1225,10 @@
         <v>15</v>
       </c>
       <c r="AR3" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AS3" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AT3" t="n">
         <v>6</v>
@@ -1240,7 +1240,7 @@
         <v>19</v>
       </c>
       <c r="AW3" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AX3" t="n">
         <v>7.8</v>
@@ -1252,7 +1252,7 @@
         <v>18.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BB3" t="n">
         <v>14</v>
@@ -1261,16 +1261,16 @@
         <v>17</v>
       </c>
       <c r="BD3" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BE3" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BF3" t="n">
         <v>11</v>
       </c>
       <c r="BG3" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BH3" t="n">
         <v>1000</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-17 11:19:35</t>
+          <t>2026-07-17 13:44:14</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
         <v>3.9</v>
       </c>
       <c r="L4" t="n">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="M4" t="n">
         <v>1.09</v>
@@ -1425,7 +1425,7 @@
         <v>8</v>
       </c>
       <c r="Z4" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AA4" t="n">
         <v>23</v>
@@ -1437,7 +1437,7 @@
         <v>9.6</v>
       </c>
       <c r="AD4" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AE4" t="n">
         <v>25</v>
@@ -1473,31 +1473,31 @@
         <v>17.5</v>
       </c>
       <c r="AP4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ4" t="n">
         <v>6.4</v>
       </c>
       <c r="AR4" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS4" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AT4" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AU4" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AV4" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW4" t="n">
         <v>16.5</v>
       </c>
       <c r="AX4" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AY4" t="n">
         <v>16.5</v>
@@ -1509,7 +1509,7 @@
         <v>5</v>
       </c>
       <c r="BB4" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BC4" t="n">
         <v>5.2</v>
@@ -1518,13 +1518,13 @@
         <v>5.3</v>
       </c>
       <c r="BE4" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BF4" t="n">
         <v>5.3</v>
       </c>
       <c r="BG4" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BH4" t="n">
         <v>3.45</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-17 11:19:35</t>
+          <t>2026-07-17 13:44:14</t>
         </is>
       </c>
     </row>
@@ -1652,7 +1652,7 @@
         <v>1.87</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="R5" t="n">
         <v>1.32</v>
@@ -1751,22 +1751,22 @@
         <v>1.01</v>
       </c>
       <c r="AX5" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AY5" t="n">
         <v>8.6</v>
       </c>
-      <c r="AY5" t="n">
-        <v>8</v>
-      </c>
       <c r="AZ5" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BA5" t="n">
         <v>1.01</v>
       </c>
       <c r="BB5" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="BC5" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="BD5" t="n">
         <v>1.01</v>
@@ -1775,7 +1775,7 @@
         <v>1.01</v>
       </c>
       <c r="BF5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BG5" t="n">
         <v>1.01</v>
@@ -1790,16 +1790,16 @@
         <v>12</v>
       </c>
       <c r="BK5" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BL5" t="n">
         <v>160</v>
       </c>
       <c r="BM5" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BN5" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="BO5" t="n">
         <v>3.6</v>
@@ -1808,31 +1808,31 @@
         <v>15</v>
       </c>
       <c r="BQ5" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BR5" t="n">
         <v>34</v>
       </c>
       <c r="BS5" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BT5" t="n">
         <v>9.4</v>
       </c>
       <c r="BU5" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BV5" t="n">
         <v>50</v>
       </c>
       <c r="BW5" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BX5" t="n">
         <v>60</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BZ5" t="n">
         <v>0</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-17 11:19:35</t>
+          <t>2026-07-17 13:44:14</t>
         </is>
       </c>
     </row>
@@ -1885,7 +1885,7 @@
         <v>2.84</v>
       </c>
       <c r="J6" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K6" t="n">
         <v>3.8</v>
@@ -1924,7 +1924,7 @@
         <v>1.54</v>
       </c>
       <c r="W6" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="X6" t="n">
         <v>16.5</v>
@@ -1987,7 +1987,7 @@
         <v>8.4</v>
       </c>
       <c r="AR6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AS6" t="n">
         <v>1.01</v>
@@ -2044,13 +2044,13 @@
         <v>11</v>
       </c>
       <c r="BK6" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BL6" t="n">
         <v>140</v>
       </c>
       <c r="BM6" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BN6" t="n">
         <v>6.8</v>
@@ -2062,13 +2062,13 @@
         <v>26</v>
       </c>
       <c r="BQ6" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BR6" t="n">
         <v>40</v>
       </c>
       <c r="BS6" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BT6" t="n">
         <v>5.8</v>
@@ -2080,13 +2080,13 @@
         <v>23</v>
       </c>
       <c r="BW6" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BX6" t="n">
         <v>38</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BZ6" t="n">
         <v>0</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-17 11:19:35</t>
+          <t>2026-07-17 13:44:14</t>
         </is>
       </c>
     </row>
@@ -2259,7 +2259,7 @@
         <v>20</v>
       </c>
       <c r="AX7" t="n">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="AY7" t="n">
         <v>10</v>
@@ -2298,13 +2298,13 @@
         <v>11.5</v>
       </c>
       <c r="BK7" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BL7" t="n">
         <v>150</v>
       </c>
       <c r="BM7" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BN7" t="n">
         <v>7.4</v>
@@ -2316,13 +2316,13 @@
         <v>30</v>
       </c>
       <c r="BQ7" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BR7" t="n">
         <v>46</v>
       </c>
       <c r="BS7" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BT7" t="n">
         <v>6.4</v>
@@ -2334,13 +2334,13 @@
         <v>23</v>
       </c>
       <c r="BW7" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BX7" t="n">
         <v>40</v>
       </c>
       <c r="BY7" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BZ7" t="n">
         <v>0</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-17 11:19:35</t>
+          <t>2026-07-17 13:44:14</t>
         </is>
       </c>
     </row>
@@ -2396,7 +2396,7 @@
         <v>4.9</v>
       </c>
       <c r="K8" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="L8" t="n">
         <v>1.28</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-17 11:19:35</t>
+          <t>2026-07-17 13:44:14</t>
         </is>
       </c>
     </row>
@@ -2659,28 +2659,28 @@
         <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O9" t="n">
         <v>1.01</v>
       </c>
       <c r="P9" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.02</v>
+        <v>1.52</v>
       </c>
       <c r="R9" t="n">
         <v>1.18</v>
       </c>
       <c r="S9" t="n">
-        <v>1.02</v>
+        <v>1.52</v>
       </c>
       <c r="T9" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U9" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V9" t="n">
         <v>1.01</v>
@@ -2800,65 +2800,65 @@
         <v>1000</v>
       </c>
       <c r="BI9" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ9" t="n">
         <v>1000</v>
       </c>
       <c r="BK9" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN9" t="n">
         <v>1000</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP9" t="n">
         <v>1000</v>
       </c>
       <c r="BQ9" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR9" t="n">
         <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT9" t="n">
         <v>1000</v>
       </c>
       <c r="BU9" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV9" t="n">
         <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ9" t="n">
         <v>1000</v>
       </c>
       <c r="CA9" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-17 11:19:35</t>
+          <t>2026-07-17 13:44:14</t>
         </is>
       </c>
     </row>
@@ -2922,13 +2922,13 @@
         <v>2.72</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="R10" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="S10" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="T10" t="n">
         <v>1.54</v>
@@ -2946,7 +2946,7 @@
         <v>34</v>
       </c>
       <c r="Y10" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Z10" t="n">
         <v>60</v>
@@ -2958,13 +2958,13 @@
         <v>15.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AD10" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AE10" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AF10" t="n">
         <v>14.5</v>
@@ -2979,7 +2979,7 @@
         <v>65</v>
       </c>
       <c r="AJ10" t="n">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="AK10" t="n">
         <v>17.5</v>
@@ -2997,40 +2997,40 @@
         <v>60</v>
       </c>
       <c r="AP10" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="AQ10" t="n">
         <v>21</v>
       </c>
       <c r="AR10" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="AS10" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="AT10" t="n">
         <v>10</v>
       </c>
       <c r="AU10" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AV10" t="n">
         <v>17</v>
       </c>
       <c r="AW10" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="AX10" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AY10" t="n">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ10" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BA10" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="BB10" t="n">
         <v>12.5</v>
@@ -3042,13 +3042,13 @@
         <v>19.5</v>
       </c>
       <c r="BE10" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="BF10" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="BG10" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="BH10" t="n">
         <v>5.4</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-17 11:19:35</t>
+          <t>2026-07-17 13:44:14</t>
         </is>
       </c>
     </row>
@@ -3155,40 +3155,40 @@
         <v>1000</v>
       </c>
       <c r="J11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O11" t="n">
         <v>1.02</v>
       </c>
-      <c r="K11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N11" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="O11" t="n">
-        <v>1.01</v>
-      </c>
       <c r="P11" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.02</v>
+        <v>1.53</v>
       </c>
       <c r="R11" t="n">
         <v>1.18</v>
       </c>
       <c r="S11" t="n">
-        <v>1.02</v>
+        <v>1.52</v>
       </c>
       <c r="T11" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U11" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V11" t="n">
         <v>1.02</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-17 11:19:35</t>
+          <t>2026-07-17 13:44:14</t>
         </is>
       </c>
     </row>
@@ -3409,22 +3409,22 @@
         <v>1000</v>
       </c>
       <c r="J12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N12" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O12" t="n">
         <v>1.02</v>
-      </c>
-      <c r="K12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N12" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="O12" t="n">
-        <v>1.01</v>
       </c>
       <c r="P12" t="n">
         <v>1.24</v>
@@ -3439,10 +3439,10 @@
         <v>1.42</v>
       </c>
       <c r="T12" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U12" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V12" t="n">
         <v>1.02</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-17 11:19:35</t>
+          <t>2026-07-17 13:44:14</t>
         </is>
       </c>
     </row>
@@ -3663,46 +3663,46 @@
         <v>1000</v>
       </c>
       <c r="J13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N13" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O13" t="n">
         <v>1.02</v>
       </c>
-      <c r="K13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N13" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="O13" t="n">
-        <v>1.01</v>
-      </c>
       <c r="P13" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.01</v>
+        <v>1.49</v>
       </c>
       <c r="R13" t="n">
         <v>1.18</v>
       </c>
       <c r="S13" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="T13" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U13" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V13" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W13" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X13" t="n">
         <v>1000</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-17 11:19:35</t>
+          <t>2026-07-17 13:44:14</t>
         </is>
       </c>
     </row>
@@ -3917,46 +3917,46 @@
         <v>1000</v>
       </c>
       <c r="J14" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N14" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O14" t="n">
         <v>1.02</v>
       </c>
-      <c r="K14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N14" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="O14" t="n">
-        <v>1.01</v>
-      </c>
       <c r="P14" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.02</v>
+        <v>1.46</v>
       </c>
       <c r="R14" t="n">
         <v>1.18</v>
       </c>
       <c r="S14" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="T14" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U14" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V14" t="n">
         <v>1.02</v>
       </c>
       <c r="W14" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X14" t="n">
         <v>1000</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-17 11:19:35</t>
+          <t>2026-07-17 13:44:14</t>
         </is>
       </c>
     </row>
@@ -4171,7 +4171,7 @@
         <v>1000</v>
       </c>
       <c r="J15" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="K15" t="n">
         <v>1000</v>
@@ -4183,13 +4183,13 @@
         <v>1.01</v>
       </c>
       <c r="N15" t="n">
-        <v>1.24</v>
+        <v>1.1</v>
       </c>
       <c r="O15" t="n">
         <v>1.01</v>
       </c>
       <c r="P15" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q15" t="n">
         <v>1.02</v>
@@ -4198,19 +4198,19 @@
         <v>1.18</v>
       </c>
       <c r="S15" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="T15" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U15" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V15" t="n">
         <v>1.02</v>
       </c>
       <c r="W15" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X15" t="n">
         <v>1000</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-17 11:19:35</t>
+          <t>2026-07-17 13:44:14</t>
         </is>
       </c>
     </row>
@@ -4437,28 +4437,28 @@
         <v>1.01</v>
       </c>
       <c r="N16" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O16" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P16" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.02</v>
+        <v>1.41</v>
       </c>
       <c r="R16" t="n">
         <v>1.18</v>
       </c>
       <c r="S16" t="n">
-        <v>1.02</v>
+        <v>1.42</v>
       </c>
       <c r="T16" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U16" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V16" t="n">
         <v>1.02</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-17 11:19:35</t>
+          <t>2026-07-17 13:44:14</t>
         </is>
       </c>
     </row>
@@ -4685,34 +4685,34 @@
         <v>3.55</v>
       </c>
       <c r="L17" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="M17" t="n">
         <v>1.11</v>
       </c>
       <c r="N17" t="n">
-        <v>2.48</v>
+        <v>2.38</v>
       </c>
       <c r="O17" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="P17" t="n">
         <v>1.52</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.44</v>
+        <v>2.54</v>
       </c>
       <c r="R17" t="n">
         <v>1.17</v>
       </c>
       <c r="S17" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="T17" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U17" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V17" t="n">
         <v>1.46</v>
@@ -4724,7 +4724,7 @@
         <v>10</v>
       </c>
       <c r="Y17" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z17" t="n">
         <v>21</v>
@@ -4736,7 +4736,7 @@
         <v>10.5</v>
       </c>
       <c r="AC17" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AD17" t="n">
         <v>16</v>
@@ -4763,7 +4763,7 @@
         <v>55</v>
       </c>
       <c r="AL17" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AM17" t="n">
         <v>200</v>
@@ -4775,7 +4775,7 @@
         <v>60</v>
       </c>
       <c r="AP17" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AQ17" t="n">
         <v>6.6</v>
@@ -4805,7 +4805,7 @@
         <v>10.5</v>
       </c>
       <c r="AZ17" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BA17" t="n">
         <v>1.01</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-17 11:19:35</t>
+          <t>2026-07-17 13:44:14</t>
         </is>
       </c>
     </row>
@@ -4933,28 +4933,28 @@
         <v>4.6</v>
       </c>
       <c r="J18" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K18" t="n">
         <v>4.3</v>
       </c>
       <c r="L18" t="n">
-        <v>1.3</v>
+        <v>1.01</v>
       </c>
       <c r="M18" t="n">
         <v>1.01</v>
       </c>
       <c r="N18" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="O18" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P18" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="R18" t="n">
         <v>1.37</v>
@@ -4966,7 +4966,7 @@
         <v>1.57</v>
       </c>
       <c r="U18" t="n">
-        <v>1.01</v>
+        <v>1.87</v>
       </c>
       <c r="V18" t="n">
         <v>1.29</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-17 11:19:35</t>
+          <t>2026-07-17 13:44:14</t>
         </is>
       </c>
     </row>
@@ -5175,7 +5175,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="G19" t="n">
         <v>3.05</v>
@@ -5184,7 +5184,7 @@
         <v>2.46</v>
       </c>
       <c r="I19" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="J19" t="n">
         <v>3.6</v>
@@ -5193,7 +5193,7 @@
         <v>3.9</v>
       </c>
       <c r="L19" t="n">
-        <v>1.31</v>
+        <v>1.01</v>
       </c>
       <c r="M19" t="n">
         <v>1.01</v>
@@ -5211,10 +5211,10 @@
         <v>1.71</v>
       </c>
       <c r="R19" t="n">
-        <v>1.45</v>
+        <v>1.37</v>
       </c>
       <c r="S19" t="n">
-        <v>2.24</v>
+        <v>2.48</v>
       </c>
       <c r="T19" t="n">
         <v>1.45</v>
@@ -5247,7 +5247,7 @@
         <v>12.5</v>
       </c>
       <c r="AD19" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AE19" t="n">
         <v>38</v>
@@ -5283,10 +5283,10 @@
         <v>1000</v>
       </c>
       <c r="AP19" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="AQ19" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="AR19" t="n">
         <v>12.5</v>
@@ -5298,107 +5298,107 @@
         <v>2.08</v>
       </c>
       <c r="AU19" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="AV19" t="n">
         <v>2.06</v>
       </c>
       <c r="AW19" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="AX19" t="n">
         <v>2.16</v>
       </c>
       <c r="AY19" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="AZ19" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="BA19" t="n">
         <v>2.22</v>
       </c>
       <c r="BB19" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="BC19" t="n">
         <v>20</v>
       </c>
       <c r="BD19" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="BE19" t="n">
         <v>2.28</v>
       </c>
       <c r="BF19" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="BH19" t="n">
         <v>1000</v>
       </c>
       <c r="BI19" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ19" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BK19" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL19" t="n">
         <v>1000</v>
       </c>
       <c r="BM19" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN19" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BP19" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BQ19" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR19" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BS19" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT19" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="BU19" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BV19" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BW19" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX19" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BY19" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ19" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="CA19" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-17 11:19:35</t>
+          <t>2026-07-17 13:44:14</t>
         </is>
       </c>
     </row>
@@ -5459,7 +5459,7 @@
         <v>1.16</v>
       </c>
       <c r="P20" t="n">
-        <v>1.24</v>
+        <v>1.5</v>
       </c>
       <c r="Q20" t="n">
         <v>1.16</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-17 11:19:35</t>
+          <t>2026-07-17 13:44:14</t>
         </is>
       </c>
     </row>
@@ -5686,28 +5686,28 @@
         <v>2.06</v>
       </c>
       <c r="G21" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="H21" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="I21" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="J21" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="K21" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="L21" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="M21" t="n">
         <v>1.07</v>
       </c>
       <c r="N21" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="O21" t="n">
         <v>1.32</v>
@@ -5716,16 +5716,16 @@
         <v>1.91</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="R21" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S21" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="T21" t="n">
-        <v>1.67</v>
+        <v>1.79</v>
       </c>
       <c r="U21" t="n">
         <v>2.1</v>
@@ -5734,115 +5734,115 @@
         <v>1.3</v>
       </c>
       <c r="W21" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="X21" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="Y21" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="Z21" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="AA21" t="n">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="AB21" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AG21" t="n">
         <v>11</v>
       </c>
-      <c r="AC21" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>60</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>12.5</v>
-      </c>
       <c r="AH21" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI21" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AJ21" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AK21" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL21" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AM21" t="n">
         <v>110</v>
       </c>
       <c r="AN21" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AO21" t="n">
         <v>55</v>
       </c>
       <c r="AP21" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AQ21" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AR21" t="n">
-        <v>4.6</v>
+        <v>25</v>
       </c>
       <c r="AS21" t="n">
-        <v>4.9</v>
+        <v>6.6</v>
       </c>
       <c r="AT21" t="n">
         <v>8.4</v>
       </c>
       <c r="AU21" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV21" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="AW21" t="n">
-        <v>4.8</v>
+        <v>42</v>
       </c>
       <c r="AX21" t="n">
         <v>11.5</v>
       </c>
       <c r="AY21" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ21" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BA21" t="n">
-        <v>4.9</v>
+        <v>48</v>
       </c>
       <c r="BB21" t="n">
+        <v>22</v>
+      </c>
+      <c r="BC21" t="n">
         <v>19</v>
       </c>
-      <c r="BC21" t="n">
-        <v>17</v>
-      </c>
       <c r="BD21" t="n">
-        <v>4.6</v>
+        <v>32</v>
       </c>
       <c r="BE21" t="n">
-        <v>5</v>
+        <v>6.6</v>
       </c>
       <c r="BF21" t="n">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="BG21" t="n">
-        <v>4.8</v>
+        <v>42</v>
       </c>
       <c r="BH21" t="n">
         <v>3.85</v>
@@ -5854,7 +5854,7 @@
         <v>11</v>
       </c>
       <c r="BK21" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BL21" t="n">
         <v>140</v>
@@ -5866,19 +5866,19 @@
         <v>5.4</v>
       </c>
       <c r="BO21" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="BP21" t="n">
         <v>16.5</v>
       </c>
       <c r="BQ21" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BR21" t="n">
         <v>32</v>
       </c>
       <c r="BS21" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BT21" t="n">
         <v>8.6</v>
@@ -5890,23 +5890,23 @@
         <v>40</v>
       </c>
       <c r="BW21" t="n">
-        <v>25</v>
+        <v>1.01</v>
       </c>
       <c r="BX21" t="n">
         <v>50</v>
       </c>
       <c r="BY21" t="n">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="BZ21" t="n">
         <v>29</v>
       </c>
       <c r="CA21" t="n">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-07-17 11:19:35</t>
+          <t>2026-07-17 13:44:14</t>
         </is>
       </c>
     </row>
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.06</v>
+        <v>1.05</v>
       </c>
       <c r="G22" t="n">
         <v>1000</v>
@@ -5949,7 +5949,7 @@
         <v>1.98</v>
       </c>
       <c r="J22" t="n">
-        <v>2.06</v>
+        <v>1.05</v>
       </c>
       <c r="K22" t="n">
         <v>1000</v>
@@ -5961,22 +5961,22 @@
         <v>1.01</v>
       </c>
       <c r="N22" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O22" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="P22" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="R22" t="n">
         <v>1.12</v>
       </c>
       <c r="S22" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="T22" t="n">
         <v>1.01</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-07-17 11:19:35</t>
+          <t>2026-07-17 13:44:14</t>
         </is>
       </c>
     </row>
@@ -6212,7 +6212,7 @@
         <v>1.01</v>
       </c>
       <c r="M23" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N23" t="n">
         <v>1.01</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-07-17 11:19:35</t>
+          <t>2026-07-17 13:44:14</t>
         </is>
       </c>
     </row>
@@ -6448,10 +6448,10 @@
         <v>5.7</v>
       </c>
       <c r="G24" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="H24" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="I24" t="n">
         <v>1.64</v>
@@ -6463,16 +6463,16 @@
         <v>4.8</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="P24" t="n">
         <v>2.62</v>
@@ -6481,194 +6481,194 @@
         <v>1.54</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AL24" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AM24" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AN24" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AO24" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AP24" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AR24" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS24" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AT24" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AU24" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AV24" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AW24" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AX24" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AY24" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AZ24" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="BA24" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BB24" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="BC24" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="BD24" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="BE24" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="BF24" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="BG24" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="BH24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-07-17 11:19:35</t>
+          <t>2026-07-17 13:44:14</t>
         </is>
       </c>
     </row>
@@ -6705,224 +6705,224 @@
         <v>3.85</v>
       </c>
       <c r="H25" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="I25" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="J25" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K25" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="P25" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AK25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL25" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AM25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP25" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR25" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS25" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT25" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU25" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV25" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW25" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX25" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY25" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ25" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA25" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB25" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="BC25" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE25" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF25" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BG25" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BH25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-07-17 11:19:35</t>
+          <t>2026-07-17 13:44:14</t>
         </is>
       </c>
     </row>
@@ -6953,230 +6953,230 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="G26" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="H26" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="I26" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="J26" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="K26" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="P26" t="n">
         <v>2.52</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AI26" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AK26" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AL26" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AM26" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="AN26" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AO26" t="n">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="AP26" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AQ26" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AR26" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AS26" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AT26" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AU26" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AV26" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AW26" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AX26" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AY26" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ26" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BA26" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="BB26" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="BC26" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="BD26" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="BE26" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="BF26" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BG26" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="BH26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-07-17 11:19:35</t>
+          <t>2026-07-17 13:44:14</t>
         </is>
       </c>
     </row>
@@ -7207,220 +7207,220 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.85</v>
+        <v>2.98</v>
       </c>
       <c r="G27" t="n">
         <v>1000</v>
       </c>
       <c r="H27" t="n">
-        <v>1.04</v>
+        <v>1.26</v>
       </c>
       <c r="I27" t="n">
-        <v>2.22</v>
+        <v>1000</v>
       </c>
       <c r="J27" t="n">
-        <v>1.85</v>
+        <v>1.02</v>
       </c>
       <c r="K27" t="n">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="P27" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ27" t="n">
         <v>0</v>
@@ -7430,14 +7430,14 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-07-17 11:19:35</t>
+          <t>2026-07-17 13:44:14</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Kazakhstan Premier League</t>
+          <t>Finnish Veikkausliiga</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -7447,234 +7447,234 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>12:00:00</t>
+          <t>12:30:00</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>FC Ordabasy</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Elimai FC</t>
+          <t>FC Inter</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="G28" t="n">
-        <v>1.79</v>
+        <v>6.8</v>
       </c>
       <c r="H28" t="n">
-        <v>2.3</v>
+        <v>1.55</v>
       </c>
       <c r="I28" t="n">
-        <v>1000</v>
+        <v>1.66</v>
       </c>
       <c r="J28" t="n">
-        <v>2.3</v>
+        <v>4.2</v>
       </c>
       <c r="K28" t="n">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="P28" t="n">
-        <v>1.24</v>
+        <v>2.14</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.01</v>
+        <v>1.69</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AI28" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK28" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AL28" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AM28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO28" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AP28" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AR28" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AS28" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AT28" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AU28" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AV28" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AW28" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AX28" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="AY28" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AZ28" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="BA28" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="BB28" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="BC28" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="BD28" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="BE28" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="BF28" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="BG28" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="BH28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ28" t="n">
         <v>0</v>
@@ -7684,14 +7684,14 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-07-17 11:19:35</t>
+          <t>2026-07-17 13:44:14</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Finnish Veikkausliiga</t>
+          <t>Lithuanian A Lyga</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -7701,234 +7701,234 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>12:30:00</t>
+          <t>12:45:00</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>FC Dziugas</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>FC Inter</t>
+          <t>FK Banga Gargzdu</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>6</v>
+        <v>2.72</v>
       </c>
       <c r="G29" t="n">
-        <v>6.8</v>
+        <v>3.1</v>
       </c>
       <c r="H29" t="n">
-        <v>1.55</v>
+        <v>2.7</v>
       </c>
       <c r="I29" t="n">
-        <v>1.66</v>
+        <v>3.1</v>
       </c>
       <c r="J29" t="n">
-        <v>4.2</v>
+        <v>2.84</v>
       </c>
       <c r="K29" t="n">
-        <v>4.8</v>
+        <v>3.8</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P29" t="n">
-        <v>2.18</v>
+        <v>1.67</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.71</v>
+        <v>2.2</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ29" t="n">
         <v>0</v>
@@ -7938,14 +7938,14 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-07-17 11:19:35</t>
+          <t>2026-07-17 13:44:14</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Lithuanian A Lyga</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -7955,251 +7955,251 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>12:45:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>FC Dziugas</t>
+          <t>Cerro</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>FK Banga Gargzdu</t>
+          <t>Racing Club (Uru)</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>2.72</v>
+        <v>5.8</v>
       </c>
       <c r="G30" t="n">
-        <v>3.3</v>
+        <v>6.6</v>
       </c>
       <c r="H30" t="n">
-        <v>2.7</v>
+        <v>1.76</v>
       </c>
       <c r="I30" t="n">
-        <v>3.3</v>
+        <v>1.84</v>
       </c>
       <c r="J30" t="n">
-        <v>2.52</v>
+        <v>3.5</v>
       </c>
       <c r="K30" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="P30" t="n">
-        <v>1.67</v>
+        <v>1.52</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.2</v>
+        <v>2.64</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AI30" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="AK30" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="AL30" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="AM30" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="AN30" t="n">
-        <v>0</v>
+        <v>320</v>
       </c>
       <c r="AO30" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AP30" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AQ30" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AR30" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AS30" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AT30" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AU30" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AV30" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AW30" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AX30" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AY30" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AZ30" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BA30" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BB30" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="BC30" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="BD30" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="BE30" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="BF30" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="BG30" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BH30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-07-17 11:19:35</t>
+          <t>2026-07-17 13:44:14</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Slovenian Premier League</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -8214,246 +8214,246 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Cerro</t>
+          <t>NK Aluminij</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Racing Club (Uru)</t>
+          <t>NK Maribor</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>5.9</v>
+        <v>4.8</v>
       </c>
       <c r="G31" t="n">
-        <v>6.8</v>
+        <v>5.8</v>
       </c>
       <c r="H31" t="n">
-        <v>1.76</v>
+        <v>1.59</v>
       </c>
       <c r="I31" t="n">
-        <v>1.83</v>
+        <v>1.74</v>
       </c>
       <c r="J31" t="n">
-        <v>3.5</v>
+        <v>3.95</v>
       </c>
       <c r="K31" t="n">
-        <v>3.65</v>
+        <v>5.3</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M31" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="P31" t="n">
-        <v>1.52</v>
+        <v>2.68</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.64</v>
+        <v>1.48</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X31" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="Y31" t="n">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="Z31" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="AA31" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AB31" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AC31" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="AD31" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AE31" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AF31" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AG31" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AH31" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AI31" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AJ31" t="n">
-        <v>270</v>
+        <v>1000</v>
       </c>
       <c r="AK31" t="n">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AL31" t="n">
-        <v>190</v>
+        <v>1000</v>
       </c>
       <c r="AM31" t="n">
-        <v>360</v>
+        <v>1000</v>
       </c>
       <c r="AN31" t="n">
-        <v>320</v>
+        <v>1000</v>
       </c>
       <c r="AO31" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AP31" t="n">
-        <v>3.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ31" t="n">
-        <v>2.98</v>
+        <v>1.01</v>
       </c>
       <c r="AR31" t="n">
-        <v>3.35</v>
+        <v>1.01</v>
       </c>
       <c r="AS31" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="AT31" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="AU31" t="n">
-        <v>3.25</v>
+        <v>1.01</v>
       </c>
       <c r="AV31" t="n">
-        <v>3.8</v>
+        <v>1.01</v>
       </c>
       <c r="AW31" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="AX31" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="AY31" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ31" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BA31" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BB31" t="n">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="BC31" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BD31" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BE31" t="n">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="BF31" t="n">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="BG31" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BH31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-07-17 11:19:35</t>
+          <t>2026-07-17 13:44:14</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Slovenian Premier League</t>
+          <t>Peruvian Primera Division</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -8468,246 +8468,246 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NK Aluminij</t>
+          <t>CD Los Chankas</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>NK Maribor</t>
+          <t>Sport Boys (Per)</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>4.8</v>
+        <v>1.22</v>
       </c>
       <c r="G32" t="n">
-        <v>5.8</v>
+        <v>2</v>
       </c>
       <c r="H32" t="n">
-        <v>1.59</v>
+        <v>1.04</v>
       </c>
       <c r="I32" t="n">
-        <v>1.74</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J32" t="n">
-        <v>3.95</v>
+        <v>2.56</v>
       </c>
       <c r="K32" t="n">
-        <v>5.3</v>
+        <v>1000</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="P32" t="n">
-        <v>2.68</v>
+        <v>1.64</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.48</v>
+        <v>1.86</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU32" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AV32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ32" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="BA32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE32" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BF32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-07-17 11:19:35</t>
+          <t>2026-07-17 13:44:14</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Peruvian Primera Division</t>
+          <t>Lithuanian A Lyga</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -8722,229 +8722,229 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>CD Los Chankas</t>
+          <t>VMFD Zalgiris</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Sport Boys (Per)</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="K33" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="P33" t="n">
-        <v>1.24</v>
+        <v>2.06</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.01</v>
+        <v>1.66</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ33" t="n">
         <v>0</v>
@@ -8954,14 +8954,14 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-07-17 11:19:35</t>
+          <t>2026-07-17 13:44:14</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Lithuanian A Lyga</t>
+          <t>Icelandic Urvalsdeild</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -8976,239 +8976,239 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VMFD Zalgiris</t>
+          <t>KR Reykjavik</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P34" t="n">
-        <v>2.06</v>
+        <v>1.25</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.66</v>
+        <v>1.01</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-07-17 11:19:35</t>
+          <t>2026-07-17 13:44:14</t>
         </is>
       </c>
     </row>
@@ -9257,202 +9257,202 @@
         <v>1000</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="P35" t="n">
         <v>1.24</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ35" t="n">
         <v>0</v>
@@ -9462,14 +9462,14 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-07-17 11:19:35</t>
+          <t>2026-07-17 13:44:14</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Icelandic Urvalsdeild</t>
+          <t>Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -9484,239 +9484,239 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>KR Reykjavik</t>
+          <t>FC Ordabasy</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Elimai FC</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="K36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="P36" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-07-17 11:19:35</t>
+          <t>2026-07-17 13:44:14</t>
         </is>
       </c>
     </row>
@@ -9756,7 +9756,7 @@
         <v>2.88</v>
       </c>
       <c r="I37" t="n">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="J37" t="n">
         <v>2.8</v>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-07-17 11:19:35</t>
+          <t>2026-07-17 13:44:14</t>
         </is>
       </c>
     </row>
@@ -10007,7 +10007,7 @@
         <v>4.5</v>
       </c>
       <c r="H38" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="I38" t="n">
         <v>2.18</v>
@@ -10019,16 +10019,16 @@
         <v>3.5</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="P38" t="n">
         <v>1.65</v>
@@ -10037,194 +10037,194 @@
         <v>2.26</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK38" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AL38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP38" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AQ38" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AR38" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AS38" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AT38" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AU38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV38" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AW38" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AX38" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AY38" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AZ38" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BA38" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BB38" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BC38" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BD38" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BE38" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BF38" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BG38" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BH38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-07-17 11:19:35</t>
+          <t>2026-07-17 13:44:14</t>
         </is>
       </c>
     </row>
@@ -10264,7 +10264,7 @@
         <v>2.32</v>
       </c>
       <c r="I39" t="n">
-        <v>2.62</v>
+        <v>2.78</v>
       </c>
       <c r="J39" t="n">
         <v>3</v>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-07-17 11:19:35</t>
+          <t>2026-07-17 13:44:14</t>
         </is>
       </c>
     </row>
@@ -10732,7 +10732,7 @@
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-07-17 11:19:35</t>
+          <t>2026-07-17 13:44:14</t>
         </is>
       </c>
     </row>
@@ -10772,10 +10772,10 @@
         <v>4.1</v>
       </c>
       <c r="I41" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="J41" t="n">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="K41" t="n">
         <v>5.5</v>
@@ -10986,7 +10986,7 @@
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-07-17 11:19:35</t>
+          <t>2026-07-17 13:44:14</t>
         </is>
       </c>
     </row>
@@ -11050,7 +11050,7 @@
         <v>1.68</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="R42" t="n">
         <v>0</v>
@@ -11240,7 +11240,7 @@
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-07-17 11:19:35</t>
+          <t>2026-07-17 13:44:14</t>
         </is>
       </c>
     </row>
@@ -11494,7 +11494,7 @@
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-07-17 11:19:35</t>
+          <t>2026-07-17 13:44:14</t>
         </is>
       </c>
     </row>
@@ -11748,7 +11748,7 @@
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-07-17 11:19:35</t>
+          <t>2026-07-17 13:44:14</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-19.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-19.xlsx
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="G2" t="n">
         <v>4.3</v>
@@ -866,16 +866,16 @@
         <v>2.02</v>
       </c>
       <c r="I2" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="J2" t="n">
         <v>3.55</v>
       </c>
       <c r="K2" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L2" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="M2" t="n">
         <v>1.07</v>
@@ -887,13 +887,13 @@
         <v>1.31</v>
       </c>
       <c r="P2" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="Q2" t="n">
         <v>1.9</v>
       </c>
       <c r="R2" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S2" t="n">
         <v>3.3</v>
@@ -902,10 +902,10 @@
         <v>1.74</v>
       </c>
       <c r="U2" t="n">
-        <v>1.94</v>
+        <v>2.12</v>
       </c>
       <c r="V2" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="W2" t="n">
         <v>1.31</v>
@@ -1022,7 +1022,7 @@
         <v>4.1</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.78</v>
+        <v>3.05</v>
       </c>
       <c r="BJ2" t="n">
         <v>11.5</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-17 13:44:14</t>
+          <t>2026-07-17 16:08:18</t>
         </is>
       </c>
     </row>
@@ -1114,10 +1114,10 @@
         <v>1.64</v>
       </c>
       <c r="G3" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="H3" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="I3" t="n">
         <v>7.4</v>
@@ -1141,10 +1141,10 @@
         <v>1.41</v>
       </c>
       <c r="P3" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="R3" t="n">
         <v>1.26</v>
@@ -1162,7 +1162,7 @@
         <v>1.16</v>
       </c>
       <c r="W3" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="X3" t="n">
         <v>12.5</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-17 13:44:14</t>
+          <t>2026-07-17 16:08:18</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
         <v>3.9</v>
       </c>
       <c r="L4" t="n">
-        <v>1.47</v>
+        <v>1.41</v>
       </c>
       <c r="M4" t="n">
         <v>1.09</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-17 13:44:14</t>
+          <t>2026-07-17 16:08:18</t>
         </is>
       </c>
     </row>
@@ -1652,7 +1652,7 @@
         <v>1.87</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="R5" t="n">
         <v>1.32</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-17 13:44:14</t>
+          <t>2026-07-17 16:08:18</t>
         </is>
       </c>
     </row>
@@ -1891,7 +1891,7 @@
         <v>3.8</v>
       </c>
       <c r="L6" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="M6" t="n">
         <v>1.07</v>
@@ -1915,16 +1915,16 @@
         <v>3.4</v>
       </c>
       <c r="T6" t="n">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="U6" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="V6" t="n">
         <v>1.54</v>
       </c>
       <c r="W6" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="X6" t="n">
         <v>16.5</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-17 13:44:14</t>
+          <t>2026-07-17 16:08:18</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
         <v>3.75</v>
       </c>
       <c r="L7" t="n">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="M7" t="n">
         <v>1.07</v>
@@ -2172,7 +2172,7 @@
         <v>1.64</v>
       </c>
       <c r="U7" t="n">
-        <v>1.91</v>
+        <v>2.08</v>
       </c>
       <c r="V7" t="n">
         <v>1.59</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-17 13:44:14</t>
+          <t>2026-07-17 16:08:18</t>
         </is>
       </c>
     </row>
@@ -2396,7 +2396,7 @@
         <v>4.9</v>
       </c>
       <c r="K8" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="L8" t="n">
         <v>1.28</v>
@@ -2504,7 +2504,7 @@
         <v>6.4</v>
       </c>
       <c r="AU8" t="n">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AV8" t="n">
         <v>1.01</v>
@@ -2519,7 +2519,7 @@
         <v>7.6</v>
       </c>
       <c r="AZ8" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="BA8" t="n">
         <v>1.01</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-17 13:44:14</t>
+          <t>2026-07-17 16:08:18</t>
         </is>
       </c>
     </row>
@@ -2647,7 +2647,7 @@
         <v>1000</v>
       </c>
       <c r="J9" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="K9" t="n">
         <v>1000</v>
@@ -2686,7 +2686,7 @@
         <v>1.01</v>
       </c>
       <c r="W9" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X9" t="n">
         <v>1000</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-17 13:44:14</t>
+          <t>2026-07-17 16:08:18</t>
         </is>
       </c>
     </row>
@@ -2892,10 +2892,10 @@
         <v>1.57</v>
       </c>
       <c r="G10" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="H10" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="I10" t="n">
         <v>6.2</v>
@@ -2916,13 +2916,13 @@
         <v>6</v>
       </c>
       <c r="O10" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="P10" t="n">
         <v>2.72</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="R10" t="n">
         <v>1.69</v>
@@ -2931,16 +2931,16 @@
         <v>2.24</v>
       </c>
       <c r="T10" t="n">
-        <v>1.54</v>
+        <v>1.63</v>
       </c>
       <c r="U10" t="n">
-        <v>2.2</v>
+        <v>2.34</v>
       </c>
       <c r="V10" t="n">
         <v>1.19</v>
       </c>
       <c r="W10" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="X10" t="n">
         <v>34</v>
@@ -2952,10 +2952,10 @@
         <v>60</v>
       </c>
       <c r="AA10" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AB10" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AC10" t="n">
         <v>13.5</v>
@@ -2997,13 +2997,13 @@
         <v>60</v>
       </c>
       <c r="AP10" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AQ10" t="n">
         <v>21</v>
       </c>
       <c r="AR10" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AS10" t="n">
         <v>5.2</v>
@@ -3030,7 +3030,7 @@
         <v>15</v>
       </c>
       <c r="BA10" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BB10" t="n">
         <v>12.5</v>
@@ -3042,13 +3042,13 @@
         <v>19.5</v>
       </c>
       <c r="BE10" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BF10" t="n">
         <v>5.2</v>
       </c>
       <c r="BG10" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BH10" t="n">
         <v>5.4</v>
@@ -3069,10 +3069,10 @@
         <v>1.01</v>
       </c>
       <c r="BN10" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BO10" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="BP10" t="n">
         <v>11</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-17 13:44:14</t>
+          <t>2026-07-17 16:08:18</t>
         </is>
       </c>
     </row>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-17 13:44:14</t>
+          <t>2026-07-17 16:08:18</t>
         </is>
       </c>
     </row>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-17 13:44:14</t>
+          <t>2026-07-17 16:08:18</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
         <v>1.25</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="R13" t="n">
         <v>1.18</v>
@@ -3702,7 +3702,7 @@
         <v>1.01</v>
       </c>
       <c r="W13" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X13" t="n">
         <v>1000</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-17 13:44:14</t>
+          <t>2026-07-17 16:08:18</t>
         </is>
       </c>
     </row>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-17 13:44:14</t>
+          <t>2026-07-17 16:08:18</t>
         </is>
       </c>
     </row>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-17 13:44:14</t>
+          <t>2026-07-17 16:08:18</t>
         </is>
       </c>
     </row>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-17 13:44:14</t>
+          <t>2026-07-17 16:08:18</t>
         </is>
       </c>
     </row>
@@ -4685,13 +4685,13 @@
         <v>3.55</v>
       </c>
       <c r="L17" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="M17" t="n">
         <v>1.11</v>
       </c>
       <c r="N17" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="O17" t="n">
         <v>1.52</v>
@@ -4706,7 +4706,7 @@
         <v>1.17</v>
       </c>
       <c r="S17" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="T17" t="n">
         <v>1.11</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-17 13:44:14</t>
+          <t>2026-07-17 16:08:18</t>
         </is>
       </c>
     </row>
@@ -4924,7 +4924,7 @@
         <v>1.85</v>
       </c>
       <c r="G18" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="H18" t="n">
         <v>4</v>
@@ -4945,16 +4945,16 @@
         <v>1.01</v>
       </c>
       <c r="N18" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="O18" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P18" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="R18" t="n">
         <v>1.37</v>
@@ -4972,7 +4972,7 @@
         <v>1.29</v>
       </c>
       <c r="W18" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="X18" t="n">
         <v>28</v>
@@ -4999,7 +4999,7 @@
         <v>70</v>
       </c>
       <c r="AF18" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AG18" t="n">
         <v>15.5</v>
@@ -5020,7 +5020,7 @@
         <v>46</v>
       </c>
       <c r="AM18" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AN18" t="n">
         <v>15.5</v>
@@ -5029,58 +5029,58 @@
         <v>1000</v>
       </c>
       <c r="AP18" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="AQ18" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="AR18" t="n">
-        <v>2.48</v>
+        <v>2.42</v>
       </c>
       <c r="AS18" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="AT18" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AX18" t="n">
         <v>2.24</v>
       </c>
-      <c r="AU18" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>9.199999999999999</v>
-      </c>
       <c r="AY18" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="AZ18" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="BB18" t="n">
         <v>2.36</v>
       </c>
-      <c r="BA18" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>2.4</v>
-      </c>
       <c r="BC18" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="BD18" t="n">
-        <v>2.48</v>
+        <v>2.42</v>
       </c>
       <c r="BE18" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="BF18" t="n">
         <v>6.6</v>
       </c>
       <c r="BG18" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="BH18" t="n">
         <v>1000</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-17 13:44:14</t>
+          <t>2026-07-17 16:08:18</t>
         </is>
       </c>
     </row>
@@ -5175,16 +5175,16 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="G19" t="n">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="H19" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="I19" t="n">
-        <v>2.7</v>
+        <v>2.78</v>
       </c>
       <c r="J19" t="n">
         <v>3.6</v>
@@ -5199,13 +5199,13 @@
         <v>1.01</v>
       </c>
       <c r="N19" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="O19" t="n">
         <v>1.24</v>
       </c>
       <c r="P19" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="Q19" t="n">
         <v>1.71</v>
@@ -5214,19 +5214,19 @@
         <v>1.37</v>
       </c>
       <c r="S19" t="n">
-        <v>2.48</v>
+        <v>2.68</v>
       </c>
       <c r="T19" t="n">
         <v>1.45</v>
       </c>
       <c r="U19" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="V19" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="W19" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="X19" t="n">
         <v>28</v>
@@ -5241,13 +5241,13 @@
         <v>50</v>
       </c>
       <c r="AB19" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AC19" t="n">
         <v>12.5</v>
       </c>
       <c r="AD19" t="n">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="AE19" t="n">
         <v>38</v>
@@ -5265,13 +5265,13 @@
         <v>50</v>
       </c>
       <c r="AJ19" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AK19" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AL19" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AM19" t="n">
         <v>100</v>
@@ -5283,76 +5283,76 @@
         <v>1000</v>
       </c>
       <c r="AP19" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AQ19" t="n">
         <v>2.16</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>2.08</v>
       </c>
       <c r="AR19" t="n">
         <v>12.5</v>
       </c>
       <c r="AS19" t="n">
-        <v>2.22</v>
+        <v>24</v>
       </c>
       <c r="AT19" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AU19" t="n">
-        <v>1.97</v>
+        <v>7</v>
       </c>
       <c r="AV19" t="n">
-        <v>2.06</v>
+        <v>9.4</v>
       </c>
       <c r="AW19" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>16</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AZ19" t="n">
         <v>2.2</v>
       </c>
-      <c r="AX19" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>2.12</v>
-      </c>
       <c r="BA19" t="n">
-        <v>2.22</v>
+        <v>2.32</v>
       </c>
       <c r="BB19" t="n">
-        <v>2.26</v>
+        <v>2.34</v>
       </c>
       <c r="BC19" t="n">
         <v>20</v>
       </c>
       <c r="BD19" t="n">
-        <v>2.24</v>
+        <v>2.32</v>
       </c>
       <c r="BE19" t="n">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="BF19" t="n">
-        <v>2.34</v>
+        <v>2.44</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.34</v>
+        <v>2.44</v>
       </c>
       <c r="BH19" t="n">
         <v>1000</v>
       </c>
       <c r="BI19" t="n">
-        <v>1.04</v>
+        <v>1.88</v>
       </c>
       <c r="BJ19" t="n">
         <v>13</v>
       </c>
       <c r="BK19" t="n">
-        <v>1.04</v>
+        <v>1.64</v>
       </c>
       <c r="BL19" t="n">
         <v>1000</v>
       </c>
       <c r="BM19" t="n">
-        <v>1.04</v>
+        <v>1.88</v>
       </c>
       <c r="BN19" t="n">
         <v>8.800000000000001</v>
@@ -5364,13 +5364,13 @@
         <v>30</v>
       </c>
       <c r="BQ19" t="n">
-        <v>1.04</v>
+        <v>1.77</v>
       </c>
       <c r="BR19" t="n">
         <v>44</v>
       </c>
       <c r="BS19" t="n">
-        <v>1.04</v>
+        <v>1.8</v>
       </c>
       <c r="BT19" t="n">
         <v>8</v>
@@ -5382,23 +5382,23 @@
         <v>26</v>
       </c>
       <c r="BW19" t="n">
-        <v>1.04</v>
+        <v>1.75</v>
       </c>
       <c r="BX19" t="n">
         <v>40</v>
       </c>
       <c r="BY19" t="n">
-        <v>1.04</v>
+        <v>1.8</v>
       </c>
       <c r="BZ19" t="n">
         <v>30</v>
       </c>
       <c r="CA19" t="n">
-        <v>1.04</v>
+        <v>1.77</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-17 13:44:14</t>
+          <t>2026-07-17 16:08:18</t>
         </is>
       </c>
     </row>
@@ -5441,7 +5441,7 @@
         <v>1000</v>
       </c>
       <c r="J20" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="K20" t="n">
         <v>1000</v>
@@ -5453,13 +5453,13 @@
         <v>1.01</v>
       </c>
       <c r="N20" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O20" t="n">
         <v>1.16</v>
       </c>
       <c r="P20" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="Q20" t="n">
         <v>1.16</v>
@@ -5471,16 +5471,16 @@
         <v>1.16</v>
       </c>
       <c r="T20" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U20" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V20" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W20" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X20" t="n">
         <v>1000</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-17 13:44:14</t>
+          <t>2026-07-17 16:08:18</t>
         </is>
       </c>
     </row>
@@ -5743,7 +5743,7 @@
         <v>17</v>
       </c>
       <c r="Z21" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AA21" t="n">
         <v>100</v>
@@ -5830,7 +5830,7 @@
         <v>22</v>
       </c>
       <c r="BC21" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BD21" t="n">
         <v>32</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-07-17 13:44:14</t>
+          <t>2026-07-17 16:08:18</t>
         </is>
       </c>
     </row>
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="G22" t="n">
         <v>1000</v>
@@ -5946,10 +5946,10 @@
         <v>1.04</v>
       </c>
       <c r="I22" t="n">
-        <v>1.98</v>
+        <v>1000</v>
       </c>
       <c r="J22" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="K22" t="n">
         <v>1000</v>
@@ -5961,13 +5961,13 @@
         <v>1.01</v>
       </c>
       <c r="N22" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="O22" t="n">
         <v>1.2</v>
       </c>
       <c r="P22" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Q22" t="n">
         <v>1.2</v>
@@ -5979,13 +5979,13 @@
         <v>1.2</v>
       </c>
       <c r="T22" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U22" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V22" t="n">
-        <v>2.02</v>
+        <v>1.01</v>
       </c>
       <c r="W22" t="n">
         <v>1.01</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-07-17 13:44:14</t>
+          <t>2026-07-17 16:08:18</t>
         </is>
       </c>
     </row>
@@ -6215,7 +6215,7 @@
         <v>1.02</v>
       </c>
       <c r="N23" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="O23" t="n">
         <v>1.11</v>
@@ -6233,10 +6233,10 @@
         <v>1.11</v>
       </c>
       <c r="T23" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U23" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V23" t="n">
         <v>1.01</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-07-17 13:44:14</t>
+          <t>2026-07-17 16:08:18</t>
         </is>
       </c>
     </row>
@@ -6463,13 +6463,13 @@
         <v>4.8</v>
       </c>
       <c r="L24" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="M24" t="n">
         <v>1.03</v>
       </c>
       <c r="N24" t="n">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="O24" t="n">
         <v>1.16</v>
@@ -6481,10 +6481,10 @@
         <v>1.54</v>
       </c>
       <c r="R24" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="S24" t="n">
-        <v>2.12</v>
+        <v>2.36</v>
       </c>
       <c r="T24" t="n">
         <v>1.54</v>
@@ -6514,7 +6514,7 @@
         <v>34</v>
       </c>
       <c r="AC24" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AD24" t="n">
         <v>11</v>
@@ -6589,86 +6589,86 @@
         <v>20</v>
       </c>
       <c r="BB24" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BC24" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BD24" t="n">
         <v>42</v>
       </c>
       <c r="BE24" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BF24" t="n">
         <v>36</v>
       </c>
       <c r="BG24" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="BH24" t="n">
         <v>1000</v>
       </c>
       <c r="BI24" t="n">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="BJ24" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BK24" t="n">
-        <v>1.01</v>
+        <v>1.74</v>
       </c>
       <c r="BL24" t="n">
         <v>1000</v>
       </c>
       <c r="BM24" t="n">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="BN24" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BO24" t="n">
-        <v>1.01</v>
+        <v>1.74</v>
       </c>
       <c r="BP24" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BQ24" t="n">
-        <v>1.01</v>
+        <v>1.93</v>
       </c>
       <c r="BR24" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BS24" t="n">
-        <v>1.01</v>
+        <v>1.93</v>
       </c>
       <c r="BT24" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BU24" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="BV24" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="BW24" t="n">
-        <v>1.01</v>
+        <v>1.77</v>
       </c>
       <c r="BX24" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BY24" t="n">
-        <v>1.01</v>
+        <v>1.88</v>
       </c>
       <c r="BZ24" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="CA24" t="n">
-        <v>1.01</v>
+        <v>1.81</v>
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-07-17 13:44:14</t>
+          <t>2026-07-17 16:08:18</t>
         </is>
       </c>
     </row>
@@ -6717,34 +6717,34 @@
         <v>4.1</v>
       </c>
       <c r="L25" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="M25" t="n">
         <v>1.04</v>
       </c>
       <c r="N25" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="O25" t="n">
         <v>1.24</v>
       </c>
       <c r="P25" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="R25" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="S25" t="n">
-        <v>2.58</v>
+        <v>2.74</v>
       </c>
       <c r="T25" t="n">
-        <v>1.54</v>
+        <v>1.63</v>
       </c>
       <c r="U25" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V25" t="n">
         <v>1.92</v>
@@ -6789,7 +6789,7 @@
         <v>1000</v>
       </c>
       <c r="AJ25" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AK25" t="n">
         <v>1000</v>
@@ -6807,58 +6807,58 @@
         <v>1000</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AR25" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AS25" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AT25" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AU25" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AV25" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AW25" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AX25" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AY25" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AZ25" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="BA25" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="BB25" t="n">
         <v>1.02</v>
       </c>
       <c r="BC25" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="BD25" t="n">
         <v>1.01</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="BG25" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="BH25" t="n">
         <v>1000</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-07-17 13:44:14</t>
+          <t>2026-07-17 16:08:18</t>
         </is>
       </c>
     </row>
@@ -6977,7 +6977,7 @@
         <v>1.03</v>
       </c>
       <c r="N26" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="O26" t="n">
         <v>1.19</v>
@@ -6989,10 +6989,10 @@
         <v>1.54</v>
       </c>
       <c r="R26" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="S26" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="T26" t="n">
         <v>1.99</v>
@@ -7061,7 +7061,7 @@
         <v>250</v>
       </c>
       <c r="AP26" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="AQ26" t="n">
         <v>5</v>
@@ -7091,7 +7091,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ26" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="BA26" t="n">
         <v>5.4</v>
@@ -7103,7 +7103,7 @@
         <v>11.5</v>
       </c>
       <c r="BD26" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="BE26" t="n">
         <v>5.4</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-07-17 13:44:14</t>
+          <t>2026-07-17 16:08:18</t>
         </is>
       </c>
     </row>
@@ -7207,7 +7207,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.98</v>
+        <v>3.2</v>
       </c>
       <c r="G27" t="n">
         <v>1000</v>
@@ -7216,22 +7216,22 @@
         <v>1.26</v>
       </c>
       <c r="I27" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J27" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="K27" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="L27" t="n">
-        <v>1.23</v>
+        <v>1.01</v>
       </c>
       <c r="M27" t="n">
         <v>1.01</v>
       </c>
       <c r="N27" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="O27" t="n">
         <v>1.15</v>
@@ -7249,13 +7249,13 @@
         <v>1.14</v>
       </c>
       <c r="T27" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U27" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V27" t="n">
-        <v>1.01</v>
+        <v>1.74</v>
       </c>
       <c r="W27" t="n">
         <v>1.01</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-07-17 13:44:14</t>
+          <t>2026-07-17 16:08:18</t>
         </is>
       </c>
     </row>
@@ -7479,10 +7479,10 @@
         <v>4.8</v>
       </c>
       <c r="L28" t="n">
-        <v>1.31</v>
+        <v>1.01</v>
       </c>
       <c r="M28" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N28" t="n">
         <v>2.28</v>
@@ -7491,10 +7491,10 @@
         <v>1.23</v>
       </c>
       <c r="P28" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="R28" t="n">
         <v>1.37</v>
@@ -7503,10 +7503,10 @@
         <v>2.52</v>
       </c>
       <c r="T28" t="n">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="U28" t="n">
-        <v>1.01</v>
+        <v>1.75</v>
       </c>
       <c r="V28" t="n">
         <v>2.5</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-07-17 13:44:14</t>
+          <t>2026-07-17 16:08:18</t>
         </is>
       </c>
     </row>
@@ -7715,22 +7715,22 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="G29" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="H29" t="n">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="I29" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="J29" t="n">
-        <v>2.84</v>
+        <v>3.05</v>
       </c>
       <c r="K29" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L29" t="n">
         <v>1.01</v>
@@ -7739,34 +7739,34 @@
         <v>1.01</v>
       </c>
       <c r="N29" t="n">
-        <v>1.67</v>
+        <v>2.56</v>
       </c>
       <c r="O29" t="n">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="P29" t="n">
         <v>1.67</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="R29" t="n">
         <v>1.18</v>
       </c>
       <c r="S29" t="n">
-        <v>2.2</v>
+        <v>2.92</v>
       </c>
       <c r="T29" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U29" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V29" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="W29" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="X29" t="n">
         <v>1000</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-07-17 13:44:14</t>
+          <t>2026-07-17 16:08:18</t>
         </is>
       </c>
     </row>
@@ -7987,13 +7987,13 @@
         <v>3.6</v>
       </c>
       <c r="L30" t="n">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="M30" t="n">
         <v>1.12</v>
       </c>
       <c r="N30" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="O30" t="n">
         <v>1.56</v>
@@ -8014,7 +8014,7 @@
         <v>2.12</v>
       </c>
       <c r="U30" t="n">
-        <v>1.52</v>
+        <v>1.63</v>
       </c>
       <c r="V30" t="n">
         <v>2.18</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-07-17 13:44:14</t>
+          <t>2026-07-17 16:08:18</t>
         </is>
       </c>
     </row>
@@ -8235,7 +8235,7 @@
         <v>1.74</v>
       </c>
       <c r="J31" t="n">
-        <v>3.95</v>
+        <v>4.5</v>
       </c>
       <c r="K31" t="n">
         <v>5.3</v>
@@ -8244,7 +8244,7 @@
         <v>1.01</v>
       </c>
       <c r="M31" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N31" t="n">
         <v>2.68</v>
@@ -8265,10 +8265,10 @@
         <v>2</v>
       </c>
       <c r="T31" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="U31" t="n">
-        <v>1.01</v>
+        <v>1.98</v>
       </c>
       <c r="V31" t="n">
         <v>2.34</v>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-07-17 13:44:14</t>
+          <t>2026-07-17 16:08:18</t>
         </is>
       </c>
     </row>
@@ -8477,166 +8477,166 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1.22</v>
+        <v>1.66</v>
       </c>
       <c r="G32" t="n">
-        <v>2</v>
+        <v>1.77</v>
       </c>
       <c r="H32" t="n">
-        <v>1.04</v>
+        <v>5.6</v>
       </c>
       <c r="I32" t="n">
-        <v>9.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="J32" t="n">
-        <v>2.56</v>
+        <v>3.7</v>
       </c>
       <c r="K32" t="n">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="L32" t="n">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="M32" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N32" t="n">
-        <v>1.64</v>
+        <v>3.35</v>
       </c>
       <c r="O32" t="n">
         <v>1.35</v>
       </c>
       <c r="P32" t="n">
-        <v>1.64</v>
+        <v>1.79</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="R32" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="S32" t="n">
-        <v>1.86</v>
+        <v>3.7</v>
       </c>
       <c r="T32" t="n">
-        <v>1.01</v>
+        <v>1.96</v>
       </c>
       <c r="U32" t="n">
-        <v>1.01</v>
+        <v>1.84</v>
       </c>
       <c r="V32" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="W32" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="X32" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="Y32" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Z32" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AA32" t="n">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AB32" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AC32" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AD32" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AE32" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AF32" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AG32" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH32" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AI32" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AJ32" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AK32" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AL32" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AM32" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AN32" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AO32" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AP32" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ32" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AR32" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AS32" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AT32" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="AU32" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="AV32" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="AW32" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AX32" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AY32" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AZ32" t="n">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="BA32" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BB32" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BC32" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BD32" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BE32" t="n">
-        <v>40</v>
+        <v>4.2</v>
       </c>
       <c r="BF32" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BG32" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BH32" t="n">
         <v>1000</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-07-17 13:44:14</t>
+          <t>2026-07-17 16:08:18</t>
         </is>
       </c>
     </row>
@@ -8737,13 +8737,13 @@
         <v>2.3</v>
       </c>
       <c r="H33" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="I33" t="n">
         <v>3.9</v>
       </c>
       <c r="J33" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="K33" t="n">
         <v>4.5</v>
@@ -8752,31 +8752,31 @@
         <v>1.01</v>
       </c>
       <c r="M33" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N33" t="n">
-        <v>2.06</v>
+        <v>1.1</v>
       </c>
       <c r="O33" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="P33" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.66</v>
+        <v>1.74</v>
       </c>
       <c r="R33" t="n">
-        <v>1.18</v>
+        <v>1.41</v>
       </c>
       <c r="S33" t="n">
         <v>2.5</v>
       </c>
       <c r="T33" t="n">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="U33" t="n">
-        <v>1.01</v>
+        <v>1.91</v>
       </c>
       <c r="V33" t="n">
         <v>1.34</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-07-17 13:44:14</t>
+          <t>2026-07-17 16:08:18</t>
         </is>
       </c>
     </row>
@@ -9009,7 +9009,7 @@
         <v>1.01</v>
       </c>
       <c r="N34" t="n">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="O34" t="n">
         <v>1.01</v>
@@ -9024,13 +9024,13 @@
         <v>1.24</v>
       </c>
       <c r="S34" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="T34" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U34" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V34" t="n">
         <v>1.01</v>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-07-17 13:44:14</t>
+          <t>2026-07-17 16:08:18</t>
         </is>
       </c>
     </row>
@@ -9263,13 +9263,13 @@
         <v>1.01</v>
       </c>
       <c r="N35" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O35" t="n">
         <v>1.15</v>
       </c>
       <c r="P35" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q35" t="n">
         <v>1.15</v>
@@ -9281,10 +9281,10 @@
         <v>1.15</v>
       </c>
       <c r="T35" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U35" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V35" t="n">
         <v>1.01</v>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-07-17 13:44:14</t>
+          <t>2026-07-17 16:08:18</t>
         </is>
       </c>
     </row>
@@ -9499,7 +9499,7 @@
         <v>1.79</v>
       </c>
       <c r="H36" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="I36" t="n">
         <v>1000</v>
@@ -9535,10 +9535,10 @@
         <v>1.27</v>
       </c>
       <c r="T36" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U36" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V36" t="n">
         <v>1.01</v>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-07-17 13:44:14</t>
+          <t>2026-07-17 16:08:18</t>
         </is>
       </c>
     </row>
@@ -9747,16 +9747,16 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>2.76</v>
+        <v>2.88</v>
       </c>
       <c r="G37" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="H37" t="n">
         <v>2.88</v>
       </c>
       <c r="I37" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="J37" t="n">
         <v>2.8</v>
@@ -9765,16 +9765,16 @@
         <v>3.25</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="P37" t="n">
         <v>1.5</v>
@@ -9783,194 +9783,194 @@
         <v>2.62</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH37" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI37" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ37" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK37" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL37" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM37" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN37" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO37" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP37" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ37" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AR37" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AS37" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AT37" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AU37" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AV37" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AW37" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AX37" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AY37" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AZ37" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BA37" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BB37" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BC37" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BD37" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BE37" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BF37" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BG37" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BH37" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI37" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="BJ37" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BK37" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="BL37" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM37" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="BN37" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BO37" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="BP37" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BQ37" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="BR37" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS37" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="BT37" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU37" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="BV37" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="BW37" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BX37" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY37" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="BZ37" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA37" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-07-17 13:44:14</t>
+          <t>2026-07-17 16:08:18</t>
         </is>
       </c>
     </row>
@@ -10013,19 +10013,19 @@
         <v>2.18</v>
       </c>
       <c r="J38" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="K38" t="n">
         <v>3.5</v>
       </c>
       <c r="L38" t="n">
-        <v>1.47</v>
+        <v>1.01</v>
       </c>
       <c r="M38" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N38" t="n">
-        <v>1.65</v>
+        <v>2.84</v>
       </c>
       <c r="O38" t="n">
         <v>1.42</v>
@@ -10037,16 +10037,16 @@
         <v>2.26</v>
       </c>
       <c r="R38" t="n">
-        <v>1.05</v>
+        <v>1.24</v>
       </c>
       <c r="S38" t="n">
-        <v>2.26</v>
+        <v>4.3</v>
       </c>
       <c r="T38" t="n">
-        <v>1.01</v>
+        <v>1.83</v>
       </c>
       <c r="U38" t="n">
-        <v>1.01</v>
+        <v>1.76</v>
       </c>
       <c r="V38" t="n">
         <v>1.84</v>
@@ -10224,7 +10224,7 @@
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-07-17 13:44:14</t>
+          <t>2026-07-17 16:08:18</t>
         </is>
       </c>
     </row>
@@ -10258,13 +10258,13 @@
         <v>3.25</v>
       </c>
       <c r="G39" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="H39" t="n">
         <v>2.32</v>
       </c>
       <c r="I39" t="n">
-        <v>2.78</v>
+        <v>2.62</v>
       </c>
       <c r="J39" t="n">
         <v>3</v>
@@ -10273,212 +10273,212 @@
         <v>3.8</v>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="P39" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="Q39" t="n">
         <v>2.28</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH39" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI39" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ39" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK39" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL39" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM39" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN39" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO39" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH39" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ39" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL39" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN39" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP39" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR39" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT39" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV39" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX39" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ39" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-07-17 13:44:14</t>
+          <t>2026-07-17 16:08:18</t>
         </is>
       </c>
     </row>
@@ -10527,202 +10527,202 @@
         <v>1000</v>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="P40" t="n">
         <v>1.07</v>
       </c>
       <c r="Q40" t="n">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF40" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG40" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH40" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI40" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ40" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK40" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL40" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM40" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN40" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO40" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP40" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ40" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR40" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS40" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT40" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU40" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV40" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW40" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX40" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY40" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ40" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA40" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB40" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC40" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD40" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE40" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF40" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG40" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH40" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI40" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ40" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK40" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL40" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM40" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN40" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO40" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP40" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ40" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR40" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS40" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT40" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU40" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV40" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW40" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX40" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY40" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ40" t="n">
         <v>0</v>
@@ -10732,7 +10732,7 @@
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-07-17 13:44:14</t>
+          <t>2026-07-17 16:08:18</t>
         </is>
       </c>
     </row>
@@ -10766,31 +10766,31 @@
         <v>1.58</v>
       </c>
       <c r="G41" t="n">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="H41" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="I41" t="n">
         <v>7.6</v>
       </c>
       <c r="J41" t="n">
-        <v>3.4</v>
+        <v>3.85</v>
       </c>
       <c r="K41" t="n">
         <v>5.5</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="P41" t="n">
         <v>1.98</v>
@@ -10799,184 +10799,184 @@
         <v>1.6</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD41" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE41" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF41" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG41" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH41" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI41" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ41" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK41" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL41" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM41" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN41" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO41" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP41" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ41" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR41" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS41" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT41" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU41" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV41" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW41" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX41" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY41" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ41" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA41" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB41" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC41" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD41" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE41" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF41" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG41" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH41" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI41" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ41" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK41" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL41" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM41" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN41" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO41" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP41" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ41" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR41" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS41" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT41" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU41" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV41" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW41" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX41" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY41" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ41" t="n">
         <v>0</v>
@@ -10986,7 +10986,7 @@
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-07-17 13:44:14</t>
+          <t>2026-07-17 16:08:18</t>
         </is>
       </c>
     </row>
@@ -11023,7 +11023,7 @@
         <v>2.14</v>
       </c>
       <c r="H42" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="I42" t="n">
         <v>5.6</v>
@@ -11032,19 +11032,19 @@
         <v>3.15</v>
       </c>
       <c r="K42" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="P42" t="n">
         <v>1.68</v>
@@ -11053,184 +11053,184 @@
         <v>2.06</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ42" t="n">
         <v>0</v>
@@ -11240,7 +11240,7 @@
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-07-17 13:44:14</t>
+          <t>2026-07-17 16:08:18</t>
         </is>
       </c>
     </row>
@@ -11271,22 +11271,22 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="G43" t="n">
-        <v>2.62</v>
+        <v>2.48</v>
       </c>
       <c r="H43" t="n">
-        <v>2.92</v>
+        <v>3.65</v>
       </c>
       <c r="I43" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="J43" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="K43" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
@@ -11301,10 +11301,10 @@
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="Q43" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="R43" t="n">
         <v>0</v>
@@ -11494,7 +11494,7 @@
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-07-17 13:44:14</t>
+          <t>2026-07-17 16:08:18</t>
         </is>
       </c>
     </row>
@@ -11748,7 +11748,7 @@
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-07-17 13:44:14</t>
+          <t>2026-07-17 16:08:18</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-19.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-19.xlsx
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="G2" t="n">
         <v>4.3</v>
@@ -866,7 +866,7 @@
         <v>2.02</v>
       </c>
       <c r="I2" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="J2" t="n">
         <v>3.55</v>
@@ -875,19 +875,19 @@
         <v>3.85</v>
       </c>
       <c r="L2" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="M2" t="n">
         <v>1.07</v>
       </c>
       <c r="N2" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="O2" t="n">
         <v>1.31</v>
       </c>
       <c r="P2" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="Q2" t="n">
         <v>1.9</v>
@@ -905,7 +905,7 @@
         <v>2.12</v>
       </c>
       <c r="V2" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="W2" t="n">
         <v>1.31</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-17 16:08:18</t>
+          <t>2026-07-17 18:30:45</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
         <v>1.64</v>
       </c>
       <c r="G3" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="H3" t="n">
         <v>6.4</v>
@@ -1129,40 +1129,40 @@
         <v>4.2</v>
       </c>
       <c r="L3" t="n">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="M3" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N3" t="n">
-        <v>3.15</v>
+        <v>2.88</v>
       </c>
       <c r="O3" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="P3" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="Q3" t="n">
         <v>2.16</v>
       </c>
       <c r="R3" t="n">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>2.1</v>
       </c>
       <c r="T3" t="n">
-        <v>2.12</v>
+        <v>2.04</v>
       </c>
       <c r="U3" t="n">
-        <v>1.77</v>
+        <v>1.67</v>
       </c>
       <c r="V3" t="n">
         <v>1.16</v>
       </c>
       <c r="W3" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="X3" t="n">
         <v>12.5</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-17 16:08:18</t>
+          <t>2026-07-17 18:30:45</t>
         </is>
       </c>
     </row>
@@ -1365,10 +1365,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>5.3</v>
+        <v>4.4</v>
       </c>
       <c r="G4" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="H4" t="n">
         <v>1.77</v>
@@ -1380,10 +1380,10 @@
         <v>3.6</v>
       </c>
       <c r="K4" t="n">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="L4" t="n">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="M4" t="n">
         <v>1.09</v>
@@ -1395,22 +1395,22 @@
         <v>1.41</v>
       </c>
       <c r="P4" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="R4" t="n">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="S4" t="n">
-        <v>4.2</v>
+        <v>2.08</v>
       </c>
       <c r="T4" t="n">
-        <v>2.06</v>
+        <v>1.96</v>
       </c>
       <c r="U4" t="n">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="V4" t="n">
         <v>2.22</v>
@@ -1419,176 +1419,176 @@
         <v>1.2</v>
       </c>
       <c r="X4" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="Y4" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="Z4" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AA4" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AC4" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="AD4" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AE4" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AF4" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AG4" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AH4" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AI4" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>190</v>
+        <v>1000</v>
       </c>
       <c r="AK4" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AL4" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AM4" t="n">
-        <v>190</v>
+        <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AO4" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AQ4" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AR4" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AS4" t="n">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="AT4" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="AU4" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV4" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AW4" t="n">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="AX4" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="AY4" t="n">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ4" t="n">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="BA4" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BB4" t="n">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="BC4" t="n">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="BD4" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BE4" t="n">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="BF4" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BG4" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH4" t="n">
-        <v>3.45</v>
+        <v>1000</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.58</v>
+        <v>1.01</v>
       </c>
       <c r="BJ4" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="BK4" t="n">
         <v>1.01</v>
       </c>
       <c r="BL4" t="n">
-        <v>210</v>
+        <v>1000</v>
       </c>
       <c r="BM4" t="n">
         <v>1.01</v>
       </c>
       <c r="BN4" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BO4" t="n">
         <v>1.01</v>
       </c>
       <c r="BP4" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="BQ4" t="n">
         <v>1.01</v>
       </c>
       <c r="BR4" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="BS4" t="n">
         <v>1.01</v>
       </c>
       <c r="BT4" t="n">
-        <v>4.7</v>
+        <v>1000</v>
       </c>
       <c r="BU4" t="n">
-        <v>3.4</v>
+        <v>1.01</v>
       </c>
       <c r="BV4" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="BW4" t="n">
         <v>1.01</v>
       </c>
       <c r="BX4" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BY4" t="n">
         <v>1.01</v>
       </c>
       <c r="BZ4" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="CA4" t="n">
         <v>1.01</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-17 16:08:18</t>
+          <t>2026-07-17 18:30:45</t>
         </is>
       </c>
     </row>
@@ -1619,118 +1619,118 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.78</v>
+        <v>1.04</v>
       </c>
       <c r="G5" t="n">
-        <v>1.94</v>
+        <v>1000</v>
       </c>
       <c r="H5" t="n">
-        <v>4.6</v>
+        <v>1.04</v>
       </c>
       <c r="I5" t="n">
-        <v>5.5</v>
+        <v>1000</v>
       </c>
       <c r="J5" t="n">
-        <v>3.75</v>
+        <v>1.01</v>
       </c>
       <c r="K5" t="n">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="L5" t="n">
-        <v>1.36</v>
+        <v>1.01</v>
       </c>
       <c r="M5" t="n">
         <v>1.07</v>
       </c>
       <c r="N5" t="n">
-        <v>3.5</v>
+        <v>1.88</v>
       </c>
       <c r="O5" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="P5" t="n">
-        <v>1.87</v>
+        <v>1.25</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.95</v>
+        <v>1.31</v>
       </c>
       <c r="R5" t="n">
-        <v>1.32</v>
+        <v>1.18</v>
       </c>
       <c r="S5" t="n">
-        <v>3.5</v>
+        <v>1.05</v>
       </c>
       <c r="T5" t="n">
-        <v>1.76</v>
+        <v>1.11</v>
       </c>
       <c r="U5" t="n">
-        <v>1.86</v>
+        <v>1.11</v>
       </c>
       <c r="V5" t="n">
-        <v>1.22</v>
+        <v>1.01</v>
       </c>
       <c r="W5" t="n">
-        <v>2.06</v>
+        <v>1.01</v>
       </c>
       <c r="X5" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="Y5" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="Z5" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AA5" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="AC5" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AD5" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AE5" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AF5" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AG5" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AH5" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AI5" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AK5" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AL5" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AM5" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AO5" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ5" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR5" t="n">
         <v>1.01</v>
@@ -1739,34 +1739,34 @@
         <v>1.01</v>
       </c>
       <c r="AT5" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AU5" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AV5" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="AW5" t="n">
         <v>1.01</v>
       </c>
       <c r="AX5" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AY5" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AZ5" t="n">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="BA5" t="n">
         <v>1.01</v>
       </c>
       <c r="BB5" t="n">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="BC5" t="n">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="BD5" t="n">
         <v>1.01</v>
@@ -1775,64 +1775,64 @@
         <v>1.01</v>
       </c>
       <c r="BF5" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BG5" t="n">
         <v>1.01</v>
       </c>
       <c r="BH5" t="n">
-        <v>3.75</v>
+        <v>1000</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.78</v>
+        <v>1.04</v>
       </c>
       <c r="BJ5" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BK5" t="n">
-        <v>4.2</v>
+        <v>1.04</v>
       </c>
       <c r="BL5" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>6.2</v>
+        <v>1.04</v>
       </c>
       <c r="BN5" t="n">
-        <v>4.6</v>
+        <v>1000</v>
       </c>
       <c r="BO5" t="n">
-        <v>3.6</v>
+        <v>1.04</v>
       </c>
       <c r="BP5" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>4.5</v>
+        <v>1.04</v>
       </c>
       <c r="BR5" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>5.4</v>
+        <v>1.04</v>
       </c>
       <c r="BT5" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="BU5" t="n">
-        <v>3.85</v>
+        <v>1.04</v>
       </c>
       <c r="BV5" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>5.7</v>
+        <v>1.04</v>
       </c>
       <c r="BX5" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>5.9</v>
+        <v>1.04</v>
       </c>
       <c r="BZ5" t="n">
         <v>0</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-17 16:08:18</t>
+          <t>2026-07-17 18:30:45</t>
         </is>
       </c>
     </row>
@@ -1873,145 +1873,145 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.76</v>
+        <v>1.04</v>
       </c>
       <c r="G6" t="n">
-        <v>3.2</v>
+        <v>1000</v>
       </c>
       <c r="H6" t="n">
-        <v>2.48</v>
+        <v>1.04</v>
       </c>
       <c r="I6" t="n">
-        <v>2.84</v>
+        <v>1000</v>
       </c>
       <c r="J6" t="n">
-        <v>3.3</v>
+        <v>1.02</v>
       </c>
       <c r="K6" t="n">
-        <v>3.8</v>
+        <v>1000</v>
       </c>
       <c r="L6" t="n">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="M6" t="n">
         <v>1.07</v>
       </c>
       <c r="N6" t="n">
-        <v>3.55</v>
+        <v>1.34</v>
       </c>
       <c r="O6" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="P6" t="n">
-        <v>1.87</v>
+        <v>1.34</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.94</v>
+        <v>1.33</v>
       </c>
       <c r="R6" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S6" t="n">
         <v>1.33</v>
       </c>
-      <c r="S6" t="n">
-        <v>3.4</v>
-      </c>
       <c r="T6" t="n">
-        <v>1.73</v>
+        <v>1.11</v>
       </c>
       <c r="U6" t="n">
-        <v>2.12</v>
+        <v>1.11</v>
       </c>
       <c r="V6" t="n">
-        <v>1.54</v>
+        <v>1.01</v>
       </c>
       <c r="W6" t="n">
-        <v>1.46</v>
+        <v>1.01</v>
       </c>
       <c r="X6" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="Y6" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="Z6" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AA6" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AC6" t="n">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AD6" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AE6" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AF6" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AG6" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AH6" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AI6" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AJ6" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AK6" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AL6" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AM6" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AO6" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ6" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AR6" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="AS6" t="n">
         <v>1.01</v>
       </c>
       <c r="AT6" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AU6" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AV6" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AW6" t="n">
         <v>1.01</v>
       </c>
       <c r="AX6" t="n">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY6" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AZ6" t="n">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="BA6" t="n">
         <v>1.01</v>
@@ -2032,61 +2032,61 @@
         <v>1.01</v>
       </c>
       <c r="BG6" t="n">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH6" t="n">
-        <v>3.5</v>
+        <v>1000</v>
       </c>
       <c r="BI6" t="n">
-        <v>3</v>
+        <v>1.04</v>
       </c>
       <c r="BJ6" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BK6" t="n">
-        <v>4.4</v>
+        <v>1.04</v>
       </c>
       <c r="BL6" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>7</v>
+        <v>1.04</v>
       </c>
       <c r="BN6" t="n">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="BO6" t="n">
-        <v>4.7</v>
+        <v>1.04</v>
       </c>
       <c r="BP6" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5.8</v>
+        <v>1.04</v>
       </c>
       <c r="BR6" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>6.2</v>
+        <v>1.04</v>
       </c>
       <c r="BT6" t="n">
-        <v>5.8</v>
+        <v>1000</v>
       </c>
       <c r="BU6" t="n">
-        <v>4.4</v>
+        <v>1.04</v>
       </c>
       <c r="BV6" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>5.6</v>
+        <v>1.04</v>
       </c>
       <c r="BX6" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>6.2</v>
+        <v>1.04</v>
       </c>
       <c r="BZ6" t="n">
         <v>0</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-17 16:08:18</t>
+          <t>2026-07-17 18:30:45</t>
         </is>
       </c>
     </row>
@@ -2127,145 +2127,145 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.96</v>
+        <v>1.04</v>
       </c>
       <c r="G7" t="n">
-        <v>3.45</v>
+        <v>1000</v>
       </c>
       <c r="H7" t="n">
-        <v>2.4</v>
+        <v>1.04</v>
       </c>
       <c r="I7" t="n">
-        <v>2.68</v>
+        <v>1000</v>
       </c>
       <c r="J7" t="n">
-        <v>3.3</v>
+        <v>1.02</v>
       </c>
       <c r="K7" t="n">
-        <v>3.75</v>
+        <v>1000</v>
       </c>
       <c r="L7" t="n">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="M7" t="n">
         <v>1.07</v>
       </c>
       <c r="N7" t="n">
-        <v>3.4</v>
+        <v>1.25</v>
       </c>
       <c r="O7" t="n">
         <v>1.33</v>
       </c>
       <c r="P7" t="n">
-        <v>1.82</v>
+        <v>1.25</v>
       </c>
       <c r="Q7" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S7" t="n">
         <v>1.98</v>
       </c>
-      <c r="R7" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S7" t="n">
-        <v>3.5</v>
-      </c>
       <c r="T7" t="n">
-        <v>1.64</v>
+        <v>1.11</v>
       </c>
       <c r="U7" t="n">
-        <v>2.08</v>
+        <v>1.11</v>
       </c>
       <c r="V7" t="n">
-        <v>1.59</v>
+        <v>1.01</v>
       </c>
       <c r="W7" t="n">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="X7" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="Y7" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="Z7" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AA7" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AB7" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AC7" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="AD7" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AE7" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AF7" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AG7" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AH7" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AI7" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AJ7" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AK7" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AL7" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AM7" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AO7" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AQ7" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AR7" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AS7" t="n">
         <v>1.01</v>
       </c>
       <c r="AT7" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AU7" t="n">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="AV7" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AW7" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="AX7" t="n">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY7" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AZ7" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA7" t="n">
         <v>1.01</v>
@@ -2286,61 +2286,61 @@
         <v>1.01</v>
       </c>
       <c r="BG7" t="n">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="BH7" t="n">
-        <v>3.4</v>
+        <v>1000</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.66</v>
+        <v>1.04</v>
       </c>
       <c r="BJ7" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BK7" t="n">
-        <v>3.85</v>
+        <v>1.04</v>
       </c>
       <c r="BL7" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>5.6</v>
+        <v>1.04</v>
       </c>
       <c r="BN7" t="n">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="BO7" t="n">
-        <v>4.7</v>
+        <v>1.04</v>
       </c>
       <c r="BP7" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.9</v>
+        <v>1.04</v>
       </c>
       <c r="BR7" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>5.2</v>
+        <v>1.04</v>
       </c>
       <c r="BT7" t="n">
-        <v>6.4</v>
+        <v>1000</v>
       </c>
       <c r="BU7" t="n">
-        <v>4.1</v>
+        <v>1.04</v>
       </c>
       <c r="BV7" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>4.6</v>
+        <v>1.04</v>
       </c>
       <c r="BX7" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>5.1</v>
+        <v>1.04</v>
       </c>
       <c r="BZ7" t="n">
         <v>0</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-17 16:08:18</t>
+          <t>2026-07-17 18:30:45</t>
         </is>
       </c>
     </row>
@@ -2381,118 +2381,118 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.41</v>
+        <v>1.04</v>
       </c>
       <c r="G8" t="n">
-        <v>1.5</v>
+        <v>110</v>
       </c>
       <c r="H8" t="n">
-        <v>7.8</v>
+        <v>1.04</v>
       </c>
       <c r="I8" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="J8" t="n">
-        <v>4.9</v>
+        <v>1.02</v>
       </c>
       <c r="K8" t="n">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="L8" t="n">
-        <v>1.28</v>
+        <v>1.01</v>
       </c>
       <c r="M8" t="n">
         <v>1.05</v>
       </c>
       <c r="N8" t="n">
-        <v>4.2</v>
+        <v>1.1</v>
       </c>
       <c r="O8" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="P8" t="n">
-        <v>2.12</v>
+        <v>1.45</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.61</v>
+        <v>1.72</v>
       </c>
       <c r="R8" t="n">
-        <v>1.44</v>
+        <v>1.18</v>
       </c>
       <c r="S8" t="n">
-        <v>2.82</v>
+        <v>1.05</v>
       </c>
       <c r="T8" t="n">
-        <v>1.8</v>
+        <v>1.11</v>
       </c>
       <c r="U8" t="n">
-        <v>1.73</v>
+        <v>1.11</v>
       </c>
       <c r="V8" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="W8" t="n">
-        <v>3</v>
+        <v>1.01</v>
       </c>
       <c r="X8" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="Y8" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="Z8" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AA8" t="n">
-        <v>350</v>
+        <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AC8" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AD8" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AE8" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AF8" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AG8" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH8" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AI8" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AJ8" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AK8" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AL8" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AM8" t="n">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AO8" t="n">
-        <v>210</v>
+        <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="AQ8" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="AR8" t="n">
         <v>1.01</v>
@@ -2501,10 +2501,10 @@
         <v>1.01</v>
       </c>
       <c r="AT8" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AU8" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AV8" t="n">
         <v>1.01</v>
@@ -2513,22 +2513,22 @@
         <v>1.01</v>
       </c>
       <c r="AX8" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AY8" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AZ8" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BA8" t="n">
         <v>1.01</v>
       </c>
       <c r="BB8" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BC8" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BD8" t="n">
         <v>1.01</v>
@@ -2537,61 +2537,61 @@
         <v>1.01</v>
       </c>
       <c r="BF8" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BG8" t="n">
         <v>1.01</v>
       </c>
       <c r="BH8" t="n">
-        <v>4.6</v>
+        <v>1000</v>
       </c>
       <c r="BI8" t="n">
-        <v>3.05</v>
+        <v>1.01</v>
       </c>
       <c r="BJ8" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="BK8" t="n">
         <v>1.01</v>
       </c>
       <c r="BL8" t="n">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="BM8" t="n">
         <v>1.01</v>
       </c>
       <c r="BN8" t="n">
-        <v>4.6</v>
+        <v>1000</v>
       </c>
       <c r="BO8" t="n">
-        <v>3.1</v>
+        <v>1.01</v>
       </c>
       <c r="BP8" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ8" t="n">
         <v>1.01</v>
       </c>
       <c r="BR8" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="BS8" t="n">
         <v>1.01</v>
       </c>
       <c r="BT8" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="BU8" t="n">
         <v>1.01</v>
       </c>
       <c r="BV8" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="BW8" t="n">
         <v>1.01</v>
       </c>
       <c r="BX8" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="BY8" t="n">
         <v>1.01</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-17 16:08:18</t>
+          <t>2026-07-17 18:30:45</t>
         </is>
       </c>
     </row>
@@ -2647,7 +2647,7 @@
         <v>1000</v>
       </c>
       <c r="J9" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="K9" t="n">
         <v>1000</v>
@@ -2683,7 +2683,7 @@
         <v>1.11</v>
       </c>
       <c r="V9" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W9" t="n">
         <v>1.02</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-17 16:08:18</t>
+          <t>2026-07-17 18:30:45</t>
         </is>
       </c>
     </row>
@@ -2889,230 +2889,230 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="G10" t="n">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
       <c r="H10" t="n">
-        <v>5.5</v>
+        <v>1.62</v>
       </c>
       <c r="I10" t="n">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="J10" t="n">
-        <v>4.6</v>
+        <v>1.48</v>
       </c>
       <c r="K10" t="n">
-        <v>5.2</v>
+        <v>950</v>
       </c>
       <c r="L10" t="n">
-        <v>1.23</v>
+        <v>1.01</v>
       </c>
       <c r="M10" t="n">
         <v>1.01</v>
       </c>
       <c r="N10" t="n">
-        <v>6</v>
+        <v>1.27</v>
       </c>
       <c r="O10" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="P10" t="n">
-        <v>2.72</v>
+        <v>1.27</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.51</v>
+        <v>1.14</v>
       </c>
       <c r="R10" t="n">
-        <v>1.69</v>
+        <v>1.27</v>
       </c>
       <c r="S10" t="n">
-        <v>2.24</v>
+        <v>1.42</v>
       </c>
       <c r="T10" t="n">
-        <v>1.63</v>
+        <v>1.11</v>
       </c>
       <c r="U10" t="n">
-        <v>2.34</v>
+        <v>1.11</v>
       </c>
       <c r="V10" t="n">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="W10" t="n">
-        <v>2.56</v>
+        <v>2.32</v>
       </c>
       <c r="X10" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="Y10" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="Z10" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AA10" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AB10" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AC10" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AD10" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AE10" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AF10" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AG10" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH10" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AI10" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AJ10" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AK10" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AL10" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AM10" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AN10" t="n">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="AO10" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="AQ10" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="AR10" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="AS10" t="n">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="AT10" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AU10" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AV10" t="n">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="AW10" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="AX10" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AY10" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AZ10" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="BA10" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BB10" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC10" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD10" t="n">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="BE10" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BF10" t="n">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="BG10" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BH10" t="n">
-        <v>5.4</v>
+        <v>1000</v>
       </c>
       <c r="BI10" t="n">
-        <v>3.8</v>
+        <v>1.04</v>
       </c>
       <c r="BJ10" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BK10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL10" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN10" t="n">
-        <v>5.2</v>
+        <v>1000</v>
       </c>
       <c r="BO10" t="n">
-        <v>3.7</v>
+        <v>1.04</v>
       </c>
       <c r="BP10" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BQ10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR10" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT10" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BU10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV10" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="BW10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX10" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ10" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="CA10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-17 16:08:18</t>
+          <t>2026-07-17 18:30:45</t>
         </is>
       </c>
     </row>
@@ -3155,7 +3155,7 @@
         <v>1000</v>
       </c>
       <c r="J11" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="K11" t="n">
         <v>1000</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-17 16:08:18</t>
+          <t>2026-07-17 18:30:45</t>
         </is>
       </c>
     </row>
@@ -3409,7 +3409,7 @@
         <v>1000</v>
       </c>
       <c r="J12" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="K12" t="n">
         <v>1000</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-17 16:08:18</t>
+          <t>2026-07-17 18:30:45</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
         <v>1000</v>
       </c>
       <c r="J13" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="K13" t="n">
         <v>1000</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-17 16:08:18</t>
+          <t>2026-07-17 18:30:45</t>
         </is>
       </c>
     </row>
@@ -3917,7 +3917,7 @@
         <v>1000</v>
       </c>
       <c r="J14" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="K14" t="n">
         <v>1000</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-17 16:08:18</t>
+          <t>2026-07-17 18:30:45</t>
         </is>
       </c>
     </row>
@@ -4171,7 +4171,7 @@
         <v>1000</v>
       </c>
       <c r="J15" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="K15" t="n">
         <v>1000</v>
@@ -4183,7 +4183,7 @@
         <v>1.01</v>
       </c>
       <c r="N15" t="n">
-        <v>1.1</v>
+        <v>1.24</v>
       </c>
       <c r="O15" t="n">
         <v>1.01</v>
@@ -4210,7 +4210,7 @@
         <v>1.02</v>
       </c>
       <c r="W15" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X15" t="n">
         <v>1000</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-17 16:08:18</t>
+          <t>2026-07-17 18:30:45</t>
         </is>
       </c>
     </row>
@@ -4425,7 +4425,7 @@
         <v>1000</v>
       </c>
       <c r="J16" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="K16" t="n">
         <v>1000</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-17 16:08:18</t>
+          <t>2026-07-17 18:30:45</t>
         </is>
       </c>
     </row>
@@ -4667,46 +4667,46 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.82</v>
+        <v>1.04</v>
       </c>
       <c r="G17" t="n">
-        <v>3.3</v>
+        <v>1000</v>
       </c>
       <c r="H17" t="n">
-        <v>2.7</v>
+        <v>1.04</v>
       </c>
       <c r="I17" t="n">
-        <v>3.15</v>
+        <v>1000</v>
       </c>
       <c r="J17" t="n">
-        <v>2.96</v>
+        <v>1.02</v>
       </c>
       <c r="K17" t="n">
-        <v>3.55</v>
+        <v>1000</v>
       </c>
       <c r="L17" t="n">
-        <v>1.45</v>
+        <v>1.01</v>
       </c>
       <c r="M17" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="N17" t="n">
-        <v>2.4</v>
+        <v>1.24</v>
       </c>
       <c r="O17" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="P17" t="n">
-        <v>1.52</v>
+        <v>1.24</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.54</v>
+        <v>1.5</v>
       </c>
       <c r="R17" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="S17" t="n">
-        <v>5.1</v>
+        <v>1.05</v>
       </c>
       <c r="T17" t="n">
         <v>1.11</v>
@@ -4715,97 +4715,97 @@
         <v>1.11</v>
       </c>
       <c r="V17" t="n">
-        <v>1.46</v>
+        <v>1.01</v>
       </c>
       <c r="W17" t="n">
-        <v>1.43</v>
+        <v>1.01</v>
       </c>
       <c r="X17" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="Y17" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="Z17" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AA17" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AB17" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AC17" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="AD17" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AE17" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AF17" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AG17" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AH17" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AI17" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AJ17" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AK17" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AL17" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AM17" t="n">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="AN17" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AO17" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AP17" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AQ17" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AR17" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS17" t="n">
         <v>1.01</v>
       </c>
       <c r="AT17" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="AU17" t="n">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="AV17" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW17" t="n">
         <v>1.01</v>
       </c>
       <c r="AX17" t="n">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY17" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ17" t="n">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="BA17" t="n">
         <v>1.01</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-17 16:08:18</t>
+          <t>2026-07-17 18:30:45</t>
         </is>
       </c>
     </row>
@@ -4921,22 +4921,22 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.85</v>
+        <v>1.31</v>
       </c>
       <c r="G18" t="n">
-        <v>2</v>
+        <v>1000</v>
       </c>
       <c r="H18" t="n">
-        <v>4</v>
+        <v>1.04</v>
       </c>
       <c r="I18" t="n">
-        <v>4.6</v>
+        <v>100</v>
       </c>
       <c r="J18" t="n">
-        <v>3.85</v>
+        <v>1.31</v>
       </c>
       <c r="K18" t="n">
-        <v>4.3</v>
+        <v>1000</v>
       </c>
       <c r="L18" t="n">
         <v>1.01</v>
@@ -4945,142 +4945,142 @@
         <v>1.01</v>
       </c>
       <c r="N18" t="n">
-        <v>4.1</v>
+        <v>1.25</v>
       </c>
       <c r="O18" t="n">
         <v>1.23</v>
       </c>
       <c r="P18" t="n">
-        <v>2.2</v>
+        <v>1.25</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.69</v>
+        <v>1.23</v>
       </c>
       <c r="R18" t="n">
-        <v>1.37</v>
+        <v>1.25</v>
       </c>
       <c r="S18" t="n">
-        <v>2.68</v>
+        <v>1.01</v>
       </c>
       <c r="T18" t="n">
-        <v>1.57</v>
+        <v>1.11</v>
       </c>
       <c r="U18" t="n">
-        <v>1.87</v>
+        <v>1.11</v>
       </c>
       <c r="V18" t="n">
         <v>1.29</v>
       </c>
       <c r="W18" t="n">
-        <v>2</v>
+        <v>1.01</v>
       </c>
       <c r="X18" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="Y18" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="Z18" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AA18" t="n">
         <v>1000</v>
       </c>
       <c r="AB18" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AC18" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AD18" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AE18" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AF18" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AG18" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AH18" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AI18" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AJ18" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AK18" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AL18" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AM18" t="n">
         <v>1000</v>
       </c>
       <c r="AN18" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AO18" t="n">
         <v>1000</v>
       </c>
       <c r="AP18" t="n">
-        <v>2.34</v>
+        <v>1.01</v>
       </c>
       <c r="AQ18" t="n">
-        <v>2.34</v>
+        <v>1.01</v>
       </c>
       <c r="AR18" t="n">
-        <v>2.42</v>
+        <v>1.01</v>
       </c>
       <c r="AS18" t="n">
-        <v>2.56</v>
+        <v>1.01</v>
       </c>
       <c r="AT18" t="n">
-        <v>2.2</v>
+        <v>1.01</v>
       </c>
       <c r="AU18" t="n">
-        <v>2.14</v>
+        <v>1.01</v>
       </c>
       <c r="AV18" t="n">
-        <v>2.32</v>
+        <v>1.01</v>
       </c>
       <c r="AW18" t="n">
-        <v>2.46</v>
+        <v>1.01</v>
       </c>
       <c r="AX18" t="n">
-        <v>2.24</v>
+        <v>1.01</v>
       </c>
       <c r="AY18" t="n">
-        <v>2.2</v>
+        <v>1.01</v>
       </c>
       <c r="AZ18" t="n">
-        <v>2.32</v>
+        <v>1.01</v>
       </c>
       <c r="BA18" t="n">
-        <v>2.46</v>
+        <v>1.01</v>
       </c>
       <c r="BB18" t="n">
-        <v>2.36</v>
+        <v>1.01</v>
       </c>
       <c r="BC18" t="n">
-        <v>2.34</v>
+        <v>1.01</v>
       </c>
       <c r="BD18" t="n">
-        <v>2.42</v>
+        <v>1.01</v>
       </c>
       <c r="BE18" t="n">
-        <v>2.56</v>
+        <v>1.01</v>
       </c>
       <c r="BF18" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BG18" t="n">
-        <v>2.56</v>
+        <v>1.01</v>
       </c>
       <c r="BH18" t="n">
         <v>1000</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-17 16:08:18</t>
+          <t>2026-07-17 18:30:45</t>
         </is>
       </c>
     </row>
@@ -5175,22 +5175,22 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.72</v>
+        <v>2.56</v>
       </c>
       <c r="G19" t="n">
-        <v>2.98</v>
+        <v>3.4</v>
       </c>
       <c r="H19" t="n">
-        <v>2.48</v>
+        <v>2.36</v>
       </c>
       <c r="I19" t="n">
-        <v>2.78</v>
+        <v>2.92</v>
       </c>
       <c r="J19" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="K19" t="n">
-        <v>3.9</v>
+        <v>950</v>
       </c>
       <c r="L19" t="n">
         <v>1.01</v>
@@ -5199,82 +5199,82 @@
         <v>1.01</v>
       </c>
       <c r="N19" t="n">
-        <v>4.4</v>
+        <v>1.1</v>
       </c>
       <c r="O19" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P19" t="n">
-        <v>2.16</v>
+        <v>1.25</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.71</v>
+        <v>1.23</v>
       </c>
       <c r="R19" t="n">
-        <v>1.37</v>
+        <v>1.25</v>
       </c>
       <c r="S19" t="n">
-        <v>2.68</v>
+        <v>1.23</v>
       </c>
       <c r="T19" t="n">
-        <v>1.45</v>
+        <v>1.11</v>
       </c>
       <c r="U19" t="n">
-        <v>1.97</v>
+        <v>1.11</v>
       </c>
       <c r="V19" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="W19" t="n">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="X19" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="Y19" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="Z19" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AA19" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AB19" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AC19" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AD19" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AE19" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AF19" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AG19" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AH19" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AI19" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AJ19" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AK19" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AL19" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AM19" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AN19" t="n">
         <v>1000</v>
@@ -5283,122 +5283,122 @@
         <v>1000</v>
       </c>
       <c r="AP19" t="n">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ19" t="n">
-        <v>2.16</v>
+        <v>1.01</v>
       </c>
       <c r="AR19" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS19" t="n">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="AT19" t="n">
-        <v>2.14</v>
+        <v>1.01</v>
       </c>
       <c r="AU19" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AV19" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AW19" t="n">
-        <v>2.3</v>
+        <v>1.01</v>
       </c>
       <c r="AX19" t="n">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="AY19" t="n">
-        <v>2.16</v>
+        <v>1.01</v>
       </c>
       <c r="AZ19" t="n">
-        <v>2.2</v>
+        <v>1.01</v>
       </c>
       <c r="BA19" t="n">
-        <v>2.32</v>
+        <v>1.01</v>
       </c>
       <c r="BB19" t="n">
-        <v>2.34</v>
+        <v>1.01</v>
       </c>
       <c r="BC19" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BD19" t="n">
-        <v>2.32</v>
+        <v>1.01</v>
       </c>
       <c r="BE19" t="n">
-        <v>2.38</v>
+        <v>1.01</v>
       </c>
       <c r="BF19" t="n">
-        <v>2.44</v>
+        <v>1.01</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.44</v>
+        <v>1.01</v>
       </c>
       <c r="BH19" t="n">
         <v>1000</v>
       </c>
       <c r="BI19" t="n">
-        <v>1.88</v>
+        <v>1.04</v>
       </c>
       <c r="BJ19" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="BK19" t="n">
-        <v>1.64</v>
+        <v>1.04</v>
       </c>
       <c r="BL19" t="n">
         <v>1000</v>
       </c>
       <c r="BM19" t="n">
-        <v>1.88</v>
+        <v>1.04</v>
       </c>
       <c r="BN19" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BO19" t="n">
-        <v>4.1</v>
+        <v>1.04</v>
       </c>
       <c r="BP19" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="BQ19" t="n">
-        <v>1.77</v>
+        <v>1.04</v>
       </c>
       <c r="BR19" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BS19" t="n">
-        <v>1.8</v>
+        <v>1.04</v>
       </c>
       <c r="BT19" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="BU19" t="n">
-        <v>3.8</v>
+        <v>1.04</v>
       </c>
       <c r="BV19" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BW19" t="n">
-        <v>1.75</v>
+        <v>1.04</v>
       </c>
       <c r="BX19" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BY19" t="n">
-        <v>1.8</v>
+        <v>1.04</v>
       </c>
       <c r="BZ19" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="CA19" t="n">
-        <v>1.77</v>
+        <v>1.04</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-17 16:08:18</t>
+          <t>2026-07-17 18:30:45</t>
         </is>
       </c>
     </row>
@@ -5441,7 +5441,7 @@
         <v>1000</v>
       </c>
       <c r="J20" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="K20" t="n">
         <v>1000</v>
@@ -5453,13 +5453,13 @@
         <v>1.01</v>
       </c>
       <c r="N20" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="O20" t="n">
         <v>1.16</v>
       </c>
       <c r="P20" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Q20" t="n">
         <v>1.16</v>
@@ -5468,7 +5468,7 @@
         <v>1.07</v>
       </c>
       <c r="S20" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="T20" t="n">
         <v>1.11</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-17 16:08:18</t>
+          <t>2026-07-17 18:30:45</t>
         </is>
       </c>
     </row>
@@ -5683,13 +5683,13 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="G21" t="n">
-        <v>2.14</v>
+        <v>2.24</v>
       </c>
       <c r="H21" t="n">
-        <v>3.95</v>
+        <v>3.55</v>
       </c>
       <c r="I21" t="n">
         <v>4.3</v>
@@ -5701,91 +5701,91 @@
         <v>3.7</v>
       </c>
       <c r="L21" t="n">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="M21" t="n">
         <v>1.07</v>
       </c>
       <c r="N21" t="n">
-        <v>3.7</v>
+        <v>1.1</v>
       </c>
       <c r="O21" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="P21" t="n">
-        <v>1.91</v>
+        <v>1.25</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.93</v>
+        <v>1.31</v>
       </c>
       <c r="R21" t="n">
-        <v>1.36</v>
+        <v>1.15</v>
       </c>
       <c r="S21" t="n">
-        <v>3.35</v>
+        <v>1.05</v>
       </c>
       <c r="T21" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="U21" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="V21" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W21" t="n">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="X21" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y21" t="n">
         <v>15</v>
       </c>
-      <c r="Y21" t="n">
-        <v>17</v>
-      </c>
       <c r="Z21" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AA21" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="AB21" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC21" t="n">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD21" t="n">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="AE21" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AF21" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AG21" t="n">
         <v>11</v>
       </c>
       <c r="AH21" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AI21" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AJ21" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AK21" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AL21" t="n">
         <v>38</v>
       </c>
       <c r="AM21" t="n">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="AN21" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AO21" t="n">
         <v>55</v>
@@ -5797,22 +5797,22 @@
         <v>13</v>
       </c>
       <c r="AR21" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AS21" t="n">
-        <v>6.6</v>
+        <v>12</v>
       </c>
       <c r="AT21" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AU21" t="n">
         <v>7.2</v>
       </c>
       <c r="AV21" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AW21" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AX21" t="n">
         <v>11.5</v>
@@ -5830,25 +5830,25 @@
         <v>22</v>
       </c>
       <c r="BC21" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BD21" t="n">
         <v>32</v>
       </c>
       <c r="BE21" t="n">
-        <v>6.6</v>
+        <v>75</v>
       </c>
       <c r="BF21" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BG21" t="n">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="BH21" t="n">
         <v>3.85</v>
       </c>
       <c r="BI21" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="BJ21" t="n">
         <v>11</v>
@@ -5866,28 +5866,28 @@
         <v>5.4</v>
       </c>
       <c r="BO21" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BP21" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BQ21" t="n">
         <v>1.01</v>
       </c>
       <c r="BR21" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BS21" t="n">
         <v>1.01</v>
       </c>
       <c r="BT21" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BU21" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BV21" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BW21" t="n">
         <v>1.01</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-07-17 16:08:18</t>
+          <t>2026-07-17 18:30:45</t>
         </is>
       </c>
     </row>
@@ -5943,13 +5943,13 @@
         <v>1000</v>
       </c>
       <c r="H22" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="I22" t="n">
         <v>1000</v>
       </c>
       <c r="J22" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="K22" t="n">
         <v>1000</v>
@@ -5961,22 +5961,22 @@
         <v>1.01</v>
       </c>
       <c r="N22" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="O22" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="P22" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="R22" t="n">
         <v>1.12</v>
       </c>
       <c r="S22" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="T22" t="n">
         <v>1.11</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-07-17 16:08:18</t>
+          <t>2026-07-17 18:30:45</t>
         </is>
       </c>
     </row>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-07-17 16:08:18</t>
+          <t>2026-07-17 18:30:45</t>
         </is>
       </c>
     </row>
@@ -6445,10 +6445,10 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="G24" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="H24" t="n">
         <v>1.62</v>
@@ -6469,28 +6469,28 @@
         <v>1.03</v>
       </c>
       <c r="N24" t="n">
-        <v>5.5</v>
+        <v>1.11</v>
       </c>
       <c r="O24" t="n">
         <v>1.16</v>
       </c>
       <c r="P24" t="n">
-        <v>2.62</v>
+        <v>1.61</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.54</v>
+        <v>1.01</v>
       </c>
       <c r="R24" t="n">
         <v>1.58</v>
       </c>
       <c r="S24" t="n">
-        <v>2.36</v>
+        <v>1.17</v>
       </c>
       <c r="T24" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="U24" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="V24" t="n">
         <v>2.56</v>
@@ -6499,49 +6499,49 @@
         <v>1.2</v>
       </c>
       <c r="X24" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="Y24" t="n">
         <v>14</v>
       </c>
       <c r="Z24" t="n">
-        <v>14</v>
+        <v>970</v>
       </c>
       <c r="AA24" t="n">
-        <v>19.5</v>
+        <v>970</v>
       </c>
       <c r="AB24" t="n">
         <v>34</v>
       </c>
       <c r="AC24" t="n">
-        <v>12.5</v>
+        <v>970</v>
       </c>
       <c r="AD24" t="n">
-        <v>11</v>
+        <v>970</v>
       </c>
       <c r="AE24" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AF24" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AG24" t="n">
+        <v>22</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI24" t="n">
         <v>25</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>29</v>
       </c>
       <c r="AJ24" t="n">
         <v>160</v>
       </c>
       <c r="AK24" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AL24" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AM24" t="n">
         <v>75</v>
@@ -6550,125 +6550,125 @@
         <v>50</v>
       </c>
       <c r="AO24" t="n">
-        <v>7.2</v>
+        <v>970</v>
       </c>
       <c r="AP24" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AQ24" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AR24" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AS24" t="n">
-        <v>14</v>
+        <v>6.6</v>
       </c>
       <c r="AT24" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AU24" t="n">
-        <v>9.4</v>
+        <v>5.5</v>
       </c>
       <c r="AV24" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AW24" t="n">
-        <v>12</v>
+        <v>6.4</v>
       </c>
       <c r="AX24" t="n">
-        <v>40</v>
+        <v>9.6</v>
       </c>
       <c r="AY24" t="n">
-        <v>18.5</v>
+        <v>7.6</v>
       </c>
       <c r="AZ24" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="BA24" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BB24" t="n">
-        <v>5.9</v>
+        <v>2.96</v>
       </c>
       <c r="BC24" t="n">
-        <v>5.6</v>
+        <v>2.88</v>
       </c>
       <c r="BD24" t="n">
-        <v>42</v>
+        <v>2.86</v>
       </c>
       <c r="BE24" t="n">
-        <v>5.7</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF24" t="n">
         <v>36</v>
       </c>
       <c r="BG24" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="BH24" t="n">
         <v>1000</v>
       </c>
       <c r="BI24" t="n">
-        <v>2</v>
+        <v>1.04</v>
       </c>
       <c r="BJ24" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="BK24" t="n">
-        <v>1.74</v>
+        <v>1.04</v>
       </c>
       <c r="BL24" t="n">
         <v>1000</v>
       </c>
       <c r="BM24" t="n">
-        <v>2</v>
+        <v>1.04</v>
       </c>
       <c r="BN24" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="BO24" t="n">
-        <v>1.74</v>
+        <v>1.04</v>
       </c>
       <c r="BP24" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BQ24" t="n">
-        <v>1.93</v>
+        <v>1.04</v>
       </c>
       <c r="BR24" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BS24" t="n">
-        <v>1.93</v>
+        <v>1.04</v>
       </c>
       <c r="BT24" t="n">
-        <v>6.4</v>
+        <v>1000</v>
       </c>
       <c r="BU24" t="n">
-        <v>3.15</v>
+        <v>1.04</v>
       </c>
       <c r="BV24" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="BW24" t="n">
-        <v>1.77</v>
+        <v>1.04</v>
       </c>
       <c r="BX24" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="BY24" t="n">
-        <v>1.88</v>
+        <v>1.04</v>
       </c>
       <c r="BZ24" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="CA24" t="n">
-        <v>1.81</v>
+        <v>1.04</v>
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-07-17 16:08:18</t>
+          <t>2026-07-17 18:30:45</t>
         </is>
       </c>
     </row>
@@ -6717,31 +6717,31 @@
         <v>4.1</v>
       </c>
       <c r="L25" t="n">
-        <v>1.24</v>
+        <v>1.01</v>
       </c>
       <c r="M25" t="n">
         <v>1.04</v>
       </c>
       <c r="N25" t="n">
-        <v>4.6</v>
+        <v>3</v>
       </c>
       <c r="O25" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P25" t="n">
         <v>2.3</v>
       </c>
       <c r="Q25" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S25" t="n">
         <v>1.7</v>
       </c>
-      <c r="R25" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="S25" t="n">
-        <v>2.74</v>
-      </c>
       <c r="T25" t="n">
-        <v>1.63</v>
+        <v>1.54</v>
       </c>
       <c r="U25" t="n">
         <v>1.11</v>
@@ -6795,7 +6795,7 @@
         <v>1000</v>
       </c>
       <c r="AL25" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AM25" t="n">
         <v>1000</v>
@@ -6807,58 +6807,58 @@
         <v>1000</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AR25" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AS25" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AT25" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AU25" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AV25" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AW25" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AX25" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AY25" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AZ25" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="BA25" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="BC25" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="BD25" t="n">
         <v>1.01</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="BG25" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="BH25" t="n">
         <v>1000</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-07-17 16:08:18</t>
+          <t>2026-07-17 18:30:45</t>
         </is>
       </c>
     </row>
@@ -6959,10 +6959,10 @@
         <v>1.32</v>
       </c>
       <c r="H26" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I26" t="n">
-        <v>13.5</v>
+        <v>17.5</v>
       </c>
       <c r="J26" t="n">
         <v>6.2</v>
@@ -6971,212 +6971,212 @@
         <v>6.8</v>
       </c>
       <c r="L26" t="n">
-        <v>1.2</v>
+        <v>1.01</v>
       </c>
       <c r="M26" t="n">
         <v>1.03</v>
       </c>
       <c r="N26" t="n">
-        <v>5.6</v>
+        <v>2.36</v>
       </c>
       <c r="O26" t="n">
         <v>1.19</v>
       </c>
       <c r="P26" t="n">
-        <v>2.52</v>
+        <v>1.25</v>
       </c>
       <c r="Q26" t="n">
         <v>1.54</v>
       </c>
       <c r="R26" t="n">
-        <v>1.62</v>
+        <v>1.24</v>
       </c>
       <c r="S26" t="n">
-        <v>2.36</v>
+        <v>1.55</v>
       </c>
       <c r="T26" t="n">
-        <v>1.99</v>
+        <v>1.11</v>
       </c>
       <c r="U26" t="n">
-        <v>1.84</v>
+        <v>1.11</v>
       </c>
       <c r="V26" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="W26" t="n">
         <v>4</v>
       </c>
       <c r="X26" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="Y26" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="Z26" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AA26" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AB26" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AC26" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AD26" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AE26" t="n">
-        <v>210</v>
+        <v>1000</v>
       </c>
       <c r="AF26" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AG26" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH26" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AI26" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AJ26" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AK26" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AL26" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AM26" t="n">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AN26" t="n">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="AO26" t="n">
-        <v>250</v>
+        <v>1000</v>
       </c>
       <c r="AP26" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="AQ26" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="AR26" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="AS26" t="n">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="AT26" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AU26" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="AV26" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="AW26" t="n">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="AX26" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AY26" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AZ26" t="n">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="BA26" t="n">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="BB26" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="BC26" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD26" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BE26" t="n">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="BF26" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BG26" t="n">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH26" t="n">
         <v>1000</v>
       </c>
       <c r="BI26" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ26" t="n">
         <v>1000</v>
       </c>
       <c r="BK26" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL26" t="n">
         <v>1000</v>
       </c>
       <c r="BM26" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN26" t="n">
         <v>1000</v>
       </c>
       <c r="BO26" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP26" t="n">
         <v>1000</v>
       </c>
       <c r="BQ26" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR26" t="n">
         <v>1000</v>
       </c>
       <c r="BS26" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT26" t="n">
         <v>1000</v>
       </c>
       <c r="BU26" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV26" t="n">
         <v>1000</v>
       </c>
       <c r="BW26" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX26" t="n">
         <v>1000</v>
       </c>
       <c r="BY26" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ26" t="n">
         <v>1000</v>
       </c>
       <c r="CA26" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-07-17 16:08:18</t>
+          <t>2026-07-17 18:30:45</t>
         </is>
       </c>
     </row>
@@ -7216,10 +7216,10 @@
         <v>1.26</v>
       </c>
       <c r="I27" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="J27" t="n">
-        <v>1.1</v>
+        <v>1.79</v>
       </c>
       <c r="K27" t="n">
         <v>5</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-07-17 16:08:18</t>
+          <t>2026-07-17 18:30:45</t>
         </is>
       </c>
     </row>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-07-17 16:08:18</t>
+          <t>2026-07-17 18:30:45</t>
         </is>
       </c>
     </row>
@@ -7724,7 +7724,7 @@
         <v>2.66</v>
       </c>
       <c r="I29" t="n">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="J29" t="n">
         <v>3.05</v>
@@ -7733,7 +7733,7 @@
         <v>3.85</v>
       </c>
       <c r="L29" t="n">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="M29" t="n">
         <v>1.01</v>
@@ -7742,7 +7742,7 @@
         <v>2.56</v>
       </c>
       <c r="O29" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="P29" t="n">
         <v>1.67</v>
@@ -7763,7 +7763,7 @@
         <v>1.11</v>
       </c>
       <c r="V29" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="W29" t="n">
         <v>1.42</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-07-17 16:08:18</t>
+          <t>2026-07-17 18:30:45</t>
         </is>
       </c>
     </row>
@@ -7969,230 +7969,230 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>5.8</v>
+        <v>2.2</v>
       </c>
       <c r="G30" t="n">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="H30" t="n">
-        <v>1.76</v>
+        <v>1.54</v>
       </c>
       <c r="I30" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="J30" t="n">
         <v>3.5</v>
       </c>
       <c r="K30" t="n">
-        <v>3.6</v>
+        <v>1000</v>
       </c>
       <c r="L30" t="n">
-        <v>1.48</v>
+        <v>1.01</v>
       </c>
       <c r="M30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N30" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P30" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="R30" t="n">
         <v>1.12</v>
       </c>
-      <c r="N30" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="O30" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="P30" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="R30" t="n">
-        <v>1.18</v>
-      </c>
       <c r="S30" t="n">
-        <v>5.7</v>
+        <v>1.05</v>
       </c>
       <c r="T30" t="n">
-        <v>2.12</v>
+        <v>1.11</v>
       </c>
       <c r="U30" t="n">
-        <v>1.63</v>
+        <v>1.11</v>
       </c>
       <c r="V30" t="n">
         <v>2.18</v>
       </c>
       <c r="W30" t="n">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="X30" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="Y30" t="n">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="Z30" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="AA30" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AB30" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AC30" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="AD30" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AE30" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AF30" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AG30" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AH30" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AI30" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AJ30" t="n">
-        <v>270</v>
+        <v>1000</v>
       </c>
       <c r="AK30" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AL30" t="n">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AM30" t="n">
-        <v>350</v>
+        <v>1000</v>
       </c>
       <c r="AN30" t="n">
-        <v>320</v>
+        <v>1000</v>
       </c>
       <c r="AO30" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AP30" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AQ30" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="AR30" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="AS30" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="AT30" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AU30" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AV30" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AW30" t="n">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="AX30" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="AY30" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="AZ30" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BA30" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BB30" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BC30" t="n">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="BD30" t="n">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="BE30" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BF30" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BG30" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BH30" t="n">
         <v>1000</v>
       </c>
       <c r="BI30" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ30" t="n">
         <v>1000</v>
       </c>
       <c r="BK30" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL30" t="n">
         <v>1000</v>
       </c>
       <c r="BM30" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN30" t="n">
         <v>1000</v>
       </c>
       <c r="BO30" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP30" t="n">
         <v>1000</v>
       </c>
       <c r="BQ30" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR30" t="n">
         <v>1000</v>
       </c>
       <c r="BS30" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT30" t="n">
         <v>1000</v>
       </c>
       <c r="BU30" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV30" t="n">
         <v>1000</v>
       </c>
       <c r="BW30" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX30" t="n">
         <v>1000</v>
       </c>
       <c r="BY30" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ30" t="n">
         <v>1000</v>
       </c>
       <c r="CA30" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-07-17 16:08:18</t>
+          <t>2026-07-17 18:30:45</t>
         </is>
       </c>
     </row>
@@ -8244,7 +8244,7 @@
         <v>1.01</v>
       </c>
       <c r="M31" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="N31" t="n">
         <v>2.68</v>
@@ -8265,16 +8265,16 @@
         <v>2</v>
       </c>
       <c r="T31" t="n">
-        <v>1.4</v>
+        <v>1.11</v>
       </c>
       <c r="U31" t="n">
-        <v>1.98</v>
+        <v>1.11</v>
       </c>
       <c r="V31" t="n">
-        <v>2.34</v>
+        <v>1.01</v>
       </c>
       <c r="W31" t="n">
-        <v>1.2</v>
+        <v>1.01</v>
       </c>
       <c r="X31" t="n">
         <v>1000</v>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-07-17 16:08:18</t>
+          <t>2026-07-17 18:30:45</t>
         </is>
       </c>
     </row>
@@ -8477,7 +8477,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="G32" t="n">
         <v>1.77</v>
@@ -8492,7 +8492,7 @@
         <v>3.7</v>
       </c>
       <c r="K32" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="L32" t="n">
         <v>1.01</v>
@@ -8507,7 +8507,7 @@
         <v>1.35</v>
       </c>
       <c r="P32" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="Q32" t="n">
         <v>2</v>
@@ -8519,7 +8519,7 @@
         <v>3.7</v>
       </c>
       <c r="T32" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="U32" t="n">
         <v>1.84</v>
@@ -8540,13 +8540,13 @@
         <v>60</v>
       </c>
       <c r="AA32" t="n">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="AB32" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC32" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD32" t="n">
         <v>29</v>
@@ -8582,7 +8582,7 @@
         <v>15</v>
       </c>
       <c r="AO32" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AP32" t="n">
         <v>9.800000000000001</v>
@@ -8591,10 +8591,10 @@
         <v>13</v>
       </c>
       <c r="AR32" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AS32" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="AT32" t="n">
         <v>5.7</v>
@@ -8606,7 +8606,7 @@
         <v>17</v>
       </c>
       <c r="AW32" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="AX32" t="n">
         <v>7.2</v>
@@ -8618,7 +8618,7 @@
         <v>19</v>
       </c>
       <c r="BA32" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="BB32" t="n">
         <v>12.5</v>
@@ -8627,16 +8627,16 @@
         <v>14</v>
       </c>
       <c r="BD32" t="n">
-        <v>3.95</v>
+        <v>30</v>
       </c>
       <c r="BE32" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BF32" t="n">
         <v>9</v>
       </c>
       <c r="BG32" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BH32" t="n">
         <v>1000</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-07-17 16:08:18</t>
+          <t>2026-07-17 18:30:45</t>
         </is>
       </c>
     </row>
@@ -8731,7 +8731,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="G33" t="n">
         <v>2.3</v>
@@ -8740,16 +8740,16 @@
         <v>3.3</v>
       </c>
       <c r="I33" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="J33" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K33" t="n">
         <v>4.5</v>
       </c>
       <c r="L33" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="M33" t="n">
         <v>1.04</v>
@@ -8776,10 +8776,10 @@
         <v>1.47</v>
       </c>
       <c r="U33" t="n">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="V33" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="W33" t="n">
         <v>1.76</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-07-17 16:08:18</t>
+          <t>2026-07-17 18:30:45</t>
         </is>
       </c>
     </row>
@@ -9009,7 +9009,7 @@
         <v>1.01</v>
       </c>
       <c r="N34" t="n">
-        <v>1.24</v>
+        <v>1.1</v>
       </c>
       <c r="O34" t="n">
         <v>1.01</v>
@@ -9021,7 +9021,7 @@
         <v>1.01</v>
       </c>
       <c r="R34" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S34" t="n">
         <v>1.05</v>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-07-17 16:08:18</t>
+          <t>2026-07-17 18:30:45</t>
         </is>
       </c>
     </row>
@@ -9263,13 +9263,13 @@
         <v>1.01</v>
       </c>
       <c r="N35" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="O35" t="n">
         <v>1.15</v>
       </c>
       <c r="P35" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Q35" t="n">
         <v>1.15</v>
@@ -9404,55 +9404,55 @@
         <v>1000</v>
       </c>
       <c r="BI35" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ35" t="n">
         <v>1000</v>
       </c>
       <c r="BK35" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL35" t="n">
         <v>1000</v>
       </c>
       <c r="BM35" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN35" t="n">
         <v>1000</v>
       </c>
       <c r="BO35" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP35" t="n">
         <v>1000</v>
       </c>
       <c r="BQ35" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR35" t="n">
         <v>1000</v>
       </c>
       <c r="BS35" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT35" t="n">
         <v>1000</v>
       </c>
       <c r="BU35" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV35" t="n">
         <v>1000</v>
       </c>
       <c r="BW35" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX35" t="n">
         <v>1000</v>
       </c>
       <c r="BY35" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ35" t="n">
         <v>0</v>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-07-17 16:08:18</t>
+          <t>2026-07-17 18:30:45</t>
         </is>
       </c>
     </row>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-07-17 16:08:18</t>
+          <t>2026-07-17 18:30:45</t>
         </is>
       </c>
     </row>
@@ -9780,7 +9780,7 @@
         <v>1.5</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="R37" t="n">
         <v>1.18</v>
@@ -9792,7 +9792,7 @@
         <v>1.9</v>
       </c>
       <c r="U37" t="n">
-        <v>1.11</v>
+        <v>1.67</v>
       </c>
       <c r="V37" t="n">
         <v>1.43</v>
@@ -9855,7 +9855,7 @@
         <v>1000</v>
       </c>
       <c r="AP37" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="AQ37" t="n">
         <v>1.11</v>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-07-17 16:08:18</t>
+          <t>2026-07-17 18:30:45</t>
         </is>
       </c>
     </row>
@@ -10037,22 +10037,22 @@
         <v>2.26</v>
       </c>
       <c r="R38" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="S38" t="n">
-        <v>4.3</v>
+        <v>1.42</v>
       </c>
       <c r="T38" t="n">
-        <v>1.83</v>
+        <v>1.11</v>
       </c>
       <c r="U38" t="n">
-        <v>1.76</v>
+        <v>1.11</v>
       </c>
       <c r="V38" t="n">
         <v>1.84</v>
       </c>
       <c r="W38" t="n">
-        <v>1.28</v>
+        <v>1.01</v>
       </c>
       <c r="X38" t="n">
         <v>1000</v>
@@ -10166,65 +10166,65 @@
         <v>1000</v>
       </c>
       <c r="BI38" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ38" t="n">
         <v>1000</v>
       </c>
       <c r="BK38" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL38" t="n">
         <v>1000</v>
       </c>
       <c r="BM38" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN38" t="n">
         <v>1000</v>
       </c>
       <c r="BO38" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP38" t="n">
         <v>1000</v>
       </c>
       <c r="BQ38" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR38" t="n">
         <v>1000</v>
       </c>
       <c r="BS38" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT38" t="n">
         <v>1000</v>
       </c>
       <c r="BU38" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV38" t="n">
         <v>1000</v>
       </c>
       <c r="BW38" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX38" t="n">
         <v>1000</v>
       </c>
       <c r="BY38" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ38" t="n">
         <v>1000</v>
       </c>
       <c r="CA38" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-07-17 16:08:18</t>
+          <t>2026-07-17 18:30:45</t>
         </is>
       </c>
     </row>
@@ -10279,16 +10279,16 @@
         <v>1.01</v>
       </c>
       <c r="N39" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="O39" t="n">
         <v>1.42</v>
       </c>
       <c r="P39" t="n">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="R39" t="n">
         <v>1.18</v>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-07-17 16:08:18</t>
+          <t>2026-07-17 18:30:45</t>
         </is>
       </c>
     </row>
@@ -10521,7 +10521,7 @@
         <v>1000</v>
       </c>
       <c r="J40" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="K40" t="n">
         <v>1000</v>
@@ -10732,7 +10732,7 @@
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-07-17 16:08:18</t>
+          <t>2026-07-17 18:30:45</t>
         </is>
       </c>
     </row>
@@ -10763,52 +10763,52 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1.58</v>
+        <v>1.04</v>
       </c>
       <c r="G41" t="n">
-        <v>1.78</v>
+        <v>1000</v>
       </c>
       <c r="H41" t="n">
-        <v>3.8</v>
+        <v>1.04</v>
       </c>
       <c r="I41" t="n">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="J41" t="n">
-        <v>3.85</v>
+        <v>1.02</v>
       </c>
       <c r="K41" t="n">
-        <v>5.5</v>
+        <v>1000</v>
       </c>
       <c r="L41" t="n">
-        <v>1.23</v>
+        <v>1.01</v>
       </c>
       <c r="M41" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N41" t="n">
-        <v>3.15</v>
+        <v>1.1</v>
       </c>
       <c r="O41" t="n">
         <v>1.23</v>
       </c>
       <c r="P41" t="n">
-        <v>1.98</v>
+        <v>1.07</v>
       </c>
       <c r="Q41" t="n">
-        <v>1.6</v>
+        <v>1.23</v>
       </c>
       <c r="R41" t="n">
-        <v>1.38</v>
+        <v>1.07</v>
       </c>
       <c r="S41" t="n">
-        <v>2.44</v>
+        <v>1.23</v>
       </c>
       <c r="T41" t="n">
-        <v>1.53</v>
+        <v>1.75</v>
       </c>
       <c r="U41" t="n">
-        <v>1.74</v>
+        <v>2.04</v>
       </c>
       <c r="V41" t="n">
         <v>1.15</v>
@@ -10986,7 +10986,7 @@
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-07-17 16:08:18</t>
+          <t>2026-07-17 18:30:45</t>
         </is>
       </c>
     </row>
@@ -11023,16 +11023,16 @@
         <v>2.14</v>
       </c>
       <c r="H42" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="I42" t="n">
         <v>5.6</v>
       </c>
       <c r="J42" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="K42" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L42" t="n">
         <v>1.01</v>
@@ -11044,13 +11044,13 @@
         <v>2.54</v>
       </c>
       <c r="O42" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="P42" t="n">
         <v>1.68</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="R42" t="n">
         <v>1.19</v>
@@ -11065,10 +11065,10 @@
         <v>1.66</v>
       </c>
       <c r="V42" t="n">
-        <v>1.21</v>
+        <v>1.01</v>
       </c>
       <c r="W42" t="n">
-        <v>1.87</v>
+        <v>1.01</v>
       </c>
       <c r="X42" t="n">
         <v>1000</v>
@@ -11240,7 +11240,7 @@
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-07-17 16:08:18</t>
+          <t>2026-07-17 18:30:45</t>
         </is>
       </c>
     </row>
@@ -11271,19 +11271,19 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="G43" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="H43" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="I43" t="n">
         <v>4.8</v>
       </c>
       <c r="J43" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="K43" t="n">
         <v>3.75</v>
@@ -11301,10 +11301,10 @@
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="Q43" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="R43" t="n">
         <v>0</v>
@@ -11494,7 +11494,7 @@
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-07-17 16:08:18</t>
+          <t>2026-07-17 18:30:45</t>
         </is>
       </c>
     </row>
@@ -11748,7 +11748,7 @@
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-07-17 16:08:18</t>
+          <t>2026-07-17 18:30:45</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-19.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-19.xlsx
@@ -857,230 +857,230 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3.75</v>
+        <v>1.45</v>
       </c>
       <c r="G2" t="n">
-        <v>4.3</v>
+        <v>1000</v>
       </c>
       <c r="H2" t="n">
-        <v>2.02</v>
+        <v>1.41</v>
       </c>
       <c r="I2" t="n">
-        <v>2.18</v>
+        <v>100</v>
       </c>
       <c r="J2" t="n">
-        <v>3.55</v>
+        <v>1.28</v>
       </c>
       <c r="K2" t="n">
-        <v>3.85</v>
+        <v>950</v>
       </c>
       <c r="L2" t="n">
-        <v>1.38</v>
+        <v>1.13</v>
       </c>
       <c r="M2" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N2" t="n">
-        <v>3.9</v>
+        <v>1.32</v>
       </c>
       <c r="O2" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S2" t="n">
         <v>1.31</v>
       </c>
-      <c r="P2" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="S2" t="n">
-        <v>3.3</v>
-      </c>
       <c r="T2" t="n">
-        <v>1.74</v>
+        <v>1.11</v>
       </c>
       <c r="U2" t="n">
-        <v>2.12</v>
+        <v>1.11</v>
       </c>
       <c r="V2" t="n">
-        <v>1.86</v>
+        <v>1.04</v>
       </c>
       <c r="W2" t="n">
-        <v>1.31</v>
+        <v>1.01</v>
       </c>
       <c r="X2" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="Y2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>8</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>18</v>
+      </c>
+      <c r="AT2" t="n">
         <v>10.5</v>
       </c>
-      <c r="Z2" t="n">
-        <v>14</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>26</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AC2" t="n">
+      <c r="AU2" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV2" t="n">
         <v>8.6</v>
       </c>
-      <c r="AD2" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>23</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>30</v>
-      </c>
-      <c r="AG2" t="n">
+      <c r="AW2" t="n">
         <v>16.5</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>38</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>95</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>50</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>65</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>120</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>50</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>21</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>18.5</v>
       </c>
       <c r="AX2" t="n">
         <v>19</v>
       </c>
       <c r="AY2" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="AZ2" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BA2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BB2" t="n">
-        <v>8.6</v>
+        <v>40</v>
       </c>
       <c r="BC2" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BD2" t="n">
         <v>36</v>
       </c>
       <c r="BE2" t="n">
-        <v>8.800000000000001</v>
+        <v>40</v>
       </c>
       <c r="BF2" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BG2" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BH2" t="n">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.05</v>
+        <v>2.8</v>
       </c>
       <c r="BJ2" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BL2" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BN2" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BO2" t="n">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="BP2" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>23</v>
+        <v>1.01</v>
       </c>
       <c r="BR2" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>29</v>
+        <v>1.01</v>
       </c>
       <c r="BT2" t="n">
-        <v>5.1</v>
+        <v>1000</v>
       </c>
       <c r="BU2" t="n">
-        <v>3.75</v>
+        <v>1.01</v>
       </c>
       <c r="BV2" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BX2" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BZ2" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-17 18:30:45</t>
+          <t>2026-07-17 20:53:41</t>
         </is>
       </c>
     </row>
@@ -1111,52 +1111,52 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="G3" t="n">
         <v>1.7</v>
       </c>
       <c r="H3" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="I3" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="J3" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="K3" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="L3" t="n">
         <v>1.01</v>
       </c>
       <c r="M3" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N3" t="n">
-        <v>2.88</v>
+        <v>3.25</v>
       </c>
       <c r="O3" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="P3" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="Q3" t="n">
         <v>2.16</v>
       </c>
       <c r="R3" t="n">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="S3" t="n">
-        <v>2.1</v>
+        <v>4</v>
       </c>
       <c r="T3" t="n">
-        <v>2.04</v>
+        <v>2.16</v>
       </c>
       <c r="U3" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="V3" t="n">
         <v>1.16</v>
@@ -1165,112 +1165,112 @@
         <v>2.42</v>
       </c>
       <c r="X3" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="Y3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Z3" t="n">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="AA3" t="n">
-        <v>280</v>
+        <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AC3" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AD3" t="n">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="AE3" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AF3" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AG3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AH3" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="AI3" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="AK3" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="AL3" t="n">
-        <v>70</v>
+        <v>250</v>
       </c>
       <c r="AM3" t="n">
-        <v>230</v>
+        <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AO3" t="n">
-        <v>240</v>
+        <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AR3" t="n">
-        <v>7.2</v>
+        <v>34</v>
       </c>
       <c r="AS3" t="n">
-        <v>8</v>
+        <v>46</v>
       </c>
       <c r="AT3" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AU3" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AV3" t="n">
         <v>19</v>
       </c>
       <c r="AW3" t="n">
-        <v>7.8</v>
+        <v>38</v>
       </c>
       <c r="AX3" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="AY3" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ3" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BA3" t="n">
-        <v>7.8</v>
+        <v>42</v>
       </c>
       <c r="BB3" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="BC3" t="n">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="BE3" t="n">
-        <v>8</v>
+        <v>48</v>
       </c>
       <c r="BF3" t="n">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG3" t="n">
-        <v>8</v>
+        <v>46</v>
       </c>
       <c r="BH3" t="n">
         <v>1000</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-17 18:30:45</t>
+          <t>2026-07-17 20:53:41</t>
         </is>
       </c>
     </row>
@@ -1365,22 +1365,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="G4" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="H4" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="I4" t="n">
-        <v>1.81</v>
+        <v>1.9</v>
       </c>
       <c r="J4" t="n">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="K4" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="L4" t="n">
         <v>1.01</v>
@@ -1389,40 +1389,40 @@
         <v>1.09</v>
       </c>
       <c r="N4" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="O4" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="P4" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="R4" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="S4" t="n">
         <v>2.08</v>
       </c>
       <c r="T4" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="U4" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="V4" t="n">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="W4" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="X4" t="n">
         <v>1000</v>
       </c>
       <c r="Y4" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z4" t="n">
         <v>1000</v>
@@ -1473,58 +1473,58 @@
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AQ4" t="n">
         <v>1.01</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="BH4" t="n">
         <v>1000</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-17 18:30:45</t>
+          <t>2026-07-17 20:53:41</t>
         </is>
       </c>
     </row>
@@ -1631,7 +1631,7 @@
         <v>1000</v>
       </c>
       <c r="J5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K5" t="n">
         <v>1000</v>
@@ -1640,10 +1640,10 @@
         <v>1.01</v>
       </c>
       <c r="M5" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N5" t="n">
-        <v>1.88</v>
+        <v>1.34</v>
       </c>
       <c r="O5" t="n">
         <v>1.31</v>
@@ -1658,7 +1658,7 @@
         <v>1.18</v>
       </c>
       <c r="S5" t="n">
-        <v>1.05</v>
+        <v>1.32</v>
       </c>
       <c r="T5" t="n">
         <v>1.11</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-17 18:30:45</t>
+          <t>2026-07-17 20:53:41</t>
         </is>
       </c>
     </row>
@@ -1894,16 +1894,16 @@
         <v>1.01</v>
       </c>
       <c r="M6" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N6" t="n">
-        <v>1.34</v>
+        <v>1.1</v>
       </c>
       <c r="O6" t="n">
         <v>1.31</v>
       </c>
       <c r="P6" t="n">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="Q6" t="n">
         <v>1.33</v>
@@ -1915,10 +1915,10 @@
         <v>1.33</v>
       </c>
       <c r="T6" t="n">
-        <v>1.11</v>
+        <v>1.43</v>
       </c>
       <c r="U6" t="n">
-        <v>1.11</v>
+        <v>1.7</v>
       </c>
       <c r="V6" t="n">
         <v>1.01</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-17 18:30:45</t>
+          <t>2026-07-17 20:53:41</t>
         </is>
       </c>
     </row>
@@ -2148,10 +2148,10 @@
         <v>1.01</v>
       </c>
       <c r="M7" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N7" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="O7" t="n">
         <v>1.33</v>
@@ -2160,13 +2160,13 @@
         <v>1.25</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="R7" t="n">
         <v>1.18</v>
       </c>
       <c r="S7" t="n">
-        <v>1.98</v>
+        <v>1.05</v>
       </c>
       <c r="T7" t="n">
         <v>1.11</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-17 18:30:45</t>
+          <t>2026-07-17 20:53:41</t>
         </is>
       </c>
     </row>
@@ -2384,7 +2384,7 @@
         <v>1.04</v>
       </c>
       <c r="G8" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="H8" t="n">
         <v>1.04</v>
@@ -2402,25 +2402,25 @@
         <v>1.01</v>
       </c>
       <c r="M8" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N8" t="n">
-        <v>1.1</v>
+        <v>1.45</v>
       </c>
       <c r="O8" t="n">
         <v>1.22</v>
       </c>
       <c r="P8" t="n">
-        <v>1.45</v>
+        <v>1.25</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.72</v>
+        <v>1.22</v>
       </c>
       <c r="R8" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="S8" t="n">
-        <v>1.05</v>
+        <v>1.22</v>
       </c>
       <c r="T8" t="n">
         <v>1.11</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-17 18:30:45</t>
+          <t>2026-07-17 20:53:41</t>
         </is>
       </c>
     </row>
@@ -2647,7 +2647,7 @@
         <v>1000</v>
       </c>
       <c r="J9" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="K9" t="n">
         <v>1000</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-17 18:30:45</t>
+          <t>2026-07-17 20:53:41</t>
         </is>
       </c>
     </row>
@@ -2889,22 +2889,22 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.5</v>
+        <v>1.27</v>
       </c>
       <c r="G10" t="n">
-        <v>1.69</v>
+        <v>1.74</v>
       </c>
       <c r="H10" t="n">
-        <v>1.62</v>
+        <v>4.1</v>
       </c>
       <c r="I10" t="n">
         <v>1000</v>
       </c>
       <c r="J10" t="n">
-        <v>1.48</v>
+        <v>3.65</v>
       </c>
       <c r="K10" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L10" t="n">
         <v>1.01</v>
@@ -2928,7 +2928,7 @@
         <v>1.27</v>
       </c>
       <c r="S10" t="n">
-        <v>1.42</v>
+        <v>1.14</v>
       </c>
       <c r="T10" t="n">
         <v>1.11</v>
@@ -2937,10 +2937,10 @@
         <v>1.11</v>
       </c>
       <c r="V10" t="n">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="W10" t="n">
-        <v>2.32</v>
+        <v>1.01</v>
       </c>
       <c r="X10" t="n">
         <v>1000</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-17 18:30:45</t>
+          <t>2026-07-17 20:53:41</t>
         </is>
       </c>
     </row>
@@ -3155,7 +3155,7 @@
         <v>1000</v>
       </c>
       <c r="J11" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="K11" t="n">
         <v>1000</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-17 18:30:45</t>
+          <t>2026-07-17 20:53:41</t>
         </is>
       </c>
     </row>
@@ -3409,7 +3409,7 @@
         <v>1000</v>
       </c>
       <c r="J12" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="K12" t="n">
         <v>1000</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-17 18:30:45</t>
+          <t>2026-07-17 20:53:41</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
         <v>1000</v>
       </c>
       <c r="J13" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="K13" t="n">
         <v>1000</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-17 18:30:45</t>
+          <t>2026-07-17 20:53:41</t>
         </is>
       </c>
     </row>
@@ -3917,7 +3917,7 @@
         <v>1000</v>
       </c>
       <c r="J14" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="K14" t="n">
         <v>1000</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-17 18:30:45</t>
+          <t>2026-07-17 20:53:41</t>
         </is>
       </c>
     </row>
@@ -4171,7 +4171,7 @@
         <v>1000</v>
       </c>
       <c r="J15" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="K15" t="n">
         <v>1000</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-17 18:30:45</t>
+          <t>2026-07-17 20:53:41</t>
         </is>
       </c>
     </row>
@@ -4425,7 +4425,7 @@
         <v>1000</v>
       </c>
       <c r="J16" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="K16" t="n">
         <v>1000</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-17 18:30:45</t>
+          <t>2026-07-17 20:53:41</t>
         </is>
       </c>
     </row>
@@ -4691,13 +4691,13 @@
         <v>1.01</v>
       </c>
       <c r="N17" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="O17" t="n">
         <v>1.5</v>
       </c>
       <c r="P17" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q17" t="n">
         <v>1.5</v>
@@ -4706,13 +4706,13 @@
         <v>1.12</v>
       </c>
       <c r="S17" t="n">
-        <v>1.05</v>
+        <v>1.49</v>
       </c>
       <c r="T17" t="n">
-        <v>1.11</v>
+        <v>1.72</v>
       </c>
       <c r="U17" t="n">
-        <v>1.11</v>
+        <v>1.41</v>
       </c>
       <c r="V17" t="n">
         <v>1.01</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-17 18:30:45</t>
+          <t>2026-07-17 20:53:41</t>
         </is>
       </c>
     </row>
@@ -4921,7 +4921,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.31</v>
+        <v>1.54</v>
       </c>
       <c r="G18" t="n">
         <v>1000</v>
@@ -4930,10 +4930,10 @@
         <v>1.04</v>
       </c>
       <c r="I18" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="J18" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="K18" t="n">
         <v>1000</v>
@@ -4957,10 +4957,10 @@
         <v>1.23</v>
       </c>
       <c r="R18" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="S18" t="n">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="T18" t="n">
         <v>1.11</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-17 18:30:45</t>
+          <t>2026-07-17 20:53:41</t>
         </is>
       </c>
     </row>
@@ -5178,10 +5178,10 @@
         <v>2.56</v>
       </c>
       <c r="G19" t="n">
-        <v>3.4</v>
+        <v>1000</v>
       </c>
       <c r="H19" t="n">
-        <v>2.36</v>
+        <v>1.4</v>
       </c>
       <c r="I19" t="n">
         <v>2.92</v>
@@ -5190,7 +5190,7 @@
         <v>3.3</v>
       </c>
       <c r="K19" t="n">
-        <v>950</v>
+        <v>3.95</v>
       </c>
       <c r="L19" t="n">
         <v>1.01</v>
@@ -5199,7 +5199,7 @@
         <v>1.01</v>
       </c>
       <c r="N19" t="n">
-        <v>1.1</v>
+        <v>1.47</v>
       </c>
       <c r="O19" t="n">
         <v>1.23</v>
@@ -5214,7 +5214,7 @@
         <v>1.25</v>
       </c>
       <c r="S19" t="n">
-        <v>1.23</v>
+        <v>2.24</v>
       </c>
       <c r="T19" t="n">
         <v>1.11</v>
@@ -5226,7 +5226,7 @@
         <v>1.55</v>
       </c>
       <c r="W19" t="n">
-        <v>1.41</v>
+        <v>1.03</v>
       </c>
       <c r="X19" t="n">
         <v>1000</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-17 18:30:45</t>
+          <t>2026-07-17 20:53:41</t>
         </is>
       </c>
     </row>
@@ -5441,7 +5441,7 @@
         <v>1000</v>
       </c>
       <c r="J20" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="K20" t="n">
         <v>1000</v>
@@ -5453,13 +5453,13 @@
         <v>1.01</v>
       </c>
       <c r="N20" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="O20" t="n">
         <v>1.16</v>
       </c>
       <c r="P20" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Q20" t="n">
         <v>1.16</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-17 18:30:45</t>
+          <t>2026-07-17 20:53:41</t>
         </is>
       </c>
     </row>
@@ -5686,34 +5686,34 @@
         <v>2.08</v>
       </c>
       <c r="G21" t="n">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="H21" t="n">
-        <v>3.55</v>
+        <v>1.38</v>
       </c>
       <c r="I21" t="n">
-        <v>4.3</v>
+        <v>990</v>
       </c>
       <c r="J21" t="n">
-        <v>3.55</v>
+        <v>1.85</v>
       </c>
       <c r="K21" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="L21" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="M21" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N21" t="n">
-        <v>1.1</v>
+        <v>1.54</v>
       </c>
       <c r="O21" t="n">
         <v>1.3</v>
       </c>
       <c r="P21" t="n">
-        <v>1.25</v>
+        <v>1.53</v>
       </c>
       <c r="Q21" t="n">
         <v>1.31</v>
@@ -5725,188 +5725,188 @@
         <v>1.05</v>
       </c>
       <c r="T21" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="W21" t="n">
         <v>1.78</v>
       </c>
-      <c r="U21" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="W21" t="n">
+      <c r="X21" t="n">
+        <v>50</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>42</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>48</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>130</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>29</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>23</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>95</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>26</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>32</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>130</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>36</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>38</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>75</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>250</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>38</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>140</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AQ21" t="n">
         <v>1.83</v>
       </c>
-      <c r="X21" t="n">
-        <v>14</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>15</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>30</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>85</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>50</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>18</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>60</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>26</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>23</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>38</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>130</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>16</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>55</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>13</v>
-      </c>
       <c r="AR21" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AS21" t="n">
-        <v>12</v>
+        <v>1.89</v>
       </c>
       <c r="AT21" t="n">
-        <v>8.6</v>
+        <v>4.4</v>
       </c>
       <c r="AU21" t="n">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="AV21" t="n">
         <v>14</v>
       </c>
       <c r="AW21" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="AX21" t="n">
-        <v>11.5</v>
+        <v>9.6</v>
       </c>
       <c r="AY21" t="n">
-        <v>9.800000000000001</v>
+        <v>1.68</v>
       </c>
       <c r="AZ21" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>21</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>23</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD21" t="n">
         <v>15.5</v>
       </c>
-      <c r="BA21" t="n">
-        <v>48</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>22</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>19</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>32</v>
-      </c>
       <c r="BE21" t="n">
-        <v>75</v>
+        <v>30</v>
       </c>
       <c r="BF21" t="n">
-        <v>13.5</v>
+        <v>4.6</v>
       </c>
       <c r="BG21" t="n">
-        <v>32</v>
+        <v>9.6</v>
       </c>
       <c r="BH21" t="n">
-        <v>3.85</v>
+        <v>1000</v>
       </c>
       <c r="BI21" t="n">
-        <v>2.84</v>
+        <v>1.01</v>
       </c>
       <c r="BJ21" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BK21" t="n">
         <v>1.01</v>
       </c>
       <c r="BL21" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="BM21" t="n">
         <v>1.01</v>
       </c>
       <c r="BN21" t="n">
-        <v>5.4</v>
+        <v>1000</v>
       </c>
       <c r="BO21" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BP21" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="BQ21" t="n">
         <v>1.01</v>
       </c>
       <c r="BR21" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BS21" t="n">
         <v>1.01</v>
       </c>
       <c r="BT21" t="n">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="BU21" t="n">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="BV21" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BW21" t="n">
         <v>1.01</v>
       </c>
       <c r="BX21" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BY21" t="n">
         <v>1.01</v>
       </c>
       <c r="BZ21" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="CA21" t="n">
         <v>1.01</v>
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-07-17 18:30:45</t>
+          <t>2026-07-17 20:53:41</t>
         </is>
       </c>
     </row>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-07-17 18:30:45</t>
+          <t>2026-07-17 20:53:41</t>
         </is>
       </c>
     </row>
@@ -6221,16 +6221,16 @@
         <v>1.11</v>
       </c>
       <c r="P23" t="n">
-        <v>1.25</v>
+        <v>1.43</v>
       </c>
       <c r="Q23" t="n">
         <v>1.11</v>
       </c>
       <c r="R23" t="n">
-        <v>1.23</v>
+        <v>1.43</v>
       </c>
       <c r="S23" t="n">
-        <v>1.11</v>
+        <v>1.72</v>
       </c>
       <c r="T23" t="n">
         <v>1.11</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-07-17 18:30:45</t>
+          <t>2026-07-17 20:53:41</t>
         </is>
       </c>
     </row>
@@ -6448,7 +6448,7 @@
         <v>5.6</v>
       </c>
       <c r="G24" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="H24" t="n">
         <v>1.62</v>
@@ -6469,13 +6469,13 @@
         <v>1.03</v>
       </c>
       <c r="N24" t="n">
-        <v>1.11</v>
+        <v>3.55</v>
       </c>
       <c r="O24" t="n">
         <v>1.16</v>
       </c>
       <c r="P24" t="n">
-        <v>1.61</v>
+        <v>2.5</v>
       </c>
       <c r="Q24" t="n">
         <v>1.01</v>
@@ -6484,7 +6484,7 @@
         <v>1.58</v>
       </c>
       <c r="S24" t="n">
-        <v>1.17</v>
+        <v>1.52</v>
       </c>
       <c r="T24" t="n">
         <v>1.55</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-07-17 18:30:45</t>
+          <t>2026-07-17 20:53:41</t>
         </is>
       </c>
     </row>
@@ -6723,28 +6723,28 @@
         <v>1.04</v>
       </c>
       <c r="N25" t="n">
-        <v>3</v>
+        <v>4.3</v>
       </c>
       <c r="O25" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="P25" t="n">
         <v>2.3</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="R25" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="S25" t="n">
-        <v>1.7</v>
+        <v>2.16</v>
       </c>
       <c r="T25" t="n">
         <v>1.54</v>
       </c>
       <c r="U25" t="n">
-        <v>1.11</v>
+        <v>1.92</v>
       </c>
       <c r="V25" t="n">
         <v>1.92</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-07-17 18:30:45</t>
+          <t>2026-07-17 20:53:41</t>
         </is>
       </c>
     </row>
@@ -6959,16 +6959,16 @@
         <v>1.32</v>
       </c>
       <c r="H26" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="I26" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="J26" t="n">
         <v>6.2</v>
       </c>
       <c r="K26" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="L26" t="n">
         <v>1.01</v>
@@ -6977,19 +6977,19 @@
         <v>1.03</v>
       </c>
       <c r="N26" t="n">
-        <v>2.36</v>
+        <v>2.48</v>
       </c>
       <c r="O26" t="n">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="P26" t="n">
         <v>1.25</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="R26" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S26" t="n">
         <v>1.55</v>
@@ -7001,7 +7001,7 @@
         <v>1.11</v>
       </c>
       <c r="V26" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="W26" t="n">
         <v>4</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-07-17 18:30:45</t>
+          <t>2026-07-17 20:53:41</t>
         </is>
       </c>
     </row>
@@ -7207,13 +7207,13 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>3.2</v>
+        <v>1.8</v>
       </c>
       <c r="G27" t="n">
         <v>1000</v>
       </c>
       <c r="H27" t="n">
-        <v>1.26</v>
+        <v>1.72</v>
       </c>
       <c r="I27" t="n">
         <v>100</v>
@@ -7222,7 +7222,7 @@
         <v>1.79</v>
       </c>
       <c r="K27" t="n">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="L27" t="n">
         <v>1.01</v>
@@ -7231,13 +7231,13 @@
         <v>1.01</v>
       </c>
       <c r="N27" t="n">
-        <v>1.1</v>
+        <v>1.28</v>
       </c>
       <c r="O27" t="n">
         <v>1.15</v>
       </c>
       <c r="P27" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="Q27" t="n">
         <v>1.15</v>
@@ -7255,7 +7255,7 @@
         <v>1.11</v>
       </c>
       <c r="V27" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="W27" t="n">
         <v>1.01</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-07-17 18:30:45</t>
+          <t>2026-07-17 20:53:41</t>
         </is>
       </c>
     </row>
@@ -7461,22 +7461,22 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="G28" t="n">
-        <v>6.8</v>
+        <v>8.4</v>
       </c>
       <c r="H28" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="I28" t="n">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="J28" t="n">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="K28" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="L28" t="n">
         <v>1.01</v>
@@ -7485,79 +7485,79 @@
         <v>1.04</v>
       </c>
       <c r="N28" t="n">
-        <v>2.28</v>
+        <v>1.46</v>
       </c>
       <c r="O28" t="n">
         <v>1.23</v>
       </c>
       <c r="P28" t="n">
-        <v>2.18</v>
+        <v>1.46</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.71</v>
+        <v>1.23</v>
       </c>
       <c r="R28" t="n">
-        <v>1.37</v>
+        <v>1.21</v>
       </c>
       <c r="S28" t="n">
-        <v>2.52</v>
+        <v>1.23</v>
       </c>
       <c r="T28" t="n">
-        <v>1.57</v>
+        <v>1.11</v>
       </c>
       <c r="U28" t="n">
-        <v>1.75</v>
+        <v>1.11</v>
       </c>
       <c r="V28" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="W28" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="X28" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="Y28" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="Z28" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AA28" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AB28" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AC28" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AD28" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AE28" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AF28" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AG28" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AH28" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AI28" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AJ28" t="n">
         <v>1000</v>
       </c>
       <c r="AK28" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AL28" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AM28" t="n">
         <v>1000</v>
@@ -7566,61 +7566,61 @@
         <v>1000</v>
       </c>
       <c r="AO28" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AP28" t="n">
-        <v>2.66</v>
+        <v>1.01</v>
       </c>
       <c r="AQ28" t="n">
-        <v>2.4</v>
+        <v>1.01</v>
       </c>
       <c r="AR28" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AS28" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AT28" t="n">
-        <v>2.7</v>
+        <v>1.01</v>
       </c>
       <c r="AU28" t="n">
-        <v>2.44</v>
+        <v>1.01</v>
       </c>
       <c r="AV28" t="n">
-        <v>2.42</v>
+        <v>1.01</v>
       </c>
       <c r="AW28" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AX28" t="n">
-        <v>2.82</v>
+        <v>1.01</v>
       </c>
       <c r="AY28" t="n">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="AZ28" t="n">
-        <v>2.66</v>
+        <v>1.01</v>
       </c>
       <c r="BA28" t="n">
-        <v>2.76</v>
+        <v>1.01</v>
       </c>
       <c r="BB28" t="n">
-        <v>2.94</v>
+        <v>1.01</v>
       </c>
       <c r="BC28" t="n">
-        <v>2.86</v>
+        <v>1.01</v>
       </c>
       <c r="BD28" t="n">
-        <v>2.86</v>
+        <v>1.01</v>
       </c>
       <c r="BE28" t="n">
-        <v>2.94</v>
+        <v>1.01</v>
       </c>
       <c r="BF28" t="n">
-        <v>2.94</v>
+        <v>1.01</v>
       </c>
       <c r="BG28" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BH28" t="n">
         <v>1000</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-07-17 18:30:45</t>
+          <t>2026-07-17 20:53:41</t>
         </is>
       </c>
     </row>
@@ -7715,46 +7715,46 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2.74</v>
+        <v>1.04</v>
       </c>
       <c r="G29" t="n">
-        <v>3.15</v>
+        <v>1000</v>
       </c>
       <c r="H29" t="n">
-        <v>2.66</v>
+        <v>1.04</v>
       </c>
       <c r="I29" t="n">
-        <v>3.05</v>
+        <v>1000</v>
       </c>
       <c r="J29" t="n">
-        <v>3.05</v>
+        <v>1.02</v>
       </c>
       <c r="K29" t="n">
-        <v>3.85</v>
+        <v>1000</v>
       </c>
       <c r="L29" t="n">
-        <v>1.38</v>
+        <v>1.01</v>
       </c>
       <c r="M29" t="n">
         <v>1.01</v>
       </c>
       <c r="N29" t="n">
-        <v>2.56</v>
+        <v>1.25</v>
       </c>
       <c r="O29" t="n">
         <v>1.38</v>
       </c>
       <c r="P29" t="n">
-        <v>1.67</v>
+        <v>1.25</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.18</v>
+        <v>1.38</v>
       </c>
       <c r="R29" t="n">
         <v>1.18</v>
       </c>
       <c r="S29" t="n">
-        <v>2.92</v>
+        <v>1.37</v>
       </c>
       <c r="T29" t="n">
         <v>1.11</v>
@@ -7763,10 +7763,10 @@
         <v>1.11</v>
       </c>
       <c r="V29" t="n">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="W29" t="n">
-        <v>1.42</v>
+        <v>1.01</v>
       </c>
       <c r="X29" t="n">
         <v>1000</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-07-17 18:30:45</t>
+          <t>2026-07-17 20:53:41</t>
         </is>
       </c>
     </row>
@@ -7969,16 +7969,16 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>2.2</v>
+        <v>1.05</v>
       </c>
       <c r="G30" t="n">
         <v>1000</v>
       </c>
       <c r="H30" t="n">
-        <v>1.54</v>
+        <v>1.06</v>
       </c>
       <c r="I30" t="n">
-        <v>1.85</v>
+        <v>110</v>
       </c>
       <c r="J30" t="n">
         <v>3.5</v>
@@ -7993,10 +7993,10 @@
         <v>1.01</v>
       </c>
       <c r="N30" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="O30" t="n">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="P30" t="n">
         <v>1.25</v>
@@ -8008,7 +8008,7 @@
         <v>1.12</v>
       </c>
       <c r="S30" t="n">
-        <v>1.05</v>
+        <v>1.53</v>
       </c>
       <c r="T30" t="n">
         <v>1.11</v>
@@ -8017,10 +8017,10 @@
         <v>1.11</v>
       </c>
       <c r="V30" t="n">
-        <v>2.18</v>
+        <v>1.03</v>
       </c>
       <c r="W30" t="n">
-        <v>1.12</v>
+        <v>1.03</v>
       </c>
       <c r="X30" t="n">
         <v>1000</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-07-17 18:30:45</t>
+          <t>2026-07-17 20:53:41</t>
         </is>
       </c>
     </row>
@@ -8223,22 +8223,22 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>4.8</v>
+        <v>1.04</v>
       </c>
       <c r="G31" t="n">
-        <v>5.8</v>
+        <v>1000</v>
       </c>
       <c r="H31" t="n">
-        <v>1.59</v>
+        <v>1.04</v>
       </c>
       <c r="I31" t="n">
-        <v>1.74</v>
+        <v>1000</v>
       </c>
       <c r="J31" t="n">
-        <v>4.5</v>
+        <v>1.02</v>
       </c>
       <c r="K31" t="n">
-        <v>5.3</v>
+        <v>1000</v>
       </c>
       <c r="L31" t="n">
         <v>1.01</v>
@@ -8247,22 +8247,22 @@
         <v>1.01</v>
       </c>
       <c r="N31" t="n">
-        <v>2.68</v>
+        <v>1.27</v>
       </c>
       <c r="O31" t="n">
         <v>1.14</v>
       </c>
       <c r="P31" t="n">
-        <v>2.68</v>
+        <v>1.27</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.48</v>
+        <v>1.13</v>
       </c>
       <c r="R31" t="n">
-        <v>1.57</v>
+        <v>1.18</v>
       </c>
       <c r="S31" t="n">
-        <v>2</v>
+        <v>1.14</v>
       </c>
       <c r="T31" t="n">
         <v>1.11</v>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-07-17 18:30:45</t>
+          <t>2026-07-17 20:53:41</t>
         </is>
       </c>
     </row>
@@ -8477,166 +8477,166 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1.64</v>
+        <v>1.04</v>
       </c>
       <c r="G32" t="n">
-        <v>1.77</v>
+        <v>1000</v>
       </c>
       <c r="H32" t="n">
-        <v>5.6</v>
+        <v>1.04</v>
       </c>
       <c r="I32" t="n">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="J32" t="n">
-        <v>3.7</v>
+        <v>1.01</v>
       </c>
       <c r="K32" t="n">
-        <v>4.8</v>
+        <v>1000</v>
       </c>
       <c r="L32" t="n">
         <v>1.01</v>
       </c>
       <c r="M32" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N32" t="n">
-        <v>3.35</v>
+        <v>1.33</v>
       </c>
       <c r="O32" t="n">
         <v>1.35</v>
       </c>
       <c r="P32" t="n">
-        <v>1.81</v>
+        <v>1.33</v>
       </c>
       <c r="Q32" t="n">
-        <v>2</v>
+        <v>1.35</v>
       </c>
       <c r="R32" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="S32" t="n">
-        <v>3.7</v>
+        <v>1.05</v>
       </c>
       <c r="T32" t="n">
-        <v>1.95</v>
+        <v>1.11</v>
       </c>
       <c r="U32" t="n">
-        <v>1.84</v>
+        <v>1.11</v>
       </c>
       <c r="V32" t="n">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="W32" t="n">
-        <v>2.3</v>
+        <v>1.01</v>
       </c>
       <c r="X32" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="Y32" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="Z32" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AA32" t="n">
-        <v>210</v>
+        <v>1000</v>
       </c>
       <c r="AB32" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="AC32" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AD32" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AE32" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AF32" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AG32" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH32" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AI32" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AJ32" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AK32" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AL32" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AM32" t="n">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AN32" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AO32" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AP32" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AQ32" t="n">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="AR32" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="AS32" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="AT32" t="n">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="AU32" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AV32" t="n">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="AW32" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="AX32" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AY32" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AZ32" t="n">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="BA32" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BB32" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC32" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="BD32" t="n">
-        <v>30</v>
+        <v>1.01</v>
       </c>
       <c r="BE32" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BF32" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="BG32" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH32" t="n">
         <v>1000</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-07-17 18:30:45</t>
+          <t>2026-07-17 20:53:41</t>
         </is>
       </c>
     </row>
@@ -8731,58 +8731,58 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>2.04</v>
+        <v>1.04</v>
       </c>
       <c r="G33" t="n">
-        <v>2.3</v>
+        <v>1000</v>
       </c>
       <c r="H33" t="n">
-        <v>3.3</v>
+        <v>1.04</v>
       </c>
       <c r="I33" t="n">
-        <v>4.2</v>
+        <v>1000</v>
       </c>
       <c r="J33" t="n">
-        <v>3.55</v>
+        <v>1.02</v>
       </c>
       <c r="K33" t="n">
-        <v>4.5</v>
+        <v>1000</v>
       </c>
       <c r="L33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M33" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N33" t="n">
         <v>1.25</v>
-      </c>
-      <c r="M33" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="N33" t="n">
-        <v>1.1</v>
       </c>
       <c r="O33" t="n">
         <v>1.22</v>
       </c>
       <c r="P33" t="n">
-        <v>2.1</v>
+        <v>1.25</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.74</v>
+        <v>1.22</v>
       </c>
       <c r="R33" t="n">
-        <v>1.41</v>
+        <v>1.18</v>
       </c>
       <c r="S33" t="n">
-        <v>2.5</v>
+        <v>1.22</v>
       </c>
       <c r="T33" t="n">
-        <v>1.47</v>
+        <v>1.11</v>
       </c>
       <c r="U33" t="n">
-        <v>1.96</v>
+        <v>1.11</v>
       </c>
       <c r="V33" t="n">
-        <v>1.31</v>
+        <v>1.01</v>
       </c>
       <c r="W33" t="n">
-        <v>1.76</v>
+        <v>1.01</v>
       </c>
       <c r="X33" t="n">
         <v>1000</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-07-17 18:30:45</t>
+          <t>2026-07-17 20:53:41</t>
         </is>
       </c>
     </row>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-07-17 18:30:45</t>
+          <t>2026-07-17 20:53:41</t>
         </is>
       </c>
     </row>
@@ -9263,7 +9263,7 @@
         <v>1.01</v>
       </c>
       <c r="N35" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="O35" t="n">
         <v>1.15</v>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-07-17 18:30:45</t>
+          <t>2026-07-17 20:53:41</t>
         </is>
       </c>
     </row>
@@ -9499,13 +9499,13 @@
         <v>1.79</v>
       </c>
       <c r="H36" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="I36" t="n">
         <v>1000</v>
       </c>
       <c r="J36" t="n">
-        <v>3.65</v>
+        <v>1.03</v>
       </c>
       <c r="K36" t="n">
         <v>1000</v>
@@ -9541,7 +9541,7 @@
         <v>1.11</v>
       </c>
       <c r="V36" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W36" t="n">
         <v>2.26</v>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-07-17 18:30:45</t>
+          <t>2026-07-17 20:53:41</t>
         </is>
       </c>
     </row>
@@ -9747,22 +9747,22 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>2.88</v>
+        <v>1.04</v>
       </c>
       <c r="G37" t="n">
-        <v>3.15</v>
+        <v>1000</v>
       </c>
       <c r="H37" t="n">
-        <v>2.88</v>
+        <v>1.04</v>
       </c>
       <c r="I37" t="n">
-        <v>3.3</v>
+        <v>1000</v>
       </c>
       <c r="J37" t="n">
-        <v>2.8</v>
+        <v>1.03</v>
       </c>
       <c r="K37" t="n">
-        <v>3.25</v>
+        <v>1000</v>
       </c>
       <c r="L37" t="n">
         <v>1.01</v>
@@ -9771,37 +9771,37 @@
         <v>1.01</v>
       </c>
       <c r="N37" t="n">
-        <v>2.2</v>
+        <v>1.25</v>
       </c>
       <c r="O37" t="n">
         <v>1.53</v>
       </c>
       <c r="P37" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.66</v>
+        <v>1.53</v>
       </c>
       <c r="R37" t="n">
         <v>1.18</v>
       </c>
       <c r="S37" t="n">
-        <v>4.4</v>
+        <v>1.53</v>
       </c>
       <c r="T37" t="n">
-        <v>1.9</v>
+        <v>1.11</v>
       </c>
       <c r="U37" t="n">
-        <v>1.67</v>
+        <v>1.11</v>
       </c>
       <c r="V37" t="n">
-        <v>1.43</v>
+        <v>1.01</v>
       </c>
       <c r="W37" t="n">
-        <v>1.46</v>
+        <v>1.01</v>
       </c>
       <c r="X37" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="Y37" t="n">
         <v>1000</v>
@@ -9855,122 +9855,122 @@
         <v>1000</v>
       </c>
       <c r="AP37" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="AQ37" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="AR37" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="AS37" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="AT37" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="AU37" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="AV37" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="AW37" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="AX37" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="AY37" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="AZ37" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="BA37" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="BB37" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="BC37" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="BD37" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="BE37" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="BF37" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="BG37" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="BH37" t="n">
         <v>1000</v>
       </c>
       <c r="BI37" t="n">
-        <v>1.55</v>
+        <v>1.04</v>
       </c>
       <c r="BJ37" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="BK37" t="n">
-        <v>1.42</v>
+        <v>1.04</v>
       </c>
       <c r="BL37" t="n">
         <v>1000</v>
       </c>
       <c r="BM37" t="n">
-        <v>1.56</v>
+        <v>1.04</v>
       </c>
       <c r="BN37" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="BO37" t="n">
-        <v>3.7</v>
+        <v>1.04</v>
       </c>
       <c r="BP37" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BQ37" t="n">
-        <v>1.49</v>
+        <v>1.04</v>
       </c>
       <c r="BR37" t="n">
         <v>1000</v>
       </c>
       <c r="BS37" t="n">
-        <v>1.56</v>
+        <v>1.04</v>
       </c>
       <c r="BT37" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BU37" t="n">
-        <v>3.85</v>
+        <v>1.04</v>
       </c>
       <c r="BV37" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BW37" t="n">
-        <v>1.5</v>
+        <v>1.04</v>
       </c>
       <c r="BX37" t="n">
         <v>1000</v>
       </c>
       <c r="BY37" t="n">
-        <v>1.56</v>
+        <v>1.04</v>
       </c>
       <c r="BZ37" t="n">
         <v>1000</v>
       </c>
       <c r="CA37" t="n">
-        <v>1.56</v>
+        <v>1.04</v>
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-07-17 18:30:45</t>
+          <t>2026-07-17 20:53:41</t>
         </is>
       </c>
     </row>
@@ -10001,40 +10001,40 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>3.9</v>
+        <v>1.85</v>
       </c>
       <c r="G38" t="n">
-        <v>4.5</v>
+        <v>1000</v>
       </c>
       <c r="H38" t="n">
-        <v>2.1</v>
+        <v>1.04</v>
       </c>
       <c r="I38" t="n">
         <v>2.18</v>
       </c>
       <c r="J38" t="n">
-        <v>3.15</v>
+        <v>1.88</v>
       </c>
       <c r="K38" t="n">
-        <v>3.5</v>
+        <v>1000</v>
       </c>
       <c r="L38" t="n">
         <v>1.01</v>
       </c>
       <c r="M38" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N38" t="n">
-        <v>2.84</v>
+        <v>1.26</v>
       </c>
       <c r="O38" t="n">
         <v>1.42</v>
       </c>
       <c r="P38" t="n">
-        <v>1.65</v>
+        <v>1.25</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.26</v>
+        <v>1.42</v>
       </c>
       <c r="R38" t="n">
         <v>1.18</v>
@@ -10070,7 +10070,7 @@
         <v>1000</v>
       </c>
       <c r="AC38" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="AD38" t="n">
         <v>1000</v>
@@ -10094,7 +10094,7 @@
         <v>1000</v>
       </c>
       <c r="AK38" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AL38" t="n">
         <v>1000</v>
@@ -10109,58 +10109,58 @@
         <v>1000</v>
       </c>
       <c r="AP38" t="n">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="AQ38" t="n">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="AR38" t="n">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="AS38" t="n">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="AT38" t="n">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="AU38" t="n">
         <v>1.01</v>
       </c>
       <c r="AV38" t="n">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="AW38" t="n">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="AX38" t="n">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="AY38" t="n">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="AZ38" t="n">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="BA38" t="n">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="BB38" t="n">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="BC38" t="n">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="BD38" t="n">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="BE38" t="n">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="BF38" t="n">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="BG38" t="n">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="BH38" t="n">
         <v>1000</v>
@@ -10224,7 +10224,7 @@
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-07-17 18:30:45</t>
+          <t>2026-07-17 20:53:41</t>
         </is>
       </c>
     </row>
@@ -10255,22 +10255,22 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>3.25</v>
+        <v>1.04</v>
       </c>
       <c r="G39" t="n">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="H39" t="n">
-        <v>2.32</v>
+        <v>1.04</v>
       </c>
       <c r="I39" t="n">
-        <v>2.62</v>
+        <v>1000</v>
       </c>
       <c r="J39" t="n">
-        <v>3</v>
+        <v>1.01</v>
       </c>
       <c r="K39" t="n">
-        <v>3.8</v>
+        <v>1000</v>
       </c>
       <c r="L39" t="n">
         <v>1.01</v>
@@ -10279,22 +10279,22 @@
         <v>1.01</v>
       </c>
       <c r="N39" t="n">
-        <v>2.48</v>
+        <v>1.25</v>
       </c>
       <c r="O39" t="n">
         <v>1.42</v>
       </c>
       <c r="P39" t="n">
-        <v>1.53</v>
+        <v>1.25</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.2</v>
+        <v>1.42</v>
       </c>
       <c r="R39" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="S39" t="n">
-        <v>3.7</v>
+        <v>1.02</v>
       </c>
       <c r="T39" t="n">
         <v>1.11</v>
@@ -10303,10 +10303,10 @@
         <v>1.11</v>
       </c>
       <c r="V39" t="n">
-        <v>1.61</v>
+        <v>1.01</v>
       </c>
       <c r="W39" t="n">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="X39" t="n">
         <v>1000</v>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-07-17 18:30:45</t>
+          <t>2026-07-17 20:53:41</t>
         </is>
       </c>
     </row>
@@ -10539,7 +10539,7 @@
         <v>1.3</v>
       </c>
       <c r="P40" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Q40" t="n">
         <v>1.3</v>
@@ -10548,7 +10548,7 @@
         <v>1.07</v>
       </c>
       <c r="S40" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T40" t="n">
         <v>1.11</v>
@@ -10732,7 +10732,7 @@
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-07-17 18:30:45</t>
+          <t>2026-07-17 20:53:41</t>
         </is>
       </c>
     </row>
@@ -10784,7 +10784,7 @@
         <v>1.01</v>
       </c>
       <c r="M41" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N41" t="n">
         <v>1.1</v>
@@ -10793,7 +10793,7 @@
         <v>1.23</v>
       </c>
       <c r="P41" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Q41" t="n">
         <v>1.23</v>
@@ -10805,16 +10805,16 @@
         <v>1.23</v>
       </c>
       <c r="T41" t="n">
-        <v>1.75</v>
+        <v>1.11</v>
       </c>
       <c r="U41" t="n">
-        <v>2.04</v>
+        <v>1.11</v>
       </c>
       <c r="V41" t="n">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="W41" t="n">
-        <v>2.34</v>
+        <v>1.01</v>
       </c>
       <c r="X41" t="n">
         <v>1000</v>
@@ -10986,7 +10986,7 @@
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-07-17 18:30:45</t>
+          <t>2026-07-17 20:53:41</t>
         </is>
       </c>
     </row>
@@ -11017,52 +11017,52 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>1.9</v>
+        <v>1.04</v>
       </c>
       <c r="G42" t="n">
-        <v>2.14</v>
+        <v>1000</v>
       </c>
       <c r="H42" t="n">
-        <v>3.45</v>
+        <v>1.04</v>
       </c>
       <c r="I42" t="n">
-        <v>5.6</v>
+        <v>1000</v>
       </c>
       <c r="J42" t="n">
-        <v>3</v>
+        <v>1.02</v>
       </c>
       <c r="K42" t="n">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="L42" t="n">
         <v>1.01</v>
       </c>
       <c r="M42" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N42" t="n">
-        <v>2.54</v>
+        <v>1.1</v>
       </c>
       <c r="O42" t="n">
         <v>1.38</v>
       </c>
       <c r="P42" t="n">
-        <v>1.68</v>
+        <v>1.08</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.04</v>
+        <v>1.38</v>
       </c>
       <c r="R42" t="n">
-        <v>1.19</v>
+        <v>1.07</v>
       </c>
       <c r="S42" t="n">
-        <v>3.3</v>
+        <v>1.37</v>
       </c>
       <c r="T42" t="n">
-        <v>1.71</v>
+        <v>1.11</v>
       </c>
       <c r="U42" t="n">
-        <v>1.66</v>
+        <v>1.11</v>
       </c>
       <c r="V42" t="n">
         <v>1.01</v>
@@ -11240,7 +11240,7 @@
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-07-17 18:30:45</t>
+          <t>2026-07-17 20:53:41</t>
         </is>
       </c>
     </row>
@@ -11271,230 +11271,230 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>2.2</v>
+        <v>1.04</v>
       </c>
       <c r="G43" t="n">
-        <v>2.5</v>
+        <v>1000</v>
       </c>
       <c r="H43" t="n">
-        <v>3.6</v>
+        <v>1.04</v>
       </c>
       <c r="I43" t="n">
-        <v>4.8</v>
+        <v>1000</v>
       </c>
       <c r="J43" t="n">
-        <v>2.94</v>
+        <v>1.02</v>
       </c>
       <c r="K43" t="n">
-        <v>3.75</v>
+        <v>1000</v>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="P43" t="n">
-        <v>1.54</v>
+        <v>1.25</v>
       </c>
       <c r="Q43" t="n">
-        <v>2.46</v>
+        <v>1.02</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC43" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD43" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE43" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF43" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG43" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH43" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI43" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ43" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK43" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL43" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM43" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN43" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO43" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH43" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ43" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL43" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN43" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP43" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR43" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT43" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV43" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX43" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ43" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-07-17 18:30:45</t>
+          <t>2026-07-17 20:53:41</t>
         </is>
       </c>
     </row>
@@ -11543,212 +11543,212 @@
         <v>1000</v>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P44" t="n">
         <v>1.24</v>
       </c>
       <c r="Q44" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP44" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ44" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR44" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS44" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT44" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU44" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV44" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW44" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX44" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY44" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ44" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA44" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB44" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC44" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD44" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE44" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF44" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG44" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI44" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK44" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM44" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO44" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ44" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS44" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU44" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW44" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY44" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA44" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-07-17 18:30:45</t>
+          <t>2026-07-17 20:53:41</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-19.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-19.xlsx
@@ -857,22 +857,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.45</v>
+        <v>3.05</v>
       </c>
       <c r="G2" t="n">
         <v>1000</v>
       </c>
       <c r="H2" t="n">
-        <v>1.41</v>
+        <v>1.65</v>
       </c>
       <c r="I2" t="n">
-        <v>100</v>
+        <v>2.6</v>
       </c>
       <c r="J2" t="n">
-        <v>1.28</v>
+        <v>2.88</v>
       </c>
       <c r="K2" t="n">
-        <v>950</v>
+        <v>500</v>
       </c>
       <c r="L2" t="n">
         <v>1.13</v>
@@ -881,13 +881,13 @@
         <v>1.06</v>
       </c>
       <c r="N2" t="n">
-        <v>1.32</v>
+        <v>1.1</v>
       </c>
       <c r="O2" t="n">
         <v>1.29</v>
       </c>
       <c r="P2" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="Q2" t="n">
         <v>1.3</v>
@@ -896,7 +896,7 @@
         <v>1.18</v>
       </c>
       <c r="S2" t="n">
-        <v>1.31</v>
+        <v>1.81</v>
       </c>
       <c r="T2" t="n">
         <v>1.11</v>
@@ -905,7 +905,7 @@
         <v>1.11</v>
       </c>
       <c r="V2" t="n">
-        <v>1.04</v>
+        <v>1.82</v>
       </c>
       <c r="W2" t="n">
         <v>1.01</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-17 20:53:41</t>
+          <t>2026-07-17 23:15:15</t>
         </is>
       </c>
     </row>
@@ -1114,13 +1114,13 @@
         <v>1.66</v>
       </c>
       <c r="G3" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="H3" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="I3" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="J3" t="n">
         <v>3.8</v>
@@ -1138,37 +1138,37 @@
         <v>3.25</v>
       </c>
       <c r="O3" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="P3" t="n">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="R3" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="T3" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="U3" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="V3" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="W3" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="X3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Y3" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="Z3" t="n">
         <v>150</v>
@@ -1180,7 +1180,7 @@
         <v>7.4</v>
       </c>
       <c r="AC3" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD3" t="n">
         <v>42</v>
@@ -1192,7 +1192,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AG3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AH3" t="n">
         <v>46</v>
@@ -1201,10 +1201,10 @@
         <v>1000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AK3" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AL3" t="n">
         <v>250</v>
@@ -1213,19 +1213,19 @@
         <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AO3" t="n">
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AR3" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="AS3" t="n">
         <v>46</v>
@@ -1234,40 +1234,40 @@
         <v>6.2</v>
       </c>
       <c r="AU3" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV3" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AW3" t="n">
         <v>38</v>
       </c>
       <c r="AX3" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AY3" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AZ3" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BA3" t="n">
         <v>42</v>
       </c>
       <c r="BB3" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BC3" t="n">
         <v>14.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="BE3" t="n">
         <v>48</v>
       </c>
       <c r="BF3" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BG3" t="n">
         <v>46</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-17 20:53:41</t>
+          <t>2026-07-17 23:15:15</t>
         </is>
       </c>
     </row>
@@ -1365,22 +1365,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="G4" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="H4" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="I4" t="n">
-        <v>1.9</v>
+        <v>1.96</v>
       </c>
       <c r="J4" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K4" t="n">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="L4" t="n">
         <v>1.01</v>
@@ -1389,13 +1389,13 @@
         <v>1.09</v>
       </c>
       <c r="N4" t="n">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="O4" t="n">
         <v>1.38</v>
       </c>
       <c r="P4" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="Q4" t="n">
         <v>2.08</v>
@@ -1404,28 +1404,28 @@
         <v>1.23</v>
       </c>
       <c r="S4" t="n">
-        <v>2.08</v>
+        <v>3.7</v>
       </c>
       <c r="T4" t="n">
         <v>1.97</v>
       </c>
       <c r="U4" t="n">
-        <v>1.74</v>
+        <v>1.81</v>
       </c>
       <c r="V4" t="n">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="W4" t="n">
         <v>1.21</v>
       </c>
       <c r="X4" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Y4" t="n">
         <v>970</v>
       </c>
       <c r="Z4" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AA4" t="n">
         <v>1000</v>
@@ -1434,10 +1434,10 @@
         <v>1000</v>
       </c>
       <c r="AC4" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD4" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AE4" t="n">
         <v>1000</v>
@@ -1473,58 +1473,58 @@
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.11</v>
+        <v>1.41</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.11</v>
+        <v>1.38</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.11</v>
+        <v>1.5</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.11</v>
+        <v>1.5</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.11</v>
+        <v>1.34</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.11</v>
+        <v>1.4</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.11</v>
+        <v>1.5</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.11</v>
+        <v>1.5</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.11</v>
+        <v>1.5</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.11</v>
+        <v>1.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.11</v>
+        <v>1.5</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.11</v>
+        <v>1.5</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.11</v>
+        <v>1.5</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.11</v>
+        <v>1.5</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.11</v>
+        <v>1.5</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.11</v>
+        <v>1.5</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.11</v>
+        <v>1.5</v>
       </c>
       <c r="BH4" t="n">
         <v>1000</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-17 20:53:41</t>
+          <t>2026-07-17 23:15:15</t>
         </is>
       </c>
     </row>
@@ -1658,7 +1658,7 @@
         <v>1.18</v>
       </c>
       <c r="S5" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="T5" t="n">
         <v>1.11</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-17 20:53:41</t>
+          <t>2026-07-17 23:15:15</t>
         </is>
       </c>
     </row>
@@ -1906,13 +1906,13 @@
         <v>1.25</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="R6" t="n">
         <v>1.18</v>
       </c>
       <c r="S6" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="T6" t="n">
         <v>1.43</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-17 20:53:41</t>
+          <t>2026-07-17 23:15:15</t>
         </is>
       </c>
     </row>
@@ -2166,7 +2166,7 @@
         <v>1.18</v>
       </c>
       <c r="S7" t="n">
-        <v>1.05</v>
+        <v>1.34</v>
       </c>
       <c r="T7" t="n">
         <v>1.11</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-17 20:53:41</t>
+          <t>2026-07-17 23:15:15</t>
         </is>
       </c>
     </row>
@@ -2420,13 +2420,13 @@
         <v>1.21</v>
       </c>
       <c r="S8" t="n">
-        <v>1.22</v>
+        <v>2.3</v>
       </c>
       <c r="T8" t="n">
-        <v>1.11</v>
+        <v>1.58</v>
       </c>
       <c r="U8" t="n">
-        <v>1.11</v>
+        <v>1.57</v>
       </c>
       <c r="V8" t="n">
         <v>1.01</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-17 20:53:41</t>
+          <t>2026-07-17 23:15:15</t>
         </is>
       </c>
     </row>
@@ -2686,7 +2686,7 @@
         <v>1.02</v>
       </c>
       <c r="W9" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X9" t="n">
         <v>1000</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-17 20:53:41</t>
+          <t>2026-07-17 23:15:15</t>
         </is>
       </c>
     </row>
@@ -2940,7 +2940,7 @@
         <v>1.01</v>
       </c>
       <c r="W10" t="n">
-        <v>1.01</v>
+        <v>2.34</v>
       </c>
       <c r="X10" t="n">
         <v>1000</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-17 20:53:41</t>
+          <t>2026-07-17 23:15:15</t>
         </is>
       </c>
     </row>
@@ -3194,7 +3194,7 @@
         <v>1.02</v>
       </c>
       <c r="W11" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X11" t="n">
         <v>1000</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-17 20:53:41</t>
+          <t>2026-07-17 23:15:15</t>
         </is>
       </c>
     </row>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-17 20:53:41</t>
+          <t>2026-07-17 23:15:15</t>
         </is>
       </c>
     </row>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-17 20:53:41</t>
+          <t>2026-07-17 23:15:15</t>
         </is>
       </c>
     </row>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-17 20:53:41</t>
+          <t>2026-07-17 23:15:15</t>
         </is>
       </c>
     </row>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-17 20:53:41</t>
+          <t>2026-07-17 23:15:15</t>
         </is>
       </c>
     </row>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-17 20:53:41</t>
+          <t>2026-07-17 23:15:15</t>
         </is>
       </c>
     </row>
@@ -4691,7 +4691,7 @@
         <v>1.01</v>
       </c>
       <c r="N17" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="O17" t="n">
         <v>1.5</v>
@@ -4706,7 +4706,7 @@
         <v>1.12</v>
       </c>
       <c r="S17" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="T17" t="n">
         <v>1.72</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-17 20:53:41</t>
+          <t>2026-07-17 23:15:15</t>
         </is>
       </c>
     </row>
@@ -4924,16 +4924,16 @@
         <v>1.54</v>
       </c>
       <c r="G18" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="H18" t="n">
-        <v>1.04</v>
+        <v>1.96</v>
       </c>
       <c r="I18" t="n">
         <v>110</v>
       </c>
       <c r="J18" t="n">
-        <v>1.33</v>
+        <v>3.15</v>
       </c>
       <c r="K18" t="n">
         <v>1000</v>
@@ -4945,7 +4945,7 @@
         <v>1.01</v>
       </c>
       <c r="N18" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="O18" t="n">
         <v>1.23</v>
@@ -4957,10 +4957,10 @@
         <v>1.23</v>
       </c>
       <c r="R18" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S18" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="T18" t="n">
         <v>1.11</v>
@@ -4972,7 +4972,7 @@
         <v>1.29</v>
       </c>
       <c r="W18" t="n">
-        <v>1.01</v>
+        <v>1.92</v>
       </c>
       <c r="X18" t="n">
         <v>1000</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-17 20:53:41</t>
+          <t>2026-07-17 23:15:15</t>
         </is>
       </c>
     </row>
@@ -5175,7 +5175,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.56</v>
+        <v>2.66</v>
       </c>
       <c r="G19" t="n">
         <v>1000</v>
@@ -5223,7 +5223,7 @@
         <v>1.11</v>
       </c>
       <c r="V19" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="W19" t="n">
         <v>1.03</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-17 20:53:41</t>
+          <t>2026-07-17 23:15:15</t>
         </is>
       </c>
     </row>
@@ -5441,7 +5441,7 @@
         <v>1000</v>
       </c>
       <c r="J20" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="K20" t="n">
         <v>1000</v>
@@ -5453,7 +5453,7 @@
         <v>1.01</v>
       </c>
       <c r="N20" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="O20" t="n">
         <v>1.16</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-17 20:53:41</t>
+          <t>2026-07-17 23:15:15</t>
         </is>
       </c>
     </row>
@@ -5707,13 +5707,13 @@
         <v>1.06</v>
       </c>
       <c r="N21" t="n">
-        <v>1.54</v>
+        <v>1.62</v>
       </c>
       <c r="O21" t="n">
         <v>1.3</v>
       </c>
       <c r="P21" t="n">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="Q21" t="n">
         <v>1.31</v>
@@ -5722,7 +5722,7 @@
         <v>1.15</v>
       </c>
       <c r="S21" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="T21" t="n">
         <v>1.11</v>
@@ -5746,7 +5746,7 @@
         <v>48</v>
       </c>
       <c r="AA21" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AB21" t="n">
         <v>29</v>
@@ -5755,10 +5755,10 @@
         <v>15.5</v>
       </c>
       <c r="AD21" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AE21" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="AF21" t="n">
         <v>26</v>
@@ -5767,40 +5767,40 @@
         <v>14</v>
       </c>
       <c r="AH21" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AI21" t="n">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="AJ21" t="n">
         <v>36</v>
       </c>
       <c r="AK21" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AL21" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AM21" t="n">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="AN21" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AO21" t="n">
-        <v>140</v>
+        <v>110</v>
       </c>
       <c r="AP21" t="n">
         <v>4.4</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AR21" t="n">
         <v>22</v>
       </c>
       <c r="AS21" t="n">
-        <v>1.89</v>
+        <v>1.98</v>
       </c>
       <c r="AT21" t="n">
         <v>4.4</v>
@@ -5818,7 +5818,7 @@
         <v>9.6</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.68</v>
+        <v>1.76</v>
       </c>
       <c r="AZ21" t="n">
         <v>11</v>
@@ -5839,7 +5839,7 @@
         <v>30</v>
       </c>
       <c r="BF21" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BG21" t="n">
         <v>9.6</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-07-17 20:53:41</t>
+          <t>2026-07-17 23:15:15</t>
         </is>
       </c>
     </row>
@@ -5943,13 +5943,13 @@
         <v>1000</v>
       </c>
       <c r="H22" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="I22" t="n">
         <v>1000</v>
       </c>
       <c r="J22" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="K22" t="n">
         <v>1000</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-07-17 20:53:41</t>
+          <t>2026-07-17 23:15:15</t>
         </is>
       </c>
     </row>
@@ -6221,7 +6221,7 @@
         <v>1.11</v>
       </c>
       <c r="P23" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="Q23" t="n">
         <v>1.11</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-07-17 20:53:41</t>
+          <t>2026-07-17 23:15:15</t>
         </is>
       </c>
     </row>
@@ -6469,7 +6469,7 @@
         <v>1.03</v>
       </c>
       <c r="N24" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="O24" t="n">
         <v>1.16</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-07-17 20:53:41</t>
+          <t>2026-07-17 23:15:15</t>
         </is>
       </c>
     </row>
@@ -6729,10 +6729,10 @@
         <v>1.22</v>
       </c>
       <c r="P25" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="R25" t="n">
         <v>1.24</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-07-17 20:53:41</t>
+          <t>2026-07-17 23:15:15</t>
         </is>
       </c>
     </row>
@@ -6959,10 +6959,10 @@
         <v>1.32</v>
       </c>
       <c r="H26" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="I26" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="J26" t="n">
         <v>6.2</v>
@@ -6977,40 +6977,40 @@
         <v>1.03</v>
       </c>
       <c r="N26" t="n">
-        <v>2.48</v>
+        <v>5.4</v>
       </c>
       <c r="O26" t="n">
         <v>1.16</v>
       </c>
       <c r="P26" t="n">
-        <v>1.25</v>
+        <v>2.56</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="R26" t="n">
-        <v>1.25</v>
+        <v>1.62</v>
       </c>
       <c r="S26" t="n">
-        <v>1.55</v>
+        <v>2.32</v>
       </c>
       <c r="T26" t="n">
-        <v>1.11</v>
+        <v>1.96</v>
       </c>
       <c r="U26" t="n">
-        <v>1.11</v>
+        <v>1.86</v>
       </c>
       <c r="V26" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="W26" t="n">
         <v>4</v>
       </c>
       <c r="X26" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="Y26" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="Z26" t="n">
         <v>1000</v>
@@ -7019,100 +7019,100 @@
         <v>1000</v>
       </c>
       <c r="AB26" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AC26" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AD26" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AE26" t="n">
         <v>1000</v>
       </c>
       <c r="AF26" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG26" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH26" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AI26" t="n">
         <v>1000</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AK26" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AL26" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AM26" t="n">
         <v>1000</v>
       </c>
       <c r="AN26" t="n">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="AO26" t="n">
         <v>1000</v>
       </c>
       <c r="AP26" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1.01</v>
+        <v>29</v>
       </c>
       <c r="AR26" t="n">
-        <v>1.01</v>
+        <v>38</v>
       </c>
       <c r="AS26" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AT26" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AU26" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AV26" t="n">
-        <v>1.01</v>
+        <v>29</v>
       </c>
       <c r="AW26" t="n">
-        <v>1.01</v>
+        <v>44</v>
       </c>
       <c r="AX26" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AY26" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ26" t="n">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="BA26" t="n">
-        <v>1.01</v>
+        <v>42</v>
       </c>
       <c r="BB26" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BC26" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BD26" t="n">
-        <v>1.01</v>
+        <v>27</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.01</v>
+        <v>44</v>
       </c>
       <c r="BF26" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BG26" t="n">
-        <v>1.01</v>
+        <v>48</v>
       </c>
       <c r="BH26" t="n">
         <v>1000</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-07-17 20:53:41</t>
+          <t>2026-07-17 23:15:15</t>
         </is>
       </c>
     </row>
@@ -7216,10 +7216,10 @@
         <v>1.72</v>
       </c>
       <c r="I27" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="J27" t="n">
-        <v>1.79</v>
+        <v>1.1</v>
       </c>
       <c r="K27" t="n">
         <v>1000</v>
@@ -7255,7 +7255,7 @@
         <v>1.11</v>
       </c>
       <c r="V27" t="n">
-        <v>1.73</v>
+        <v>1.01</v>
       </c>
       <c r="W27" t="n">
         <v>1.01</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-07-17 20:53:41</t>
+          <t>2026-07-17 23:15:15</t>
         </is>
       </c>
     </row>
@@ -7485,19 +7485,19 @@
         <v>1.04</v>
       </c>
       <c r="N28" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="O28" t="n">
         <v>1.23</v>
       </c>
       <c r="P28" t="n">
-        <v>1.46</v>
+        <v>1.25</v>
       </c>
       <c r="Q28" t="n">
         <v>1.23</v>
       </c>
       <c r="R28" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="S28" t="n">
         <v>1.23</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-07-17 20:53:41</t>
+          <t>2026-07-17 23:15:15</t>
         </is>
       </c>
     </row>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-07-17 20:53:41</t>
+          <t>2026-07-17 23:15:15</t>
         </is>
       </c>
     </row>
@@ -7969,10 +7969,10 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="G30" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="H30" t="n">
         <v>1.06</v>
@@ -8011,10 +8011,10 @@
         <v>1.53</v>
       </c>
       <c r="T30" t="n">
-        <v>1.11</v>
+        <v>1.92</v>
       </c>
       <c r="U30" t="n">
-        <v>1.11</v>
+        <v>1.29</v>
       </c>
       <c r="V30" t="n">
         <v>1.03</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-07-17 20:53:41</t>
+          <t>2026-07-17 23:15:15</t>
         </is>
       </c>
     </row>
@@ -8223,7 +8223,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1.04</v>
+        <v>1.5</v>
       </c>
       <c r="G31" t="n">
         <v>1000</v>
@@ -8235,7 +8235,7 @@
         <v>1000</v>
       </c>
       <c r="J31" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K31" t="n">
         <v>1000</v>
@@ -8247,7 +8247,7 @@
         <v>1.01</v>
       </c>
       <c r="N31" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="O31" t="n">
         <v>1.14</v>
@@ -8256,7 +8256,7 @@
         <v>1.27</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="R31" t="n">
         <v>1.18</v>
@@ -8271,10 +8271,10 @@
         <v>1.11</v>
       </c>
       <c r="V31" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W31" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X31" t="n">
         <v>1000</v>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-07-17 20:53:41</t>
+          <t>2026-07-17 23:15:15</t>
         </is>
       </c>
     </row>
@@ -8477,19 +8477,19 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1.04</v>
+        <v>1.44</v>
       </c>
       <c r="G32" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="H32" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="I32" t="n">
         <v>1000</v>
       </c>
       <c r="J32" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="K32" t="n">
         <v>1000</v>
@@ -8501,13 +8501,13 @@
         <v>1.06</v>
       </c>
       <c r="N32" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="O32" t="n">
         <v>1.35</v>
       </c>
       <c r="P32" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="Q32" t="n">
         <v>1.35</v>
@@ -8516,13 +8516,13 @@
         <v>1.18</v>
       </c>
       <c r="S32" t="n">
-        <v>1.05</v>
+        <v>1.36</v>
       </c>
       <c r="T32" t="n">
-        <v>1.11</v>
+        <v>1.61</v>
       </c>
       <c r="U32" t="n">
-        <v>1.11</v>
+        <v>1.45</v>
       </c>
       <c r="V32" t="n">
         <v>1.01</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-07-17 20:53:41</t>
+          <t>2026-07-17 23:15:15</t>
         </is>
       </c>
     </row>
@@ -8755,7 +8755,7 @@
         <v>1.03</v>
       </c>
       <c r="N33" t="n">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="O33" t="n">
         <v>1.22</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-07-17 20:53:41</t>
+          <t>2026-07-17 23:15:15</t>
         </is>
       </c>
     </row>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-07-17 20:53:41</t>
+          <t>2026-07-17 23:15:15</t>
         </is>
       </c>
     </row>
@@ -9263,13 +9263,13 @@
         <v>1.01</v>
       </c>
       <c r="N35" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="O35" t="n">
         <v>1.15</v>
       </c>
       <c r="P35" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Q35" t="n">
         <v>1.15</v>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-07-17 20:53:41</t>
+          <t>2026-07-17 23:15:15</t>
         </is>
       </c>
     </row>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-07-17 20:53:41</t>
+          <t>2026-07-17 23:15:15</t>
         </is>
       </c>
     </row>
@@ -9747,22 +9747,22 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>1.04</v>
+        <v>1.51</v>
       </c>
       <c r="G37" t="n">
         <v>1000</v>
       </c>
       <c r="H37" t="n">
-        <v>1.04</v>
+        <v>1.51</v>
       </c>
       <c r="I37" t="n">
         <v>1000</v>
       </c>
       <c r="J37" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="K37" t="n">
-        <v>1000</v>
+        <v>3.25</v>
       </c>
       <c r="L37" t="n">
         <v>1.01</v>
@@ -9771,13 +9771,13 @@
         <v>1.01</v>
       </c>
       <c r="N37" t="n">
-        <v>1.25</v>
+        <v>1.39</v>
       </c>
       <c r="O37" t="n">
         <v>1.53</v>
       </c>
       <c r="P37" t="n">
-        <v>1.25</v>
+        <v>1.39</v>
       </c>
       <c r="Q37" t="n">
         <v>1.53</v>
@@ -9786,19 +9786,19 @@
         <v>1.18</v>
       </c>
       <c r="S37" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="T37" t="n">
-        <v>1.11</v>
+        <v>1.93</v>
       </c>
       <c r="U37" t="n">
         <v>1.11</v>
       </c>
       <c r="V37" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W37" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X37" t="n">
         <v>1000</v>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-07-17 20:53:41</t>
+          <t>2026-07-17 23:15:15</t>
         </is>
       </c>
     </row>
@@ -10001,19 +10001,19 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="G38" t="n">
         <v>1000</v>
       </c>
       <c r="H38" t="n">
-        <v>1.04</v>
+        <v>1.75</v>
       </c>
       <c r="I38" t="n">
         <v>2.18</v>
       </c>
       <c r="J38" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="K38" t="n">
         <v>1000</v>
@@ -10025,13 +10025,13 @@
         <v>1.08</v>
       </c>
       <c r="N38" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="O38" t="n">
         <v>1.42</v>
       </c>
       <c r="P38" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Q38" t="n">
         <v>1.42</v>
@@ -10224,7 +10224,7 @@
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-07-17 20:53:41</t>
+          <t>2026-07-17 23:15:15</t>
         </is>
       </c>
     </row>
@@ -10267,7 +10267,7 @@
         <v>1000</v>
       </c>
       <c r="J39" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="K39" t="n">
         <v>1000</v>
@@ -10279,13 +10279,13 @@
         <v>1.01</v>
       </c>
       <c r="N39" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="O39" t="n">
         <v>1.42</v>
       </c>
       <c r="P39" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Q39" t="n">
         <v>1.42</v>
@@ -10294,7 +10294,7 @@
         <v>1.17</v>
       </c>
       <c r="S39" t="n">
-        <v>1.02</v>
+        <v>1.42</v>
       </c>
       <c r="T39" t="n">
         <v>1.11</v>
@@ -10303,7 +10303,7 @@
         <v>1.11</v>
       </c>
       <c r="V39" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W39" t="n">
         <v>1.01</v>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-07-17 20:53:41</t>
+          <t>2026-07-17 23:15:15</t>
         </is>
       </c>
     </row>
@@ -10515,7 +10515,7 @@
         <v>1000</v>
       </c>
       <c r="H40" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="I40" t="n">
         <v>1000</v>
@@ -10732,7 +10732,7 @@
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-07-17 20:53:41</t>
+          <t>2026-07-17 23:15:15</t>
         </is>
       </c>
     </row>
@@ -10986,7 +10986,7 @@
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-07-17 20:53:41</t>
+          <t>2026-07-17 23:15:15</t>
         </is>
       </c>
     </row>
@@ -11240,7 +11240,7 @@
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-07-17 20:53:41</t>
+          <t>2026-07-17 23:15:15</t>
         </is>
       </c>
     </row>
@@ -11304,7 +11304,7 @@
         <v>1.25</v>
       </c>
       <c r="Q43" t="n">
-        <v>1.02</v>
+        <v>1.48</v>
       </c>
       <c r="R43" t="n">
         <v>1.18</v>
@@ -11494,7 +11494,7 @@
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-07-17 20:53:41</t>
+          <t>2026-07-17 23:15:15</t>
         </is>
       </c>
     </row>
@@ -11555,7 +11555,7 @@
         <v>1.01</v>
       </c>
       <c r="P44" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q44" t="n">
         <v>1.02</v>
@@ -11564,7 +11564,7 @@
         <v>1.18</v>
       </c>
       <c r="S44" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="T44" t="n">
         <v>1.01</v>
@@ -11748,7 +11748,7 @@
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-07-17 20:53:41</t>
+          <t>2026-07-17 23:15:15</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-19.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-19.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB44"/>
+  <dimension ref="A1:CB46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -857,46 +857,46 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3.05</v>
+        <v>3.9</v>
       </c>
       <c r="G2" t="n">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="H2" t="n">
-        <v>1.65</v>
+        <v>2.04</v>
       </c>
       <c r="I2" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="J2" t="n">
-        <v>2.88</v>
+        <v>3.6</v>
       </c>
       <c r="K2" t="n">
-        <v>500</v>
+        <v>3.85</v>
       </c>
       <c r="L2" t="n">
-        <v>1.13</v>
+        <v>1.39</v>
       </c>
       <c r="M2" t="n">
         <v>1.06</v>
       </c>
       <c r="N2" t="n">
-        <v>1.1</v>
+        <v>4</v>
       </c>
       <c r="O2" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="P2" t="n">
-        <v>1.25</v>
+        <v>2</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.3</v>
+        <v>1.95</v>
       </c>
       <c r="R2" t="n">
-        <v>1.18</v>
+        <v>1.38</v>
       </c>
       <c r="S2" t="n">
-        <v>1.81</v>
+        <v>3.45</v>
       </c>
       <c r="T2" t="n">
         <v>1.11</v>
@@ -905,10 +905,10 @@
         <v>1.11</v>
       </c>
       <c r="V2" t="n">
-        <v>1.82</v>
+        <v>1.9</v>
       </c>
       <c r="W2" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="X2" t="n">
         <v>1000</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-17 23:15:15</t>
+          <t>2026-07-18 01:36:59</t>
         </is>
       </c>
     </row>
@@ -1117,13 +1117,13 @@
         <v>1.71</v>
       </c>
       <c r="H3" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="I3" t="n">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="J3" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="K3" t="n">
         <v>3.9</v>
@@ -1141,7 +1141,7 @@
         <v>1.39</v>
       </c>
       <c r="P3" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="Q3" t="n">
         <v>2.22</v>
@@ -1153,13 +1153,13 @@
         <v>4.2</v>
       </c>
       <c r="T3" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="U3" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="V3" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="W3" t="n">
         <v>2.4</v>
@@ -1180,7 +1180,7 @@
         <v>7.4</v>
       </c>
       <c r="AC3" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD3" t="n">
         <v>42</v>
@@ -1201,10 +1201,10 @@
         <v>1000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AK3" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AL3" t="n">
         <v>250</v>
@@ -1219,10 +1219,10 @@
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ3" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AR3" t="n">
         <v>26</v>
@@ -1240,13 +1240,13 @@
         <v>18</v>
       </c>
       <c r="AW3" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AX3" t="n">
         <v>7.6</v>
       </c>
       <c r="AY3" t="n">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ3" t="n">
         <v>18.5</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-17 23:15:15</t>
+          <t>2026-07-18 01:36:59</t>
         </is>
       </c>
     </row>
@@ -1365,13 +1365,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="G4" t="n">
-        <v>5.8</v>
+        <v>7</v>
       </c>
       <c r="H4" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="I4" t="n">
         <v>1.96</v>
@@ -1410,13 +1410,13 @@
         <v>1.97</v>
       </c>
       <c r="U4" t="n">
-        <v>1.81</v>
+        <v>1.74</v>
       </c>
       <c r="V4" t="n">
         <v>2.04</v>
       </c>
       <c r="W4" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="X4" t="n">
         <v>970</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-17 23:15:15</t>
+          <t>2026-07-18 01:36:59</t>
         </is>
       </c>
     </row>
@@ -1640,10 +1640,10 @@
         <v>1.01</v>
       </c>
       <c r="M5" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="O5" t="n">
         <v>1.31</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-17 23:15:15</t>
+          <t>2026-07-18 01:36:59</t>
         </is>
       </c>
     </row>
@@ -1906,13 +1906,13 @@
         <v>1.25</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="R6" t="n">
         <v>1.18</v>
       </c>
       <c r="S6" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="T6" t="n">
         <v>1.43</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-17 23:15:15</t>
+          <t>2026-07-18 01:36:59</t>
         </is>
       </c>
     </row>
@@ -2148,7 +2148,7 @@
         <v>1.01</v>
       </c>
       <c r="M7" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="N7" t="n">
         <v>1.33</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-17 23:15:15</t>
+          <t>2026-07-18 01:36:59</t>
         </is>
       </c>
     </row>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-17 23:15:15</t>
+          <t>2026-07-18 01:36:59</t>
         </is>
       </c>
     </row>
@@ -2626,28 +2626,28 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Dalian Yingbo II</t>
+          <t>Taian Tiankuang</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Xian Chongde Ronghai</t>
+          <t>Qingdao Red Lions</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="G9" t="n">
         <v>1000</v>
       </c>
       <c r="H9" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="I9" t="n">
         <v>1000</v>
       </c>
       <c r="J9" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="K9" t="n">
         <v>1000</v>
@@ -2662,13 +2662,13 @@
         <v>1.25</v>
       </c>
       <c r="O9" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P9" t="n">
         <v>1.25</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="R9" t="n">
         <v>1.18</v>
@@ -2686,7 +2686,7 @@
         <v>1.02</v>
       </c>
       <c r="W9" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X9" t="n">
         <v>1000</v>
@@ -2800,72 +2800,72 @@
         <v>1000</v>
       </c>
       <c r="BI9" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BJ9" t="n">
         <v>1000</v>
       </c>
       <c r="BK9" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BN9" t="n">
         <v>1000</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BP9" t="n">
         <v>1000</v>
       </c>
       <c r="BQ9" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BR9" t="n">
         <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BT9" t="n">
         <v>1000</v>
       </c>
       <c r="BU9" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BV9" t="n">
         <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BZ9" t="n">
         <v>1000</v>
       </c>
       <c r="CA9" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-17 23:15:15</t>
+          <t>2026-07-18 01:36:59</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Swedish Superettan</t>
+          <t>Chinese League 2</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2880,28 +2880,28 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Norrkoping</t>
+          <t>Dalian Yingbo II</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sandvikens IF</t>
+          <t>Xian Chongde Ronghai</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.27</v>
+        <v>1.1</v>
       </c>
       <c r="G10" t="n">
-        <v>1.74</v>
+        <v>1000</v>
       </c>
       <c r="H10" t="n">
-        <v>4.1</v>
+        <v>1.1</v>
       </c>
       <c r="I10" t="n">
         <v>1000</v>
       </c>
       <c r="J10" t="n">
-        <v>3.65</v>
+        <v>1.18</v>
       </c>
       <c r="K10" t="n">
         <v>1000</v>
@@ -2913,22 +2913,22 @@
         <v>1.01</v>
       </c>
       <c r="N10" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="O10" t="n">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="P10" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.14</v>
+        <v>1.52</v>
       </c>
       <c r="R10" t="n">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="S10" t="n">
-        <v>1.14</v>
+        <v>1.52</v>
       </c>
       <c r="T10" t="n">
         <v>1.11</v>
@@ -2940,7 +2940,7 @@
         <v>1.01</v>
       </c>
       <c r="W10" t="n">
-        <v>2.34</v>
+        <v>1.01</v>
       </c>
       <c r="X10" t="n">
         <v>1000</v>
@@ -3112,14 +3112,14 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-17 23:15:15</t>
+          <t>2026-07-18 01:36:59</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Chinese League 2</t>
+          <t>Swedish Superettan</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3134,28 +3134,28 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Taian Tiankuang</t>
+          <t>Norrkoping</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Qingdao Red Lions</t>
+          <t>Sandvikens IF</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.04</v>
+        <v>1.27</v>
       </c>
       <c r="G11" t="n">
-        <v>1000</v>
+        <v>1.7</v>
       </c>
       <c r="H11" t="n">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="I11" t="n">
         <v>1000</v>
       </c>
       <c r="J11" t="n">
-        <v>1.1</v>
+        <v>3.65</v>
       </c>
       <c r="K11" t="n">
         <v>1000</v>
@@ -3167,22 +3167,22 @@
         <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="O11" t="n">
-        <v>1.02</v>
+        <v>1.14</v>
       </c>
       <c r="P11" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.53</v>
+        <v>1.14</v>
       </c>
       <c r="R11" t="n">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="S11" t="n">
-        <v>1.52</v>
+        <v>1.15</v>
       </c>
       <c r="T11" t="n">
         <v>1.11</v>
@@ -3191,10 +3191,10 @@
         <v>1.11</v>
       </c>
       <c r="V11" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W11" t="n">
-        <v>1.01</v>
+        <v>2.34</v>
       </c>
       <c r="X11" t="n">
         <v>1000</v>
@@ -3308,65 +3308,65 @@
         <v>1000</v>
       </c>
       <c r="BI11" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ11" t="n">
         <v>1000</v>
       </c>
       <c r="BK11" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN11" t="n">
         <v>1000</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP11" t="n">
         <v>1000</v>
       </c>
       <c r="BQ11" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR11" t="n">
         <v>1000</v>
       </c>
       <c r="BS11" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT11" t="n">
         <v>1000</v>
       </c>
       <c r="BU11" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV11" t="n">
         <v>1000</v>
       </c>
       <c r="BW11" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX11" t="n">
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ11" t="n">
         <v>1000</v>
       </c>
       <c r="CA11" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-17 23:15:15</t>
+          <t>2026-07-18 01:36:59</t>
         </is>
       </c>
     </row>
@@ -3388,28 +3388,28 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Jiangxi Lushan</t>
+          <t>Haimen Codion</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Guangdong Mingtu</t>
+          <t>Lanzhou Longyuan Athletic</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="G12" t="n">
         <v>1000</v>
       </c>
       <c r="H12" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="I12" t="n">
         <v>1000</v>
       </c>
       <c r="J12" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="K12" t="n">
         <v>1000</v>
@@ -3421,22 +3421,22 @@
         <v>1.01</v>
       </c>
       <c r="N12" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P12" t="n">
         <v>1.25</v>
       </c>
-      <c r="O12" t="n">
+      <c r="Q12" t="n">
         <v>1.02</v>
-      </c>
-      <c r="P12" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1.42</v>
       </c>
       <c r="R12" t="n">
         <v>1.18</v>
       </c>
       <c r="S12" t="n">
-        <v>1.42</v>
+        <v>1.05</v>
       </c>
       <c r="T12" t="n">
         <v>1.11</v>
@@ -3448,7 +3448,7 @@
         <v>1.02</v>
       </c>
       <c r="W12" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X12" t="n">
         <v>1000</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-17 23:15:15</t>
+          <t>2026-07-18 01:36:59</t>
         </is>
       </c>
     </row>
@@ -3642,12 +3642,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Hangzhou Linping Wuyue</t>
+          <t>Wuhan Three Towns II</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Chengdu Rongcheng II</t>
+          <t>Guizhou Zhucheng Athletic</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -3657,13 +3657,13 @@
         <v>1000</v>
       </c>
       <c r="H13" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="I13" t="n">
         <v>1000</v>
       </c>
       <c r="J13" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="K13" t="n">
         <v>1000</v>
@@ -3684,13 +3684,13 @@
         <v>1.25</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="R13" t="n">
         <v>1.18</v>
       </c>
       <c r="S13" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="T13" t="n">
         <v>1.11</v>
@@ -3702,7 +3702,7 @@
         <v>1.01</v>
       </c>
       <c r="W13" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X13" t="n">
         <v>1000</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-17 23:15:15</t>
+          <t>2026-07-18 01:36:59</t>
         </is>
       </c>
     </row>
@@ -3896,28 +3896,28 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns II</t>
+          <t>Hangzhou Linping Wuyue</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Guizhou Zhucheng Athletic</t>
+          <t>Chengdu Rongcheng II</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="G14" t="n">
         <v>1000</v>
       </c>
       <c r="H14" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="I14" t="n">
         <v>1000</v>
       </c>
       <c r="J14" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="K14" t="n">
         <v>1000</v>
@@ -3938,13 +3938,13 @@
         <v>1.25</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="R14" t="n">
         <v>1.18</v>
       </c>
       <c r="S14" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="T14" t="n">
         <v>1.11</v>
@@ -3956,7 +3956,7 @@
         <v>1.02</v>
       </c>
       <c r="W14" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X14" t="n">
         <v>1000</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-17 23:15:15</t>
+          <t>2026-07-18 01:36:59</t>
         </is>
       </c>
     </row>
@@ -4150,28 +4150,28 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Haimen Codion</t>
+          <t>Jiangxi Lushan</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Lanzhou Longyuan Athletic</t>
+          <t>Guangdong Mingtu</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="G15" t="n">
         <v>1000</v>
       </c>
       <c r="H15" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="I15" t="n">
         <v>1000</v>
       </c>
       <c r="J15" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="K15" t="n">
         <v>1000</v>
@@ -4183,22 +4183,22 @@
         <v>1.01</v>
       </c>
       <c r="N15" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="P15" t="n">
         <v>1.24</v>
       </c>
-      <c r="O15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="P15" t="n">
-        <v>1.25</v>
-      </c>
       <c r="Q15" t="n">
-        <v>1.02</v>
+        <v>1.42</v>
       </c>
       <c r="R15" t="n">
         <v>1.18</v>
       </c>
       <c r="S15" t="n">
-        <v>1.05</v>
+        <v>1.42</v>
       </c>
       <c r="T15" t="n">
         <v>1.11</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-17 23:15:15</t>
+          <t>2026-07-18 01:36:59</t>
         </is>
       </c>
     </row>
@@ -4413,19 +4413,19 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="G16" t="n">
         <v>1000</v>
       </c>
       <c r="H16" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="I16" t="n">
         <v>1000</v>
       </c>
       <c r="J16" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="K16" t="n">
         <v>1000</v>
@@ -4636,14 +4636,14 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-17 23:15:15</t>
+          <t>2026-07-18 01:36:59</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Swedish Superettan</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -4658,28 +4658,28 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Central Espanol</t>
+          <t>United IK Nordic</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Cerro Largo FC</t>
+          <t>Orebro</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.04</v>
+        <v>1.54</v>
       </c>
       <c r="G17" t="n">
-        <v>1000</v>
+        <v>2.1</v>
       </c>
       <c r="H17" t="n">
-        <v>1.04</v>
+        <v>1.99</v>
       </c>
       <c r="I17" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J17" t="n">
-        <v>1.02</v>
+        <v>3.15</v>
       </c>
       <c r="K17" t="n">
         <v>1000</v>
@@ -4691,34 +4691,34 @@
         <v>1.01</v>
       </c>
       <c r="N17" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="O17" t="n">
-        <v>1.5</v>
+        <v>1.23</v>
       </c>
       <c r="P17" t="n">
         <v>1.25</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.5</v>
+        <v>1.23</v>
       </c>
       <c r="R17" t="n">
-        <v>1.12</v>
+        <v>1.25</v>
       </c>
       <c r="S17" t="n">
-        <v>1.5</v>
+        <v>1.23</v>
       </c>
       <c r="T17" t="n">
-        <v>1.72</v>
+        <v>1.11</v>
       </c>
       <c r="U17" t="n">
-        <v>1.41</v>
+        <v>1.11</v>
       </c>
       <c r="V17" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="W17" t="n">
-        <v>1.01</v>
+        <v>1.92</v>
       </c>
       <c r="X17" t="n">
         <v>1000</v>
@@ -4883,14 +4883,14 @@
         <v>1.01</v>
       </c>
       <c r="BZ17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-17 23:15:15</t>
+          <t>2026-07-18 01:36:59</t>
         </is>
       </c>
     </row>
@@ -4912,31 +4912,31 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>United IK Nordic</t>
+          <t>Varnamo</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Orebro</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.54</v>
+        <v>2.7</v>
       </c>
       <c r="G18" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="H18" t="n">
-        <v>1.96</v>
+        <v>1.41</v>
       </c>
       <c r="I18" t="n">
-        <v>110</v>
+        <v>2.78</v>
       </c>
       <c r="J18" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="K18" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="L18" t="n">
         <v>1.01</v>
@@ -4945,7 +4945,7 @@
         <v>1.01</v>
       </c>
       <c r="N18" t="n">
-        <v>1.26</v>
+        <v>1.47</v>
       </c>
       <c r="O18" t="n">
         <v>1.23</v>
@@ -4960,7 +4960,7 @@
         <v>1.25</v>
       </c>
       <c r="S18" t="n">
-        <v>1.23</v>
+        <v>2.24</v>
       </c>
       <c r="T18" t="n">
         <v>1.11</v>
@@ -4969,10 +4969,10 @@
         <v>1.11</v>
       </c>
       <c r="V18" t="n">
-        <v>1.29</v>
+        <v>1.58</v>
       </c>
       <c r="W18" t="n">
-        <v>1.92</v>
+        <v>1.03</v>
       </c>
       <c r="X18" t="n">
         <v>1000</v>
@@ -5086,72 +5086,72 @@
         <v>1000</v>
       </c>
       <c r="BI18" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ18" t="n">
         <v>1000</v>
       </c>
       <c r="BK18" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL18" t="n">
         <v>1000</v>
       </c>
       <c r="BM18" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN18" t="n">
         <v>1000</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP18" t="n">
         <v>1000</v>
       </c>
       <c r="BQ18" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR18" t="n">
         <v>1000</v>
       </c>
       <c r="BS18" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT18" t="n">
         <v>1000</v>
       </c>
       <c r="BU18" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV18" t="n">
         <v>1000</v>
       </c>
       <c r="BW18" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX18" t="n">
         <v>1000</v>
       </c>
       <c r="BY18" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ18" t="n">
         <v>1000</v>
       </c>
       <c r="CA18" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-17 23:15:15</t>
+          <t>2026-07-18 01:36:59</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Swedish Superettan</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -5166,31 +5166,31 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Varnamo</t>
+          <t>Central Espanol</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Cerro Largo FC</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.66</v>
+        <v>1.43</v>
       </c>
       <c r="G19" t="n">
         <v>1000</v>
       </c>
       <c r="H19" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="I19" t="n">
-        <v>2.92</v>
+        <v>1000</v>
       </c>
       <c r="J19" t="n">
-        <v>3.3</v>
+        <v>1.02</v>
       </c>
       <c r="K19" t="n">
-        <v>3.95</v>
+        <v>3.4</v>
       </c>
       <c r="L19" t="n">
         <v>1.01</v>
@@ -5199,34 +5199,34 @@
         <v>1.01</v>
       </c>
       <c r="N19" t="n">
-        <v>1.47</v>
+        <v>1.25</v>
       </c>
       <c r="O19" t="n">
-        <v>1.23</v>
+        <v>1.5</v>
       </c>
       <c r="P19" t="n">
         <v>1.25</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.23</v>
+        <v>1.5</v>
       </c>
       <c r="R19" t="n">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="S19" t="n">
-        <v>2.24</v>
+        <v>1.5</v>
       </c>
       <c r="T19" t="n">
-        <v>1.11</v>
+        <v>1.72</v>
       </c>
       <c r="U19" t="n">
-        <v>1.11</v>
+        <v>1.41</v>
       </c>
       <c r="V19" t="n">
-        <v>1.56</v>
+        <v>1.01</v>
       </c>
       <c r="W19" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X19" t="n">
         <v>1000</v>
@@ -5340,72 +5340,72 @@
         <v>1000</v>
       </c>
       <c r="BI19" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BJ19" t="n">
         <v>1000</v>
       </c>
       <c r="BK19" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BL19" t="n">
         <v>1000</v>
       </c>
       <c r="BM19" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BN19" t="n">
         <v>1000</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BP19" t="n">
         <v>1000</v>
       </c>
       <c r="BQ19" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BR19" t="n">
         <v>1000</v>
       </c>
       <c r="BS19" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BT19" t="n">
         <v>1000</v>
       </c>
       <c r="BU19" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BV19" t="n">
         <v>1000</v>
       </c>
       <c r="BW19" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BX19" t="n">
         <v>1000</v>
       </c>
       <c r="BY19" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BZ19" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA19" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-17 23:15:15</t>
+          <t>2026-07-18 01:36:59</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Latvian Virsliga</t>
+          <t>Estonian Premier League</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -5420,12 +5420,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Nomme Kalju</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -5435,13 +5435,13 @@
         <v>1000</v>
       </c>
       <c r="H20" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I20" t="n">
-        <v>1000</v>
+        <v>3.55</v>
       </c>
       <c r="J20" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="K20" t="n">
         <v>1000</v>
@@ -5453,22 +5453,22 @@
         <v>1.01</v>
       </c>
       <c r="N20" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="O20" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="P20" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="R20" t="n">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="S20" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="T20" t="n">
         <v>1.11</v>
@@ -5477,10 +5477,10 @@
         <v>1.11</v>
       </c>
       <c r="V20" t="n">
-        <v>1.02</v>
+        <v>1.39</v>
       </c>
       <c r="W20" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X20" t="n">
         <v>1000</v>
@@ -5645,21 +5645,21 @@
         <v>1.01</v>
       </c>
       <c r="BZ20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-17 23:15:15</t>
+          <t>2026-07-18 01:36:59</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Romanian Liga I</t>
+          <t>Icelandic Urvalsdeild</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -5674,55 +5674,55 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>IBV</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Farul Constanta</t>
+          <t>KA Akureyri</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>990</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="M21" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="N21" t="n">
-        <v>1.62</v>
+        <v>1.1</v>
       </c>
       <c r="O21" t="n">
-        <v>1.3</v>
+        <v>1.11</v>
       </c>
       <c r="P21" t="n">
-        <v>1.62</v>
+        <v>1.25</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.31</v>
+        <v>1.11</v>
       </c>
       <c r="R21" t="n">
-        <v>1.15</v>
+        <v>1.43</v>
       </c>
       <c r="S21" t="n">
-        <v>1.06</v>
+        <v>1.72</v>
       </c>
       <c r="T21" t="n">
         <v>1.11</v>
@@ -5731,118 +5731,118 @@
         <v>1.11</v>
       </c>
       <c r="V21" t="n">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="W21" t="n">
-        <v>1.78</v>
+        <v>1.01</v>
       </c>
       <c r="X21" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="Y21" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="Z21" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AA21" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AB21" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AC21" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AD21" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AE21" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AF21" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AG21" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AH21" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AI21" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AJ21" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AK21" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AL21" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AM21" t="n">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="AN21" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AO21" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AP21" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.92</v>
+        <v>1.01</v>
       </c>
       <c r="AR21" t="n">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="AS21" t="n">
-        <v>1.98</v>
+        <v>1.01</v>
       </c>
       <c r="AT21" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="AU21" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AV21" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="AW21" t="n">
-        <v>23</v>
+        <v>1.01</v>
       </c>
       <c r="AX21" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.76</v>
+        <v>1.01</v>
       </c>
       <c r="AZ21" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BA21" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BB21" t="n">
-        <v>23</v>
+        <v>1.01</v>
       </c>
       <c r="BC21" t="n">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="BD21" t="n">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="BE21" t="n">
-        <v>30</v>
+        <v>1.01</v>
       </c>
       <c r="BF21" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BG21" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="BH21" t="n">
         <v>1000</v>
@@ -5906,14 +5906,14 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-07-17 23:15:15</t>
+          <t>2026-07-18 01:36:59</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Estonian Premier League</t>
+          <t>Latvian Virsliga</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -5928,12 +5928,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Nomme Kalju</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F22" t="n">
@@ -5943,40 +5943,40 @@
         <v>1000</v>
       </c>
       <c r="H22" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N22" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="R22" t="n">
         <v>1.07</v>
       </c>
-      <c r="I22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J22" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="K22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N22" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="O22" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="P22" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.12</v>
-      </c>
       <c r="S22" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="T22" t="n">
         <v>1.11</v>
@@ -5985,10 +5985,10 @@
         <v>1.11</v>
       </c>
       <c r="V22" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W22" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X22" t="n">
         <v>1000</v>
@@ -6153,21 +6153,21 @@
         <v>1.01</v>
       </c>
       <c r="BZ22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-07-17 23:15:15</t>
+          <t>2026-07-18 01:36:59</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Icelandic Urvalsdeild</t>
+          <t>Romanian Liga I</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -6182,55 +6182,55 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>IBV</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>KA Akureyri</t>
+          <t>Farul Constanta</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>990</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L23" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="M23" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="N23" t="n">
         <v>1.1</v>
       </c>
       <c r="O23" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="P23" t="n">
         <v>1.25</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="R23" t="n">
-        <v>1.43</v>
+        <v>1.15</v>
       </c>
       <c r="S23" t="n">
-        <v>1.72</v>
+        <v>1.31</v>
       </c>
       <c r="T23" t="n">
         <v>1.11</v>
@@ -6239,118 +6239,118 @@
         <v>1.11</v>
       </c>
       <c r="V23" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="W23" t="n">
-        <v>1.01</v>
+        <v>1.78</v>
       </c>
       <c r="X23" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="Y23" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="Z23" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AA23" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AB23" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AC23" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AD23" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AE23" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AF23" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AG23" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AH23" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AI23" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AK23" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AL23" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM23" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AN23" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AO23" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.01</v>
+        <v>1.93</v>
       </c>
       <c r="AR23" t="n">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="AS23" t="n">
-        <v>1.01</v>
+        <v>1.99</v>
       </c>
       <c r="AT23" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AU23" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AV23" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AW23" t="n">
-        <v>1.01</v>
+        <v>23</v>
       </c>
       <c r="AX23" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AY23" t="n">
-        <v>1.01</v>
+        <v>1.77</v>
       </c>
       <c r="AZ23" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BA23" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.01</v>
+        <v>23</v>
       </c>
       <c r="BC23" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BD23" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.01</v>
+        <v>30</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BG23" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="BH23" t="n">
         <v>1000</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-07-17 23:15:15</t>
+          <t>2026-07-18 01:36:59</t>
         </is>
       </c>
     </row>
@@ -6436,175 +6436,175 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Halmstads</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Hacken</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>5.6</v>
+        <v>1.3</v>
       </c>
       <c r="G24" t="n">
-        <v>5.8</v>
+        <v>1.32</v>
       </c>
       <c r="H24" t="n">
-        <v>1.62</v>
+        <v>11</v>
       </c>
       <c r="I24" t="n">
-        <v>1.64</v>
+        <v>14</v>
       </c>
       <c r="J24" t="n">
-        <v>4.7</v>
+        <v>6.2</v>
       </c>
       <c r="K24" t="n">
-        <v>4.8</v>
+        <v>6.8</v>
       </c>
       <c r="L24" t="n">
-        <v>1.26</v>
+        <v>1.01</v>
       </c>
       <c r="M24" t="n">
         <v>1.03</v>
       </c>
       <c r="N24" t="n">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="O24" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="P24" t="n">
-        <v>2.5</v>
+        <v>2.66</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="R24" t="n">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="S24" t="n">
-        <v>1.52</v>
+        <v>2.34</v>
       </c>
       <c r="T24" t="n">
-        <v>1.55</v>
+        <v>2</v>
       </c>
       <c r="U24" t="n">
-        <v>2.26</v>
+        <v>1.91</v>
       </c>
       <c r="V24" t="n">
-        <v>2.56</v>
+        <v>1.08</v>
       </c>
       <c r="W24" t="n">
-        <v>1.2</v>
+        <v>4.1</v>
       </c>
       <c r="X24" t="n">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="Y24" t="n">
-        <v>14</v>
+        <v>90</v>
       </c>
       <c r="Z24" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AA24" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AB24" t="n">
-        <v>34</v>
+        <v>11.5</v>
       </c>
       <c r="AC24" t="n">
-        <v>970</v>
+        <v>16.5</v>
       </c>
       <c r="AD24" t="n">
-        <v>970</v>
+        <v>95</v>
       </c>
       <c r="AE24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>55</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AK24" t="n">
         <v>15</v>
       </c>
-      <c r="AF24" t="n">
-        <v>55</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>22</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>25</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>160</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>65</v>
-      </c>
       <c r="AL24" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="AM24" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AN24" t="n">
-        <v>50</v>
+        <v>4.4</v>
       </c>
       <c r="AO24" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AP24" t="n">
         <v>21</v>
       </c>
       <c r="AQ24" t="n">
-        <v>9.4</v>
+        <v>29</v>
       </c>
       <c r="AR24" t="n">
-        <v>9.800000000000001</v>
+        <v>38</v>
       </c>
       <c r="AS24" t="n">
-        <v>6.6</v>
+        <v>5.7</v>
       </c>
       <c r="AT24" t="n">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="AU24" t="n">
-        <v>5.5</v>
+        <v>11.5</v>
       </c>
       <c r="AV24" t="n">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="AW24" t="n">
-        <v>6.4</v>
+        <v>44</v>
       </c>
       <c r="AX24" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AY24" t="n">
         <v>9.6</v>
       </c>
-      <c r="AY24" t="n">
-        <v>7.6</v>
-      </c>
       <c r="AZ24" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="BA24" t="n">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="BB24" t="n">
-        <v>2.96</v>
+        <v>8.6</v>
       </c>
       <c r="BC24" t="n">
-        <v>2.88</v>
+        <v>11</v>
       </c>
       <c r="BD24" t="n">
-        <v>2.86</v>
+        <v>27</v>
       </c>
       <c r="BE24" t="n">
-        <v>9.800000000000001</v>
+        <v>44</v>
       </c>
       <c r="BF24" t="n">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="BG24" t="n">
-        <v>4.2</v>
+        <v>48</v>
       </c>
       <c r="BH24" t="n">
         <v>1000</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-07-17 23:15:15</t>
+          <t>2026-07-18 01:36:59</t>
         </is>
       </c>
     </row>
@@ -6690,239 +6690,239 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Halmstads</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Hacken</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>3.7</v>
+        <v>5.6</v>
       </c>
       <c r="G25" t="n">
-        <v>3.85</v>
+        <v>5.8</v>
       </c>
       <c r="H25" t="n">
-        <v>2.06</v>
+        <v>1.62</v>
       </c>
       <c r="I25" t="n">
-        <v>2.08</v>
+        <v>1.64</v>
       </c>
       <c r="J25" t="n">
-        <v>3.95</v>
+        <v>4.7</v>
       </c>
       <c r="K25" t="n">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="L25" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="M25" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N25" t="n">
-        <v>4.3</v>
+        <v>5.9</v>
       </c>
       <c r="O25" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="P25" t="n">
-        <v>2.32</v>
+        <v>2.68</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.63</v>
+        <v>1.55</v>
       </c>
       <c r="R25" t="n">
-        <v>1.24</v>
+        <v>1.64</v>
       </c>
       <c r="S25" t="n">
-        <v>2.16</v>
+        <v>2.36</v>
       </c>
       <c r="T25" t="n">
-        <v>1.54</v>
+        <v>1.61</v>
       </c>
       <c r="U25" t="n">
-        <v>1.92</v>
+        <v>2.46</v>
       </c>
       <c r="V25" t="n">
-        <v>1.92</v>
+        <v>2.56</v>
       </c>
       <c r="W25" t="n">
-        <v>1.35</v>
+        <v>1.2</v>
       </c>
       <c r="X25" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="Y25" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Z25" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AA25" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AB25" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AC25" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AD25" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AE25" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AF25" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AG25" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AH25" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AI25" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AK25" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AL25" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM25" t="n">
         <v>1000</v>
       </c>
       <c r="AN25" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AO25" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.01</v>
+        <v>23</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AR25" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AS25" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AT25" t="n">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="AU25" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AV25" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW25" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AX25" t="n">
-        <v>1.01</v>
+        <v>26</v>
       </c>
       <c r="AY25" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AZ25" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BA25" t="n">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.01</v>
+        <v>42</v>
       </c>
       <c r="BC25" t="n">
-        <v>1.01</v>
+        <v>29</v>
       </c>
       <c r="BD25" t="n">
-        <v>1.01</v>
+        <v>28</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.01</v>
+        <v>38</v>
       </c>
       <c r="BG25" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BH25" t="n">
         <v>1000</v>
       </c>
       <c r="BI25" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ25" t="n">
         <v>1000</v>
       </c>
       <c r="BK25" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL25" t="n">
         <v>1000</v>
       </c>
       <c r="BM25" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN25" t="n">
         <v>1000</v>
       </c>
       <c r="BO25" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP25" t="n">
         <v>1000</v>
       </c>
       <c r="BQ25" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR25" t="n">
         <v>1000</v>
       </c>
       <c r="BS25" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT25" t="n">
         <v>1000</v>
       </c>
       <c r="BU25" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV25" t="n">
         <v>1000</v>
       </c>
       <c r="BW25" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX25" t="n">
         <v>1000</v>
       </c>
       <c r="BY25" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ25" t="n">
         <v>1000</v>
       </c>
       <c r="CA25" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-07-17 23:15:15</t>
+          <t>2026-07-18 01:36:59</t>
         </is>
       </c>
     </row>
@@ -6944,73 +6944,73 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.29</v>
+        <v>3.7</v>
       </c>
       <c r="G26" t="n">
-        <v>1.32</v>
+        <v>3.85</v>
       </c>
       <c r="H26" t="n">
-        <v>10</v>
+        <v>2.06</v>
       </c>
       <c r="I26" t="n">
-        <v>15.5</v>
+        <v>2.08</v>
       </c>
       <c r="J26" t="n">
-        <v>6.2</v>
+        <v>3.95</v>
       </c>
       <c r="K26" t="n">
-        <v>7.2</v>
+        <v>4.1</v>
       </c>
       <c r="L26" t="n">
         <v>1.01</v>
       </c>
       <c r="M26" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="N26" t="n">
-        <v>5.4</v>
+        <v>4.7</v>
       </c>
       <c r="O26" t="n">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="P26" t="n">
-        <v>2.56</v>
+        <v>2.3</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="R26" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="S26" t="n">
-        <v>2.32</v>
+        <v>2.72</v>
       </c>
       <c r="T26" t="n">
-        <v>1.96</v>
+        <v>1.56</v>
       </c>
       <c r="U26" t="n">
-        <v>1.86</v>
+        <v>2.28</v>
       </c>
       <c r="V26" t="n">
-        <v>1.07</v>
+        <v>1.92</v>
       </c>
       <c r="W26" t="n">
-        <v>4</v>
+        <v>1.35</v>
       </c>
       <c r="X26" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="Y26" t="n">
-        <v>90</v>
+        <v>26</v>
       </c>
       <c r="Z26" t="n">
         <v>1000</v>
@@ -7019,164 +7019,164 @@
         <v>1000</v>
       </c>
       <c r="AB26" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AC26" t="n">
-        <v>17.5</v>
+        <v>970</v>
       </c>
       <c r="AD26" t="n">
-        <v>95</v>
+        <v>970</v>
       </c>
       <c r="AE26" t="n">
         <v>1000</v>
       </c>
       <c r="AF26" t="n">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AG26" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AH26" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AI26" t="n">
         <v>1000</v>
       </c>
       <c r="AJ26" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AK26" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AL26" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AM26" t="n">
         <v>1000</v>
       </c>
       <c r="AN26" t="n">
-        <v>4.4</v>
+        <v>1000</v>
       </c>
       <c r="AO26" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AP26" t="n">
-        <v>21</v>
+        <v>1.25</v>
       </c>
       <c r="AQ26" t="n">
-        <v>29</v>
+        <v>1.19</v>
       </c>
       <c r="AR26" t="n">
-        <v>38</v>
+        <v>1.25</v>
       </c>
       <c r="AS26" t="n">
-        <v>4.4</v>
+        <v>1.25</v>
       </c>
       <c r="AT26" t="n">
-        <v>9</v>
+        <v>1.25</v>
       </c>
       <c r="AU26" t="n">
-        <v>11.5</v>
+        <v>6.4</v>
       </c>
       <c r="AV26" t="n">
-        <v>29</v>
+        <v>1.17</v>
       </c>
       <c r="AW26" t="n">
-        <v>44</v>
+        <v>1.25</v>
       </c>
       <c r="AX26" t="n">
-        <v>7.2</v>
+        <v>1.25</v>
       </c>
       <c r="AY26" t="n">
-        <v>9.199999999999999</v>
+        <v>1.25</v>
       </c>
       <c r="AZ26" t="n">
-        <v>22</v>
+        <v>1.25</v>
       </c>
       <c r="BA26" t="n">
-        <v>42</v>
+        <v>1.25</v>
       </c>
       <c r="BB26" t="n">
-        <v>8.4</v>
+        <v>1.25</v>
       </c>
       <c r="BC26" t="n">
-        <v>11</v>
+        <v>1.25</v>
       </c>
       <c r="BD26" t="n">
-        <v>27</v>
+        <v>1.25</v>
       </c>
       <c r="BE26" t="n">
-        <v>44</v>
+        <v>1.25</v>
       </c>
       <c r="BF26" t="n">
-        <v>3.95</v>
+        <v>1.25</v>
       </c>
       <c r="BG26" t="n">
-        <v>48</v>
+        <v>1.19</v>
       </c>
       <c r="BH26" t="n">
         <v>1000</v>
       </c>
       <c r="BI26" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BJ26" t="n">
         <v>1000</v>
       </c>
       <c r="BK26" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BL26" t="n">
         <v>1000</v>
       </c>
       <c r="BM26" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BN26" t="n">
         <v>1000</v>
       </c>
       <c r="BO26" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BP26" t="n">
         <v>1000</v>
       </c>
       <c r="BQ26" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BR26" t="n">
         <v>1000</v>
       </c>
       <c r="BS26" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BT26" t="n">
         <v>1000</v>
       </c>
       <c r="BU26" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BV26" t="n">
         <v>1000</v>
       </c>
       <c r="BW26" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BX26" t="n">
         <v>1000</v>
       </c>
       <c r="BY26" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BZ26" t="n">
         <v>1000</v>
       </c>
       <c r="CA26" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-07-17 23:15:15</t>
+          <t>2026-07-18 01:36:59</t>
         </is>
       </c>
     </row>
@@ -7207,7 +7207,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.8</v>
+        <v>2.7</v>
       </c>
       <c r="G27" t="n">
         <v>1000</v>
@@ -7219,10 +7219,10 @@
         <v>1000</v>
       </c>
       <c r="J27" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="K27" t="n">
-        <v>1000</v>
+        <v>4</v>
       </c>
       <c r="L27" t="n">
         <v>1.01</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-07-17 23:15:15</t>
+          <t>2026-07-18 01:36:59</t>
         </is>
       </c>
     </row>
@@ -7461,58 +7461,58 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>5.2</v>
+        <v>5.9</v>
       </c>
       <c r="G28" t="n">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="H28" t="n">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="I28" t="n">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="J28" t="n">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="K28" t="n">
-        <v>5.6</v>
+        <v>4.9</v>
       </c>
       <c r="L28" t="n">
         <v>1.01</v>
       </c>
       <c r="M28" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N28" t="n">
-        <v>1.47</v>
+        <v>2.06</v>
       </c>
       <c r="O28" t="n">
         <v>1.23</v>
       </c>
       <c r="P28" t="n">
-        <v>1.25</v>
+        <v>1.47</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.23</v>
+        <v>1.67</v>
       </c>
       <c r="R28" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="S28" t="n">
-        <v>1.23</v>
+        <v>1.68</v>
       </c>
       <c r="T28" t="n">
-        <v>1.11</v>
+        <v>1.75</v>
       </c>
       <c r="U28" t="n">
-        <v>1.11</v>
+        <v>1.92</v>
       </c>
       <c r="V28" t="n">
-        <v>2.38</v>
+        <v>2.52</v>
       </c>
       <c r="W28" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="X28" t="n">
         <v>1000</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-07-17 23:15:15</t>
+          <t>2026-07-18 01:36:59</t>
         </is>
       </c>
     </row>
@@ -7715,13 +7715,13 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="G29" t="n">
         <v>1000</v>
       </c>
       <c r="H29" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="I29" t="n">
         <v>1000</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-07-17 23:15:15</t>
+          <t>2026-07-18 01:36:59</t>
         </is>
       </c>
     </row>
@@ -7969,22 +7969,22 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.06</v>
+        <v>1.36</v>
       </c>
       <c r="G30" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="H30" t="n">
-        <v>1.06</v>
+        <v>1.36</v>
       </c>
       <c r="I30" t="n">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="J30" t="n">
         <v>3.5</v>
       </c>
       <c r="K30" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L30" t="n">
         <v>1.01</v>
@@ -7993,10 +7993,10 @@
         <v>1.01</v>
       </c>
       <c r="N30" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="O30" t="n">
-        <v>1.53</v>
+        <v>1.02</v>
       </c>
       <c r="P30" t="n">
         <v>1.25</v>
@@ -8017,10 +8017,10 @@
         <v>1.29</v>
       </c>
       <c r="V30" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="W30" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X30" t="n">
         <v>1000</v>
@@ -8192,14 +8192,14 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-07-17 23:15:15</t>
+          <t>2026-07-18 01:36:59</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Slovenian Premier League</t>
+          <t>Peruvian Primera Division</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -8214,19 +8214,19 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NK Aluminij</t>
+          <t>CD Los Chankas</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>NK Maribor</t>
+          <t>Sport Boys (Per)</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="G31" t="n">
-        <v>1000</v>
+        <v>1.91</v>
       </c>
       <c r="H31" t="n">
         <v>1.04</v>
@@ -8235,7 +8235,7 @@
         <v>1000</v>
       </c>
       <c r="J31" t="n">
-        <v>1.03</v>
+        <v>2.2</v>
       </c>
       <c r="K31" t="n">
         <v>1000</v>
@@ -8244,37 +8244,37 @@
         <v>1.01</v>
       </c>
       <c r="M31" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N31" t="n">
-        <v>1.28</v>
+        <v>2.1</v>
       </c>
       <c r="O31" t="n">
-        <v>1.14</v>
+        <v>1.35</v>
       </c>
       <c r="P31" t="n">
-        <v>1.27</v>
+        <v>1.81</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.14</v>
+        <v>1.35</v>
       </c>
       <c r="R31" t="n">
         <v>1.18</v>
       </c>
       <c r="S31" t="n">
-        <v>1.14</v>
+        <v>1.36</v>
       </c>
       <c r="T31" t="n">
-        <v>1.11</v>
+        <v>1.61</v>
       </c>
       <c r="U31" t="n">
-        <v>1.11</v>
+        <v>1.45</v>
       </c>
       <c r="V31" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W31" t="n">
-        <v>1.02</v>
+        <v>2.1</v>
       </c>
       <c r="X31" t="n">
         <v>1000</v>
@@ -8446,14 +8446,14 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-07-17 23:15:15</t>
+          <t>2026-07-18 01:36:59</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Peruvian Primera Division</t>
+          <t>Lithuanian A Lyga</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -8468,19 +8468,19 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>CD Los Chankas</t>
+          <t>VMFD Zalgiris</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Sport Boys (Per)</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1.44</v>
+        <v>1.05</v>
       </c>
       <c r="G32" t="n">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="H32" t="n">
         <v>1.05</v>
@@ -8489,40 +8489,40 @@
         <v>1000</v>
       </c>
       <c r="J32" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="K32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N32" t="n">
         <v>1.1</v>
       </c>
-      <c r="K32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M32" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N32" t="n">
-        <v>1.31</v>
-      </c>
       <c r="O32" t="n">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="P32" t="n">
         <v>1.25</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="R32" t="n">
         <v>1.18</v>
       </c>
       <c r="S32" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="T32" t="n">
-        <v>1.61</v>
+        <v>1.11</v>
       </c>
       <c r="U32" t="n">
-        <v>1.45</v>
+        <v>1.11</v>
       </c>
       <c r="V32" t="n">
         <v>1.01</v>
@@ -8693,21 +8693,21 @@
         <v>1.01</v>
       </c>
       <c r="BZ32" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA32" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-07-17 23:15:15</t>
+          <t>2026-07-18 01:36:59</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Lithuanian A Lyga</t>
+          <t>Slovenian Premier League</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -8722,28 +8722,28 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VMFD Zalgiris</t>
+          <t>NK Aluminij</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>NK Maribor</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1.04</v>
+        <v>1.52</v>
       </c>
       <c r="G33" t="n">
         <v>1000</v>
       </c>
       <c r="H33" t="n">
-        <v>1.04</v>
+        <v>1.19</v>
       </c>
       <c r="I33" t="n">
         <v>1000</v>
       </c>
       <c r="J33" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K33" t="n">
         <v>1000</v>
@@ -8752,25 +8752,25 @@
         <v>1.01</v>
       </c>
       <c r="M33" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="N33" t="n">
-        <v>1.1</v>
+        <v>1.29</v>
       </c>
       <c r="O33" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="P33" t="n">
         <v>1.25</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="R33" t="n">
         <v>1.18</v>
       </c>
       <c r="S33" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="T33" t="n">
         <v>1.11</v>
@@ -8779,10 +8779,10 @@
         <v>1.11</v>
       </c>
       <c r="V33" t="n">
-        <v>1.01</v>
+        <v>1.49</v>
       </c>
       <c r="W33" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X33" t="n">
         <v>1000</v>
@@ -8947,14 +8947,14 @@
         <v>1.01</v>
       </c>
       <c r="BZ33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-07-17 23:15:15</t>
+          <t>2026-07-18 01:36:59</t>
         </is>
       </c>
     </row>
@@ -9009,7 +9009,7 @@
         <v>1.01</v>
       </c>
       <c r="N34" t="n">
-        <v>1.1</v>
+        <v>1.26</v>
       </c>
       <c r="O34" t="n">
         <v>1.01</v>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-07-17 23:15:15</t>
+          <t>2026-07-18 01:36:59</t>
         </is>
       </c>
     </row>
@@ -9263,22 +9263,22 @@
         <v>1.01</v>
       </c>
       <c r="N35" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="O35" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="P35" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="R35" t="n">
         <v>1.18</v>
       </c>
       <c r="S35" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="T35" t="n">
         <v>1.11</v>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-07-17 23:15:15</t>
+          <t>2026-07-18 01:36:59</t>
         </is>
       </c>
     </row>
@@ -9493,7 +9493,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="G36" t="n">
         <v>1.79</v>
@@ -9505,7 +9505,7 @@
         <v>1000</v>
       </c>
       <c r="J36" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="K36" t="n">
         <v>1000</v>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-07-17 23:15:15</t>
+          <t>2026-07-18 01:36:59</t>
         </is>
       </c>
     </row>
@@ -9747,22 +9747,22 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="G37" t="n">
         <v>1000</v>
       </c>
       <c r="H37" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="I37" t="n">
         <v>1000</v>
       </c>
       <c r="J37" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="K37" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="L37" t="n">
         <v>1.01</v>
@@ -9771,13 +9771,13 @@
         <v>1.01</v>
       </c>
       <c r="N37" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="O37" t="n">
         <v>1.53</v>
       </c>
       <c r="P37" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="Q37" t="n">
         <v>1.53</v>
@@ -9786,13 +9786,13 @@
         <v>1.18</v>
       </c>
       <c r="S37" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="T37" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="U37" t="n">
-        <v>1.11</v>
+        <v>1.38</v>
       </c>
       <c r="V37" t="n">
         <v>1.02</v>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-07-17 23:15:15</t>
+          <t>2026-07-18 01:36:59</t>
         </is>
       </c>
     </row>
@@ -10001,7 +10001,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="G38" t="n">
         <v>1000</v>
@@ -10013,7 +10013,7 @@
         <v>2.18</v>
       </c>
       <c r="J38" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="K38" t="n">
         <v>1000</v>
@@ -10025,13 +10025,13 @@
         <v>1.08</v>
       </c>
       <c r="N38" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="O38" t="n">
         <v>1.42</v>
       </c>
       <c r="P38" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Q38" t="n">
         <v>1.42</v>
@@ -10224,7 +10224,7 @@
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-07-17 23:15:15</t>
+          <t>2026-07-18 01:36:59</t>
         </is>
       </c>
     </row>
@@ -10261,13 +10261,13 @@
         <v>1000</v>
       </c>
       <c r="H39" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="I39" t="n">
         <v>1000</v>
       </c>
       <c r="J39" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="K39" t="n">
         <v>1000</v>
@@ -10279,13 +10279,13 @@
         <v>1.01</v>
       </c>
       <c r="N39" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="O39" t="n">
         <v>1.42</v>
       </c>
       <c r="P39" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Q39" t="n">
         <v>1.42</v>
@@ -10303,11 +10303,11 @@
         <v>1.11</v>
       </c>
       <c r="V39" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W39" t="n">
         <v>1.02</v>
       </c>
-      <c r="W39" t="n">
-        <v>1.01</v>
-      </c>
       <c r="X39" t="n">
         <v>1000</v>
       </c>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-07-17 23:15:15</t>
+          <t>2026-07-18 01:36:59</t>
         </is>
       </c>
     </row>
@@ -10515,13 +10515,13 @@
         <v>1000</v>
       </c>
       <c r="H40" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="I40" t="n">
         <v>1000</v>
       </c>
       <c r="J40" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K40" t="n">
         <v>1000</v>
@@ -10548,7 +10548,7 @@
         <v>1.07</v>
       </c>
       <c r="S40" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T40" t="n">
         <v>1.11</v>
@@ -10732,7 +10732,7 @@
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-07-17 23:15:15</t>
+          <t>2026-07-18 01:36:59</t>
         </is>
       </c>
     </row>
@@ -10763,13 +10763,13 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="G41" t="n">
         <v>1000</v>
       </c>
       <c r="H41" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="I41" t="n">
         <v>1000</v>
@@ -10986,7 +10986,7 @@
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-07-17 23:15:15</t>
+          <t>2026-07-18 01:36:59</t>
         </is>
       </c>
     </row>
@@ -11017,7 +11017,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="G42" t="n">
         <v>1000</v>
@@ -11041,22 +11041,22 @@
         <v>1.06</v>
       </c>
       <c r="N42" t="n">
-        <v>1.1</v>
+        <v>2.1</v>
       </c>
       <c r="O42" t="n">
         <v>1.38</v>
       </c>
       <c r="P42" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Q42" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="R42" t="n">
         <v>1.07</v>
       </c>
       <c r="S42" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="T42" t="n">
         <v>1.11</v>
@@ -11240,7 +11240,7 @@
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-07-17 23:15:15</t>
+          <t>2026-07-18 01:36:59</t>
         </is>
       </c>
     </row>
@@ -11271,22 +11271,22 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>1.04</v>
+        <v>1.8</v>
       </c>
       <c r="G43" t="n">
         <v>1000</v>
       </c>
       <c r="H43" t="n">
-        <v>1.04</v>
+        <v>1.47</v>
       </c>
       <c r="I43" t="n">
         <v>1000</v>
       </c>
       <c r="J43" t="n">
-        <v>1.02</v>
+        <v>1.69</v>
       </c>
       <c r="K43" t="n">
-        <v>1000</v>
+        <v>3.3</v>
       </c>
       <c r="L43" t="n">
         <v>1.01</v>
@@ -11310,7 +11310,7 @@
         <v>1.18</v>
       </c>
       <c r="S43" t="n">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="T43" t="n">
         <v>1.01</v>
@@ -11494,7 +11494,7 @@
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-07-17 23:15:15</t>
+          <t>2026-07-18 01:36:59</t>
         </is>
       </c>
     </row>
@@ -11748,7 +11748,515 @@
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-07-17 23:15:15</t>
+          <t>2026-07-18 01:36:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Peruvian Primera Division</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Alianza Lima</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Sport Huancayo</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G45" t="n">
+        <v>110</v>
+      </c>
+      <c r="H45" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N45" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="O45" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="P45" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="R45" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S45" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB45" t="inlineStr">
+        <is>
+          <t>2026-07-18 01:36:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Ecuadorian Serie A</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>21:15:00</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Independiente (Ecu)</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Emelec</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="G46" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="H46" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="I46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J46" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="K46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L46" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M46" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N46" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="O46" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="P46" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="R46" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S46" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="T46" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="V46" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W46" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP46" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ46" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR46" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS46" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT46" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU46" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV46" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW46" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX46" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY46" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ46" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA46" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB46" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC46" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD46" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE46" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF46" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG46" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI46" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK46" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM46" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO46" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ46" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS46" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU46" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW46" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY46" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA46" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB46" t="inlineStr">
+        <is>
+          <t>2026-07-18 01:36:59</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-19.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-19.xlsx
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="G2" t="n">
         <v>4.1</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-18 01:36:59</t>
+          <t>2026-07-18 03:58:50</t>
         </is>
       </c>
     </row>
@@ -1153,10 +1153,10 @@
         <v>4.2</v>
       </c>
       <c r="T3" t="n">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="U3" t="n">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="V3" t="n">
         <v>1.16</v>
@@ -1165,22 +1165,22 @@
         <v>2.4</v>
       </c>
       <c r="X3" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Y3" t="n">
         <v>19</v>
       </c>
       <c r="Z3" t="n">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AA3" t="n">
         <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AC3" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AD3" t="n">
         <v>42</v>
@@ -1195,19 +1195,19 @@
         <v>11</v>
       </c>
       <c r="AH3" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AI3" t="n">
         <v>1000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AK3" t="n">
         <v>21</v>
       </c>
       <c r="AL3" t="n">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="AM3" t="n">
         <v>1000</v>
@@ -1219,10 +1219,10 @@
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AR3" t="n">
         <v>26</v>
@@ -1240,13 +1240,13 @@
         <v>18</v>
       </c>
       <c r="AW3" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AX3" t="n">
         <v>7.6</v>
       </c>
       <c r="AY3" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AZ3" t="n">
         <v>18.5</v>
@@ -1264,10 +1264,10 @@
         <v>28</v>
       </c>
       <c r="BE3" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BF3" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BG3" t="n">
         <v>46</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-18 01:36:59</t>
+          <t>2026-07-18 03:58:50</t>
         </is>
       </c>
     </row>
@@ -1368,19 +1368,19 @@
         <v>4.7</v>
       </c>
       <c r="G4" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="H4" t="n">
         <v>1.77</v>
       </c>
       <c r="I4" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="J4" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K4" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L4" t="n">
         <v>1.01</v>
@@ -1389,28 +1389,28 @@
         <v>1.09</v>
       </c>
       <c r="N4" t="n">
-        <v>2.94</v>
+        <v>3.1</v>
       </c>
       <c r="O4" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="P4" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="R4" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="S4" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="T4" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="U4" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="V4" t="n">
         <v>2.04</v>
@@ -1476,55 +1476,55 @@
         <v>1.41</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.31</v>
+        <v>5.4</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.38</v>
+        <v>6.8</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.34</v>
+        <v>6.2</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="BH4" t="n">
         <v>1000</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-18 01:36:59</t>
+          <t>2026-07-18 03:58:50</t>
         </is>
       </c>
     </row>
@@ -1619,13 +1619,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="G5" t="n">
         <v>1000</v>
       </c>
       <c r="H5" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="I5" t="n">
         <v>1000</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-18 01:36:59</t>
+          <t>2026-07-18 03:58:50</t>
         </is>
       </c>
     </row>
@@ -1873,13 +1873,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="G6" t="n">
         <v>1000</v>
       </c>
       <c r="H6" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="I6" t="n">
         <v>1000</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-18 01:36:59</t>
+          <t>2026-07-18 03:58:50</t>
         </is>
       </c>
     </row>
@@ -2127,13 +2127,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="G7" t="n">
         <v>1000</v>
       </c>
       <c r="H7" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="I7" t="n">
         <v>1000</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-18 01:36:59</t>
+          <t>2026-07-18 03:58:50</t>
         </is>
       </c>
     </row>
@@ -2381,7 +2381,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="G8" t="n">
         <v>1000</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-18 01:36:59</t>
+          <t>2026-07-18 03:58:50</t>
         </is>
       </c>
     </row>
@@ -2647,7 +2647,7 @@
         <v>1000</v>
       </c>
       <c r="J9" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="K9" t="n">
         <v>1000</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-18 01:36:59</t>
+          <t>2026-07-18 03:58:50</t>
         </is>
       </c>
     </row>
@@ -2901,7 +2901,7 @@
         <v>1000</v>
       </c>
       <c r="J10" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="K10" t="n">
         <v>1000</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-18 01:36:59</t>
+          <t>2026-07-18 03:58:50</t>
         </is>
       </c>
     </row>
@@ -3167,13 +3167,13 @@
         <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="O11" t="n">
         <v>1.14</v>
       </c>
       <c r="P11" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="Q11" t="n">
         <v>1.14</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-18 01:36:59</t>
+          <t>2026-07-18 03:58:50</t>
         </is>
       </c>
     </row>
@@ -3409,7 +3409,7 @@
         <v>1000</v>
       </c>
       <c r="J12" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="K12" t="n">
         <v>1000</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-18 01:36:59</t>
+          <t>2026-07-18 03:58:50</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
         <v>1000</v>
       </c>
       <c r="J13" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="K13" t="n">
         <v>1000</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-18 01:36:59</t>
+          <t>2026-07-18 03:58:50</t>
         </is>
       </c>
     </row>
@@ -3917,7 +3917,7 @@
         <v>1000</v>
       </c>
       <c r="J14" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="K14" t="n">
         <v>1000</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-18 01:36:59</t>
+          <t>2026-07-18 03:58:50</t>
         </is>
       </c>
     </row>
@@ -4171,7 +4171,7 @@
         <v>1000</v>
       </c>
       <c r="J15" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="K15" t="n">
         <v>1000</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-18 01:36:59</t>
+          <t>2026-07-18 03:58:50</t>
         </is>
       </c>
     </row>
@@ -4413,19 +4413,19 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.11</v>
+        <v>1.5</v>
       </c>
       <c r="G16" t="n">
         <v>1000</v>
       </c>
       <c r="H16" t="n">
-        <v>1.11</v>
+        <v>1.5</v>
       </c>
       <c r="I16" t="n">
         <v>1000</v>
       </c>
       <c r="J16" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="K16" t="n">
         <v>1000</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-18 01:36:59</t>
+          <t>2026-07-18 03:58:50</t>
         </is>
       </c>
     </row>
@@ -4685,19 +4685,19 @@
         <v>1000</v>
       </c>
       <c r="L17" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="M17" t="n">
         <v>1.01</v>
       </c>
       <c r="N17" t="n">
-        <v>1.26</v>
+        <v>2.32</v>
       </c>
       <c r="O17" t="n">
         <v>1.23</v>
       </c>
       <c r="P17" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Q17" t="n">
         <v>1.23</v>
@@ -4706,7 +4706,7 @@
         <v>1.25</v>
       </c>
       <c r="S17" t="n">
-        <v>1.23</v>
+        <v>1.05</v>
       </c>
       <c r="T17" t="n">
         <v>1.11</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-18 01:36:59</t>
+          <t>2026-07-18 03:58:50</t>
         </is>
       </c>
     </row>
@@ -4921,16 +4921,16 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.7</v>
+        <v>2.56</v>
       </c>
       <c r="G18" t="n">
         <v>1000</v>
       </c>
       <c r="H18" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="I18" t="n">
-        <v>2.78</v>
+        <v>2.92</v>
       </c>
       <c r="J18" t="n">
         <v>3.3</v>
@@ -4972,7 +4972,7 @@
         <v>1.58</v>
       </c>
       <c r="W18" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X18" t="n">
         <v>1000</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-18 01:36:59</t>
+          <t>2026-07-18 03:58:50</t>
         </is>
       </c>
     </row>
@@ -5175,19 +5175,19 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="G19" t="n">
         <v>1000</v>
       </c>
       <c r="H19" t="n">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="I19" t="n">
         <v>1000</v>
       </c>
       <c r="J19" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="K19" t="n">
         <v>3.4</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-18 01:36:59</t>
+          <t>2026-07-18 03:58:50</t>
         </is>
       </c>
     </row>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-18 01:36:59</t>
+          <t>2026-07-18 03:58:50</t>
         </is>
       </c>
     </row>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-07-18 01:36:59</t>
+          <t>2026-07-18 03:58:50</t>
         </is>
       </c>
     </row>
@@ -5949,7 +5949,7 @@
         <v>1000</v>
       </c>
       <c r="J22" t="n">
-        <v>1.16</v>
+        <v>3.3</v>
       </c>
       <c r="K22" t="n">
         <v>1000</v>
@@ -5958,25 +5958,25 @@
         <v>1.01</v>
       </c>
       <c r="M22" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N22" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="O22" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="P22" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="R22" t="n">
         <v>1.07</v>
       </c>
       <c r="S22" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="T22" t="n">
         <v>1.11</v>
@@ -5985,10 +5985,10 @@
         <v>1.11</v>
       </c>
       <c r="V22" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W22" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X22" t="n">
         <v>1000</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-07-18 01:36:59</t>
+          <t>2026-07-18 03:58:50</t>
         </is>
       </c>
     </row>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-07-18 01:36:59</t>
+          <t>2026-07-18 03:58:50</t>
         </is>
       </c>
     </row>
@@ -6454,7 +6454,7 @@
         <v>11</v>
       </c>
       <c r="I24" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="J24" t="n">
         <v>6.2</v>
@@ -6469,13 +6469,13 @@
         <v>1.03</v>
       </c>
       <c r="N24" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="O24" t="n">
         <v>1.17</v>
       </c>
       <c r="P24" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="Q24" t="n">
         <v>1.56</v>
@@ -6484,13 +6484,13 @@
         <v>1.63</v>
       </c>
       <c r="S24" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="T24" t="n">
         <v>2</v>
       </c>
       <c r="U24" t="n">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="V24" t="n">
         <v>1.08</v>
@@ -6502,7 +6502,7 @@
         <v>48</v>
       </c>
       <c r="Y24" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="Z24" t="n">
         <v>1000</v>
@@ -6511,10 +6511,10 @@
         <v>1000</v>
       </c>
       <c r="AB24" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AC24" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AD24" t="n">
         <v>95</v>
@@ -6538,7 +6538,7 @@
         <v>10.5</v>
       </c>
       <c r="AK24" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AL24" t="n">
         <v>80</v>
@@ -6562,10 +6562,10 @@
         <v>38</v>
       </c>
       <c r="AS24" t="n">
-        <v>5.7</v>
+        <v>55</v>
       </c>
       <c r="AT24" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AU24" t="n">
         <v>11.5</v>
@@ -6589,7 +6589,7 @@
         <v>42</v>
       </c>
       <c r="BB24" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC24" t="n">
         <v>11</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-07-18 01:36:59</t>
+          <t>2026-07-18 03:58:50</t>
         </is>
       </c>
     </row>
@@ -6723,25 +6723,25 @@
         <v>1.03</v>
       </c>
       <c r="N25" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="O25" t="n">
         <v>1.17</v>
       </c>
       <c r="P25" t="n">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="R25" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T25" t="n">
         <v>1.64</v>
-      </c>
-      <c r="S25" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="T25" t="n">
-        <v>1.61</v>
       </c>
       <c r="U25" t="n">
         <v>2.46</v>
@@ -6762,10 +6762,10 @@
         <v>12</v>
       </c>
       <c r="AA25" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AB25" t="n">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="AC25" t="n">
         <v>11.5</v>
@@ -6807,7 +6807,7 @@
         <v>6.6</v>
       </c>
       <c r="AP25" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AQ25" t="n">
         <v>11</v>
@@ -6825,13 +6825,13 @@
         <v>10</v>
       </c>
       <c r="AV25" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AW25" t="n">
         <v>11.5</v>
       </c>
       <c r="AX25" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AY25" t="n">
         <v>15.5</v>
@@ -6846,7 +6846,7 @@
         <v>42</v>
       </c>
       <c r="BC25" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BD25" t="n">
         <v>28</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-07-18 01:36:59</t>
+          <t>2026-07-18 03:58:50</t>
         </is>
       </c>
     </row>
@@ -6956,7 +6956,7 @@
         <v>3.7</v>
       </c>
       <c r="G26" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="H26" t="n">
         <v>2.06</v>
@@ -6971,13 +6971,13 @@
         <v>4.1</v>
       </c>
       <c r="L26" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="M26" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N26" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="O26" t="n">
         <v>1.23</v>
@@ -6986,13 +6986,13 @@
         <v>2.3</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="R26" t="n">
         <v>1.44</v>
       </c>
       <c r="S26" t="n">
-        <v>2.72</v>
+        <v>2.58</v>
       </c>
       <c r="T26" t="n">
         <v>1.56</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-07-18 01:36:59</t>
+          <t>2026-07-18 03:58:50</t>
         </is>
       </c>
     </row>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-07-18 01:36:59</t>
+          <t>2026-07-18 03:58:50</t>
         </is>
       </c>
     </row>
@@ -7461,22 +7461,22 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="G28" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="H28" t="n">
         <v>1.58</v>
       </c>
       <c r="I28" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="J28" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K28" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="L28" t="n">
         <v>1.01</v>
@@ -7485,43 +7485,43 @@
         <v>1.05</v>
       </c>
       <c r="N28" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="O28" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="P28" t="n">
         <v>2.06</v>
       </c>
-      <c r="O28" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="P28" t="n">
-        <v>1.47</v>
-      </c>
       <c r="Q28" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="R28" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="S28" t="n">
-        <v>1.68</v>
+        <v>2.66</v>
       </c>
       <c r="T28" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="U28" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="V28" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="W28" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="X28" t="n">
         <v>1000</v>
       </c>
       <c r="Y28" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z28" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AA28" t="n">
         <v>1000</v>
@@ -7530,10 +7530,10 @@
         <v>1000</v>
       </c>
       <c r="AC28" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD28" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AE28" t="n">
         <v>1000</v>
@@ -7566,61 +7566,61 @@
         <v>1000</v>
       </c>
       <c r="AO28" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AP28" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="AQ28" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="AR28" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="AS28" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="AT28" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="AU28" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="AV28" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="AW28" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="AX28" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="AY28" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="AZ28" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="BA28" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="BB28" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="BC28" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="BD28" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="BE28" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="BF28" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="BG28" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="BH28" t="n">
         <v>1000</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-07-18 01:36:59</t>
+          <t>2026-07-18 03:58:50</t>
         </is>
       </c>
     </row>
@@ -7715,19 +7715,19 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="G29" t="n">
         <v>1000</v>
       </c>
       <c r="H29" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="I29" t="n">
         <v>1000</v>
       </c>
       <c r="J29" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="K29" t="n">
         <v>1000</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-07-18 01:36:59</t>
+          <t>2026-07-18 03:58:50</t>
         </is>
       </c>
     </row>
@@ -7969,16 +7969,16 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="G30" t="n">
+        <v>990</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="I30" t="n">
         <v>110</v>
-      </c>
-      <c r="H30" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="I30" t="n">
-        <v>95</v>
       </c>
       <c r="J30" t="n">
         <v>3.5</v>
@@ -8017,10 +8017,10 @@
         <v>1.29</v>
       </c>
       <c r="V30" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="W30" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X30" t="n">
         <v>1000</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-07-18 01:36:59</t>
+          <t>2026-07-18 03:58:50</t>
         </is>
       </c>
     </row>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-07-18 01:36:59</t>
+          <t>2026-07-18 03:58:50</t>
         </is>
       </c>
     </row>
@@ -8477,19 +8477,19 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1.05</v>
+        <v>1.43</v>
       </c>
       <c r="G32" t="n">
         <v>1000</v>
       </c>
       <c r="H32" t="n">
-        <v>1.05</v>
+        <v>1.45</v>
       </c>
       <c r="I32" t="n">
         <v>1000</v>
       </c>
       <c r="J32" t="n">
-        <v>1.02</v>
+        <v>3.3</v>
       </c>
       <c r="K32" t="n">
         <v>1000</v>
@@ -8504,19 +8504,19 @@
         <v>1.1</v>
       </c>
       <c r="O32" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="P32" t="n">
         <v>1.25</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="R32" t="n">
         <v>1.18</v>
       </c>
       <c r="S32" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="T32" t="n">
         <v>1.11</v>
@@ -8525,10 +8525,10 @@
         <v>1.11</v>
       </c>
       <c r="V32" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W32" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X32" t="n">
         <v>1000</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-07-18 01:36:59</t>
+          <t>2026-07-18 03:58:50</t>
         </is>
       </c>
     </row>
@@ -8731,19 +8731,19 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1.52</v>
+        <v>1.04</v>
       </c>
       <c r="G33" t="n">
         <v>1000</v>
       </c>
       <c r="H33" t="n">
-        <v>1.19</v>
+        <v>1.37</v>
       </c>
       <c r="I33" t="n">
         <v>1000</v>
       </c>
       <c r="J33" t="n">
-        <v>1.03</v>
+        <v>1.56</v>
       </c>
       <c r="K33" t="n">
         <v>1000</v>
@@ -8761,7 +8761,7 @@
         <v>1.14</v>
       </c>
       <c r="P33" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="Q33" t="n">
         <v>1.14</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-07-18 01:36:59</t>
+          <t>2026-07-18 03:58:50</t>
         </is>
       </c>
     </row>
@@ -9009,7 +9009,7 @@
         <v>1.01</v>
       </c>
       <c r="N34" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="O34" t="n">
         <v>1.01</v>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-07-18 01:36:59</t>
+          <t>2026-07-18 03:58:50</t>
         </is>
       </c>
     </row>
@@ -9263,13 +9263,13 @@
         <v>1.01</v>
       </c>
       <c r="N35" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="O35" t="n">
         <v>1.18</v>
       </c>
       <c r="P35" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="Q35" t="n">
         <v>1.18</v>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-07-18 01:36:59</t>
+          <t>2026-07-18 03:58:50</t>
         </is>
       </c>
     </row>
@@ -9493,7 +9493,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="G36" t="n">
         <v>1.79</v>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-07-18 01:36:59</t>
+          <t>2026-07-18 03:58:50</t>
         </is>
       </c>
     </row>
@@ -9747,19 +9747,19 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="G37" t="n">
         <v>1000</v>
       </c>
       <c r="H37" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="I37" t="n">
         <v>1000</v>
       </c>
       <c r="J37" t="n">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="K37" t="n">
         <v>3.2</v>
@@ -9786,10 +9786,10 @@
         <v>1.18</v>
       </c>
       <c r="S37" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="T37" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="U37" t="n">
         <v>1.38</v>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-07-18 01:36:59</t>
+          <t>2026-07-18 03:58:50</t>
         </is>
       </c>
     </row>
@@ -10025,16 +10025,16 @@
         <v>1.08</v>
       </c>
       <c r="N38" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="O38" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="P38" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="R38" t="n">
         <v>1.18</v>
@@ -10224,7 +10224,7 @@
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-07-18 01:36:59</t>
+          <t>2026-07-18 03:58:50</t>
         </is>
       </c>
     </row>
@@ -10261,13 +10261,13 @@
         <v>1000</v>
       </c>
       <c r="H39" t="n">
-        <v>1.05</v>
+        <v>1.55</v>
       </c>
       <c r="I39" t="n">
         <v>1000</v>
       </c>
       <c r="J39" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="K39" t="n">
         <v>1000</v>
@@ -10306,7 +10306,7 @@
         <v>1.08</v>
       </c>
       <c r="W39" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X39" t="n">
         <v>1000</v>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-07-18 01:36:59</t>
+          <t>2026-07-18 03:58:50</t>
         </is>
       </c>
     </row>
@@ -10521,7 +10521,7 @@
         <v>1000</v>
       </c>
       <c r="J40" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="K40" t="n">
         <v>1000</v>
@@ -10732,7 +10732,7 @@
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-07-18 01:36:59</t>
+          <t>2026-07-18 03:58:50</t>
         </is>
       </c>
     </row>
@@ -10763,19 +10763,19 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1.05</v>
+        <v>1.34</v>
       </c>
       <c r="G41" t="n">
         <v>1000</v>
       </c>
       <c r="H41" t="n">
-        <v>1.05</v>
+        <v>1.31</v>
       </c>
       <c r="I41" t="n">
         <v>1000</v>
       </c>
       <c r="J41" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="K41" t="n">
         <v>1000</v>
@@ -10986,7 +10986,7 @@
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-07-18 01:36:59</t>
+          <t>2026-07-18 03:58:50</t>
         </is>
       </c>
     </row>
@@ -11017,7 +11017,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>1.05</v>
+        <v>1.48</v>
       </c>
       <c r="G42" t="n">
         <v>1000</v>
@@ -11240,7 +11240,7 @@
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-07-18 01:36:59</t>
+          <t>2026-07-18 03:58:50</t>
         </is>
       </c>
     </row>
@@ -11494,7 +11494,7 @@
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-07-18 01:36:59</t>
+          <t>2026-07-18 03:58:50</t>
         </is>
       </c>
     </row>
@@ -11748,7 +11748,7 @@
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-07-18 01:36:59</t>
+          <t>2026-07-18 03:58:50</t>
         </is>
       </c>
     </row>
@@ -11782,7 +11782,7 @@
         <v>1.04</v>
       </c>
       <c r="G45" t="n">
-        <v>110</v>
+        <v>1.55</v>
       </c>
       <c r="H45" t="n">
         <v>1.04</v>
@@ -12002,7 +12002,7 @@
       </c>
       <c r="CB45" t="inlineStr">
         <is>
-          <t>2026-07-18 01:36:59</t>
+          <t>2026-07-18 03:58:50</t>
         </is>
       </c>
     </row>
@@ -12033,7 +12033,7 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="G46" t="n">
         <v>1.46</v>
@@ -12075,7 +12075,7 @@
         <v>1.82</v>
       </c>
       <c r="T46" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="U46" t="n">
         <v>1.03</v>
@@ -12256,7 +12256,7 @@
       </c>
       <c r="CB46" t="inlineStr">
         <is>
-          <t>2026-07-18 01:36:59</t>
+          <t>2026-07-18 03:58:50</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-19.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-19.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB46"/>
+  <dimension ref="A1:CB47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -875,10 +875,10 @@
         <v>3.85</v>
       </c>
       <c r="L2" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="M2" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N2" t="n">
         <v>4</v>
@@ -890,19 +890,19 @@
         <v>2</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="R2" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S2" t="n">
         <v>3.45</v>
       </c>
       <c r="T2" t="n">
-        <v>1.11</v>
+        <v>1.73</v>
       </c>
       <c r="U2" t="n">
-        <v>1.11</v>
+        <v>1.93</v>
       </c>
       <c r="V2" t="n">
         <v>1.9</v>
@@ -911,176 +911,176 @@
         <v>1.32</v>
       </c>
       <c r="X2" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AA2" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AB2" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD2" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AF2" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AG2" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AH2" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI2" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AK2" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AL2" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM2" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AN2" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AO2" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AP2" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AR2" t="n">
         <v>11</v>
       </c>
-      <c r="AQ2" t="n">
-        <v>8</v>
-      </c>
-      <c r="AR2" t="n">
+      <c r="AS2" t="n">
+        <v>21</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV2" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AS2" t="n">
-        <v>18</v>
-      </c>
-      <c r="AT2" t="n">
+      <c r="AW2" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>38</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>38</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>11</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>7</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>140</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>21</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>40</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>23</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>50</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>29</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BW2" t="n">
         <v>10.5</v>
       </c>
-      <c r="AU2" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>19</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>14</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>26</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>40</v>
-      </c>
-      <c r="BC2" t="n">
+      <c r="BX2" t="n">
+        <v>34</v>
+      </c>
+      <c r="BY2" t="n">
+        <v>20</v>
+      </c>
+      <c r="BZ2" t="n">
         <v>29</v>
       </c>
-      <c r="BD2" t="n">
-        <v>36</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>40</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BP2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BR2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BT2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BV2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BX2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BZ2" t="n">
-        <v>1000</v>
-      </c>
       <c r="CA2" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-18 03:58:50</t>
+          <t>2026-07-18 06:20:25</t>
         </is>
       </c>
     </row>
@@ -1111,13 +1111,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="G3" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="H3" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="I3" t="n">
         <v>7</v>
@@ -1126,10 +1126,10 @@
         <v>3.75</v>
       </c>
       <c r="K3" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="L3" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="M3" t="n">
         <v>1.09</v>
@@ -1138,10 +1138,10 @@
         <v>3.25</v>
       </c>
       <c r="O3" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="P3" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="Q3" t="n">
         <v>2.22</v>
@@ -1153,7 +1153,7 @@
         <v>4.2</v>
       </c>
       <c r="T3" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="U3" t="n">
         <v>1.77</v>
@@ -1162,40 +1162,40 @@
         <v>1.16</v>
       </c>
       <c r="W3" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="X3" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Y3" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="AA3" t="n">
         <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AC3" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD3" t="n">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="AE3" t="n">
         <v>1000</v>
       </c>
       <c r="AF3" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AG3" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="AI3" t="n">
         <v>1000</v>
@@ -1207,7 +1207,7 @@
         <v>21</v>
       </c>
       <c r="AL3" t="n">
-        <v>260</v>
+        <v>60</v>
       </c>
       <c r="AM3" t="n">
         <v>1000</v>
@@ -1222,7 +1222,7 @@
         <v>10.5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AR3" t="n">
         <v>26</v>
@@ -1237,34 +1237,34 @@
         <v>7.8</v>
       </c>
       <c r="AV3" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AW3" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AX3" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AY3" t="n">
         <v>9.6</v>
       </c>
       <c r="AZ3" t="n">
-        <v>18.5</v>
+        <v>23</v>
       </c>
       <c r="BA3" t="n">
         <v>42</v>
       </c>
       <c r="BB3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BC3" t="n">
-        <v>14.5</v>
+        <v>17.5</v>
       </c>
       <c r="BD3" t="n">
         <v>28</v>
       </c>
       <c r="BE3" t="n">
-        <v>46</v>
+        <v>95</v>
       </c>
       <c r="BF3" t="n">
         <v>11</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-18 03:58:50</t>
+          <t>2026-07-18 06:20:25</t>
         </is>
       </c>
     </row>
@@ -1365,25 +1365,25 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="G4" t="n">
-        <v>7.2</v>
+        <v>5.7</v>
       </c>
       <c r="H4" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="I4" t="n">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="J4" t="n">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="K4" t="n">
         <v>3.85</v>
       </c>
       <c r="L4" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="M4" t="n">
         <v>1.09</v>
@@ -1392,203 +1392,203 @@
         <v>3.1</v>
       </c>
       <c r="O4" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="P4" t="n">
-        <v>1.63</v>
+        <v>1.71</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.16</v>
+        <v>2.24</v>
       </c>
       <c r="R4" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="S4" t="n">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="T4" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="U4" t="n">
-        <v>1.73</v>
+        <v>1.82</v>
       </c>
       <c r="V4" t="n">
-        <v>2.04</v>
+        <v>2.14</v>
       </c>
       <c r="W4" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="X4" t="n">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>970</v>
+        <v>7.2</v>
       </c>
       <c r="Z4" t="n">
-        <v>970</v>
+        <v>10.5</v>
       </c>
       <c r="AA4" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AB4" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>970</v>
+        <v>8.4</v>
       </c>
       <c r="AD4" t="n">
-        <v>970</v>
+        <v>10.5</v>
       </c>
       <c r="AE4" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AF4" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AG4" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AH4" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI4" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AK4" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AL4" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AM4" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AN4" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AO4" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.41</v>
+        <v>10</v>
       </c>
       <c r="AQ4" t="n">
-        <v>5.4</v>
+        <v>6.4</v>
       </c>
       <c r="AR4" t="n">
-        <v>6.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.52</v>
+        <v>17.5</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.52</v>
+        <v>13</v>
       </c>
       <c r="AU4" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.41</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.52</v>
+        <v>19.5</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.52</v>
+        <v>9.6</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.52</v>
+        <v>19</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.52</v>
+        <v>20</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.52</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.52</v>
+        <v>10.5</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.52</v>
+        <v>10</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.52</v>
+        <v>10</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.52</v>
+        <v>10.5</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.52</v>
+        <v>10</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.52</v>
+        <v>14</v>
       </c>
       <c r="BH4" t="n">
-        <v>1000</v>
+        <v>3.1</v>
       </c>
       <c r="BI4" t="n">
-        <v>1.01</v>
+        <v>2.54</v>
       </c>
       <c r="BJ4" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BK4" t="n">
         <v>1.01</v>
       </c>
       <c r="BL4" t="n">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="BM4" t="n">
         <v>1.01</v>
       </c>
       <c r="BN4" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="BO4" t="n">
         <v>1.01</v>
       </c>
       <c r="BP4" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BQ4" t="n">
         <v>1.01</v>
       </c>
       <c r="BR4" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="BS4" t="n">
         <v>1.01</v>
       </c>
       <c r="BT4" t="n">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="BU4" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="BV4" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="BW4" t="n">
         <v>1.01</v>
       </c>
       <c r="BX4" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BY4" t="n">
         <v>1.01</v>
       </c>
       <c r="BZ4" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="CA4" t="n">
         <v>1.01</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-18 03:58:50</t>
+          <t>2026-07-18 06:20:25</t>
         </is>
       </c>
     </row>
@@ -1619,118 +1619,118 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.05</v>
+        <v>1.75</v>
       </c>
       <c r="G5" t="n">
-        <v>1000</v>
+        <v>1.89</v>
       </c>
       <c r="H5" t="n">
-        <v>1.05</v>
+        <v>4.7</v>
       </c>
       <c r="I5" t="n">
-        <v>1000</v>
+        <v>5.7</v>
       </c>
       <c r="J5" t="n">
-        <v>1.02</v>
+        <v>3.85</v>
       </c>
       <c r="K5" t="n">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="L5" t="n">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="M5" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N5" t="n">
-        <v>1.35</v>
+        <v>3.65</v>
       </c>
       <c r="O5" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="P5" t="n">
-        <v>1.25</v>
+        <v>1.92</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.31</v>
+        <v>1.9</v>
       </c>
       <c r="R5" t="n">
-        <v>1.18</v>
+        <v>1.34</v>
       </c>
       <c r="S5" t="n">
-        <v>1.33</v>
+        <v>3.45</v>
       </c>
       <c r="T5" t="n">
-        <v>1.11</v>
+        <v>1.75</v>
       </c>
       <c r="U5" t="n">
-        <v>1.11</v>
+        <v>1.87</v>
       </c>
       <c r="V5" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="W5" t="n">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="X5" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="Y5" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="Z5" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AA5" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AB5" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC5" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD5" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AE5" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AF5" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AG5" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH5" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI5" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AK5" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AL5" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AM5" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN5" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AO5" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AR5" t="n">
         <v>1.01</v>
@@ -1739,34 +1739,34 @@
         <v>1.01</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="AW5" t="n">
         <v>1.01</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BA5" t="n">
         <v>1.01</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BD5" t="n">
         <v>1.01</v>
@@ -1775,64 +1775,64 @@
         <v>1.01</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="BG5" t="n">
         <v>1.01</v>
       </c>
       <c r="BH5" t="n">
-        <v>1000</v>
+        <v>3.8</v>
       </c>
       <c r="BI5" t="n">
-        <v>1.04</v>
+        <v>2.82</v>
       </c>
       <c r="BJ5" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK5" t="n">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="BL5" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="BM5" t="n">
-        <v>1.04</v>
+        <v>5.7</v>
       </c>
       <c r="BN5" t="n">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.04</v>
+        <v>3.55</v>
       </c>
       <c r="BP5" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BQ5" t="n">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="BR5" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BS5" t="n">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="BT5" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="BU5" t="n">
-        <v>1.04</v>
+        <v>3.65</v>
       </c>
       <c r="BV5" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BW5" t="n">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="BX5" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="BZ5" t="n">
         <v>0</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-18 03:58:50</t>
+          <t>2026-07-18 06:20:25</t>
         </is>
       </c>
     </row>
@@ -1873,145 +1873,145 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.06</v>
+        <v>2.76</v>
       </c>
       <c r="G6" t="n">
-        <v>1000</v>
+        <v>3.15</v>
       </c>
       <c r="H6" t="n">
-        <v>1.06</v>
+        <v>2.52</v>
       </c>
       <c r="I6" t="n">
-        <v>1000</v>
+        <v>2.84</v>
       </c>
       <c r="J6" t="n">
-        <v>1.02</v>
+        <v>3</v>
       </c>
       <c r="K6" t="n">
-        <v>1000</v>
+        <v>3.8</v>
       </c>
       <c r="L6" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="M6" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N6" t="n">
-        <v>1.1</v>
+        <v>3.55</v>
       </c>
       <c r="O6" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="P6" t="n">
-        <v>1.25</v>
+        <v>1.86</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.34</v>
+        <v>1.94</v>
       </c>
       <c r="R6" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="S6" t="n">
-        <v>1.34</v>
+        <v>3.45</v>
       </c>
       <c r="T6" t="n">
-        <v>1.43</v>
+        <v>1.74</v>
       </c>
       <c r="U6" t="n">
-        <v>1.7</v>
+        <v>2.12</v>
       </c>
       <c r="V6" t="n">
-        <v>1.01</v>
+        <v>1.54</v>
       </c>
       <c r="W6" t="n">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="X6" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="Y6" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AA6" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AB6" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AC6" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD6" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AE6" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AF6" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AG6" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AI6" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AK6" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AL6" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AM6" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN6" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AO6" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AS6" t="n">
         <v>1.01</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AW6" t="n">
         <v>1.01</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BA6" t="n">
         <v>1.01</v>
@@ -2032,61 +2032,61 @@
         <v>1.01</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BH6" t="n">
-        <v>1000</v>
+        <v>3.45</v>
       </c>
       <c r="BI6" t="n">
-        <v>1.04</v>
+        <v>3</v>
       </c>
       <c r="BJ6" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK6" t="n">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="BL6" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="BM6" t="n">
-        <v>1.04</v>
+        <v>8</v>
       </c>
       <c r="BN6" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="BP6" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BQ6" t="n">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="BR6" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BS6" t="n">
-        <v>1.04</v>
+        <v>7</v>
       </c>
       <c r="BT6" t="n">
-        <v>1000</v>
+        <v>5.8</v>
       </c>
       <c r="BU6" t="n">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BV6" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BW6" t="n">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="BX6" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.04</v>
+        <v>6.8</v>
       </c>
       <c r="BZ6" t="n">
         <v>0</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-18 03:58:50</t>
+          <t>2026-07-18 06:20:25</t>
         </is>
       </c>
     </row>
@@ -2127,145 +2127,145 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.06</v>
+        <v>2.94</v>
       </c>
       <c r="G7" t="n">
-        <v>1000</v>
+        <v>3.4</v>
       </c>
       <c r="H7" t="n">
-        <v>1.06</v>
+        <v>2.4</v>
       </c>
       <c r="I7" t="n">
-        <v>1000</v>
+        <v>2.7</v>
       </c>
       <c r="J7" t="n">
-        <v>1.02</v>
+        <v>3.3</v>
       </c>
       <c r="K7" t="n">
-        <v>1000</v>
+        <v>3.7</v>
       </c>
       <c r="L7" t="n">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="M7" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N7" t="n">
-        <v>1.33</v>
+        <v>3.4</v>
       </c>
       <c r="O7" t="n">
         <v>1.33</v>
       </c>
       <c r="P7" t="n">
-        <v>1.25</v>
+        <v>1.83</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.33</v>
+        <v>1.98</v>
       </c>
       <c r="R7" t="n">
-        <v>1.18</v>
+        <v>1.32</v>
       </c>
       <c r="S7" t="n">
-        <v>1.34</v>
+        <v>3.55</v>
       </c>
       <c r="T7" t="n">
-        <v>1.11</v>
+        <v>1.64</v>
       </c>
       <c r="U7" t="n">
-        <v>1.11</v>
+        <v>1.91</v>
       </c>
       <c r="V7" t="n">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="W7" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="X7" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AA7" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AB7" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AD7" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AE7" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AF7" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AG7" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI7" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AK7" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AL7" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM7" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AN7" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AO7" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AS7" t="n">
         <v>1.01</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BA7" t="n">
         <v>1.01</v>
@@ -2286,61 +2286,61 @@
         <v>1.01</v>
       </c>
       <c r="BG7" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BH7" t="n">
-        <v>1000</v>
+        <v>3.8</v>
       </c>
       <c r="BI7" t="n">
-        <v>1.04</v>
+        <v>2.64</v>
       </c>
       <c r="BJ7" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK7" t="n">
-        <v>1.04</v>
+        <v>7</v>
       </c>
       <c r="BL7" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="BM7" t="n">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="BN7" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="BP7" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BQ7" t="n">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="BR7" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BS7" t="n">
-        <v>1.04</v>
+        <v>5.6</v>
       </c>
       <c r="BT7" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BU7" t="n">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="BV7" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BW7" t="n">
-        <v>1.04</v>
+        <v>5.1</v>
       </c>
       <c r="BX7" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BY7" t="n">
-        <v>1.04</v>
+        <v>5.5</v>
       </c>
       <c r="BZ7" t="n">
         <v>0</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-18 03:58:50</t>
+          <t>2026-07-18 06:20:25</t>
         </is>
       </c>
     </row>
@@ -2381,118 +2381,118 @@
         </is>
       </c>
       <c r="F8" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="H8" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="I8" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="J8" t="n">
+        <v>5</v>
+      </c>
+      <c r="K8" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="M8" t="n">
         <v>1.05</v>
       </c>
-      <c r="G8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H8" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="I8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J8" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="K8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1.04</v>
-      </c>
       <c r="N8" t="n">
-        <v>1.45</v>
+        <v>4.3</v>
       </c>
       <c r="O8" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="P8" t="n">
-        <v>1.25</v>
+        <v>2.14</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.22</v>
+        <v>1.71</v>
       </c>
       <c r="R8" t="n">
-        <v>1.21</v>
+        <v>1.44</v>
       </c>
       <c r="S8" t="n">
-        <v>2.3</v>
+        <v>2.82</v>
       </c>
       <c r="T8" t="n">
-        <v>1.58</v>
+        <v>1.96</v>
       </c>
       <c r="U8" t="n">
-        <v>1.57</v>
+        <v>1.86</v>
       </c>
       <c r="V8" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="W8" t="n">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="X8" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="Y8" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="Z8" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AA8" t="n">
-        <v>1000</v>
+        <v>360</v>
       </c>
       <c r="AB8" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AD8" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AE8" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AF8" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AG8" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AI8" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AK8" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AL8" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AM8" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AN8" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AO8" t="n">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AR8" t="n">
         <v>1.01</v>
@@ -2501,10 +2501,10 @@
         <v>1.01</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AV8" t="n">
         <v>1.01</v>
@@ -2513,22 +2513,22 @@
         <v>1.01</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="BA8" t="n">
         <v>1.01</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BD8" t="n">
         <v>1.01</v>
@@ -2537,61 +2537,61 @@
         <v>1.01</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BG8" t="n">
         <v>1.01</v>
       </c>
       <c r="BH8" t="n">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="BI8" t="n">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="BJ8" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BK8" t="n">
         <v>1.01</v>
       </c>
       <c r="BL8" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="BM8" t="n">
         <v>1.01</v>
       </c>
       <c r="BN8" t="n">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="BP8" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BQ8" t="n">
         <v>1.01</v>
       </c>
       <c r="BR8" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BS8" t="n">
         <v>1.01</v>
       </c>
       <c r="BT8" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BU8" t="n">
         <v>1.01</v>
       </c>
       <c r="BV8" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="BW8" t="n">
         <v>1.01</v>
       </c>
       <c r="BX8" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="BY8" t="n">
         <v>1.01</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-18 03:58:50</t>
+          <t>2026-07-18 06:20:25</t>
         </is>
       </c>
     </row>
@@ -2635,19 +2635,19 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="G9" t="n">
         <v>1000</v>
       </c>
       <c r="H9" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="I9" t="n">
         <v>1000</v>
       </c>
       <c r="J9" t="n">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="K9" t="n">
         <v>1000</v>
@@ -2674,7 +2674,7 @@
         <v>1.18</v>
       </c>
       <c r="S9" t="n">
-        <v>1.52</v>
+        <v>1.05</v>
       </c>
       <c r="T9" t="n">
         <v>1.11</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-18 03:58:50</t>
+          <t>2026-07-18 06:20:25</t>
         </is>
       </c>
     </row>
@@ -2889,19 +2889,19 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="G10" t="n">
         <v>1000</v>
       </c>
       <c r="H10" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="I10" t="n">
         <v>1000</v>
       </c>
       <c r="J10" t="n">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="K10" t="n">
         <v>1000</v>
@@ -2937,10 +2937,10 @@
         <v>1.11</v>
       </c>
       <c r="V10" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W10" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X10" t="n">
         <v>1000</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-18 03:58:50</t>
+          <t>2026-07-18 06:20:25</t>
         </is>
       </c>
     </row>
@@ -3143,230 +3143,230 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.27</v>
+        <v>1.57</v>
       </c>
       <c r="G11" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="H11" t="n">
-        <v>4.1</v>
+        <v>5.4</v>
       </c>
       <c r="I11" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="J11" t="n">
-        <v>3.65</v>
+        <v>4.6</v>
       </c>
       <c r="K11" t="n">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="L11" t="n">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="M11" t="n">
         <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>1.35</v>
+        <v>6</v>
       </c>
       <c r="O11" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="P11" t="n">
-        <v>1.35</v>
+        <v>2.7</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.14</v>
+        <v>1.5</v>
       </c>
       <c r="R11" t="n">
-        <v>1.27</v>
+        <v>1.69</v>
       </c>
       <c r="S11" t="n">
-        <v>1.15</v>
+        <v>2.24</v>
       </c>
       <c r="T11" t="n">
-        <v>1.11</v>
+        <v>1.63</v>
       </c>
       <c r="U11" t="n">
-        <v>1.11</v>
+        <v>2.38</v>
       </c>
       <c r="V11" t="n">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="W11" t="n">
-        <v>2.34</v>
+        <v>2.52</v>
       </c>
       <c r="X11" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="Y11" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="Z11" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AA11" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AB11" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AD11" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AE11" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AF11" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AG11" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AH11" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AI11" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AK11" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AL11" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AM11" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AN11" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="AO11" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AV11" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BA11" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BD11" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BG11" t="n">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="BH11" t="n">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="BI11" t="n">
-        <v>1.04</v>
+        <v>3.8</v>
       </c>
       <c r="BJ11" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK11" t="n">
-        <v>1.04</v>
+        <v>3.7</v>
       </c>
       <c r="BL11" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="BM11" t="n">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="BN11" t="n">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.04</v>
+        <v>3.7</v>
       </c>
       <c r="BP11" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BQ11" t="n">
-        <v>1.04</v>
+        <v>3.7</v>
       </c>
       <c r="BR11" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BS11" t="n">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BT11" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BU11" t="n">
-        <v>1.04</v>
+        <v>3.7</v>
       </c>
       <c r="BV11" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BW11" t="n">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="BX11" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BY11" t="n">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="BZ11" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="CA11" t="n">
-        <v>1.04</v>
+        <v>3.95</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-18 03:58:50</t>
+          <t>2026-07-18 06:20:25</t>
         </is>
       </c>
     </row>
@@ -3397,19 +3397,19 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="G12" t="n">
         <v>1000</v>
       </c>
       <c r="H12" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="I12" t="n">
         <v>1000</v>
       </c>
       <c r="J12" t="n">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="K12" t="n">
         <v>1000</v>
@@ -3421,7 +3421,7 @@
         <v>1.01</v>
       </c>
       <c r="N12" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O12" t="n">
         <v>1.01</v>
@@ -3430,7 +3430,7 @@
         <v>1.25</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="R12" t="n">
         <v>1.18</v>
@@ -3445,11 +3445,11 @@
         <v>1.11</v>
       </c>
       <c r="V12" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W12" t="n">
         <v>1.02</v>
       </c>
-      <c r="W12" t="n">
-        <v>1.01</v>
-      </c>
       <c r="X12" t="n">
         <v>1000</v>
       </c>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-18 03:58:50</t>
+          <t>2026-07-18 06:20:25</t>
         </is>
       </c>
     </row>
@@ -3651,19 +3651,19 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="G13" t="n">
         <v>1000</v>
       </c>
       <c r="H13" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="I13" t="n">
         <v>1000</v>
       </c>
       <c r="J13" t="n">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="K13" t="n">
         <v>1000</v>
@@ -3699,7 +3699,7 @@
         <v>1.11</v>
       </c>
       <c r="V13" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W13" t="n">
         <v>1.01</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-18 03:58:50</t>
+          <t>2026-07-18 06:20:25</t>
         </is>
       </c>
     </row>
@@ -3905,19 +3905,19 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="G14" t="n">
         <v>1000</v>
       </c>
       <c r="H14" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="I14" t="n">
         <v>1000</v>
       </c>
       <c r="J14" t="n">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="K14" t="n">
         <v>1000</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-18 03:58:50</t>
+          <t>2026-07-18 06:20:25</t>
         </is>
       </c>
     </row>
@@ -4159,19 +4159,19 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="G15" t="n">
         <v>1000</v>
       </c>
       <c r="H15" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="I15" t="n">
         <v>1000</v>
       </c>
       <c r="J15" t="n">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="K15" t="n">
         <v>1000</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-18 03:58:50</t>
+          <t>2026-07-18 06:20:25</t>
         </is>
       </c>
     </row>
@@ -4425,7 +4425,7 @@
         <v>1000</v>
       </c>
       <c r="J16" t="n">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="K16" t="n">
         <v>1000</v>
@@ -4446,13 +4446,13 @@
         <v>1.25</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="R16" t="n">
         <v>1.18</v>
       </c>
       <c r="S16" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="T16" t="n">
         <v>1.11</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-18 03:58:50</t>
+          <t>2026-07-18 06:20:25</t>
         </is>
       </c>
     </row>
@@ -4667,166 +4667,166 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.54</v>
+        <v>1.85</v>
       </c>
       <c r="G17" t="n">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="H17" t="n">
-        <v>1.99</v>
+        <v>4</v>
       </c>
       <c r="I17" t="n">
-        <v>110</v>
+        <v>4.6</v>
       </c>
       <c r="J17" t="n">
-        <v>3.15</v>
+        <v>3.95</v>
       </c>
       <c r="K17" t="n">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="L17" t="n">
         <v>1.37</v>
       </c>
       <c r="M17" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N17" t="n">
-        <v>2.32</v>
+        <v>4.4</v>
       </c>
       <c r="O17" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="P17" t="n">
-        <v>1.26</v>
+        <v>2.14</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.23</v>
+        <v>1.7</v>
       </c>
       <c r="R17" t="n">
-        <v>1.25</v>
+        <v>1.45</v>
       </c>
       <c r="S17" t="n">
-        <v>1.05</v>
+        <v>2.74</v>
       </c>
       <c r="T17" t="n">
-        <v>1.11</v>
+        <v>1.66</v>
       </c>
       <c r="U17" t="n">
-        <v>1.11</v>
+        <v>2.24</v>
       </c>
       <c r="V17" t="n">
         <v>1.29</v>
       </c>
       <c r="W17" t="n">
-        <v>1.92</v>
+        <v>2.02</v>
       </c>
       <c r="X17" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="Y17" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="Z17" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AA17" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AB17" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AC17" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD17" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AE17" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AF17" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AG17" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AH17" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AI17" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AK17" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AL17" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AM17" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AN17" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AO17" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AS17" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AV17" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ17" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BA17" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="BD17" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BG17" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BH17" t="n">
         <v>1000</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-18 03:58:50</t>
+          <t>2026-07-18 06:20:25</t>
         </is>
       </c>
     </row>
@@ -4921,230 +4921,230 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="G18" t="n">
-        <v>1000</v>
+        <v>2.98</v>
       </c>
       <c r="H18" t="n">
-        <v>1.45</v>
+        <v>2.38</v>
       </c>
       <c r="I18" t="n">
-        <v>2.92</v>
+        <v>2.78</v>
       </c>
       <c r="J18" t="n">
         <v>3.3</v>
       </c>
       <c r="K18" t="n">
-        <v>500</v>
+        <v>38</v>
       </c>
       <c r="L18" t="n">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="M18" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N18" t="n">
-        <v>1.47</v>
+        <v>3.75</v>
       </c>
       <c r="O18" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P18" t="n">
-        <v>1.25</v>
+        <v>2.12</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.23</v>
+        <v>1.72</v>
       </c>
       <c r="R18" t="n">
-        <v>1.25</v>
+        <v>1.45</v>
       </c>
       <c r="S18" t="n">
-        <v>2.24</v>
+        <v>2.84</v>
       </c>
       <c r="T18" t="n">
-        <v>1.11</v>
+        <v>1.52</v>
       </c>
       <c r="U18" t="n">
-        <v>1.11</v>
+        <v>2.32</v>
       </c>
       <c r="V18" t="n">
         <v>1.58</v>
       </c>
       <c r="W18" t="n">
-        <v>1.04</v>
+        <v>1.5</v>
       </c>
       <c r="X18" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="Y18" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Z18" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AA18" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AB18" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AC18" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD18" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AE18" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AF18" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AG18" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH18" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AI18" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AK18" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AL18" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AM18" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AN18" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AO18" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AS18" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="AT18" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AU18" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AV18" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AW18" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="AX18" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="AY18" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AZ18" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BA18" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.01</v>
+        <v>34</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BD18" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BG18" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BH18" t="n">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="BI18" t="n">
-        <v>1.04</v>
+        <v>3.05</v>
       </c>
       <c r="BJ18" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK18" t="n">
-        <v>1.04</v>
+        <v>3.2</v>
       </c>
       <c r="BL18" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="BM18" t="n">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BN18" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="BP18" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BQ18" t="n">
-        <v>1.04</v>
+        <v>3.95</v>
       </c>
       <c r="BR18" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BS18" t="n">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="BT18" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BU18" t="n">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="BV18" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BW18" t="n">
-        <v>1.04</v>
+        <v>3.85</v>
       </c>
       <c r="BX18" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BY18" t="n">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="BZ18" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="CA18" t="n">
-        <v>1.04</v>
+        <v>3.95</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-18 03:58:50</t>
+          <t>2026-07-18 06:20:25</t>
         </is>
       </c>
     </row>
@@ -5175,145 +5175,145 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.49</v>
+        <v>2.86</v>
       </c>
       <c r="G19" t="n">
-        <v>1000</v>
+        <v>3.3</v>
       </c>
       <c r="H19" t="n">
-        <v>1.49</v>
+        <v>2.76</v>
       </c>
       <c r="I19" t="n">
-        <v>1000</v>
+        <v>3.15</v>
       </c>
       <c r="J19" t="n">
-        <v>1.08</v>
+        <v>2.92</v>
       </c>
       <c r="K19" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="L19" t="n">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="M19" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="N19" t="n">
-        <v>1.25</v>
+        <v>2.52</v>
       </c>
       <c r="O19" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="P19" t="n">
-        <v>1.25</v>
+        <v>1.51</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.5</v>
+        <v>2.6</v>
       </c>
       <c r="R19" t="n">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="S19" t="n">
-        <v>1.5</v>
+        <v>5.2</v>
       </c>
       <c r="T19" t="n">
-        <v>1.72</v>
+        <v>2.06</v>
       </c>
       <c r="U19" t="n">
-        <v>1.41</v>
+        <v>1.78</v>
       </c>
       <c r="V19" t="n">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="W19" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="X19" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y19" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z19" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AA19" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AB19" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AC19" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="AD19" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AE19" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AF19" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AG19" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AH19" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AI19" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AK19" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AL19" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AM19" t="n">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AN19" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AO19" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AR19" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AS19" t="n">
         <v>1.01</v>
       </c>
       <c r="AT19" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AU19" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="AV19" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AW19" t="n">
         <v>1.01</v>
       </c>
       <c r="AX19" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AY19" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AZ19" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BA19" t="n">
         <v>1.01</v>
@@ -5337,58 +5337,58 @@
         <v>1.01</v>
       </c>
       <c r="BH19" t="n">
-        <v>1000</v>
+        <v>2.96</v>
       </c>
       <c r="BI19" t="n">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="BJ19" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BK19" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BL19" t="n">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="BM19" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BN19" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BP19" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BQ19" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BR19" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BS19" t="n">
-        <v>1.01</v>
+        <v>38</v>
       </c>
       <c r="BT19" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BU19" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BV19" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BW19" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BX19" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BY19" t="n">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="BZ19" t="n">
         <v>0</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-18 03:58:50</t>
+          <t>2026-07-18 06:20:25</t>
         </is>
       </c>
     </row>
@@ -5429,220 +5429,220 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="G20" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="H20" t="n">
-        <v>1.09</v>
+        <v>1.53</v>
       </c>
       <c r="I20" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="J20" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="K20" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N20" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2</v>
+      </c>
+      <c r="V20" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X20" t="n">
+        <v>26</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>16</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>18</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>34</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>100</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>8</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>17</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>8</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>19</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>21</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BH20" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BI20" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BJ20" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BK20" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BL20" t="n">
+        <v>120</v>
+      </c>
+      <c r="BM20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN20" t="n">
+        <v>11</v>
+      </c>
+      <c r="BO20" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BP20" t="n">
+        <v>55</v>
+      </c>
+      <c r="BQ20" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BR20" t="n">
+        <v>55</v>
+      </c>
+      <c r="BS20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT20" t="n">
+        <v>5</v>
+      </c>
+      <c r="BU20" t="n">
         <v>3.55</v>
       </c>
-      <c r="J20" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="K20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N20" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="O20" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="P20" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="S20" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="T20" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BD20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BE20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BJ20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BP20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BR20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BT20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU20" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BV20" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BW20" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BX20" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BY20" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BZ20" t="n">
         <v>0</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-18 03:58:50</t>
+          <t>2026-07-18 06:20:25</t>
         </is>
       </c>
     </row>
@@ -5707,13 +5707,13 @@
         <v>1.02</v>
       </c>
       <c r="N21" t="n">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="O21" t="n">
         <v>1.11</v>
       </c>
       <c r="P21" t="n">
-        <v>1.25</v>
+        <v>1.7</v>
       </c>
       <c r="Q21" t="n">
         <v>1.11</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-07-18 03:58:50</t>
+          <t>2026-07-18 06:20:25</t>
         </is>
       </c>
     </row>
@@ -5961,22 +5961,22 @@
         <v>1.02</v>
       </c>
       <c r="N22" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="O22" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="P22" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="R22" t="n">
         <v>1.07</v>
       </c>
       <c r="S22" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="T22" t="n">
         <v>1.11</v>
@@ -5985,10 +5985,10 @@
         <v>1.11</v>
       </c>
       <c r="V22" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="W22" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X22" t="n">
         <v>1000</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-07-18 03:58:50</t>
+          <t>2026-07-18 06:20:25</t>
         </is>
       </c>
     </row>
@@ -6194,227 +6194,227 @@
         <v>2.08</v>
       </c>
       <c r="G23" t="n">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="H23" t="n">
-        <v>1.49</v>
+        <v>3.8</v>
       </c>
       <c r="I23" t="n">
-        <v>990</v>
+        <v>4.3</v>
       </c>
       <c r="J23" t="n">
-        <v>1.85</v>
+        <v>3.55</v>
       </c>
       <c r="K23" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L23" t="n">
-        <v>1.15</v>
+        <v>1.4</v>
       </c>
       <c r="M23" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N23" t="n">
-        <v>1.1</v>
+        <v>3.6</v>
       </c>
       <c r="O23" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="P23" t="n">
-        <v>1.25</v>
+        <v>1.9</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.3</v>
+        <v>1.95</v>
       </c>
       <c r="R23" t="n">
-        <v>1.15</v>
+        <v>1.36</v>
       </c>
       <c r="S23" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="V23" t="n">
         <v>1.31</v>
       </c>
-      <c r="T23" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.29</v>
-      </c>
       <c r="W23" t="n">
-        <v>1.78</v>
+        <v>1.84</v>
       </c>
       <c r="X23" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>30</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>100</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AE23" t="n">
         <v>50</v>
       </c>
-      <c r="Y23" t="n">
-        <v>42</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>48</v>
-      </c>
-      <c r="AA23" t="n">
+      <c r="AF23" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>18</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>26</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>23</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM23" t="n">
         <v>120</v>
       </c>
-      <c r="AB23" t="n">
-        <v>29</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>21</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>80</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>26</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>14</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>28</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>100</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>36</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>34</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>200</v>
-      </c>
       <c r="AN23" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="AO23" t="n">
-        <v>110</v>
+        <v>55</v>
       </c>
       <c r="AP23" t="n">
-        <v>4.4</v>
+        <v>12.5</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.93</v>
+        <v>13</v>
       </c>
       <c r="AR23" t="n">
         <v>22</v>
       </c>
       <c r="AS23" t="n">
-        <v>1.99</v>
+        <v>12.5</v>
       </c>
       <c r="AT23" t="n">
-        <v>4.4</v>
+        <v>8.6</v>
       </c>
       <c r="AU23" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="AV23" t="n">
         <v>14</v>
       </c>
       <c r="AW23" t="n">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="AX23" t="n">
-        <v>9.6</v>
+        <v>11.5</v>
       </c>
       <c r="AY23" t="n">
-        <v>1.77</v>
+        <v>6.2</v>
       </c>
       <c r="AZ23" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="BA23" t="n">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="BB23" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BC23" t="n">
-        <v>13</v>
+        <v>19.5</v>
       </c>
       <c r="BD23" t="n">
-        <v>15.5</v>
+        <v>32</v>
       </c>
       <c r="BE23" t="n">
-        <v>30</v>
+        <v>11.5</v>
       </c>
       <c r="BF23" t="n">
-        <v>5</v>
+        <v>13.5</v>
       </c>
       <c r="BG23" t="n">
-        <v>9.6</v>
+        <v>32</v>
       </c>
       <c r="BH23" t="n">
-        <v>1000</v>
+        <v>3.85</v>
       </c>
       <c r="BI23" t="n">
-        <v>1.01</v>
+        <v>2.84</v>
       </c>
       <c r="BJ23" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK23" t="n">
         <v>1.01</v>
       </c>
       <c r="BL23" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="BM23" t="n">
         <v>1.01</v>
       </c>
       <c r="BN23" t="n">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="BO23" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BP23" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="BQ23" t="n">
         <v>1.01</v>
       </c>
       <c r="BR23" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BS23" t="n">
         <v>1.01</v>
       </c>
       <c r="BT23" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="BU23" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BV23" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BW23" t="n">
         <v>1.01</v>
       </c>
       <c r="BX23" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BY23" t="n">
         <v>1.01</v>
       </c>
       <c r="BZ23" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="CA23" t="n">
         <v>1.01</v>
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-07-18 03:58:50</t>
+          <t>2026-07-18 06:20:25</t>
         </is>
       </c>
     </row>
@@ -6445,121 +6445,121 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="G24" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="H24" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I24" t="n">
         <v>13.5</v>
       </c>
       <c r="J24" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="K24" t="n">
         <v>6.8</v>
       </c>
       <c r="L24" t="n">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="M24" t="n">
         <v>1.03</v>
       </c>
       <c r="N24" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="O24" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="P24" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="R24" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="S24" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="T24" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="U24" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="V24" t="n">
         <v>1.08</v>
       </c>
       <c r="W24" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="X24" t="n">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="Y24" t="n">
-        <v>85</v>
+        <v>46</v>
       </c>
       <c r="Z24" t="n">
         <v>1000</v>
       </c>
       <c r="AA24" t="n">
-        <v>1000</v>
+        <v>570</v>
       </c>
       <c r="AB24" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AC24" t="n">
         <v>15.5</v>
       </c>
       <c r="AD24" t="n">
-        <v>95</v>
+        <v>46</v>
       </c>
       <c r="AE24" t="n">
         <v>1000</v>
       </c>
       <c r="AF24" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AG24" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH24" t="n">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="AI24" t="n">
         <v>1000</v>
       </c>
       <c r="AJ24" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AK24" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AL24" t="n">
-        <v>80</v>
+        <v>38</v>
       </c>
       <c r="AM24" t="n">
         <v>1000</v>
       </c>
       <c r="AN24" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="AO24" t="n">
         <v>1000</v>
       </c>
       <c r="AP24" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AQ24" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="AR24" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AS24" t="n">
         <v>55</v>
@@ -6568,13 +6568,13 @@
         <v>9.4</v>
       </c>
       <c r="AU24" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AV24" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="AW24" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AX24" t="n">
         <v>7.4</v>
@@ -6583,92 +6583,92 @@
         <v>9.6</v>
       </c>
       <c r="AZ24" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BA24" t="n">
         <v>42</v>
       </c>
       <c r="BB24" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BC24" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BD24" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="BE24" t="n">
         <v>44</v>
       </c>
       <c r="BF24" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="BG24" t="n">
         <v>48</v>
       </c>
       <c r="BH24" t="n">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="BI24" t="n">
-        <v>1.04</v>
+        <v>3.65</v>
       </c>
       <c r="BJ24" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="BK24" t="n">
-        <v>1.04</v>
+        <v>9.6</v>
       </c>
       <c r="BL24" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="BM24" t="n">
         <v>1.04</v>
       </c>
       <c r="BN24" t="n">
-        <v>1000</v>
+        <v>4</v>
       </c>
       <c r="BO24" t="n">
-        <v>1.04</v>
+        <v>3.35</v>
       </c>
       <c r="BP24" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="BQ24" t="n">
-        <v>1.04</v>
+        <v>5.5</v>
       </c>
       <c r="BR24" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BS24" t="n">
         <v>1.04</v>
       </c>
       <c r="BT24" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="BU24" t="n">
         <v>1.04</v>
       </c>
       <c r="BV24" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="BW24" t="n">
         <v>1.04</v>
       </c>
       <c r="BX24" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="BY24" t="n">
         <v>1.04</v>
       </c>
       <c r="BZ24" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="CA24" t="n">
-        <v>1.04</v>
+        <v>7.8</v>
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-07-18 03:58:50</t>
+          <t>2026-07-18 06:20:25</t>
         </is>
       </c>
     </row>
@@ -6699,7 +6699,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="G25" t="n">
         <v>5.8</v>
@@ -6726,13 +6726,13 @@
         <v>6</v>
       </c>
       <c r="O25" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="P25" t="n">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="R25" t="n">
         <v>1.66</v>
@@ -6756,7 +6756,7 @@
         <v>27</v>
       </c>
       <c r="Y25" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Z25" t="n">
         <v>12</v>
@@ -6765,13 +6765,13 @@
         <v>17</v>
       </c>
       <c r="AB25" t="n">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="AC25" t="n">
         <v>11.5</v>
       </c>
       <c r="AD25" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AE25" t="n">
         <v>15</v>
@@ -6783,58 +6783,58 @@
         <v>22</v>
       </c>
       <c r="AH25" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AI25" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="AJ25" t="n">
         <v>160</v>
       </c>
       <c r="AK25" t="n">
-        <v>65</v>
+        <v>680</v>
       </c>
       <c r="AL25" t="n">
-        <v>60</v>
+        <v>330</v>
       </c>
       <c r="AM25" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AN25" t="n">
         <v>50</v>
       </c>
       <c r="AO25" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AP25" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ25" t="n">
         <v>11</v>
       </c>
       <c r="AR25" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AS25" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AT25" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AU25" t="n">
         <v>10</v>
       </c>
       <c r="AV25" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW25" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AX25" t="n">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="AY25" t="n">
-        <v>15.5</v>
+        <v>19.5</v>
       </c>
       <c r="AZ25" t="n">
         <v>16</v>
@@ -6846,10 +6846,10 @@
         <v>42</v>
       </c>
       <c r="BC25" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="BD25" t="n">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="BE25" t="n">
         <v>32</v>
@@ -6858,71 +6858,71 @@
         <v>38</v>
       </c>
       <c r="BG25" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BH25" t="n">
         <v>1000</v>
       </c>
       <c r="BI25" t="n">
-        <v>1.04</v>
+        <v>2</v>
       </c>
       <c r="BJ25" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BK25" t="n">
-        <v>1.04</v>
+        <v>1.74</v>
       </c>
       <c r="BL25" t="n">
         <v>1000</v>
       </c>
       <c r="BM25" t="n">
-        <v>1.04</v>
+        <v>2</v>
       </c>
       <c r="BN25" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BO25" t="n">
-        <v>1.04</v>
+        <v>1.75</v>
       </c>
       <c r="BP25" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BQ25" t="n">
-        <v>1.04</v>
+        <v>1.94</v>
       </c>
       <c r="BR25" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BS25" t="n">
-        <v>1.04</v>
+        <v>1.94</v>
       </c>
       <c r="BT25" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BU25" t="n">
-        <v>1.04</v>
+        <v>3.25</v>
       </c>
       <c r="BV25" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BW25" t="n">
-        <v>1.04</v>
+        <v>1.76</v>
       </c>
       <c r="BX25" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BY25" t="n">
-        <v>1.04</v>
+        <v>1.88</v>
       </c>
       <c r="BZ25" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="CA25" t="n">
-        <v>1.04</v>
+        <v>1.81</v>
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-07-18 03:58:50</t>
+          <t>2026-07-18 06:20:25</t>
         </is>
       </c>
     </row>
@@ -6956,7 +6956,7 @@
         <v>3.7</v>
       </c>
       <c r="G26" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="H26" t="n">
         <v>2.06</v>
@@ -6971,16 +6971,16 @@
         <v>4.1</v>
       </c>
       <c r="L26" t="n">
-        <v>1.03</v>
+        <v>1.33</v>
       </c>
       <c r="M26" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N26" t="n">
         <v>4.8</v>
       </c>
       <c r="O26" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P26" t="n">
         <v>2.3</v>
@@ -6989,16 +6989,16 @@
         <v>1.7</v>
       </c>
       <c r="R26" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="S26" t="n">
-        <v>2.58</v>
+        <v>2.78</v>
       </c>
       <c r="T26" t="n">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="U26" t="n">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="V26" t="n">
         <v>1.92</v>
@@ -7007,112 +7007,112 @@
         <v>1.35</v>
       </c>
       <c r="X26" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="Y26" t="n">
-        <v>26</v>
+        <v>12.5</v>
       </c>
       <c r="Z26" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AA26" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AB26" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AC26" t="n">
-        <v>970</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD26" t="n">
-        <v>970</v>
+        <v>11</v>
       </c>
       <c r="AE26" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AF26" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AG26" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AH26" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AI26" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AK26" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AL26" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AM26" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AN26" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AO26" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="AP26" t="n">
-        <v>1.25</v>
+        <v>17</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1.19</v>
+        <v>10.5</v>
       </c>
       <c r="AR26" t="n">
-        <v>1.25</v>
+        <v>13</v>
       </c>
       <c r="AS26" t="n">
-        <v>1.25</v>
+        <v>21</v>
       </c>
       <c r="AT26" t="n">
-        <v>1.25</v>
+        <v>15</v>
       </c>
       <c r="AU26" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BB26" t="n">
         <v>6.4</v>
       </c>
-      <c r="AV26" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AY26" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AZ26" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BA26" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BB26" t="n">
-        <v>1.25</v>
-      </c>
       <c r="BC26" t="n">
-        <v>1.25</v>
+        <v>6</v>
       </c>
       <c r="BD26" t="n">
-        <v>1.25</v>
+        <v>6.2</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.25</v>
+        <v>6.4</v>
       </c>
       <c r="BF26" t="n">
-        <v>1.25</v>
+        <v>5.9</v>
       </c>
       <c r="BG26" t="n">
-        <v>1.19</v>
+        <v>10</v>
       </c>
       <c r="BH26" t="n">
         <v>1000</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-07-18 03:58:50</t>
+          <t>2026-07-18 06:20:25</t>
         </is>
       </c>
     </row>
@@ -7231,19 +7231,19 @@
         <v>1.01</v>
       </c>
       <c r="N27" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="O27" t="n">
         <v>1.15</v>
       </c>
       <c r="P27" t="n">
-        <v>1.27</v>
+        <v>2.16</v>
       </c>
       <c r="Q27" t="n">
         <v>1.15</v>
       </c>
       <c r="R27" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S27" t="n">
         <v>1.14</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-07-18 03:58:50</t>
+          <t>2026-07-18 06:20:25</t>
         </is>
       </c>
     </row>
@@ -7470,7 +7470,7 @@
         <v>1.58</v>
       </c>
       <c r="I28" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="J28" t="n">
         <v>4.4</v>
@@ -7485,31 +7485,31 @@
         <v>1.05</v>
       </c>
       <c r="N28" t="n">
-        <v>3.85</v>
+        <v>4.4</v>
       </c>
       <c r="O28" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P28" t="n">
-        <v>2.06</v>
+        <v>2.18</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="R28" t="n">
         <v>1.42</v>
       </c>
       <c r="S28" t="n">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="T28" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="U28" t="n">
-        <v>1.95</v>
+        <v>2.06</v>
       </c>
       <c r="V28" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="W28" t="n">
         <v>1.17</v>
@@ -7518,7 +7518,7 @@
         <v>1000</v>
       </c>
       <c r="Y28" t="n">
-        <v>970</v>
+        <v>11</v>
       </c>
       <c r="Z28" t="n">
         <v>970</v>
@@ -7533,13 +7533,13 @@
         <v>970</v>
       </c>
       <c r="AD28" t="n">
-        <v>970</v>
+        <v>12</v>
       </c>
       <c r="AE28" t="n">
         <v>1000</v>
       </c>
       <c r="AF28" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AG28" t="n">
         <v>1000</v>
@@ -7548,7 +7548,7 @@
         <v>1000</v>
       </c>
       <c r="AI28" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AJ28" t="n">
         <v>1000</v>
@@ -7566,61 +7566,61 @@
         <v>1000</v>
       </c>
       <c r="AO28" t="n">
-        <v>970</v>
+        <v>9</v>
       </c>
       <c r="AP28" t="n">
-        <v>1.5</v>
+        <v>1.83</v>
       </c>
       <c r="AQ28" t="n">
-        <v>1.36</v>
+        <v>1.56</v>
       </c>
       <c r="AR28" t="n">
-        <v>1.37</v>
+        <v>7.8</v>
       </c>
       <c r="AS28" t="n">
-        <v>1.5</v>
+        <v>1.83</v>
       </c>
       <c r="AT28" t="n">
-        <v>1.5</v>
+        <v>1.83</v>
       </c>
       <c r="AU28" t="n">
-        <v>1.37</v>
+        <v>1.65</v>
       </c>
       <c r="AV28" t="n">
-        <v>1.37</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW28" t="n">
-        <v>1.5</v>
+        <v>1.83</v>
       </c>
       <c r="AX28" t="n">
-        <v>1.5</v>
+        <v>1.78</v>
       </c>
       <c r="AY28" t="n">
-        <v>1.5</v>
+        <v>1.83</v>
       </c>
       <c r="AZ28" t="n">
-        <v>1.5</v>
+        <v>1.83</v>
       </c>
       <c r="BA28" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="BB28" t="n">
-        <v>1.5</v>
+        <v>1.83</v>
       </c>
       <c r="BC28" t="n">
-        <v>1.5</v>
+        <v>1.83</v>
       </c>
       <c r="BD28" t="n">
-        <v>1.5</v>
+        <v>1.83</v>
       </c>
       <c r="BE28" t="n">
-        <v>1.5</v>
+        <v>1.83</v>
       </c>
       <c r="BF28" t="n">
-        <v>1.5</v>
+        <v>1.83</v>
       </c>
       <c r="BG28" t="n">
-        <v>1.32</v>
+        <v>1.51</v>
       </c>
       <c r="BH28" t="n">
         <v>1000</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-07-18 03:58:50</t>
+          <t>2026-07-18 06:20:25</t>
         </is>
       </c>
     </row>
@@ -7715,22 +7715,22 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.04</v>
+        <v>2.74</v>
       </c>
       <c r="G29" t="n">
-        <v>1000</v>
+        <v>3.15</v>
       </c>
       <c r="H29" t="n">
-        <v>1.04</v>
+        <v>2.66</v>
       </c>
       <c r="I29" t="n">
-        <v>1000</v>
+        <v>3.25</v>
       </c>
       <c r="J29" t="n">
-        <v>1.08</v>
+        <v>2.82</v>
       </c>
       <c r="K29" t="n">
-        <v>1000</v>
+        <v>3.5</v>
       </c>
       <c r="L29" t="n">
         <v>1.01</v>
@@ -7739,34 +7739,34 @@
         <v>1.01</v>
       </c>
       <c r="N29" t="n">
-        <v>1.25</v>
+        <v>2.32</v>
       </c>
       <c r="O29" t="n">
         <v>1.38</v>
       </c>
       <c r="P29" t="n">
-        <v>1.25</v>
+        <v>1.67</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.38</v>
+        <v>2.06</v>
       </c>
       <c r="R29" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S29" t="n">
-        <v>1.37</v>
+        <v>3.3</v>
       </c>
       <c r="T29" t="n">
-        <v>1.11</v>
+        <v>1.63</v>
       </c>
       <c r="U29" t="n">
-        <v>1.11</v>
+        <v>1.69</v>
       </c>
       <c r="V29" t="n">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="W29" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="X29" t="n">
         <v>1000</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-07-18 03:58:50</t>
+          <t>2026-07-18 06:20:25</t>
         </is>
       </c>
     </row>
@@ -7969,230 +7969,230 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.45</v>
+        <v>5.9</v>
       </c>
       <c r="G30" t="n">
-        <v>990</v>
+        <v>6.8</v>
       </c>
       <c r="H30" t="n">
-        <v>1.45</v>
+        <v>1.74</v>
       </c>
       <c r="I30" t="n">
-        <v>110</v>
+        <v>1.83</v>
       </c>
       <c r="J30" t="n">
         <v>3.5</v>
       </c>
       <c r="K30" t="n">
-        <v>950</v>
+        <v>3.65</v>
       </c>
       <c r="L30" t="n">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="M30" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="N30" t="n">
-        <v>1.25</v>
+        <v>2.54</v>
       </c>
       <c r="O30" t="n">
-        <v>1.02</v>
+        <v>1.56</v>
       </c>
       <c r="P30" t="n">
-        <v>1.25</v>
+        <v>1.52</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.53</v>
+        <v>2.66</v>
       </c>
       <c r="R30" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="S30" t="n">
-        <v>1.53</v>
+        <v>5.5</v>
       </c>
       <c r="T30" t="n">
-        <v>1.92</v>
+        <v>2.4</v>
       </c>
       <c r="U30" t="n">
-        <v>1.29</v>
+        <v>1.62</v>
       </c>
       <c r="V30" t="n">
-        <v>1.05</v>
+        <v>2.2</v>
       </c>
       <c r="W30" t="n">
-        <v>1.05</v>
+        <v>1.17</v>
       </c>
       <c r="X30" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="Y30" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="Z30" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AA30" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AB30" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AC30" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AD30" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AE30" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AF30" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AG30" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AH30" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AI30" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AJ30" t="n">
-        <v>1000</v>
+        <v>290</v>
       </c>
       <c r="AK30" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AL30" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AM30" t="n">
-        <v>1000</v>
+        <v>360</v>
       </c>
       <c r="AN30" t="n">
-        <v>1000</v>
+        <v>340</v>
       </c>
       <c r="AO30" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AP30" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AQ30" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AR30" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AS30" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="AT30" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AU30" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AV30" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AW30" t="n">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="AX30" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AY30" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AZ30" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BA30" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BB30" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BC30" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BD30" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BE30" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BF30" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BG30" t="n">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="BH30" t="n">
-        <v>1000</v>
+        <v>3.1</v>
       </c>
       <c r="BI30" t="n">
-        <v>1.04</v>
+        <v>2.2</v>
       </c>
       <c r="BJ30" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="BK30" t="n">
         <v>1.04</v>
       </c>
       <c r="BL30" t="n">
-        <v>1000</v>
+        <v>340</v>
       </c>
       <c r="BM30" t="n">
         <v>1.04</v>
       </c>
       <c r="BN30" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BO30" t="n">
         <v>1.04</v>
       </c>
       <c r="BP30" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="BQ30" t="n">
         <v>1.04</v>
       </c>
       <c r="BR30" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="BS30" t="n">
         <v>1.04</v>
       </c>
       <c r="BT30" t="n">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="BU30" t="n">
-        <v>1.04</v>
+        <v>3.15</v>
       </c>
       <c r="BV30" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="BW30" t="n">
         <v>1.04</v>
       </c>
       <c r="BX30" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BY30" t="n">
         <v>1.04</v>
       </c>
       <c r="BZ30" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="CA30" t="n">
         <v>1.04</v>
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-07-18 03:58:50</t>
+          <t>2026-07-18 06:20:25</t>
         </is>
       </c>
     </row>
@@ -8223,230 +8223,230 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1.44</v>
+        <v>1.64</v>
       </c>
       <c r="G31" t="n">
-        <v>1.91</v>
+        <v>1.79</v>
       </c>
       <c r="H31" t="n">
-        <v>1.04</v>
+        <v>5.6</v>
       </c>
       <c r="I31" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="J31" t="n">
-        <v>2.2</v>
+        <v>3.7</v>
       </c>
       <c r="K31" t="n">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="L31" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="M31" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N31" t="n">
-        <v>2.1</v>
+        <v>3.35</v>
       </c>
       <c r="O31" t="n">
         <v>1.35</v>
       </c>
       <c r="P31" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.35</v>
+        <v>2</v>
       </c>
       <c r="R31" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="S31" t="n">
-        <v>1.36</v>
+        <v>3.7</v>
       </c>
       <c r="T31" t="n">
-        <v>1.61</v>
+        <v>1.95</v>
       </c>
       <c r="U31" t="n">
-        <v>1.45</v>
+        <v>1.84</v>
       </c>
       <c r="V31" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="W31" t="n">
-        <v>2.1</v>
+        <v>2.26</v>
       </c>
       <c r="X31" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="Y31" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Z31" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AA31" t="n">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AB31" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AC31" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD31" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AE31" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AF31" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AG31" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH31" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AI31" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AJ31" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AK31" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AL31" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AM31" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AN31" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AO31" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AP31" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ31" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AR31" t="n">
-        <v>1.01</v>
+        <v>34</v>
       </c>
       <c r="AS31" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="AT31" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AU31" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AV31" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="AW31" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="AX31" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY31" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AZ31" t="n">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BA31" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BB31" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BC31" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BD31" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BE31" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BF31" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BG31" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BH31" t="n">
-        <v>1000</v>
+        <v>3.8</v>
       </c>
       <c r="BI31" t="n">
-        <v>1.01</v>
+        <v>2.64</v>
       </c>
       <c r="BJ31" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BK31" t="n">
         <v>1.01</v>
       </c>
       <c r="BL31" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="BM31" t="n">
         <v>1.01</v>
       </c>
       <c r="BN31" t="n">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="BO31" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="BP31" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="BQ31" t="n">
         <v>1.01</v>
       </c>
       <c r="BR31" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BS31" t="n">
         <v>1.01</v>
       </c>
       <c r="BT31" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BU31" t="n">
         <v>1.01</v>
       </c>
       <c r="BV31" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="BW31" t="n">
         <v>1.01</v>
       </c>
       <c r="BX31" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="BY31" t="n">
         <v>1.01</v>
       </c>
       <c r="BZ31" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="CA31" t="n">
         <v>1.01</v>
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-07-18 03:58:50</t>
+          <t>2026-07-18 06:20:25</t>
         </is>
       </c>
     </row>
@@ -8477,58 +8477,58 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1.43</v>
+        <v>1.92</v>
       </c>
       <c r="G32" t="n">
-        <v>1000</v>
+        <v>2.16</v>
       </c>
       <c r="H32" t="n">
-        <v>1.45</v>
+        <v>3.7</v>
       </c>
       <c r="I32" t="n">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="J32" t="n">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="K32" t="n">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="L32" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="M32" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N32" t="n">
         <v>1.1</v>
       </c>
       <c r="O32" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="P32" t="n">
-        <v>1.25</v>
+        <v>2.1</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.23</v>
+        <v>1.65</v>
       </c>
       <c r="R32" t="n">
-        <v>1.18</v>
+        <v>1.35</v>
       </c>
       <c r="S32" t="n">
-        <v>1.23</v>
+        <v>2.26</v>
       </c>
       <c r="T32" t="n">
         <v>1.11</v>
       </c>
       <c r="U32" t="n">
-        <v>1.11</v>
+        <v>1.96</v>
       </c>
       <c r="V32" t="n">
-        <v>1.03</v>
+        <v>1.26</v>
       </c>
       <c r="W32" t="n">
-        <v>1.03</v>
+        <v>1.86</v>
       </c>
       <c r="X32" t="n">
         <v>1000</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-07-18 03:58:50</t>
+          <t>2026-07-18 06:20:25</t>
         </is>
       </c>
     </row>
@@ -8731,166 +8731,166 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="G33" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="H33" t="n">
-        <v>1.37</v>
+        <v>1.53</v>
       </c>
       <c r="I33" t="n">
-        <v>1000</v>
+        <v>1.66</v>
       </c>
       <c r="J33" t="n">
-        <v>1.56</v>
+        <v>4.6</v>
       </c>
       <c r="K33" t="n">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="L33" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="M33" t="n">
         <v>1.01</v>
       </c>
       <c r="N33" t="n">
-        <v>1.29</v>
+        <v>6</v>
       </c>
       <c r="O33" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="P33" t="n">
-        <v>1.29</v>
+        <v>2.7</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.14</v>
+        <v>1.48</v>
       </c>
       <c r="R33" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="S33" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="U33" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="V33" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="W33" t="n">
         <v>1.18</v>
       </c>
-      <c r="S33" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="T33" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="U33" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="V33" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="W33" t="n">
-        <v>1.02</v>
-      </c>
       <c r="X33" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="Y33" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Z33" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AA33" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AB33" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AC33" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AD33" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AE33" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AF33" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AG33" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AH33" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AI33" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AJ33" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AK33" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AL33" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM33" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AN33" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AO33" t="n">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="AP33" t="n">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="AQ33" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR33" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS33" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AT33" t="n">
-        <v>1.01</v>
+        <v>24</v>
       </c>
       <c r="AU33" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AV33" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AW33" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AX33" t="n">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="AY33" t="n">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="AZ33" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BA33" t="n">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="BB33" t="n">
-        <v>1.01</v>
+        <v>85</v>
       </c>
       <c r="BC33" t="n">
-        <v>1.01</v>
+        <v>42</v>
       </c>
       <c r="BD33" t="n">
-        <v>1.01</v>
+        <v>38</v>
       </c>
       <c r="BE33" t="n">
-        <v>1.01</v>
+        <v>48</v>
       </c>
       <c r="BF33" t="n">
-        <v>1.01</v>
+        <v>34</v>
       </c>
       <c r="BG33" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BH33" t="n">
         <v>1000</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-07-18 03:58:50</t>
+          <t>2026-07-18 06:20:25</t>
         </is>
       </c>
     </row>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-07-18 03:58:50</t>
+          <t>2026-07-18 06:20:25</t>
         </is>
       </c>
     </row>
@@ -9239,61 +9239,61 @@
         </is>
       </c>
       <c r="F35" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="G35" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H35" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="I35" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="J35" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="K35" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L35" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="M35" t="n">
         <v>1.04</v>
       </c>
-      <c r="G35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H35" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="I35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J35" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="K35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L35" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M35" t="n">
-        <v>1.01</v>
-      </c>
       <c r="N35" t="n">
-        <v>1.32</v>
+        <v>4.4</v>
       </c>
       <c r="O35" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="P35" t="n">
-        <v>1.32</v>
+        <v>2.24</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.18</v>
+        <v>1.57</v>
       </c>
       <c r="R35" t="n">
-        <v>1.18</v>
+        <v>1.52</v>
       </c>
       <c r="S35" t="n">
-        <v>1.18</v>
+        <v>2.56</v>
       </c>
       <c r="T35" t="n">
-        <v>1.11</v>
+        <v>1.58</v>
       </c>
       <c r="U35" t="n">
-        <v>1.11</v>
+        <v>2.1</v>
       </c>
       <c r="V35" t="n">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="W35" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="X35" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="Y35" t="n">
         <v>1000</v>
@@ -9305,19 +9305,19 @@
         <v>1000</v>
       </c>
       <c r="AB35" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AC35" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AD35" t="n">
         <v>1000</v>
       </c>
       <c r="AE35" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AF35" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AG35" t="n">
         <v>1000</v>
@@ -9329,13 +9329,13 @@
         <v>1000</v>
       </c>
       <c r="AJ35" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AK35" t="n">
         <v>1000</v>
       </c>
       <c r="AL35" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM35" t="n">
         <v>1000</v>
@@ -9344,13 +9344,13 @@
         <v>1000</v>
       </c>
       <c r="AO35" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AP35" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="AQ35" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AR35" t="n">
         <v>1.01</v>
@@ -9359,19 +9359,19 @@
         <v>1.01</v>
       </c>
       <c r="AT35" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AU35" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AV35" t="n">
         <v>1.01</v>
       </c>
       <c r="AW35" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AX35" t="n">
-        <v>1.01</v>
+        <v>28</v>
       </c>
       <c r="AY35" t="n">
         <v>1.01</v>
@@ -9398,58 +9398,58 @@
         <v>1.01</v>
       </c>
       <c r="BG35" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BH35" t="n">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="BI35" t="n">
         <v>1.04</v>
       </c>
       <c r="BJ35" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK35" t="n">
         <v>1.04</v>
       </c>
       <c r="BL35" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="BM35" t="n">
         <v>1.04</v>
       </c>
       <c r="BN35" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="BO35" t="n">
         <v>1.04</v>
       </c>
       <c r="BP35" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BQ35" t="n">
         <v>1.04</v>
       </c>
       <c r="BR35" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BS35" t="n">
         <v>1.04</v>
       </c>
       <c r="BT35" t="n">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="BU35" t="n">
         <v>1.04</v>
       </c>
       <c r="BV35" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BW35" t="n">
         <v>1.04</v>
       </c>
       <c r="BX35" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BY35" t="n">
         <v>1.04</v>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-07-18 03:58:50</t>
+          <t>2026-07-18 06:20:25</t>
         </is>
       </c>
     </row>
@@ -9520,19 +9520,19 @@
         <v>1.25</v>
       </c>
       <c r="O36" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="P36" t="n">
         <v>1.25</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="R36" t="n">
         <v>1.07</v>
       </c>
       <c r="S36" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="T36" t="n">
         <v>1.11</v>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-07-18 03:58:50</t>
+          <t>2026-07-18 06:20:25</t>
         </is>
       </c>
     </row>
@@ -9747,64 +9747,64 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>1.56</v>
+        <v>2.88</v>
       </c>
       <c r="G37" t="n">
-        <v>1000</v>
+        <v>3.2</v>
       </c>
       <c r="H37" t="n">
-        <v>1.57</v>
+        <v>2.98</v>
       </c>
       <c r="I37" t="n">
-        <v>1000</v>
+        <v>3.3</v>
       </c>
       <c r="J37" t="n">
-        <v>1.16</v>
+        <v>2.6</v>
       </c>
       <c r="K37" t="n">
         <v>3.2</v>
       </c>
       <c r="L37" t="n">
-        <v>1.01</v>
+        <v>1.54</v>
       </c>
       <c r="M37" t="n">
         <v>1.01</v>
       </c>
       <c r="N37" t="n">
-        <v>1.4</v>
+        <v>2.46</v>
       </c>
       <c r="O37" t="n">
         <v>1.53</v>
       </c>
       <c r="P37" t="n">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.53</v>
+        <v>2.7</v>
       </c>
       <c r="R37" t="n">
         <v>1.18</v>
       </c>
       <c r="S37" t="n">
-        <v>1.53</v>
+        <v>5.5</v>
       </c>
       <c r="T37" t="n">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="U37" t="n">
         <v>1.38</v>
       </c>
       <c r="V37" t="n">
-        <v>1.02</v>
+        <v>1.43</v>
       </c>
       <c r="W37" t="n">
-        <v>1.03</v>
+        <v>1.46</v>
       </c>
       <c r="X37" t="n">
         <v>1000</v>
       </c>
       <c r="Y37" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="Z37" t="n">
         <v>1000</v>
@@ -9831,7 +9831,7 @@
         <v>1000</v>
       </c>
       <c r="AH37" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI37" t="n">
         <v>1000</v>
@@ -9849,91 +9849,91 @@
         <v>1000</v>
       </c>
       <c r="AN37" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AO37" t="n">
         <v>1000</v>
       </c>
       <c r="AP37" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AQ37" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AR37" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="AS37" t="n">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="AT37" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AU37" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AV37" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AW37" t="n">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="AX37" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="AY37" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AZ37" t="n">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BA37" t="n">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="BB37" t="n">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="BC37" t="n">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="BD37" t="n">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="BE37" t="n">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="BF37" t="n">
-        <v>1.01</v>
+        <v>40</v>
       </c>
       <c r="BG37" t="n">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="BH37" t="n">
         <v>1000</v>
       </c>
       <c r="BI37" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="BJ37" t="n">
         <v>1000</v>
       </c>
       <c r="BK37" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="BL37" t="n">
         <v>1000</v>
       </c>
       <c r="BM37" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="BN37" t="n">
         <v>1000</v>
       </c>
       <c r="BO37" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="BP37" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BQ37" t="n">
         <v>1.04</v>
@@ -9942,16 +9942,16 @@
         <v>1000</v>
       </c>
       <c r="BS37" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="BT37" t="n">
         <v>1000</v>
       </c>
       <c r="BU37" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="BV37" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BW37" t="n">
         <v>1.04</v>
@@ -9960,17 +9960,17 @@
         <v>1000</v>
       </c>
       <c r="BY37" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="BZ37" t="n">
         <v>1000</v>
       </c>
       <c r="CA37" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-07-18 03:58:50</t>
+          <t>2026-07-18 06:20:25</t>
         </is>
       </c>
     </row>
@@ -10001,22 +10001,22 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>1.88</v>
+        <v>3.9</v>
       </c>
       <c r="G38" t="n">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="H38" t="n">
-        <v>1.75</v>
+        <v>2.08</v>
       </c>
       <c r="I38" t="n">
         <v>2.18</v>
       </c>
       <c r="J38" t="n">
-        <v>1.88</v>
+        <v>3.15</v>
       </c>
       <c r="K38" t="n">
-        <v>1000</v>
+        <v>3.8</v>
       </c>
       <c r="L38" t="n">
         <v>1.01</v>
@@ -10025,40 +10025,40 @@
         <v>1.08</v>
       </c>
       <c r="N38" t="n">
-        <v>1.35</v>
+        <v>2.98</v>
       </c>
       <c r="O38" t="n">
         <v>1.43</v>
       </c>
       <c r="P38" t="n">
-        <v>1.34</v>
+        <v>1.67</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.43</v>
+        <v>2.22</v>
       </c>
       <c r="R38" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="S38" t="n">
-        <v>1.42</v>
+        <v>4.3</v>
       </c>
       <c r="T38" t="n">
-        <v>1.11</v>
+        <v>1.92</v>
       </c>
       <c r="U38" t="n">
-        <v>1.11</v>
+        <v>1.88</v>
       </c>
       <c r="V38" t="n">
         <v>1.84</v>
       </c>
       <c r="W38" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="X38" t="n">
         <v>1000</v>
       </c>
       <c r="Y38" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="Z38" t="n">
         <v>1000</v>
@@ -10070,7 +10070,7 @@
         <v>1000</v>
       </c>
       <c r="AC38" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AD38" t="n">
         <v>1000</v>
@@ -10094,7 +10094,7 @@
         <v>1000</v>
       </c>
       <c r="AK38" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AL38" t="n">
         <v>1000</v>
@@ -10109,58 +10109,58 @@
         <v>1000</v>
       </c>
       <c r="AP38" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AQ38" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AR38" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AS38" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="AT38" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AU38" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AV38" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AW38" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="AX38" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="AY38" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AZ38" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BA38" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="BB38" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="BC38" t="n">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="BD38" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="BE38" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="BF38" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="BG38" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BH38" t="n">
         <v>1000</v>
@@ -10181,10 +10181,10 @@
         <v>1.04</v>
       </c>
       <c r="BN38" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BO38" t="n">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="BP38" t="n">
         <v>1000</v>
@@ -10199,10 +10199,10 @@
         <v>1.04</v>
       </c>
       <c r="BT38" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BU38" t="n">
-        <v>1.04</v>
+        <v>3.3</v>
       </c>
       <c r="BV38" t="n">
         <v>1000</v>
@@ -10217,14 +10217,14 @@
         <v>1.04</v>
       </c>
       <c r="BZ38" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="CA38" t="n">
         <v>1.04</v>
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-07-18 03:58:50</t>
+          <t>2026-07-18 06:20:25</t>
         </is>
       </c>
     </row>
@@ -10255,22 +10255,22 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>1.04</v>
+        <v>3.3</v>
       </c>
       <c r="G39" t="n">
-        <v>1000</v>
+        <v>3.85</v>
       </c>
       <c r="H39" t="n">
-        <v>1.55</v>
+        <v>2.32</v>
       </c>
       <c r="I39" t="n">
-        <v>1000</v>
+        <v>2.58</v>
       </c>
       <c r="J39" t="n">
-        <v>1.14</v>
+        <v>2.84</v>
       </c>
       <c r="K39" t="n">
-        <v>1000</v>
+        <v>3.5</v>
       </c>
       <c r="L39" t="n">
         <v>1.01</v>
@@ -10279,34 +10279,34 @@
         <v>1.01</v>
       </c>
       <c r="N39" t="n">
-        <v>1.3</v>
+        <v>2.14</v>
       </c>
       <c r="O39" t="n">
         <v>1.42</v>
       </c>
       <c r="P39" t="n">
-        <v>1.3</v>
+        <v>1.54</v>
       </c>
       <c r="Q39" t="n">
-        <v>1.42</v>
+        <v>2.1</v>
       </c>
       <c r="R39" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="S39" t="n">
-        <v>1.42</v>
+        <v>3.8</v>
       </c>
       <c r="T39" t="n">
-        <v>1.11</v>
+        <v>1.76</v>
       </c>
       <c r="U39" t="n">
-        <v>1.11</v>
+        <v>1.78</v>
       </c>
       <c r="V39" t="n">
-        <v>1.08</v>
+        <v>1.63</v>
       </c>
       <c r="W39" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="X39" t="n">
         <v>1000</v>
@@ -10318,40 +10318,40 @@
         <v>1000</v>
       </c>
       <c r="AA39" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AB39" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AC39" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AD39" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AE39" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AF39" t="n">
         <v>1000</v>
       </c>
       <c r="AG39" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AH39" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AI39" t="n">
         <v>1000</v>
       </c>
       <c r="AJ39" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AK39" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AL39" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AM39" t="n">
         <v>1000</v>
@@ -10363,58 +10363,58 @@
         <v>1000</v>
       </c>
       <c r="AP39" t="n">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="AQ39" t="n">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="AR39" t="n">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="AS39" t="n">
-        <v>1.01</v>
+        <v>1.59</v>
       </c>
       <c r="AT39" t="n">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="AU39" t="n">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="AV39" t="n">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="AW39" t="n">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="AX39" t="n">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="AY39" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AZ39" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BA39" t="n">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="BB39" t="n">
-        <v>1.01</v>
+        <v>1.61</v>
       </c>
       <c r="BC39" t="n">
-        <v>1.01</v>
+        <v>1.6</v>
       </c>
       <c r="BD39" t="n">
-        <v>1.01</v>
+        <v>1.61</v>
       </c>
       <c r="BE39" t="n">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="BF39" t="n">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="BG39" t="n">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="BH39" t="n">
         <v>1000</v>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-07-18 03:58:50</t>
+          <t>2026-07-18 06:20:25</t>
         </is>
       </c>
     </row>
@@ -10521,19 +10521,19 @@
         <v>1000</v>
       </c>
       <c r="J40" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="K40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L40" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M40" t="n">
         <v>1.06</v>
       </c>
-      <c r="K40" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L40" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M40" t="n">
-        <v>1.01</v>
-      </c>
       <c r="N40" t="n">
-        <v>1.1</v>
+        <v>3.3</v>
       </c>
       <c r="O40" t="n">
         <v>1.3</v>
@@ -10542,13 +10542,13 @@
         <v>1.08</v>
       </c>
       <c r="Q40" t="n">
-        <v>1.3</v>
+        <v>1.81</v>
       </c>
       <c r="R40" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="S40" t="n">
-        <v>1.3</v>
+        <v>2.96</v>
       </c>
       <c r="T40" t="n">
         <v>1.11</v>
@@ -10732,7 +10732,7 @@
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-07-18 03:58:50</t>
+          <t>2026-07-18 06:20:25</t>
         </is>
       </c>
     </row>
@@ -10763,112 +10763,112 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1.34</v>
+        <v>1.58</v>
       </c>
       <c r="G41" t="n">
-        <v>1000</v>
+        <v>1.78</v>
       </c>
       <c r="H41" t="n">
-        <v>1.31</v>
+        <v>4.8</v>
       </c>
       <c r="I41" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="J41" t="n">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="K41" t="n">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="L41" t="n">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="M41" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="N41" t="n">
-        <v>1.1</v>
+        <v>3.05</v>
       </c>
       <c r="O41" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P41" t="n">
-        <v>1.08</v>
+        <v>1.98</v>
       </c>
       <c r="Q41" t="n">
-        <v>1.23</v>
+        <v>1.6</v>
       </c>
       <c r="R41" t="n">
-        <v>1.07</v>
+        <v>1.45</v>
       </c>
       <c r="S41" t="n">
-        <v>1.23</v>
+        <v>2.52</v>
       </c>
       <c r="T41" t="n">
-        <v>1.11</v>
+        <v>1.74</v>
       </c>
       <c r="U41" t="n">
-        <v>1.11</v>
+        <v>1.9</v>
       </c>
       <c r="V41" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="W41" t="n">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="X41" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="Y41" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="Z41" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AA41" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AB41" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AC41" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AD41" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AE41" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AF41" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AG41" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AH41" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI41" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AJ41" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AK41" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AL41" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AM41" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AN41" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AO41" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AP41" t="n">
         <v>1.01</v>
@@ -10925,58 +10925,58 @@
         <v>1.01</v>
       </c>
       <c r="BH41" t="n">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="BI41" t="n">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="BJ41" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK41" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BL41" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="BM41" t="n">
         <v>1.01</v>
       </c>
       <c r="BN41" t="n">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="BO41" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="BP41" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BQ41" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BR41" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BS41" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BT41" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BU41" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BV41" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BW41" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX41" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BY41" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ41" t="n">
         <v>0</v>
@@ -10986,7 +10986,7 @@
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-07-18 03:58:50</t>
+          <t>2026-07-18 06:20:25</t>
         </is>
       </c>
     </row>
@@ -11017,58 +11017,58 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>1.48</v>
+        <v>1.9</v>
       </c>
       <c r="G42" t="n">
-        <v>1000</v>
+        <v>2.24</v>
       </c>
       <c r="H42" t="n">
-        <v>1.04</v>
+        <v>3.8</v>
       </c>
       <c r="I42" t="n">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="J42" t="n">
-        <v>1.02</v>
+        <v>2.64</v>
       </c>
       <c r="K42" t="n">
-        <v>1000</v>
+        <v>3.7</v>
       </c>
       <c r="L42" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="M42" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="N42" t="n">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
       <c r="O42" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="P42" t="n">
-        <v>1.07</v>
+        <v>1.68</v>
       </c>
       <c r="Q42" t="n">
-        <v>1.39</v>
+        <v>2.04</v>
       </c>
       <c r="R42" t="n">
-        <v>1.07</v>
+        <v>1.25</v>
       </c>
       <c r="S42" t="n">
-        <v>1.39</v>
+        <v>3.35</v>
       </c>
       <c r="T42" t="n">
-        <v>1.11</v>
+        <v>1.93</v>
       </c>
       <c r="U42" t="n">
-        <v>1.11</v>
+        <v>1.86</v>
       </c>
       <c r="V42" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="W42" t="n">
-        <v>1.01</v>
+        <v>1.81</v>
       </c>
       <c r="X42" t="n">
         <v>1000</v>
@@ -11179,55 +11179,55 @@
         <v>1.01</v>
       </c>
       <c r="BH42" t="n">
-        <v>1000</v>
+        <v>3.4</v>
       </c>
       <c r="BI42" t="n">
-        <v>1.01</v>
+        <v>2.56</v>
       </c>
       <c r="BJ42" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK42" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BL42" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="BM42" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN42" t="n">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="BO42" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="BP42" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="BQ42" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BR42" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BS42" t="n">
-        <v>1.01</v>
+        <v>25</v>
       </c>
       <c r="BT42" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU42" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BV42" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BW42" t="n">
         <v>1.01</v>
       </c>
       <c r="BX42" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BY42" t="n">
         <v>1.01</v>
@@ -11240,7 +11240,7 @@
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-07-18 03:58:50</t>
+          <t>2026-07-18 06:20:25</t>
         </is>
       </c>
     </row>
@@ -11271,19 +11271,19 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>1.8</v>
+        <v>2.18</v>
       </c>
       <c r="G43" t="n">
-        <v>1000</v>
+        <v>2.46</v>
       </c>
       <c r="H43" t="n">
-        <v>1.47</v>
+        <v>3.65</v>
       </c>
       <c r="I43" t="n">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="J43" t="n">
-        <v>1.69</v>
+        <v>2.94</v>
       </c>
       <c r="K43" t="n">
         <v>3.3</v>
@@ -11295,22 +11295,22 @@
         <v>1.01</v>
       </c>
       <c r="N43" t="n">
-        <v>1.01</v>
+        <v>2.56</v>
       </c>
       <c r="O43" t="n">
         <v>1.48</v>
       </c>
       <c r="P43" t="n">
-        <v>1.25</v>
+        <v>1.54</v>
       </c>
       <c r="Q43" t="n">
-        <v>1.48</v>
+        <v>2.46</v>
       </c>
       <c r="R43" t="n">
         <v>1.18</v>
       </c>
       <c r="S43" t="n">
-        <v>1.48</v>
+        <v>4.1</v>
       </c>
       <c r="T43" t="n">
         <v>1.01</v>
@@ -11319,10 +11319,10 @@
         <v>1.01</v>
       </c>
       <c r="V43" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="W43" t="n">
-        <v>1.01</v>
+        <v>1.68</v>
       </c>
       <c r="X43" t="n">
         <v>1000</v>
@@ -11494,7 +11494,7 @@
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-07-18 03:58:50</t>
+          <t>2026-07-18 06:20:25</t>
         </is>
       </c>
     </row>
@@ -11552,7 +11552,7 @@
         <v>1.25</v>
       </c>
       <c r="O44" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P44" t="n">
         <v>1.25</v>
@@ -11748,7 +11748,7 @@
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-07-18 03:58:50</t>
+          <t>2026-07-18 06:20:25</t>
         </is>
       </c>
     </row>
@@ -11779,230 +11779,230 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>1.04</v>
+        <v>1.4</v>
       </c>
       <c r="G45" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="H45" t="n">
-        <v>1.04</v>
+        <v>8.4</v>
       </c>
       <c r="I45" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="J45" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="K45" t="n">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="L45" t="n">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="M45" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N45" t="n">
-        <v>1.4</v>
+        <v>4</v>
       </c>
       <c r="O45" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P45" t="n">
-        <v>1.25</v>
+        <v>2.06</v>
       </c>
       <c r="Q45" t="n">
-        <v>1.25</v>
+        <v>1.8</v>
       </c>
       <c r="R45" t="n">
-        <v>1.18</v>
+        <v>1.41</v>
       </c>
       <c r="S45" t="n">
-        <v>1.25</v>
+        <v>3.05</v>
       </c>
       <c r="T45" t="n">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="U45" t="n">
-        <v>1.01</v>
+        <v>1.68</v>
       </c>
       <c r="V45" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="W45" t="n">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="X45" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Y45" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="Z45" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AA45" t="n">
-        <v>1000</v>
+        <v>400</v>
       </c>
       <c r="AB45" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AC45" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AD45" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AE45" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AF45" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AG45" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AH45" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AI45" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AJ45" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AK45" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AL45" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AM45" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AN45" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="AO45" t="n">
-        <v>1000</v>
+        <v>270</v>
       </c>
       <c r="AP45" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="AQ45" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="AR45" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AS45" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AT45" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AU45" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AV45" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="AW45" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AX45" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AY45" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AZ45" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BA45" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BB45" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BC45" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BD45" t="n">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="BE45" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BF45" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BG45" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BH45" t="n">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="BI45" t="n">
-        <v>1.01</v>
+        <v>2.96</v>
       </c>
       <c r="BJ45" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="BK45" t="n">
         <v>1.01</v>
       </c>
       <c r="BL45" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="BM45" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BN45" t="n">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="BO45" t="n">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="BP45" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BQ45" t="n">
         <v>1.01</v>
       </c>
       <c r="BR45" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BS45" t="n">
         <v>1.01</v>
       </c>
       <c r="BT45" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BU45" t="n">
         <v>1.01</v>
       </c>
       <c r="BV45" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="BW45" t="n">
         <v>1.01</v>
       </c>
       <c r="BX45" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="BY45" t="n">
         <v>1.01</v>
       </c>
       <c r="BZ45" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="CA45" t="n">
         <v>1.01</v>
       </c>
       <c r="CB45" t="inlineStr">
         <is>
-          <t>2026-07-18 03:58:50</t>
+          <t>2026-07-18 06:20:25</t>
         </is>
       </c>
     </row>
@@ -12033,230 +12033,484 @@
         </is>
       </c>
       <c r="F46" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="G46" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="H46" t="n">
+        <v>10</v>
+      </c>
+      <c r="I46" t="n">
+        <v>14</v>
+      </c>
+      <c r="J46" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="K46" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="L46" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="M46" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N46" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="O46" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="P46" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="R46" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S46" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="V46" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W46" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="X46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>36</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>540</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF46" t="n">
+        <v>9</v>
+      </c>
+      <c r="AG46" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI46" t="n">
+        <v>190</v>
+      </c>
+      <c r="AJ46" t="n">
+        <v>13</v>
+      </c>
+      <c r="AK46" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AL46" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AO46" t="n">
+        <v>370</v>
+      </c>
+      <c r="AP46" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AQ46" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AR46" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AS46" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AT46" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AU46" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV46" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AW46" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AX46" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AY46" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ46" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BA46" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BB46" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BC46" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BD46" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BE46" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BF46" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BG46" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BH46" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BI46" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BJ46" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BK46" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BL46" t="n">
+        <v>220</v>
+      </c>
+      <c r="BM46" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN46" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BO46" t="n">
+        <v>3</v>
+      </c>
+      <c r="BP46" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BQ46" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BR46" t="n">
+        <v>32</v>
+      </c>
+      <c r="BS46" t="n">
+        <v>20</v>
+      </c>
+      <c r="BT46" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BU46" t="n">
+        <v>10</v>
+      </c>
+      <c r="BV46" t="n">
+        <v>120</v>
+      </c>
+      <c r="BW46" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX46" t="n">
+        <v>110</v>
+      </c>
+      <c r="BY46" t="n">
+        <v>21</v>
+      </c>
+      <c r="BZ46" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="CA46" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="CB46" t="inlineStr">
+        <is>
+          <t>2026-07-18 06:20:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Bolivian Liga de Futbol Profesional</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Blooming Santa Cruz</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Real Tomayapo</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
         <v>1.04</v>
       </c>
-      <c r="G46" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="H46" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="I46" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J46" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="K46" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L46" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M46" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N46" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="O46" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="P46" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="R46" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S46" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="T46" t="n">
+      <c r="G47" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H47" t="n">
         <v>1.04</v>
       </c>
-      <c r="U46" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="V46" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W46" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X46" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y46" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z46" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA46" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB46" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC46" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD46" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE46" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF46" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG46" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH46" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI46" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ46" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK46" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL46" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM46" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN46" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO46" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP46" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ46" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AR46" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS46" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT46" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AU46" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AV46" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AW46" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX46" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AY46" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AZ46" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BA46" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB46" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BC46" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BD46" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BE46" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF46" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG46" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH46" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI46" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BJ46" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK46" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL46" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM46" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN46" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO46" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BP46" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ46" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BR46" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS46" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BT46" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU46" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BV46" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW46" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BX46" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY46" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BZ46" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA46" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="CB46" t="inlineStr">
-        <is>
-          <t>2026-07-18 03:58:50</t>
+      <c r="I47" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J47" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="K47" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L47" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M47" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N47" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="O47" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="P47" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="R47" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S47" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="T47" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V47" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W47" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X47" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE47" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF47" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG47" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH47" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI47" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ47" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK47" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL47" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM47" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO47" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP47" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ47" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR47" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS47" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT47" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU47" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV47" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW47" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX47" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY47" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ47" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA47" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB47" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC47" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD47" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE47" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF47" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG47" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH47" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI47" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ47" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK47" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL47" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM47" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN47" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO47" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP47" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ47" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR47" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS47" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT47" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU47" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV47" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW47" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX47" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY47" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ47" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA47" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB47" t="inlineStr">
+        <is>
+          <t>2026-07-18 06:20:25</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-19.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-19.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB47"/>
+  <dimension ref="A1:CB48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -869,7 +869,7 @@
         <v>2.1</v>
       </c>
       <c r="J2" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="K2" t="n">
         <v>3.85</v>
@@ -902,7 +902,7 @@
         <v>1.73</v>
       </c>
       <c r="U2" t="n">
-        <v>1.93</v>
+        <v>2.14</v>
       </c>
       <c r="V2" t="n">
         <v>1.9</v>
@@ -944,7 +944,7 @@
         <v>21</v>
       </c>
       <c r="AI2" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AJ2" t="n">
         <v>85</v>
@@ -989,7 +989,7 @@
         <v>18.5</v>
       </c>
       <c r="AX2" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AY2" t="n">
         <v>13.5</v>
@@ -1001,7 +1001,7 @@
         <v>6.2</v>
       </c>
       <c r="BB2" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BC2" t="n">
         <v>38</v>
@@ -1010,10 +1010,10 @@
         <v>38</v>
       </c>
       <c r="BE2" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BF2" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BG2" t="n">
         <v>11</v>
@@ -1022,7 +1022,7 @@
         <v>4.1</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="BJ2" t="n">
         <v>11.5</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-18 06:20:25</t>
+          <t>2026-07-18 08:41:26</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
         <v>1.64</v>
       </c>
       <c r="G3" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="H3" t="n">
         <v>6.4</v>
@@ -1123,7 +1123,7 @@
         <v>7</v>
       </c>
       <c r="J3" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="K3" t="n">
         <v>4.1</v>
@@ -1138,7 +1138,7 @@
         <v>3.25</v>
       </c>
       <c r="O3" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="P3" t="n">
         <v>1.76</v>
@@ -1153,16 +1153,16 @@
         <v>4.2</v>
       </c>
       <c r="T3" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="U3" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="V3" t="n">
         <v>1.16</v>
       </c>
       <c r="W3" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="X3" t="n">
         <v>12</v>
@@ -1171,7 +1171,7 @@
         <v>18.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>170</v>
+        <v>60</v>
       </c>
       <c r="AA3" t="n">
         <v>1000</v>
@@ -1195,7 +1195,7 @@
         <v>10.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AI3" t="n">
         <v>1000</v>
@@ -1249,7 +1249,7 @@
         <v>9.6</v>
       </c>
       <c r="AZ3" t="n">
-        <v>23</v>
+        <v>18.5</v>
       </c>
       <c r="BA3" t="n">
         <v>42</v>
@@ -1261,7 +1261,7 @@
         <v>17.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="BE3" t="n">
         <v>95</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-18 06:20:25</t>
+          <t>2026-07-18 08:41:26</t>
         </is>
       </c>
     </row>
@@ -1365,25 +1365,25 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="G4" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="H4" t="n">
         <v>1.79</v>
       </c>
       <c r="I4" t="n">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="J4" t="n">
         <v>3.6</v>
       </c>
       <c r="K4" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L4" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="M4" t="n">
         <v>1.09</v>
@@ -1407,13 +1407,13 @@
         <v>4.3</v>
       </c>
       <c r="T4" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="U4" t="n">
         <v>1.82</v>
       </c>
       <c r="V4" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="W4" t="n">
         <v>1.21</v>
@@ -1425,7 +1425,7 @@
         <v>7.2</v>
       </c>
       <c r="Z4" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AA4" t="n">
         <v>20</v>
@@ -1440,10 +1440,10 @@
         <v>10.5</v>
       </c>
       <c r="AE4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AF4" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AG4" t="n">
         <v>24</v>
@@ -1470,7 +1470,7 @@
         <v>160</v>
       </c>
       <c r="AO4" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AP4" t="n">
         <v>10</v>
@@ -1488,7 +1488,7 @@
         <v>13</v>
       </c>
       <c r="AU4" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV4" t="n">
         <v>9.199999999999999</v>
@@ -1497,7 +1497,7 @@
         <v>19.5</v>
       </c>
       <c r="AX4" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY4" t="n">
         <v>19</v>
@@ -1506,22 +1506,22 @@
         <v>20</v>
       </c>
       <c r="BA4" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BB4" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BC4" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BD4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BE4" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BF4" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BG4" t="n">
         <v>14</v>
@@ -1563,13 +1563,13 @@
         <v>1.01</v>
       </c>
       <c r="BT4" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BU4" t="n">
         <v>3.4</v>
       </c>
       <c r="BV4" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BW4" t="n">
         <v>1.01</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-18 06:20:25</t>
+          <t>2026-07-18 08:41:26</t>
         </is>
       </c>
     </row>
@@ -1622,7 +1622,7 @@
         <v>1.75</v>
       </c>
       <c r="G5" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="H5" t="n">
         <v>4.7</v>
@@ -1661,10 +1661,10 @@
         <v>3.45</v>
       </c>
       <c r="T5" t="n">
-        <v>1.75</v>
+        <v>1.86</v>
       </c>
       <c r="U5" t="n">
-        <v>1.87</v>
+        <v>1.98</v>
       </c>
       <c r="V5" t="n">
         <v>1.21</v>
@@ -1691,13 +1691,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AD5" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AE5" t="n">
         <v>75</v>
       </c>
       <c r="AF5" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AG5" t="n">
         <v>12</v>
@@ -1706,7 +1706,7 @@
         <v>23</v>
       </c>
       <c r="AI5" t="n">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="AJ5" t="n">
         <v>23</v>
@@ -1715,7 +1715,7 @@
         <v>23</v>
       </c>
       <c r="AL5" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AM5" t="n">
         <v>140</v>
@@ -1790,13 +1790,13 @@
         <v>12</v>
       </c>
       <c r="BK5" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="BL5" t="n">
         <v>160</v>
       </c>
       <c r="BM5" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="BN5" t="n">
         <v>5</v>
@@ -1808,31 +1808,31 @@
         <v>14.5</v>
       </c>
       <c r="BQ5" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BR5" t="n">
         <v>32</v>
       </c>
       <c r="BS5" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="BT5" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BU5" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="BV5" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BW5" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BX5" t="n">
         <v>60</v>
       </c>
       <c r="BY5" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="BZ5" t="n">
         <v>0</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-18 06:20:25</t>
+          <t>2026-07-18 08:41:26</t>
         </is>
       </c>
     </row>
@@ -1873,25 +1873,25 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="G6" t="n">
         <v>3.15</v>
       </c>
       <c r="H6" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="I6" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="J6" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="K6" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L6" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="M6" t="n">
         <v>1.07</v>
@@ -1903,10 +1903,10 @@
         <v>1.33</v>
       </c>
       <c r="P6" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="R6" t="n">
         <v>1.33</v>
@@ -1915,13 +1915,13 @@
         <v>3.45</v>
       </c>
       <c r="T6" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="U6" t="n">
         <v>2.12</v>
       </c>
       <c r="V6" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="W6" t="n">
         <v>1.47</v>
@@ -1933,7 +1933,7 @@
         <v>11.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AA6" t="n">
         <v>42</v>
@@ -1942,7 +1942,7 @@
         <v>12</v>
       </c>
       <c r="AC6" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD6" t="n">
         <v>12.5</v>
@@ -2035,13 +2035,13 @@
         <v>19</v>
       </c>
       <c r="BH6" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="BI6" t="n">
         <v>3</v>
       </c>
       <c r="BJ6" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="BK6" t="n">
         <v>4.7</v>
@@ -2050,28 +2050,28 @@
         <v>140</v>
       </c>
       <c r="BM6" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN6" t="n">
         <v>6.8</v>
       </c>
       <c r="BO6" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BP6" t="n">
         <v>23</v>
       </c>
       <c r="BQ6" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BR6" t="n">
         <v>40</v>
       </c>
       <c r="BS6" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BT6" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BU6" t="n">
         <v>4.5</v>
@@ -2080,13 +2080,13 @@
         <v>24</v>
       </c>
       <c r="BW6" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BX6" t="n">
         <v>38</v>
       </c>
       <c r="BY6" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="BZ6" t="n">
         <v>0</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-18 06:20:25</t>
+          <t>2026-07-18 08:41:26</t>
         </is>
       </c>
     </row>
@@ -2127,16 +2127,16 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="G7" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="H7" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="I7" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="J7" t="n">
         <v>3.3</v>
@@ -2145,22 +2145,22 @@
         <v>3.7</v>
       </c>
       <c r="L7" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="M7" t="n">
         <v>1.07</v>
       </c>
       <c r="N7" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="O7" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="P7" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="R7" t="n">
         <v>1.32</v>
@@ -2175,13 +2175,13 @@
         <v>1.91</v>
       </c>
       <c r="V7" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="W7" t="n">
         <v>1.42</v>
       </c>
       <c r="X7" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Y7" t="n">
         <v>12.5</v>
@@ -2298,31 +2298,31 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BK7" t="n">
-        <v>7</v>
+        <v>3.6</v>
       </c>
       <c r="BL7" t="n">
         <v>150</v>
       </c>
       <c r="BM7" t="n">
-        <v>6.2</v>
+        <v>5.5</v>
       </c>
       <c r="BN7" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="BO7" t="n">
-        <v>5.4</v>
+        <v>4.7</v>
       </c>
       <c r="BP7" t="n">
         <v>30</v>
       </c>
       <c r="BQ7" t="n">
-        <v>5.4</v>
+        <v>4.8</v>
       </c>
       <c r="BR7" t="n">
         <v>55</v>
       </c>
       <c r="BS7" t="n">
-        <v>5.6</v>
+        <v>5</v>
       </c>
       <c r="BT7" t="n">
         <v>6.4</v>
@@ -2334,13 +2334,13 @@
         <v>24</v>
       </c>
       <c r="BW7" t="n">
-        <v>5.1</v>
+        <v>4.6</v>
       </c>
       <c r="BX7" t="n">
         <v>48</v>
       </c>
       <c r="BY7" t="n">
-        <v>5.5</v>
+        <v>4.9</v>
       </c>
       <c r="BZ7" t="n">
         <v>0</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-18 06:20:25</t>
+          <t>2026-07-18 08:41:26</t>
         </is>
       </c>
     </row>
@@ -2381,10 +2381,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="G8" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="H8" t="n">
         <v>8.199999999999999</v>
@@ -2396,10 +2396,10 @@
         <v>5</v>
       </c>
       <c r="K8" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="L8" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="M8" t="n">
         <v>1.05</v>
@@ -2411,22 +2411,22 @@
         <v>1.24</v>
       </c>
       <c r="P8" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="R8" t="n">
         <v>1.44</v>
       </c>
       <c r="S8" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="T8" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="U8" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="V8" t="n">
         <v>1.1</v>
@@ -2435,7 +2435,7 @@
         <v>3.1</v>
       </c>
       <c r="X8" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Y8" t="n">
         <v>36</v>
@@ -2471,7 +2471,7 @@
         <v>140</v>
       </c>
       <c r="AJ8" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AK8" t="n">
         <v>19</v>
@@ -2483,7 +2483,7 @@
         <v>170</v>
       </c>
       <c r="AN8" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AO8" t="n">
         <v>220</v>
@@ -2549,7 +2549,7 @@
         <v>3.05</v>
       </c>
       <c r="BJ8" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BK8" t="n">
         <v>1.01</v>
@@ -2582,10 +2582,10 @@
         <v>12.5</v>
       </c>
       <c r="BU8" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BV8" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="BW8" t="n">
         <v>1.01</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-18 06:20:25</t>
+          <t>2026-07-18 08:41:26</t>
         </is>
       </c>
     </row>
@@ -2635,46 +2635,46 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.12</v>
+        <v>2.1</v>
       </c>
       <c r="G9" t="n">
-        <v>1000</v>
+        <v>2.54</v>
       </c>
       <c r="H9" t="n">
-        <v>1.12</v>
+        <v>3.45</v>
       </c>
       <c r="I9" t="n">
-        <v>1000</v>
+        <v>5.3</v>
       </c>
       <c r="J9" t="n">
-        <v>1.24</v>
+        <v>2.46</v>
       </c>
       <c r="K9" t="n">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="L9" t="n">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="M9" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="N9" t="n">
-        <v>1.25</v>
+        <v>2.36</v>
       </c>
       <c r="O9" t="n">
-        <v>1.02</v>
+        <v>1.56</v>
       </c>
       <c r="P9" t="n">
-        <v>1.25</v>
+        <v>1.45</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.53</v>
+        <v>2.72</v>
       </c>
       <c r="R9" t="n">
         <v>1.18</v>
       </c>
       <c r="S9" t="n">
-        <v>1.05</v>
+        <v>5.1</v>
       </c>
       <c r="T9" t="n">
         <v>1.11</v>
@@ -2683,64 +2683,64 @@
         <v>1.11</v>
       </c>
       <c r="V9" t="n">
-        <v>1.02</v>
+        <v>1.25</v>
       </c>
       <c r="W9" t="n">
-        <v>1.02</v>
+        <v>1.65</v>
       </c>
       <c r="X9" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="Y9" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Z9" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AA9" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AB9" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AC9" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AD9" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AE9" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AF9" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AG9" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AI9" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AK9" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AL9" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AM9" t="n">
-        <v>1000</v>
+        <v>270</v>
       </c>
       <c r="AN9" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AO9" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AP9" t="n">
         <v>1.01</v>
@@ -2797,68 +2797,68 @@
         <v>1.01</v>
       </c>
       <c r="BH9" t="n">
-        <v>1000</v>
+        <v>2.92</v>
       </c>
       <c r="BI9" t="n">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="BJ9" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BK9" t="n">
         <v>1.01</v>
       </c>
       <c r="BL9" t="n">
-        <v>1000</v>
+        <v>310</v>
       </c>
       <c r="BM9" t="n">
         <v>1.01</v>
       </c>
       <c r="BN9" t="n">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BP9" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BQ9" t="n">
         <v>1.01</v>
       </c>
       <c r="BR9" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BS9" t="n">
         <v>1.01</v>
       </c>
       <c r="BT9" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="BU9" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BV9" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BW9" t="n">
         <v>1.01</v>
       </c>
       <c r="BX9" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="BY9" t="n">
         <v>1.01</v>
       </c>
       <c r="BZ9" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="CA9" t="n">
         <v>1.01</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-18 06:20:25</t>
+          <t>2026-07-18 08:41:26</t>
         </is>
       </c>
     </row>
@@ -2889,112 +2889,112 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.12</v>
+        <v>2.86</v>
       </c>
       <c r="G10" t="n">
-        <v>1000</v>
+        <v>3.45</v>
       </c>
       <c r="H10" t="n">
-        <v>1.12</v>
+        <v>2.66</v>
       </c>
       <c r="I10" t="n">
-        <v>1000</v>
+        <v>3.2</v>
       </c>
       <c r="J10" t="n">
-        <v>1.24</v>
+        <v>2.6</v>
       </c>
       <c r="K10" t="n">
-        <v>1000</v>
+        <v>3.5</v>
       </c>
       <c r="L10" t="n">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="M10" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="N10" t="n">
-        <v>1.25</v>
+        <v>2.3</v>
       </c>
       <c r="O10" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="P10" t="n">
-        <v>1.25</v>
+        <v>1.47</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.52</v>
+        <v>2.5</v>
       </c>
       <c r="R10" t="n">
         <v>1.18</v>
       </c>
       <c r="S10" t="n">
-        <v>1.52</v>
+        <v>3.45</v>
       </c>
       <c r="T10" t="n">
-        <v>1.11</v>
+        <v>1.98</v>
       </c>
       <c r="U10" t="n">
-        <v>1.11</v>
+        <v>1.66</v>
       </c>
       <c r="V10" t="n">
-        <v>1.02</v>
+        <v>1.46</v>
       </c>
       <c r="W10" t="n">
-        <v>1.02</v>
+        <v>1.4</v>
       </c>
       <c r="X10" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="Y10" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z10" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AA10" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AB10" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC10" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="AD10" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AE10" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AF10" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AG10" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AI10" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AK10" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AL10" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AM10" t="n">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AN10" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AO10" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AP10" t="n">
         <v>1.01</v>
@@ -3051,68 +3051,68 @@
         <v>1.01</v>
       </c>
       <c r="BH10" t="n">
-        <v>1000</v>
+        <v>2.9</v>
       </c>
       <c r="BI10" t="n">
-        <v>1.04</v>
+        <v>2.24</v>
       </c>
       <c r="BJ10" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BK10" t="n">
         <v>1.04</v>
       </c>
       <c r="BL10" t="n">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="BM10" t="n">
         <v>1.04</v>
       </c>
       <c r="BN10" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BO10" t="n">
         <v>1.04</v>
       </c>
       <c r="BP10" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BQ10" t="n">
         <v>1.04</v>
       </c>
       <c r="BR10" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BS10" t="n">
         <v>1.04</v>
       </c>
       <c r="BT10" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BU10" t="n">
         <v>1.04</v>
       </c>
       <c r="BV10" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BW10" t="n">
         <v>1.04</v>
       </c>
       <c r="BX10" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BY10" t="n">
         <v>1.04</v>
       </c>
       <c r="BZ10" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="CA10" t="n">
         <v>1.04</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-18 06:20:25</t>
+          <t>2026-07-18 08:41:26</t>
         </is>
       </c>
     </row>
@@ -3143,28 +3143,28 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="G11" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="H11" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="I11" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="J11" t="n">
         <v>4.6</v>
       </c>
       <c r="K11" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="L11" t="n">
         <v>1.23</v>
       </c>
       <c r="M11" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N11" t="n">
         <v>6</v>
@@ -3173,16 +3173,16 @@
         <v>1.17</v>
       </c>
       <c r="P11" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="R11" t="n">
         <v>1.69</v>
       </c>
       <c r="S11" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="T11" t="n">
         <v>1.63</v>
@@ -3191,10 +3191,10 @@
         <v>2.38</v>
       </c>
       <c r="V11" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="W11" t="n">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="X11" t="n">
         <v>29</v>
@@ -3203,7 +3203,7 @@
         <v>29</v>
       </c>
       <c r="Z11" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AA11" t="n">
         <v>150</v>
@@ -3215,19 +3215,19 @@
         <v>12</v>
       </c>
       <c r="AD11" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AE11" t="n">
         <v>70</v>
       </c>
       <c r="AF11" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AG11" t="n">
         <v>11</v>
       </c>
       <c r="AH11" t="n">
-        <v>18.5</v>
+        <v>970</v>
       </c>
       <c r="AI11" t="n">
         <v>55</v>
@@ -3248,19 +3248,19 @@
         <v>6.6</v>
       </c>
       <c r="AO11" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AP11" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AQ11" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AR11" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AS11" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AT11" t="n">
         <v>11.5</v>
@@ -3269,10 +3269,10 @@
         <v>10</v>
       </c>
       <c r="AV11" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AW11" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX11" t="n">
         <v>11</v>
@@ -3281,7 +3281,7 @@
         <v>9.4</v>
       </c>
       <c r="AZ11" t="n">
-        <v>6.6</v>
+        <v>15.5</v>
       </c>
       <c r="BA11" t="n">
         <v>8.6</v>
@@ -3293,10 +3293,10 @@
         <v>13</v>
       </c>
       <c r="BD11" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BE11" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF11" t="n">
         <v>5.2</v>
@@ -3305,68 +3305,68 @@
         <v>36</v>
       </c>
       <c r="BH11" t="n">
-        <v>5.4</v>
+        <v>4.8</v>
       </c>
       <c r="BI11" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="BJ11" t="n">
         <v>11</v>
       </c>
       <c r="BK11" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="BL11" t="n">
         <v>95</v>
       </c>
       <c r="BM11" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="BN11" t="n">
         <v>5.2</v>
       </c>
       <c r="BO11" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BP11" t="n">
         <v>11</v>
       </c>
       <c r="BQ11" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="BR11" t="n">
         <v>22</v>
       </c>
       <c r="BS11" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="BT11" t="n">
         <v>11</v>
       </c>
       <c r="BU11" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="BV11" t="n">
         <v>46</v>
       </c>
       <c r="BW11" t="n">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="BX11" t="n">
         <v>46</v>
       </c>
       <c r="BY11" t="n">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="BZ11" t="n">
         <v>13.5</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.95</v>
+        <v>4.4</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-18 06:20:25</t>
+          <t>2026-07-18 08:41:26</t>
         </is>
       </c>
     </row>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-18 06:20:25</t>
+          <t>2026-07-18 08:41:26</t>
         </is>
       </c>
     </row>
@@ -3657,13 +3657,13 @@
         <v>1000</v>
       </c>
       <c r="H13" t="n">
-        <v>1.12</v>
+        <v>1.04</v>
       </c>
       <c r="I13" t="n">
         <v>1000</v>
       </c>
       <c r="J13" t="n">
-        <v>1.24</v>
+        <v>1.01</v>
       </c>
       <c r="K13" t="n">
         <v>1000</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-18 06:20:25</t>
+          <t>2026-07-18 08:41:26</t>
         </is>
       </c>
     </row>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-18 06:20:25</t>
+          <t>2026-07-18 08:41:26</t>
         </is>
       </c>
     </row>
@@ -4159,7 +4159,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.12</v>
+        <v>1.04</v>
       </c>
       <c r="G15" t="n">
         <v>1000</v>
@@ -4171,7 +4171,7 @@
         <v>1000</v>
       </c>
       <c r="J15" t="n">
-        <v>1.24</v>
+        <v>1.01</v>
       </c>
       <c r="K15" t="n">
         <v>1000</v>
@@ -4207,7 +4207,7 @@
         <v>1.11</v>
       </c>
       <c r="V15" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W15" t="n">
         <v>1.02</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-18 06:20:25</t>
+          <t>2026-07-18 08:41:26</t>
         </is>
       </c>
     </row>
@@ -4413,13 +4413,13 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="G16" t="n">
         <v>1000</v>
       </c>
       <c r="H16" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="I16" t="n">
         <v>1000</v>
@@ -4452,7 +4452,7 @@
         <v>1.18</v>
       </c>
       <c r="S16" t="n">
-        <v>1.4</v>
+        <v>1.05</v>
       </c>
       <c r="T16" t="n">
         <v>1.11</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-18 06:20:25</t>
+          <t>2026-07-18 08:41:26</t>
         </is>
       </c>
     </row>
@@ -4697,16 +4697,16 @@
         <v>1.25</v>
       </c>
       <c r="P17" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="R17" t="n">
         <v>1.45</v>
       </c>
       <c r="S17" t="n">
-        <v>2.74</v>
+        <v>2.82</v>
       </c>
       <c r="T17" t="n">
         <v>1.66</v>
@@ -4733,7 +4733,7 @@
         <v>110</v>
       </c>
       <c r="AB17" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AC17" t="n">
         <v>9.800000000000001</v>
@@ -4781,10 +4781,10 @@
         <v>15.5</v>
       </c>
       <c r="AR17" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AS17" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT17" t="n">
         <v>9.199999999999999</v>
@@ -4796,7 +4796,7 @@
         <v>14.5</v>
       </c>
       <c r="AW17" t="n">
-        <v>6.8</v>
+        <v>40</v>
       </c>
       <c r="AX17" t="n">
         <v>11</v>
@@ -4808,7 +4808,7 @@
         <v>14.5</v>
       </c>
       <c r="BA17" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="BB17" t="n">
         <v>18</v>
@@ -4817,16 +4817,16 @@
         <v>15.5</v>
       </c>
       <c r="BD17" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="BE17" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="BF17" t="n">
         <v>7.8</v>
       </c>
       <c r="BG17" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BH17" t="n">
         <v>1000</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-18 06:20:25</t>
+          <t>2026-07-18 08:41:26</t>
         </is>
       </c>
     </row>
@@ -4921,22 +4921,22 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.62</v>
+        <v>2.72</v>
       </c>
       <c r="G18" t="n">
         <v>2.98</v>
       </c>
       <c r="H18" t="n">
-        <v>2.38</v>
+        <v>2.48</v>
       </c>
       <c r="I18" t="n">
-        <v>2.78</v>
+        <v>2.72</v>
       </c>
       <c r="J18" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="K18" t="n">
-        <v>38</v>
+        <v>4.1</v>
       </c>
       <c r="L18" t="n">
         <v>1.28</v>
@@ -4945,19 +4945,19 @@
         <v>1.05</v>
       </c>
       <c r="N18" t="n">
-        <v>3.75</v>
+        <v>4.4</v>
       </c>
       <c r="O18" t="n">
         <v>1.24</v>
       </c>
       <c r="P18" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="R18" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="S18" t="n">
         <v>2.84</v>
@@ -4966,7 +4966,7 @@
         <v>1.52</v>
       </c>
       <c r="U18" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="V18" t="n">
         <v>1.58</v>
@@ -4981,7 +4981,7 @@
         <v>14</v>
       </c>
       <c r="Z18" t="n">
-        <v>23</v>
+        <v>19.5</v>
       </c>
       <c r="AA18" t="n">
         <v>44</v>
@@ -4996,7 +4996,7 @@
         <v>13</v>
       </c>
       <c r="AE18" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AF18" t="n">
         <v>22</v>
@@ -5008,10 +5008,10 @@
         <v>16.5</v>
       </c>
       <c r="AI18" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AJ18" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AK18" t="n">
         <v>32</v>
@@ -5023,10 +5023,10 @@
         <v>80</v>
       </c>
       <c r="AN18" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="AO18" t="n">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="AP18" t="n">
         <v>15.5</v>
@@ -5038,7 +5038,7 @@
         <v>15.5</v>
       </c>
       <c r="AS18" t="n">
-        <v>5.4</v>
+        <v>7</v>
       </c>
       <c r="AT18" t="n">
         <v>11.5</v>
@@ -5062,19 +5062,19 @@
         <v>13</v>
       </c>
       <c r="BA18" t="n">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="BB18" t="n">
         <v>34</v>
       </c>
       <c r="BC18" t="n">
-        <v>5.2</v>
+        <v>6.6</v>
       </c>
       <c r="BD18" t="n">
-        <v>5.4</v>
+        <v>7</v>
       </c>
       <c r="BE18" t="n">
-        <v>5.8</v>
+        <v>7.6</v>
       </c>
       <c r="BF18" t="n">
         <v>15</v>
@@ -5092,7 +5092,7 @@
         <v>10.5</v>
       </c>
       <c r="BK18" t="n">
-        <v>3.2</v>
+        <v>6.8</v>
       </c>
       <c r="BL18" t="n">
         <v>110</v>
@@ -5104,7 +5104,7 @@
         <v>7.4</v>
       </c>
       <c r="BO18" t="n">
-        <v>5.3</v>
+        <v>4.6</v>
       </c>
       <c r="BP18" t="n">
         <v>25</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-18 06:20:25</t>
+          <t>2026-07-18 08:41:26</t>
         </is>
       </c>
     </row>
@@ -5190,16 +5190,16 @@
         <v>2.92</v>
       </c>
       <c r="K19" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="L19" t="n">
         <v>1.51</v>
       </c>
       <c r="M19" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N19" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="O19" t="n">
         <v>1.54</v>
@@ -5229,10 +5229,10 @@
         <v>1.44</v>
       </c>
       <c r="X19" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="Y19" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="Z19" t="n">
         <v>21</v>
@@ -5346,13 +5346,13 @@
         <v>13</v>
       </c>
       <c r="BK19" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="BL19" t="n">
         <v>240</v>
       </c>
       <c r="BM19" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BN19" t="n">
         <v>6.6</v>
@@ -5364,13 +5364,13 @@
         <v>34</v>
       </c>
       <c r="BQ19" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BR19" t="n">
         <v>60</v>
       </c>
       <c r="BS19" t="n">
-        <v>38</v>
+        <v>1.01</v>
       </c>
       <c r="BT19" t="n">
         <v>6.4</v>
@@ -5382,13 +5382,13 @@
         <v>32</v>
       </c>
       <c r="BW19" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BX19" t="n">
         <v>60</v>
       </c>
       <c r="BY19" t="n">
-        <v>36</v>
+        <v>1.01</v>
       </c>
       <c r="BZ19" t="n">
         <v>0</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-18 06:20:25</t>
+          <t>2026-07-18 08:41:26</t>
         </is>
       </c>
     </row>
@@ -5429,43 +5429,43 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="G20" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="H20" t="n">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="I20" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="J20" t="n">
-        <v>3.95</v>
+        <v>4.4</v>
       </c>
       <c r="K20" t="n">
-        <v>5.6</v>
+        <v>5.1</v>
       </c>
       <c r="L20" t="n">
         <v>1.27</v>
       </c>
       <c r="M20" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N20" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="O20" t="n">
         <v>1.21</v>
       </c>
       <c r="P20" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="Q20" t="n">
         <v>1.6</v>
       </c>
       <c r="R20" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="S20" t="n">
         <v>2.52</v>
@@ -5474,103 +5474,103 @@
         <v>1.72</v>
       </c>
       <c r="U20" t="n">
-        <v>2</v>
+        <v>2.22</v>
       </c>
       <c r="V20" t="n">
-        <v>2.58</v>
+        <v>2.66</v>
       </c>
       <c r="W20" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="X20" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="Y20" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Z20" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AA20" t="n">
         <v>16</v>
       </c>
       <c r="AB20" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AC20" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AD20" t="n">
         <v>10.5</v>
       </c>
       <c r="AE20" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AF20" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AG20" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AH20" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AI20" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AK20" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AL20" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AM20" t="n">
         <v>100</v>
       </c>
       <c r="AN20" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AO20" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="AP20" t="n">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="AQ20" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="AR20" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AS20" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AT20" t="n">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="AU20" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AV20" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AW20" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AX20" t="n">
         <v>1.01</v>
       </c>
       <c r="AY20" t="n">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="AZ20" t="n">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA20" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BB20" t="n">
         <v>1.01</v>
@@ -5582,25 +5582,25 @@
         <v>1.01</v>
       </c>
       <c r="BE20" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BF20" t="n">
         <v>1.01</v>
       </c>
       <c r="BG20" t="n">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH20" t="n">
         <v>4.7</v>
       </c>
       <c r="BI20" t="n">
-        <v>3.4</v>
+        <v>1.01</v>
       </c>
       <c r="BJ20" t="n">
         <v>11.5</v>
       </c>
       <c r="BK20" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BL20" t="n">
         <v>120</v>
@@ -5612,13 +5612,13 @@
         <v>11</v>
       </c>
       <c r="BO20" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BP20" t="n">
         <v>55</v>
       </c>
       <c r="BQ20" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BR20" t="n">
         <v>55</v>
@@ -5630,19 +5630,19 @@
         <v>5</v>
       </c>
       <c r="BU20" t="n">
-        <v>3.55</v>
+        <v>1.01</v>
       </c>
       <c r="BV20" t="n">
         <v>11.5</v>
       </c>
       <c r="BW20" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BX20" t="n">
         <v>25</v>
       </c>
       <c r="BY20" t="n">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="BZ20" t="n">
         <v>0</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-18 06:20:25</t>
+          <t>2026-07-18 08:41:26</t>
         </is>
       </c>
     </row>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-07-18 06:20:25</t>
+          <t>2026-07-18 08:41:26</t>
         </is>
       </c>
     </row>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-07-18 06:20:25</t>
+          <t>2026-07-18 08:41:26</t>
         </is>
       </c>
     </row>
@@ -6206,7 +6206,7 @@
         <v>3.55</v>
       </c>
       <c r="K23" t="n">
-        <v>3.95</v>
+        <v>3.75</v>
       </c>
       <c r="L23" t="n">
         <v>1.4</v>
@@ -6215,13 +6215,13 @@
         <v>1.07</v>
       </c>
       <c r="N23" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="O23" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="P23" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="Q23" t="n">
         <v>1.95</v>
@@ -6230,7 +6230,7 @@
         <v>1.36</v>
       </c>
       <c r="S23" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="T23" t="n">
         <v>1.79</v>
@@ -6242,25 +6242,25 @@
         <v>1.31</v>
       </c>
       <c r="W23" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="X23" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y23" t="n">
         <v>14.5</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>15</v>
       </c>
       <c r="Z23" t="n">
         <v>30</v>
       </c>
       <c r="AA23" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="AB23" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AC23" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD23" t="n">
         <v>16.5</v>
@@ -6305,10 +6305,10 @@
         <v>13</v>
       </c>
       <c r="AR23" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AS23" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AT23" t="n">
         <v>8.6</v>
@@ -6317,7 +6317,7 @@
         <v>7.2</v>
       </c>
       <c r="AV23" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AW23" t="n">
         <v>34</v>
@@ -6326,7 +6326,7 @@
         <v>11.5</v>
       </c>
       <c r="AY23" t="n">
-        <v>6.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ23" t="n">
         <v>16</v>
@@ -6344,7 +6344,7 @@
         <v>32</v>
       </c>
       <c r="BE23" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="BF23" t="n">
         <v>13.5</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-07-18 06:20:25</t>
+          <t>2026-07-18 08:41:26</t>
         </is>
       </c>
     </row>
@@ -6448,7 +6448,7 @@
         <v>1.29</v>
       </c>
       <c r="G24" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="H24" t="n">
         <v>12</v>
@@ -6457,31 +6457,31 @@
         <v>13.5</v>
       </c>
       <c r="J24" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="K24" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="L24" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="M24" t="n">
         <v>1.03</v>
       </c>
       <c r="N24" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="O24" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="P24" t="n">
         <v>2.66</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="R24" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="S24" t="n">
         <v>2.38</v>
@@ -6496,40 +6496,40 @@
         <v>1.08</v>
       </c>
       <c r="W24" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="X24" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="Y24" t="n">
         <v>46</v>
       </c>
       <c r="Z24" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AA24" t="n">
-        <v>570</v>
+        <v>520</v>
       </c>
       <c r="AB24" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AC24" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AD24" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AE24" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AF24" t="n">
         <v>8.4</v>
       </c>
       <c r="AG24" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH24" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AI24" t="n">
         <v>1000</v>
@@ -6541,22 +6541,22 @@
         <v>13.5</v>
       </c>
       <c r="AL24" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AM24" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AN24" t="n">
         <v>4.3</v>
       </c>
       <c r="AO24" t="n">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AP24" t="n">
-        <v>19.5</v>
+        <v>24</v>
       </c>
       <c r="AQ24" t="n">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="AR24" t="n">
         <v>40</v>
@@ -6565,22 +6565,22 @@
         <v>55</v>
       </c>
       <c r="AT24" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU24" t="n">
         <v>13</v>
       </c>
       <c r="AV24" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AW24" t="n">
         <v>46</v>
       </c>
       <c r="AX24" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AY24" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AZ24" t="n">
         <v>21</v>
@@ -6589,19 +6589,19 @@
         <v>42</v>
       </c>
       <c r="BB24" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC24" t="n">
         <v>12</v>
       </c>
       <c r="BD24" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="BE24" t="n">
         <v>44</v>
       </c>
       <c r="BF24" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BG24" t="n">
         <v>48</v>
@@ -6628,13 +6628,13 @@
         <v>4</v>
       </c>
       <c r="BO24" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="BP24" t="n">
         <v>8</v>
       </c>
       <c r="BQ24" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="BR24" t="n">
         <v>23</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-07-18 06:20:25</t>
+          <t>2026-07-18 08:41:26</t>
         </is>
       </c>
     </row>
@@ -6690,239 +6690,239 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Halmstads</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Hacken</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>5.7</v>
+        <v>3.75</v>
       </c>
       <c r="G25" t="n">
-        <v>5.8</v>
+        <v>3.85</v>
       </c>
       <c r="H25" t="n">
-        <v>1.62</v>
+        <v>2.06</v>
       </c>
       <c r="I25" t="n">
-        <v>1.64</v>
+        <v>2.08</v>
       </c>
       <c r="J25" t="n">
-        <v>4.7</v>
+        <v>3.95</v>
       </c>
       <c r="K25" t="n">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="L25" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="M25" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="N25" t="n">
-        <v>6</v>
+        <v>4.9</v>
       </c>
       <c r="O25" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="P25" t="n">
-        <v>2.68</v>
+        <v>2.3</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="R25" t="n">
-        <v>1.66</v>
+        <v>1.5</v>
       </c>
       <c r="S25" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="U25" t="n">
         <v>2.38</v>
       </c>
-      <c r="T25" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="U25" t="n">
-        <v>2.46</v>
-      </c>
       <c r="V25" t="n">
-        <v>2.56</v>
+        <v>1.92</v>
       </c>
       <c r="W25" t="n">
-        <v>1.2</v>
+        <v>1.35</v>
       </c>
       <c r="X25" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="Y25" t="n">
         <v>12.5</v>
       </c>
       <c r="Z25" t="n">
+        <v>17</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>29</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>20</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>24</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>34</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>18</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>36</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>80</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>46</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>85</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>38</v>
+      </c>
+      <c r="AO25" t="n">
         <v>12</v>
       </c>
-      <c r="AA25" t="n">
+      <c r="AP25" t="n">
         <v>17</v>
       </c>
-      <c r="AB25" t="n">
-        <v>29</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AD25" t="n">
+      <c r="AQ25" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>13</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>21</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>15</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>6</v>
+      </c>
+      <c r="BG25" t="n">
         <v>10</v>
       </c>
-      <c r="AE25" t="n">
-        <v>15</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>55</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>22</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>28</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>160</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>680</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>330</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>75</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>50</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>22</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>11</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>11</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>15</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>25</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>10</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>44</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AZ25" t="n">
-        <v>16</v>
-      </c>
-      <c r="BA25" t="n">
-        <v>22</v>
-      </c>
-      <c r="BB25" t="n">
-        <v>42</v>
-      </c>
-      <c r="BC25" t="n">
-        <v>50</v>
-      </c>
-      <c r="BD25" t="n">
-        <v>48</v>
-      </c>
-      <c r="BE25" t="n">
-        <v>32</v>
-      </c>
-      <c r="BF25" t="n">
-        <v>38</v>
-      </c>
-      <c r="BG25" t="n">
-        <v>5.8</v>
-      </c>
       <c r="BH25" t="n">
         <v>1000</v>
       </c>
       <c r="BI25" t="n">
-        <v>2</v>
+        <v>1.01</v>
       </c>
       <c r="BJ25" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="BK25" t="n">
-        <v>1.74</v>
+        <v>1.01</v>
       </c>
       <c r="BL25" t="n">
         <v>1000</v>
       </c>
       <c r="BM25" t="n">
-        <v>2</v>
+        <v>1.01</v>
       </c>
       <c r="BN25" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="BO25" t="n">
-        <v>1.75</v>
+        <v>1.01</v>
       </c>
       <c r="BP25" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BQ25" t="n">
-        <v>1.94</v>
+        <v>1.01</v>
       </c>
       <c r="BR25" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BS25" t="n">
-        <v>1.94</v>
+        <v>1.01</v>
       </c>
       <c r="BT25" t="n">
-        <v>6.4</v>
+        <v>1000</v>
       </c>
       <c r="BU25" t="n">
-        <v>3.25</v>
+        <v>1.01</v>
       </c>
       <c r="BV25" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="BW25" t="n">
-        <v>1.76</v>
+        <v>1.01</v>
       </c>
       <c r="BX25" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="BY25" t="n">
-        <v>1.88</v>
+        <v>1.01</v>
       </c>
       <c r="BZ25" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="CA25" t="n">
-        <v>1.81</v>
+        <v>1.01</v>
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-07-18 06:20:25</t>
+          <t>2026-07-18 08:41:26</t>
         </is>
       </c>
     </row>
@@ -6944,239 +6944,239 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Halmstads</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Hacken</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>3.7</v>
+        <v>5.6</v>
       </c>
       <c r="G26" t="n">
-        <v>3.85</v>
+        <v>5.8</v>
       </c>
       <c r="H26" t="n">
-        <v>2.06</v>
+        <v>1.63</v>
       </c>
       <c r="I26" t="n">
-        <v>2.08</v>
+        <v>1.64</v>
       </c>
       <c r="J26" t="n">
-        <v>3.95</v>
+        <v>4.7</v>
       </c>
       <c r="K26" t="n">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="L26" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="M26" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="N26" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="O26" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="P26" t="n">
-        <v>2.3</v>
+        <v>2.68</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="R26" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="S26" t="n">
-        <v>2.78</v>
+        <v>2.36</v>
       </c>
       <c r="T26" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="U26" t="n">
-        <v>2.38</v>
+        <v>2.46</v>
       </c>
       <c r="V26" t="n">
-        <v>1.92</v>
+        <v>2.56</v>
       </c>
       <c r="W26" t="n">
-        <v>1.35</v>
+        <v>1.21</v>
       </c>
       <c r="X26" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="Y26" t="n">
         <v>12.5</v>
       </c>
       <c r="Z26" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA26" t="n">
         <v>17</v>
       </c>
-      <c r="AA26" t="n">
+      <c r="AB26" t="n">
         <v>29</v>
       </c>
-      <c r="AB26" t="n">
+      <c r="AC26" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>15</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>180</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>22</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>18</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>28</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>160</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>65</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>75</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>50</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>22</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>11</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>25</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>44</v>
+      </c>
+      <c r="AY26" t="n">
         <v>20</v>
       </c>
-      <c r="AC26" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>11</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>24</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>34</v>
-      </c>
-      <c r="AG26" t="n">
+      <c r="AZ26" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>22</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>42</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>50</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>48</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>32</v>
+      </c>
+      <c r="BF26" t="n">
+        <v>38</v>
+      </c>
+      <c r="BG26" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BH26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI26" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ26" t="n">
+        <v>13</v>
+      </c>
+      <c r="BK26" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BL26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM26" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN26" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BO26" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BP26" t="n">
+        <v>55</v>
+      </c>
+      <c r="BQ26" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="BR26" t="n">
+        <v>55</v>
+      </c>
+      <c r="BS26" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="BT26" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BU26" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BV26" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BW26" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="BX26" t="n">
+        <v>29</v>
+      </c>
+      <c r="BY26" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BZ26" t="n">
         <v>18</v>
       </c>
-      <c r="AH26" t="n">
-        <v>19</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>36</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>80</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>46</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>50</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>85</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>38</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>12</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>17</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>13</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>21</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>15</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AY26" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AZ26" t="n">
-        <v>14</v>
-      </c>
-      <c r="BA26" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BB26" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BC26" t="n">
-        <v>6</v>
-      </c>
-      <c r="BD26" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BE26" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BF26" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BG26" t="n">
-        <v>10</v>
-      </c>
-      <c r="BH26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI26" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BJ26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK26" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM26" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO26" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BP26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ26" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BR26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS26" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BT26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU26" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BV26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW26" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BX26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY26" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BZ26" t="n">
-        <v>1000</v>
-      </c>
       <c r="CA26" t="n">
-        <v>1.01</v>
+        <v>1.81</v>
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-07-18 06:20:25</t>
+          <t>2026-07-18 08:41:26</t>
         </is>
       </c>
     </row>
@@ -7216,10 +7216,10 @@
         <v>1.72</v>
       </c>
       <c r="I27" t="n">
-        <v>1000</v>
+        <v>2.68</v>
       </c>
       <c r="J27" t="n">
-        <v>1.8</v>
+        <v>3.2</v>
       </c>
       <c r="K27" t="n">
         <v>4</v>
@@ -7231,7 +7231,7 @@
         <v>1.01</v>
       </c>
       <c r="N27" t="n">
-        <v>1.29</v>
+        <v>1.1</v>
       </c>
       <c r="O27" t="n">
         <v>1.15</v>
@@ -7243,7 +7243,7 @@
         <v>1.15</v>
       </c>
       <c r="R27" t="n">
-        <v>1.28</v>
+        <v>1.43</v>
       </c>
       <c r="S27" t="n">
         <v>1.14</v>
@@ -7255,10 +7255,10 @@
         <v>1.11</v>
       </c>
       <c r="V27" t="n">
-        <v>1.01</v>
+        <v>1.74</v>
       </c>
       <c r="W27" t="n">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="X27" t="n">
         <v>1000</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-07-18 06:20:25</t>
+          <t>2026-07-18 08:41:26</t>
         </is>
       </c>
     </row>
@@ -7464,7 +7464,7 @@
         <v>6.2</v>
       </c>
       <c r="G28" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="H28" t="n">
         <v>1.58</v>
@@ -7491,19 +7491,19 @@
         <v>1.25</v>
       </c>
       <c r="P28" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="Q28" t="n">
         <v>1.72</v>
       </c>
       <c r="R28" t="n">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="S28" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="T28" t="n">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="U28" t="n">
         <v>2.06</v>
@@ -7512,115 +7512,115 @@
         <v>2.58</v>
       </c>
       <c r="W28" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X28" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="Y28" t="n">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z28" t="n">
-        <v>970</v>
+        <v>10.5</v>
       </c>
       <c r="AA28" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AB28" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AC28" t="n">
-        <v>970</v>
+        <v>10.5</v>
       </c>
       <c r="AD28" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AE28" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AF28" t="n">
         <v>65</v>
       </c>
       <c r="AG28" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AH28" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI28" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="AJ28" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AK28" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AL28" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AM28" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN28" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AO28" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>16</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AR28" t="n">
         <v>9</v>
       </c>
-      <c r="AP28" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AQ28" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AR28" t="n">
-        <v>7.8</v>
-      </c>
       <c r="AS28" t="n">
-        <v>1.83</v>
+        <v>12.5</v>
       </c>
       <c r="AT28" t="n">
-        <v>1.83</v>
+        <v>19.5</v>
       </c>
       <c r="AU28" t="n">
-        <v>1.65</v>
+        <v>9</v>
       </c>
       <c r="AV28" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AW28" t="n">
-        <v>1.83</v>
+        <v>14</v>
       </c>
       <c r="AX28" t="n">
-        <v>1.78</v>
+        <v>44</v>
       </c>
       <c r="AY28" t="n">
-        <v>1.83</v>
+        <v>20</v>
       </c>
       <c r="AZ28" t="n">
-        <v>1.83</v>
+        <v>18</v>
       </c>
       <c r="BA28" t="n">
-        <v>1.75</v>
+        <v>7.6</v>
       </c>
       <c r="BB28" t="n">
-        <v>1.83</v>
+        <v>9.4</v>
       </c>
       <c r="BC28" t="n">
-        <v>1.83</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BD28" t="n">
-        <v>1.83</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE28" t="n">
-        <v>1.83</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF28" t="n">
-        <v>1.83</v>
+        <v>9</v>
       </c>
       <c r="BG28" t="n">
-        <v>1.51</v>
+        <v>6.8</v>
       </c>
       <c r="BH28" t="n">
         <v>1000</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-07-18 06:20:25</t>
+          <t>2026-07-18 08:41:26</t>
         </is>
       </c>
     </row>
@@ -7724,7 +7724,7 @@
         <v>2.66</v>
       </c>
       <c r="I29" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="J29" t="n">
         <v>2.82</v>
@@ -7733,34 +7733,34 @@
         <v>3.5</v>
       </c>
       <c r="L29" t="n">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="M29" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N29" t="n">
-        <v>2.32</v>
+        <v>2.98</v>
       </c>
       <c r="O29" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="P29" t="n">
         <v>1.67</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.06</v>
+        <v>2.22</v>
       </c>
       <c r="R29" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="S29" t="n">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="T29" t="n">
-        <v>1.63</v>
+        <v>1.86</v>
       </c>
       <c r="U29" t="n">
-        <v>1.69</v>
+        <v>1.95</v>
       </c>
       <c r="V29" t="n">
         <v>1.48</v>
@@ -7769,91 +7769,91 @@
         <v>1.46</v>
       </c>
       <c r="X29" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Y29" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Z29" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AA29" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AB29" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AC29" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AD29" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AE29" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AF29" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AG29" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AH29" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI29" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ29" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AK29" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AL29" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AM29" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN29" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AO29" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AQ29" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AR29" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AS29" t="n">
         <v>1.01</v>
       </c>
       <c r="AT29" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AU29" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AV29" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AW29" t="n">
         <v>1.01</v>
       </c>
       <c r="AX29" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AY29" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AZ29" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BA29" t="n">
         <v>1.01</v>
@@ -7877,55 +7877,55 @@
         <v>1.01</v>
       </c>
       <c r="BH29" t="n">
-        <v>1000</v>
+        <v>3.35</v>
       </c>
       <c r="BI29" t="n">
-        <v>1.01</v>
+        <v>2.52</v>
       </c>
       <c r="BJ29" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK29" t="n">
         <v>1.01</v>
       </c>
       <c r="BL29" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="BM29" t="n">
         <v>1.01</v>
       </c>
       <c r="BN29" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BO29" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BP29" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BQ29" t="n">
         <v>1.01</v>
       </c>
       <c r="BR29" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BS29" t="n">
         <v>1.01</v>
       </c>
       <c r="BT29" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BU29" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BV29" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BW29" t="n">
         <v>1.01</v>
       </c>
       <c r="BX29" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BY29" t="n">
         <v>1.01</v>
@@ -7938,14 +7938,14 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-07-18 06:20:25</t>
+          <t>2026-07-18 08:41:26</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Estonian Premier League</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -7960,246 +7960,246 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Cerro</t>
+          <t>Harju JK Laagri</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Racing Club (Uru)</t>
+          <t>Paide Linnameeskond</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>5.9</v>
+        <v>4</v>
       </c>
       <c r="G30" t="n">
-        <v>6.8</v>
+        <v>4.9</v>
       </c>
       <c r="H30" t="n">
         <v>1.74</v>
       </c>
       <c r="I30" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="J30" t="n">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="K30" t="n">
-        <v>3.65</v>
+        <v>4.7</v>
       </c>
       <c r="L30" t="n">
-        <v>1.58</v>
+        <v>1.28</v>
       </c>
       <c r="M30" t="n">
-        <v>1.13</v>
+        <v>1.04</v>
       </c>
       <c r="N30" t="n">
-        <v>2.54</v>
+        <v>4.7</v>
       </c>
       <c r="O30" t="n">
-        <v>1.56</v>
+        <v>1.22</v>
       </c>
       <c r="P30" t="n">
-        <v>1.52</v>
+        <v>2.24</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.66</v>
+        <v>1.64</v>
       </c>
       <c r="R30" t="n">
-        <v>1.18</v>
+        <v>1.5</v>
       </c>
       <c r="S30" t="n">
-        <v>5.5</v>
+        <v>2.5</v>
       </c>
       <c r="T30" t="n">
-        <v>2.4</v>
+        <v>1.65</v>
       </c>
       <c r="U30" t="n">
-        <v>1.62</v>
+        <v>2.24</v>
       </c>
       <c r="V30" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="W30" t="n">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="X30" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>22</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>24</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>20</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>44</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>34</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>110</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>55</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>90</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>55</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH30" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BI30" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="BJ30" t="n">
         <v>11</v>
       </c>
-      <c r="Y30" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AA30" t="n">
+      <c r="BK30" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BL30" t="n">
+        <v>110</v>
+      </c>
+      <c r="BM30" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BN30" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BO30" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BP30" t="n">
+        <v>42</v>
+      </c>
+      <c r="BQ30" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BR30" t="n">
+        <v>46</v>
+      </c>
+      <c r="BS30" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BT30" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BU30" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="BV30" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BW30" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BX30" t="n">
         <v>24</v>
       </c>
-      <c r="AB30" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>32</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>60</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>34</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>40</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>80</v>
-      </c>
-      <c r="AJ30" t="n">
-        <v>290</v>
-      </c>
-      <c r="AK30" t="n">
-        <v>170</v>
-      </c>
-      <c r="AL30" t="n">
-        <v>190</v>
-      </c>
-      <c r="AM30" t="n">
-        <v>360</v>
-      </c>
-      <c r="AN30" t="n">
-        <v>340</v>
-      </c>
-      <c r="AO30" t="n">
-        <v>26</v>
-      </c>
-      <c r="AP30" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AQ30" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AR30" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AS30" t="n">
-        <v>17</v>
-      </c>
-      <c r="AT30" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AU30" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV30" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AW30" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AX30" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AY30" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AZ30" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BA30" t="n">
+      <c r="BY30" t="n">
         <v>4.9</v>
       </c>
-      <c r="BB30" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BC30" t="n">
-        <v>5</v>
-      </c>
-      <c r="BD30" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BE30" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BF30" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BG30" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BH30" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BI30" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="BJ30" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BK30" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BL30" t="n">
-        <v>340</v>
-      </c>
-      <c r="BM30" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BN30" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BO30" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BP30" t="n">
-        <v>90</v>
-      </c>
-      <c r="BQ30" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BR30" t="n">
-        <v>120</v>
-      </c>
-      <c r="BS30" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BT30" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BU30" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="BV30" t="n">
-        <v>17</v>
-      </c>
-      <c r="BW30" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BX30" t="n">
-        <v>50</v>
-      </c>
-      <c r="BY30" t="n">
-        <v>1.04</v>
-      </c>
       <c r="BZ30" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="CA30" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-07-18 06:20:25</t>
+          <t>2026-07-18 08:41:26</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Peruvian Primera Division</t>
+          <t>Icelandic Urvalsdeild</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -8214,246 +8214,246 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>CD Los Chankas</t>
+          <t>KR Reykjavik</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Sport Boys (Per)</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>1.36</v>
+        <v>1.01</v>
       </c>
       <c r="M31" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="N31" t="n">
-        <v>3.35</v>
+        <v>1.25</v>
       </c>
       <c r="O31" t="n">
-        <v>1.35</v>
+        <v>1.01</v>
       </c>
       <c r="P31" t="n">
-        <v>1.82</v>
+        <v>1.25</v>
       </c>
       <c r="Q31" t="n">
-        <v>2</v>
+        <v>1.01</v>
       </c>
       <c r="R31" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="S31" t="n">
-        <v>3.7</v>
+        <v>1.05</v>
       </c>
       <c r="T31" t="n">
-        <v>1.95</v>
+        <v>1.11</v>
       </c>
       <c r="U31" t="n">
-        <v>1.84</v>
+        <v>1.11</v>
       </c>
       <c r="V31" t="n">
-        <v>1.17</v>
+        <v>1.01</v>
       </c>
       <c r="W31" t="n">
-        <v>2.26</v>
+        <v>1.01</v>
       </c>
       <c r="X31" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="Y31" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="Z31" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AA31" t="n">
-        <v>220</v>
+        <v>1000</v>
       </c>
       <c r="AB31" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="AC31" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AD31" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AE31" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AF31" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AG31" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AH31" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AI31" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AJ31" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AK31" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AL31" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AM31" t="n">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AN31" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AO31" t="n">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AP31" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AQ31" t="n">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="AR31" t="n">
-        <v>34</v>
+        <v>1.01</v>
       </c>
       <c r="AS31" t="n">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="AT31" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AU31" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AV31" t="n">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="AW31" t="n">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="AX31" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AY31" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AZ31" t="n">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="BA31" t="n">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="BB31" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC31" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="BD31" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BE31" t="n">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="BF31" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BG31" t="n">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="BH31" t="n">
-        <v>3.8</v>
+        <v>1000</v>
       </c>
       <c r="BI31" t="n">
-        <v>2.64</v>
+        <v>1.01</v>
       </c>
       <c r="BJ31" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="BK31" t="n">
         <v>1.01</v>
       </c>
       <c r="BL31" t="n">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="BM31" t="n">
         <v>1.01</v>
       </c>
       <c r="BN31" t="n">
-        <v>4.9</v>
+        <v>1000</v>
       </c>
       <c r="BO31" t="n">
-        <v>3.25</v>
+        <v>1.01</v>
       </c>
       <c r="BP31" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="BQ31" t="n">
         <v>1.01</v>
       </c>
       <c r="BR31" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BS31" t="n">
         <v>1.01</v>
       </c>
       <c r="BT31" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BU31" t="n">
         <v>1.01</v>
       </c>
       <c r="BV31" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="BW31" t="n">
         <v>1.01</v>
       </c>
       <c r="BX31" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="BY31" t="n">
         <v>1.01</v>
       </c>
       <c r="BZ31" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="CA31" t="n">
         <v>1.01</v>
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-07-18 06:20:25</t>
+          <t>2026-07-18 08:41:26</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Lithuanian A Lyga</t>
+          <t>Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -8468,67 +8468,67 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VMFD Zalgiris</t>
+          <t>FC Ordabasy</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Elimai FC</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1.92</v>
+        <v>1.04</v>
       </c>
       <c r="G32" t="n">
-        <v>2.16</v>
+        <v>1.79</v>
       </c>
       <c r="H32" t="n">
-        <v>3.7</v>
+        <v>2.3</v>
       </c>
       <c r="I32" t="n">
-        <v>4.8</v>
+        <v>1000</v>
       </c>
       <c r="J32" t="n">
-        <v>3.65</v>
+        <v>1.01</v>
       </c>
       <c r="K32" t="n">
-        <v>4.3</v>
+        <v>1000</v>
       </c>
       <c r="L32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N32" t="n">
         <v>1.25</v>
       </c>
-      <c r="M32" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="N32" t="n">
-        <v>1.1</v>
-      </c>
       <c r="O32" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="P32" t="n">
-        <v>2.1</v>
+        <v>1.25</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.65</v>
+        <v>1.28</v>
       </c>
       <c r="R32" t="n">
-        <v>1.35</v>
+        <v>1.07</v>
       </c>
       <c r="S32" t="n">
-        <v>2.26</v>
+        <v>1.28</v>
       </c>
       <c r="T32" t="n">
         <v>1.11</v>
       </c>
       <c r="U32" t="n">
-        <v>1.96</v>
+        <v>1.11</v>
       </c>
       <c r="V32" t="n">
-        <v>1.26</v>
+        <v>1.02</v>
       </c>
       <c r="W32" t="n">
-        <v>1.86</v>
+        <v>2.26</v>
       </c>
       <c r="X32" t="n">
         <v>1000</v>
@@ -8693,21 +8693,21 @@
         <v>1.01</v>
       </c>
       <c r="BZ32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-07-18 06:20:25</t>
+          <t>2026-07-18 08:41:26</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Slovenian Premier League</t>
+          <t>Lithuanian A Lyga</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -8722,175 +8722,175 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NK Aluminij</t>
+          <t>VMFD Zalgiris</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>NK Maribor</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>5.3</v>
+        <v>1.92</v>
       </c>
       <c r="G33" t="n">
-        <v>6.4</v>
+        <v>2.1</v>
       </c>
       <c r="H33" t="n">
-        <v>1.53</v>
+        <v>3.75</v>
       </c>
       <c r="I33" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J33" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="K33" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L33" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="M33" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N33" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O33" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="P33" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S33" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="T33" t="n">
         <v>1.66</v>
       </c>
-      <c r="J33" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="K33" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="L33" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="M33" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N33" t="n">
-        <v>6</v>
-      </c>
-      <c r="O33" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="P33" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="R33" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="S33" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="T33" t="n">
-        <v>1.6</v>
-      </c>
       <c r="U33" t="n">
-        <v>2.34</v>
+        <v>2.24</v>
       </c>
       <c r="V33" t="n">
-        <v>2.5</v>
+        <v>1.29</v>
       </c>
       <c r="W33" t="n">
-        <v>1.18</v>
+        <v>1.9</v>
       </c>
       <c r="X33" t="n">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="Y33" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="Z33" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="AA33" t="n">
-        <v>17</v>
+        <v>90</v>
       </c>
       <c r="AB33" t="n">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="AC33" t="n">
-        <v>14.5</v>
+        <v>10.5</v>
       </c>
       <c r="AD33" t="n">
+        <v>19</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG33" t="n">
         <v>12.5</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>55</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>24</v>
       </c>
       <c r="AH33" t="n">
         <v>19.5</v>
       </c>
       <c r="AI33" t="n">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="AJ33" t="n">
-        <v>150</v>
+        <v>25</v>
       </c>
       <c r="AK33" t="n">
-        <v>65</v>
+        <v>23</v>
       </c>
       <c r="AL33" t="n">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="AM33" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AN33" t="n">
-        <v>60</v>
+        <v>13.5</v>
       </c>
       <c r="AO33" t="n">
-        <v>6</v>
+        <v>42</v>
       </c>
       <c r="AP33" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="AQ33" t="n">
-        <v>9.800000000000001</v>
+        <v>13.5</v>
       </c>
       <c r="AR33" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AS33" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="AT33" t="n">
-        <v>24</v>
+        <v>8.4</v>
       </c>
       <c r="AU33" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AV33" t="n">
-        <v>7.8</v>
+        <v>12.5</v>
       </c>
       <c r="AW33" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AX33" t="n">
-        <v>36</v>
+        <v>10.5</v>
       </c>
       <c r="AY33" t="n">
-        <v>19</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ33" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BA33" t="n">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="BB33" t="n">
-        <v>85</v>
+        <v>17.5</v>
       </c>
       <c r="BC33" t="n">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="BD33" t="n">
-        <v>38</v>
+        <v>1.01</v>
       </c>
       <c r="BE33" t="n">
-        <v>48</v>
+        <v>1.01</v>
       </c>
       <c r="BF33" t="n">
-        <v>34</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG33" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BH33" t="n">
         <v>1000</v>
@@ -8947,21 +8947,21 @@
         <v>1.01</v>
       </c>
       <c r="BZ33" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA33" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-07-18 06:20:25</t>
+          <t>2026-07-18 08:41:26</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Icelandic Urvalsdeild</t>
+          <t>Peruvian Primera Division</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -8976,246 +8976,246 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>KR Reykjavik</t>
+          <t>CD Los Chankas</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Sport Boys (Per)</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="I34" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="K34" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="L34" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="M34" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N34" t="n">
-        <v>1.25</v>
+        <v>3.4</v>
       </c>
       <c r="O34" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="P34" t="n">
-        <v>1.25</v>
+        <v>1.81</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="R34" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="S34" t="n">
-        <v>1.05</v>
+        <v>3.7</v>
       </c>
       <c r="T34" t="n">
-        <v>1.11</v>
+        <v>1.97</v>
       </c>
       <c r="U34" t="n">
-        <v>1.11</v>
+        <v>1.86</v>
       </c>
       <c r="V34" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="W34" t="n">
-        <v>1.01</v>
+        <v>2.26</v>
       </c>
       <c r="X34" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="Y34" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Z34" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AA34" t="n">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AB34" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AC34" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD34" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AE34" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AF34" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AG34" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH34" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AI34" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AK34" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AL34" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AM34" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AN34" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AO34" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AP34" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AR34" t="n">
-        <v>1.01</v>
+        <v>34</v>
       </c>
       <c r="AS34" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AT34" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="AU34" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AV34" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="AW34" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AX34" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AY34" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AZ34" t="n">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BA34" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BB34" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BC34" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BD34" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BE34" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BF34" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BG34" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BH34" t="n">
-        <v>1000</v>
+        <v>3.8</v>
       </c>
       <c r="BI34" t="n">
-        <v>1.01</v>
+        <v>2.92</v>
       </c>
       <c r="BJ34" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BK34" t="n">
         <v>1.01</v>
       </c>
       <c r="BL34" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="BM34" t="n">
         <v>1.01</v>
       </c>
       <c r="BN34" t="n">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="BO34" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="BP34" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="BQ34" t="n">
         <v>1.01</v>
       </c>
       <c r="BR34" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BS34" t="n">
         <v>1.01</v>
       </c>
       <c r="BT34" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BU34" t="n">
         <v>1.01</v>
       </c>
       <c r="BV34" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="BW34" t="n">
         <v>1.01</v>
       </c>
       <c r="BX34" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="BY34" t="n">
         <v>1.01</v>
       </c>
       <c r="BZ34" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="CA34" t="n">
         <v>1.01</v>
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-07-18 06:20:25</t>
+          <t>2026-07-18 08:41:26</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Estonian Premier League</t>
+          <t>Slovenian Premier League</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -9230,166 +9230,166 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Harju JK Laagri</t>
+          <t>NK Aluminij</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Paide Linnameeskond</t>
+          <t>NK Maribor</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>3.9</v>
+        <v>5.3</v>
       </c>
       <c r="G35" t="n">
-        <v>4.7</v>
+        <v>6.4</v>
       </c>
       <c r="H35" t="n">
-        <v>1.77</v>
+        <v>1.53</v>
       </c>
       <c r="I35" t="n">
-        <v>1.91</v>
+        <v>1.65</v>
       </c>
       <c r="J35" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="K35" t="n">
-        <v>4.6</v>
+        <v>5.5</v>
       </c>
       <c r="L35" t="n">
-        <v>1.28</v>
+        <v>1.17</v>
       </c>
       <c r="M35" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="N35" t="n">
-        <v>4.4</v>
+        <v>6</v>
       </c>
       <c r="O35" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="P35" t="n">
-        <v>2.24</v>
+        <v>2.72</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="R35" t="n">
-        <v>1.52</v>
+        <v>1.69</v>
       </c>
       <c r="S35" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="U35" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="V35" t="n">
         <v>2.56</v>
       </c>
-      <c r="T35" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="U35" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="V35" t="n">
-        <v>2.12</v>
-      </c>
       <c r="W35" t="n">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="X35" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="Y35" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Z35" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AA35" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AB35" t="n">
+        <v>30</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>55</v>
+      </c>
+      <c r="AG35" t="n">
         <v>24</v>
       </c>
-      <c r="AC35" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE35" t="n">
-        <v>21</v>
-      </c>
-      <c r="AF35" t="n">
-        <v>44</v>
-      </c>
-      <c r="AG35" t="n">
-        <v>1000</v>
-      </c>
       <c r="AH35" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AI35" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AJ35" t="n">
-        <v>110</v>
+        <v>150</v>
       </c>
       <c r="AK35" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AL35" t="n">
         <v>60</v>
       </c>
       <c r="AM35" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AN35" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AO35" t="n">
-        <v>10.5</v>
+        <v>6</v>
       </c>
       <c r="AP35" t="n">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="AQ35" t="n">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR35" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS35" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AT35" t="n">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="AU35" t="n">
-        <v>7.6</v>
+        <v>10</v>
       </c>
       <c r="AV35" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AW35" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AX35" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="AY35" t="n">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="AZ35" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BA35" t="n">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="BB35" t="n">
         <v>1.01</v>
       </c>
       <c r="BC35" t="n">
-        <v>1.01</v>
+        <v>42</v>
       </c>
       <c r="BD35" t="n">
-        <v>1.01</v>
+        <v>38</v>
       </c>
       <c r="BE35" t="n">
         <v>1.01</v>
@@ -9398,78 +9398,78 @@
         <v>1.01</v>
       </c>
       <c r="BG35" t="n">
-        <v>7</v>
+        <v>4.4</v>
       </c>
       <c r="BH35" t="n">
-        <v>4.6</v>
+        <v>1000</v>
       </c>
       <c r="BI35" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BJ35" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BK35" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BL35" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="BM35" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BN35" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="BO35" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BP35" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BQ35" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BR35" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="BS35" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BT35" t="n">
-        <v>4.9</v>
+        <v>1000</v>
       </c>
       <c r="BU35" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BV35" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="BW35" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BX35" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="BY35" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BZ35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-07-18 06:20:25</t>
+          <t>2026-07-18 08:41:26</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Kazakhstan Premier League</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -9484,246 +9484,246 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>FC Ordabasy</t>
+          <t>Cerro</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Elimai FC</t>
+          <t>Racing Club (Uru)</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1.04</v>
+        <v>5.9</v>
       </c>
       <c r="G36" t="n">
-        <v>1.79</v>
+        <v>6.8</v>
       </c>
       <c r="H36" t="n">
-        <v>2.3</v>
+        <v>1.74</v>
       </c>
       <c r="I36" t="n">
-        <v>1000</v>
+        <v>1.83</v>
       </c>
       <c r="J36" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="K36" t="n">
-        <v>1000</v>
+        <v>3.65</v>
       </c>
       <c r="L36" t="n">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="M36" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="N36" t="n">
-        <v>1.25</v>
+        <v>2.54</v>
       </c>
       <c r="O36" t="n">
-        <v>1.28</v>
+        <v>1.56</v>
       </c>
       <c r="P36" t="n">
-        <v>1.25</v>
+        <v>1.52</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.28</v>
+        <v>2.66</v>
       </c>
       <c r="R36" t="n">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="S36" t="n">
-        <v>1.28</v>
+        <v>5.5</v>
       </c>
       <c r="T36" t="n">
-        <v>1.11</v>
+        <v>2.4</v>
       </c>
       <c r="U36" t="n">
-        <v>1.11</v>
+        <v>1.62</v>
       </c>
       <c r="V36" t="n">
-        <v>1.02</v>
+        <v>2.2</v>
       </c>
       <c r="W36" t="n">
-        <v>2.26</v>
+        <v>1.17</v>
       </c>
       <c r="X36" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="Y36" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="Z36" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AA36" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AB36" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AC36" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AD36" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AE36" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AF36" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AG36" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AH36" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AI36" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AJ36" t="n">
-        <v>1000</v>
+        <v>290</v>
       </c>
       <c r="AK36" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AL36" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AM36" t="n">
-        <v>1000</v>
+        <v>360</v>
       </c>
       <c r="AN36" t="n">
-        <v>1000</v>
+        <v>340</v>
       </c>
       <c r="AO36" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AP36" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AQ36" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AR36" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AS36" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="AT36" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AU36" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AV36" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AW36" t="n">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="AX36" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AY36" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AZ36" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BA36" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BB36" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BC36" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BD36" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BE36" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BF36" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BG36" t="n">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="BH36" t="n">
-        <v>1000</v>
+        <v>3.1</v>
       </c>
       <c r="BI36" t="n">
-        <v>1.01</v>
+        <v>2.2</v>
       </c>
       <c r="BJ36" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="BK36" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BL36" t="n">
-        <v>1000</v>
+        <v>330</v>
       </c>
       <c r="BM36" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BN36" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BO36" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="BP36" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="BQ36" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BR36" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="BS36" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BT36" t="n">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="BU36" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="BV36" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="BW36" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BX36" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BY36" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BZ36" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="CA36" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-07-18 06:20:25</t>
+          <t>2026-07-18 08:41:26</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Bulgarian A League</t>
+          <t>Romanian Liga I</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -9738,246 +9738,246 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>ACS Petrolul 52</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Dinamo Bucharest</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>2.88</v>
+        <v>3.9</v>
       </c>
       <c r="G37" t="n">
-        <v>3.2</v>
+        <v>4.4</v>
       </c>
       <c r="H37" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="I37" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="J37" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="K37" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L37" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="M37" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N37" t="n">
         <v>2.98</v>
       </c>
-      <c r="I37" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="J37" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="K37" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="L37" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="M37" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N37" t="n">
-        <v>2.46</v>
-      </c>
       <c r="O37" t="n">
-        <v>1.53</v>
+        <v>1.43</v>
       </c>
       <c r="P37" t="n">
-        <v>1.49</v>
+        <v>1.67</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.7</v>
+        <v>2.22</v>
       </c>
       <c r="R37" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="S37" t="n">
-        <v>5.5</v>
+        <v>4.3</v>
       </c>
       <c r="T37" t="n">
-        <v>1.99</v>
+        <v>1.92</v>
       </c>
       <c r="U37" t="n">
-        <v>1.38</v>
+        <v>1.9</v>
       </c>
       <c r="V37" t="n">
-        <v>1.43</v>
+        <v>1.84</v>
       </c>
       <c r="W37" t="n">
-        <v>1.46</v>
+        <v>1.29</v>
       </c>
       <c r="X37" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Y37" t="n">
         <v>9</v>
       </c>
       <c r="Z37" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AA37" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AB37" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AC37" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AD37" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AE37" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AF37" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AG37" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AH37" t="n">
         <v>24</v>
       </c>
       <c r="AI37" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ37" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AK37" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AL37" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AM37" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AN37" t="n">
+        <v>95</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>27</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>9</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AU37" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV37" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AW37" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AX37" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AY37" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AZ37" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BA37" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB37" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BC37" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BD37" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BE37" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BF37" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BG37" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BH37" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BI37" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BJ37" t="n">
+        <v>12</v>
+      </c>
+      <c r="BK37" t="n">
+        <v>7</v>
+      </c>
+      <c r="BL37" t="n">
+        <v>190</v>
+      </c>
+      <c r="BM37" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BN37" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BO37" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BP37" t="n">
+        <v>44</v>
+      </c>
+      <c r="BQ37" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BR37" t="n">
         <v>65</v>
       </c>
-      <c r="AO37" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP37" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AQ37" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AR37" t="n">
-        <v>16</v>
-      </c>
-      <c r="AS37" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AT37" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AU37" t="n">
+      <c r="BS37" t="n">
         <v>6</v>
       </c>
-      <c r="AV37" t="n">
-        <v>12</v>
-      </c>
-      <c r="AW37" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AX37" t="n">
-        <v>15</v>
-      </c>
-      <c r="AY37" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AZ37" t="n">
-        <v>19</v>
-      </c>
-      <c r="BA37" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BB37" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BC37" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BD37" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BE37" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BF37" t="n">
-        <v>40</v>
-      </c>
-      <c r="BG37" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BH37" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI37" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="BJ37" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK37" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="BL37" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM37" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="BN37" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO37" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="BP37" t="n">
-        <v>40</v>
-      </c>
-      <c r="BQ37" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BR37" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS37" t="n">
-        <v>1.05</v>
-      </c>
       <c r="BT37" t="n">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="BU37" t="n">
-        <v>1.05</v>
+        <v>4.1</v>
       </c>
       <c r="BV37" t="n">
-        <v>44</v>
+        <v>19.5</v>
       </c>
       <c r="BW37" t="n">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="BX37" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BY37" t="n">
-        <v>1.05</v>
+        <v>5.7</v>
       </c>
       <c r="BZ37" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="CA37" t="n">
-        <v>1.05</v>
+        <v>5.7</v>
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-07-18 06:20:25</t>
+          <t>2026-07-18 08:41:26</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Romanian Liga I</t>
+          <t>Bulgarian A League</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -9992,239 +9992,239 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>ACS Petrolul 52</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Dinamo Bucharest</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>3.9</v>
+        <v>2.9</v>
       </c>
       <c r="G38" t="n">
-        <v>4.4</v>
+        <v>3.1</v>
       </c>
       <c r="H38" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="I38" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J38" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="K38" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="L38" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="M38" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="N38" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="O38" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="P38" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S38" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="T38" t="n">
         <v>2.08</v>
       </c>
-      <c r="I38" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="J38" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="K38" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="L38" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M38" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N38" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="O38" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="P38" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="R38" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S38" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="T38" t="n">
-        <v>1.92</v>
-      </c>
       <c r="U38" t="n">
-        <v>1.88</v>
+        <v>1.75</v>
       </c>
       <c r="V38" t="n">
-        <v>1.84</v>
+        <v>1.44</v>
       </c>
       <c r="W38" t="n">
-        <v>1.29</v>
+        <v>1.47</v>
       </c>
       <c r="X38" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="Y38" t="n">
         <v>9</v>
       </c>
       <c r="Z38" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AA38" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AB38" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AC38" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="AD38" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AE38" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AF38" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AG38" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AH38" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI38" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AJ38" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AK38" t="n">
+        <v>48</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>85</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>230</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>60</v>
+      </c>
+      <c r="AO38" t="n">
         <v>65</v>
       </c>
-      <c r="AL38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO38" t="n">
-        <v>1000</v>
-      </c>
       <c r="AP38" t="n">
-        <v>9</v>
+        <v>6.2</v>
       </c>
       <c r="AQ38" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>16</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AU38" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV38" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW38" t="n">
+        <v>38</v>
+      </c>
+      <c r="AX38" t="n">
+        <v>15</v>
+      </c>
+      <c r="AY38" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AZ38" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA38" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB38" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BC38" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BD38" t="n">
+        <v>6</v>
+      </c>
+      <c r="BE38" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BF38" t="n">
+        <v>40</v>
+      </c>
+      <c r="BG38" t="n">
+        <v>42</v>
+      </c>
+      <c r="BH38" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BI38" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BJ38" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BK38" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BL38" t="n">
+        <v>260</v>
+      </c>
+      <c r="BM38" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BN38" t="n">
         <v>6.8</v>
       </c>
-      <c r="AR38" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AS38" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AT38" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AU38" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV38" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AW38" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AX38" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AY38" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AZ38" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BA38" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="BB38" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="BC38" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="BD38" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="BE38" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="BF38" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="BG38" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BH38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI38" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BJ38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK38" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BL38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM38" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BN38" t="n">
-        <v>9.800000000000001</v>
-      </c>
       <c r="BO38" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BP38" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BQ38" t="n">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="BR38" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BS38" t="n">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="BT38" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BU38" t="n">
-        <v>3.3</v>
+        <v>5</v>
       </c>
       <c r="BV38" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BW38" t="n">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="BX38" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BY38" t="n">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="BZ38" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="CA38" t="n">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-07-18 06:20:25</t>
+          <t>2026-07-18 08:41:26</t>
         </is>
       </c>
     </row>
@@ -10264,157 +10264,157 @@
         <v>2.32</v>
       </c>
       <c r="I39" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="J39" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="K39" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="L39" t="n">
         <v>1.01</v>
       </c>
       <c r="M39" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N39" t="n">
-        <v>2.14</v>
+        <v>3</v>
       </c>
       <c r="O39" t="n">
         <v>1.42</v>
       </c>
       <c r="P39" t="n">
-        <v>1.54</v>
+        <v>1.68</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="R39" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="S39" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="T39" t="n">
-        <v>1.76</v>
+        <v>1.87</v>
       </c>
       <c r="U39" t="n">
-        <v>1.78</v>
+        <v>1.93</v>
       </c>
       <c r="V39" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="W39" t="n">
         <v>1.35</v>
       </c>
       <c r="X39" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Y39" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="Z39" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AA39" t="n">
+        <v>36</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>30</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>25</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI39" t="n">
         <v>50</v>
       </c>
-      <c r="AB39" t="n">
-        <v>15</v>
-      </c>
-      <c r="AC39" t="n">
+      <c r="AJ39" t="n">
+        <v>70</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>50</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>150</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>60</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>28</v>
+      </c>
+      <c r="AP39" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AQ39" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AT39" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AU39" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV39" t="n">
         <v>10</v>
       </c>
-      <c r="AD39" t="n">
-        <v>16</v>
-      </c>
-      <c r="AE39" t="n">
-        <v>44</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG39" t="n">
-        <v>21</v>
-      </c>
-      <c r="AH39" t="n">
-        <v>28</v>
-      </c>
-      <c r="AI39" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ39" t="n">
-        <v>95</v>
-      </c>
-      <c r="AK39" t="n">
-        <v>70</v>
-      </c>
-      <c r="AL39" t="n">
-        <v>90</v>
-      </c>
-      <c r="AM39" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN39" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO39" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP39" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AQ39" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AR39" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AS39" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AT39" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AU39" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AV39" t="n">
-        <v>1.48</v>
-      </c>
       <c r="AW39" t="n">
-        <v>1.58</v>
+        <v>7.4</v>
       </c>
       <c r="AX39" t="n">
-        <v>1.64</v>
+        <v>20</v>
       </c>
       <c r="AY39" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AZ39" t="n">
-        <v>1.55</v>
+        <v>16.5</v>
       </c>
       <c r="BA39" t="n">
-        <v>1.64</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB39" t="n">
-        <v>1.61</v>
+        <v>8.6</v>
       </c>
       <c r="BC39" t="n">
-        <v>1.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD39" t="n">
-        <v>1.61</v>
+        <v>8.6</v>
       </c>
       <c r="BE39" t="n">
-        <v>1.64</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF39" t="n">
-        <v>1.64</v>
+        <v>8.4</v>
       </c>
       <c r="BG39" t="n">
-        <v>1.64</v>
+        <v>7.2</v>
       </c>
       <c r="BH39" t="n">
         <v>1000</v>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-07-18 06:20:25</t>
+          <t>2026-07-18 08:41:26</t>
         </is>
       </c>
     </row>
@@ -10521,7 +10521,7 @@
         <v>1000</v>
       </c>
       <c r="J40" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="K40" t="n">
         <v>1000</v>
@@ -10560,7 +10560,7 @@
         <v>1.01</v>
       </c>
       <c r="W40" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="X40" t="n">
         <v>1000</v>
@@ -10732,7 +10732,7 @@
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-07-18 06:20:25</t>
+          <t>2026-07-18 08:41:26</t>
         </is>
       </c>
     </row>
@@ -10766,19 +10766,19 @@
         <v>1.58</v>
       </c>
       <c r="G41" t="n">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="H41" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="I41" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="J41" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="K41" t="n">
         <v>4.8</v>
-      </c>
-      <c r="I41" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="J41" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="K41" t="n">
-        <v>4.9</v>
       </c>
       <c r="L41" t="n">
         <v>1.28</v>
@@ -10787,13 +10787,13 @@
         <v>1.05</v>
       </c>
       <c r="N41" t="n">
-        <v>3.05</v>
+        <v>1.1</v>
       </c>
       <c r="O41" t="n">
         <v>1.24</v>
       </c>
       <c r="P41" t="n">
-        <v>1.98</v>
+        <v>2.06</v>
       </c>
       <c r="Q41" t="n">
         <v>1.6</v>
@@ -10802,25 +10802,25 @@
         <v>1.45</v>
       </c>
       <c r="S41" t="n">
-        <v>2.52</v>
+        <v>2.74</v>
       </c>
       <c r="T41" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="U41" t="n">
-        <v>1.9</v>
+        <v>2.04</v>
       </c>
       <c r="V41" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="W41" t="n">
-        <v>2.28</v>
+        <v>2.36</v>
       </c>
       <c r="X41" t="n">
         <v>24</v>
       </c>
       <c r="Y41" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="Z41" t="n">
         <v>60</v>
@@ -10829,10 +10829,10 @@
         <v>180</v>
       </c>
       <c r="AB41" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AC41" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AD41" t="n">
         <v>24</v>
@@ -10841,22 +10841,22 @@
         <v>95</v>
       </c>
       <c r="AF41" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AG41" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH41" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AI41" t="n">
         <v>85</v>
       </c>
       <c r="AJ41" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AK41" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="AL41" t="n">
         <v>40</v>
@@ -10865,7 +10865,7 @@
         <v>120</v>
       </c>
       <c r="AN41" t="n">
-        <v>10</v>
+        <v>8.6</v>
       </c>
       <c r="AO41" t="n">
         <v>100</v>
@@ -10928,13 +10928,13 @@
         <v>4.6</v>
       </c>
       <c r="BI41" t="n">
-        <v>3.05</v>
+        <v>1.01</v>
       </c>
       <c r="BJ41" t="n">
         <v>12</v>
       </c>
       <c r="BK41" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BL41" t="n">
         <v>140</v>
@@ -10946,37 +10946,37 @@
         <v>5.1</v>
       </c>
       <c r="BO41" t="n">
-        <v>3.4</v>
+        <v>1.01</v>
       </c>
       <c r="BP41" t="n">
         <v>12.5</v>
       </c>
       <c r="BQ41" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BR41" t="n">
         <v>28</v>
       </c>
       <c r="BS41" t="n">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="BT41" t="n">
         <v>11.5</v>
       </c>
       <c r="BU41" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BV41" t="n">
         <v>60</v>
       </c>
       <c r="BW41" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BX41" t="n">
         <v>60</v>
       </c>
       <c r="BY41" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BZ41" t="n">
         <v>0</v>
@@ -10986,7 +10986,7 @@
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-07-18 06:20:25</t>
+          <t>2026-07-18 08:41:26</t>
         </is>
       </c>
     </row>
@@ -11023,19 +11023,19 @@
         <v>2.24</v>
       </c>
       <c r="H42" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="I42" t="n">
         <v>5.6</v>
       </c>
       <c r="J42" t="n">
-        <v>2.64</v>
+        <v>2.78</v>
       </c>
       <c r="K42" t="n">
         <v>3.7</v>
       </c>
       <c r="L42" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="M42" t="n">
         <v>1.09</v>
@@ -11050,19 +11050,19 @@
         <v>1.68</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="R42" t="n">
         <v>1.25</v>
       </c>
       <c r="S42" t="n">
-        <v>3.35</v>
+        <v>1.05</v>
       </c>
       <c r="T42" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="U42" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="V42" t="n">
         <v>1.21</v>
@@ -11188,37 +11188,37 @@
         <v>12.5</v>
       </c>
       <c r="BK42" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BL42" t="n">
         <v>190</v>
       </c>
       <c r="BM42" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BN42" t="n">
         <v>5.1</v>
       </c>
       <c r="BO42" t="n">
-        <v>3.65</v>
+        <v>1.01</v>
       </c>
       <c r="BP42" t="n">
         <v>17.5</v>
       </c>
       <c r="BQ42" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BR42" t="n">
         <v>38</v>
       </c>
       <c r="BS42" t="n">
-        <v>25</v>
+        <v>1.01</v>
       </c>
       <c r="BT42" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BU42" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BV42" t="n">
         <v>50</v>
@@ -11240,7 +11240,7 @@
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-07-18 06:20:25</t>
+          <t>2026-07-18 08:41:26</t>
         </is>
       </c>
     </row>
@@ -11274,25 +11274,25 @@
         <v>2.18</v>
       </c>
       <c r="G43" t="n">
-        <v>2.46</v>
+        <v>2.64</v>
       </c>
       <c r="H43" t="n">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="I43" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="J43" t="n">
-        <v>2.94</v>
+        <v>3.1</v>
       </c>
       <c r="K43" t="n">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="L43" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="M43" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="N43" t="n">
         <v>2.56</v>
@@ -11301,28 +11301,28 @@
         <v>1.48</v>
       </c>
       <c r="P43" t="n">
-        <v>1.54</v>
+        <v>1.45</v>
       </c>
       <c r="Q43" t="n">
-        <v>2.46</v>
+        <v>2.36</v>
       </c>
       <c r="R43" t="n">
         <v>1.18</v>
       </c>
       <c r="S43" t="n">
-        <v>4.1</v>
+        <v>2.36</v>
       </c>
       <c r="T43" t="n">
         <v>1.01</v>
       </c>
       <c r="U43" t="n">
-        <v>1.01</v>
+        <v>1.68</v>
       </c>
       <c r="V43" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="W43" t="n">
-        <v>1.68</v>
+        <v>1.61</v>
       </c>
       <c r="X43" t="n">
         <v>1000</v>
@@ -11494,7 +11494,7 @@
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-07-18 06:20:25</t>
+          <t>2026-07-18 08:41:26</t>
         </is>
       </c>
     </row>
@@ -11748,14 +11748,14 @@
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-07-18 06:20:25</t>
+          <t>2026-07-18 08:41:26</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Peruvian Primera Division</t>
+          <t>Uruguayan Segunda Division</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -11765,251 +11765,251 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Alianza Lima</t>
+          <t>Colon FC</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Sport Huancayo</t>
+          <t>Paysandu FC</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>1.4</v>
+        <v>1.83</v>
       </c>
       <c r="G45" t="n">
-        <v>1.5</v>
+        <v>2.44</v>
       </c>
       <c r="H45" t="n">
-        <v>8.4</v>
+        <v>3.4</v>
       </c>
       <c r="I45" t="n">
-        <v>10.5</v>
+        <v>6.2</v>
       </c>
       <c r="J45" t="n">
-        <v>4.5</v>
+        <v>2.78</v>
       </c>
       <c r="K45" t="n">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="L45" t="n">
-        <v>1.3</v>
+        <v>1.01</v>
       </c>
       <c r="M45" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="N45" t="n">
-        <v>4</v>
+        <v>2.72</v>
       </c>
       <c r="O45" t="n">
-        <v>1.26</v>
+        <v>1.01</v>
       </c>
       <c r="P45" t="n">
-        <v>2.06</v>
+        <v>1.45</v>
       </c>
       <c r="Q45" t="n">
-        <v>1.8</v>
+        <v>2.18</v>
       </c>
       <c r="R45" t="n">
-        <v>1.41</v>
+        <v>1.14</v>
       </c>
       <c r="S45" t="n">
-        <v>3.05</v>
+        <v>2.18</v>
       </c>
       <c r="T45" t="n">
-        <v>2.04</v>
+        <v>1.01</v>
       </c>
       <c r="U45" t="n">
-        <v>1.68</v>
+        <v>1.01</v>
       </c>
       <c r="V45" t="n">
-        <v>1.1</v>
+        <v>1.19</v>
       </c>
       <c r="W45" t="n">
-        <v>3</v>
+        <v>1.7</v>
       </c>
       <c r="X45" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="Y45" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="Z45" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AA45" t="n">
-        <v>400</v>
+        <v>1000</v>
       </c>
       <c r="AB45" t="n">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="AC45" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AD45" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AE45" t="n">
-        <v>190</v>
+        <v>1000</v>
       </c>
       <c r="AF45" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AG45" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AH45" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AI45" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AJ45" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AK45" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AL45" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AM45" t="n">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="AN45" t="n">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="AO45" t="n">
-        <v>270</v>
+        <v>1000</v>
       </c>
       <c r="AP45" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="AQ45" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="AR45" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AS45" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AT45" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="AU45" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV45" t="n">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW45" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AX45" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AY45" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AZ45" t="n">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="BA45" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BB45" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BC45" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD45" t="n">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="BE45" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BF45" t="n">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="BG45" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BH45" t="n">
-        <v>4.4</v>
+        <v>1000</v>
       </c>
       <c r="BI45" t="n">
-        <v>2.96</v>
+        <v>1.01</v>
       </c>
       <c r="BJ45" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="BK45" t="n">
         <v>1.01</v>
       </c>
       <c r="BL45" t="n">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="BM45" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BN45" t="n">
-        <v>4.5</v>
+        <v>1000</v>
       </c>
       <c r="BO45" t="n">
-        <v>3</v>
+        <v>1.01</v>
       </c>
       <c r="BP45" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ45" t="n">
         <v>1.01</v>
       </c>
       <c r="BR45" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BS45" t="n">
         <v>1.01</v>
       </c>
       <c r="BT45" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="BU45" t="n">
         <v>1.01</v>
       </c>
       <c r="BV45" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="BW45" t="n">
         <v>1.01</v>
       </c>
       <c r="BX45" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="BY45" t="n">
         <v>1.01</v>
       </c>
       <c r="BZ45" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="CA45" t="n">
         <v>1.01</v>
       </c>
       <c r="CB45" t="inlineStr">
         <is>
-          <t>2026-07-18 06:20:25</t>
+          <t>2026-07-18 08:41:26</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>Peruvian Primera Division</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -12019,498 +12019,752 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>21:15:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Independiente (Ecu)</t>
+          <t>Alianza Lima</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Emelec</t>
+          <t>Sport Huancayo</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="G46" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="H46" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="I46" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="J46" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K46" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="L46" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="M46" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N46" t="n">
+        <v>4</v>
+      </c>
+      <c r="O46" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="P46" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="R46" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S46" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="V46" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="W46" t="n">
+        <v>3</v>
+      </c>
+      <c r="X46" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>29</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>400</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>36</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>190</v>
+      </c>
+      <c r="AF46" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AG46" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH46" t="n">
+        <v>28</v>
+      </c>
+      <c r="AI46" t="n">
+        <v>160</v>
+      </c>
+      <c r="AJ46" t="n">
+        <v>15</v>
+      </c>
+      <c r="AK46" t="n">
+        <v>17</v>
+      </c>
+      <c r="AL46" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM46" t="n">
+        <v>200</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AO46" t="n">
+        <v>270</v>
+      </c>
+      <c r="AP46" t="n">
+        <v>15</v>
+      </c>
+      <c r="AQ46" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AR46" t="n">
+        <v>6</v>
+      </c>
+      <c r="AS46" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AT46" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU46" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AV46" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AW46" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AX46" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AY46" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AZ46" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BA46" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BB46" t="n">
         <v>10</v>
-      </c>
-      <c r="I46" t="n">
-        <v>14</v>
-      </c>
-      <c r="J46" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="K46" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="L46" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="M46" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N46" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="O46" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="P46" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="R46" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S46" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="T46" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="U46" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="V46" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W46" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="X46" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y46" t="n">
-        <v>36</v>
-      </c>
-      <c r="Z46" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA46" t="n">
-        <v>540</v>
-      </c>
-      <c r="AB46" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AC46" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AD46" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE46" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF46" t="n">
-        <v>9</v>
-      </c>
-      <c r="AG46" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH46" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI46" t="n">
-        <v>190</v>
-      </c>
-      <c r="AJ46" t="n">
-        <v>13</v>
-      </c>
-      <c r="AK46" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AL46" t="n">
-        <v>50</v>
-      </c>
-      <c r="AM46" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN46" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AO46" t="n">
-        <v>370</v>
-      </c>
-      <c r="AP46" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AQ46" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AR46" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AS46" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AT46" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AU46" t="n">
-        <v>10</v>
-      </c>
-      <c r="AV46" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AW46" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AX46" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AY46" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ46" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="BA46" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BB46" t="n">
-        <v>9.4</v>
       </c>
       <c r="BC46" t="n">
         <v>13.5</v>
       </c>
       <c r="BD46" t="n">
-        <v>3.1</v>
+        <v>32</v>
       </c>
       <c r="BE46" t="n">
-        <v>3.35</v>
+        <v>6.2</v>
       </c>
       <c r="BF46" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BG46" t="n">
-        <v>3.3</v>
+        <v>6.2</v>
       </c>
       <c r="BH46" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BI46" t="n">
-        <v>3.05</v>
+        <v>2.96</v>
       </c>
       <c r="BJ46" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BK46" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="BL46" t="n">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="BM46" t="n">
         <v>1.01</v>
       </c>
       <c r="BN46" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BO46" t="n">
         <v>3</v>
       </c>
       <c r="BP46" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="BQ46" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BR46" t="n">
         <v>32</v>
       </c>
       <c r="BS46" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BT46" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="BU46" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BV46" t="n">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="BW46" t="n">
         <v>1.01</v>
       </c>
       <c r="BX46" t="n">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="BY46" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BZ46" t="n">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="CA46" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="CB46" t="inlineStr">
         <is>
-          <t>2026-07-18 06:20:25</t>
+          <t>2026-07-18 08:41:26</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
+          <t>Ecuadorian Serie A</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>21:15:00</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Independiente (Ecu)</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Emelec</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="G47" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="H47" t="n">
+        <v>10</v>
+      </c>
+      <c r="I47" t="n">
+        <v>14</v>
+      </c>
+      <c r="J47" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="K47" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="L47" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="M47" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N47" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="O47" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="P47" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="R47" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S47" t="n">
+        <v>3</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="V47" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W47" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="X47" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>36</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>120</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>540</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>48</v>
+      </c>
+      <c r="AE47" t="n">
+        <v>240</v>
+      </c>
+      <c r="AF47" t="n">
+        <v>9</v>
+      </c>
+      <c r="AG47" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH47" t="n">
+        <v>36</v>
+      </c>
+      <c r="AI47" t="n">
+        <v>190</v>
+      </c>
+      <c r="AJ47" t="n">
+        <v>13</v>
+      </c>
+      <c r="AK47" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AL47" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM47" t="n">
+        <v>230</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AO47" t="n">
+        <v>370</v>
+      </c>
+      <c r="AP47" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AQ47" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AR47" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AS47" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AT47" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AU47" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV47" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AW47" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AX47" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AY47" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ47" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BA47" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BB47" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BC47" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BD47" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BE47" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BF47" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BG47" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BH47" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BI47" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BJ47" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BK47" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL47" t="n">
+        <v>220</v>
+      </c>
+      <c r="BM47" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN47" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BO47" t="n">
+        <v>3</v>
+      </c>
+      <c r="BP47" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BQ47" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR47" t="n">
+        <v>32</v>
+      </c>
+      <c r="BS47" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT47" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BU47" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV47" t="n">
+        <v>120</v>
+      </c>
+      <c r="BW47" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX47" t="n">
+        <v>110</v>
+      </c>
+      <c r="BY47" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ47" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="CA47" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB47" t="inlineStr">
+        <is>
+          <t>2026-07-18 08:41:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
           <t>Bolivian Liga de Futbol Profesional</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B48" t="inlineStr">
         <is>
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C48" t="inlineStr">
         <is>
           <t>21:30:00</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="D48" t="inlineStr">
         <is>
           <t>Blooming Santa Cruz</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="E48" t="inlineStr">
         <is>
           <t>Real Tomayapo</t>
         </is>
       </c>
-      <c r="F47" t="n">
+      <c r="F48" t="n">
         <v>1.04</v>
       </c>
-      <c r="G47" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H47" t="n">
+      <c r="G48" t="n">
+        <v>110</v>
+      </c>
+      <c r="H48" t="n">
         <v>1.04</v>
       </c>
-      <c r="I47" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J47" t="n">
+      <c r="I48" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J48" t="n">
         <v>1.02</v>
       </c>
-      <c r="K47" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L47" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M47" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N47" t="n">
+      <c r="K48" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L48" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M48" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N48" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="O48" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="P48" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="R48" t="n">
         <v>1.33</v>
       </c>
-      <c r="O47" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="P47" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Q47" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="R47" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S47" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="T47" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U47" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V47" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W47" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X47" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y47" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z47" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA47" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB47" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC47" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD47" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE47" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF47" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG47" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH47" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI47" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ47" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK47" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL47" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM47" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN47" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO47" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP47" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ47" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AR47" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS47" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT47" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AU47" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AV47" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AW47" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX47" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AY47" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AZ47" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BA47" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB47" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BC47" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BD47" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BE47" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF47" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG47" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH47" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI47" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BJ47" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK47" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL47" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM47" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN47" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO47" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BP47" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ47" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BR47" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS47" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BT47" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU47" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BV47" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW47" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BX47" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY47" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BZ47" t="n">
+      <c r="S48" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="T48" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V48" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W48" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X48" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE48" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF48" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG48" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH48" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI48" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ48" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK48" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL48" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM48" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO48" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP48" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ48" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR48" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS48" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT48" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU48" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV48" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW48" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX48" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY48" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ48" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA48" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB48" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC48" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD48" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE48" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF48" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG48" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH48" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI48" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ48" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK48" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL48" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM48" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN48" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO48" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP48" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ48" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR48" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS48" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT48" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU48" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV48" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW48" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX48" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY48" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ48" t="n">
         <v>0</v>
       </c>
-      <c r="CA47" t="n">
+      <c r="CA48" t="n">
         <v>0</v>
       </c>
-      <c r="CB47" t="inlineStr">
-        <is>
-          <t>2026-07-18 06:20:25</t>
+      <c r="CB48" t="inlineStr">
+        <is>
+          <t>2026-07-18 08:41:26</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-19.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-19.xlsx
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="G2" t="n">
         <v>4.1</v>
@@ -869,7 +869,7 @@
         <v>2.1</v>
       </c>
       <c r="J2" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="K2" t="n">
         <v>3.85</v>
@@ -884,19 +884,19 @@
         <v>4</v>
       </c>
       <c r="O2" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="P2" t="n">
         <v>2</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="R2" t="n">
         <v>1.38</v>
       </c>
       <c r="S2" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="T2" t="n">
         <v>1.75</v>
@@ -923,7 +923,7 @@
         <v>27</v>
       </c>
       <c r="AB2" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AC2" t="n">
         <v>8.800000000000001</v>
@@ -941,7 +941,7 @@
         <v>17</v>
       </c>
       <c r="AH2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI2" t="n">
         <v>38</v>
@@ -989,7 +989,7 @@
         <v>18.5</v>
       </c>
       <c r="AX2" t="n">
-        <v>6</v>
+        <v>17.5</v>
       </c>
       <c r="AY2" t="n">
         <v>13.5</v>
@@ -998,10 +998,10 @@
         <v>15</v>
       </c>
       <c r="BA2" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BB2" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BC2" t="n">
         <v>38</v>
@@ -1010,7 +1010,7 @@
         <v>38</v>
       </c>
       <c r="BE2" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BF2" t="n">
         <v>34</v>
@@ -1028,13 +1028,13 @@
         <v>11.5</v>
       </c>
       <c r="BK2" t="n">
-        <v>7</v>
+        <v>1.04</v>
       </c>
       <c r="BL2" t="n">
         <v>140</v>
       </c>
       <c r="BM2" t="n">
-        <v>21</v>
+        <v>1.04</v>
       </c>
       <c r="BN2" t="n">
         <v>8.800000000000001</v>
@@ -1046,13 +1046,13 @@
         <v>40</v>
       </c>
       <c r="BQ2" t="n">
-        <v>23</v>
+        <v>1.04</v>
       </c>
       <c r="BR2" t="n">
         <v>50</v>
       </c>
       <c r="BS2" t="n">
-        <v>29</v>
+        <v>1.04</v>
       </c>
       <c r="BT2" t="n">
         <v>5.7</v>
@@ -1064,23 +1064,23 @@
         <v>17.5</v>
       </c>
       <c r="BW2" t="n">
-        <v>10.5</v>
+        <v>1.04</v>
       </c>
       <c r="BX2" t="n">
         <v>34</v>
       </c>
       <c r="BY2" t="n">
-        <v>20</v>
+        <v>1.04</v>
       </c>
       <c r="BZ2" t="n">
         <v>29</v>
       </c>
       <c r="CA2" t="n">
-        <v>17</v>
+        <v>1.04</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-18 11:02:06</t>
+          <t>2026-07-18 11:58:18</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-18 11:02:06</t>
+          <t>2026-07-18 11:58:18</t>
         </is>
       </c>
     </row>
@@ -1371,7 +1371,7 @@
         <v>5.9</v>
       </c>
       <c r="H4" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="I4" t="n">
         <v>1.83</v>
@@ -1383,7 +1383,7 @@
         <v>3.85</v>
       </c>
       <c r="L4" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="M4" t="n">
         <v>1.09</v>
@@ -1395,7 +1395,7 @@
         <v>1.43</v>
       </c>
       <c r="P4" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="Q4" t="n">
         <v>2.26</v>
@@ -1416,7 +1416,7 @@
         <v>2.2</v>
       </c>
       <c r="W4" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="X4" t="n">
         <v>11.5</v>
@@ -1425,7 +1425,7 @@
         <v>7.2</v>
       </c>
       <c r="Z4" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AA4" t="n">
         <v>19.5</v>
@@ -1512,7 +1512,7 @@
         <v>12.5</v>
       </c>
       <c r="BC4" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BD4" t="n">
         <v>12</v>
@@ -1521,7 +1521,7 @@
         <v>12.5</v>
       </c>
       <c r="BF4" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BG4" t="n">
         <v>14</v>
@@ -1563,7 +1563,7 @@
         <v>1.01</v>
       </c>
       <c r="BT4" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="BU4" t="n">
         <v>3.4</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-18 11:02:06</t>
+          <t>2026-07-18 11:58:18</t>
         </is>
       </c>
     </row>
@@ -1790,13 +1790,13 @@
         <v>12</v>
       </c>
       <c r="BK5" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="BL5" t="n">
         <v>160</v>
       </c>
       <c r="BM5" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="BN5" t="n">
         <v>5</v>
@@ -1808,16 +1808,16 @@
         <v>14.5</v>
       </c>
       <c r="BQ5" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BR5" t="n">
         <v>32</v>
       </c>
       <c r="BS5" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BT5" t="n">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU5" t="n">
         <v>3.6</v>
@@ -1826,13 +1826,13 @@
         <v>55</v>
       </c>
       <c r="BW5" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BX5" t="n">
         <v>60</v>
       </c>
       <c r="BY5" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BZ5" t="n">
         <v>0</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-18 11:02:06</t>
+          <t>2026-07-18 11:58:18</t>
         </is>
       </c>
     </row>
@@ -1891,7 +1891,7 @@
         <v>3.75</v>
       </c>
       <c r="L6" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="M6" t="n">
         <v>1.07</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-18 11:02:06</t>
+          <t>2026-07-18 11:58:18</t>
         </is>
       </c>
     </row>
@@ -2169,10 +2169,10 @@
         <v>3.55</v>
       </c>
       <c r="T7" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="U7" t="n">
-        <v>2.08</v>
+        <v>1.91</v>
       </c>
       <c r="V7" t="n">
         <v>1.59</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-18 11:02:06</t>
+          <t>2026-07-18 11:58:18</t>
         </is>
       </c>
     </row>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-18 11:02:06</t>
+          <t>2026-07-18 11:58:18</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-18 11:02:06</t>
+          <t>2026-07-18 11:58:18</t>
         </is>
       </c>
     </row>
@@ -2892,7 +2892,7 @@
         <v>2.86</v>
       </c>
       <c r="G10" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="H10" t="n">
         <v>2.66</v>
@@ -2901,13 +2901,13 @@
         <v>3.15</v>
       </c>
       <c r="J10" t="n">
-        <v>2.68</v>
+        <v>2.82</v>
       </c>
       <c r="K10" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="L10" t="n">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="M10" t="n">
         <v>1.12</v>
@@ -2940,7 +2940,7 @@
         <v>1.46</v>
       </c>
       <c r="W10" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="X10" t="n">
         <v>9.4</v>
@@ -3060,59 +3060,59 @@
         <v>12.5</v>
       </c>
       <c r="BK10" t="n">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="BL10" t="n">
         <v>220</v>
       </c>
       <c r="BM10" t="n">
-        <v>1.04</v>
+        <v>5.8</v>
       </c>
       <c r="BN10" t="n">
         <v>6.8</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.04</v>
+        <v>3.15</v>
       </c>
       <c r="BP10" t="n">
         <v>32</v>
       </c>
       <c r="BQ10" t="n">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="BR10" t="n">
         <v>60</v>
       </c>
       <c r="BS10" t="n">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="BT10" t="n">
         <v>6.4</v>
       </c>
       <c r="BU10" t="n">
-        <v>1.04</v>
+        <v>3.1</v>
       </c>
       <c r="BV10" t="n">
         <v>29</v>
       </c>
       <c r="BW10" t="n">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="BX10" t="n">
         <v>55</v>
       </c>
       <c r="BY10" t="n">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="BZ10" t="n">
         <v>55</v>
       </c>
       <c r="CA10" t="n">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-18 11:02:06</t>
+          <t>2026-07-18 11:58:18</t>
         </is>
       </c>
     </row>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-18 11:02:06</t>
+          <t>2026-07-18 11:58:18</t>
         </is>
       </c>
     </row>
@@ -3397,19 +3397,19 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.16</v>
+        <v>2.32</v>
       </c>
       <c r="G12" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="H12" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="I12" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="J12" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="K12" t="n">
         <v>3.35</v>
@@ -3421,13 +3421,13 @@
         <v>1.13</v>
       </c>
       <c r="N12" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="O12" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="P12" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="Q12" t="n">
         <v>2.78</v>
@@ -3439,16 +3439,16 @@
         <v>5.9</v>
       </c>
       <c r="T12" t="n">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="U12" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="V12" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="W12" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="X12" t="n">
         <v>8.800000000000001</v>
@@ -3460,7 +3460,7 @@
         <v>27</v>
       </c>
       <c r="AA12" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AB12" t="n">
         <v>7.8</v>
@@ -3472,10 +3472,10 @@
         <v>24</v>
       </c>
       <c r="AE12" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AF12" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AG12" t="n">
         <v>15.5</v>
@@ -3487,7 +3487,7 @@
         <v>120</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AK12" t="n">
         <v>50</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-18 11:02:06</t>
+          <t>2026-07-18 11:58:18</t>
         </is>
       </c>
     </row>
@@ -3651,22 +3651,22 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="G13" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="H13" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="I13" t="n">
-        <v>2.44</v>
+        <v>2.68</v>
       </c>
       <c r="J13" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="K13" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="L13" t="n">
         <v>1.52</v>
@@ -3675,13 +3675,13 @@
         <v>1.1</v>
       </c>
       <c r="N13" t="n">
-        <v>2.28</v>
+        <v>2.36</v>
       </c>
       <c r="O13" t="n">
         <v>1.5</v>
       </c>
       <c r="P13" t="n">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="Q13" t="n">
         <v>2.32</v>
@@ -3696,13 +3696,13 @@
         <v>2</v>
       </c>
       <c r="U13" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="V13" t="n">
-        <v>1.7</v>
+        <v>1.59</v>
       </c>
       <c r="W13" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="X13" t="n">
         <v>10.5</v>
@@ -3759,7 +3759,7 @@
         <v>40</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AQ13" t="n">
         <v>1.01</v>
@@ -3825,7 +3825,7 @@
         <v>1.01</v>
       </c>
       <c r="BL13" t="n">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="BM13" t="n">
         <v>1.01</v>
@@ -3837,44 +3837,44 @@
         <v>1.01</v>
       </c>
       <c r="BP13" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="BQ13" t="n">
         <v>1.01</v>
       </c>
       <c r="BR13" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="BS13" t="n">
         <v>1.01</v>
       </c>
       <c r="BT13" t="n">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="BU13" t="n">
         <v>3.7</v>
       </c>
       <c r="BV13" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BW13" t="n">
         <v>1.01</v>
       </c>
       <c r="BX13" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY13" t="n">
         <v>1.01</v>
       </c>
       <c r="BZ13" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="CA13" t="n">
         <v>1.01</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-18 11:02:06</t>
+          <t>2026-07-18 11:58:18</t>
         </is>
       </c>
     </row>
@@ -3905,118 +3905,118 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="G14" t="n">
-        <v>2.06</v>
+        <v>1.95</v>
       </c>
       <c r="H14" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="I14" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="J14" t="n">
         <v>3.25</v>
       </c>
       <c r="K14" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="L14" t="n">
         <v>1.38</v>
       </c>
       <c r="M14" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N14" t="n">
-        <v>2.86</v>
+        <v>2.78</v>
       </c>
       <c r="O14" t="n">
         <v>1.37</v>
       </c>
       <c r="P14" t="n">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="R14" t="n">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="S14" t="n">
-        <v>2.96</v>
+        <v>3.25</v>
       </c>
       <c r="T14" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="U14" t="n">
         <v>1.83</v>
       </c>
       <c r="V14" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="W14" t="n">
-        <v>1.94</v>
+        <v>2.04</v>
       </c>
       <c r="X14" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Y14" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="Z14" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AA14" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AB14" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AC14" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AD14" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AE14" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AF14" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AG14" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AI14" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AK14" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AL14" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM14" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AN14" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AO14" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AR14" t="n">
         <v>1.01</v>
@@ -4025,34 +4025,34 @@
         <v>1.01</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AV14" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AW14" t="n">
         <v>1.01</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BA14" t="n">
         <v>1.01</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="BD14" t="n">
         <v>1.01</v>
@@ -4061,7 +4061,7 @@
         <v>1.01</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BG14" t="n">
         <v>1.01</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-18 11:02:06</t>
+          <t>2026-07-18 11:58:18</t>
         </is>
       </c>
     </row>
@@ -4165,25 +4165,25 @@
         <v>2.7</v>
       </c>
       <c r="H15" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="I15" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="J15" t="n">
         <v>2.86</v>
       </c>
       <c r="K15" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="L15" t="n">
-        <v>1.46</v>
+        <v>1.54</v>
       </c>
       <c r="M15" t="n">
         <v>1.12</v>
       </c>
       <c r="N15" t="n">
-        <v>2.56</v>
+        <v>2.66</v>
       </c>
       <c r="O15" t="n">
         <v>1.51</v>
@@ -4198,19 +4198,19 @@
         <v>1.19</v>
       </c>
       <c r="S15" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="T15" t="n">
         <v>2.06</v>
       </c>
       <c r="U15" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="V15" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W15" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="X15" t="n">
         <v>10</v>
@@ -4222,10 +4222,10 @@
         <v>24</v>
       </c>
       <c r="AA15" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AB15" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC15" t="n">
         <v>7.4</v>
@@ -4264,7 +4264,7 @@
         <v>46</v>
       </c>
       <c r="AO15" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AP15" t="n">
         <v>1.01</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-18 11:02:06</t>
+          <t>2026-07-18 11:58:18</t>
         </is>
       </c>
     </row>
@@ -4422,22 +4422,22 @@
         <v>2.5</v>
       </c>
       <c r="I16" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="J16" t="n">
         <v>3</v>
       </c>
       <c r="K16" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="L16" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="M16" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="N16" t="n">
-        <v>2.92</v>
+        <v>3.05</v>
       </c>
       <c r="O16" t="n">
         <v>1.37</v>
@@ -4446,19 +4446,19 @@
         <v>1.74</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="R16" t="n">
         <v>1.28</v>
       </c>
       <c r="S16" t="n">
-        <v>3.75</v>
+        <v>3.45</v>
       </c>
       <c r="T16" t="n">
-        <v>1.82</v>
+        <v>1.77</v>
       </c>
       <c r="U16" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="V16" t="n">
         <v>1.54</v>
@@ -4497,10 +4497,10 @@
         <v>14</v>
       </c>
       <c r="AH16" t="n">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="AI16" t="n">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="AJ16" t="n">
         <v>65</v>
@@ -4515,7 +4515,7 @@
         <v>130</v>
       </c>
       <c r="AN16" t="n">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="AO16" t="n">
         <v>32</v>
@@ -4575,19 +4575,19 @@
         <v>1.01</v>
       </c>
       <c r="BH16" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="BJ16" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BK16" t="n">
         <v>1.01</v>
       </c>
       <c r="BL16" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="BM16" t="n">
         <v>1.01</v>
@@ -4599,44 +4599,44 @@
         <v>1.01</v>
       </c>
       <c r="BP16" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BQ16" t="n">
         <v>1.01</v>
       </c>
       <c r="BR16" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BS16" t="n">
         <v>1.01</v>
       </c>
       <c r="BT16" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BU16" t="n">
         <v>1.01</v>
       </c>
       <c r="BV16" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BW16" t="n">
         <v>1.01</v>
       </c>
       <c r="BX16" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BY16" t="n">
         <v>1.01</v>
       </c>
       <c r="BZ16" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="CA16" t="n">
         <v>1.01</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-18 11:02:06</t>
+          <t>2026-07-18 11:58:18</t>
         </is>
       </c>
     </row>
@@ -4676,7 +4676,7 @@
         <v>4</v>
       </c>
       <c r="I17" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="J17" t="n">
         <v>3.95</v>
@@ -4829,68 +4829,68 @@
         <v>7.4</v>
       </c>
       <c r="BH17" t="n">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="BI17" t="n">
-        <v>1.04</v>
+        <v>3.05</v>
       </c>
       <c r="BJ17" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>120</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BN17" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO17" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BP17" t="n">
         <v>13.5</v>
       </c>
-      <c r="BK17" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BL17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM17" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BN17" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BO17" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BP17" t="n">
-        <v>18.5</v>
-      </c>
       <c r="BQ17" t="n">
-        <v>1.04</v>
+        <v>7.8</v>
       </c>
       <c r="BR17" t="n">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="BS17" t="n">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BT17" t="n">
-        <v>11</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU17" t="n">
         <v>5</v>
       </c>
       <c r="BV17" t="n">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="BW17" t="n">
-        <v>1.04</v>
+        <v>6.4</v>
       </c>
       <c r="BX17" t="n">
         <v>55</v>
       </c>
       <c r="BY17" t="n">
-        <v>1.04</v>
+        <v>6.6</v>
       </c>
       <c r="BZ17" t="n">
-        <v>28</v>
+        <v>19.5</v>
       </c>
       <c r="CA17" t="n">
-        <v>1.04</v>
+        <v>5.7</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-18 11:02:06</t>
+          <t>2026-07-18 11:58:18</t>
         </is>
       </c>
     </row>
@@ -5098,10 +5098,10 @@
         <v>110</v>
       </c>
       <c r="BM18" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="BN18" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BO18" t="n">
         <v>4.6</v>
@@ -5110,13 +5110,13 @@
         <v>25</v>
       </c>
       <c r="BQ18" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="BR18" t="n">
         <v>36</v>
       </c>
       <c r="BS18" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="BT18" t="n">
         <v>7</v>
@@ -5128,23 +5128,23 @@
         <v>22</v>
       </c>
       <c r="BW18" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="BX18" t="n">
         <v>34</v>
       </c>
       <c r="BY18" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="BZ18" t="n">
         <v>25</v>
       </c>
       <c r="CA18" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-18 11:02:06</t>
+          <t>2026-07-18 11:58:18</t>
         </is>
       </c>
     </row>
@@ -5208,13 +5208,13 @@
         <v>1.56</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="R19" t="n">
         <v>1.2</v>
       </c>
       <c r="S19" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="T19" t="n">
         <v>2.06</v>
@@ -5253,7 +5253,7 @@
         <v>55</v>
       </c>
       <c r="AF19" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AG19" t="n">
         <v>16</v>
@@ -5286,16 +5286,16 @@
         <v>6.6</v>
       </c>
       <c r="AQ19" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>14</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT19" t="n">
         <v>6.6</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>6.8</v>
       </c>
       <c r="AU19" t="n">
         <v>5.5</v>
@@ -5307,7 +5307,7 @@
         <v>1.01</v>
       </c>
       <c r="AX19" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AY19" t="n">
         <v>10.5</v>
@@ -5340,7 +5340,7 @@
         <v>2.96</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.42</v>
+        <v>2.28</v>
       </c>
       <c r="BJ19" t="n">
         <v>13</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-18 11:02:06</t>
+          <t>2026-07-18 11:58:18</t>
         </is>
       </c>
     </row>
@@ -5429,46 +5429,46 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>3.35</v>
+        <v>3.85</v>
       </c>
       <c r="G20" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="H20" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="I20" t="n">
-        <v>2.58</v>
+        <v>2.48</v>
       </c>
       <c r="J20" t="n">
-        <v>2.74</v>
+        <v>2.88</v>
       </c>
       <c r="K20" t="n">
-        <v>4.6</v>
+        <v>3.7</v>
       </c>
       <c r="L20" t="n">
         <v>1.47</v>
       </c>
       <c r="M20" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="N20" t="n">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="O20" t="n">
-        <v>1.47</v>
+        <v>1.54</v>
       </c>
       <c r="P20" t="n">
-        <v>1.41</v>
+        <v>1.49</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="R20" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="S20" t="n">
-        <v>3.05</v>
+        <v>5.5</v>
       </c>
       <c r="T20" t="n">
         <v>1.11</v>
@@ -5477,118 +5477,118 @@
         <v>1.11</v>
       </c>
       <c r="V20" t="n">
-        <v>1.63</v>
+        <v>1.69</v>
       </c>
       <c r="W20" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="X20" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="Y20" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="Z20" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AA20" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AB20" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AC20" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AD20" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AE20" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AF20" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AG20" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AH20" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AI20" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AK20" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AL20" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AM20" t="n">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="AN20" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AO20" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AS20" t="n">
-        <v>1.01</v>
+        <v>23</v>
       </c>
       <c r="AT20" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AU20" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="AV20" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW20" t="n">
-        <v>1.01</v>
+        <v>24</v>
       </c>
       <c r="AX20" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AZ20" t="n">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BA20" t="n">
-        <v>1.01</v>
+        <v>46</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.01</v>
+        <v>75</v>
       </c>
       <c r="BC20" t="n">
-        <v>1.01</v>
+        <v>50</v>
       </c>
       <c r="BD20" t="n">
-        <v>1.01</v>
+        <v>70</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.01</v>
+        <v>140</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.01</v>
+        <v>80</v>
       </c>
       <c r="BG20" t="n">
-        <v>1.01</v>
+        <v>24</v>
       </c>
       <c r="BH20" t="n">
         <v>1000</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-18 11:02:06</t>
+          <t>2026-07-18 11:58:18</t>
         </is>
       </c>
     </row>
@@ -5689,10 +5689,10 @@
         <v>2.18</v>
       </c>
       <c r="H21" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="I21" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="J21" t="n">
         <v>3.55</v>
@@ -5701,7 +5701,7 @@
         <v>3.7</v>
       </c>
       <c r="L21" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="M21" t="n">
         <v>1.07</v>
@@ -5716,13 +5716,13 @@
         <v>1.91</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="R21" t="n">
         <v>1.36</v>
       </c>
       <c r="S21" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="T21" t="n">
         <v>1.79</v>
@@ -5731,7 +5731,7 @@
         <v>2.1</v>
       </c>
       <c r="V21" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W21" t="n">
         <v>1.85</v>
@@ -5797,16 +5797,16 @@
         <v>13</v>
       </c>
       <c r="AR21" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AS21" t="n">
         <v>13</v>
       </c>
       <c r="AT21" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AU21" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AV21" t="n">
         <v>14.5</v>
@@ -5836,7 +5836,7 @@
         <v>32</v>
       </c>
       <c r="BE21" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BF21" t="n">
         <v>13.5</v>
@@ -5845,7 +5845,7 @@
         <v>32</v>
       </c>
       <c r="BH21" t="n">
-        <v>3.85</v>
+        <v>3.45</v>
       </c>
       <c r="BI21" t="n">
         <v>2.84</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-07-18 11:02:06</t>
+          <t>2026-07-18 11:58:18</t>
         </is>
       </c>
     </row>
@@ -5961,13 +5961,13 @@
         <v>1.01</v>
       </c>
       <c r="N22" t="n">
-        <v>1.24</v>
+        <v>1.4</v>
       </c>
       <c r="O22" t="n">
         <v>1.01</v>
       </c>
       <c r="P22" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q22" t="n">
         <v>1.35</v>
@@ -5979,10 +5979,10 @@
         <v>1.36</v>
       </c>
       <c r="T22" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U22" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V22" t="n">
         <v>1.01</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-07-18 11:02:06</t>
+          <t>2026-07-18 11:58:18</t>
         </is>
       </c>
     </row>
@@ -6191,28 +6191,28 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="G23" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="H23" t="n">
         <v>1.58</v>
       </c>
       <c r="I23" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="J23" t="n">
         <v>4.4</v>
       </c>
       <c r="K23" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="L23" t="n">
         <v>1.27</v>
       </c>
       <c r="M23" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N23" t="n">
         <v>5.2</v>
@@ -6224,13 +6224,13 @@
         <v>2.38</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="R23" t="n">
         <v>1.55</v>
       </c>
       <c r="S23" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="T23" t="n">
         <v>1.71</v>
@@ -6239,13 +6239,13 @@
         <v>2.22</v>
       </c>
       <c r="V23" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="W23" t="n">
         <v>1.18</v>
       </c>
       <c r="X23" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Y23" t="n">
         <v>11</v>
@@ -6269,7 +6269,7 @@
         <v>16.5</v>
       </c>
       <c r="AF23" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AG23" t="n">
         <v>26</v>
@@ -6287,7 +6287,7 @@
         <v>80</v>
       </c>
       <c r="AL23" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AM23" t="n">
         <v>90</v>
@@ -6296,10 +6296,10 @@
         <v>85</v>
       </c>
       <c r="AO23" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="AQ23" t="n">
         <v>1.01</v>
@@ -6311,7 +6311,7 @@
         <v>1.01</v>
       </c>
       <c r="AT23" t="n">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="AU23" t="n">
         <v>1.01</v>
@@ -6320,7 +6320,7 @@
         <v>1.01</v>
       </c>
       <c r="AW23" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AX23" t="n">
         <v>1.01</v>
@@ -6329,10 +6329,10 @@
         <v>1.01</v>
       </c>
       <c r="AZ23" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BA23" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BB23" t="n">
         <v>1.01</v>
@@ -6353,10 +6353,10 @@
         <v>1.01</v>
       </c>
       <c r="BH23" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="BI23" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="BJ23" t="n">
         <v>11</v>
@@ -6371,19 +6371,19 @@
         <v>1.01</v>
       </c>
       <c r="BN23" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BO23" t="n">
         <v>1.01</v>
       </c>
       <c r="BP23" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BQ23" t="n">
         <v>1.01</v>
       </c>
       <c r="BR23" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BS23" t="n">
         <v>1.01</v>
@@ -6401,7 +6401,7 @@
         <v>1.01</v>
       </c>
       <c r="BX23" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BY23" t="n">
         <v>1.01</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-07-18 11:02:06</t>
+          <t>2026-07-18 11:58:18</t>
         </is>
       </c>
     </row>
@@ -6445,58 +6445,58 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="L24" t="n">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="M24" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N24" t="n">
-        <v>2</v>
+        <v>6.4</v>
       </c>
       <c r="O24" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="P24" t="n">
-        <v>1.7</v>
+        <v>2.84</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.11</v>
+        <v>1.37</v>
       </c>
       <c r="R24" t="n">
-        <v>1.43</v>
+        <v>1.75</v>
       </c>
       <c r="S24" t="n">
-        <v>1.72</v>
+        <v>2.08</v>
       </c>
       <c r="T24" t="n">
-        <v>1.11</v>
+        <v>1.45</v>
       </c>
       <c r="U24" t="n">
-        <v>1.11</v>
+        <v>2.84</v>
       </c>
       <c r="V24" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="W24" t="n">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="X24" t="n">
         <v>1000</v>
@@ -6607,68 +6607,68 @@
         <v>1.01</v>
       </c>
       <c r="BH24" t="n">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="BI24" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BJ24" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK24" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BL24" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="BM24" t="n">
         <v>1.01</v>
       </c>
       <c r="BN24" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="BO24" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BP24" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="BQ24" t="n">
         <v>1.01</v>
       </c>
       <c r="BR24" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BS24" t="n">
         <v>1.01</v>
       </c>
       <c r="BT24" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="BU24" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BV24" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BW24" t="n">
         <v>1.01</v>
       </c>
       <c r="BX24" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BY24" t="n">
         <v>1.01</v>
       </c>
       <c r="BZ24" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="CA24" t="n">
         <v>1.01</v>
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-07-18 11:02:06</t>
+          <t>2026-07-18 11:58:18</t>
         </is>
       </c>
     </row>
@@ -6699,13 +6699,13 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.04</v>
+        <v>1.4</v>
       </c>
       <c r="G25" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="H25" t="n">
-        <v>1.04</v>
+        <v>1.81</v>
       </c>
       <c r="I25" t="n">
         <v>1000</v>
@@ -6723,22 +6723,22 @@
         <v>1.02</v>
       </c>
       <c r="N25" t="n">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="O25" t="n">
         <v>1.19</v>
       </c>
       <c r="P25" t="n">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="R25" t="n">
         <v>1.07</v>
       </c>
       <c r="S25" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="T25" t="n">
         <v>1.11</v>
@@ -6750,7 +6750,7 @@
         <v>1.05</v>
       </c>
       <c r="W25" t="n">
-        <v>1.05</v>
+        <v>1.17</v>
       </c>
       <c r="X25" t="n">
         <v>1000</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-07-18 11:02:06</t>
+          <t>2026-07-18 11:58:18</t>
         </is>
       </c>
     </row>
@@ -6989,16 +6989,16 @@
         <v>1.7</v>
       </c>
       <c r="R26" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="S26" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="T26" t="n">
         <v>1.64</v>
       </c>
       <c r="U26" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="V26" t="n">
         <v>1.92</v>
@@ -7013,16 +7013,16 @@
         <v>12.5</v>
       </c>
       <c r="Z26" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AA26" t="n">
         <v>28</v>
       </c>
       <c r="AB26" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AC26" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD26" t="n">
         <v>11</v>
@@ -7031,22 +7031,22 @@
         <v>20</v>
       </c>
       <c r="AF26" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AG26" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH26" t="n">
         <v>17</v>
       </c>
-      <c r="AH26" t="n">
-        <v>18</v>
-      </c>
       <c r="AI26" t="n">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="AJ26" t="n">
         <v>1000</v>
       </c>
       <c r="AK26" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AL26" t="n">
         <v>50</v>
@@ -7061,7 +7061,7 @@
         <v>11.5</v>
       </c>
       <c r="AP26" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AQ26" t="n">
         <v>11</v>
@@ -7085,7 +7085,7 @@
         <v>17.5</v>
       </c>
       <c r="AX26" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AY26" t="n">
         <v>13.5</v>
@@ -7109,7 +7109,7 @@
         <v>32</v>
       </c>
       <c r="BF26" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="BG26" t="n">
         <v>10</v>
@@ -7124,13 +7124,13 @@
         <v>9</v>
       </c>
       <c r="BK26" t="n">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="BL26" t="n">
         <v>110</v>
       </c>
       <c r="BM26" t="n">
-        <v>1.04</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN26" t="n">
         <v>7.2</v>
@@ -7142,13 +7142,13 @@
         <v>30</v>
       </c>
       <c r="BQ26" t="n">
-        <v>1.04</v>
+        <v>7.4</v>
       </c>
       <c r="BR26" t="n">
         <v>38</v>
       </c>
       <c r="BS26" t="n">
-        <v>1.04</v>
+        <v>7.8</v>
       </c>
       <c r="BT26" t="n">
         <v>5.1</v>
@@ -7160,23 +7160,23 @@
         <v>14</v>
       </c>
       <c r="BW26" t="n">
-        <v>1.04</v>
+        <v>5.8</v>
       </c>
       <c r="BX26" t="n">
         <v>25</v>
       </c>
       <c r="BY26" t="n">
-        <v>1.04</v>
+        <v>7</v>
       </c>
       <c r="BZ26" t="n">
         <v>19</v>
       </c>
       <c r="CA26" t="n">
-        <v>1.04</v>
+        <v>6.4</v>
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-07-18 11:02:06</t>
+          <t>2026-07-18 11:58:18</t>
         </is>
       </c>
     </row>
@@ -7210,7 +7210,7 @@
         <v>1.29</v>
       </c>
       <c r="G27" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="H27" t="n">
         <v>12</v>
@@ -7225,7 +7225,7 @@
         <v>7</v>
       </c>
       <c r="L27" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="M27" t="n">
         <v>1.03</v>
@@ -7237,16 +7237,16 @@
         <v>1.17</v>
       </c>
       <c r="P27" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="Q27" t="n">
         <v>1.55</v>
       </c>
       <c r="R27" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="S27" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="T27" t="n">
         <v>2.04</v>
@@ -7273,7 +7273,7 @@
         <v>500</v>
       </c>
       <c r="AB27" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC27" t="n">
         <v>15</v>
@@ -7339,7 +7339,7 @@
         <v>46</v>
       </c>
       <c r="AX27" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AY27" t="n">
         <v>10</v>
@@ -7393,7 +7393,7 @@
         <v>3.35</v>
       </c>
       <c r="BP27" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="BQ27" t="n">
         <v>6</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-07-18 11:02:06</t>
+          <t>2026-07-18 11:58:18</t>
         </is>
       </c>
     </row>
@@ -7464,13 +7464,13 @@
         <v>5.5</v>
       </c>
       <c r="G28" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="H28" t="n">
         <v>1.63</v>
       </c>
       <c r="I28" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="J28" t="n">
         <v>4.7</v>
@@ -7497,10 +7497,10 @@
         <v>1.55</v>
       </c>
       <c r="R28" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="S28" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="T28" t="n">
         <v>1.64</v>
@@ -7509,7 +7509,7 @@
         <v>2.46</v>
       </c>
       <c r="V28" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="W28" t="n">
         <v>1.21</v>
@@ -7521,13 +7521,13 @@
         <v>12.5</v>
       </c>
       <c r="Z28" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AA28" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AB28" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AC28" t="n">
         <v>11</v>
@@ -7554,19 +7554,19 @@
         <v>160</v>
       </c>
       <c r="AK28" t="n">
-        <v>65</v>
+        <v>600</v>
       </c>
       <c r="AL28" t="n">
-        <v>60</v>
+        <v>310</v>
       </c>
       <c r="AM28" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AN28" t="n">
         <v>50</v>
       </c>
       <c r="AO28" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AP28" t="n">
         <v>22</v>
@@ -7596,7 +7596,7 @@
         <v>42</v>
       </c>
       <c r="AY28" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AZ28" t="n">
         <v>16</v>
@@ -7620,46 +7620,46 @@
         <v>38</v>
       </c>
       <c r="BG28" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="BH28" t="n">
         <v>5.4</v>
       </c>
       <c r="BI28" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="BJ28" t="n">
         <v>11</v>
       </c>
       <c r="BK28" t="n">
-        <v>6.8</v>
+        <v>3.3</v>
       </c>
       <c r="BL28" t="n">
         <v>100</v>
       </c>
       <c r="BM28" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BN28" t="n">
         <v>11</v>
       </c>
       <c r="BO28" t="n">
-        <v>6.8</v>
+        <v>3.3</v>
       </c>
       <c r="BP28" t="n">
         <v>46</v>
       </c>
       <c r="BQ28" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BR28" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BS28" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BT28" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BU28" t="n">
         <v>4.2</v>
@@ -7668,7 +7668,7 @@
         <v>12</v>
       </c>
       <c r="BW28" t="n">
-        <v>7.4</v>
+        <v>3.4</v>
       </c>
       <c r="BX28" t="n">
         <v>24</v>
@@ -7677,14 +7677,14 @@
         <v>4</v>
       </c>
       <c r="BZ28" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="CA28" t="n">
-        <v>9.199999999999999</v>
+        <v>3.65</v>
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-07-18 11:02:06</t>
+          <t>2026-07-18 11:58:18</t>
         </is>
       </c>
     </row>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-07-18 11:02:06</t>
+          <t>2026-07-18 11:58:18</t>
         </is>
       </c>
     </row>
@@ -7969,16 +7969,16 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="G30" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="H30" t="n">
         <v>1.58</v>
       </c>
       <c r="I30" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="J30" t="n">
         <v>4.4</v>
@@ -7987,7 +7987,7 @@
         <v>4.7</v>
       </c>
       <c r="L30" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="M30" t="n">
         <v>1.05</v>
@@ -7999,10 +7999,10 @@
         <v>1.25</v>
       </c>
       <c r="P30" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="R30" t="n">
         <v>1.47</v>
@@ -8011,13 +8011,13 @@
         <v>2.86</v>
       </c>
       <c r="T30" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="U30" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="V30" t="n">
-        <v>2.6</v>
+        <v>2.52</v>
       </c>
       <c r="W30" t="n">
         <v>1.18</v>
@@ -8053,7 +8053,7 @@
         <v>26</v>
       </c>
       <c r="AH30" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI30" t="n">
         <v>34</v>
@@ -8074,7 +8074,7 @@
         <v>110</v>
       </c>
       <c r="AO30" t="n">
-        <v>7.8</v>
+        <v>10</v>
       </c>
       <c r="AP30" t="n">
         <v>16</v>
@@ -8110,76 +8110,76 @@
         <v>18</v>
       </c>
       <c r="BA30" t="n">
-        <v>8.800000000000001</v>
+        <v>7</v>
       </c>
       <c r="BB30" t="n">
-        <v>10.5</v>
+        <v>8.4</v>
       </c>
       <c r="BC30" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BD30" t="n">
-        <v>10</v>
+        <v>7.8</v>
       </c>
       <c r="BE30" t="n">
-        <v>10.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF30" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BG30" t="n">
         <v>6.8</v>
       </c>
       <c r="BH30" t="n">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="BI30" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="BJ30" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK30" t="n">
         <v>1.01</v>
       </c>
       <c r="BL30" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="BM30" t="n">
         <v>1.01</v>
       </c>
       <c r="BN30" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BO30" t="n">
         <v>1.01</v>
       </c>
       <c r="BP30" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BQ30" t="n">
         <v>1.01</v>
       </c>
       <c r="BR30" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BS30" t="n">
         <v>1.01</v>
       </c>
       <c r="BT30" t="n">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="BU30" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="BV30" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BW30" t="n">
         <v>1.01</v>
       </c>
       <c r="BX30" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BY30" t="n">
         <v>1.01</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-07-18 11:02:06</t>
+          <t>2026-07-18 11:58:18</t>
         </is>
       </c>
     </row>
@@ -8232,10 +8232,10 @@
         <v>2.66</v>
       </c>
       <c r="I31" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="J31" t="n">
         <v>3.05</v>
-      </c>
-      <c r="J31" t="n">
-        <v>2.84</v>
       </c>
       <c r="K31" t="n">
         <v>3.5</v>
@@ -8247,16 +8247,16 @@
         <v>1.09</v>
       </c>
       <c r="N31" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="O31" t="n">
         <v>1.41</v>
       </c>
       <c r="P31" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="R31" t="n">
         <v>1.25</v>
@@ -8265,13 +8265,13 @@
         <v>4.1</v>
       </c>
       <c r="T31" t="n">
-        <v>1.78</v>
+        <v>1.86</v>
       </c>
       <c r="U31" t="n">
-        <v>1.84</v>
+        <v>1.95</v>
       </c>
       <c r="V31" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="W31" t="n">
         <v>1.46</v>
@@ -8310,7 +8310,7 @@
         <v>22</v>
       </c>
       <c r="AI31" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AJ31" t="n">
         <v>60</v>
@@ -8328,7 +8328,7 @@
         <v>46</v>
       </c>
       <c r="AO31" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AP31" t="n">
         <v>8.4</v>
@@ -8421,7 +8421,7 @@
         <v>1.01</v>
       </c>
       <c r="BT31" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BU31" t="n">
         <v>4.5</v>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-07-18 11:02:06</t>
+          <t>2026-07-18 11:58:18</t>
         </is>
       </c>
     </row>
@@ -8501,7 +8501,7 @@
         <v>1.01</v>
       </c>
       <c r="N32" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O32" t="n">
         <v>1.37</v>
@@ -8516,7 +8516,7 @@
         <v>1.16</v>
       </c>
       <c r="S32" t="n">
-        <v>1.36</v>
+        <v>1.05</v>
       </c>
       <c r="T32" t="n">
         <v>1.11</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-07-18 11:02:06</t>
+          <t>2026-07-18 11:58:18</t>
         </is>
       </c>
     </row>
@@ -8731,22 +8731,22 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="G33" t="n">
         <v>6.8</v>
       </c>
       <c r="H33" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="I33" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="J33" t="n">
         <v>3.5</v>
       </c>
       <c r="K33" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L33" t="n">
         <v>1.58</v>
@@ -8773,13 +8773,13 @@
         <v>5.5</v>
       </c>
       <c r="T33" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="U33" t="n">
         <v>1.62</v>
       </c>
       <c r="V33" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="W33" t="n">
         <v>1.17</v>
@@ -8791,7 +8791,7 @@
         <v>6.8</v>
       </c>
       <c r="Z33" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AA33" t="n">
         <v>24</v>
@@ -8836,7 +8836,7 @@
         <v>340</v>
       </c>
       <c r="AO33" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AP33" t="n">
         <v>6.6</v>
@@ -8848,7 +8848,7 @@
         <v>6.6</v>
       </c>
       <c r="AS33" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AT33" t="n">
         <v>10.5</v>
@@ -8857,40 +8857,40 @@
         <v>6.4</v>
       </c>
       <c r="AV33" t="n">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AW33" t="n">
         <v>18.5</v>
       </c>
       <c r="AX33" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AY33" t="n">
         <v>4.7</v>
       </c>
       <c r="AZ33" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BA33" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BB33" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BC33" t="n">
         <v>5.1</v>
       </c>
-      <c r="BC33" t="n">
-        <v>5</v>
-      </c>
       <c r="BD33" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BE33" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BF33" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BG33" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BH33" t="n">
         <v>3.1</v>
@@ -8905,7 +8905,7 @@
         <v>3.9</v>
       </c>
       <c r="BL33" t="n">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="BM33" t="n">
         <v>5.1</v>
@@ -8917,7 +8917,7 @@
         <v>3.55</v>
       </c>
       <c r="BP33" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="BQ33" t="n">
         <v>4.9</v>
@@ -8947,14 +8947,14 @@
         <v>4.7</v>
       </c>
       <c r="BZ33" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="CA33" t="n">
         <v>4.7</v>
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-07-18 11:02:06</t>
+          <t>2026-07-18 11:58:18</t>
         </is>
       </c>
     </row>
@@ -9003,7 +9003,7 @@
         <v>4.3</v>
       </c>
       <c r="L34" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="M34" t="n">
         <v>1.05</v>
@@ -9018,7 +9018,7 @@
         <v>2.22</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="R34" t="n">
         <v>1.47</v>
@@ -9030,7 +9030,7 @@
         <v>1.62</v>
       </c>
       <c r="U34" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="V34" t="n">
         <v>1.91</v>
@@ -9186,7 +9186,7 @@
         <v>5.9</v>
       </c>
       <c r="BU34" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BV34" t="n">
         <v>15.5</v>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-07-18 11:02:06</t>
+          <t>2026-07-18 11:58:18</t>
         </is>
       </c>
     </row>
@@ -9263,7 +9263,7 @@
         <v>1.01</v>
       </c>
       <c r="N35" t="n">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="O35" t="n">
         <v>1.01</v>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-07-18 11:02:06</t>
+          <t>2026-07-18 11:58:18</t>
         </is>
       </c>
     </row>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-07-18 11:02:06</t>
+          <t>2026-07-18 11:58:18</t>
         </is>
       </c>
     </row>
@@ -9771,13 +9771,13 @@
         <v>1.01</v>
       </c>
       <c r="N37" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="O37" t="n">
         <v>1.16</v>
       </c>
       <c r="P37" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="Q37" t="n">
         <v>1.16</v>
@@ -9789,10 +9789,10 @@
         <v>1.15</v>
       </c>
       <c r="T37" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U37" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V37" t="n">
         <v>1.01</v>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-07-18 11:02:06</t>
+          <t>2026-07-18 11:58:18</t>
         </is>
       </c>
     </row>
@@ -10031,7 +10031,7 @@
         <v>1.25</v>
       </c>
       <c r="P38" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="Q38" t="n">
         <v>1.71</v>
@@ -10142,7 +10142,7 @@
         <v>12.5</v>
       </c>
       <c r="BA38" t="n">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="BB38" t="n">
         <v>17.5</v>
@@ -10172,13 +10172,13 @@
         <v>10.5</v>
       </c>
       <c r="BK38" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BL38" t="n">
         <v>110</v>
       </c>
       <c r="BM38" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BN38" t="n">
         <v>5.6</v>
@@ -10190,31 +10190,31 @@
         <v>15.5</v>
       </c>
       <c r="BQ38" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BR38" t="n">
         <v>29</v>
       </c>
       <c r="BS38" t="n">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="BT38" t="n">
         <v>8.6</v>
       </c>
       <c r="BU38" t="n">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="BV38" t="n">
         <v>36</v>
       </c>
       <c r="BW38" t="n">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="BX38" t="n">
         <v>44</v>
       </c>
       <c r="BY38" t="n">
-        <v>27</v>
+        <v>1.01</v>
       </c>
       <c r="BZ38" t="n">
         <v>0</v>
@@ -10224,7 +10224,7 @@
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-07-18 11:02:06</t>
+          <t>2026-07-18 11:58:18</t>
         </is>
       </c>
     </row>
@@ -10255,97 +10255,97 @@
         </is>
       </c>
       <c r="F39" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="G39" t="n">
         <v>1.65</v>
       </c>
-      <c r="G39" t="n">
-        <v>1.77</v>
-      </c>
       <c r="H39" t="n">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="I39" t="n">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="J39" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="K39" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="L39" t="n">
-        <v>1.42</v>
+        <v>1.34</v>
       </c>
       <c r="M39" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N39" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="O39" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="P39" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="R39" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="S39" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="T39" t="n">
-        <v>1.96</v>
+        <v>2.04</v>
       </c>
       <c r="U39" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="V39" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="W39" t="n">
-        <v>2.28</v>
+        <v>2.52</v>
       </c>
       <c r="X39" t="n">
         <v>16</v>
       </c>
       <c r="Y39" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Z39" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AA39" t="n">
-        <v>220</v>
+        <v>290</v>
       </c>
       <c r="AB39" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AC39" t="n">
-        <v>9.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="AD39" t="n">
         <v>29</v>
       </c>
       <c r="AE39" t="n">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="AF39" t="n">
         <v>10.5</v>
       </c>
       <c r="AG39" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AH39" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AI39" t="n">
         <v>120</v>
       </c>
       <c r="AJ39" t="n">
-        <v>20</v>
+        <v>15.5</v>
       </c>
       <c r="AK39" t="n">
         <v>21</v>
@@ -10357,10 +10357,10 @@
         <v>180</v>
       </c>
       <c r="AN39" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AO39" t="n">
-        <v>170</v>
+        <v>210</v>
       </c>
       <c r="AP39" t="n">
         <v>9.800000000000001</v>
@@ -10369,13 +10369,13 @@
         <v>13</v>
       </c>
       <c r="AR39" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AS39" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AT39" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="AU39" t="n">
         <v>7.6</v>
@@ -10384,7 +10384,7 @@
         <v>17</v>
       </c>
       <c r="AW39" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AX39" t="n">
         <v>7.2</v>
@@ -10396,7 +10396,7 @@
         <v>19</v>
       </c>
       <c r="BA39" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BB39" t="n">
         <v>12.5</v>
@@ -10405,25 +10405,25 @@
         <v>14</v>
       </c>
       <c r="BD39" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BE39" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BF39" t="n">
-        <v>9</v>
+        <v>7.4</v>
       </c>
       <c r="BG39" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BH39" t="n">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="BI39" t="n">
-        <v>2.92</v>
+        <v>2.72</v>
       </c>
       <c r="BJ39" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BK39" t="n">
         <v>1.01</v>
@@ -10435,50 +10435,50 @@
         <v>1.01</v>
       </c>
       <c r="BN39" t="n">
-        <v>4.9</v>
+        <v>4.1</v>
       </c>
       <c r="BO39" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="BP39" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="BQ39" t="n">
         <v>1.01</v>
       </c>
       <c r="BR39" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BS39" t="n">
         <v>1.01</v>
       </c>
       <c r="BT39" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BU39" t="n">
         <v>1.01</v>
       </c>
       <c r="BV39" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="BW39" t="n">
         <v>1.01</v>
       </c>
       <c r="BX39" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="BY39" t="n">
         <v>1.01</v>
       </c>
       <c r="BZ39" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="CA39" t="n">
         <v>1.01</v>
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-07-18 11:02:06</t>
+          <t>2026-07-18 11:58:18</t>
         </is>
       </c>
     </row>
@@ -10732,7 +10732,7 @@
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-07-18 11:02:06</t>
+          <t>2026-07-18 11:58:18</t>
         </is>
       </c>
     </row>
@@ -10763,7 +10763,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="G41" t="n">
         <v>2.4</v>
@@ -10772,25 +10772,25 @@
         <v>3.25</v>
       </c>
       <c r="I41" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="J41" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K41" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L41" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="M41" t="n">
         <v>1.01</v>
       </c>
       <c r="N41" t="n">
-        <v>2.58</v>
+        <v>3.3</v>
       </c>
       <c r="O41" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="P41" t="n">
         <v>1.64</v>
@@ -10986,7 +10986,7 @@
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-07-18 11:02:06</t>
+          <t>2026-07-18 11:58:18</t>
         </is>
       </c>
     </row>
@@ -11017,25 +11017,25 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="G42" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="H42" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="I42" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="J42" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="K42" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="L42" t="n">
-        <v>1.48</v>
+        <v>1.56</v>
       </c>
       <c r="M42" t="n">
         <v>1.13</v>
@@ -11044,13 +11044,13 @@
         <v>2.52</v>
       </c>
       <c r="O42" t="n">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="P42" t="n">
         <v>1.5</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="R42" t="n">
         <v>1.18</v>
@@ -11059,7 +11059,7 @@
         <v>5.3</v>
       </c>
       <c r="T42" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="U42" t="n">
         <v>1.77</v>
@@ -11068,7 +11068,7 @@
         <v>1.44</v>
       </c>
       <c r="W42" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="X42" t="n">
         <v>10</v>
@@ -11119,7 +11119,7 @@
         <v>220</v>
       </c>
       <c r="AN42" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AO42" t="n">
         <v>65</v>
@@ -11164,7 +11164,7 @@
         <v>6</v>
       </c>
       <c r="BC42" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BD42" t="n">
         <v>6.2</v>
@@ -11200,7 +11200,7 @@
         <v>6.8</v>
       </c>
       <c r="BO42" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BP42" t="n">
         <v>32</v>
@@ -11218,10 +11218,10 @@
         <v>7</v>
       </c>
       <c r="BU42" t="n">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="BV42" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BW42" t="n">
         <v>4.3</v>
@@ -11230,17 +11230,17 @@
         <v>65</v>
       </c>
       <c r="BY42" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BZ42" t="n">
         <v>65</v>
       </c>
       <c r="CA42" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-07-18 11:02:06</t>
+          <t>2026-07-18 11:58:18</t>
         </is>
       </c>
     </row>
@@ -11277,7 +11277,7 @@
         <v>4.4</v>
       </c>
       <c r="H43" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="I43" t="n">
         <v>2.18</v>
@@ -11442,13 +11442,13 @@
         <v>12</v>
       </c>
       <c r="BK43" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="BL43" t="n">
         <v>190</v>
       </c>
       <c r="BM43" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="BN43" t="n">
         <v>8.199999999999999</v>
@@ -11460,16 +11460,16 @@
         <v>44</v>
       </c>
       <c r="BQ43" t="n">
-        <v>5.9</v>
+        <v>5.4</v>
       </c>
       <c r="BR43" t="n">
         <v>65</v>
       </c>
       <c r="BS43" t="n">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="BT43" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="BU43" t="n">
         <v>4.1</v>
@@ -11478,23 +11478,23 @@
         <v>19.5</v>
       </c>
       <c r="BW43" t="n">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="BX43" t="n">
         <v>42</v>
       </c>
       <c r="BY43" t="n">
-        <v>5.8</v>
+        <v>5.3</v>
       </c>
       <c r="BZ43" t="n">
         <v>42</v>
       </c>
       <c r="CA43" t="n">
-        <v>5.8</v>
+        <v>5.3</v>
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-07-18 11:02:06</t>
+          <t>2026-07-18 11:58:18</t>
         </is>
       </c>
     </row>
@@ -11525,7 +11525,7 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="G44" t="n">
         <v>3.75</v>
@@ -11543,7 +11543,7 @@
         <v>3.55</v>
       </c>
       <c r="L44" t="n">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="M44" t="n">
         <v>1.09</v>
@@ -11636,13 +11636,13 @@
         <v>9.6</v>
       </c>
       <c r="AQ44" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AR44" t="n">
         <v>12.5</v>
       </c>
       <c r="AS44" t="n">
-        <v>28</v>
+        <v>7.8</v>
       </c>
       <c r="AT44" t="n">
         <v>9.800000000000001</v>
@@ -11660,7 +11660,7 @@
         <v>20</v>
       </c>
       <c r="AY44" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AZ44" t="n">
         <v>16.5</v>
@@ -11681,74 +11681,74 @@
         <v>9.4</v>
       </c>
       <c r="BF44" t="n">
-        <v>8.6</v>
+        <v>40</v>
       </c>
       <c r="BG44" t="n">
+        <v>20</v>
+      </c>
+      <c r="BH44" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BI44" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="BJ44" t="n">
+        <v>12</v>
+      </c>
+      <c r="BK44" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL44" t="n">
+        <v>180</v>
+      </c>
+      <c r="BM44" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN44" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BO44" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BP44" t="n">
+        <v>36</v>
+      </c>
+      <c r="BQ44" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR44" t="n">
+        <v>55</v>
+      </c>
+      <c r="BS44" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT44" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BU44" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BV44" t="n">
         <v>22</v>
       </c>
-      <c r="BH44" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI44" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BJ44" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK44" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL44" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM44" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN44" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BO44" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BP44" t="n">
-        <v>44</v>
-      </c>
-      <c r="BQ44" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BR44" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS44" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BT44" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU44" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BV44" t="n">
-        <v>26</v>
-      </c>
       <c r="BW44" t="n">
         <v>1.01</v>
       </c>
       <c r="BX44" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="BY44" t="n">
         <v>1.01</v>
       </c>
       <c r="BZ44" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="CA44" t="n">
         <v>1.01</v>
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-07-18 11:02:06</t>
+          <t>2026-07-18 11:58:18</t>
         </is>
       </c>
     </row>
@@ -11809,13 +11809,13 @@
         <v>1.3</v>
       </c>
       <c r="P45" t="n">
-        <v>1.09</v>
+        <v>1.16</v>
       </c>
       <c r="Q45" t="n">
         <v>1.84</v>
       </c>
       <c r="R45" t="n">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="S45" t="n">
         <v>2.96</v>
@@ -12002,7 +12002,7 @@
       </c>
       <c r="CB45" t="inlineStr">
         <is>
-          <t>2026-07-18 11:02:06</t>
+          <t>2026-07-18 11:58:18</t>
         </is>
       </c>
     </row>
@@ -12256,7 +12256,7 @@
       </c>
       <c r="CB46" t="inlineStr">
         <is>
-          <t>2026-07-18 11:02:06</t>
+          <t>2026-07-18 11:58:18</t>
         </is>
       </c>
     </row>
@@ -12305,7 +12305,7 @@
         <v>3.7</v>
       </c>
       <c r="L47" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="M47" t="n">
         <v>1.09</v>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="CB47" t="inlineStr">
         <is>
-          <t>2026-07-18 11:02:06</t>
+          <t>2026-07-18 11:58:18</t>
         </is>
       </c>
     </row>
@@ -12764,7 +12764,7 @@
       </c>
       <c r="CB48" t="inlineStr">
         <is>
-          <t>2026-07-18 11:02:06</t>
+          <t>2026-07-18 11:58:18</t>
         </is>
       </c>
     </row>
@@ -12801,7 +12801,7 @@
         <v>2.44</v>
       </c>
       <c r="H49" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="I49" t="n">
         <v>4.3</v>
@@ -12828,7 +12828,7 @@
         <v>1.54</v>
       </c>
       <c r="Q49" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="R49" t="n">
         <v>1.2</v>
@@ -12837,7 +12837,7 @@
         <v>5.1</v>
       </c>
       <c r="T49" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="U49" t="n">
         <v>1.78</v>
@@ -12867,10 +12867,10 @@
         <v>7.6</v>
       </c>
       <c r="AD49" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AE49" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AF49" t="n">
         <v>14</v>
@@ -12891,7 +12891,7 @@
         <v>34</v>
       </c>
       <c r="AL49" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AM49" t="n">
         <v>210</v>
@@ -12909,10 +12909,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AR49" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AS49" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT49" t="n">
         <v>6.4</v>
@@ -12924,38 +12924,38 @@
         <v>14.5</v>
       </c>
       <c r="AW49" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AX49" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AY49" t="n">
         <v>10</v>
       </c>
       <c r="AZ49" t="n">
-        <v>6.6</v>
+        <v>19</v>
       </c>
       <c r="BA49" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BB49" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BC49" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BD49" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE49" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BF49" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BG49" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="BF49" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BG49" t="n">
-        <v>8.4</v>
-      </c>
       <c r="BH49" t="n">
         <v>1000</v>
       </c>
@@ -13018,7 +13018,7 @@
       </c>
       <c r="CB49" t="inlineStr">
         <is>
-          <t>2026-07-18 11:02:06</t>
+          <t>2026-07-18 11:58:18</t>
         </is>
       </c>
     </row>
@@ -13091,10 +13091,10 @@
         <v>1.44</v>
       </c>
       <c r="T50" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U50" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V50" t="n">
         <v>1.01</v>
@@ -13272,7 +13272,7 @@
       </c>
       <c r="CB50" t="inlineStr">
         <is>
-          <t>2026-07-18 11:02:06</t>
+          <t>2026-07-18 11:58:18</t>
         </is>
       </c>
     </row>
@@ -13345,10 +13345,10 @@
         <v>3.55</v>
       </c>
       <c r="T51" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U51" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V51" t="n">
         <v>1.48</v>
@@ -13526,7 +13526,7 @@
       </c>
       <c r="CB51" t="inlineStr">
         <is>
-          <t>2026-07-18 11:02:06</t>
+          <t>2026-07-18 11:58:18</t>
         </is>
       </c>
     </row>
@@ -13557,230 +13557,230 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>1.83</v>
+        <v>1.98</v>
       </c>
       <c r="G52" t="n">
-        <v>2.44</v>
+        <v>2.26</v>
       </c>
       <c r="H52" t="n">
-        <v>3.4</v>
+        <v>3.85</v>
       </c>
       <c r="I52" t="n">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="J52" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="K52" t="n">
-        <v>6.2</v>
+        <v>4.1</v>
       </c>
       <c r="L52" t="n">
-        <v>1.43</v>
+        <v>1.52</v>
       </c>
       <c r="M52" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="N52" t="n">
-        <v>2.04</v>
+        <v>2.68</v>
       </c>
       <c r="O52" t="n">
-        <v>1.24</v>
+        <v>1.47</v>
       </c>
       <c r="P52" t="n">
-        <v>1.45</v>
+        <v>1.56</v>
       </c>
       <c r="Q52" t="n">
-        <v>2.18</v>
+        <v>2.4</v>
       </c>
       <c r="R52" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="S52" t="n">
-        <v>2.56</v>
+        <v>4.2</v>
       </c>
       <c r="T52" t="n">
-        <v>1.11</v>
+        <v>1.89</v>
       </c>
       <c r="U52" t="n">
-        <v>1.11</v>
+        <v>1.66</v>
       </c>
       <c r="V52" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="W52" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="X52" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Y52" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Z52" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AA52" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AB52" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AC52" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AD52" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AE52" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AF52" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AG52" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH52" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AI52" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AJ52" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AK52" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AL52" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AM52" t="n">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AN52" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AO52" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AP52" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AQ52" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AR52" t="n">
-        <v>1.01</v>
+        <v>23</v>
       </c>
       <c r="AS52" t="n">
-        <v>1.01</v>
+        <v>80</v>
       </c>
       <c r="AT52" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="AU52" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="AV52" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AW52" t="n">
-        <v>1.01</v>
+        <v>50</v>
       </c>
       <c r="AX52" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AY52" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ52" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BA52" t="n">
-        <v>1.01</v>
+        <v>65</v>
       </c>
       <c r="BB52" t="n">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="BC52" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BD52" t="n">
-        <v>1.01</v>
+        <v>38</v>
       </c>
       <c r="BE52" t="n">
-        <v>1.01</v>
+        <v>120</v>
       </c>
       <c r="BF52" t="n">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BG52" t="n">
-        <v>1.01</v>
+        <v>80</v>
       </c>
       <c r="BH52" t="n">
-        <v>1000</v>
+        <v>3.25</v>
       </c>
       <c r="BI52" t="n">
-        <v>1.04</v>
+        <v>2.3</v>
       </c>
       <c r="BJ52" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BK52" t="n">
         <v>1.04</v>
       </c>
       <c r="BL52" t="n">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="BM52" t="n">
         <v>1.04</v>
       </c>
       <c r="BN52" t="n">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="BO52" t="n">
-        <v>1.04</v>
+        <v>3.55</v>
       </c>
       <c r="BP52" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BQ52" t="n">
         <v>1.04</v>
       </c>
       <c r="BR52" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BS52" t="n">
         <v>1.04</v>
       </c>
       <c r="BT52" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BU52" t="n">
-        <v>1.04</v>
+        <v>5.7</v>
       </c>
       <c r="BV52" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BW52" t="n">
         <v>1.04</v>
       </c>
       <c r="BX52" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="BY52" t="n">
         <v>1.04</v>
       </c>
       <c r="BZ52" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="CA52" t="n">
         <v>1.04</v>
       </c>
       <c r="CB52" t="inlineStr">
         <is>
-          <t>2026-07-18 11:02:06</t>
+          <t>2026-07-18 11:58:18</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="CB53" t="inlineStr">
         <is>
-          <t>2026-07-18 11:02:06</t>
+          <t>2026-07-18 11:58:18</t>
         </is>
       </c>
     </row>
@@ -14074,22 +14074,22 @@
         <v>10</v>
       </c>
       <c r="I54" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="J54" t="n">
         <v>4.8</v>
       </c>
       <c r="K54" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="L54" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="M54" t="n">
         <v>1.05</v>
       </c>
       <c r="N54" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="O54" t="n">
         <v>1.27</v>
@@ -14101,19 +14101,19 @@
         <v>1.79</v>
       </c>
       <c r="R54" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="S54" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="T54" t="n">
         <v>2.14</v>
       </c>
       <c r="U54" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="V54" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="W54" t="n">
         <v>3.3</v>
@@ -14173,7 +14173,7 @@
         <v>370</v>
       </c>
       <c r="AP54" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AQ54" t="n">
         <v>4.7</v>
@@ -14197,10 +14197,10 @@
         <v>5.2</v>
       </c>
       <c r="AX54" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AY54" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AZ54" t="n">
         <v>4.7</v>
@@ -14209,7 +14209,7 @@
         <v>5.2</v>
       </c>
       <c r="BB54" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BC54" t="n">
         <v>13.5</v>
@@ -14227,7 +14227,7 @@
         <v>5.3</v>
       </c>
       <c r="BH54" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BI54" t="n">
         <v>3.05</v>
@@ -14288,7 +14288,7 @@
       </c>
       <c r="CB54" t="inlineStr">
         <is>
-          <t>2026-07-18 11:02:06</t>
+          <t>2026-07-18 11:58:18</t>
         </is>
       </c>
     </row>
@@ -14542,7 +14542,7 @@
       </c>
       <c r="CB55" t="inlineStr">
         <is>
-          <t>2026-07-18 11:02:06</t>
+          <t>2026-07-18 11:58:18</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-19.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-19.xlsx
@@ -857,22 +857,22 @@
         </is>
       </c>
       <c r="F2" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="G2" t="n">
         <v>3.95</v>
       </c>
-      <c r="G2" t="n">
-        <v>4.1</v>
-      </c>
       <c r="H2" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="I2" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="J2" t="n">
         <v>3.65</v>
       </c>
       <c r="K2" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L2" t="n">
         <v>1.4</v>
@@ -881,10 +881,10 @@
         <v>1.07</v>
       </c>
       <c r="N2" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="O2" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="P2" t="n">
         <v>2</v>
@@ -893,10 +893,10 @@
         <v>1.95</v>
       </c>
       <c r="R2" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S2" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="T2" t="n">
         <v>1.75</v>
@@ -905,13 +905,13 @@
         <v>2.12</v>
       </c>
       <c r="V2" t="n">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="W2" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="X2" t="n">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="Y2" t="n">
         <v>10</v>
@@ -920,13 +920,13 @@
         <v>14</v>
       </c>
       <c r="AA2" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AB2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AC2" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD2" t="n">
         <v>11.5</v>
@@ -935,31 +935,31 @@
         <v>23</v>
       </c>
       <c r="AF2" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AG2" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AI2" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AJ2" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AK2" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AL2" t="n">
         <v>55</v>
       </c>
       <c r="AM2" t="n">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="AN2" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AO2" t="n">
         <v>16</v>
@@ -998,10 +998,10 @@
         <v>15</v>
       </c>
       <c r="BA2" t="n">
-        <v>6.6</v>
+        <v>9</v>
       </c>
       <c r="BB2" t="n">
-        <v>7.4</v>
+        <v>10.5</v>
       </c>
       <c r="BC2" t="n">
         <v>38</v>
@@ -1010,7 +1010,7 @@
         <v>38</v>
       </c>
       <c r="BE2" t="n">
-        <v>7.6</v>
+        <v>10.5</v>
       </c>
       <c r="BF2" t="n">
         <v>34</v>
@@ -1022,65 +1022,65 @@
         <v>4.1</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="BJ2" t="n">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK2" t="n">
         <v>1.04</v>
       </c>
       <c r="BL2" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="BM2" t="n">
         <v>1.04</v>
       </c>
       <c r="BN2" t="n">
-        <v>8.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="BO2" t="n">
         <v>5.5</v>
       </c>
       <c r="BP2" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="BQ2" t="n">
         <v>1.04</v>
       </c>
       <c r="BR2" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="BS2" t="n">
         <v>1.04</v>
       </c>
       <c r="BT2" t="n">
-        <v>5.7</v>
+        <v>5.1</v>
       </c>
       <c r="BU2" t="n">
-        <v>3.75</v>
+        <v>4.3</v>
       </c>
       <c r="BV2" t="n">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="BW2" t="n">
         <v>1.04</v>
       </c>
       <c r="BX2" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="BY2" t="n">
         <v>1.04</v>
       </c>
       <c r="BZ2" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="CA2" t="n">
         <v>1.04</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-18 11:58:18</t>
+          <t>2026-07-18 14:16:24</t>
         </is>
       </c>
     </row>
@@ -1111,22 +1111,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="G3" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="H3" t="n">
         <v>6.4</v>
       </c>
       <c r="I3" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="J3" t="n">
         <v>3.8</v>
       </c>
       <c r="K3" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L3" t="n">
         <v>1.45</v>
@@ -1138,37 +1138,37 @@
         <v>3.25</v>
       </c>
       <c r="O3" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="P3" t="n">
         <v>1.75</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="R3" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="S3" t="n">
         <v>4.2</v>
       </c>
       <c r="T3" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="U3" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="V3" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="W3" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="X3" t="n">
         <v>12</v>
       </c>
       <c r="Y3" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="Z3" t="n">
         <v>60</v>
@@ -1189,7 +1189,7 @@
         <v>1000</v>
       </c>
       <c r="AF3" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AG3" t="n">
         <v>10.5</v>
@@ -1201,7 +1201,7 @@
         <v>1000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AK3" t="n">
         <v>21</v>
@@ -1234,22 +1234,22 @@
         <v>6.2</v>
       </c>
       <c r="AU3" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AV3" t="n">
         <v>18.5</v>
       </c>
       <c r="AW3" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AX3" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AY3" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AZ3" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="BA3" t="n">
         <v>42</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-18 11:58:18</t>
+          <t>2026-07-18 14:16:24</t>
         </is>
       </c>
     </row>
@@ -1371,10 +1371,10 @@
         <v>5.9</v>
       </c>
       <c r="H4" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="I4" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="J4" t="n">
         <v>3.6</v>
@@ -1422,7 +1422,7 @@
         <v>11.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="Z4" t="n">
         <v>9.800000000000001</v>
@@ -1497,7 +1497,7 @@
         <v>19.5</v>
       </c>
       <c r="AX4" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AY4" t="n">
         <v>19</v>
@@ -1506,22 +1506,22 @@
         <v>20</v>
       </c>
       <c r="BA4" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BB4" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BC4" t="n">
         <v>12.5</v>
       </c>
       <c r="BD4" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BE4" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BF4" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BG4" t="n">
         <v>14</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-18 11:58:18</t>
+          <t>2026-07-18 14:16:24</t>
         </is>
       </c>
     </row>
@@ -1643,7 +1643,7 @@
         <v>1.07</v>
       </c>
       <c r="N5" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="O5" t="n">
         <v>1.32</v>
@@ -1652,7 +1652,7 @@
         <v>1.92</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="R5" t="n">
         <v>1.34</v>
@@ -1700,7 +1700,7 @@
         <v>12.5</v>
       </c>
       <c r="AG5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AH5" t="n">
         <v>23</v>
@@ -1790,13 +1790,13 @@
         <v>12</v>
       </c>
       <c r="BK5" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="BL5" t="n">
         <v>160</v>
       </c>
       <c r="BM5" t="n">
-        <v>5.9</v>
+        <v>5.6</v>
       </c>
       <c r="BN5" t="n">
         <v>5</v>
@@ -1814,25 +1814,25 @@
         <v>32</v>
       </c>
       <c r="BS5" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="BT5" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BU5" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="BV5" t="n">
         <v>55</v>
       </c>
       <c r="BW5" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="BX5" t="n">
         <v>60</v>
       </c>
       <c r="BY5" t="n">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="BZ5" t="n">
         <v>0</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-18 11:58:18</t>
+          <t>2026-07-18 14:16:24</t>
         </is>
       </c>
     </row>
@@ -1885,13 +1885,13 @@
         <v>2.82</v>
       </c>
       <c r="J6" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="K6" t="n">
         <v>3.75</v>
       </c>
       <c r="L6" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="M6" t="n">
         <v>1.07</v>
@@ -2014,16 +2014,16 @@
         <v>13</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.01</v>
+        <v>30</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.01</v>
+        <v>34</v>
       </c>
       <c r="BC6" t="n">
         <v>1.01</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="BE6" t="n">
         <v>1.01</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-18 11:58:18</t>
+          <t>2026-07-18 14:16:24</t>
         </is>
       </c>
     </row>
@@ -2142,7 +2142,7 @@
         <v>3.3</v>
       </c>
       <c r="K7" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L7" t="n">
         <v>1.42</v>
@@ -2172,7 +2172,7 @@
         <v>1.76</v>
       </c>
       <c r="U7" t="n">
-        <v>1.91</v>
+        <v>2.08</v>
       </c>
       <c r="V7" t="n">
         <v>1.59</v>
@@ -2196,7 +2196,7 @@
         <v>14.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>9.4</v>
+        <v>8</v>
       </c>
       <c r="AD7" t="n">
         <v>14.5</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-18 11:58:18</t>
+          <t>2026-07-18 14:16:24</t>
         </is>
       </c>
     </row>
@@ -2381,118 +2381,118 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.4</v>
+        <v>1.04</v>
       </c>
       <c r="G8" t="n">
-        <v>1.47</v>
+        <v>2.14</v>
       </c>
       <c r="H8" t="n">
-        <v>8.199999999999999</v>
+        <v>1.9</v>
       </c>
       <c r="I8" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="J8" t="n">
-        <v>5</v>
+        <v>1.92</v>
       </c>
       <c r="K8" t="n">
-        <v>5.5</v>
+        <v>1000</v>
       </c>
       <c r="L8" t="n">
-        <v>1.33</v>
+        <v>1.01</v>
       </c>
       <c r="M8" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N8" t="n">
-        <v>4.3</v>
+        <v>1.26</v>
       </c>
       <c r="O8" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="P8" t="n">
-        <v>2.12</v>
+        <v>1.94</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.72</v>
+        <v>1.22</v>
       </c>
       <c r="R8" t="n">
-        <v>1.44</v>
+        <v>1.21</v>
       </c>
       <c r="S8" t="n">
-        <v>2.86</v>
+        <v>2.3</v>
       </c>
       <c r="T8" t="n">
-        <v>2</v>
+        <v>1.58</v>
       </c>
       <c r="U8" t="n">
-        <v>1.84</v>
+        <v>1.57</v>
       </c>
       <c r="V8" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="W8" t="n">
-        <v>3.1</v>
+        <v>1.89</v>
       </c>
       <c r="X8" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="Y8" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="Z8" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AA8" t="n">
-        <v>360</v>
+        <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AC8" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AD8" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AE8" t="n">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AF8" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AG8" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH8" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AI8" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AJ8" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AK8" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AL8" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AM8" t="n">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="AO8" t="n">
-        <v>220</v>
+        <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="AQ8" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="AR8" t="n">
         <v>1.01</v>
@@ -2501,10 +2501,10 @@
         <v>1.01</v>
       </c>
       <c r="AT8" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AU8" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV8" t="n">
         <v>1.01</v>
@@ -2513,22 +2513,22 @@
         <v>1.01</v>
       </c>
       <c r="AX8" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AY8" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AZ8" t="n">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA8" t="n">
         <v>1.01</v>
       </c>
       <c r="BB8" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="BC8" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BD8" t="n">
         <v>1.01</v>
@@ -2537,61 +2537,61 @@
         <v>1.01</v>
       </c>
       <c r="BF8" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BG8" t="n">
         <v>1.01</v>
       </c>
       <c r="BH8" t="n">
-        <v>4.6</v>
+        <v>1000</v>
       </c>
       <c r="BI8" t="n">
-        <v>3.05</v>
+        <v>1.01</v>
       </c>
       <c r="BJ8" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="BK8" t="n">
         <v>1.01</v>
       </c>
       <c r="BL8" t="n">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="BM8" t="n">
         <v>1.01</v>
       </c>
       <c r="BN8" t="n">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="BO8" t="n">
-        <v>3.05</v>
+        <v>1.01</v>
       </c>
       <c r="BP8" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ8" t="n">
         <v>1.01</v>
       </c>
       <c r="BR8" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="BS8" t="n">
         <v>1.01</v>
       </c>
       <c r="BT8" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BU8" t="n">
         <v>1.01</v>
       </c>
       <c r="BV8" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="BW8" t="n">
         <v>1.01</v>
       </c>
       <c r="BX8" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="BY8" t="n">
         <v>1.01</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-18 11:58:18</t>
+          <t>2026-07-18 14:16:24</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-18 11:58:18</t>
+          <t>2026-07-18 14:16:24</t>
         </is>
       </c>
     </row>
@@ -2907,7 +2907,7 @@
         <v>3.4</v>
       </c>
       <c r="L10" t="n">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="M10" t="n">
         <v>1.12</v>
@@ -2937,7 +2937,7 @@
         <v>1.78</v>
       </c>
       <c r="V10" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W10" t="n">
         <v>1.41</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-18 11:58:18</t>
+          <t>2026-07-18 14:16:24</t>
         </is>
       </c>
     </row>
@@ -3158,10 +3158,10 @@
         <v>4.6</v>
       </c>
       <c r="K11" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="L11" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="M11" t="n">
         <v>1.02</v>
@@ -3269,7 +3269,7 @@
         <v>10</v>
       </c>
       <c r="AV11" t="n">
-        <v>7.2</v>
+        <v>16</v>
       </c>
       <c r="AW11" t="n">
         <v>9.199999999999999</v>
@@ -3293,7 +3293,7 @@
         <v>13</v>
       </c>
       <c r="BD11" t="n">
-        <v>7.6</v>
+        <v>18.5</v>
       </c>
       <c r="BE11" t="n">
         <v>9.4</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-18 11:58:18</t>
+          <t>2026-07-18 14:16:24</t>
         </is>
       </c>
     </row>
@@ -3400,10 +3400,10 @@
         <v>2.32</v>
       </c>
       <c r="G12" t="n">
-        <v>2.86</v>
+        <v>2.8</v>
       </c>
       <c r="H12" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="I12" t="n">
         <v>4.3</v>
@@ -3412,7 +3412,7 @@
         <v>2.5</v>
       </c>
       <c r="K12" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="L12" t="n">
         <v>1.53</v>
@@ -3448,7 +3448,7 @@
         <v>1.31</v>
       </c>
       <c r="W12" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="X12" t="n">
         <v>8.800000000000001</v>
@@ -3490,7 +3490,7 @@
         <v>48</v>
       </c>
       <c r="AK12" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AL12" t="n">
         <v>80</v>
@@ -3499,7 +3499,7 @@
         <v>280</v>
       </c>
       <c r="AN12" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AO12" t="n">
         <v>120</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-18 11:58:18</t>
+          <t>2026-07-18 14:16:24</t>
         </is>
       </c>
     </row>
@@ -3717,10 +3717,10 @@
         <v>40</v>
       </c>
       <c r="AB13" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AC13" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD13" t="n">
         <v>13.5</v>
@@ -3729,10 +3729,10 @@
         <v>38</v>
       </c>
       <c r="AF13" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AG13" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AH13" t="n">
         <v>25</v>
@@ -3744,7 +3744,7 @@
         <v>100</v>
       </c>
       <c r="AK13" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AL13" t="n">
         <v>95</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-18 11:58:18</t>
+          <t>2026-07-18 14:16:24</t>
         </is>
       </c>
     </row>
@@ -3905,79 +3905,79 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="G14" t="n">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="H14" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="I14" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="J14" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="K14" t="n">
         <v>4.3</v>
       </c>
       <c r="L14" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="M14" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="N14" t="n">
         <v>2.78</v>
       </c>
       <c r="O14" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="P14" t="n">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="R14" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="S14" t="n">
-        <v>3.25</v>
+        <v>3.85</v>
       </c>
       <c r="T14" t="n">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="U14" t="n">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="V14" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="W14" t="n">
-        <v>2.04</v>
+        <v>1.98</v>
       </c>
       <c r="X14" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="Y14" t="n">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="Z14" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AA14" t="n">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AB14" t="n">
-        <v>9</v>
+        <v>7.6</v>
       </c>
       <c r="AC14" t="n">
-        <v>10</v>
+        <v>8.6</v>
       </c>
       <c r="AD14" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AE14" t="n">
         <v>110</v>
@@ -4013,10 +4013,10 @@
         <v>150</v>
       </c>
       <c r="AP14" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AQ14" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR14" t="n">
         <v>1.01</v>
@@ -4025,34 +4025,34 @@
         <v>1.01</v>
       </c>
       <c r="AT14" t="n">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="AU14" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AV14" t="n">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW14" t="n">
         <v>1.01</v>
       </c>
       <c r="AX14" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AY14" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AZ14" t="n">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="BA14" t="n">
         <v>1.01</v>
       </c>
       <c r="BB14" t="n">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC14" t="n">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD14" t="n">
         <v>1.01</v>
@@ -4061,74 +4061,74 @@
         <v>1.01</v>
       </c>
       <c r="BF14" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BG14" t="n">
         <v>1.01</v>
       </c>
       <c r="BH14" t="n">
-        <v>1000</v>
+        <v>3.5</v>
       </c>
       <c r="BI14" t="n">
-        <v>1.01</v>
+        <v>2.44</v>
       </c>
       <c r="BJ14" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BK14" t="n">
         <v>1.01</v>
       </c>
       <c r="BL14" t="n">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="BM14" t="n">
         <v>1.01</v>
       </c>
       <c r="BN14" t="n">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="BO14" t="n">
         <v>1.01</v>
       </c>
       <c r="BP14" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="BQ14" t="n">
         <v>1.01</v>
       </c>
       <c r="BR14" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BS14" t="n">
         <v>1.01</v>
       </c>
       <c r="BT14" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="BU14" t="n">
         <v>1.01</v>
       </c>
       <c r="BV14" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BW14" t="n">
         <v>1.01</v>
       </c>
       <c r="BX14" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="BY14" t="n">
         <v>1.01</v>
       </c>
       <c r="BZ14" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="CA14" t="n">
         <v>1.01</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-18 11:58:18</t>
+          <t>2026-07-18 14:16:24</t>
         </is>
       </c>
     </row>
@@ -4162,7 +4162,7 @@
         <v>2.34</v>
       </c>
       <c r="G15" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="H15" t="n">
         <v>3.25</v>
@@ -4171,7 +4171,7 @@
         <v>3.85</v>
       </c>
       <c r="J15" t="n">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="K15" t="n">
         <v>3.2</v>
@@ -4183,7 +4183,7 @@
         <v>1.12</v>
       </c>
       <c r="N15" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="O15" t="n">
         <v>1.51</v>
@@ -4198,7 +4198,7 @@
         <v>1.19</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="T15" t="n">
         <v>2.06</v>
@@ -4210,7 +4210,7 @@
         <v>1.35</v>
       </c>
       <c r="W15" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="X15" t="n">
         <v>10</v>
@@ -4321,68 +4321,68 @@
         <v>1.01</v>
       </c>
       <c r="BH15" t="n">
-        <v>1000</v>
+        <v>3</v>
       </c>
       <c r="BI15" t="n">
-        <v>1.01</v>
+        <v>2.3</v>
       </c>
       <c r="BJ15" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BK15" t="n">
         <v>1.01</v>
       </c>
       <c r="BL15" t="n">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="BM15" t="n">
         <v>1.01</v>
       </c>
       <c r="BN15" t="n">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="BO15" t="n">
         <v>1.01</v>
       </c>
       <c r="BP15" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BQ15" t="n">
         <v>1.01</v>
       </c>
       <c r="BR15" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BS15" t="n">
         <v>1.01</v>
       </c>
       <c r="BT15" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="BU15" t="n">
         <v>1.01</v>
       </c>
       <c r="BV15" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BW15" t="n">
         <v>1.01</v>
       </c>
       <c r="BX15" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BY15" t="n">
         <v>1.01</v>
       </c>
       <c r="BZ15" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="CA15" t="n">
         <v>1.01</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-18 11:58:18</t>
+          <t>2026-07-18 14:16:24</t>
         </is>
       </c>
     </row>
@@ -4416,40 +4416,40 @@
         <v>2.9</v>
       </c>
       <c r="G16" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="H16" t="n">
         <v>2.5</v>
       </c>
       <c r="I16" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="J16" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="K16" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="L16" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="M16" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N16" t="n">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="O16" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="P16" t="n">
-        <v>1.74</v>
+        <v>1.81</v>
       </c>
       <c r="Q16" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="R16" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="S16" t="n">
         <v>3.45</v>
@@ -4461,10 +4461,10 @@
         <v>2.06</v>
       </c>
       <c r="V16" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="W16" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="X16" t="n">
         <v>13</v>
@@ -4473,25 +4473,25 @@
         <v>11</v>
       </c>
       <c r="Z16" t="n">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="AA16" t="n">
         <v>48</v>
       </c>
       <c r="AB16" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD16" t="n">
         <v>12.5</v>
       </c>
-      <c r="AC16" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>13</v>
-      </c>
       <c r="AE16" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AF16" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AG16" t="n">
         <v>14</v>
@@ -4503,22 +4503,22 @@
         <v>46</v>
       </c>
       <c r="AJ16" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AK16" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AL16" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AM16" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AN16" t="n">
         <v>36</v>
       </c>
       <c r="AO16" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AP16" t="n">
         <v>1.01</v>
@@ -4527,7 +4527,7 @@
         <v>1.01</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AS16" t="n">
         <v>1.01</v>
@@ -4536,16 +4536,16 @@
         <v>1.01</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AV16" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AY16" t="n">
         <v>1.01</v>
@@ -4554,13 +4554,13 @@
         <v>1.01</v>
       </c>
       <c r="BA16" t="n">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="BB16" t="n">
         <v>1.01</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.01</v>
+        <v>30</v>
       </c>
       <c r="BD16" t="n">
         <v>1.01</v>
@@ -4569,13 +4569,13 @@
         <v>1.01</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BG16" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BH16" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="BI16" t="n">
         <v>2.7</v>
@@ -4611,13 +4611,13 @@
         <v>1.01</v>
       </c>
       <c r="BT16" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BU16" t="n">
         <v>1.01</v>
       </c>
       <c r="BV16" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BW16" t="n">
         <v>1.01</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-18 11:58:18</t>
+          <t>2026-07-18 14:16:24</t>
         </is>
       </c>
     </row>
@@ -4703,7 +4703,7 @@
         <v>1.72</v>
       </c>
       <c r="R17" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="S17" t="n">
         <v>2.82</v>
@@ -4712,7 +4712,7 @@
         <v>1.66</v>
       </c>
       <c r="U17" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="V17" t="n">
         <v>1.29</v>
@@ -4835,7 +4835,7 @@
         <v>3.05</v>
       </c>
       <c r="BJ17" t="n">
-        <v>9.6</v>
+        <v>11.5</v>
       </c>
       <c r="BK17" t="n">
         <v>5.8</v>
@@ -4844,7 +4844,7 @@
         <v>120</v>
       </c>
       <c r="BM17" t="n">
-        <v>7.4</v>
+        <v>5.9</v>
       </c>
       <c r="BN17" t="n">
         <v>5</v>
@@ -4853,7 +4853,7 @@
         <v>4.1</v>
       </c>
       <c r="BP17" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="BQ17" t="n">
         <v>7.8</v>
@@ -4862,7 +4862,7 @@
         <v>25</v>
       </c>
       <c r="BS17" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BT17" t="n">
         <v>8.199999999999999</v>
@@ -4871,26 +4871,26 @@
         <v>5</v>
       </c>
       <c r="BV17" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="BW17" t="n">
-        <v>6.4</v>
+        <v>5.4</v>
       </c>
       <c r="BX17" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="BY17" t="n">
-        <v>6.6</v>
+        <v>5.5</v>
       </c>
       <c r="BZ17" t="n">
         <v>19.5</v>
       </c>
       <c r="CA17" t="n">
-        <v>5.7</v>
+        <v>4.7</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-18 11:58:18</t>
+          <t>2026-07-18 14:16:24</t>
         </is>
       </c>
     </row>
@@ -4924,10 +4924,10 @@
         <v>2.7</v>
       </c>
       <c r="G18" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="H18" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="I18" t="n">
         <v>2.72</v>
@@ -4936,7 +4936,7 @@
         <v>3.6</v>
       </c>
       <c r="K18" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L18" t="n">
         <v>1.33</v>
@@ -4954,10 +4954,10 @@
         <v>2.18</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="R18" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="S18" t="n">
         <v>2.82</v>
@@ -4972,7 +4972,7 @@
         <v>1.58</v>
       </c>
       <c r="W18" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="X18" t="n">
         <v>19.5</v>
@@ -5074,7 +5074,7 @@
         <v>7</v>
       </c>
       <c r="BE18" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BF18" t="n">
         <v>15</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-18 11:58:18</t>
+          <t>2026-07-18 14:16:24</t>
         </is>
       </c>
     </row>
@@ -5217,7 +5217,7 @@
         <v>5.3</v>
       </c>
       <c r="T19" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="U19" t="n">
         <v>1.78</v>
@@ -5226,7 +5226,7 @@
         <v>1.47</v>
       </c>
       <c r="W19" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="X19" t="n">
         <v>9.6</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-18 11:58:18</t>
+          <t>2026-07-18 14:16:24</t>
         </is>
       </c>
     </row>
@@ -5432,37 +5432,37 @@
         <v>3.85</v>
       </c>
       <c r="G20" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="H20" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="I20" t="n">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="J20" t="n">
         <v>2.88</v>
       </c>
       <c r="K20" t="n">
-        <v>3.7</v>
+        <v>3.25</v>
       </c>
       <c r="L20" t="n">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="M20" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="N20" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="O20" t="n">
         <v>1.54</v>
       </c>
       <c r="P20" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="R20" t="n">
         <v>1.17</v>
@@ -5471,16 +5471,16 @@
         <v>5.5</v>
       </c>
       <c r="T20" t="n">
-        <v>1.11</v>
+        <v>2.12</v>
       </c>
       <c r="U20" t="n">
-        <v>1.11</v>
+        <v>1.71</v>
       </c>
       <c r="V20" t="n">
         <v>1.69</v>
       </c>
       <c r="W20" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="X20" t="n">
         <v>10</v>
@@ -5546,7 +5546,7 @@
         <v>9.4</v>
       </c>
       <c r="AS20" t="n">
-        <v>23</v>
+        <v>1.01</v>
       </c>
       <c r="AT20" t="n">
         <v>8</v>
@@ -5558,7 +5558,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AW20" t="n">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="AX20" t="n">
         <v>20</v>
@@ -5570,89 +5570,89 @@
         <v>18</v>
       </c>
       <c r="BA20" t="n">
-        <v>46</v>
+        <v>1.01</v>
       </c>
       <c r="BB20" t="n">
-        <v>75</v>
+        <v>1.01</v>
       </c>
       <c r="BC20" t="n">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="BD20" t="n">
-        <v>70</v>
+        <v>1.01</v>
       </c>
       <c r="BE20" t="n">
-        <v>140</v>
+        <v>1.01</v>
       </c>
       <c r="BF20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH20" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BI20" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BJ20" t="n">
+        <v>14</v>
+      </c>
+      <c r="BK20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL20" t="n">
+        <v>270</v>
+      </c>
+      <c r="BM20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN20" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BO20" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BP20" t="n">
+        <v>55</v>
+      </c>
+      <c r="BQ20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR20" t="n">
         <v>80</v>
       </c>
-      <c r="BG20" t="n">
+      <c r="BS20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT20" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BU20" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BV20" t="n">
         <v>24</v>
       </c>
-      <c r="BH20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BJ20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BP20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BR20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BT20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BV20" t="n">
-        <v>1000</v>
-      </c>
       <c r="BW20" t="n">
         <v>1.01</v>
       </c>
       <c r="BX20" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY20" t="n">
         <v>1.01</v>
       </c>
       <c r="BZ20" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="CA20" t="n">
         <v>1.01</v>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-18 11:58:18</t>
+          <t>2026-07-18 14:16:24</t>
         </is>
       </c>
     </row>
@@ -5713,19 +5713,19 @@
         <v>1.33</v>
       </c>
       <c r="P21" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="Q21" t="n">
         <v>1.97</v>
       </c>
       <c r="R21" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="S21" t="n">
         <v>3.45</v>
       </c>
       <c r="T21" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="U21" t="n">
         <v>2.1</v>
@@ -5785,13 +5785,13 @@
         <v>120</v>
       </c>
       <c r="AN21" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AO21" t="n">
         <v>55</v>
       </c>
       <c r="AP21" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AQ21" t="n">
         <v>13</v>
@@ -5803,7 +5803,7 @@
         <v>13</v>
       </c>
       <c r="AT21" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AU21" t="n">
         <v>7</v>
@@ -5812,7 +5812,7 @@
         <v>14.5</v>
       </c>
       <c r="AW21" t="n">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="AX21" t="n">
         <v>11.5</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-07-18 11:58:18</t>
+          <t>2026-07-18 14:16:24</t>
         </is>
       </c>
     </row>
@@ -5937,139 +5937,139 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="G22" t="n">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="H22" t="n">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="I22" t="n">
-        <v>1000</v>
+        <v>2.36</v>
       </c>
       <c r="J22" t="n">
-        <v>1.02</v>
+        <v>3</v>
       </c>
       <c r="K22" t="n">
-        <v>1000</v>
+        <v>3.6</v>
       </c>
       <c r="L22" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="M22" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N22" t="n">
-        <v>1.4</v>
+        <v>2.84</v>
       </c>
       <c r="O22" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="P22" t="n">
-        <v>1.25</v>
+        <v>1.62</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.35</v>
+        <v>2.12</v>
       </c>
       <c r="R22" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="S22" t="n">
-        <v>1.36</v>
+        <v>3.95</v>
       </c>
       <c r="T22" t="n">
-        <v>1.11</v>
+        <v>1.96</v>
       </c>
       <c r="U22" t="n">
-        <v>1.11</v>
+        <v>1.85</v>
       </c>
       <c r="V22" t="n">
-        <v>1.01</v>
+        <v>1.73</v>
       </c>
       <c r="W22" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="X22" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="Y22" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z22" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AA22" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AB22" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AC22" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD22" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AE22" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AF22" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AG22" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AH22" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AI22" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AK22" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AL22" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AM22" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AN22" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AO22" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="AR22" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AS22" t="n">
         <v>1.01</v>
       </c>
       <c r="AT22" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU22" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="AV22" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AW22" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AX22" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AY22" t="n">
         <v>1.01</v>
@@ -6084,16 +6084,16 @@
         <v>1.01</v>
       </c>
       <c r="BC22" t="n">
-        <v>1.01</v>
+        <v>42</v>
       </c>
       <c r="BD22" t="n">
         <v>1.01</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.01</v>
+        <v>100</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.01</v>
+        <v>55</v>
       </c>
       <c r="BG22" t="n">
         <v>1.01</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-07-18 11:58:18</t>
+          <t>2026-07-18 14:16:24</t>
         </is>
       </c>
     </row>
@@ -6191,13 +6191,13 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="G23" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="H23" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="I23" t="n">
         <v>1.66</v>
@@ -6206,13 +6206,13 @@
         <v>4.4</v>
       </c>
       <c r="K23" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="L23" t="n">
         <v>1.27</v>
       </c>
       <c r="M23" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N23" t="n">
         <v>5.2</v>
@@ -6242,7 +6242,7 @@
         <v>2.5</v>
       </c>
       <c r="W23" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="X23" t="n">
         <v>23</v>
@@ -6257,7 +6257,7 @@
         <v>17</v>
       </c>
       <c r="AB23" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="AC23" t="n">
         <v>11.5</v>
@@ -6269,7 +6269,7 @@
         <v>16.5</v>
       </c>
       <c r="AF23" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AG23" t="n">
         <v>26</v>
@@ -6302,22 +6302,22 @@
         <v>17</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AR23" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS23" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AT23" t="n">
         <v>19.5</v>
       </c>
       <c r="AU23" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AV23" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AW23" t="n">
         <v>12</v>
@@ -6326,7 +6326,7 @@
         <v>1.01</v>
       </c>
       <c r="AY23" t="n">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="AZ23" t="n">
         <v>14.5</v>
@@ -6350,13 +6350,13 @@
         <v>1.01</v>
       </c>
       <c r="BG23" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BH23" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="BI23" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="BJ23" t="n">
         <v>11</v>
@@ -6371,19 +6371,19 @@
         <v>1.01</v>
       </c>
       <c r="BN23" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BO23" t="n">
         <v>1.01</v>
       </c>
       <c r="BP23" t="n">
+        <v>48</v>
+      </c>
+      <c r="BQ23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR23" t="n">
         <v>50</v>
-      </c>
-      <c r="BQ23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BR23" t="n">
-        <v>55</v>
       </c>
       <c r="BS23" t="n">
         <v>1.01</v>
@@ -6401,7 +6401,7 @@
         <v>1.01</v>
       </c>
       <c r="BX23" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BY23" t="n">
         <v>1.01</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-07-18 11:58:18</t>
+          <t>2026-07-18 14:16:24</t>
         </is>
       </c>
     </row>
@@ -6448,7 +6448,7 @@
         <v>2.3</v>
       </c>
       <c r="G24" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="H24" t="n">
         <v>2.64</v>
@@ -6457,7 +6457,7 @@
         <v>2.98</v>
       </c>
       <c r="J24" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K24" t="n">
         <v>4.8</v>
@@ -6478,7 +6478,7 @@
         <v>2.84</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="R24" t="n">
         <v>1.75</v>
@@ -6607,7 +6607,7 @@
         <v>1.01</v>
       </c>
       <c r="BH24" t="n">
-        <v>5.9</v>
+        <v>5.1</v>
       </c>
       <c r="BI24" t="n">
         <v>3.8</v>
@@ -6619,7 +6619,7 @@
         <v>6</v>
       </c>
       <c r="BL24" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="BM24" t="n">
         <v>1.01</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-07-18 11:58:18</t>
+          <t>2026-07-18 14:16:24</t>
         </is>
       </c>
     </row>
@@ -6699,145 +6699,145 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.4</v>
+        <v>3.75</v>
       </c>
       <c r="G25" t="n">
-        <v>7</v>
+        <v>4.4</v>
       </c>
       <c r="H25" t="n">
-        <v>1.81</v>
+        <v>1.9</v>
       </c>
       <c r="I25" t="n">
-        <v>1000</v>
+        <v>2.04</v>
       </c>
       <c r="J25" t="n">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="K25" t="n">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="L25" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="M25" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="N25" t="n">
-        <v>1.34</v>
+        <v>4.1</v>
       </c>
       <c r="O25" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="P25" t="n">
-        <v>1.34</v>
+        <v>2.12</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.2</v>
+        <v>1.73</v>
       </c>
       <c r="R25" t="n">
-        <v>1.07</v>
+        <v>1.47</v>
       </c>
       <c r="S25" t="n">
-        <v>1.2</v>
+        <v>2.86</v>
       </c>
       <c r="T25" t="n">
-        <v>1.11</v>
+        <v>1.69</v>
       </c>
       <c r="U25" t="n">
-        <v>1.11</v>
+        <v>2.18</v>
       </c>
       <c r="V25" t="n">
-        <v>1.05</v>
+        <v>1.96</v>
       </c>
       <c r="W25" t="n">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="X25" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Y25" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Z25" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AA25" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AB25" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AC25" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD25" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AE25" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AF25" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AG25" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AH25" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AI25" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AK25" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AL25" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM25" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AN25" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AO25" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AR25" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AS25" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="AT25" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AU25" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AV25" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AW25" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="AX25" t="n">
         <v>1.01</v>
       </c>
       <c r="AY25" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AZ25" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BA25" t="n">
         <v>1.01</v>
@@ -6849,80 +6849,80 @@
         <v>1.01</v>
       </c>
       <c r="BD25" t="n">
-        <v>1.01</v>
+        <v>34</v>
       </c>
       <c r="BE25" t="n">
         <v>1.01</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.01</v>
+        <v>30</v>
       </c>
       <c r="BG25" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH25" t="n">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="BI25" t="n">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="BJ25" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK25" t="n">
         <v>1.01</v>
       </c>
       <c r="BL25" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="BM25" t="n">
         <v>1.01</v>
       </c>
       <c r="BN25" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BO25" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BP25" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BQ25" t="n">
         <v>1.01</v>
       </c>
       <c r="BR25" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BS25" t="n">
         <v>1.01</v>
       </c>
       <c r="BT25" t="n">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="BU25" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BV25" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="BW25" t="n">
         <v>1.01</v>
       </c>
       <c r="BX25" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BY25" t="n">
         <v>1.01</v>
       </c>
       <c r="BZ25" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="CA25" t="n">
         <v>1.01</v>
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-07-18 11:58:18</t>
+          <t>2026-07-18 14:16:24</t>
         </is>
       </c>
     </row>
@@ -6959,7 +6959,7 @@
         <v>3.85</v>
       </c>
       <c r="H26" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="I26" t="n">
         <v>2.08</v>
@@ -6986,10 +6986,10 @@
         <v>2.32</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="R26" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="S26" t="n">
         <v>2.76</v>
@@ -6998,7 +6998,7 @@
         <v>1.64</v>
       </c>
       <c r="U26" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="V26" t="n">
         <v>1.92</v>
@@ -7007,22 +7007,22 @@
         <v>1.35</v>
       </c>
       <c r="X26" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="Y26" t="n">
         <v>12.5</v>
       </c>
       <c r="Z26" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AA26" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AB26" t="n">
         <v>18.5</v>
       </c>
       <c r="AC26" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AD26" t="n">
         <v>11</v>
@@ -7031,37 +7031,37 @@
         <v>20</v>
       </c>
       <c r="AF26" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AG26" t="n">
         <v>16</v>
       </c>
       <c r="AH26" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AI26" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="AJ26" t="n">
         <v>1000</v>
       </c>
       <c r="AK26" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AL26" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AM26" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AN26" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AO26" t="n">
         <v>11.5</v>
       </c>
       <c r="AP26" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AQ26" t="n">
         <v>11</v>
@@ -7070,43 +7070,43 @@
         <v>13</v>
       </c>
       <c r="AS26" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AT26" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AU26" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV26" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AW26" t="n">
         <v>17.5</v>
       </c>
       <c r="AX26" t="n">
-        <v>19.5</v>
+        <v>26</v>
       </c>
       <c r="AY26" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AZ26" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BA26" t="n">
-        <v>19.5</v>
+        <v>26</v>
       </c>
       <c r="BB26" t="n">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="BC26" t="n">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="BD26" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="BE26" t="n">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="BF26" t="n">
         <v>21</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-07-18 11:58:18</t>
+          <t>2026-07-18 14:16:24</t>
         </is>
       </c>
     </row>
@@ -7210,19 +7210,19 @@
         <v>1.29</v>
       </c>
       <c r="G27" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="H27" t="n">
         <v>12</v>
       </c>
       <c r="I27" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="J27" t="n">
         <v>6.6</v>
       </c>
       <c r="K27" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="L27" t="n">
         <v>1.27</v>
@@ -7237,7 +7237,7 @@
         <v>1.17</v>
       </c>
       <c r="P27" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="Q27" t="n">
         <v>1.55</v>
@@ -7264,13 +7264,13 @@
         <v>30</v>
       </c>
       <c r="Y27" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="Z27" t="n">
         <v>130</v>
       </c>
       <c r="AA27" t="n">
-        <v>500</v>
+        <v>510</v>
       </c>
       <c r="AB27" t="n">
         <v>11</v>
@@ -7279,7 +7279,7 @@
         <v>15</v>
       </c>
       <c r="AD27" t="n">
-        <v>100</v>
+        <v>46</v>
       </c>
       <c r="AE27" t="n">
         <v>200</v>
@@ -7294,7 +7294,7 @@
         <v>32</v>
       </c>
       <c r="AI27" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AJ27" t="n">
         <v>10</v>
@@ -7312,10 +7312,10 @@
         <v>4.3</v>
       </c>
       <c r="AO27" t="n">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="AP27" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AQ27" t="n">
         <v>38</v>
@@ -7345,7 +7345,7 @@
         <v>10</v>
       </c>
       <c r="AZ27" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="BA27" t="n">
         <v>42</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-07-18 11:58:18</t>
+          <t>2026-07-18 14:16:24</t>
         </is>
       </c>
     </row>
@@ -7464,13 +7464,13 @@
         <v>5.5</v>
       </c>
       <c r="G28" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="H28" t="n">
         <v>1.63</v>
       </c>
       <c r="I28" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="J28" t="n">
         <v>4.7</v>
@@ -7491,7 +7491,7 @@
         <v>1.18</v>
       </c>
       <c r="P28" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="Q28" t="n">
         <v>1.55</v>
@@ -7500,7 +7500,7 @@
         <v>1.68</v>
       </c>
       <c r="S28" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="T28" t="n">
         <v>1.64</v>
@@ -7509,7 +7509,7 @@
         <v>2.46</v>
       </c>
       <c r="V28" t="n">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="W28" t="n">
         <v>1.21</v>
@@ -7521,16 +7521,16 @@
         <v>12.5</v>
       </c>
       <c r="Z28" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AA28" t="n">
         <v>17</v>
       </c>
       <c r="AB28" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AC28" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AD28" t="n">
         <v>10</v>
@@ -7539,7 +7539,7 @@
         <v>15</v>
       </c>
       <c r="AF28" t="n">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="AG28" t="n">
         <v>22</v>
@@ -7554,10 +7554,10 @@
         <v>160</v>
       </c>
       <c r="AK28" t="n">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="AL28" t="n">
-        <v>310</v>
+        <v>280</v>
       </c>
       <c r="AM28" t="n">
         <v>1000</v>
@@ -7572,7 +7572,7 @@
         <v>22</v>
       </c>
       <c r="AQ28" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AR28" t="n">
         <v>11</v>
@@ -7596,7 +7596,7 @@
         <v>42</v>
       </c>
       <c r="AY28" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="AZ28" t="n">
         <v>16</v>
@@ -7617,7 +7617,7 @@
         <v>60</v>
       </c>
       <c r="BF28" t="n">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="BG28" t="n">
         <v>5.8</v>
@@ -7662,7 +7662,7 @@
         <v>5.5</v>
       </c>
       <c r="BU28" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="BV28" t="n">
         <v>12</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-07-18 11:58:18</t>
+          <t>2026-07-18 14:16:24</t>
         </is>
       </c>
     </row>
@@ -7715,16 +7715,16 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2.7</v>
+        <v>3.7</v>
       </c>
       <c r="G29" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="H29" t="n">
-        <v>1.72</v>
+        <v>1.87</v>
       </c>
       <c r="I29" t="n">
-        <v>2.68</v>
+        <v>2.02</v>
       </c>
       <c r="J29" t="n">
         <v>3.2</v>
@@ -7733,28 +7733,28 @@
         <v>4</v>
       </c>
       <c r="L29" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="M29" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N29" t="n">
-        <v>1.1</v>
+        <v>5.1</v>
       </c>
       <c r="O29" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="P29" t="n">
-        <v>2.16</v>
+        <v>2.58</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.15</v>
+        <v>1.5</v>
       </c>
       <c r="R29" t="n">
-        <v>1.43</v>
+        <v>1.62</v>
       </c>
       <c r="S29" t="n">
-        <v>1.14</v>
+        <v>2.26</v>
       </c>
       <c r="T29" t="n">
         <v>1.11</v>
@@ -7763,10 +7763,10 @@
         <v>1.11</v>
       </c>
       <c r="V29" t="n">
-        <v>1.74</v>
+        <v>1.98</v>
       </c>
       <c r="W29" t="n">
-        <v>1.19</v>
+        <v>1.27</v>
       </c>
       <c r="X29" t="n">
         <v>1000</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-07-18 11:58:18</t>
+          <t>2026-07-18 14:16:24</t>
         </is>
       </c>
     </row>
@@ -7969,58 +7969,58 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="G30" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="H30" t="n">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="I30" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="J30" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="K30" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="L30" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="M30" t="n">
         <v>1.05</v>
       </c>
       <c r="N30" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="O30" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P30" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="R30" t="n">
         <v>1.47</v>
       </c>
       <c r="S30" t="n">
-        <v>2.86</v>
+        <v>2.94</v>
       </c>
       <c r="T30" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="U30" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="V30" t="n">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="W30" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="X30" t="n">
         <v>20</v>
@@ -8032,13 +8032,13 @@
         <v>10.5</v>
       </c>
       <c r="AA30" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AB30" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="AC30" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD30" t="n">
         <v>10.5</v>
@@ -8047,61 +8047,61 @@
         <v>17</v>
       </c>
       <c r="AF30" t="n">
+        <v>150</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>24</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI30" t="n">
         <v>65</v>
       </c>
-      <c r="AG30" t="n">
-        <v>26</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>34</v>
-      </c>
       <c r="AJ30" t="n">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="AK30" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AL30" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AM30" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AN30" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AO30" t="n">
-        <v>10</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AP30" t="n">
         <v>16</v>
       </c>
       <c r="AQ30" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AR30" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AS30" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AT30" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AU30" t="n">
         <v>9</v>
       </c>
       <c r="AV30" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AW30" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AX30" t="n">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="AY30" t="n">
         <v>20</v>
@@ -8110,34 +8110,34 @@
         <v>18</v>
       </c>
       <c r="BA30" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="BB30" t="n">
-        <v>8.4</v>
+        <v>44</v>
       </c>
       <c r="BC30" t="n">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="BD30" t="n">
-        <v>7.8</v>
+        <v>34</v>
       </c>
       <c r="BE30" t="n">
-        <v>8.199999999999999</v>
+        <v>38</v>
       </c>
       <c r="BF30" t="n">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="BG30" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BH30" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BI30" t="n">
         <v>3.15</v>
       </c>
       <c r="BJ30" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BK30" t="n">
         <v>1.01</v>
@@ -8149,28 +8149,28 @@
         <v>1.01</v>
       </c>
       <c r="BN30" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BO30" t="n">
         <v>1.01</v>
       </c>
       <c r="BP30" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="BQ30" t="n">
         <v>1.01</v>
       </c>
       <c r="BR30" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="BS30" t="n">
         <v>1.01</v>
       </c>
       <c r="BT30" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="BU30" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="BV30" t="n">
         <v>11.5</v>
@@ -8179,7 +8179,7 @@
         <v>1.01</v>
       </c>
       <c r="BX30" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="BY30" t="n">
         <v>1.01</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-07-18 11:58:18</t>
+          <t>2026-07-18 14:16:24</t>
         </is>
       </c>
     </row>
@@ -8223,7 +8223,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="G31" t="n">
         <v>3.15</v>
@@ -8238,7 +8238,7 @@
         <v>3.05</v>
       </c>
       <c r="K31" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="L31" t="n">
         <v>1.47</v>
@@ -8331,13 +8331,13 @@
         <v>42</v>
       </c>
       <c r="AP31" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AQ31" t="n">
         <v>7.6</v>
       </c>
       <c r="AR31" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AS31" t="n">
         <v>1.01</v>
@@ -8349,16 +8349,16 @@
         <v>5.8</v>
       </c>
       <c r="AV31" t="n">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW31" t="n">
         <v>1.01</v>
       </c>
       <c r="AX31" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AY31" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ31" t="n">
         <v>14.5</v>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-07-18 11:58:18</t>
+          <t>2026-07-18 14:16:24</t>
         </is>
       </c>
     </row>
@@ -8489,7 +8489,7 @@
         <v>1000</v>
       </c>
       <c r="J32" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K32" t="n">
         <v>1000</v>
@@ -8507,7 +8507,7 @@
         <v>1.37</v>
       </c>
       <c r="P32" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Q32" t="n">
         <v>1.37</v>
@@ -8516,7 +8516,7 @@
         <v>1.16</v>
       </c>
       <c r="S32" t="n">
-        <v>1.05</v>
+        <v>1.36</v>
       </c>
       <c r="T32" t="n">
         <v>1.11</v>
@@ -8528,7 +8528,7 @@
         <v>1.01</v>
       </c>
       <c r="W32" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X32" t="n">
         <v>1000</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-07-18 11:58:18</t>
+          <t>2026-07-18 14:16:24</t>
         </is>
       </c>
     </row>
@@ -8734,22 +8734,22 @@
         <v>6</v>
       </c>
       <c r="G33" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="H33" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="I33" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="J33" t="n">
         <v>3.5</v>
       </c>
       <c r="K33" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="L33" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="M33" t="n">
         <v>1.13</v>
@@ -8758,19 +8758,19 @@
         <v>2.54</v>
       </c>
       <c r="O33" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="P33" t="n">
         <v>1.52</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="R33" t="n">
         <v>1.18</v>
       </c>
       <c r="S33" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="T33" t="n">
         <v>2.42</v>
@@ -8782,7 +8782,7 @@
         <v>2.22</v>
       </c>
       <c r="W33" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X33" t="n">
         <v>11</v>
@@ -8866,7 +8866,7 @@
         <v>4.9</v>
       </c>
       <c r="AY33" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="AZ33" t="n">
         <v>4.7</v>
@@ -8893,7 +8893,7 @@
         <v>18</v>
       </c>
       <c r="BH33" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="BI33" t="n">
         <v>2.2</v>
@@ -8902,31 +8902,31 @@
         <v>15.5</v>
       </c>
       <c r="BK33" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BL33" t="n">
         <v>340</v>
       </c>
       <c r="BM33" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BN33" t="n">
         <v>11.5</v>
       </c>
       <c r="BO33" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="BP33" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="BQ33" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BR33" t="n">
         <v>120</v>
       </c>
       <c r="BS33" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BT33" t="n">
         <v>4.7</v>
@@ -8938,23 +8938,23 @@
         <v>17</v>
       </c>
       <c r="BW33" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BX33" t="n">
+        <v>55</v>
+      </c>
+      <c r="BY33" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BZ33" t="n">
         <v>50</v>
-      </c>
-      <c r="BY33" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BZ33" t="n">
-        <v>48</v>
       </c>
       <c r="CA33" t="n">
         <v>4.7</v>
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-07-18 11:58:18</t>
+          <t>2026-07-18 14:16:24</t>
         </is>
       </c>
     </row>
@@ -8985,7 +8985,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="G34" t="n">
         <v>3.75</v>
@@ -9000,7 +9000,7 @@
         <v>3.95</v>
       </c>
       <c r="K34" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L34" t="n">
         <v>1.33</v>
@@ -9009,7 +9009,7 @@
         <v>1.05</v>
       </c>
       <c r="N34" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="O34" t="n">
         <v>1.23</v>
@@ -9024,7 +9024,7 @@
         <v>1.47</v>
       </c>
       <c r="S34" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="T34" t="n">
         <v>1.62</v>
@@ -9093,55 +9093,55 @@
         <v>14.5</v>
       </c>
       <c r="AP34" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR34" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AS34" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AT34" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AU34" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AV34" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AW34" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="AX34" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AY34" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AZ34" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BA34" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BB34" t="n">
         <v>1.01</v>
       </c>
       <c r="BC34" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BD34" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BE34" t="n">
         <v>1.01</v>
       </c>
       <c r="BF34" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BG34" t="n">
         <v>1.01</v>
@@ -9153,7 +9153,7 @@
         <v>3.2</v>
       </c>
       <c r="BJ34" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="BK34" t="n">
         <v>4</v>
@@ -9162,7 +9162,7 @@
         <v>110</v>
       </c>
       <c r="BM34" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BN34" t="n">
         <v>7.2</v>
@@ -9174,13 +9174,13 @@
         <v>27</v>
       </c>
       <c r="BQ34" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BR34" t="n">
         <v>34</v>
       </c>
       <c r="BS34" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="BT34" t="n">
         <v>5.9</v>
@@ -9192,13 +9192,13 @@
         <v>15.5</v>
       </c>
       <c r="BW34" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BX34" t="n">
         <v>29</v>
       </c>
       <c r="BY34" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="BZ34" t="n">
         <v>0</v>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-07-18 11:58:18</t>
+          <t>2026-07-18 14:16:24</t>
         </is>
       </c>
     </row>
@@ -9239,230 +9239,230 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="I35" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="L35" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="M35" t="n">
         <v>1.01</v>
       </c>
       <c r="N35" t="n">
-        <v>1.1</v>
+        <v>2.58</v>
       </c>
       <c r="O35" t="n">
         <v>1.01</v>
       </c>
       <c r="P35" t="n">
-        <v>1.25</v>
+        <v>7</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="R35" t="n">
-        <v>1.25</v>
+        <v>3.45</v>
       </c>
       <c r="S35" t="n">
-        <v>1.05</v>
+        <v>1.3</v>
       </c>
       <c r="T35" t="n">
-        <v>1.11</v>
+        <v>1.21</v>
       </c>
       <c r="U35" t="n">
-        <v>1.11</v>
+        <v>4.1</v>
       </c>
       <c r="V35" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="W35" t="n">
-        <v>1.01</v>
+        <v>2.42</v>
       </c>
       <c r="X35" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="Y35" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="Z35" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AA35" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AB35" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AC35" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AD35" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AE35" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AF35" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AG35" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AH35" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AI35" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AJ35" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AK35" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AL35" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AM35" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AN35" t="n">
-        <v>1000</v>
+        <v>3.4</v>
       </c>
       <c r="AO35" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AP35" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AQ35" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="AR35" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AS35" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AT35" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="AU35" t="n">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="AV35" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="AW35" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="AX35" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="AY35" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AZ35" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BA35" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BB35" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BC35" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BD35" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BE35" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BF35" t="n">
-        <v>1.01</v>
+        <v>2.86</v>
       </c>
       <c r="BG35" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BH35" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BI35" t="n">
         <v>1.01</v>
       </c>
       <c r="BJ35" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="BK35" t="n">
         <v>1.01</v>
       </c>
       <c r="BL35" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BM35" t="n">
         <v>1.01</v>
       </c>
       <c r="BN35" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="BO35" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BP35" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BQ35" t="n">
         <v>1.01</v>
       </c>
       <c r="BR35" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BS35" t="n">
         <v>1.01</v>
       </c>
       <c r="BT35" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BU35" t="n">
         <v>1.01</v>
       </c>
       <c r="BV35" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BW35" t="n">
         <v>1.01</v>
       </c>
       <c r="BX35" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BY35" t="n">
         <v>1.01</v>
       </c>
       <c r="BZ35" t="n">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="CA35" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-07-18 11:58:18</t>
+          <t>2026-07-18 14:16:24</t>
         </is>
       </c>
     </row>
@@ -9493,230 +9493,230 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1.04</v>
+        <v>1.6</v>
       </c>
       <c r="G36" t="n">
-        <v>1.79</v>
+        <v>1.72</v>
       </c>
       <c r="H36" t="n">
-        <v>2.3</v>
+        <v>5.6</v>
       </c>
       <c r="I36" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="J36" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="K36" t="n">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="L36" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="M36" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N36" t="n">
-        <v>1.25</v>
+        <v>3.7</v>
       </c>
       <c r="O36" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="P36" t="n">
-        <v>1.25</v>
+        <v>1.94</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.28</v>
+        <v>1.9</v>
       </c>
       <c r="R36" t="n">
-        <v>1.07</v>
+        <v>1.36</v>
       </c>
       <c r="S36" t="n">
-        <v>1.28</v>
+        <v>3.35</v>
       </c>
       <c r="T36" t="n">
-        <v>1.11</v>
+        <v>1.9</v>
       </c>
       <c r="U36" t="n">
-        <v>1.11</v>
+        <v>1.91</v>
       </c>
       <c r="V36" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="W36" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="X36" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>24</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>200</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>25</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>110</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>110</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>17</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>42</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>150</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>140</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV36" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AW36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY36" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AZ36" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BA36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB36" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BC36" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BD36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF36" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BG36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH36" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BI36" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BJ36" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BK36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL36" t="n">
+        <v>170</v>
+      </c>
+      <c r="BM36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN36" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BO36" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BP36" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BQ36" t="n">
         <v>1.02</v>
       </c>
-      <c r="W36" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="X36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP36" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ36" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AR36" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS36" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT36" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AU36" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AV36" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AW36" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX36" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AY36" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AZ36" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BA36" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB36" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BC36" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BD36" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BE36" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF36" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG36" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI36" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BJ36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK36" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM36" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO36" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BP36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ36" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BR36" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BS36" t="n">
         <v>1.01</v>
       </c>
       <c r="BT36" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BU36" t="n">
         <v>1.01</v>
       </c>
       <c r="BV36" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BW36" t="n">
         <v>1.01</v>
       </c>
       <c r="BX36" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="BY36" t="n">
         <v>1.01</v>
       </c>
       <c r="BZ36" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="CA36" t="n">
         <v>1.01</v>
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-07-18 11:58:18</t>
+          <t>2026-07-18 14:16:24</t>
         </is>
       </c>
     </row>
@@ -9747,7 +9747,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="G37" t="n">
         <v>1000</v>
@@ -9759,7 +9759,7 @@
         <v>1000</v>
       </c>
       <c r="J37" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="K37" t="n">
         <v>1000</v>
@@ -9795,10 +9795,10 @@
         <v>1.11</v>
       </c>
       <c r="V37" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W37" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X37" t="n">
         <v>1000</v>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-07-18 11:58:18</t>
+          <t>2026-07-18 14:16:24</t>
         </is>
       </c>
     </row>
@@ -10010,7 +10010,7 @@
         <v>3.75</v>
       </c>
       <c r="I38" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="J38" t="n">
         <v>3.7</v>
@@ -10064,7 +10064,7 @@
         <v>36</v>
       </c>
       <c r="AA38" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AB38" t="n">
         <v>13</v>
@@ -10112,7 +10112,7 @@
         <v>14</v>
       </c>
       <c r="AQ38" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AR38" t="n">
         <v>1.01</v>
@@ -10121,16 +10121,16 @@
         <v>1.01</v>
       </c>
       <c r="AT38" t="n">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="AU38" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="AV38" t="n">
         <v>12.5</v>
       </c>
       <c r="AW38" t="n">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="AX38" t="n">
         <v>10.5</v>
@@ -10142,13 +10142,13 @@
         <v>12.5</v>
       </c>
       <c r="BA38" t="n">
-        <v>36</v>
+        <v>1.01</v>
       </c>
       <c r="BB38" t="n">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="BC38" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="BD38" t="n">
         <v>1.01</v>
@@ -10157,10 +10157,10 @@
         <v>1.01</v>
       </c>
       <c r="BF38" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG38" t="n">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="BH38" t="n">
         <v>4.3</v>
@@ -10224,7 +10224,7 @@
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-07-18 11:58:18</t>
+          <t>2026-07-18 14:16:24</t>
         </is>
       </c>
     </row>
@@ -10255,58 +10255,58 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>1.58</v>
+        <v>1.66</v>
       </c>
       <c r="G39" t="n">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="H39" t="n">
         <v>6.6</v>
       </c>
       <c r="I39" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="J39" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="K39" t="n">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="L39" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="M39" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N39" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="O39" t="n">
         <v>1.34</v>
       </c>
       <c r="P39" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="Q39" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="R39" t="n">
         <v>1.32</v>
       </c>
       <c r="S39" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="T39" t="n">
         <v>2.04</v>
       </c>
       <c r="U39" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="V39" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="W39" t="n">
-        <v>2.52</v>
+        <v>2.44</v>
       </c>
       <c r="X39" t="n">
         <v>16</v>
@@ -10318,28 +10318,28 @@
         <v>65</v>
       </c>
       <c r="AA39" t="n">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="AB39" t="n">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="AC39" t="n">
-        <v>11.5</v>
+        <v>9.4</v>
       </c>
       <c r="AD39" t="n">
         <v>29</v>
       </c>
       <c r="AE39" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AF39" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AG39" t="n">
         <v>10.5</v>
       </c>
       <c r="AH39" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI39" t="n">
         <v>120</v>
@@ -10348,79 +10348,79 @@
         <v>15.5</v>
       </c>
       <c r="AK39" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AL39" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AM39" t="n">
         <v>180</v>
       </c>
       <c r="AN39" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AO39" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AP39" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AQ39" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AR39" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="AS39" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AT39" t="n">
         <v>6.4</v>
       </c>
-      <c r="AT39" t="n">
-        <v>5.9</v>
-      </c>
       <c r="AU39" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV39" t="n">
+        <v>19</v>
+      </c>
+      <c r="AW39" t="n">
         <v>7.6</v>
       </c>
-      <c r="AV39" t="n">
-        <v>17</v>
-      </c>
-      <c r="AW39" t="n">
-        <v>6.2</v>
-      </c>
       <c r="AX39" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AY39" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ39" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BA39" t="n">
         <v>7.4</v>
       </c>
-      <c r="AZ39" t="n">
-        <v>19</v>
-      </c>
-      <c r="BA39" t="n">
-        <v>6.2</v>
-      </c>
       <c r="BB39" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="BC39" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BD39" t="n">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="BE39" t="n">
-        <v>6.2</v>
+        <v>7.6</v>
       </c>
       <c r="BF39" t="n">
-        <v>7.4</v>
+        <v>9</v>
       </c>
       <c r="BG39" t="n">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="BH39" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BI39" t="n">
-        <v>2.72</v>
+        <v>3</v>
       </c>
       <c r="BJ39" t="n">
         <v>12</v>
@@ -10438,7 +10438,7 @@
         <v>4.1</v>
       </c>
       <c r="BO39" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="BP39" t="n">
         <v>11</v>
@@ -10447,7 +10447,7 @@
         <v>1.01</v>
       </c>
       <c r="BR39" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="BS39" t="n">
         <v>1.01</v>
@@ -10459,26 +10459,26 @@
         <v>1.01</v>
       </c>
       <c r="BV39" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="BW39" t="n">
         <v>1.01</v>
       </c>
       <c r="BX39" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="BY39" t="n">
         <v>1.01</v>
       </c>
       <c r="BZ39" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="CA39" t="n">
         <v>1.01</v>
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-07-18 11:58:18</t>
+          <t>2026-07-18 14:16:24</t>
         </is>
       </c>
     </row>
@@ -10515,7 +10515,7 @@
         <v>6.2</v>
       </c>
       <c r="H40" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="I40" t="n">
         <v>1.65</v>
@@ -10524,10 +10524,10 @@
         <v>4.7</v>
       </c>
       <c r="K40" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="L40" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="M40" t="n">
         <v>1.01</v>
@@ -10542,10 +10542,10 @@
         <v>2.72</v>
       </c>
       <c r="Q40" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="R40" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="S40" t="n">
         <v>2.18</v>
@@ -10560,7 +10560,7 @@
         <v>2.56</v>
       </c>
       <c r="W40" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="X40" t="n">
         <v>38</v>
@@ -10732,7 +10732,7 @@
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-07-18 11:58:18</t>
+          <t>2026-07-18 14:16:24</t>
         </is>
       </c>
     </row>
@@ -10769,16 +10769,16 @@
         <v>2.4</v>
       </c>
       <c r="H41" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="I41" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="J41" t="n">
-        <v>3.3</v>
+        <v>2.96</v>
       </c>
       <c r="K41" t="n">
-        <v>3.9</v>
+        <v>6.6</v>
       </c>
       <c r="L41" t="n">
         <v>1.33</v>
@@ -10787,10 +10787,10 @@
         <v>1.01</v>
       </c>
       <c r="N41" t="n">
-        <v>3.3</v>
+        <v>2.58</v>
       </c>
       <c r="O41" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="P41" t="n">
         <v>1.64</v>
@@ -10811,7 +10811,7 @@
         <v>1.11</v>
       </c>
       <c r="V41" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="W41" t="n">
         <v>1.71</v>
@@ -10986,7 +10986,7 @@
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-07-18 11:58:18</t>
+          <t>2026-07-18 14:16:24</t>
         </is>
       </c>
     </row>
@@ -11017,10 +11017,10 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>2.8</v>
+        <v>2.86</v>
       </c>
       <c r="G42" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="H42" t="n">
         <v>2.94</v>
@@ -11035,22 +11035,22 @@
         <v>3.2</v>
       </c>
       <c r="L42" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="M42" t="n">
         <v>1.13</v>
       </c>
       <c r="N42" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="O42" t="n">
         <v>1.53</v>
       </c>
       <c r="P42" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="R42" t="n">
         <v>1.18</v>
@@ -11077,7 +11077,7 @@
         <v>9</v>
       </c>
       <c r="Z42" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AA42" t="n">
         <v>70</v>
@@ -11098,7 +11098,7 @@
         <v>18.5</v>
       </c>
       <c r="AG42" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="AH42" t="n">
         <v>24</v>
@@ -11125,7 +11125,7 @@
         <v>65</v>
       </c>
       <c r="AP42" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AQ42" t="n">
         <v>7.4</v>
@@ -11134,7 +11134,7 @@
         <v>16</v>
       </c>
       <c r="AS42" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="AT42" t="n">
         <v>7.2</v>
@@ -11158,22 +11158,22 @@
         <v>19</v>
       </c>
       <c r="BA42" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BB42" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BC42" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BD42" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BE42" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BF42" t="n">
         <v>6.6</v>
-      </c>
-      <c r="BF42" t="n">
-        <v>40</v>
       </c>
       <c r="BG42" t="n">
         <v>42</v>
@@ -11182,65 +11182,65 @@
         <v>3.1</v>
       </c>
       <c r="BI42" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="BJ42" t="n">
         <v>13.5</v>
       </c>
       <c r="BK42" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="BL42" t="n">
         <v>250</v>
       </c>
       <c r="BM42" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BN42" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BO42" t="n">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="BP42" t="n">
         <v>32</v>
       </c>
       <c r="BQ42" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BR42" t="n">
         <v>60</v>
       </c>
       <c r="BS42" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BT42" t="n">
         <v>7</v>
       </c>
       <c r="BU42" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BV42" t="n">
         <v>36</v>
       </c>
       <c r="BW42" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BX42" t="n">
         <v>65</v>
       </c>
       <c r="BY42" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BZ42" t="n">
         <v>65</v>
       </c>
       <c r="CA42" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-07-18 11:58:18</t>
+          <t>2026-07-18 14:16:24</t>
         </is>
       </c>
     </row>
@@ -11283,7 +11283,7 @@
         <v>2.18</v>
       </c>
       <c r="J43" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K43" t="n">
         <v>3.45</v>
@@ -11494,7 +11494,7 @@
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-07-18 11:58:18</t>
+          <t>2026-07-18 14:16:24</t>
         </is>
       </c>
     </row>
@@ -11534,16 +11534,16 @@
         <v>2.34</v>
       </c>
       <c r="I44" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="J44" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="K44" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L44" t="n">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="M44" t="n">
         <v>1.09</v>
@@ -11558,7 +11558,7 @@
         <v>1.68</v>
       </c>
       <c r="Q44" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="R44" t="n">
         <v>1.25</v>
@@ -11567,7 +11567,7 @@
         <v>4.1</v>
       </c>
       <c r="T44" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="U44" t="n">
         <v>1.93</v>
@@ -11585,7 +11585,7 @@
         <v>9</v>
       </c>
       <c r="Z44" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AA44" t="n">
         <v>36</v>
@@ -11594,7 +11594,7 @@
         <v>12</v>
       </c>
       <c r="AC44" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD44" t="n">
         <v>12</v>
@@ -11642,7 +11642,7 @@
         <v>12.5</v>
       </c>
       <c r="AS44" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT44" t="n">
         <v>9.800000000000001</v>
@@ -11654,7 +11654,7 @@
         <v>10</v>
       </c>
       <c r="AW44" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AX44" t="n">
         <v>20</v>
@@ -11666,19 +11666,19 @@
         <v>16.5</v>
       </c>
       <c r="BA44" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB44" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BC44" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="BC44" t="n">
-        <v>8.4</v>
-      </c>
       <c r="BD44" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE44" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BF44" t="n">
         <v>40</v>
@@ -11687,10 +11687,10 @@
         <v>20</v>
       </c>
       <c r="BH44" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="BI44" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="BJ44" t="n">
         <v>12</v>
@@ -11748,7 +11748,7 @@
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-07-18 11:58:18</t>
+          <t>2026-07-18 14:16:24</t>
         </is>
       </c>
     </row>
@@ -11779,112 +11779,112 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>1.39</v>
+        <v>1.89</v>
       </c>
       <c r="G45" t="n">
-        <v>1000</v>
+        <v>2.26</v>
       </c>
       <c r="H45" t="n">
-        <v>1.39</v>
+        <v>3.55</v>
       </c>
       <c r="I45" t="n">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="J45" t="n">
         <v>3.25</v>
       </c>
       <c r="K45" t="n">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="L45" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="M45" t="n">
         <v>1.06</v>
       </c>
       <c r="N45" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="O45" t="n">
         <v>1.3</v>
       </c>
       <c r="P45" t="n">
-        <v>1.16</v>
+        <v>1.81</v>
       </c>
       <c r="Q45" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="R45" t="n">
-        <v>1.15</v>
+        <v>1.31</v>
       </c>
       <c r="S45" t="n">
-        <v>2.96</v>
+        <v>3.1</v>
       </c>
       <c r="T45" t="n">
-        <v>1.11</v>
+        <v>1.72</v>
       </c>
       <c r="U45" t="n">
-        <v>1.11</v>
+        <v>1.98</v>
       </c>
       <c r="V45" t="n">
-        <v>1.02</v>
+        <v>1.27</v>
       </c>
       <c r="W45" t="n">
-        <v>1.08</v>
+        <v>1.79</v>
       </c>
       <c r="X45" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="Y45" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="Z45" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AA45" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AB45" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AC45" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AD45" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AE45" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AF45" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AG45" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH45" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI45" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AJ45" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AK45" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AL45" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AM45" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AN45" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AO45" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AP45" t="n">
         <v>1.01</v>
@@ -11941,55 +11941,55 @@
         <v>1.01</v>
       </c>
       <c r="BH45" t="n">
-        <v>1000</v>
+        <v>3.8</v>
       </c>
       <c r="BI45" t="n">
-        <v>1.01</v>
+        <v>2.8</v>
       </c>
       <c r="BJ45" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK45" t="n">
         <v>1.01</v>
       </c>
       <c r="BL45" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="BM45" t="n">
         <v>1.01</v>
       </c>
       <c r="BN45" t="n">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="BO45" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BP45" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="BQ45" t="n">
         <v>1.01</v>
       </c>
       <c r="BR45" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BS45" t="n">
         <v>1.01</v>
       </c>
       <c r="BT45" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="BU45" t="n">
         <v>1.01</v>
       </c>
       <c r="BV45" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BW45" t="n">
         <v>1.01</v>
       </c>
       <c r="BX45" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BY45" t="n">
         <v>1.01</v>
@@ -12002,7 +12002,7 @@
       </c>
       <c r="CB45" t="inlineStr">
         <is>
-          <t>2026-07-18 11:58:18</t>
+          <t>2026-07-18 14:16:24</t>
         </is>
       </c>
     </row>
@@ -12039,7 +12039,7 @@
         <v>1.73</v>
       </c>
       <c r="H46" t="n">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="I46" t="n">
         <v>6.8</v>
@@ -12057,13 +12057,13 @@
         <v>1.05</v>
       </c>
       <c r="N46" t="n">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
       <c r="O46" t="n">
         <v>1.24</v>
       </c>
       <c r="P46" t="n">
-        <v>2.06</v>
+        <v>2.14</v>
       </c>
       <c r="Q46" t="n">
         <v>1.69</v>
@@ -12072,7 +12072,7 @@
         <v>1.45</v>
       </c>
       <c r="S46" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="T46" t="n">
         <v>1.75</v>
@@ -12141,10 +12141,10 @@
         <v>100</v>
       </c>
       <c r="AP46" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AQ46" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="AR46" t="n">
         <v>1.01</v>
@@ -12153,13 +12153,13 @@
         <v>1.01</v>
       </c>
       <c r="AT46" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AU46" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AV46" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="AW46" t="n">
         <v>1.01</v>
@@ -12171,16 +12171,16 @@
         <v>1.01</v>
       </c>
       <c r="AZ46" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BA46" t="n">
         <v>1.01</v>
       </c>
       <c r="BB46" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BC46" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BD46" t="n">
         <v>1.01</v>
@@ -12189,7 +12189,7 @@
         <v>1.01</v>
       </c>
       <c r="BF46" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BG46" t="n">
         <v>1.01</v>
@@ -12256,7 +12256,7 @@
       </c>
       <c r="CB46" t="inlineStr">
         <is>
-          <t>2026-07-18 11:58:18</t>
+          <t>2026-07-18 14:16:24</t>
         </is>
       </c>
     </row>
@@ -12287,31 +12287,31 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="G47" t="n">
-        <v>2.24</v>
+        <v>2.18</v>
       </c>
       <c r="H47" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="I47" t="n">
         <v>5.6</v>
       </c>
       <c r="J47" t="n">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="K47" t="n">
         <v>3.7</v>
       </c>
       <c r="L47" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="M47" t="n">
         <v>1.09</v>
       </c>
       <c r="N47" t="n">
-        <v>2.8</v>
+        <v>3.05</v>
       </c>
       <c r="O47" t="n">
         <v>1.4</v>
@@ -12326,7 +12326,7 @@
         <v>1.25</v>
       </c>
       <c r="S47" t="n">
-        <v>1.05</v>
+        <v>3.75</v>
       </c>
       <c r="T47" t="n">
         <v>1.95</v>
@@ -12338,7 +12338,7 @@
         <v>1.21</v>
       </c>
       <c r="W47" t="n">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="X47" t="n">
         <v>1000</v>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="CB47" t="inlineStr">
         <is>
-          <t>2026-07-18 11:58:18</t>
+          <t>2026-07-18 14:16:24</t>
         </is>
       </c>
     </row>
@@ -12553,7 +12553,7 @@
         <v>1000</v>
       </c>
       <c r="J48" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="K48" t="n">
         <v>1000</v>
@@ -12589,10 +12589,10 @@
         <v>1.11</v>
       </c>
       <c r="V48" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W48" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X48" t="n">
         <v>1000</v>
@@ -12764,7 +12764,7 @@
       </c>
       <c r="CB48" t="inlineStr">
         <is>
-          <t>2026-07-18 11:58:18</t>
+          <t>2026-07-18 14:16:24</t>
         </is>
       </c>
     </row>
@@ -12795,7 +12795,7 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="G49" t="n">
         <v>2.44</v>
@@ -12813,7 +12813,7 @@
         <v>3.25</v>
       </c>
       <c r="L49" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="M49" t="n">
         <v>1.12</v>
@@ -12825,10 +12825,10 @@
         <v>1.5</v>
       </c>
       <c r="P49" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="Q49" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="R49" t="n">
         <v>1.2</v>
@@ -12837,10 +12837,10 @@
         <v>5.1</v>
       </c>
       <c r="T49" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="U49" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="V49" t="n">
         <v>1.32</v>
@@ -12885,7 +12885,7 @@
         <v>100</v>
       </c>
       <c r="AJ49" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AK49" t="n">
         <v>34</v>
@@ -12909,10 +12909,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AR49" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AS49" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AT49" t="n">
         <v>6.4</v>
@@ -12936,89 +12936,89 @@
         <v>19</v>
       </c>
       <c r="BA49" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB49" t="n">
         <v>7.6</v>
       </c>
       <c r="BC49" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BD49" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BE49" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BF49" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BG49" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BH49" t="n">
-        <v>1000</v>
+        <v>3.2</v>
       </c>
       <c r="BI49" t="n">
-        <v>1.01</v>
+        <v>2.26</v>
       </c>
       <c r="BJ49" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BK49" t="n">
         <v>1.01</v>
       </c>
       <c r="BL49" t="n">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="BM49" t="n">
         <v>1.01</v>
       </c>
       <c r="BN49" t="n">
-        <v>1000</v>
+        <v>5.8</v>
       </c>
       <c r="BO49" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BP49" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BQ49" t="n">
         <v>1.01</v>
       </c>
       <c r="BR49" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BS49" t="n">
         <v>1.01</v>
       </c>
       <c r="BT49" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU49" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BV49" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BW49" t="n">
         <v>1.01</v>
       </c>
       <c r="BX49" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="BY49" t="n">
         <v>1.01</v>
       </c>
       <c r="BZ49" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="CA49" t="n">
         <v>1.01</v>
       </c>
       <c r="CB49" t="inlineStr">
         <is>
-          <t>2026-07-18 11:58:18</t>
+          <t>2026-07-18 14:16:24</t>
         </is>
       </c>
     </row>
@@ -13049,25 +13049,25 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="G50" t="n">
         <v>1000</v>
       </c>
       <c r="H50" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="I50" t="n">
         <v>1000</v>
       </c>
       <c r="J50" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="K50" t="n">
         <v>1000</v>
       </c>
       <c r="L50" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="M50" t="n">
         <v>1.01</v>
@@ -13079,16 +13079,16 @@
         <v>1.02</v>
       </c>
       <c r="P50" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="Q50" t="n">
-        <v>1.02</v>
+        <v>1.45</v>
       </c>
       <c r="R50" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="S50" t="n">
-        <v>1.44</v>
+        <v>3.85</v>
       </c>
       <c r="T50" t="n">
         <v>1.11</v>
@@ -13097,10 +13097,10 @@
         <v>1.11</v>
       </c>
       <c r="V50" t="n">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="W50" t="n">
-        <v>1.01</v>
+        <v>1.68</v>
       </c>
       <c r="X50" t="n">
         <v>1000</v>
@@ -13211,68 +13211,68 @@
         <v>1.01</v>
       </c>
       <c r="BH50" t="n">
-        <v>1000</v>
+        <v>3.4</v>
       </c>
       <c r="BI50" t="n">
-        <v>1.01</v>
+        <v>2.4</v>
       </c>
       <c r="BJ50" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BK50" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BL50" t="n">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="BM50" t="n">
         <v>1.01</v>
       </c>
       <c r="BN50" t="n">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="BO50" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BP50" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="BQ50" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BR50" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BS50" t="n">
-        <v>1.01</v>
+        <v>25</v>
       </c>
       <c r="BT50" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU50" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BV50" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BW50" t="n">
-        <v>1.01</v>
+        <v>28</v>
       </c>
       <c r="BX50" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="BY50" t="n">
         <v>1.01</v>
       </c>
       <c r="BZ50" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="CA50" t="n">
-        <v>1.01</v>
+        <v>26</v>
       </c>
       <c r="CB50" t="inlineStr">
         <is>
-          <t>2026-07-18 11:58:18</t>
+          <t>2026-07-18 14:16:24</t>
         </is>
       </c>
     </row>
@@ -13303,145 +13303,145 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>2.82</v>
+        <v>2.68</v>
       </c>
       <c r="G51" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="H51" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="I51" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="J51" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="K51" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="L51" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="M51" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="N51" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O51" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="P51" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q51" t="n">
         <v>2.48</v>
       </c>
-      <c r="I51" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="J51" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="K51" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="L51" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="M51" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N51" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="O51" t="n">
+      <c r="R51" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S51" t="n">
+        <v>5</v>
+      </c>
+      <c r="T51" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="V51" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="W51" t="n">
         <v>1.44</v>
       </c>
-      <c r="P51" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="R51" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="S51" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="T51" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="U51" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="V51" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="W51" t="n">
-        <v>1.38</v>
-      </c>
       <c r="X51" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="Y51" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="Z51" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AA51" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AB51" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AC51" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AD51" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AE51" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AF51" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AG51" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AH51" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AI51" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AJ51" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AK51" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AL51" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AM51" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AN51" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AO51" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AP51" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AQ51" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AR51" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AS51" t="n">
         <v>1.01</v>
       </c>
       <c r="AT51" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AU51" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="AV51" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AW51" t="n">
         <v>1.01</v>
       </c>
       <c r="AX51" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AY51" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AZ51" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BA51" t="n">
         <v>1.01</v>
@@ -13465,68 +13465,68 @@
         <v>1.01</v>
       </c>
       <c r="BH51" t="n">
-        <v>1000</v>
+        <v>3</v>
       </c>
       <c r="BI51" t="n">
-        <v>1.01</v>
+        <v>2.3</v>
       </c>
       <c r="BJ51" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK51" t="n">
         <v>1.01</v>
       </c>
       <c r="BL51" t="n">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="BM51" t="n">
         <v>1.01</v>
       </c>
       <c r="BN51" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BO51" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BP51" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BQ51" t="n">
         <v>1.01</v>
       </c>
       <c r="BR51" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BS51" t="n">
         <v>1.01</v>
       </c>
       <c r="BT51" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BU51" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BV51" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BW51" t="n">
         <v>1.01</v>
       </c>
       <c r="BX51" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BY51" t="n">
         <v>1.01</v>
       </c>
       <c r="BZ51" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="CA51" t="n">
         <v>1.01</v>
       </c>
       <c r="CB51" t="inlineStr">
         <is>
-          <t>2026-07-18 11:58:18</t>
+          <t>2026-07-18 14:16:24</t>
         </is>
       </c>
     </row>
@@ -13557,230 +13557,230 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="G52" t="n">
-        <v>2.26</v>
+        <v>2.42</v>
       </c>
       <c r="H52" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="I52" t="n">
-        <v>5.2</v>
+        <v>4.5</v>
       </c>
       <c r="J52" t="n">
-        <v>2.8</v>
+        <v>2.96</v>
       </c>
       <c r="K52" t="n">
-        <v>4.1</v>
+        <v>3.45</v>
       </c>
       <c r="L52" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="M52" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="N52" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="O52" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="P52" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="Q52" t="n">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="R52" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="S52" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="T52" t="n">
-        <v>1.89</v>
+        <v>1.97</v>
       </c>
       <c r="U52" t="n">
-        <v>1.66</v>
+        <v>1.8</v>
       </c>
       <c r="V52" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="W52" t="n">
-        <v>1.8</v>
+        <v>1.71</v>
       </c>
       <c r="X52" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="Y52" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Z52" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AA52" t="n">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="AB52" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AC52" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD52" t="n">
-        <v>23</v>
+        <v>18.5</v>
       </c>
       <c r="AE52" t="n">
+        <v>90</v>
+      </c>
+      <c r="AF52" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AG52" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH52" t="n">
+        <v>27</v>
+      </c>
+      <c r="AI52" t="n">
         <v>100</v>
       </c>
-      <c r="AF52" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AG52" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH52" t="n">
-        <v>28</v>
-      </c>
-      <c r="AI52" t="n">
-        <v>120</v>
-      </c>
       <c r="AJ52" t="n">
+        <v>38</v>
+      </c>
+      <c r="AK52" t="n">
+        <v>36</v>
+      </c>
+      <c r="AL52" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM52" t="n">
+        <v>200</v>
+      </c>
+      <c r="AN52" t="n">
         <v>34</v>
       </c>
-      <c r="AK52" t="n">
-        <v>34</v>
-      </c>
-      <c r="AL52" t="n">
-        <v>70</v>
-      </c>
-      <c r="AM52" t="n">
-        <v>220</v>
-      </c>
-      <c r="AN52" t="n">
-        <v>30</v>
-      </c>
       <c r="AO52" t="n">
-        <v>140</v>
+        <v>110</v>
       </c>
       <c r="AP52" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AQ52" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="AR52" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AS52" t="n">
-        <v>80</v>
+        <v>1.01</v>
       </c>
       <c r="AT52" t="n">
-        <v>5.4</v>
+        <v>6.4</v>
       </c>
       <c r="AU52" t="n">
         <v>5.6</v>
       </c>
       <c r="AV52" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AW52" t="n">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="AX52" t="n">
-        <v>8.6</v>
+        <v>10.5</v>
       </c>
       <c r="AY52" t="n">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AZ52" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="BA52" t="n">
-        <v>65</v>
+        <v>1.01</v>
       </c>
       <c r="BB52" t="n">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="BC52" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="BD52" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="BE52" t="n">
-        <v>120</v>
+        <v>1.01</v>
       </c>
       <c r="BF52" t="n">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="BG52" t="n">
-        <v>80</v>
+        <v>1.01</v>
       </c>
       <c r="BH52" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="BI52" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="BJ52" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BK52" t="n">
-        <v>1.04</v>
+        <v>3.6</v>
       </c>
       <c r="BL52" t="n">
-        <v>240</v>
+        <v>220</v>
       </c>
       <c r="BM52" t="n">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="BN52" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="BO52" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="BP52" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BQ52" t="n">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="BR52" t="n">
+        <v>48</v>
+      </c>
+      <c r="BS52" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BT52" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BU52" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BV52" t="n">
         <v>46</v>
       </c>
-      <c r="BS52" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BT52" t="n">
-        <v>9</v>
-      </c>
-      <c r="BU52" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BV52" t="n">
-        <v>55</v>
-      </c>
       <c r="BW52" t="n">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BX52" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="BY52" t="n">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="BZ52" t="n">
         <v>50</v>
       </c>
       <c r="CA52" t="n">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="CB52" t="inlineStr">
         <is>
-          <t>2026-07-18 11:58:18</t>
+          <t>2026-07-18 14:16:24</t>
         </is>
       </c>
     </row>
@@ -13838,7 +13838,7 @@
         <v>4</v>
       </c>
       <c r="O53" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P53" t="n">
         <v>2.06</v>
@@ -13967,7 +13967,7 @@
         <v>6.2</v>
       </c>
       <c r="BF53" t="n">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="BG53" t="n">
         <v>6.2</v>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="CB53" t="inlineStr">
         <is>
-          <t>2026-07-18 11:58:18</t>
+          <t>2026-07-18 14:16:24</t>
         </is>
       </c>
     </row>
@@ -14083,22 +14083,22 @@
         <v>5.7</v>
       </c>
       <c r="L54" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="M54" t="n">
         <v>1.05</v>
       </c>
       <c r="N54" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="O54" t="n">
         <v>1.27</v>
       </c>
       <c r="P54" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q54" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="R54" t="n">
         <v>1.39</v>
@@ -14110,7 +14110,7 @@
         <v>2.14</v>
       </c>
       <c r="U54" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="V54" t="n">
         <v>1.09</v>
@@ -14119,7 +14119,7 @@
         <v>3.3</v>
       </c>
       <c r="X54" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Y54" t="n">
         <v>36</v>
@@ -14179,10 +14179,10 @@
         <v>4.7</v>
       </c>
       <c r="AR54" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AS54" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AT54" t="n">
         <v>6.6</v>
@@ -14191,10 +14191,10 @@
         <v>10</v>
       </c>
       <c r="AV54" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AW54" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AX54" t="n">
         <v>6.8</v>
@@ -14206,7 +14206,7 @@
         <v>4.7</v>
       </c>
       <c r="BA54" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BB54" t="n">
         <v>9.6</v>
@@ -14215,19 +14215,19 @@
         <v>13.5</v>
       </c>
       <c r="BD54" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BE54" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BF54" t="n">
         <v>5.3</v>
       </c>
       <c r="BG54" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BH54" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BI54" t="n">
         <v>3.05</v>
@@ -14288,7 +14288,7 @@
       </c>
       <c r="CB54" t="inlineStr">
         <is>
-          <t>2026-07-18 11:58:18</t>
+          <t>2026-07-18 14:16:24</t>
         </is>
       </c>
     </row>
@@ -14319,217 +14319,217 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>1.04</v>
+        <v>1.39</v>
       </c>
       <c r="G55" t="n">
         <v>1.5</v>
       </c>
       <c r="H55" t="n">
-        <v>1.04</v>
+        <v>5.5</v>
       </c>
       <c r="I55" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="J55" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="K55" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="L55" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="M55" t="n">
         <v>1.01</v>
       </c>
       <c r="N55" t="n">
-        <v>1.62</v>
+        <v>5.7</v>
       </c>
       <c r="O55" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="P55" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="R55" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="S55" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="T55" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="U55" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="V55" t="n">
         <v>1.12</v>
       </c>
-      <c r="P55" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="Q55" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="R55" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S55" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="T55" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U55" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V55" t="n">
-        <v>1.01</v>
-      </c>
       <c r="W55" t="n">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="X55" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="Y55" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="Z55" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AA55" t="n">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AB55" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AC55" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AD55" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AE55" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AF55" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AG55" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AH55" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI55" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AJ55" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AK55" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AL55" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AM55" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AN55" t="n">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="AO55" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AP55" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AQ55" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AR55" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="AS55" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="AT55" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AU55" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AV55" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AW55" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="AX55" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AY55" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="AZ55" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BA55" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BB55" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BC55" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BD55" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BE55" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BF55" t="n">
-        <v>1.01</v>
+        <v>2.7</v>
       </c>
       <c r="BG55" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BH55" t="n">
-        <v>1000</v>
+        <v>5.7</v>
       </c>
       <c r="BI55" t="n">
         <v>1.01</v>
       </c>
       <c r="BJ55" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK55" t="n">
         <v>1.01</v>
       </c>
       <c r="BL55" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="BM55" t="n">
         <v>1.01</v>
       </c>
       <c r="BN55" t="n">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="BO55" t="n">
         <v>1.01</v>
       </c>
       <c r="BP55" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="BQ55" t="n">
         <v>1.01</v>
       </c>
       <c r="BR55" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BS55" t="n">
         <v>1.01</v>
       </c>
       <c r="BT55" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BU55" t="n">
         <v>1.01</v>
       </c>
       <c r="BV55" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BW55" t="n">
         <v>1.01</v>
       </c>
       <c r="BX55" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY55" t="n">
         <v>1.01</v>
@@ -14542,7 +14542,7 @@
       </c>
       <c r="CB55" t="inlineStr">
         <is>
-          <t>2026-07-18 11:58:18</t>
+          <t>2026-07-18 14:16:24</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-19.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-19.xlsx
@@ -857,19 +857,19 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="G2" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="H2" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="I2" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="J2" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="K2" t="n">
         <v>3.8</v>
@@ -881,10 +881,10 @@
         <v>1.07</v>
       </c>
       <c r="N2" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="O2" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="P2" t="n">
         <v>2</v>
@@ -899,16 +899,16 @@
         <v>3.45</v>
       </c>
       <c r="T2" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="U2" t="n">
         <v>2.12</v>
       </c>
       <c r="V2" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="W2" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="X2" t="n">
         <v>16</v>
@@ -920,10 +920,10 @@
         <v>14</v>
       </c>
       <c r="AA2" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AB2" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AC2" t="n">
         <v>8.199999999999999</v>
@@ -935,7 +935,7 @@
         <v>23</v>
       </c>
       <c r="AF2" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AG2" t="n">
         <v>16.5</v>
@@ -947,7 +947,7 @@
         <v>36</v>
       </c>
       <c r="AJ2" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AK2" t="n">
         <v>46</v>
@@ -956,10 +956,10 @@
         <v>55</v>
       </c>
       <c r="AM2" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AN2" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AO2" t="n">
         <v>16</v>
@@ -989,7 +989,7 @@
         <v>18.5</v>
       </c>
       <c r="AX2" t="n">
-        <v>17.5</v>
+        <v>23</v>
       </c>
       <c r="AY2" t="n">
         <v>13.5</v>
@@ -998,19 +998,19 @@
         <v>15</v>
       </c>
       <c r="BA2" t="n">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="BB2" t="n">
-        <v>10.5</v>
+        <v>46</v>
       </c>
       <c r="BC2" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BD2" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="BE2" t="n">
-        <v>10.5</v>
+        <v>70</v>
       </c>
       <c r="BF2" t="n">
         <v>34</v>
@@ -1022,25 +1022,25 @@
         <v>4.1</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="BJ2" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BK2" t="n">
-        <v>1.04</v>
+        <v>7</v>
       </c>
       <c r="BL2" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="BM2" t="n">
         <v>1.04</v>
       </c>
       <c r="BN2" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BO2" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="BP2" t="n">
         <v>32</v>
@@ -1049,38 +1049,38 @@
         <v>1.04</v>
       </c>
       <c r="BR2" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BS2" t="n">
-        <v>1.04</v>
+        <v>28</v>
       </c>
       <c r="BT2" t="n">
         <v>5.1</v>
       </c>
       <c r="BU2" t="n">
-        <v>4.3</v>
+        <v>3.85</v>
       </c>
       <c r="BV2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BW2" t="n">
-        <v>1.04</v>
+        <v>11</v>
       </c>
       <c r="BX2" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="BY2" t="n">
         <v>1.04</v>
       </c>
       <c r="BZ2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="CA2" t="n">
         <v>1.04</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-18 14:16:24</t>
+          <t>2026-07-18 16:34:23</t>
         </is>
       </c>
     </row>
@@ -1111,10 +1111,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="G3" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="H3" t="n">
         <v>6.4</v>
@@ -1135,7 +1135,7 @@
         <v>1.09</v>
       </c>
       <c r="N3" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="O3" t="n">
         <v>1.42</v>
@@ -1153,22 +1153,22 @@
         <v>4.2</v>
       </c>
       <c r="T3" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="U3" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="V3" t="n">
         <v>1.17</v>
       </c>
       <c r="W3" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="X3" t="n">
         <v>12</v>
       </c>
       <c r="Y3" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="Z3" t="n">
         <v>60</v>
@@ -1177,7 +1177,7 @@
         <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AC3" t="n">
         <v>8.800000000000001</v>
@@ -1189,7 +1189,7 @@
         <v>1000</v>
       </c>
       <c r="AF3" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AG3" t="n">
         <v>10.5</v>
@@ -1201,7 +1201,7 @@
         <v>1000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AK3" t="n">
         <v>21</v>
@@ -1240,13 +1240,13 @@
         <v>18.5</v>
       </c>
       <c r="AW3" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AX3" t="n">
         <v>8</v>
       </c>
       <c r="AY3" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ3" t="n">
         <v>19.5</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-18 14:16:24</t>
+          <t>2026-07-18 16:34:23</t>
         </is>
       </c>
     </row>
@@ -1365,10 +1365,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="G4" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="H4" t="n">
         <v>1.76</v>
@@ -1377,7 +1377,7 @@
         <v>1.82</v>
       </c>
       <c r="J4" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="K4" t="n">
         <v>3.85</v>
@@ -1389,7 +1389,7 @@
         <v>1.09</v>
       </c>
       <c r="N4" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="O4" t="n">
         <v>1.43</v>
@@ -1431,7 +1431,7 @@
         <v>19.5</v>
       </c>
       <c r="AB4" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AC4" t="n">
         <v>8.4</v>
@@ -1443,7 +1443,7 @@
         <v>22</v>
       </c>
       <c r="AF4" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AG4" t="n">
         <v>23</v>
@@ -1512,16 +1512,16 @@
         <v>13.5</v>
       </c>
       <c r="BC4" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BD4" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BE4" t="n">
         <v>13.5</v>
       </c>
       <c r="BF4" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BG4" t="n">
         <v>14</v>
@@ -1557,7 +1557,7 @@
         <v>1.01</v>
       </c>
       <c r="BR4" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="BS4" t="n">
         <v>1.01</v>
@@ -1581,14 +1581,14 @@
         <v>1.01</v>
       </c>
       <c r="BZ4" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="CA4" t="n">
         <v>1.01</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-18 14:16:24</t>
+          <t>2026-07-18 16:34:23</t>
         </is>
       </c>
     </row>
@@ -1619,13 +1619,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="G5" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="H5" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="I5" t="n">
         <v>5.7</v>
@@ -1652,7 +1652,7 @@
         <v>1.92</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="R5" t="n">
         <v>1.34</v>
@@ -1670,7 +1670,7 @@
         <v>1.21</v>
       </c>
       <c r="W5" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="X5" t="n">
         <v>17</v>
@@ -1709,10 +1709,10 @@
         <v>75</v>
       </c>
       <c r="AJ5" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AK5" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AL5" t="n">
         <v>42</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-18 14:16:24</t>
+          <t>2026-07-18 16:34:23</t>
         </is>
       </c>
     </row>
@@ -1876,7 +1876,7 @@
         <v>2.78</v>
       </c>
       <c r="G6" t="n">
-        <v>3.15</v>
+        <v>2.98</v>
       </c>
       <c r="H6" t="n">
         <v>2.54</v>
@@ -1888,7 +1888,7 @@
         <v>3.3</v>
       </c>
       <c r="K6" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L6" t="n">
         <v>1.41</v>
@@ -1897,7 +1897,7 @@
         <v>1.07</v>
       </c>
       <c r="N6" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="O6" t="n">
         <v>1.33</v>
@@ -1918,13 +1918,13 @@
         <v>1.75</v>
       </c>
       <c r="U6" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="V6" t="n">
         <v>1.55</v>
       </c>
       <c r="W6" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="X6" t="n">
         <v>16</v>
@@ -1936,7 +1936,7 @@
         <v>18</v>
       </c>
       <c r="AA6" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AB6" t="n">
         <v>12</v>
@@ -2035,43 +2035,43 @@
         <v>19</v>
       </c>
       <c r="BH6" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="BI6" t="n">
-        <v>3</v>
+        <v>2.78</v>
       </c>
       <c r="BJ6" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="BK6" t="n">
-        <v>4.7</v>
+        <v>3.8</v>
       </c>
       <c r="BL6" t="n">
         <v>140</v>
       </c>
       <c r="BM6" t="n">
-        <v>8.800000000000001</v>
+        <v>5.6</v>
       </c>
       <c r="BN6" t="n">
         <v>6.8</v>
       </c>
       <c r="BO6" t="n">
-        <v>5.3</v>
+        <v>4.7</v>
       </c>
       <c r="BP6" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="BQ6" t="n">
-        <v>6.6</v>
+        <v>4.8</v>
       </c>
       <c r="BR6" t="n">
         <v>40</v>
       </c>
       <c r="BS6" t="n">
-        <v>7.6</v>
+        <v>5.1</v>
       </c>
       <c r="BT6" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="BU6" t="n">
         <v>4.5</v>
@@ -2080,13 +2080,13 @@
         <v>24</v>
       </c>
       <c r="BW6" t="n">
-        <v>6.8</v>
+        <v>4.7</v>
       </c>
       <c r="BX6" t="n">
         <v>38</v>
       </c>
       <c r="BY6" t="n">
-        <v>7.6</v>
+        <v>5.1</v>
       </c>
       <c r="BZ6" t="n">
         <v>0</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-18 14:16:24</t>
+          <t>2026-07-18 16:34:23</t>
         </is>
       </c>
     </row>
@@ -2127,13 +2127,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="G7" t="n">
         <v>3.35</v>
       </c>
       <c r="H7" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="I7" t="n">
         <v>2.68</v>
@@ -2211,7 +2211,7 @@
         <v>16.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI7" t="n">
         <v>55</v>
@@ -2220,7 +2220,7 @@
         <v>65</v>
       </c>
       <c r="AK7" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AL7" t="n">
         <v>60</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-18 14:16:24</t>
+          <t>2026-07-18 16:34:23</t>
         </is>
       </c>
     </row>
@@ -2381,118 +2381,118 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.04</v>
+        <v>1.39</v>
       </c>
       <c r="G8" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="H8" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="I8" t="n">
+        <v>10</v>
+      </c>
+      <c r="J8" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="K8" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N8" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="P8" t="n">
         <v>2.14</v>
       </c>
-      <c r="H8" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="I8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J8" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="K8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="N8" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="P8" t="n">
-        <v>1.94</v>
-      </c>
       <c r="Q8" t="n">
-        <v>1.22</v>
+        <v>1.71</v>
       </c>
       <c r="R8" t="n">
-        <v>1.21</v>
+        <v>1.44</v>
       </c>
       <c r="S8" t="n">
-        <v>2.3</v>
+        <v>2.86</v>
       </c>
       <c r="T8" t="n">
-        <v>1.58</v>
+        <v>1.98</v>
       </c>
       <c r="U8" t="n">
-        <v>1.57</v>
+        <v>1.84</v>
       </c>
       <c r="V8" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="W8" t="n">
-        <v>1.89</v>
+        <v>3.05</v>
       </c>
       <c r="X8" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Y8" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="Z8" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AA8" t="n">
-        <v>1000</v>
+        <v>370</v>
       </c>
       <c r="AB8" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AC8" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AD8" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AE8" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AF8" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AG8" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AI8" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AK8" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AL8" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AM8" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AN8" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="AO8" t="n">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AR8" t="n">
         <v>1.01</v>
@@ -2501,10 +2501,10 @@
         <v>1.01</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AV8" t="n">
         <v>1.01</v>
@@ -2513,22 +2513,22 @@
         <v>1.01</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="BA8" t="n">
         <v>1.01</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BD8" t="n">
         <v>1.01</v>
@@ -2537,61 +2537,61 @@
         <v>1.01</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BG8" t="n">
         <v>1.01</v>
       </c>
       <c r="BH8" t="n">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="BI8" t="n">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="BJ8" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="BK8" t="n">
         <v>1.01</v>
       </c>
       <c r="BL8" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="BM8" t="n">
         <v>1.01</v>
       </c>
       <c r="BN8" t="n">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="BP8" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BQ8" t="n">
         <v>1.01</v>
       </c>
       <c r="BR8" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BS8" t="n">
         <v>1.01</v>
       </c>
       <c r="BT8" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BU8" t="n">
         <v>1.01</v>
       </c>
       <c r="BV8" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="BW8" t="n">
         <v>1.01</v>
       </c>
       <c r="BX8" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="BY8" t="n">
         <v>1.01</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-18 14:16:24</t>
+          <t>2026-07-18 16:34:23</t>
         </is>
       </c>
     </row>
@@ -2650,7 +2650,7 @@
         <v>2.64</v>
       </c>
       <c r="K9" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="L9" t="n">
         <v>1.53</v>
@@ -2662,13 +2662,13 @@
         <v>2.24</v>
       </c>
       <c r="O9" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="P9" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="R9" t="n">
         <v>1.18</v>
@@ -2683,7 +2683,7 @@
         <v>1.63</v>
       </c>
       <c r="V9" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W9" t="n">
         <v>1.47</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-18 14:16:24</t>
+          <t>2026-07-18 16:34:23</t>
         </is>
       </c>
     </row>
@@ -2931,10 +2931,10 @@
         <v>4.4</v>
       </c>
       <c r="T10" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
         <v>1.47</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-18 14:16:24</t>
+          <t>2026-07-18 16:34:23</t>
         </is>
       </c>
     </row>
@@ -3143,13 +3143,13 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="G11" t="n">
         <v>1.67</v>
       </c>
       <c r="H11" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="I11" t="n">
         <v>5.9</v>
@@ -3173,7 +3173,7 @@
         <v>1.17</v>
       </c>
       <c r="P11" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="Q11" t="n">
         <v>1.51</v>
@@ -3239,7 +3239,7 @@
         <v>15.5</v>
       </c>
       <c r="AL11" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AM11" t="n">
         <v>70</v>
@@ -3254,7 +3254,7 @@
         <v>7.8</v>
       </c>
       <c r="AQ11" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AR11" t="n">
         <v>8.800000000000001</v>
@@ -3272,7 +3272,7 @@
         <v>16</v>
       </c>
       <c r="AW11" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AX11" t="n">
         <v>11</v>
@@ -3296,10 +3296,10 @@
         <v>18.5</v>
       </c>
       <c r="BE11" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF11" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BG11" t="n">
         <v>36</v>
@@ -3314,16 +3314,16 @@
         <v>11</v>
       </c>
       <c r="BK11" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="BL11" t="n">
         <v>95</v>
       </c>
       <c r="BM11" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BN11" t="n">
         <v>5.3</v>
-      </c>
-      <c r="BN11" t="n">
-        <v>5.2</v>
       </c>
       <c r="BO11" t="n">
         <v>3.75</v>
@@ -3332,41 +3332,41 @@
         <v>11</v>
       </c>
       <c r="BQ11" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="BR11" t="n">
         <v>22</v>
       </c>
       <c r="BS11" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="BT11" t="n">
         <v>11</v>
       </c>
       <c r="BU11" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="BV11" t="n">
         <v>46</v>
       </c>
       <c r="BW11" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="BX11" t="n">
         <v>46</v>
       </c>
       <c r="BY11" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="BZ11" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-18 14:16:24</t>
+          <t>2026-07-18 16:34:23</t>
         </is>
       </c>
     </row>
@@ -3442,7 +3442,7 @@
         <v>2.12</v>
       </c>
       <c r="U12" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="V12" t="n">
         <v>1.31</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-18 14:16:24</t>
+          <t>2026-07-18 16:34:23</t>
         </is>
       </c>
     </row>
@@ -3666,7 +3666,7 @@
         <v>2.76</v>
       </c>
       <c r="K13" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="L13" t="n">
         <v>1.52</v>
@@ -3690,7 +3690,7 @@
         <v>1.18</v>
       </c>
       <c r="S13" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="T13" t="n">
         <v>2</v>
@@ -3702,7 +3702,7 @@
         <v>1.59</v>
       </c>
       <c r="W13" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="X13" t="n">
         <v>10.5</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-18 14:16:24</t>
+          <t>2026-07-18 16:34:23</t>
         </is>
       </c>
     </row>
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="G14" t="n">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="H14" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="I14" t="n">
         <v>6</v>
@@ -3920,10 +3920,10 @@
         <v>3.2</v>
       </c>
       <c r="K14" t="n">
-        <v>4.3</v>
+        <v>3.95</v>
       </c>
       <c r="L14" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="M14" t="n">
         <v>1.09</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-18 14:16:24</t>
+          <t>2026-07-18 16:34:23</t>
         </is>
       </c>
     </row>
@@ -4192,7 +4192,7 @@
         <v>1.54</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="R15" t="n">
         <v>1.19</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-18 14:16:24</t>
+          <t>2026-07-18 16:34:23</t>
         </is>
       </c>
     </row>
@@ -4425,7 +4425,7 @@
         <v>2.8</v>
       </c>
       <c r="J16" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K16" t="n">
         <v>3.6</v>
@@ -4452,7 +4452,7 @@
         <v>1.31</v>
       </c>
       <c r="S16" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="T16" t="n">
         <v>1.77</v>
@@ -4476,7 +4476,7 @@
         <v>17.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AB16" t="n">
         <v>12</v>
@@ -4530,19 +4530,19 @@
         <v>12.5</v>
       </c>
       <c r="AS16" t="n">
-        <v>1.01</v>
+        <v>25</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU16" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="AV16" t="n">
         <v>10</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AX16" t="n">
         <v>15.5</v>
@@ -4554,7 +4554,7 @@
         <v>1.01</v>
       </c>
       <c r="BA16" t="n">
-        <v>36</v>
+        <v>1.01</v>
       </c>
       <c r="BB16" t="n">
         <v>1.01</v>
@@ -4569,10 +4569,10 @@
         <v>1.01</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="BG16" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="BH16" t="n">
         <v>3.6</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-18 14:16:24</t>
+          <t>2026-07-18 16:34:23</t>
         </is>
       </c>
     </row>
@@ -4667,10 +4667,10 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="G17" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="H17" t="n">
         <v>4</v>
@@ -4838,59 +4838,59 @@
         <v>11.5</v>
       </c>
       <c r="BK17" t="n">
-        <v>5.8</v>
+        <v>3.35</v>
       </c>
       <c r="BL17" t="n">
         <v>120</v>
       </c>
       <c r="BM17" t="n">
-        <v>5.9</v>
+        <v>4.5</v>
       </c>
       <c r="BN17" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="BO17" t="n">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="BP17" t="n">
         <v>15.5</v>
       </c>
       <c r="BQ17" t="n">
-        <v>7.8</v>
+        <v>3.65</v>
       </c>
       <c r="BR17" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="BS17" t="n">
-        <v>5</v>
+        <v>4.1</v>
       </c>
       <c r="BT17" t="n">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BU17" t="n">
-        <v>5</v>
+        <v>3.15</v>
       </c>
       <c r="BV17" t="n">
         <v>40</v>
       </c>
       <c r="BW17" t="n">
-        <v>5.4</v>
+        <v>4.2</v>
       </c>
       <c r="BX17" t="n">
         <v>48</v>
       </c>
       <c r="BY17" t="n">
-        <v>5.5</v>
+        <v>4.3</v>
       </c>
       <c r="BZ17" t="n">
-        <v>19.5</v>
+        <v>23</v>
       </c>
       <c r="CA17" t="n">
-        <v>4.7</v>
+        <v>3.95</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-18 14:16:24</t>
+          <t>2026-07-18 16:34:23</t>
         </is>
       </c>
     </row>
@@ -4921,22 +4921,22 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="G18" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="H18" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="I18" t="n">
         <v>2.72</v>
       </c>
       <c r="J18" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K18" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="L18" t="n">
         <v>1.33</v>
@@ -4972,7 +4972,7 @@
         <v>1.58</v>
       </c>
       <c r="W18" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="X18" t="n">
         <v>19.5</v>
@@ -4987,7 +4987,7 @@
         <v>44</v>
       </c>
       <c r="AB18" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AC18" t="n">
         <v>10.5</v>
@@ -5038,7 +5038,7 @@
         <v>15.5</v>
       </c>
       <c r="AS18" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AT18" t="n">
         <v>11.5</v>
@@ -5068,7 +5068,7 @@
         <v>34</v>
       </c>
       <c r="BC18" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BD18" t="n">
         <v>7</v>
@@ -5089,7 +5089,7 @@
         <v>3.05</v>
       </c>
       <c r="BJ18" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BK18" t="n">
         <v>6.8</v>
@@ -5098,28 +5098,28 @@
         <v>110</v>
       </c>
       <c r="BM18" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="BN18" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BO18" t="n">
-        <v>4.6</v>
+        <v>5.3</v>
       </c>
       <c r="BP18" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="BQ18" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BR18" t="n">
         <v>36</v>
       </c>
       <c r="BS18" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="BT18" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BU18" t="n">
         <v>5</v>
@@ -5128,23 +5128,23 @@
         <v>22</v>
       </c>
       <c r="BW18" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="BX18" t="n">
         <v>34</v>
       </c>
       <c r="BY18" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="BZ18" t="n">
         <v>25</v>
       </c>
       <c r="CA18" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-18 14:16:24</t>
+          <t>2026-07-18 16:34:23</t>
         </is>
       </c>
     </row>
@@ -5175,13 +5175,13 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="G19" t="n">
         <v>3.15</v>
       </c>
       <c r="H19" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="I19" t="n">
         <v>3.15</v>
@@ -5190,7 +5190,7 @@
         <v>2.92</v>
       </c>
       <c r="K19" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="L19" t="n">
         <v>1.56</v>
@@ -5214,7 +5214,7 @@
         <v>1.2</v>
       </c>
       <c r="S19" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="T19" t="n">
         <v>2.04</v>
@@ -5232,16 +5232,16 @@
         <v>9.6</v>
       </c>
       <c r="Y19" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="Z19" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AA19" t="n">
         <v>60</v>
       </c>
       <c r="AB19" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC19" t="n">
         <v>7.4</v>
@@ -5253,13 +5253,13 @@
         <v>55</v>
       </c>
       <c r="AF19" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AG19" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AH19" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AI19" t="n">
         <v>75</v>
@@ -5268,13 +5268,13 @@
         <v>65</v>
       </c>
       <c r="AK19" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AL19" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AM19" t="n">
-        <v>210</v>
+        <v>190</v>
       </c>
       <c r="AN19" t="n">
         <v>65</v>
@@ -5292,7 +5292,7 @@
         <v>14</v>
       </c>
       <c r="AS19" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AT19" t="n">
         <v>6.6</v>
@@ -5304,7 +5304,7 @@
         <v>10.5</v>
       </c>
       <c r="AW19" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AX19" t="n">
         <v>14</v>
@@ -5316,25 +5316,25 @@
         <v>17</v>
       </c>
       <c r="BA19" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BC19" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BD19" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BG19" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BH19" t="n">
         <v>2.96</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-18 14:16:24</t>
+          <t>2026-07-18 16:34:23</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
         <v>3.85</v>
       </c>
       <c r="G20" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="H20" t="n">
         <v>2.18</v>
@@ -5480,7 +5480,7 @@
         <v>1.69</v>
       </c>
       <c r="W20" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="X20" t="n">
         <v>10</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-18 14:16:24</t>
+          <t>2026-07-18 16:34:23</t>
         </is>
       </c>
     </row>
@@ -5683,7 +5683,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="G21" t="n">
         <v>2.18</v>
@@ -5692,13 +5692,13 @@
         <v>3.85</v>
       </c>
       <c r="I21" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="J21" t="n">
         <v>3.55</v>
       </c>
       <c r="K21" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L21" t="n">
         <v>1.41</v>
@@ -5707,22 +5707,22 @@
         <v>1.07</v>
       </c>
       <c r="N21" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="O21" t="n">
         <v>1.33</v>
       </c>
       <c r="P21" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="R21" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S21" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="T21" t="n">
         <v>1.8</v>
@@ -5731,7 +5731,7 @@
         <v>2.1</v>
       </c>
       <c r="V21" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W21" t="n">
         <v>1.85</v>
@@ -5743,10 +5743,10 @@
         <v>14.5</v>
       </c>
       <c r="Z21" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AA21" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AB21" t="n">
         <v>9.6</v>
@@ -5758,7 +5758,7 @@
         <v>16.5</v>
       </c>
       <c r="AE21" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AF21" t="n">
         <v>13.5</v>
@@ -5800,13 +5800,13 @@
         <v>25</v>
       </c>
       <c r="AS21" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AT21" t="n">
         <v>8.6</v>
       </c>
       <c r="AU21" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV21" t="n">
         <v>14.5</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-07-18 14:16:24</t>
+          <t>2026-07-18 16:34:23</t>
         </is>
       </c>
     </row>
@@ -5940,16 +5940,16 @@
         <v>3.7</v>
       </c>
       <c r="G22" t="n">
-        <v>4.9</v>
+        <v>4.4</v>
       </c>
       <c r="H22" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="I22" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="J22" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K22" t="n">
         <v>3.6</v>
@@ -5970,7 +5970,7 @@
         <v>1.62</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.12</v>
+        <v>2.3</v>
       </c>
       <c r="R22" t="n">
         <v>1.23</v>
@@ -5985,10 +5985,10 @@
         <v>1.85</v>
       </c>
       <c r="V22" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="W22" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="X22" t="n">
         <v>12</v>
@@ -6084,16 +6084,16 @@
         <v>1.01</v>
       </c>
       <c r="BC22" t="n">
-        <v>42</v>
+        <v>1.01</v>
       </c>
       <c r="BD22" t="n">
         <v>1.01</v>
       </c>
       <c r="BE22" t="n">
-        <v>100</v>
+        <v>1.01</v>
       </c>
       <c r="BF22" t="n">
-        <v>55</v>
+        <v>1.01</v>
       </c>
       <c r="BG22" t="n">
         <v>1.01</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-07-18 14:16:24</t>
+          <t>2026-07-18 16:34:23</t>
         </is>
       </c>
     </row>
@@ -6191,7 +6191,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="G23" t="n">
         <v>6.2</v>
@@ -6209,7 +6209,7 @@
         <v>4.9</v>
       </c>
       <c r="L23" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="M23" t="n">
         <v>1.04</v>
@@ -6224,7 +6224,7 @@
         <v>2.38</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="R23" t="n">
         <v>1.55</v>
@@ -6251,7 +6251,7 @@
         <v>11</v>
       </c>
       <c r="Z23" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AA23" t="n">
         <v>17</v>
@@ -6260,7 +6260,7 @@
         <v>30</v>
       </c>
       <c r="AC23" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD23" t="n">
         <v>10.5</v>
@@ -6272,19 +6272,19 @@
         <v>50</v>
       </c>
       <c r="AG23" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AH23" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AI23" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AJ23" t="n">
         <v>160</v>
       </c>
       <c r="AK23" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AL23" t="n">
         <v>65</v>
@@ -6293,7 +6293,7 @@
         <v>90</v>
       </c>
       <c r="AN23" t="n">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="AO23" t="n">
         <v>7.6</v>
@@ -6311,7 +6311,7 @@
         <v>12.5</v>
       </c>
       <c r="AT23" t="n">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="AU23" t="n">
         <v>9</v>
@@ -6323,7 +6323,7 @@
         <v>12</v>
       </c>
       <c r="AX23" t="n">
-        <v>1.01</v>
+        <v>40</v>
       </c>
       <c r="AY23" t="n">
         <v>18</v>
@@ -6356,7 +6356,7 @@
         <v>4.7</v>
       </c>
       <c r="BI23" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="BJ23" t="n">
         <v>11</v>
@@ -6392,7 +6392,7 @@
         <v>5.1</v>
       </c>
       <c r="BU23" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BV23" t="n">
         <v>12</v>
@@ -6401,7 +6401,7 @@
         <v>1.01</v>
       </c>
       <c r="BX23" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BY23" t="n">
         <v>1.01</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-07-18 14:16:24</t>
+          <t>2026-07-18 16:34:23</t>
         </is>
       </c>
     </row>
@@ -6457,7 +6457,7 @@
         <v>2.98</v>
       </c>
       <c r="J24" t="n">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="K24" t="n">
         <v>4.8</v>
@@ -6493,7 +6493,7 @@
         <v>2.84</v>
       </c>
       <c r="V24" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W24" t="n">
         <v>1.64</v>
@@ -6607,7 +6607,7 @@
         <v>1.01</v>
       </c>
       <c r="BH24" t="n">
-        <v>5.1</v>
+        <v>5.9</v>
       </c>
       <c r="BI24" t="n">
         <v>3.8</v>
@@ -6619,7 +6619,7 @@
         <v>6</v>
       </c>
       <c r="BL24" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="BM24" t="n">
         <v>1.01</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-07-18 14:16:24</t>
+          <t>2026-07-18 16:34:23</t>
         </is>
       </c>
     </row>
@@ -6699,43 +6699,43 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="G25" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="H25" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="I25" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="J25" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K25" t="n">
         <v>4.2</v>
       </c>
       <c r="L25" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="M25" t="n">
         <v>1.05</v>
       </c>
       <c r="N25" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O25" t="n">
         <v>1.25</v>
       </c>
       <c r="P25" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="R25" t="n">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="S25" t="n">
         <v>2.86</v>
@@ -6744,10 +6744,10 @@
         <v>1.69</v>
       </c>
       <c r="U25" t="n">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="V25" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="W25" t="n">
         <v>1.3</v>
@@ -6762,7 +6762,7 @@
         <v>14</v>
       </c>
       <c r="AA25" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AB25" t="n">
         <v>17.5</v>
@@ -6795,10 +6795,10 @@
         <v>48</v>
       </c>
       <c r="AL25" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AM25" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AN25" t="n">
         <v>44</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-07-18 14:16:24</t>
+          <t>2026-07-18 16:34:23</t>
         </is>
       </c>
     </row>
@@ -6953,7 +6953,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="G26" t="n">
         <v>3.85</v>
@@ -6968,7 +6968,7 @@
         <v>3.95</v>
       </c>
       <c r="K26" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L26" t="n">
         <v>1.33</v>
@@ -6980,46 +6980,46 @@
         <v>5</v>
       </c>
       <c r="O26" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P26" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="R26" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="S26" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="T26" t="n">
         <v>1.64</v>
       </c>
       <c r="U26" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="V26" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="W26" t="n">
         <v>1.35</v>
       </c>
       <c r="X26" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="Y26" t="n">
         <v>12.5</v>
       </c>
       <c r="Z26" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AA26" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AB26" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AC26" t="n">
         <v>9</v>
@@ -7037,7 +7037,7 @@
         <v>16</v>
       </c>
       <c r="AH26" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AI26" t="n">
         <v>30</v>
@@ -7058,7 +7058,7 @@
         <v>32</v>
       </c>
       <c r="AO26" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AP26" t="n">
         <v>17.5</v>
@@ -7109,7 +7109,7 @@
         <v>60</v>
       </c>
       <c r="BF26" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="BG26" t="n">
         <v>10</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-07-18 14:16:24</t>
+          <t>2026-07-18 16:34:23</t>
         </is>
       </c>
     </row>
@@ -7210,7 +7210,7 @@
         <v>1.29</v>
       </c>
       <c r="G27" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="H27" t="n">
         <v>12</v>
@@ -7243,10 +7243,10 @@
         <v>1.55</v>
       </c>
       <c r="R27" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="S27" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="T27" t="n">
         <v>2.04</v>
@@ -7261,16 +7261,16 @@
         <v>4.2</v>
       </c>
       <c r="X27" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="Y27" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="Z27" t="n">
         <v>130</v>
       </c>
       <c r="AA27" t="n">
-        <v>510</v>
+        <v>490</v>
       </c>
       <c r="AB27" t="n">
         <v>11</v>
@@ -7345,7 +7345,7 @@
         <v>10</v>
       </c>
       <c r="AZ27" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BA27" t="n">
         <v>42</v>
@@ -7357,7 +7357,7 @@
         <v>12</v>
       </c>
       <c r="BD27" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="BE27" t="n">
         <v>44</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-07-18 14:16:24</t>
+          <t>2026-07-18 16:34:23</t>
         </is>
       </c>
     </row>
@@ -7476,7 +7476,7 @@
         <v>4.7</v>
       </c>
       <c r="K28" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="L28" t="n">
         <v>1.27</v>
@@ -7494,10 +7494,10 @@
         <v>2.72</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="R28" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="S28" t="n">
         <v>2.36</v>
@@ -7518,7 +7518,7 @@
         <v>27</v>
       </c>
       <c r="Y28" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="Z28" t="n">
         <v>12.5</v>
@@ -7527,7 +7527,7 @@
         <v>17</v>
       </c>
       <c r="AB28" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AC28" t="n">
         <v>11.5</v>
@@ -7539,7 +7539,7 @@
         <v>15</v>
       </c>
       <c r="AF28" t="n">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="AG28" t="n">
         <v>22</v>
@@ -7557,7 +7557,7 @@
         <v>500</v>
       </c>
       <c r="AL28" t="n">
-        <v>280</v>
+        <v>260</v>
       </c>
       <c r="AM28" t="n">
         <v>1000</v>
@@ -7566,13 +7566,13 @@
         <v>50</v>
       </c>
       <c r="AO28" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AP28" t="n">
         <v>22</v>
       </c>
       <c r="AQ28" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AR28" t="n">
         <v>11</v>
@@ -7662,7 +7662,7 @@
         <v>5.5</v>
       </c>
       <c r="BU28" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="BV28" t="n">
         <v>12</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-07-18 14:16:24</t>
+          <t>2026-07-18 16:34:23</t>
         </is>
       </c>
     </row>
@@ -7715,16 +7715,16 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="G29" t="n">
-        <v>600</v>
+        <v>4.6</v>
       </c>
       <c r="H29" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="I29" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="J29" t="n">
         <v>3.2</v>
@@ -7739,193 +7739,193 @@
         <v>1.02</v>
       </c>
       <c r="N29" t="n">
-        <v>5.1</v>
+        <v>4.2</v>
       </c>
       <c r="O29" t="n">
         <v>1.19</v>
       </c>
       <c r="P29" t="n">
-        <v>2.58</v>
+        <v>2.4</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="R29" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="S29" t="n">
-        <v>2.26</v>
+        <v>2.12</v>
       </c>
       <c r="T29" t="n">
-        <v>1.11</v>
+        <v>1.52</v>
       </c>
       <c r="U29" t="n">
-        <v>1.11</v>
+        <v>2.52</v>
       </c>
       <c r="V29" t="n">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="W29" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="X29" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="Y29" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Z29" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AA29" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AB29" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AC29" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AD29" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AE29" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AF29" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AG29" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AH29" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AI29" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AJ29" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AK29" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AL29" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AM29" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AN29" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AO29" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AQ29" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="AR29" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="AS29" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AT29" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AU29" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AV29" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AW29" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="AX29" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AY29" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="AZ29" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BA29" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BB29" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BC29" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BD29" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BE29" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BF29" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BG29" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BH29" t="n">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="BI29" t="n">
         <v>1.01</v>
       </c>
       <c r="BJ29" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="BK29" t="n">
         <v>1.01</v>
       </c>
       <c r="BL29" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="BM29" t="n">
         <v>1.01</v>
       </c>
       <c r="BN29" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BO29" t="n">
         <v>1.01</v>
       </c>
       <c r="BP29" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BQ29" t="n">
         <v>1.01</v>
       </c>
       <c r="BR29" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BS29" t="n">
         <v>1.01</v>
       </c>
       <c r="BT29" t="n">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="BU29" t="n">
         <v>1.01</v>
       </c>
       <c r="BV29" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BW29" t="n">
         <v>1.01</v>
       </c>
       <c r="BX29" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BY29" t="n">
         <v>1.01</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-07-18 14:16:24</t>
+          <t>2026-07-18 16:34:23</t>
         </is>
       </c>
     </row>
@@ -7993,7 +7993,7 @@
         <v>1.05</v>
       </c>
       <c r="N30" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="O30" t="n">
         <v>1.26</v>
@@ -8002,55 +8002,55 @@
         <v>2.24</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="R30" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="S30" t="n">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="T30" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="U30" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="V30" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="W30" t="n">
         <v>1.19</v>
       </c>
       <c r="X30" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="Y30" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="Z30" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AA30" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AB30" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AC30" t="n">
         <v>10</v>
       </c>
       <c r="AD30" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AE30" t="n">
         <v>17</v>
       </c>
       <c r="AF30" t="n">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AG30" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AH30" t="n">
         <v>21</v>
@@ -8074,7 +8074,7 @@
         <v>1000</v>
       </c>
       <c r="AO30" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AP30" t="n">
         <v>16</v>
@@ -8089,10 +8089,10 @@
         <v>14</v>
       </c>
       <c r="AT30" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AU30" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV30" t="n">
         <v>9</v>
@@ -8101,16 +8101,16 @@
         <v>14.5</v>
       </c>
       <c r="AX30" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="AY30" t="n">
         <v>20</v>
       </c>
       <c r="AZ30" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BA30" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BB30" t="n">
         <v>44</v>
@@ -8143,13 +8143,13 @@
         <v>1.01</v>
       </c>
       <c r="BL30" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="BM30" t="n">
         <v>1.01</v>
       </c>
       <c r="BN30" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BO30" t="n">
         <v>1.01</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-07-18 14:16:24</t>
+          <t>2026-07-18 16:34:23</t>
         </is>
       </c>
     </row>
@@ -8280,43 +8280,43 @@
         <v>13</v>
       </c>
       <c r="Y31" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="Z31" t="n">
+        <v>20</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>48</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>38</v>
+      </c>
+      <c r="AF31" t="n">
         <v>21</v>
       </c>
-      <c r="AA31" t="n">
-        <v>55</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>15</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>42</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>22</v>
-      </c>
       <c r="AG31" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AH31" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AI31" t="n">
         <v>60</v>
       </c>
       <c r="AJ31" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AK31" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AL31" t="n">
         <v>65</v>
@@ -8325,10 +8325,10 @@
         <v>140</v>
       </c>
       <c r="AN31" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AO31" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AP31" t="n">
         <v>8.6</v>
@@ -8364,10 +8364,10 @@
         <v>14.5</v>
       </c>
       <c r="BA31" t="n">
-        <v>1.01</v>
+        <v>38</v>
       </c>
       <c r="BB31" t="n">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="BC31" t="n">
         <v>1.01</v>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-07-18 14:16:24</t>
+          <t>2026-07-18 16:34:23</t>
         </is>
       </c>
     </row>
@@ -8477,7 +8477,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="G32" t="n">
         <v>1000</v>
@@ -8489,7 +8489,7 @@
         <v>1000</v>
       </c>
       <c r="J32" t="n">
-        <v>1.03</v>
+        <v>1.16</v>
       </c>
       <c r="K32" t="n">
         <v>1000</v>
@@ -8501,13 +8501,13 @@
         <v>1.01</v>
       </c>
       <c r="N32" t="n">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="O32" t="n">
         <v>1.37</v>
       </c>
       <c r="P32" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="Q32" t="n">
         <v>1.37</v>
@@ -8516,7 +8516,7 @@
         <v>1.16</v>
       </c>
       <c r="S32" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="T32" t="n">
         <v>1.11</v>
@@ -8525,10 +8525,10 @@
         <v>1.11</v>
       </c>
       <c r="V32" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W32" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="X32" t="n">
         <v>1000</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-07-18 14:16:24</t>
+          <t>2026-07-18 16:34:23</t>
         </is>
       </c>
     </row>
@@ -8740,7 +8740,7 @@
         <v>1.76</v>
       </c>
       <c r="I33" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="J33" t="n">
         <v>3.5</v>
@@ -8854,7 +8854,7 @@
         <v>10.5</v>
       </c>
       <c r="AU33" t="n">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV33" t="n">
         <v>9.6</v>
@@ -8902,7 +8902,7 @@
         <v>15.5</v>
       </c>
       <c r="BK33" t="n">
-        <v>3.95</v>
+        <v>9.4</v>
       </c>
       <c r="BL33" t="n">
         <v>340</v>
@@ -8914,7 +8914,7 @@
         <v>11.5</v>
       </c>
       <c r="BO33" t="n">
-        <v>3.6</v>
+        <v>7</v>
       </c>
       <c r="BP33" t="n">
         <v>90</v>
@@ -8932,13 +8932,13 @@
         <v>4.7</v>
       </c>
       <c r="BU33" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="BV33" t="n">
         <v>17</v>
       </c>
       <c r="BW33" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="BX33" t="n">
         <v>55</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-07-18 14:16:24</t>
+          <t>2026-07-18 16:34:23</t>
         </is>
       </c>
     </row>
@@ -8985,22 +8985,22 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="G34" t="n">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="H34" t="n">
-        <v>2.04</v>
+        <v>1.96</v>
       </c>
       <c r="I34" t="n">
         <v>2.1</v>
       </c>
       <c r="J34" t="n">
-        <v>3.95</v>
+        <v>3.75</v>
       </c>
       <c r="K34" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L34" t="n">
         <v>1.33</v>
@@ -9015,7 +9015,7 @@
         <v>1.23</v>
       </c>
       <c r="P34" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="Q34" t="n">
         <v>1.68</v>
@@ -9033,10 +9033,10 @@
         <v>2.3</v>
       </c>
       <c r="V34" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="W34" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="X34" t="n">
         <v>22</v>
@@ -9045,10 +9045,10 @@
         <v>13</v>
       </c>
       <c r="Z34" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AA34" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AB34" t="n">
         <v>17.5</v>
@@ -9060,13 +9060,13 @@
         <v>12</v>
       </c>
       <c r="AE34" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AF34" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AG34" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AH34" t="n">
         <v>17</v>
@@ -9075,13 +9075,13 @@
         <v>32</v>
       </c>
       <c r="AJ34" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="AK34" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AL34" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="AM34" t="n">
         <v>75</v>
@@ -9090,7 +9090,7 @@
         <v>34</v>
       </c>
       <c r="AO34" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AP34" t="n">
         <v>15</v>
@@ -9126,25 +9126,25 @@
         <v>12.5</v>
       </c>
       <c r="BA34" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="BB34" t="n">
         <v>1.01</v>
       </c>
       <c r="BC34" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="BD34" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="BE34" t="n">
         <v>1.01</v>
       </c>
       <c r="BF34" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="BG34" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BH34" t="n">
         <v>4.4</v>
@@ -9156,49 +9156,49 @@
         <v>9.4</v>
       </c>
       <c r="BK34" t="n">
-        <v>4</v>
+        <v>2.54</v>
       </c>
       <c r="BL34" t="n">
         <v>110</v>
       </c>
       <c r="BM34" t="n">
-        <v>6.6</v>
+        <v>3.35</v>
       </c>
       <c r="BN34" t="n">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="BO34" t="n">
-        <v>5.4</v>
+        <v>3.45</v>
       </c>
       <c r="BP34" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="BQ34" t="n">
-        <v>5.6</v>
+        <v>3.5</v>
       </c>
       <c r="BR34" t="n">
         <v>34</v>
       </c>
       <c r="BS34" t="n">
-        <v>5.9</v>
+        <v>3.15</v>
       </c>
       <c r="BT34" t="n">
-        <v>5.9</v>
+        <v>5.3</v>
       </c>
       <c r="BU34" t="n">
         <v>4.5</v>
       </c>
       <c r="BV34" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="BW34" t="n">
-        <v>4.8</v>
+        <v>2.82</v>
       </c>
       <c r="BX34" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="BY34" t="n">
-        <v>5.7</v>
+        <v>3.05</v>
       </c>
       <c r="BZ34" t="n">
         <v>0</v>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-07-18 14:16:24</t>
+          <t>2026-07-18 16:34:23</t>
         </is>
       </c>
     </row>
@@ -9269,7 +9269,7 @@
         <v>1.01</v>
       </c>
       <c r="P35" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="Q35" t="n">
         <v>1.13</v>
@@ -9284,7 +9284,7 @@
         <v>1.21</v>
       </c>
       <c r="U35" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="V35" t="n">
         <v>1.26</v>
@@ -9335,7 +9335,7 @@
         <v>21</v>
       </c>
       <c r="AL35" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AM35" t="n">
         <v>32</v>
@@ -9347,16 +9347,16 @@
         <v>13</v>
       </c>
       <c r="AP35" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AQ35" t="n">
         <v>6</v>
-      </c>
-      <c r="AQ35" t="n">
-        <v>5.9</v>
       </c>
       <c r="AR35" t="n">
         <v>6</v>
       </c>
       <c r="AS35" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AT35" t="n">
         <v>5.7</v>
@@ -9368,7 +9368,7 @@
         <v>21</v>
       </c>
       <c r="AW35" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AX35" t="n">
         <v>5.5</v>
@@ -9383,7 +9383,7 @@
         <v>21</v>
       </c>
       <c r="BB35" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BC35" t="n">
         <v>13.5</v>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-07-18 14:16:24</t>
+          <t>2026-07-18 16:34:23</t>
         </is>
       </c>
     </row>
@@ -9493,139 +9493,139 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="G36" t="n">
         <v>1.72</v>
       </c>
       <c r="H36" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="I36" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="J36" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="K36" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L36" t="n">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="M36" t="n">
         <v>1.07</v>
       </c>
       <c r="N36" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="O36" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="P36" t="n">
-        <v>1.94</v>
+        <v>1.79</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="R36" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="S36" t="n">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="T36" t="n">
-        <v>1.9</v>
+        <v>1.99</v>
       </c>
       <c r="U36" t="n">
-        <v>1.91</v>
+        <v>1.78</v>
       </c>
       <c r="V36" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="W36" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="X36" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="Y36" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="Z36" t="n">
         <v>60</v>
       </c>
       <c r="AA36" t="n">
-        <v>200</v>
+        <v>260</v>
       </c>
       <c r="AB36" t="n">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="AC36" t="n">
         <v>9.6</v>
       </c>
       <c r="AD36" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AE36" t="n">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="AF36" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AG36" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AH36" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AI36" t="n">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="AJ36" t="n">
         <v>17</v>
       </c>
       <c r="AK36" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AL36" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>190</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>12</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>200</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>15</v>
+      </c>
+      <c r="AR36" t="n">
         <v>42</v>
       </c>
-      <c r="AM36" t="n">
-        <v>150</v>
-      </c>
-      <c r="AN36" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AO36" t="n">
-        <v>140</v>
-      </c>
-      <c r="AP36" t="n">
-        <v>11</v>
-      </c>
-      <c r="AQ36" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AR36" t="n">
-        <v>1.01</v>
-      </c>
       <c r="AS36" t="n">
         <v>1.01</v>
       </c>
       <c r="AT36" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="AU36" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AV36" t="n">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="AW36" t="n">
         <v>1.01</v>
       </c>
       <c r="AX36" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AY36" t="n">
         <v>7.8</v>
@@ -9637,10 +9637,10 @@
         <v>1.01</v>
       </c>
       <c r="BB36" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BC36" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="BD36" t="n">
         <v>1.01</v>
@@ -9649,74 +9649,74 @@
         <v>1.01</v>
       </c>
       <c r="BF36" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BG36" t="n">
         <v>1.01</v>
       </c>
       <c r="BH36" t="n">
-        <v>3.95</v>
+        <v>3.7</v>
       </c>
       <c r="BI36" t="n">
-        <v>2.9</v>
+        <v>2.74</v>
       </c>
       <c r="BJ36" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BK36" t="n">
         <v>1.01</v>
       </c>
       <c r="BL36" t="n">
-        <v>170</v>
+        <v>200</v>
       </c>
       <c r="BM36" t="n">
         <v>1.01</v>
       </c>
       <c r="BN36" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="BO36" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="BP36" t="n">
         <v>12.5</v>
       </c>
       <c r="BQ36" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="BR36" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BS36" t="n">
         <v>1.01</v>
       </c>
       <c r="BT36" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BU36" t="n">
         <v>1.01</v>
       </c>
       <c r="BV36" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="BW36" t="n">
         <v>1.01</v>
       </c>
       <c r="BX36" t="n">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="BY36" t="n">
         <v>1.01</v>
       </c>
       <c r="BZ36" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="CA36" t="n">
         <v>1.01</v>
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-07-18 14:16:24</t>
+          <t>2026-07-18 16:34:23</t>
         </is>
       </c>
     </row>
@@ -9759,7 +9759,7 @@
         <v>1000</v>
       </c>
       <c r="J37" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="K37" t="n">
         <v>1000</v>
@@ -9786,7 +9786,7 @@
         <v>1.18</v>
       </c>
       <c r="S37" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="T37" t="n">
         <v>1.11</v>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-07-18 14:16:24</t>
+          <t>2026-07-18 16:34:23</t>
         </is>
       </c>
     </row>
@@ -10019,7 +10019,7 @@
         <v>4.3</v>
       </c>
       <c r="L38" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="M38" t="n">
         <v>1.05</v>
@@ -10031,7 +10031,7 @@
         <v>1.25</v>
       </c>
       <c r="P38" t="n">
-        <v>2.14</v>
+        <v>2.28</v>
       </c>
       <c r="Q38" t="n">
         <v>1.71</v>
@@ -10064,7 +10064,7 @@
         <v>36</v>
       </c>
       <c r="AA38" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AB38" t="n">
         <v>13</v>
@@ -10202,7 +10202,7 @@
         <v>8.6</v>
       </c>
       <c r="BU38" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BV38" t="n">
         <v>36</v>
@@ -10224,7 +10224,7 @@
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-07-18 14:16:24</t>
+          <t>2026-07-18 16:34:23</t>
         </is>
       </c>
     </row>
@@ -10255,91 +10255,91 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>1.66</v>
+        <v>1.59</v>
       </c>
       <c r="G39" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="H39" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="I39" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="J39" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K39" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L39" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="M39" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N39" t="n">
         <v>3.7</v>
-      </c>
-      <c r="K39" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="L39" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="M39" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N39" t="n">
-        <v>3.4</v>
       </c>
       <c r="O39" t="n">
         <v>1.34</v>
       </c>
       <c r="P39" t="n">
-        <v>1.82</v>
+        <v>1.91</v>
       </c>
       <c r="Q39" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="R39" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="S39" t="n">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="T39" t="n">
-        <v>2.04</v>
+        <v>1.94</v>
       </c>
       <c r="U39" t="n">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="V39" t="n">
         <v>1.15</v>
       </c>
       <c r="W39" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="X39" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Y39" t="n">
         <v>22</v>
       </c>
       <c r="Z39" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AA39" t="n">
-        <v>280</v>
+        <v>240</v>
       </c>
       <c r="AB39" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AC39" t="n">
         <v>9.4</v>
       </c>
       <c r="AD39" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="AE39" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AF39" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG39" t="n">
         <v>10.5</v>
       </c>
       <c r="AH39" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI39" t="n">
         <v>120</v>
@@ -10348,22 +10348,22 @@
         <v>15.5</v>
       </c>
       <c r="AK39" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AL39" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AM39" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AN39" t="n">
         <v>10.5</v>
       </c>
       <c r="AO39" t="n">
-        <v>200</v>
+        <v>170</v>
       </c>
       <c r="AP39" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AQ39" t="n">
         <v>14.5</v>
@@ -10372,55 +10372,55 @@
         <v>40</v>
       </c>
       <c r="AS39" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="AT39" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AU39" t="n">
         <v>7.8</v>
       </c>
       <c r="AV39" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AW39" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AX39" t="n">
         <v>7.6</v>
-      </c>
-      <c r="AX39" t="n">
-        <v>7.8</v>
       </c>
       <c r="AY39" t="n">
         <v>9</v>
       </c>
       <c r="AZ39" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BA39" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB39" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BC39" t="n">
         <v>13.5</v>
       </c>
       <c r="BD39" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BE39" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BF39" t="n">
-        <v>9</v>
+        <v>7.4</v>
       </c>
       <c r="BG39" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BH39" t="n">
         <v>3.9</v>
       </c>
       <c r="BI39" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="BJ39" t="n">
         <v>12</v>
@@ -10429,7 +10429,7 @@
         <v>1.01</v>
       </c>
       <c r="BL39" t="n">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="BM39" t="n">
         <v>1.01</v>
@@ -10459,13 +10459,13 @@
         <v>1.01</v>
       </c>
       <c r="BV39" t="n">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="BW39" t="n">
         <v>1.01</v>
       </c>
       <c r="BX39" t="n">
-        <v>95</v>
+        <v>70</v>
       </c>
       <c r="BY39" t="n">
         <v>1.01</v>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-07-18 14:16:24</t>
+          <t>2026-07-18 16:34:23</t>
         </is>
       </c>
     </row>
@@ -10518,7 +10518,7 @@
         <v>1.55</v>
       </c>
       <c r="I40" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="J40" t="n">
         <v>4.7</v>
@@ -10527,7 +10527,7 @@
         <v>5.3</v>
       </c>
       <c r="L40" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="M40" t="n">
         <v>1.01</v>
@@ -10536,19 +10536,19 @@
         <v>6</v>
       </c>
       <c r="O40" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="P40" t="n">
         <v>2.72</v>
       </c>
       <c r="Q40" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="R40" t="n">
         <v>1.7</v>
       </c>
       <c r="S40" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="T40" t="n">
         <v>1.6</v>
@@ -10572,7 +10572,7 @@
         <v>15</v>
       </c>
       <c r="AA40" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AB40" t="n">
         <v>30</v>
@@ -10590,7 +10590,7 @@
         <v>55</v>
       </c>
       <c r="AG40" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AH40" t="n">
         <v>19</v>
@@ -10614,7 +10614,7 @@
         <v>60</v>
       </c>
       <c r="AO40" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AP40" t="n">
         <v>1.01</v>
@@ -10641,7 +10641,7 @@
         <v>12.5</v>
       </c>
       <c r="AX40" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AY40" t="n">
         <v>19</v>
@@ -10671,10 +10671,10 @@
         <v>4.4</v>
       </c>
       <c r="BH40" t="n">
-        <v>5.6</v>
+        <v>4.9</v>
       </c>
       <c r="BI40" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="BJ40" t="n">
         <v>11</v>
@@ -10732,7 +10732,7 @@
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-07-18 14:16:24</t>
+          <t>2026-07-18 16:34:23</t>
         </is>
       </c>
     </row>
@@ -10763,118 +10763,118 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
       <c r="G41" t="n">
-        <v>2.4</v>
+        <v>2.12</v>
       </c>
       <c r="H41" t="n">
-        <v>3.15</v>
+        <v>4.1</v>
       </c>
       <c r="I41" t="n">
-        <v>5.9</v>
+        <v>4.9</v>
       </c>
       <c r="J41" t="n">
-        <v>2.96</v>
+        <v>3.35</v>
       </c>
       <c r="K41" t="n">
-        <v>6.6</v>
+        <v>3.8</v>
       </c>
       <c r="L41" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="M41" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N41" t="n">
-        <v>2.58</v>
+        <v>3.2</v>
       </c>
       <c r="O41" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="P41" t="n">
-        <v>1.64</v>
+        <v>1.76</v>
       </c>
       <c r="Q41" t="n">
-        <v>1.84</v>
+        <v>2.08</v>
       </c>
       <c r="R41" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="S41" t="n">
-        <v>2.74</v>
+        <v>3.85</v>
       </c>
       <c r="T41" t="n">
-        <v>1.11</v>
+        <v>1.78</v>
       </c>
       <c r="U41" t="n">
-        <v>1.11</v>
+        <v>1.83</v>
       </c>
       <c r="V41" t="n">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="W41" t="n">
-        <v>1.71</v>
+        <v>1.9</v>
       </c>
       <c r="X41" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Y41" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="Z41" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AA41" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AB41" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AC41" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD41" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AE41" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AF41" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AG41" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH41" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI41" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AJ41" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AK41" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AL41" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AM41" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AN41" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AO41" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AP41" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AQ41" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AR41" t="n">
         <v>1.01</v>
@@ -10883,34 +10883,34 @@
         <v>1.01</v>
       </c>
       <c r="AT41" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AU41" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AV41" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AW41" t="n">
         <v>1.01</v>
       </c>
       <c r="AX41" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY41" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ41" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BA41" t="n">
         <v>1.01</v>
       </c>
       <c r="BB41" t="n">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BC41" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BD41" t="n">
         <v>1.01</v>
@@ -10919,74 +10919,74 @@
         <v>1.01</v>
       </c>
       <c r="BF41" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BG41" t="n">
         <v>1.01</v>
       </c>
       <c r="BH41" t="n">
-        <v>1000</v>
+        <v>3.55</v>
       </c>
       <c r="BI41" t="n">
-        <v>1.04</v>
+        <v>2.64</v>
       </c>
       <c r="BJ41" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK41" t="n">
-        <v>1.04</v>
+        <v>3.95</v>
       </c>
       <c r="BL41" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="BM41" t="n">
-        <v>1.04</v>
+        <v>5.7</v>
       </c>
       <c r="BN41" t="n">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="BO41" t="n">
-        <v>1.04</v>
+        <v>3.7</v>
       </c>
       <c r="BP41" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="BQ41" t="n">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="BR41" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BS41" t="n">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="BT41" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU41" t="n">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BV41" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BW41" t="n">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="BX41" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BY41" t="n">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="BZ41" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="CA41" t="n">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-07-18 14:16:24</t>
+          <t>2026-07-18 16:34:23</t>
         </is>
       </c>
     </row>
@@ -11017,16 +11017,16 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="G42" t="n">
         <v>3.05</v>
       </c>
       <c r="H42" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="I42" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="J42" t="n">
         <v>2.82</v>
@@ -11056,7 +11056,7 @@
         <v>1.18</v>
       </c>
       <c r="S42" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="T42" t="n">
         <v>2.06</v>
@@ -11065,7 +11065,7 @@
         <v>1.77</v>
       </c>
       <c r="V42" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W42" t="n">
         <v>1.5</v>
@@ -11080,7 +11080,7 @@
         <v>21</v>
       </c>
       <c r="AA42" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AB42" t="n">
         <v>10</v>
@@ -11240,7 +11240,7 @@
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-07-18 14:16:24</t>
+          <t>2026-07-18 16:34:23</t>
         </is>
       </c>
     </row>
@@ -11286,7 +11286,7 @@
         <v>3.2</v>
       </c>
       <c r="K43" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="L43" t="n">
         <v>1.47</v>
@@ -11304,7 +11304,7 @@
         <v>1.67</v>
       </c>
       <c r="Q43" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="R43" t="n">
         <v>1.25</v>
@@ -11313,7 +11313,7 @@
         <v>4.3</v>
       </c>
       <c r="T43" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="U43" t="n">
         <v>1.9</v>
@@ -11442,7 +11442,7 @@
         <v>12</v>
       </c>
       <c r="BK43" t="n">
-        <v>4.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BL43" t="n">
         <v>190</v>
@@ -11454,7 +11454,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BO43" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BP43" t="n">
         <v>44</v>
@@ -11494,7 +11494,7 @@
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-07-18 14:16:24</t>
+          <t>2026-07-18 16:34:23</t>
         </is>
       </c>
     </row>
@@ -11525,16 +11525,16 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="G44" t="n">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="H44" t="n">
-        <v>2.34</v>
+        <v>2.18</v>
       </c>
       <c r="I44" t="n">
-        <v>2.54</v>
+        <v>2.38</v>
       </c>
       <c r="J44" t="n">
         <v>3.1</v>
@@ -11546,7 +11546,7 @@
         <v>1.42</v>
       </c>
       <c r="M44" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N44" t="n">
         <v>3</v>
@@ -11555,28 +11555,28 @@
         <v>1.42</v>
       </c>
       <c r="P44" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="Q44" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="R44" t="n">
         <v>1.25</v>
       </c>
       <c r="S44" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="T44" t="n">
         <v>1.89</v>
       </c>
       <c r="U44" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="V44" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="W44" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="X44" t="n">
         <v>11.5</v>
@@ -11603,10 +11603,10 @@
         <v>30</v>
       </c>
       <c r="AF44" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AG44" t="n">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="AH44" t="n">
         <v>20</v>
@@ -11615,34 +11615,34 @@
         <v>50</v>
       </c>
       <c r="AJ44" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AK44" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AL44" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AM44" t="n">
         <v>150</v>
       </c>
       <c r="AN44" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AO44" t="n">
         <v>28</v>
       </c>
       <c r="AP44" t="n">
-        <v>9.6</v>
+        <v>3.5</v>
       </c>
       <c r="AQ44" t="n">
-        <v>7.6</v>
+        <v>3.25</v>
       </c>
       <c r="AR44" t="n">
-        <v>12.5</v>
+        <v>3.8</v>
       </c>
       <c r="AS44" t="n">
-        <v>8.199999999999999</v>
+        <v>22</v>
       </c>
       <c r="AT44" t="n">
         <v>9.800000000000001</v>
@@ -11654,7 +11654,7 @@
         <v>10</v>
       </c>
       <c r="AW44" t="n">
-        <v>7.8</v>
+        <v>4.3</v>
       </c>
       <c r="AX44" t="n">
         <v>20</v>
@@ -11666,22 +11666,22 @@
         <v>16.5</v>
       </c>
       <c r="BA44" t="n">
-        <v>8.800000000000001</v>
+        <v>4.6</v>
       </c>
       <c r="BB44" t="n">
-        <v>9.199999999999999</v>
+        <v>4.8</v>
       </c>
       <c r="BC44" t="n">
-        <v>8.800000000000001</v>
+        <v>5.1</v>
       </c>
       <c r="BD44" t="n">
-        <v>9.199999999999999</v>
+        <v>5.1</v>
       </c>
       <c r="BE44" t="n">
-        <v>10</v>
+        <v>4.9</v>
       </c>
       <c r="BF44" t="n">
-        <v>40</v>
+        <v>5.1</v>
       </c>
       <c r="BG44" t="n">
         <v>20</v>
@@ -11748,7 +11748,7 @@
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-07-18 14:16:24</t>
+          <t>2026-07-18 16:34:23</t>
         </is>
       </c>
     </row>
@@ -11779,112 +11779,112 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="G45" t="n">
-        <v>2.26</v>
+        <v>2.98</v>
       </c>
       <c r="H45" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="I45" t="n">
-        <v>4.8</v>
+        <v>36</v>
       </c>
       <c r="J45" t="n">
-        <v>3.25</v>
+        <v>2.52</v>
       </c>
       <c r="K45" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="L45" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="M45" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N45" t="n">
-        <v>3.25</v>
+        <v>1.77</v>
       </c>
       <c r="O45" t="n">
         <v>1.3</v>
       </c>
       <c r="P45" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="Q45" t="n">
         <v>1.81</v>
       </c>
-      <c r="Q45" t="n">
-        <v>1.87</v>
-      </c>
       <c r="R45" t="n">
-        <v>1.31</v>
+        <v>1.07</v>
       </c>
       <c r="S45" t="n">
-        <v>3.1</v>
+        <v>2.98</v>
       </c>
       <c r="T45" t="n">
-        <v>1.72</v>
+        <v>1.44</v>
       </c>
       <c r="U45" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="V45" t="n">
         <v>1.27</v>
       </c>
       <c r="W45" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="X45" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="Y45" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="Z45" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AA45" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AB45" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AC45" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="AD45" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AE45" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AF45" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AG45" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH45" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AI45" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AJ45" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AK45" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AL45" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AM45" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AN45" t="n">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="AO45" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AP45" t="n">
         <v>1.01</v>
@@ -11941,55 +11941,55 @@
         <v>1.01</v>
       </c>
       <c r="BH45" t="n">
-        <v>3.8</v>
+        <v>1000</v>
       </c>
       <c r="BI45" t="n">
-        <v>2.8</v>
+        <v>1.01</v>
       </c>
       <c r="BJ45" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BK45" t="n">
         <v>1.01</v>
       </c>
       <c r="BL45" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="BM45" t="n">
         <v>1.01</v>
       </c>
       <c r="BN45" t="n">
-        <v>5.4</v>
+        <v>1000</v>
       </c>
       <c r="BO45" t="n">
-        <v>3.85</v>
+        <v>1.01</v>
       </c>
       <c r="BP45" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="BQ45" t="n">
         <v>1.01</v>
       </c>
       <c r="BR45" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BS45" t="n">
         <v>1.01</v>
       </c>
       <c r="BT45" t="n">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="BU45" t="n">
         <v>1.01</v>
       </c>
       <c r="BV45" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BW45" t="n">
         <v>1.01</v>
       </c>
       <c r="BX45" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BY45" t="n">
         <v>1.01</v>
@@ -12002,7 +12002,7 @@
       </c>
       <c r="CB45" t="inlineStr">
         <is>
-          <t>2026-07-18 14:16:24</t>
+          <t>2026-07-18 16:34:23</t>
         </is>
       </c>
     </row>
@@ -12033,7 +12033,7 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="G46" t="n">
         <v>1.73</v>
@@ -12051,7 +12051,7 @@
         <v>4.8</v>
       </c>
       <c r="L46" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="M46" t="n">
         <v>1.05</v>
@@ -12060,13 +12060,13 @@
         <v>4.3</v>
       </c>
       <c r="O46" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P46" t="n">
         <v>2.14</v>
       </c>
       <c r="Q46" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="R46" t="n">
         <v>1.45</v>
@@ -12256,7 +12256,7 @@
       </c>
       <c r="CB46" t="inlineStr">
         <is>
-          <t>2026-07-18 14:16:24</t>
+          <t>2026-07-18 16:34:23</t>
         </is>
       </c>
     </row>
@@ -12287,19 +12287,19 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="G47" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="H47" t="n">
         <v>4.2</v>
       </c>
       <c r="I47" t="n">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="J47" t="n">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="K47" t="n">
         <v>3.7</v>
@@ -12317,13 +12317,13 @@
         <v>1.4</v>
       </c>
       <c r="P47" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="Q47" t="n">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="R47" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="S47" t="n">
         <v>3.75</v>
@@ -12335,10 +12335,10 @@
         <v>1.88</v>
       </c>
       <c r="V47" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="W47" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="X47" t="n">
         <v>1000</v>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="CB47" t="inlineStr">
         <is>
-          <t>2026-07-18 14:16:24</t>
+          <t>2026-07-18 16:34:23</t>
         </is>
       </c>
     </row>
@@ -12541,19 +12541,19 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="G48" t="n">
         <v>1000</v>
       </c>
       <c r="H48" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="I48" t="n">
         <v>1000</v>
       </c>
       <c r="J48" t="n">
-        <v>1.04</v>
+        <v>1.15</v>
       </c>
       <c r="K48" t="n">
         <v>1000</v>
@@ -12589,10 +12589,10 @@
         <v>1.11</v>
       </c>
       <c r="V48" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W48" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X48" t="n">
         <v>1000</v>
@@ -12764,7 +12764,7 @@
       </c>
       <c r="CB48" t="inlineStr">
         <is>
-          <t>2026-07-18 14:16:24</t>
+          <t>2026-07-18 16:34:23</t>
         </is>
       </c>
     </row>
@@ -12795,22 +12795,22 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="G49" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="I49" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="J49" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="L49" t="n">
         <v>1.54</v>
@@ -12996,7 +12996,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BU49" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="BV49" t="n">
         <v>46</v>
@@ -13018,7 +13018,7 @@
       </c>
       <c r="CB49" t="inlineStr">
         <is>
-          <t>2026-07-18 14:16:24</t>
+          <t>2026-07-18 16:34:23</t>
         </is>
       </c>
     </row>
@@ -13049,52 +13049,52 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>1.03</v>
+        <v>1.86</v>
       </c>
       <c r="G50" t="n">
-        <v>1000</v>
+        <v>2.48</v>
       </c>
       <c r="H50" t="n">
-        <v>1.03</v>
+        <v>3.5</v>
       </c>
       <c r="I50" t="n">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="J50" t="n">
-        <v>1.04</v>
+        <v>2.8</v>
       </c>
       <c r="K50" t="n">
-        <v>1000</v>
+        <v>3.8</v>
       </c>
       <c r="L50" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="M50" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N50" t="n">
-        <v>1.25</v>
+        <v>2.58</v>
       </c>
       <c r="O50" t="n">
-        <v>1.02</v>
+        <v>1.41</v>
       </c>
       <c r="P50" t="n">
-        <v>1.5</v>
+        <v>1.59</v>
       </c>
       <c r="Q50" t="n">
-        <v>1.45</v>
+        <v>2.18</v>
       </c>
       <c r="R50" t="n">
         <v>1.22</v>
       </c>
       <c r="S50" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="T50" t="n">
-        <v>1.11</v>
+        <v>1.9</v>
       </c>
       <c r="U50" t="n">
-        <v>1.11</v>
+        <v>1.78</v>
       </c>
       <c r="V50" t="n">
         <v>1.23</v>
@@ -13220,7 +13220,7 @@
         <v>13</v>
       </c>
       <c r="BK50" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="BL50" t="n">
         <v>210</v>
@@ -13232,31 +13232,31 @@
         <v>5.5</v>
       </c>
       <c r="BO50" t="n">
-        <v>3.6</v>
+        <v>1.01</v>
       </c>
       <c r="BP50" t="n">
         <v>20</v>
       </c>
       <c r="BQ50" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BR50" t="n">
         <v>44</v>
       </c>
       <c r="BS50" t="n">
-        <v>25</v>
+        <v>1.01</v>
       </c>
       <c r="BT50" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BU50" t="n">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="BV50" t="n">
         <v>50</v>
       </c>
       <c r="BW50" t="n">
-        <v>28</v>
+        <v>1.01</v>
       </c>
       <c r="BX50" t="n">
         <v>70</v>
@@ -13268,11 +13268,11 @@
         <v>44</v>
       </c>
       <c r="CA50" t="n">
-        <v>26</v>
+        <v>1.01</v>
       </c>
       <c r="CB50" t="inlineStr">
         <is>
-          <t>2026-07-18 14:16:24</t>
+          <t>2026-07-18 16:34:23</t>
         </is>
       </c>
     </row>
@@ -13318,7 +13318,7 @@
         <v>2.88</v>
       </c>
       <c r="K51" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="L51" t="n">
         <v>1.53</v>
@@ -13411,7 +13411,7 @@
         <v>60</v>
       </c>
       <c r="AP51" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AQ51" t="n">
         <v>6.8</v>
@@ -13526,7 +13526,7 @@
       </c>
       <c r="CB51" t="inlineStr">
         <is>
-          <t>2026-07-18 14:16:24</t>
+          <t>2026-07-18 16:34:23</t>
         </is>
       </c>
     </row>
@@ -13560,10 +13560,10 @@
         <v>2.1</v>
       </c>
       <c r="G52" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="H52" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="I52" t="n">
         <v>4.5</v>
@@ -13572,49 +13572,49 @@
         <v>2.96</v>
       </c>
       <c r="K52" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="L52" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="M52" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N52" t="n">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="O52" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="P52" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="Q52" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="R52" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="S52" t="n">
         <v>4.7</v>
       </c>
       <c r="T52" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="U52" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="V52" t="n">
         <v>1.28</v>
       </c>
       <c r="W52" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="X52" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="Y52" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="Z52" t="n">
         <v>34</v>
@@ -13623,118 +13623,118 @@
         <v>120</v>
       </c>
       <c r="AB52" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC52" t="n">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="AD52" t="n">
         <v>18.5</v>
       </c>
       <c r="AE52" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AF52" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AG52" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AH52" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AI52" t="n">
         <v>100</v>
       </c>
       <c r="AJ52" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AK52" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="AL52" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="AM52" t="n">
         <v>200</v>
       </c>
       <c r="AN52" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="AO52" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AP52" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AQ52" t="n">
-        <v>9.6</v>
+        <v>8</v>
       </c>
       <c r="AR52" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AS52" t="n">
         <v>1.01</v>
       </c>
       <c r="AT52" t="n">
-        <v>6.4</v>
+        <v>5.9</v>
       </c>
       <c r="AU52" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="AV52" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AW52" t="n">
         <v>1.01</v>
       </c>
       <c r="AX52" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AY52" t="n">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ52" t="n">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="BA52" t="n">
         <v>1.01</v>
       </c>
       <c r="BB52" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="BC52" t="n">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD52" t="n">
-        <v>34</v>
+        <v>1.01</v>
       </c>
       <c r="BE52" t="n">
         <v>1.01</v>
       </c>
       <c r="BF52" t="n">
-        <v>15.5</v>
+        <v>22</v>
       </c>
       <c r="BG52" t="n">
         <v>1.01</v>
       </c>
       <c r="BH52" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="BI52" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="BJ52" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BK52" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="BL52" t="n">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="BM52" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BN52" t="n">
         <v>5.7</v>
@@ -13761,7 +13761,7 @@
         <v>5.3</v>
       </c>
       <c r="BV52" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BW52" t="n">
         <v>4.5</v>
@@ -13773,14 +13773,14 @@
         <v>4.6</v>
       </c>
       <c r="BZ52" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="CA52" t="n">
         <v>4.5</v>
       </c>
       <c r="CB52" t="inlineStr">
         <is>
-          <t>2026-07-18 14:16:24</t>
+          <t>2026-07-18 16:34:23</t>
         </is>
       </c>
     </row>
@@ -13916,7 +13916,7 @@
         <v>7.4</v>
       </c>
       <c r="AO53" t="n">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="AP53" t="n">
         <v>15</v>
@@ -13928,7 +13928,7 @@
         <v>6</v>
       </c>
       <c r="AS53" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AT53" t="n">
         <v>6.8</v>
@@ -13949,7 +13949,7 @@
         <v>8.6</v>
       </c>
       <c r="AZ53" t="n">
-        <v>19</v>
+        <v>5.2</v>
       </c>
       <c r="BA53" t="n">
         <v>6.2</v>
@@ -13961,7 +13961,7 @@
         <v>13.5</v>
       </c>
       <c r="BD53" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="BE53" t="n">
         <v>6.2</v>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="CB53" t="inlineStr">
         <is>
-          <t>2026-07-18 14:16:24</t>
+          <t>2026-07-18 16:34:23</t>
         </is>
       </c>
     </row>
@@ -14065,16 +14065,16 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="G54" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="H54" t="n">
         <v>10</v>
       </c>
       <c r="I54" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J54" t="n">
         <v>4.8</v>
@@ -14095,10 +14095,10 @@
         <v>1.27</v>
       </c>
       <c r="P54" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="Q54" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="R54" t="n">
         <v>1.39</v>
@@ -14113,10 +14113,10 @@
         <v>1.72</v>
       </c>
       <c r="V54" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="W54" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="X54" t="n">
         <v>20</v>
@@ -14143,7 +14143,7 @@
         <v>240</v>
       </c>
       <c r="AF54" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AG54" t="n">
         <v>12</v>
@@ -14155,7 +14155,7 @@
         <v>190</v>
       </c>
       <c r="AJ54" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AK54" t="n">
         <v>18.5</v>
@@ -14167,7 +14167,7 @@
         <v>230</v>
       </c>
       <c r="AN54" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AO54" t="n">
         <v>370</v>
@@ -14176,13 +14176,13 @@
         <v>15</v>
       </c>
       <c r="AQ54" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="AR54" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="AS54" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="AT54" t="n">
         <v>6.6</v>
@@ -14191,10 +14191,10 @@
         <v>10</v>
       </c>
       <c r="AV54" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="AW54" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="AX54" t="n">
         <v>6.8</v>
@@ -14203,10 +14203,10 @@
         <v>9</v>
       </c>
       <c r="AZ54" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="BA54" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="BB54" t="n">
         <v>9.6</v>
@@ -14215,22 +14215,22 @@
         <v>13.5</v>
       </c>
       <c r="BD54" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BE54" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="BF54" t="n">
         <v>5.3</v>
       </c>
       <c r="BG54" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="BH54" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BI54" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="BJ54" t="n">
         <v>14.5</v>
@@ -14245,50 +14245,50 @@
         <v>1.01</v>
       </c>
       <c r="BN54" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BO54" t="n">
         <v>3</v>
       </c>
       <c r="BP54" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BQ54" t="n">
         <v>1.01</v>
       </c>
       <c r="BR54" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BS54" t="n">
         <v>1.01</v>
       </c>
       <c r="BT54" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BU54" t="n">
         <v>1.01</v>
       </c>
       <c r="BV54" t="n">
+        <v>130</v>
+      </c>
+      <c r="BW54" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX54" t="n">
         <v>120</v>
       </c>
-      <c r="BW54" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BX54" t="n">
-        <v>110</v>
-      </c>
       <c r="BY54" t="n">
         <v>1.01</v>
       </c>
       <c r="BZ54" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="CA54" t="n">
         <v>1.01</v>
       </c>
       <c r="CB54" t="inlineStr">
         <is>
-          <t>2026-07-18 14:16:24</t>
+          <t>2026-07-18 16:34:23</t>
         </is>
       </c>
     </row>
@@ -14352,7 +14352,7 @@
         <v>2.66</v>
       </c>
       <c r="Q55" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="R55" t="n">
         <v>1.74</v>
@@ -14361,10 +14361,10 @@
         <v>2.04</v>
       </c>
       <c r="T55" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="U55" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="V55" t="n">
         <v>1.12</v>
@@ -14400,7 +14400,7 @@
         <v>13.5</v>
       </c>
       <c r="AG55" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AH55" t="n">
         <v>24</v>
@@ -14412,7 +14412,7 @@
         <v>16</v>
       </c>
       <c r="AK55" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AL55" t="n">
         <v>32</v>
@@ -14427,58 +14427,58 @@
         <v>85</v>
       </c>
       <c r="AP55" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AQ55" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AR55" t="n">
         <v>4.9</v>
       </c>
-      <c r="AQ55" t="n">
+      <c r="AS55" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AT55" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AU55" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AV55" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AW55" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX55" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AY55" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AZ55" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BA55" t="n">
         <v>4.9</v>
       </c>
-      <c r="AR55" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AS55" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AT55" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AU55" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AV55" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AW55" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AX55" t="n">
+      <c r="BB55" t="n">
         <v>3.95</v>
       </c>
-      <c r="AY55" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AZ55" t="n">
+      <c r="BC55" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD55" t="n">
         <v>4.5</v>
       </c>
-      <c r="BA55" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BB55" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BC55" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BD55" t="n">
-        <v>4.8</v>
-      </c>
       <c r="BE55" t="n">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="BF55" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="BG55" t="n">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="BH55" t="n">
         <v>5.7</v>
@@ -14542,7 +14542,7 @@
       </c>
       <c r="CB55" t="inlineStr">
         <is>
-          <t>2026-07-18 14:16:24</t>
+          <t>2026-07-18 16:34:23</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-19.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-19.xlsx
@@ -863,7 +863,7 @@
         <v>3.85</v>
       </c>
       <c r="H2" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="I2" t="n">
         <v>2.16</v>
@@ -890,7 +890,7 @@
         <v>2</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="R2" t="n">
         <v>1.39</v>
@@ -920,7 +920,7 @@
         <v>14</v>
       </c>
       <c r="AA2" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AB2" t="n">
         <v>14.5</v>
@@ -1052,7 +1052,7 @@
         <v>42</v>
       </c>
       <c r="BS2" t="n">
-        <v>28</v>
+        <v>1.04</v>
       </c>
       <c r="BT2" t="n">
         <v>5.1</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-18 16:34:23</t>
+          <t>2026-07-18 18:49:17</t>
         </is>
       </c>
     </row>
@@ -1123,7 +1123,7 @@
         <v>6.8</v>
       </c>
       <c r="J3" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K3" t="n">
         <v>4</v>
@@ -1135,19 +1135,19 @@
         <v>1.09</v>
       </c>
       <c r="N3" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O3" t="n">
         <v>1.42</v>
       </c>
       <c r="P3" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="R3" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S3" t="n">
         <v>4.2</v>
@@ -1156,7 +1156,7 @@
         <v>2.2</v>
       </c>
       <c r="U3" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="V3" t="n">
         <v>1.17</v>
@@ -1174,7 +1174,7 @@
         <v>60</v>
       </c>
       <c r="AA3" t="n">
-        <v>1000</v>
+        <v>690</v>
       </c>
       <c r="AB3" t="n">
         <v>6.8</v>
@@ -1186,7 +1186,7 @@
         <v>28</v>
       </c>
       <c r="AE3" t="n">
-        <v>1000</v>
+        <v>460</v>
       </c>
       <c r="AF3" t="n">
         <v>8.800000000000001</v>
@@ -1198,7 +1198,7 @@
         <v>29</v>
       </c>
       <c r="AI3" t="n">
-        <v>1000</v>
+        <v>440</v>
       </c>
       <c r="AJ3" t="n">
         <v>16.5</v>
@@ -1210,13 +1210,13 @@
         <v>60</v>
       </c>
       <c r="AM3" t="n">
-        <v>1000</v>
+        <v>570</v>
       </c>
       <c r="AN3" t="n">
         <v>13</v>
       </c>
       <c r="AO3" t="n">
-        <v>1000</v>
+        <v>690</v>
       </c>
       <c r="AP3" t="n">
         <v>10.5</v>
@@ -1225,7 +1225,7 @@
         <v>15.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AS3" t="n">
         <v>46</v>
@@ -1237,7 +1237,7 @@
         <v>8</v>
       </c>
       <c r="AV3" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AW3" t="n">
         <v>40</v>
@@ -1249,16 +1249,16 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ3" t="n">
-        <v>19.5</v>
+        <v>23</v>
       </c>
       <c r="BA3" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="BB3" t="n">
         <v>14</v>
       </c>
       <c r="BC3" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BD3" t="n">
         <v>38</v>
@@ -1273,68 +1273,68 @@
         <v>46</v>
       </c>
       <c r="BH3" t="n">
-        <v>1000</v>
+        <v>3.55</v>
       </c>
       <c r="BI3" t="n">
-        <v>1.01</v>
+        <v>2.52</v>
       </c>
       <c r="BJ3" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK3" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL3" t="n">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="BM3" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN3" t="n">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="BP3" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BQ3" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR3" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BS3" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT3" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BU3" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV3" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="BW3" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX3" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ3" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="CA3" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-18 16:34:23</t>
+          <t>2026-07-18 18:49:17</t>
         </is>
       </c>
     </row>
@@ -1371,7 +1371,7 @@
         <v>6</v>
       </c>
       <c r="H4" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="I4" t="n">
         <v>1.82</v>
@@ -1389,7 +1389,7 @@
         <v>1.09</v>
       </c>
       <c r="N4" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="O4" t="n">
         <v>1.43</v>
@@ -1410,7 +1410,7 @@
         <v>2.1</v>
       </c>
       <c r="U4" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="V4" t="n">
         <v>2.2</v>
@@ -1428,7 +1428,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AA4" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AB4" t="n">
         <v>16</v>
@@ -1446,28 +1446,28 @@
         <v>46</v>
       </c>
       <c r="AG4" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AH4" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="AI4" t="n">
         <v>48</v>
       </c>
       <c r="AJ4" t="n">
-        <v>190</v>
+        <v>700</v>
       </c>
       <c r="AK4" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AL4" t="n">
-        <v>110</v>
+        <v>240</v>
       </c>
       <c r="AM4" t="n">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="AN4" t="n">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="AO4" t="n">
         <v>15.5</v>
@@ -1479,10 +1479,10 @@
         <v>6.2</v>
       </c>
       <c r="AR4" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AS4" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AT4" t="n">
         <v>13</v>
@@ -1497,7 +1497,7 @@
         <v>19.5</v>
       </c>
       <c r="AX4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AY4" t="n">
         <v>19</v>
@@ -1506,25 +1506,25 @@
         <v>20</v>
       </c>
       <c r="BA4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BB4" t="n">
+        <v>12</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>12</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>12</v>
+      </c>
+      <c r="BG4" t="n">
         <v>13.5</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>13</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>13</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>14</v>
       </c>
       <c r="BH4" t="n">
         <v>3.4</v>
@@ -1536,59 +1536,59 @@
         <v>13</v>
       </c>
       <c r="BK4" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BL4" t="n">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="BM4" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BN4" t="n">
         <v>10.5</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BP4" t="n">
         <v>60</v>
       </c>
       <c r="BQ4" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BR4" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="BS4" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BT4" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="BU4" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="BV4" t="n">
         <v>15</v>
       </c>
       <c r="BW4" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BX4" t="n">
         <v>34</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BZ4" t="n">
         <v>30</v>
       </c>
       <c r="CA4" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-18 16:34:23</t>
+          <t>2026-07-18 18:49:17</t>
         </is>
       </c>
     </row>
@@ -1625,7 +1625,7 @@
         <v>1.86</v>
       </c>
       <c r="H5" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="I5" t="n">
         <v>5.7</v>
@@ -1655,7 +1655,7 @@
         <v>1.94</v>
       </c>
       <c r="R5" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S5" t="n">
         <v>3.45</v>
@@ -1673,16 +1673,16 @@
         <v>2.16</v>
       </c>
       <c r="X5" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="Y5" t="n">
         <v>18</v>
       </c>
       <c r="Z5" t="n">
-        <v>46</v>
+        <v>100</v>
       </c>
       <c r="AA5" t="n">
-        <v>150</v>
+        <v>700</v>
       </c>
       <c r="AB5" t="n">
         <v>9.800000000000001</v>
@@ -1694,37 +1694,37 @@
         <v>22</v>
       </c>
       <c r="AE5" t="n">
-        <v>75</v>
+        <v>400</v>
       </c>
       <c r="AF5" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AG5" t="n">
         <v>11</v>
       </c>
       <c r="AH5" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI5" t="n">
-        <v>75</v>
+        <v>700</v>
       </c>
       <c r="AJ5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AK5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AL5" t="n">
         <v>42</v>
       </c>
       <c r="AM5" t="n">
-        <v>140</v>
+        <v>580</v>
       </c>
       <c r="AN5" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AO5" t="n">
-        <v>100</v>
+        <v>700</v>
       </c>
       <c r="AP5" t="n">
         <v>11</v>
@@ -1733,13 +1733,13 @@
         <v>13</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AT5" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AU5" t="n">
         <v>6.8</v>
@@ -1748,7 +1748,7 @@
         <v>15</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AX5" t="n">
         <v>8.4</v>
@@ -1760,7 +1760,7 @@
         <v>15</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BB5" t="n">
         <v>15</v>
@@ -1769,16 +1769,16 @@
         <v>15</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BF5" t="n">
         <v>9.6</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BH5" t="n">
         <v>3.8</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-18 16:34:23</t>
+          <t>2026-07-18 18:49:17</t>
         </is>
       </c>
     </row>
@@ -1918,7 +1918,7 @@
         <v>1.75</v>
       </c>
       <c r="U6" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="V6" t="n">
         <v>1.55</v>
@@ -1990,7 +1990,7 @@
         <v>13.5</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AT6" t="n">
         <v>9</v>
@@ -2002,7 +2002,7 @@
         <v>9.4</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AX6" t="n">
         <v>15</v>
@@ -2014,22 +2014,22 @@
         <v>13</v>
       </c>
       <c r="BA6" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="BB6" t="n">
-        <v>34</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BD6" t="n">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BG6" t="n">
         <v>19</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-18 16:34:23</t>
+          <t>2026-07-18 18:49:17</t>
         </is>
       </c>
     </row>
@@ -2127,10 +2127,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="G7" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="H7" t="n">
         <v>2.44</v>
@@ -2226,7 +2226,7 @@
         <v>60</v>
       </c>
       <c r="AM7" t="n">
-        <v>120</v>
+        <v>580</v>
       </c>
       <c r="AN7" t="n">
         <v>44</v>
@@ -2244,7 +2244,7 @@
         <v>12</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AT7" t="n">
         <v>8.800000000000001</v>
@@ -2268,22 +2268,22 @@
         <v>12.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BG7" t="n">
         <v>17.5</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-18 16:34:23</t>
+          <t>2026-07-18 18:49:17</t>
         </is>
       </c>
     </row>
@@ -2384,7 +2384,7 @@
         <v>1.39</v>
       </c>
       <c r="G8" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="H8" t="n">
         <v>8.199999999999999</v>
@@ -2393,7 +2393,7 @@
         <v>10</v>
       </c>
       <c r="J8" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="K8" t="n">
         <v>5.6</v>
@@ -2423,10 +2423,10 @@
         <v>2.86</v>
       </c>
       <c r="T8" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="U8" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="V8" t="n">
         <v>1.11</v>
@@ -2441,7 +2441,7 @@
         <v>30</v>
       </c>
       <c r="Z8" t="n">
-        <v>95</v>
+        <v>540</v>
       </c>
       <c r="AA8" t="n">
         <v>370</v>
@@ -2450,7 +2450,7 @@
         <v>9</v>
       </c>
       <c r="AC8" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AD8" t="n">
         <v>34</v>
@@ -2462,13 +2462,13 @@
         <v>9</v>
       </c>
       <c r="AG8" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AH8" t="n">
         <v>27</v>
       </c>
       <c r="AI8" t="n">
-        <v>140</v>
+        <v>470</v>
       </c>
       <c r="AJ8" t="n">
         <v>15</v>
@@ -2480,7 +2480,7 @@
         <v>44</v>
       </c>
       <c r="AM8" t="n">
-        <v>180</v>
+        <v>390</v>
       </c>
       <c r="AN8" t="n">
         <v>6.8</v>
@@ -2495,22 +2495,22 @@
         <v>20</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AS8" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AT8" t="n">
         <v>6.4</v>
       </c>
       <c r="AU8" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AX8" t="n">
         <v>7.4</v>
@@ -2522,7 +2522,7 @@
         <v>18.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BB8" t="n">
         <v>9</v>
@@ -2531,16 +2531,16 @@
         <v>11</v>
       </c>
       <c r="BD8" t="n">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BF8" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="BG8" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BH8" t="n">
         <v>4.6</v>
@@ -2552,13 +2552,13 @@
         <v>14</v>
       </c>
       <c r="BK8" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="BL8" t="n">
         <v>180</v>
       </c>
       <c r="BM8" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BN8" t="n">
         <v>4.6</v>
@@ -2570,31 +2570,31 @@
         <v>10.5</v>
       </c>
       <c r="BQ8" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="BR8" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BS8" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BT8" t="n">
         <v>14.5</v>
       </c>
       <c r="BU8" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="BV8" t="n">
         <v>95</v>
       </c>
       <c r="BW8" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BX8" t="n">
         <v>90</v>
       </c>
       <c r="BY8" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BZ8" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-18 16:34:23</t>
+          <t>2026-07-18 18:49:17</t>
         </is>
       </c>
     </row>
@@ -2638,10 +2638,10 @@
         <v>2.34</v>
       </c>
       <c r="G9" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="H9" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="I9" t="n">
         <v>4.4</v>
@@ -2650,7 +2650,7 @@
         <v>2.64</v>
       </c>
       <c r="K9" t="n">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="L9" t="n">
         <v>1.53</v>
@@ -2686,7 +2686,7 @@
         <v>1.3</v>
       </c>
       <c r="W9" t="n">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="X9" t="n">
         <v>9.6</v>
@@ -2698,103 +2698,103 @@
         <v>26</v>
       </c>
       <c r="AA9" t="n">
-        <v>90</v>
+        <v>900</v>
       </c>
       <c r="AB9" t="n">
         <v>8</v>
       </c>
       <c r="AC9" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="AD9" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AE9" t="n">
-        <v>75</v>
+        <v>160</v>
       </c>
       <c r="AF9" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AG9" t="n">
         <v>14.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AI9" t="n">
-        <v>120</v>
+        <v>540</v>
       </c>
       <c r="AJ9" t="n">
-        <v>55</v>
+        <v>110</v>
       </c>
       <c r="AK9" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="AL9" t="n">
         <v>85</v>
       </c>
       <c r="AM9" t="n">
-        <v>270</v>
+        <v>500</v>
       </c>
       <c r="AN9" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AO9" t="n">
-        <v>110</v>
+        <v>500</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AS9" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BD9" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BG9" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BH9" t="n">
         <v>2.9</v>
@@ -2806,13 +2806,13 @@
         <v>14.5</v>
       </c>
       <c r="BK9" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BL9" t="n">
         <v>300</v>
       </c>
       <c r="BM9" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BN9" t="n">
         <v>6</v>
@@ -2824,13 +2824,13 @@
         <v>29</v>
       </c>
       <c r="BQ9" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BR9" t="n">
         <v>65</v>
       </c>
       <c r="BS9" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BT9" t="n">
         <v>8</v>
@@ -2842,23 +2842,23 @@
         <v>46</v>
       </c>
       <c r="BW9" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BX9" t="n">
         <v>80</v>
       </c>
       <c r="BY9" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BZ9" t="n">
         <v>75</v>
       </c>
       <c r="CA9" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-18 16:34:23</t>
+          <t>2026-07-18 18:49:17</t>
         </is>
       </c>
     </row>
@@ -2931,10 +2931,10 @@
         <v>4.4</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="V10" t="n">
         <v>1.47</v>
@@ -2952,103 +2952,103 @@
         <v>19</v>
       </c>
       <c r="AA10" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AB10" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC10" t="n">
         <v>7.4</v>
       </c>
       <c r="AD10" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AE10" t="n">
-        <v>44</v>
+        <v>290</v>
       </c>
       <c r="AF10" t="n">
         <v>21</v>
       </c>
       <c r="AG10" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AH10" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI10" t="n">
-        <v>75</v>
+        <v>500</v>
       </c>
       <c r="AJ10" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AK10" t="n">
         <v>50</v>
       </c>
       <c r="AL10" t="n">
-        <v>80</v>
+        <v>160</v>
       </c>
       <c r="AM10" t="n">
-        <v>190</v>
+        <v>500</v>
       </c>
       <c r="AN10" t="n">
-        <v>65</v>
+        <v>500</v>
       </c>
       <c r="AO10" t="n">
-        <v>55</v>
+        <v>390</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BD10" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BG10" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BH10" t="n">
         <v>3.05</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-18 16:34:23</t>
+          <t>2026-07-18 18:49:17</t>
         </is>
       </c>
     </row>
@@ -3188,7 +3188,7 @@
         <v>1.63</v>
       </c>
       <c r="U11" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="V11" t="n">
         <v>1.2</v>
@@ -3197,16 +3197,16 @@
         <v>2.48</v>
       </c>
       <c r="X11" t="n">
-        <v>29</v>
+        <v>500</v>
       </c>
       <c r="Y11" t="n">
-        <v>28</v>
+        <v>950</v>
       </c>
       <c r="Z11" t="n">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="AA11" t="n">
-        <v>140</v>
+        <v>700</v>
       </c>
       <c r="AB11" t="n">
         <v>13.5</v>
@@ -3215,10 +3215,10 @@
         <v>11.5</v>
       </c>
       <c r="AD11" t="n">
-        <v>22</v>
+        <v>500</v>
       </c>
       <c r="AE11" t="n">
-        <v>60</v>
+        <v>700</v>
       </c>
       <c r="AF11" t="n">
         <v>14</v>
@@ -3227,10 +3227,10 @@
         <v>11</v>
       </c>
       <c r="AH11" t="n">
-        <v>970</v>
+        <v>25</v>
       </c>
       <c r="AI11" t="n">
-        <v>55</v>
+        <v>700</v>
       </c>
       <c r="AJ11" t="n">
         <v>16.5</v>
@@ -3239,22 +3239,22 @@
         <v>15.5</v>
       </c>
       <c r="AL11" t="n">
-        <v>27</v>
+        <v>500</v>
       </c>
       <c r="AM11" t="n">
-        <v>70</v>
+        <v>580</v>
       </c>
       <c r="AN11" t="n">
         <v>6.6</v>
       </c>
       <c r="AO11" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AP11" t="n">
-        <v>7.8</v>
+        <v>21</v>
       </c>
       <c r="AQ11" t="n">
-        <v>7.6</v>
+        <v>14.5</v>
       </c>
       <c r="AR11" t="n">
         <v>8.800000000000001</v>
@@ -3269,7 +3269,7 @@
         <v>10</v>
       </c>
       <c r="AV11" t="n">
-        <v>16</v>
+        <v>11.5</v>
       </c>
       <c r="AW11" t="n">
         <v>9</v>
@@ -3281,10 +3281,10 @@
         <v>9.4</v>
       </c>
       <c r="AZ11" t="n">
-        <v>15.5</v>
+        <v>9</v>
       </c>
       <c r="BA11" t="n">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="BB11" t="n">
         <v>14</v>
@@ -3293,7 +3293,7 @@
         <v>13</v>
       </c>
       <c r="BD11" t="n">
-        <v>18.5</v>
+        <v>13</v>
       </c>
       <c r="BE11" t="n">
         <v>9.199999999999999</v>
@@ -3302,7 +3302,7 @@
         <v>5.4</v>
       </c>
       <c r="BG11" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BH11" t="n">
         <v>5.4</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-18 16:34:23</t>
+          <t>2026-07-18 18:49:17</t>
         </is>
       </c>
     </row>
@@ -3397,7 +3397,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="G12" t="n">
         <v>2.8</v>
@@ -3409,10 +3409,10 @@
         <v>4.3</v>
       </c>
       <c r="J12" t="n">
-        <v>2.5</v>
+        <v>2.66</v>
       </c>
       <c r="K12" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="L12" t="n">
         <v>1.53</v>
@@ -3460,7 +3460,7 @@
         <v>27</v>
       </c>
       <c r="AA12" t="n">
-        <v>110</v>
+        <v>900</v>
       </c>
       <c r="AB12" t="n">
         <v>7.8</v>
@@ -3475,7 +3475,7 @@
         <v>75</v>
       </c>
       <c r="AF12" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AG12" t="n">
         <v>15.5</v>
@@ -3484,19 +3484,19 @@
         <v>36</v>
       </c>
       <c r="AI12" t="n">
-        <v>120</v>
+        <v>260</v>
       </c>
       <c r="AJ12" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AK12" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AL12" t="n">
         <v>80</v>
       </c>
       <c r="AM12" t="n">
-        <v>280</v>
+        <v>500</v>
       </c>
       <c r="AN12" t="n">
         <v>55</v>
@@ -3505,122 +3505,122 @@
         <v>120</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AS12" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="AV12" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BD12" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BG12" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BH12" t="n">
         <v>1000</v>
       </c>
       <c r="BI12" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ12" t="n">
         <v>1000</v>
       </c>
       <c r="BK12" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN12" t="n">
         <v>1000</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP12" t="n">
         <v>1000</v>
       </c>
       <c r="BQ12" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR12" t="n">
         <v>1000</v>
       </c>
       <c r="BS12" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT12" t="n">
         <v>1000</v>
       </c>
       <c r="BU12" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV12" t="n">
         <v>1000</v>
       </c>
       <c r="BW12" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX12" t="n">
         <v>1000</v>
       </c>
       <c r="BY12" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ12" t="n">
         <v>1000</v>
       </c>
       <c r="CA12" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-18 16:34:23</t>
+          <t>2026-07-18 18:49:17</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3651,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="G13" t="n">
         <v>4.4</v>
@@ -3666,7 +3666,7 @@
         <v>2.76</v>
       </c>
       <c r="K13" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L13" t="n">
         <v>1.52</v>
@@ -3741,7 +3741,7 @@
         <v>70</v>
       </c>
       <c r="AJ13" t="n">
-        <v>100</v>
+        <v>900</v>
       </c>
       <c r="AK13" t="n">
         <v>70</v>
@@ -3750,7 +3750,7 @@
         <v>95</v>
       </c>
       <c r="AM13" t="n">
-        <v>210</v>
+        <v>500</v>
       </c>
       <c r="AN13" t="n">
         <v>110</v>
@@ -3762,55 +3762,55 @@
         <v>6.6</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AS13" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AV13" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BA13" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BD13" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BG13" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BH13" t="n">
         <v>3.1</v>
@@ -3822,31 +3822,31 @@
         <v>13</v>
       </c>
       <c r="BK13" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BL13" t="n">
         <v>240</v>
       </c>
       <c r="BM13" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BN13" t="n">
         <v>8.6</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="BP13" t="n">
         <v>44</v>
       </c>
       <c r="BQ13" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BR13" t="n">
         <v>70</v>
       </c>
       <c r="BS13" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BT13" t="n">
         <v>5.6</v>
@@ -3858,23 +3858,23 @@
         <v>24</v>
       </c>
       <c r="BW13" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BX13" t="n">
         <v>55</v>
       </c>
       <c r="BY13" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BZ13" t="n">
         <v>60</v>
       </c>
       <c r="CA13" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-18 16:34:23</t>
+          <t>2026-07-18 18:49:17</t>
         </is>
       </c>
     </row>
@@ -3905,10 +3905,10 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="G14" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="H14" t="n">
         <v>4.6</v>
@@ -3923,7 +3923,7 @@
         <v>3.95</v>
       </c>
       <c r="L14" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="M14" t="n">
         <v>1.09</v>
@@ -3944,7 +3944,7 @@
         <v>1.24</v>
       </c>
       <c r="S14" t="n">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="T14" t="n">
         <v>1.98</v>
@@ -3956,19 +3956,19 @@
         <v>1.2</v>
       </c>
       <c r="W14" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="X14" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="Y14" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Z14" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AA14" t="n">
-        <v>180</v>
+        <v>900</v>
       </c>
       <c r="AB14" t="n">
         <v>7.6</v>
@@ -3977,34 +3977,34 @@
         <v>8.6</v>
       </c>
       <c r="AD14" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AE14" t="n">
-        <v>110</v>
+        <v>240</v>
       </c>
       <c r="AF14" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AG14" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AI14" t="n">
         <v>110</v>
       </c>
       <c r="AJ14" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AK14" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL14" t="n">
         <v>55</v>
       </c>
       <c r="AM14" t="n">
-        <v>180</v>
+        <v>580</v>
       </c>
       <c r="AN14" t="n">
         <v>18.5</v>
@@ -4013,58 +4013,58 @@
         <v>150</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AS14" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AV14" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BA14" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BD14" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BG14" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BH14" t="n">
         <v>3.5</v>
@@ -4076,59 +4076,59 @@
         <v>13.5</v>
       </c>
       <c r="BK14" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="BL14" t="n">
         <v>220</v>
       </c>
       <c r="BM14" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BN14" t="n">
         <v>5.1</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.01</v>
+        <v>2.48</v>
       </c>
       <c r="BP14" t="n">
         <v>17</v>
       </c>
       <c r="BQ14" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BR14" t="n">
         <v>42</v>
       </c>
       <c r="BS14" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BT14" t="n">
         <v>10</v>
       </c>
       <c r="BU14" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="BV14" t="n">
         <v>65</v>
       </c>
       <c r="BW14" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BX14" t="n">
         <v>80</v>
       </c>
       <c r="BY14" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BZ14" t="n">
         <v>40</v>
       </c>
       <c r="CA14" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-18 16:34:23</t>
+          <t>2026-07-18 18:49:17</t>
         </is>
       </c>
     </row>
@@ -4183,7 +4183,7 @@
         <v>1.12</v>
       </c>
       <c r="N15" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="O15" t="n">
         <v>1.51</v>
@@ -4213,7 +4213,7 @@
         <v>1.58</v>
       </c>
       <c r="X15" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y15" t="n">
         <v>11</v>
@@ -4222,7 +4222,7 @@
         <v>24</v>
       </c>
       <c r="AA15" t="n">
-        <v>90</v>
+        <v>500</v>
       </c>
       <c r="AB15" t="n">
         <v>8.199999999999999</v>
@@ -4231,7 +4231,7 @@
         <v>7.4</v>
       </c>
       <c r="AD15" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AE15" t="n">
         <v>60</v>
@@ -4249,16 +4249,16 @@
         <v>85</v>
       </c>
       <c r="AJ15" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AK15" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AL15" t="n">
         <v>70</v>
       </c>
       <c r="AM15" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="AN15" t="n">
         <v>46</v>
@@ -4267,58 +4267,58 @@
         <v>90</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="AS15" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="AV15" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="AW15" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BA15" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BD15" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BG15" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BH15" t="n">
         <v>3</v>
@@ -4330,59 +4330,59 @@
         <v>13</v>
       </c>
       <c r="BK15" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BL15" t="n">
         <v>230</v>
       </c>
       <c r="BM15" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BN15" t="n">
         <v>5.9</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.01</v>
+        <v>2.96</v>
       </c>
       <c r="BP15" t="n">
         <v>26</v>
       </c>
       <c r="BQ15" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BR15" t="n">
         <v>55</v>
       </c>
       <c r="BS15" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BT15" t="n">
         <v>7.4</v>
       </c>
       <c r="BU15" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="BV15" t="n">
         <v>40</v>
       </c>
       <c r="BW15" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BX15" t="n">
         <v>65</v>
       </c>
       <c r="BY15" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BZ15" t="n">
         <v>60</v>
       </c>
       <c r="CA15" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-18 16:34:23</t>
+          <t>2026-07-18 18:49:17</t>
         </is>
       </c>
     </row>
@@ -4413,13 +4413,13 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="G16" t="n">
         <v>3.3</v>
       </c>
       <c r="H16" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="I16" t="n">
         <v>2.8</v>
@@ -4506,25 +4506,25 @@
         <v>55</v>
       </c>
       <c r="AK16" t="n">
-        <v>38</v>
+        <v>500</v>
       </c>
       <c r="AL16" t="n">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="AM16" t="n">
-        <v>120</v>
+        <v>580</v>
       </c>
       <c r="AN16" t="n">
-        <v>36</v>
+        <v>500</v>
       </c>
       <c r="AO16" t="n">
-        <v>27</v>
+        <v>500</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AR16" t="n">
         <v>12.5</v>
@@ -4533,7 +4533,7 @@
         <v>25</v>
       </c>
       <c r="AT16" t="n">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU16" t="n">
         <v>6</v>
@@ -4542,37 +4542,37 @@
         <v>10</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AX16" t="n">
         <v>15.5</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BA16" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC16" t="n">
         <v>30</v>
       </c>
       <c r="BD16" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BG16" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BH16" t="n">
         <v>3.6</v>
@@ -4584,59 +4584,59 @@
         <v>11</v>
       </c>
       <c r="BK16" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BL16" t="n">
         <v>150</v>
       </c>
       <c r="BM16" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BN16" t="n">
         <v>7</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="BP16" t="n">
         <v>28</v>
       </c>
       <c r="BQ16" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BR16" t="n">
         <v>44</v>
       </c>
       <c r="BS16" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BT16" t="n">
         <v>6.2</v>
       </c>
       <c r="BU16" t="n">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="BV16" t="n">
         <v>24</v>
       </c>
       <c r="BW16" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BX16" t="n">
         <v>40</v>
       </c>
       <c r="BY16" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BZ16" t="n">
         <v>36</v>
       </c>
       <c r="CA16" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-18 16:34:23</t>
+          <t>2026-07-18 18:49:17</t>
         </is>
       </c>
     </row>
@@ -4667,22 +4667,22 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="G17" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="H17" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="I17" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="J17" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="K17" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L17" t="n">
         <v>1.37</v>
@@ -4697,10 +4697,10 @@
         <v>1.25</v>
       </c>
       <c r="P17" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="R17" t="n">
         <v>1.46</v>
@@ -4709,7 +4709,7 @@
         <v>2.82</v>
       </c>
       <c r="T17" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="U17" t="n">
         <v>2.28</v>
@@ -4718,31 +4718,31 @@
         <v>1.29</v>
       </c>
       <c r="W17" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="X17" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="Y17" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="Z17" t="n">
         <v>48</v>
       </c>
       <c r="AA17" t="n">
-        <v>110</v>
+        <v>900</v>
       </c>
       <c r="AB17" t="n">
         <v>11.5</v>
       </c>
       <c r="AC17" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AD17" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AE17" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="AF17" t="n">
         <v>13.5</v>
@@ -4754,7 +4754,7 @@
         <v>18</v>
       </c>
       <c r="AI17" t="n">
-        <v>75</v>
+        <v>120</v>
       </c>
       <c r="AJ17" t="n">
         <v>23</v>
@@ -4766,13 +4766,13 @@
         <v>44</v>
       </c>
       <c r="AM17" t="n">
-        <v>100</v>
+        <v>320</v>
       </c>
       <c r="AN17" t="n">
         <v>11</v>
       </c>
       <c r="AO17" t="n">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="AP17" t="n">
         <v>16</v>
@@ -4781,10 +4781,10 @@
         <v>15.5</v>
       </c>
       <c r="AR17" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="AS17" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT17" t="n">
         <v>9.199999999999999</v>
@@ -4808,7 +4808,7 @@
         <v>14.5</v>
       </c>
       <c r="BA17" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="BB17" t="n">
         <v>18</v>
@@ -4817,16 +4817,16 @@
         <v>15.5</v>
       </c>
       <c r="BD17" t="n">
-        <v>7</v>
+        <v>14.5</v>
       </c>
       <c r="BE17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BF17" t="n">
         <v>7.8</v>
       </c>
       <c r="BG17" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="BH17" t="n">
         <v>4.5</v>
@@ -4838,16 +4838,16 @@
         <v>11.5</v>
       </c>
       <c r="BK17" t="n">
-        <v>3.35</v>
+        <v>3.65</v>
       </c>
       <c r="BL17" t="n">
         <v>120</v>
       </c>
       <c r="BM17" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="BN17" t="n">
-        <v>5.6</v>
+        <v>5</v>
       </c>
       <c r="BO17" t="n">
         <v>3.7</v>
@@ -4856,41 +4856,41 @@
         <v>15.5</v>
       </c>
       <c r="BQ17" t="n">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="BR17" t="n">
         <v>29</v>
       </c>
       <c r="BS17" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="BT17" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BU17" t="n">
-        <v>3.15</v>
+        <v>5.8</v>
       </c>
       <c r="BV17" t="n">
         <v>40</v>
       </c>
       <c r="BW17" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="BX17" t="n">
         <v>48</v>
       </c>
       <c r="BY17" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="BZ17" t="n">
         <v>23</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-18 16:34:23</t>
+          <t>2026-07-18 18:49:17</t>
         </is>
       </c>
     </row>
@@ -4921,10 +4921,10 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="G18" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="H18" t="n">
         <v>2.54</v>
@@ -5020,7 +5020,7 @@
         <v>42</v>
       </c>
       <c r="AM18" t="n">
-        <v>80</v>
+        <v>320</v>
       </c>
       <c r="AN18" t="n">
         <v>21</v>
@@ -5062,19 +5062,19 @@
         <v>13</v>
       </c>
       <c r="BA18" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="BB18" t="n">
         <v>34</v>
       </c>
       <c r="BC18" t="n">
-        <v>6.8</v>
+        <v>13</v>
       </c>
       <c r="BD18" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BE18" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BF18" t="n">
         <v>15</v>
@@ -5098,7 +5098,7 @@
         <v>110</v>
       </c>
       <c r="BM18" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="BN18" t="n">
         <v>7.4</v>
@@ -5110,16 +5110,16 @@
         <v>22</v>
       </c>
       <c r="BQ18" t="n">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="BR18" t="n">
         <v>36</v>
       </c>
       <c r="BS18" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="BT18" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BU18" t="n">
         <v>5</v>
@@ -5128,23 +5128,23 @@
         <v>22</v>
       </c>
       <c r="BW18" t="n">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="BX18" t="n">
         <v>34</v>
       </c>
       <c r="BY18" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="BZ18" t="n">
         <v>25</v>
       </c>
       <c r="CA18" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-18 16:34:23</t>
+          <t>2026-07-18 18:49:17</t>
         </is>
       </c>
     </row>
@@ -5229,7 +5229,7 @@
         <v>1.47</v>
       </c>
       <c r="X19" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="Y19" t="n">
         <v>9</v>
@@ -5238,7 +5238,7 @@
         <v>19.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="AB19" t="n">
         <v>8.800000000000001</v>
@@ -5247,7 +5247,7 @@
         <v>7.4</v>
       </c>
       <c r="AD19" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AE19" t="n">
         <v>55</v>
@@ -5262,25 +5262,25 @@
         <v>24</v>
       </c>
       <c r="AI19" t="n">
-        <v>75</v>
+        <v>160</v>
       </c>
       <c r="AJ19" t="n">
-        <v>65</v>
+        <v>280</v>
       </c>
       <c r="AK19" t="n">
-        <v>48</v>
+        <v>190</v>
       </c>
       <c r="AL19" t="n">
-        <v>75</v>
+        <v>380</v>
       </c>
       <c r="AM19" t="n">
-        <v>190</v>
+        <v>500</v>
       </c>
       <c r="AN19" t="n">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="AO19" t="n">
-        <v>65</v>
+        <v>500</v>
       </c>
       <c r="AP19" t="n">
         <v>6.6</v>
@@ -5292,19 +5292,19 @@
         <v>14</v>
       </c>
       <c r="AS19" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="AT19" t="n">
         <v>6.6</v>
       </c>
       <c r="AU19" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AV19" t="n">
         <v>10.5</v>
       </c>
       <c r="AW19" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="AX19" t="n">
         <v>14</v>
@@ -5316,25 +5316,25 @@
         <v>17</v>
       </c>
       <c r="BA19" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="BB19" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BC19" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="BD19" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="BE19" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="BF19" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="BG19" t="n">
-        <v>7.2</v>
+        <v>8.6</v>
       </c>
       <c r="BH19" t="n">
         <v>2.96</v>
@@ -5376,7 +5376,7 @@
         <v>6.6</v>
       </c>
       <c r="BU19" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="BV19" t="n">
         <v>32</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-18 16:34:23</t>
+          <t>2026-07-18 18:49:17</t>
         </is>
       </c>
     </row>
@@ -5435,34 +5435,34 @@
         <v>4.6</v>
       </c>
       <c r="H20" t="n">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="I20" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="J20" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="K20" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="L20" t="n">
         <v>1.57</v>
       </c>
       <c r="M20" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="N20" t="n">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="O20" t="n">
         <v>1.54</v>
       </c>
       <c r="P20" t="n">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="R20" t="n">
         <v>1.17</v>
@@ -5477,13 +5477,13 @@
         <v>1.71</v>
       </c>
       <c r="V20" t="n">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="W20" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="X20" t="n">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y20" t="n">
         <v>8.4</v>
@@ -5504,7 +5504,7 @@
         <v>14.5</v>
       </c>
       <c r="AE20" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AF20" t="n">
         <v>36</v>
@@ -5516,19 +5516,19 @@
         <v>30</v>
       </c>
       <c r="AI20" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AJ20" t="n">
         <v>130</v>
       </c>
       <c r="AK20" t="n">
-        <v>90</v>
+        <v>200</v>
       </c>
       <c r="AL20" t="n">
-        <v>120</v>
+        <v>260</v>
       </c>
       <c r="AM20" t="n">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="AN20" t="n">
         <v>140</v>
@@ -5537,28 +5537,28 @@
         <v>42</v>
       </c>
       <c r="AP20" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="AQ20" t="n">
-        <v>5.2</v>
+        <v>5.9</v>
       </c>
       <c r="AR20" t="n">
         <v>9.4</v>
       </c>
       <c r="AS20" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AT20" t="n">
         <v>8</v>
       </c>
       <c r="AU20" t="n">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="AV20" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AW20" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="AX20" t="n">
         <v>20</v>
@@ -5570,25 +5570,25 @@
         <v>18</v>
       </c>
       <c r="BA20" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BC20" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BD20" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BG20" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BH20" t="n">
         <v>3.05</v>
@@ -5600,13 +5600,13 @@
         <v>14</v>
       </c>
       <c r="BK20" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BL20" t="n">
         <v>270</v>
       </c>
       <c r="BM20" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BN20" t="n">
         <v>8.6</v>
@@ -5618,13 +5618,13 @@
         <v>55</v>
       </c>
       <c r="BQ20" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BR20" t="n">
         <v>80</v>
       </c>
       <c r="BS20" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BT20" t="n">
         <v>5.6</v>
@@ -5636,23 +5636,23 @@
         <v>24</v>
       </c>
       <c r="BW20" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BX20" t="n">
         <v>55</v>
       </c>
       <c r="BY20" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BZ20" t="n">
         <v>60</v>
       </c>
       <c r="CA20" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-18 16:34:23</t>
+          <t>2026-07-18 18:49:17</t>
         </is>
       </c>
     </row>
@@ -5683,25 +5683,25 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="G21" t="n">
         <v>2.18</v>
       </c>
       <c r="H21" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="I21" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="J21" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="K21" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L21" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="M21" t="n">
         <v>1.07</v>
@@ -5716,25 +5716,25 @@
         <v>1.91</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="R21" t="n">
         <v>1.36</v>
       </c>
       <c r="S21" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="T21" t="n">
         <v>1.8</v>
       </c>
       <c r="U21" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="V21" t="n">
         <v>1.33</v>
       </c>
       <c r="W21" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="X21" t="n">
         <v>14</v>
@@ -5746,7 +5746,7 @@
         <v>28</v>
       </c>
       <c r="AA21" t="n">
-        <v>80</v>
+        <v>900</v>
       </c>
       <c r="AB21" t="n">
         <v>9.6</v>
@@ -5755,7 +5755,7 @@
         <v>8</v>
       </c>
       <c r="AD21" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AE21" t="n">
         <v>60</v>
@@ -5797,10 +5797,10 @@
         <v>13</v>
       </c>
       <c r="AR21" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AS21" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AT21" t="n">
         <v>8.6</v>
@@ -5812,7 +5812,7 @@
         <v>14.5</v>
       </c>
       <c r="AW21" t="n">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="AX21" t="n">
         <v>11.5</v>
@@ -5836,7 +5836,7 @@
         <v>32</v>
       </c>
       <c r="BE21" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BF21" t="n">
         <v>13.5</v>
@@ -5854,13 +5854,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BK21" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BL21" t="n">
         <v>140</v>
       </c>
       <c r="BM21" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BN21" t="n">
         <v>4.8</v>
@@ -5872,41 +5872,41 @@
         <v>17</v>
       </c>
       <c r="BQ21" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BR21" t="n">
         <v>34</v>
       </c>
       <c r="BS21" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BT21" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BU21" t="n">
         <v>5.7</v>
       </c>
       <c r="BV21" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="BW21" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BX21" t="n">
         <v>50</v>
       </c>
       <c r="BY21" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BZ21" t="n">
         <v>29</v>
       </c>
       <c r="CA21" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-07-18 16:34:23</t>
+          <t>2026-07-18 18:49:17</t>
         </is>
       </c>
     </row>
@@ -5952,7 +5952,7 @@
         <v>3.05</v>
       </c>
       <c r="K22" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L22" t="n">
         <v>1.5</v>
@@ -5985,7 +5985,7 @@
         <v>1.85</v>
       </c>
       <c r="V22" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="W22" t="n">
         <v>1.29</v>
@@ -6000,7 +6000,7 @@
         <v>16</v>
       </c>
       <c r="AA22" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AB22" t="n">
         <v>14.5</v>
@@ -6012,7 +6012,7 @@
         <v>14</v>
       </c>
       <c r="AE22" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AF22" t="n">
         <v>34</v>
@@ -6027,7 +6027,7 @@
         <v>65</v>
       </c>
       <c r="AJ22" t="n">
-        <v>110</v>
+        <v>900</v>
       </c>
       <c r="AK22" t="n">
         <v>75</v>
@@ -6036,7 +6036,7 @@
         <v>95</v>
       </c>
       <c r="AM22" t="n">
-        <v>180</v>
+        <v>500</v>
       </c>
       <c r="AN22" t="n">
         <v>100</v>
@@ -6054,7 +6054,7 @@
         <v>9.6</v>
       </c>
       <c r="AS22" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AT22" t="n">
         <v>8.800000000000001</v>
@@ -6072,95 +6072,95 @@
         <v>20</v>
       </c>
       <c r="AY22" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="AZ22" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BA22" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BC22" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BD22" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BG22" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BH22" t="n">
         <v>1000</v>
       </c>
       <c r="BI22" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ22" t="n">
         <v>1000</v>
       </c>
       <c r="BK22" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL22" t="n">
         <v>1000</v>
       </c>
       <c r="BM22" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN22" t="n">
         <v>1000</v>
       </c>
       <c r="BO22" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP22" t="n">
         <v>1000</v>
       </c>
       <c r="BQ22" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR22" t="n">
         <v>1000</v>
       </c>
       <c r="BS22" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT22" t="n">
         <v>1000</v>
       </c>
       <c r="BU22" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV22" t="n">
         <v>1000</v>
       </c>
       <c r="BW22" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX22" t="n">
         <v>1000</v>
       </c>
       <c r="BY22" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ22" t="n">
         <v>1000</v>
       </c>
       <c r="CA22" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-07-18 16:34:23</t>
+          <t>2026-07-18 18:49:17</t>
         </is>
       </c>
     </row>
@@ -6191,127 +6191,127 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>5.7</v>
+        <v>5.1</v>
       </c>
       <c r="G23" t="n">
-        <v>6.2</v>
+        <v>5.4</v>
       </c>
       <c r="H23" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="I23" t="n">
-        <v>1.66</v>
+        <v>1.74</v>
       </c>
       <c r="J23" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="K23" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="L23" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="M23" t="n">
         <v>1.04</v>
       </c>
       <c r="N23" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="O23" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="P23" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="R23" t="n">
         <v>1.55</v>
       </c>
       <c r="S23" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="T23" t="n">
         <v>1.71</v>
       </c>
       <c r="U23" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="V23" t="n">
-        <v>2.5</v>
+        <v>2.34</v>
       </c>
       <c r="W23" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="X23" t="n">
-        <v>23</v>
+        <v>950</v>
       </c>
       <c r="Y23" t="n">
         <v>11</v>
       </c>
       <c r="Z23" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AA23" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AB23" t="n">
         <v>30</v>
       </c>
       <c r="AC23" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD23" t="n">
         <v>10.5</v>
       </c>
       <c r="AE23" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AF23" t="n">
         <v>50</v>
       </c>
       <c r="AG23" t="n">
-        <v>24</v>
+        <v>950</v>
       </c>
       <c r="AH23" t="n">
         <v>19.5</v>
       </c>
       <c r="AI23" t="n">
-        <v>29</v>
+        <v>500</v>
       </c>
       <c r="AJ23" t="n">
-        <v>160</v>
+        <v>700</v>
       </c>
       <c r="AK23" t="n">
         <v>75</v>
       </c>
       <c r="AL23" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AM23" t="n">
-        <v>90</v>
+        <v>500</v>
       </c>
       <c r="AN23" t="n">
-        <v>70</v>
+        <v>700</v>
       </c>
       <c r="AO23" t="n">
         <v>7.6</v>
       </c>
       <c r="AP23" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AQ23" t="n">
         <v>8</v>
       </c>
       <c r="AR23" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS23" t="n">
         <v>12.5</v>
       </c>
       <c r="AT23" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="AU23" t="n">
         <v>9</v>
@@ -6323,10 +6323,10 @@
         <v>12</v>
       </c>
       <c r="AX23" t="n">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="AY23" t="n">
-        <v>18</v>
+        <v>6.8</v>
       </c>
       <c r="AZ23" t="n">
         <v>14.5</v>
@@ -6335,19 +6335,19 @@
         <v>21</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC23" t="n">
-        <v>1.01</v>
+        <v>46</v>
       </c>
       <c r="BD23" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BG23" t="n">
         <v>6.4</v>
@@ -6362,31 +6362,31 @@
         <v>11</v>
       </c>
       <c r="BK23" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BL23" t="n">
         <v>120</v>
       </c>
       <c r="BM23" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BN23" t="n">
         <v>10.5</v>
       </c>
       <c r="BO23" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="BP23" t="n">
         <v>48</v>
       </c>
       <c r="BQ23" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BR23" t="n">
         <v>50</v>
       </c>
       <c r="BS23" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BT23" t="n">
         <v>5.1</v>
@@ -6398,13 +6398,13 @@
         <v>12</v>
       </c>
       <c r="BW23" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BX23" t="n">
         <v>25</v>
       </c>
       <c r="BY23" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BZ23" t="n">
         <v>0</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-07-18 16:34:23</t>
+          <t>2026-07-18 18:49:17</t>
         </is>
       </c>
     </row>
@@ -6451,7 +6451,7 @@
         <v>2.56</v>
       </c>
       <c r="H24" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="I24" t="n">
         <v>2.98</v>
@@ -6460,7 +6460,7 @@
         <v>4</v>
       </c>
       <c r="K24" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="L24" t="n">
         <v>1.2</v>
@@ -6475,22 +6475,22 @@
         <v>1.14</v>
       </c>
       <c r="P24" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="Q24" t="n">
         <v>1.44</v>
       </c>
       <c r="R24" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="S24" t="n">
         <v>2.08</v>
       </c>
       <c r="T24" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="U24" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="V24" t="n">
         <v>1.51</v>
@@ -6499,112 +6499,112 @@
         <v>1.64</v>
       </c>
       <c r="X24" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="Y24" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="Z24" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AA24" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AB24" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AC24" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AD24" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AE24" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AF24" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AG24" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH24" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AI24" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AK24" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AL24" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AM24" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AN24" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AO24" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.01</v>
+        <v>2.5</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="AR24" t="n">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="AS24" t="n">
         <v>1.01</v>
       </c>
       <c r="AT24" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AU24" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV24" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AW24" t="n">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AY24" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AZ24" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BA24" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BB24" t="n">
         <v>1.01</v>
       </c>
       <c r="BC24" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="BD24" t="n">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="BE24" t="n">
         <v>1.01</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BG24" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH24" t="n">
         <v>5.9</v>
@@ -6622,7 +6622,7 @@
         <v>75</v>
       </c>
       <c r="BM24" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BN24" t="n">
         <v>7.4</v>
@@ -6634,13 +6634,13 @@
         <v>19</v>
       </c>
       <c r="BQ24" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="BR24" t="n">
         <v>26</v>
       </c>
       <c r="BS24" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BT24" t="n">
         <v>8</v>
@@ -6652,23 +6652,23 @@
         <v>22</v>
       </c>
       <c r="BW24" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BX24" t="n">
         <v>28</v>
       </c>
       <c r="BY24" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BZ24" t="n">
         <v>15.5</v>
       </c>
       <c r="CA24" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-07-18 16:34:23</t>
+          <t>2026-07-18 18:49:17</t>
         </is>
       </c>
     </row>
@@ -6699,7 +6699,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="G25" t="n">
         <v>4.3</v>
@@ -6723,16 +6723,16 @@
         <v>1.05</v>
       </c>
       <c r="N25" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="O25" t="n">
         <v>1.25</v>
       </c>
       <c r="P25" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="R25" t="n">
         <v>1.43</v>
@@ -6744,7 +6744,7 @@
         <v>1.69</v>
       </c>
       <c r="U25" t="n">
-        <v>2.24</v>
+        <v>2.38</v>
       </c>
       <c r="V25" t="n">
         <v>1.98</v>
@@ -6762,7 +6762,7 @@
         <v>14</v>
       </c>
       <c r="AA25" t="n">
-        <v>24</v>
+        <v>900</v>
       </c>
       <c r="AB25" t="n">
         <v>17.5</v>
@@ -6786,22 +6786,22 @@
         <v>20</v>
       </c>
       <c r="AI25" t="n">
-        <v>34</v>
+        <v>500</v>
       </c>
       <c r="AJ25" t="n">
-        <v>90</v>
+        <v>900</v>
       </c>
       <c r="AK25" t="n">
         <v>48</v>
       </c>
       <c r="AL25" t="n">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="AM25" t="n">
-        <v>85</v>
+        <v>500</v>
       </c>
       <c r="AN25" t="n">
-        <v>44</v>
+        <v>500</v>
       </c>
       <c r="AO25" t="n">
         <v>12</v>
@@ -6870,13 +6870,13 @@
         <v>11</v>
       </c>
       <c r="BK25" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BL25" t="n">
         <v>120</v>
       </c>
       <c r="BM25" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BN25" t="n">
         <v>9</v>
@@ -6888,13 +6888,13 @@
         <v>38</v>
       </c>
       <c r="BQ25" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BR25" t="n">
         <v>46</v>
       </c>
       <c r="BS25" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BT25" t="n">
         <v>5.4</v>
@@ -6906,23 +6906,23 @@
         <v>15</v>
       </c>
       <c r="BW25" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BX25" t="n">
         <v>29</v>
       </c>
       <c r="BY25" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BZ25" t="n">
         <v>23</v>
       </c>
       <c r="CA25" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-07-18 16:34:23</t>
+          <t>2026-07-18 18:49:17</t>
         </is>
       </c>
     </row>
@@ -6974,13 +6974,13 @@
         <v>1.33</v>
       </c>
       <c r="M26" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N26" t="n">
         <v>5</v>
       </c>
       <c r="O26" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="P26" t="n">
         <v>2.34</v>
@@ -6989,16 +6989,16 @@
         <v>1.7</v>
       </c>
       <c r="R26" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="S26" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="T26" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="U26" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="V26" t="n">
         <v>1.93</v>
@@ -7007,25 +7007,25 @@
         <v>1.35</v>
       </c>
       <c r="X26" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="Y26" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="Z26" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AA26" t="n">
         <v>28</v>
       </c>
       <c r="AB26" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="AC26" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD26" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AE26" t="n">
         <v>20</v>
@@ -7040,19 +7040,19 @@
         <v>16</v>
       </c>
       <c r="AI26" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1000</v>
+        <v>490</v>
       </c>
       <c r="AK26" t="n">
+        <v>85</v>
+      </c>
+      <c r="AL26" t="n">
         <v>42</v>
       </c>
-      <c r="AL26" t="n">
-        <v>48</v>
-      </c>
       <c r="AM26" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AN26" t="n">
         <v>32</v>
@@ -7061,10 +7061,10 @@
         <v>11</v>
       </c>
       <c r="AP26" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AQ26" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AR26" t="n">
         <v>13</v>
@@ -7073,16 +7073,16 @@
         <v>22</v>
       </c>
       <c r="AT26" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AU26" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AV26" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW26" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AX26" t="n">
         <v>26</v>
@@ -7094,19 +7094,19 @@
         <v>14.5</v>
       </c>
       <c r="BA26" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BB26" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BC26" t="n">
         <v>34</v>
       </c>
       <c r="BD26" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BE26" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="BF26" t="n">
         <v>27</v>
@@ -7118,16 +7118,16 @@
         <v>4.5</v>
       </c>
       <c r="BI26" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="BJ26" t="n">
         <v>9</v>
       </c>
       <c r="BK26" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BL26" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="BM26" t="n">
         <v>9.199999999999999</v>
@@ -7139,16 +7139,16 @@
         <v>5.6</v>
       </c>
       <c r="BP26" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BQ26" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BR26" t="n">
         <v>38</v>
       </c>
       <c r="BS26" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BT26" t="n">
         <v>5.1</v>
@@ -7160,23 +7160,23 @@
         <v>14</v>
       </c>
       <c r="BW26" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BX26" t="n">
         <v>25</v>
       </c>
       <c r="BY26" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BZ26" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="CA26" t="n">
         <v>6.4</v>
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-07-18 16:34:23</t>
+          <t>2026-07-18 18:49:17</t>
         </is>
       </c>
     </row>
@@ -7210,13 +7210,13 @@
         <v>1.29</v>
       </c>
       <c r="G27" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="H27" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="I27" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="J27" t="n">
         <v>6.6</v>
@@ -7234,10 +7234,10 @@
         <v>6</v>
       </c>
       <c r="O27" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="P27" t="n">
-        <v>2.68</v>
+        <v>2.74</v>
       </c>
       <c r="Q27" t="n">
         <v>1.55</v>
@@ -7246,10 +7246,10 @@
         <v>1.68</v>
       </c>
       <c r="S27" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="T27" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="U27" t="n">
         <v>1.9</v>
@@ -7264,16 +7264,16 @@
         <v>28</v>
       </c>
       <c r="Y27" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="Z27" t="n">
         <v>130</v>
       </c>
       <c r="AA27" t="n">
-        <v>490</v>
+        <v>520</v>
       </c>
       <c r="AB27" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AC27" t="n">
         <v>15</v>
@@ -7285,7 +7285,7 @@
         <v>200</v>
       </c>
       <c r="AF27" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AG27" t="n">
         <v>11</v>
@@ -7294,10 +7294,10 @@
         <v>32</v>
       </c>
       <c r="AI27" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AJ27" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AK27" t="n">
         <v>13.5</v>
@@ -7312,10 +7312,10 @@
         <v>4.3</v>
       </c>
       <c r="AO27" t="n">
-        <v>210</v>
+        <v>1000</v>
       </c>
       <c r="AP27" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ27" t="n">
         <v>38</v>
@@ -7327,7 +7327,7 @@
         <v>55</v>
       </c>
       <c r="AT27" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AU27" t="n">
         <v>13</v>
@@ -7339,13 +7339,13 @@
         <v>46</v>
       </c>
       <c r="AX27" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AY27" t="n">
         <v>10</v>
       </c>
       <c r="AZ27" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BA27" t="n">
         <v>42</v>
@@ -7357,7 +7357,7 @@
         <v>12</v>
       </c>
       <c r="BD27" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="BE27" t="n">
         <v>44</v>
@@ -7378,7 +7378,7 @@
         <v>14</v>
       </c>
       <c r="BK27" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BL27" t="n">
         <v>170</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-07-18 16:34:23</t>
+          <t>2026-07-18 18:49:17</t>
         </is>
       </c>
     </row>
@@ -7461,16 +7461,16 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="G28" t="n">
         <v>5.7</v>
       </c>
       <c r="H28" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="I28" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="J28" t="n">
         <v>4.7</v>
@@ -7485,31 +7485,31 @@
         <v>1.03</v>
       </c>
       <c r="N28" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="O28" t="n">
         <v>1.18</v>
       </c>
       <c r="P28" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="R28" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="S28" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="T28" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="U28" t="n">
-        <v>2.46</v>
+        <v>2.56</v>
       </c>
       <c r="V28" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="W28" t="n">
         <v>1.21</v>
@@ -7524,13 +7524,13 @@
         <v>12.5</v>
       </c>
       <c r="AA28" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AB28" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AC28" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD28" t="n">
         <v>10</v>
@@ -7539,31 +7539,31 @@
         <v>15</v>
       </c>
       <c r="AF28" t="n">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AG28" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AH28" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AI28" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AJ28" t="n">
-        <v>160</v>
+        <v>690</v>
       </c>
       <c r="AK28" t="n">
-        <v>500</v>
+        <v>390</v>
       </c>
       <c r="AL28" t="n">
-        <v>260</v>
+        <v>220</v>
       </c>
       <c r="AM28" t="n">
-        <v>1000</v>
+        <v>490</v>
       </c>
       <c r="AN28" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AO28" t="n">
         <v>6.2</v>
@@ -7587,19 +7587,19 @@
         <v>10</v>
       </c>
       <c r="AV28" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AW28" t="n">
         <v>13.5</v>
       </c>
       <c r="AX28" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AY28" t="n">
         <v>19.5</v>
       </c>
       <c r="AZ28" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BA28" t="n">
         <v>22</v>
@@ -7611,13 +7611,13 @@
         <v>50</v>
       </c>
       <c r="BD28" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BE28" t="n">
         <v>60</v>
       </c>
       <c r="BF28" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BG28" t="n">
         <v>5.8</v>
@@ -7662,7 +7662,7 @@
         <v>5.5</v>
       </c>
       <c r="BU28" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="BV28" t="n">
         <v>12</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-07-18 16:34:23</t>
+          <t>2026-07-18 18:49:17</t>
         </is>
       </c>
     </row>
@@ -7715,28 +7715,28 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="G29" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="H29" t="n">
-        <v>1.89</v>
+        <v>1.97</v>
       </c>
       <c r="I29" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="J29" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="K29" t="n">
         <v>4</v>
       </c>
       <c r="L29" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="M29" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="N29" t="n">
         <v>4.2</v>
@@ -7760,31 +7760,31 @@
         <v>1.52</v>
       </c>
       <c r="U29" t="n">
-        <v>2.52</v>
+        <v>1.11</v>
       </c>
       <c r="V29" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="W29" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="X29" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="Y29" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="Z29" t="n">
         <v>16.5</v>
       </c>
       <c r="AA29" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AB29" t="n">
         <v>23</v>
       </c>
       <c r="AC29" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD29" t="n">
         <v>12</v>
@@ -7793,10 +7793,10 @@
         <v>19</v>
       </c>
       <c r="AF29" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="AG29" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AH29" t="n">
         <v>16.5</v>
@@ -7805,130 +7805,130 @@
         <v>36</v>
       </c>
       <c r="AJ29" t="n">
-        <v>75</v>
+        <v>900</v>
       </c>
       <c r="AK29" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="AL29" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="AM29" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AN29" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AO29" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AP29" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AS29" t="n">
         <v>6.6</v>
       </c>
-      <c r="AQ29" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AR29" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AS29" t="n">
-        <v>6.2</v>
-      </c>
       <c r="AT29" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AW29" t="n">
         <v>6</v>
       </c>
-      <c r="AU29" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AV29" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AW29" t="n">
+      <c r="AX29" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY29" t="n">
         <v>5.8</v>
       </c>
-      <c r="AX29" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AY29" t="n">
-        <v>5.7</v>
-      </c>
       <c r="AZ29" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BA29" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BB29" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BC29" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BD29" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BE29" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BF29" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BG29" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BH29" t="n">
         <v>5.2</v>
       </c>
       <c r="BI29" t="n">
-        <v>1.01</v>
+        <v>2.8</v>
       </c>
       <c r="BJ29" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BK29" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BL29" t="n">
         <v>85</v>
       </c>
       <c r="BM29" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BN29" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BO29" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="BP29" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BQ29" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BR29" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BS29" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BT29" t="n">
         <v>5.9</v>
       </c>
       <c r="BU29" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BV29" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BW29" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BX29" t="n">
         <v>24</v>
       </c>
       <c r="BY29" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BZ29" t="n">
         <v>0</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-07-18 16:34:23</t>
+          <t>2026-07-18 18:49:17</t>
         </is>
       </c>
     </row>
@@ -7975,10 +7975,10 @@
         <v>6.2</v>
       </c>
       <c r="H30" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="I30" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="J30" t="n">
         <v>4.3</v>
@@ -7987,13 +7987,13 @@
         <v>4.5</v>
       </c>
       <c r="L30" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="M30" t="n">
         <v>1.05</v>
       </c>
       <c r="N30" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="O30" t="n">
         <v>1.26</v>
@@ -8005,7 +8005,7 @@
         <v>1.76</v>
       </c>
       <c r="R30" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="S30" t="n">
         <v>2.9</v>
@@ -8017,7 +8017,7 @@
         <v>2.12</v>
       </c>
       <c r="V30" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="W30" t="n">
         <v>1.19</v>
@@ -8032,7 +8032,7 @@
         <v>11</v>
       </c>
       <c r="AA30" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AB30" t="n">
         <v>30</v>
@@ -8050,7 +8050,7 @@
         <v>160</v>
       </c>
       <c r="AG30" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="AH30" t="n">
         <v>21</v>
@@ -8059,22 +8059,22 @@
         <v>65</v>
       </c>
       <c r="AJ30" t="n">
-        <v>1000</v>
+        <v>690</v>
       </c>
       <c r="AK30" t="n">
-        <v>1000</v>
+        <v>690</v>
       </c>
       <c r="AL30" t="n">
-        <v>1000</v>
+        <v>690</v>
       </c>
       <c r="AM30" t="n">
-        <v>1000</v>
+        <v>490</v>
       </c>
       <c r="AN30" t="n">
-        <v>1000</v>
+        <v>690</v>
       </c>
       <c r="AO30" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AP30" t="n">
         <v>16</v>
@@ -8083,13 +8083,13 @@
         <v>8.6</v>
       </c>
       <c r="AR30" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AS30" t="n">
         <v>14</v>
       </c>
       <c r="AT30" t="n">
-        <v>18.5</v>
+        <v>15.5</v>
       </c>
       <c r="AU30" t="n">
         <v>8.800000000000001</v>
@@ -8107,7 +8107,7 @@
         <v>20</v>
       </c>
       <c r="AZ30" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BA30" t="n">
         <v>24</v>
@@ -8140,31 +8140,31 @@
         <v>11.5</v>
       </c>
       <c r="BK30" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BL30" t="n">
         <v>130</v>
       </c>
       <c r="BM30" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BN30" t="n">
         <v>10.5</v>
       </c>
       <c r="BO30" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BP30" t="n">
         <v>55</v>
       </c>
       <c r="BQ30" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BR30" t="n">
         <v>55</v>
       </c>
       <c r="BS30" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BT30" t="n">
         <v>4.5</v>
@@ -8176,13 +8176,13 @@
         <v>11.5</v>
       </c>
       <c r="BW30" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BX30" t="n">
         <v>25</v>
       </c>
       <c r="BY30" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BZ30" t="n">
         <v>0</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-07-18 16:34:23</t>
+          <t>2026-07-18 18:49:17</t>
         </is>
       </c>
     </row>
@@ -8322,7 +8322,7 @@
         <v>65</v>
       </c>
       <c r="AM31" t="n">
-        <v>140</v>
+        <v>500</v>
       </c>
       <c r="AN31" t="n">
         <v>40</v>
@@ -8340,7 +8340,7 @@
         <v>13.5</v>
       </c>
       <c r="AS31" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AT31" t="n">
         <v>7.8</v>
@@ -8352,7 +8352,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AW31" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AX31" t="n">
         <v>14.5</v>
@@ -8370,19 +8370,19 @@
         <v>36</v>
       </c>
       <c r="BC31" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BD31" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BE31" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BF31" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BG31" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BH31" t="n">
         <v>3.35</v>
@@ -8394,13 +8394,13 @@
         <v>11.5</v>
       </c>
       <c r="BK31" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BL31" t="n">
         <v>170</v>
       </c>
       <c r="BM31" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BN31" t="n">
         <v>6.6</v>
@@ -8412,31 +8412,31 @@
         <v>28</v>
       </c>
       <c r="BQ31" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BR31" t="n">
         <v>48</v>
       </c>
       <c r="BS31" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BT31" t="n">
         <v>6.4</v>
       </c>
       <c r="BU31" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="BV31" t="n">
         <v>27</v>
       </c>
       <c r="BW31" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BX31" t="n">
         <v>46</v>
       </c>
       <c r="BY31" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BZ31" t="n">
         <v>0</v>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-07-18 16:34:23</t>
+          <t>2026-07-18 18:49:17</t>
         </is>
       </c>
     </row>
@@ -8477,19 +8477,19 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="G32" t="n">
         <v>1000</v>
       </c>
       <c r="H32" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="I32" t="n">
         <v>1000</v>
       </c>
       <c r="J32" t="n">
-        <v>1.16</v>
+        <v>3.1</v>
       </c>
       <c r="K32" t="n">
         <v>1000</v>
@@ -8507,7 +8507,7 @@
         <v>1.37</v>
       </c>
       <c r="P32" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="Q32" t="n">
         <v>1.37</v>
@@ -8516,7 +8516,7 @@
         <v>1.16</v>
       </c>
       <c r="S32" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="T32" t="n">
         <v>1.11</v>
@@ -8525,10 +8525,10 @@
         <v>1.11</v>
       </c>
       <c r="V32" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="W32" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X32" t="n">
         <v>1000</v>
@@ -8642,65 +8642,65 @@
         <v>1000</v>
       </c>
       <c r="BI32" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ32" t="n">
         <v>1000</v>
       </c>
       <c r="BK32" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL32" t="n">
         <v>1000</v>
       </c>
       <c r="BM32" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN32" t="n">
         <v>1000</v>
       </c>
       <c r="BO32" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP32" t="n">
         <v>1000</v>
       </c>
       <c r="BQ32" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR32" t="n">
         <v>1000</v>
       </c>
       <c r="BS32" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT32" t="n">
         <v>1000</v>
       </c>
       <c r="BU32" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV32" t="n">
         <v>1000</v>
       </c>
       <c r="BW32" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX32" t="n">
         <v>1000</v>
       </c>
       <c r="BY32" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ32" t="n">
         <v>1000</v>
       </c>
       <c r="CA32" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-07-18 16:34:23</t>
+          <t>2026-07-18 18:49:17</t>
         </is>
       </c>
     </row>
@@ -8740,7 +8740,7 @@
         <v>1.76</v>
       </c>
       <c r="I33" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="J33" t="n">
         <v>3.5</v>
@@ -8755,28 +8755,28 @@
         <v>1.13</v>
       </c>
       <c r="N33" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="O33" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="P33" t="n">
         <v>1.52</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.68</v>
+        <v>2.74</v>
       </c>
       <c r="R33" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="S33" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="T33" t="n">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="U33" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="V33" t="n">
         <v>2.22</v>
@@ -8785,22 +8785,22 @@
         <v>1.18</v>
       </c>
       <c r="X33" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Y33" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="Z33" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AA33" t="n">
         <v>24</v>
       </c>
       <c r="AB33" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AC33" t="n">
-        <v>8.6</v>
+        <v>11</v>
       </c>
       <c r="AD33" t="n">
         <v>13.5</v>
@@ -8821,19 +8821,19 @@
         <v>80</v>
       </c>
       <c r="AJ33" t="n">
-        <v>290</v>
+        <v>900</v>
       </c>
       <c r="AK33" t="n">
-        <v>170</v>
+        <v>700</v>
       </c>
       <c r="AL33" t="n">
-        <v>190</v>
+        <v>700</v>
       </c>
       <c r="AM33" t="n">
-        <v>360</v>
+        <v>700</v>
       </c>
       <c r="AN33" t="n">
-        <v>340</v>
+        <v>700</v>
       </c>
       <c r="AO33" t="n">
         <v>25</v>
@@ -8863,31 +8863,31 @@
         <v>18.5</v>
       </c>
       <c r="AX33" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="AY33" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="AZ33" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="BA33" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BB33" t="n">
         <v>5</v>
       </c>
-      <c r="BB33" t="n">
-        <v>5.2</v>
-      </c>
       <c r="BC33" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD33" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE33" t="n">
         <v>5.1</v>
       </c>
-      <c r="BD33" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BE33" t="n">
-        <v>5.2</v>
-      </c>
       <c r="BF33" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BG33" t="n">
         <v>18</v>
@@ -8902,7 +8902,7 @@
         <v>15.5</v>
       </c>
       <c r="BK33" t="n">
-        <v>9.4</v>
+        <v>3.95</v>
       </c>
       <c r="BL33" t="n">
         <v>340</v>
@@ -8914,7 +8914,7 @@
         <v>11.5</v>
       </c>
       <c r="BO33" t="n">
-        <v>7</v>
+        <v>3.6</v>
       </c>
       <c r="BP33" t="n">
         <v>90</v>
@@ -8932,13 +8932,13 @@
         <v>4.7</v>
       </c>
       <c r="BU33" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="BV33" t="n">
         <v>17</v>
       </c>
       <c r="BW33" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="BX33" t="n">
         <v>55</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-07-18 16:34:23</t>
+          <t>2026-07-18 18:49:17</t>
         </is>
       </c>
     </row>
@@ -8988,13 +8988,13 @@
         <v>3.5</v>
       </c>
       <c r="G34" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="H34" t="n">
         <v>1.96</v>
       </c>
       <c r="I34" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="J34" t="n">
         <v>3.75</v>
@@ -9033,7 +9033,7 @@
         <v>2.3</v>
       </c>
       <c r="V34" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="W34" t="n">
         <v>1.33</v>
@@ -9048,7 +9048,7 @@
         <v>15</v>
       </c>
       <c r="AA34" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AB34" t="n">
         <v>17.5</v>
@@ -9057,13 +9057,13 @@
         <v>9.4</v>
       </c>
       <c r="AD34" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AE34" t="n">
         <v>21</v>
       </c>
       <c r="AF34" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AG34" t="n">
         <v>16.5</v>
@@ -9075,7 +9075,7 @@
         <v>32</v>
       </c>
       <c r="AJ34" t="n">
-        <v>80</v>
+        <v>900</v>
       </c>
       <c r="AK34" t="n">
         <v>42</v>
@@ -9084,7 +9084,7 @@
         <v>50</v>
       </c>
       <c r="AM34" t="n">
-        <v>75</v>
+        <v>500</v>
       </c>
       <c r="AN34" t="n">
         <v>34</v>
@@ -9099,10 +9099,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AR34" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AS34" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AT34" t="n">
         <v>12.5</v>
@@ -9114,7 +9114,7 @@
         <v>8.4</v>
       </c>
       <c r="AW34" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AX34" t="n">
         <v>20</v>
@@ -9126,22 +9126,22 @@
         <v>12.5</v>
       </c>
       <c r="BA34" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BB34" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BC34" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BD34" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BE34" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BF34" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BG34" t="n">
         <v>9</v>
@@ -9156,31 +9156,31 @@
         <v>9.4</v>
       </c>
       <c r="BK34" t="n">
-        <v>2.54</v>
+        <v>4.5</v>
       </c>
       <c r="BL34" t="n">
         <v>110</v>
       </c>
       <c r="BM34" t="n">
-        <v>3.35</v>
+        <v>8</v>
       </c>
       <c r="BN34" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="BO34" t="n">
-        <v>3.45</v>
+        <v>5.9</v>
       </c>
       <c r="BP34" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BQ34" t="n">
-        <v>3.5</v>
+        <v>6.6</v>
       </c>
       <c r="BR34" t="n">
         <v>34</v>
       </c>
       <c r="BS34" t="n">
-        <v>3.15</v>
+        <v>6.8</v>
       </c>
       <c r="BT34" t="n">
         <v>5.3</v>
@@ -9192,13 +9192,13 @@
         <v>14.5</v>
       </c>
       <c r="BW34" t="n">
-        <v>2.82</v>
+        <v>5.4</v>
       </c>
       <c r="BX34" t="n">
         <v>26</v>
       </c>
       <c r="BY34" t="n">
-        <v>3.05</v>
+        <v>6.4</v>
       </c>
       <c r="BZ34" t="n">
         <v>0</v>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-07-18 16:34:23</t>
+          <t>2026-07-18 18:49:17</t>
         </is>
       </c>
     </row>
@@ -9239,43 +9239,43 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="G35" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="H35" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="I35" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="J35" t="n">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="K35" t="n">
         <v>7.2</v>
       </c>
       <c r="L35" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="M35" t="n">
         <v>1.01</v>
       </c>
       <c r="N35" t="n">
-        <v>2.58</v>
+        <v>2.92</v>
       </c>
       <c r="O35" t="n">
         <v>1.01</v>
       </c>
       <c r="P35" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="Q35" t="n">
         <v>1.13</v>
       </c>
       <c r="R35" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="S35" t="n">
         <v>1.3</v>
@@ -9287,22 +9287,22 @@
         <v>4.5</v>
       </c>
       <c r="V35" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="W35" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="X35" t="n">
-        <v>150</v>
+        <v>500</v>
       </c>
       <c r="Y35" t="n">
-        <v>80</v>
+        <v>500</v>
       </c>
       <c r="Z35" t="n">
-        <v>95</v>
+        <v>500</v>
       </c>
       <c r="AA35" t="n">
-        <v>130</v>
+        <v>500</v>
       </c>
       <c r="AB35" t="n">
         <v>55</v>
@@ -9341,25 +9341,25 @@
         <v>32</v>
       </c>
       <c r="AN35" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="AO35" t="n">
         <v>13</v>
       </c>
       <c r="AP35" t="n">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="AQ35" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="AR35" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="AS35" t="n">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="AT35" t="n">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="AU35" t="n">
         <v>19.5</v>
@@ -9368,10 +9368,10 @@
         <v>21</v>
       </c>
       <c r="AW35" t="n">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="AX35" t="n">
-        <v>5.5</v>
+        <v>6.6</v>
       </c>
       <c r="AY35" t="n">
         <v>13</v>
@@ -9383,7 +9383,7 @@
         <v>21</v>
       </c>
       <c r="BB35" t="n">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="BC35" t="n">
         <v>13.5</v>
@@ -9401,22 +9401,22 @@
         <v>9</v>
       </c>
       <c r="BH35" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BI35" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BJ35" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BK35" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="BL35" t="n">
         <v>36</v>
       </c>
       <c r="BM35" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BN35" t="n">
         <v>8</v>
@@ -9428,31 +9428,31 @@
         <v>12</v>
       </c>
       <c r="BQ35" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BR35" t="n">
         <v>14.5</v>
       </c>
       <c r="BS35" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BT35" t="n">
         <v>13</v>
       </c>
       <c r="BU35" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BV35" t="n">
         <v>30</v>
       </c>
       <c r="BW35" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BX35" t="n">
         <v>23</v>
       </c>
       <c r="BY35" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BZ35" t="n">
         <v>5.9</v>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-07-18 16:34:23</t>
+          <t>2026-07-18 18:49:17</t>
         </is>
       </c>
     </row>
@@ -9493,7 +9493,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="G36" t="n">
         <v>1.72</v>
@@ -9520,7 +9520,7 @@
         <v>3.3</v>
       </c>
       <c r="O36" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="P36" t="n">
         <v>1.79</v>
@@ -9538,13 +9538,13 @@
         <v>1.99</v>
       </c>
       <c r="U36" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="V36" t="n">
         <v>1.15</v>
       </c>
       <c r="W36" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="X36" t="n">
         <v>15.5</v>
@@ -9553,10 +9553,10 @@
         <v>21</v>
       </c>
       <c r="Z36" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AA36" t="n">
-        <v>260</v>
+        <v>700</v>
       </c>
       <c r="AB36" t="n">
         <v>7.6</v>
@@ -9568,7 +9568,7 @@
         <v>28</v>
       </c>
       <c r="AE36" t="n">
-        <v>130</v>
+        <v>700</v>
       </c>
       <c r="AF36" t="n">
         <v>9.6</v>
@@ -9580,7 +9580,7 @@
         <v>26</v>
       </c>
       <c r="AI36" t="n">
-        <v>130</v>
+        <v>700</v>
       </c>
       <c r="AJ36" t="n">
         <v>17</v>
@@ -9592,37 +9592,37 @@
         <v>55</v>
       </c>
       <c r="AM36" t="n">
-        <v>190</v>
+        <v>700</v>
       </c>
       <c r="AN36" t="n">
         <v>12</v>
       </c>
       <c r="AO36" t="n">
-        <v>200</v>
+        <v>700</v>
       </c>
       <c r="AP36" t="n">
         <v>10</v>
       </c>
       <c r="AQ36" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AR36" t="n">
         <v>42</v>
       </c>
       <c r="AS36" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AT36" t="n">
         <v>5.8</v>
       </c>
       <c r="AU36" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AV36" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AW36" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AX36" t="n">
         <v>7</v>
@@ -9634,7 +9634,7 @@
         <v>18.5</v>
       </c>
       <c r="BA36" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BB36" t="n">
         <v>12</v>
@@ -9643,16 +9643,16 @@
         <v>14</v>
       </c>
       <c r="BD36" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BE36" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BF36" t="n">
         <v>8.6</v>
       </c>
       <c r="BG36" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BH36" t="n">
         <v>3.7</v>
@@ -9664,13 +9664,13 @@
         <v>13</v>
       </c>
       <c r="BK36" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BL36" t="n">
         <v>200</v>
       </c>
       <c r="BM36" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BN36" t="n">
         <v>4.5</v>
@@ -9682,41 +9682,41 @@
         <v>12.5</v>
       </c>
       <c r="BQ36" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BR36" t="n">
         <v>34</v>
       </c>
       <c r="BS36" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BT36" t="n">
         <v>11.5</v>
       </c>
       <c r="BU36" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BV36" t="n">
         <v>75</v>
       </c>
       <c r="BW36" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BX36" t="n">
         <v>85</v>
       </c>
       <c r="BY36" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BZ36" t="n">
         <v>27</v>
       </c>
       <c r="CA36" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-07-18 16:34:23</t>
+          <t>2026-07-18 18:49:17</t>
         </is>
       </c>
     </row>
@@ -9759,7 +9759,7 @@
         <v>1000</v>
       </c>
       <c r="J37" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="K37" t="n">
         <v>1000</v>
@@ -9912,65 +9912,65 @@
         <v>1000</v>
       </c>
       <c r="BI37" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ37" t="n">
         <v>1000</v>
       </c>
       <c r="BK37" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL37" t="n">
         <v>1000</v>
       </c>
       <c r="BM37" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN37" t="n">
         <v>1000</v>
       </c>
       <c r="BO37" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP37" t="n">
         <v>1000</v>
       </c>
       <c r="BQ37" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR37" t="n">
         <v>1000</v>
       </c>
       <c r="BS37" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT37" t="n">
         <v>1000</v>
       </c>
       <c r="BU37" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV37" t="n">
         <v>1000</v>
       </c>
       <c r="BW37" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX37" t="n">
         <v>1000</v>
       </c>
       <c r="BY37" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ37" t="n">
         <v>1000</v>
       </c>
       <c r="CA37" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-07-18 16:34:23</t>
+          <t>2026-07-18 18:49:17</t>
         </is>
       </c>
     </row>
@@ -10019,7 +10019,7 @@
         <v>4.3</v>
       </c>
       <c r="L38" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="M38" t="n">
         <v>1.05</v>
@@ -10031,13 +10031,13 @@
         <v>1.25</v>
       </c>
       <c r="P38" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="Q38" t="n">
         <v>1.71</v>
       </c>
       <c r="R38" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S38" t="n">
         <v>2.82</v>
@@ -10058,55 +10058,55 @@
         <v>22</v>
       </c>
       <c r="Y38" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="Z38" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AA38" t="n">
-        <v>80</v>
+        <v>900</v>
       </c>
       <c r="AB38" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AC38" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD38" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="AE38" t="n">
-        <v>55</v>
+        <v>500</v>
       </c>
       <c r="AF38" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AG38" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AH38" t="n">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="AI38" t="n">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="AJ38" t="n">
-        <v>25</v>
+        <v>900</v>
       </c>
       <c r="AK38" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AL38" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AM38" t="n">
-        <v>80</v>
+        <v>500</v>
       </c>
       <c r="AN38" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AO38" t="n">
-        <v>42</v>
+        <v>500</v>
       </c>
       <c r="AP38" t="n">
         <v>14</v>
@@ -10160,7 +10160,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BG38" t="n">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="BH38" t="n">
         <v>4.3</v>
@@ -10172,49 +10172,49 @@
         <v>10.5</v>
       </c>
       <c r="BK38" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="BL38" t="n">
         <v>110</v>
       </c>
       <c r="BM38" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BN38" t="n">
         <v>5.6</v>
       </c>
       <c r="BO38" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="BP38" t="n">
         <v>15.5</v>
       </c>
       <c r="BQ38" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BR38" t="n">
         <v>29</v>
       </c>
       <c r="BS38" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BT38" t="n">
         <v>8.6</v>
       </c>
       <c r="BU38" t="n">
-        <v>5.9</v>
+        <v>3.4</v>
       </c>
       <c r="BV38" t="n">
         <v>36</v>
       </c>
       <c r="BW38" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BX38" t="n">
         <v>44</v>
       </c>
       <c r="BY38" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BZ38" t="n">
         <v>0</v>
@@ -10224,7 +10224,7 @@
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-07-18 16:34:23</t>
+          <t>2026-07-18 18:49:17</t>
         </is>
       </c>
     </row>
@@ -10255,97 +10255,97 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>1.59</v>
+        <v>1.63</v>
       </c>
       <c r="G39" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="H39" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="I39" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="J39" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="K39" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="L39" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="M39" t="n">
         <v>1.07</v>
       </c>
       <c r="N39" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="O39" t="n">
         <v>1.34</v>
       </c>
       <c r="P39" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Q39" t="n">
         <v>1.91</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>1.89</v>
       </c>
       <c r="R39" t="n">
         <v>1.35</v>
       </c>
       <c r="S39" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="T39" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="U39" t="n">
         <v>1.87</v>
       </c>
       <c r="V39" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="W39" t="n">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="X39" t="n">
         <v>15.5</v>
       </c>
       <c r="Y39" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Z39" t="n">
         <v>60</v>
       </c>
       <c r="AA39" t="n">
-        <v>240</v>
+        <v>700</v>
       </c>
       <c r="AB39" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AC39" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD39" t="n">
         <v>34</v>
       </c>
       <c r="AE39" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AF39" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AG39" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AH39" t="n">
         <v>24</v>
       </c>
       <c r="AI39" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AJ39" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AK39" t="n">
         <v>18.5</v>
@@ -10357,7 +10357,7 @@
         <v>170</v>
       </c>
       <c r="AN39" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AO39" t="n">
         <v>170</v>
@@ -10372,7 +10372,7 @@
         <v>40</v>
       </c>
       <c r="AS39" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT39" t="n">
         <v>7</v>
@@ -10396,7 +10396,7 @@
         <v>19</v>
       </c>
       <c r="BA39" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BB39" t="n">
         <v>11.5</v>
@@ -10408,34 +10408,34 @@
         <v>7.4</v>
       </c>
       <c r="BE39" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BF39" t="n">
         <v>7.4</v>
       </c>
       <c r="BG39" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BH39" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="BI39" t="n">
         <v>3.05</v>
       </c>
       <c r="BJ39" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BK39" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BL39" t="n">
         <v>180</v>
       </c>
       <c r="BM39" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BN39" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BO39" t="n">
         <v>3.5</v>
@@ -10444,41 +10444,41 @@
         <v>11</v>
       </c>
       <c r="BQ39" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BR39" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="BS39" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BT39" t="n">
         <v>11</v>
       </c>
       <c r="BU39" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BV39" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="BW39" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BX39" t="n">
         <v>70</v>
       </c>
       <c r="BY39" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BZ39" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="CA39" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-07-18 16:34:23</t>
+          <t>2026-07-18 18:49:17</t>
         </is>
       </c>
     </row>
@@ -10527,7 +10527,7 @@
         <v>5.3</v>
       </c>
       <c r="L40" t="n">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="M40" t="n">
         <v>1.01</v>
@@ -10605,10 +10605,10 @@
         <v>65</v>
       </c>
       <c r="AL40" t="n">
-        <v>55</v>
+        <v>700</v>
       </c>
       <c r="AM40" t="n">
-        <v>70</v>
+        <v>500</v>
       </c>
       <c r="AN40" t="n">
         <v>60</v>
@@ -10617,7 +10617,7 @@
         <v>5.9</v>
       </c>
       <c r="AP40" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AQ40" t="n">
         <v>9.800000000000001</v>
@@ -10629,7 +10629,7 @@
         <v>13.5</v>
       </c>
       <c r="AT40" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="AU40" t="n">
         <v>10</v>
@@ -10641,19 +10641,19 @@
         <v>12.5</v>
       </c>
       <c r="AX40" t="n">
-        <v>42</v>
+        <v>6.2</v>
       </c>
       <c r="AY40" t="n">
         <v>19</v>
       </c>
       <c r="AZ40" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="BA40" t="n">
         <v>18.5</v>
       </c>
       <c r="BB40" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BC40" t="n">
         <v>42</v>
@@ -10662,49 +10662,49 @@
         <v>38</v>
       </c>
       <c r="BE40" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BF40" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BG40" t="n">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="BH40" t="n">
-        <v>4.9</v>
+        <v>5.6</v>
       </c>
       <c r="BI40" t="n">
-        <v>4.2</v>
+        <v>3.65</v>
       </c>
       <c r="BJ40" t="n">
         <v>11</v>
       </c>
       <c r="BK40" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="BL40" t="n">
         <v>95</v>
       </c>
       <c r="BM40" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BN40" t="n">
         <v>11.5</v>
       </c>
       <c r="BO40" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="BP40" t="n">
         <v>46</v>
       </c>
       <c r="BQ40" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BR40" t="n">
         <v>46</v>
       </c>
       <c r="BS40" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BT40" t="n">
         <v>5.5</v>
@@ -10716,23 +10716,23 @@
         <v>12</v>
       </c>
       <c r="BW40" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="BX40" t="n">
         <v>23</v>
       </c>
       <c r="BY40" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BZ40" t="n">
         <v>14.5</v>
       </c>
       <c r="CA40" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-07-18 16:34:23</t>
+          <t>2026-07-18 18:49:17</t>
         </is>
       </c>
     </row>
@@ -10778,7 +10778,7 @@
         <v>3.35</v>
       </c>
       <c r="K41" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L41" t="n">
         <v>1.44</v>
@@ -10805,10 +10805,10 @@
         <v>3.85</v>
       </c>
       <c r="T41" t="n">
-        <v>1.78</v>
+        <v>1.89</v>
       </c>
       <c r="U41" t="n">
-        <v>1.83</v>
+        <v>1.93</v>
       </c>
       <c r="V41" t="n">
         <v>1.26</v>
@@ -10826,7 +10826,7 @@
         <v>38</v>
       </c>
       <c r="AA41" t="n">
-        <v>120</v>
+        <v>900</v>
       </c>
       <c r="AB41" t="n">
         <v>9.4</v>
@@ -10838,7 +10838,7 @@
         <v>21</v>
       </c>
       <c r="AE41" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AF41" t="n">
         <v>14</v>
@@ -10850,7 +10850,7 @@
         <v>24</v>
       </c>
       <c r="AI41" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AJ41" t="n">
         <v>28</v>
@@ -10859,16 +10859,16 @@
         <v>27</v>
       </c>
       <c r="AL41" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AM41" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AN41" t="n">
         <v>20</v>
       </c>
       <c r="AO41" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AP41" t="n">
         <v>9.4</v>
@@ -10877,10 +10877,10 @@
         <v>11</v>
       </c>
       <c r="AR41" t="n">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="AS41" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AT41" t="n">
         <v>6.4</v>
@@ -10892,7 +10892,7 @@
         <v>13.5</v>
       </c>
       <c r="AW41" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AX41" t="n">
         <v>9.199999999999999</v>
@@ -10904,7 +10904,7 @@
         <v>15</v>
       </c>
       <c r="BA41" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BB41" t="n">
         <v>18</v>
@@ -10913,16 +10913,16 @@
         <v>17.5</v>
       </c>
       <c r="BD41" t="n">
-        <v>1.01</v>
+        <v>28</v>
       </c>
       <c r="BE41" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BF41" t="n">
         <v>13</v>
       </c>
       <c r="BG41" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BH41" t="n">
         <v>3.55</v>
@@ -10986,7 +10986,7 @@
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-07-18 16:34:23</t>
+          <t>2026-07-18 18:49:17</t>
         </is>
       </c>
     </row>
@@ -11035,7 +11035,7 @@
         <v>3.2</v>
       </c>
       <c r="L42" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="M42" t="n">
         <v>1.13</v>
@@ -11104,19 +11104,19 @@
         <v>24</v>
       </c>
       <c r="AI42" t="n">
-        <v>75</v>
+        <v>500</v>
       </c>
       <c r="AJ42" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AK42" t="n">
         <v>46</v>
       </c>
       <c r="AL42" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AM42" t="n">
-        <v>220</v>
+        <v>500</v>
       </c>
       <c r="AN42" t="n">
         <v>55</v>
@@ -11240,7 +11240,7 @@
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-07-18 16:34:23</t>
+          <t>2026-07-18 18:49:17</t>
         </is>
       </c>
     </row>
@@ -11325,7 +11325,7 @@
         <v>1.29</v>
       </c>
       <c r="X43" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="Y43" t="n">
         <v>9</v>
@@ -11334,7 +11334,7 @@
         <v>14.5</v>
       </c>
       <c r="AA43" t="n">
-        <v>34</v>
+        <v>900</v>
       </c>
       <c r="AB43" t="n">
         <v>14.5</v>
@@ -11343,7 +11343,7 @@
         <v>8</v>
       </c>
       <c r="AD43" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AE43" t="n">
         <v>32</v>
@@ -11361,19 +11361,19 @@
         <v>55</v>
       </c>
       <c r="AJ43" t="n">
-        <v>110</v>
+        <v>900</v>
       </c>
       <c r="AK43" t="n">
         <v>65</v>
       </c>
       <c r="AL43" t="n">
-        <v>85</v>
+        <v>500</v>
       </c>
       <c r="AM43" t="n">
-        <v>170</v>
+        <v>500</v>
       </c>
       <c r="AN43" t="n">
-        <v>95</v>
+        <v>500</v>
       </c>
       <c r="AO43" t="n">
         <v>27</v>
@@ -11388,7 +11388,7 @@
         <v>10.5</v>
       </c>
       <c r="AS43" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="AT43" t="n">
         <v>10.5</v>
@@ -11400,10 +11400,10 @@
         <v>9.4</v>
       </c>
       <c r="AW43" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="AX43" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="AY43" t="n">
         <v>14.5</v>
@@ -11412,22 +11412,22 @@
         <v>17.5</v>
       </c>
       <c r="BA43" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="BB43" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="BC43" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="BD43" t="n">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="BE43" t="n">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="BF43" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="BG43" t="n">
         <v>17.5</v>
@@ -11442,7 +11442,7 @@
         <v>12</v>
       </c>
       <c r="BK43" t="n">
-        <v>8.199999999999999</v>
+        <v>4.1</v>
       </c>
       <c r="BL43" t="n">
         <v>190</v>
@@ -11494,7 +11494,7 @@
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-07-18 16:34:23</t>
+          <t>2026-07-18 18:49:17</t>
         </is>
       </c>
     </row>
@@ -11528,10 +11528,10 @@
         <v>3.55</v>
       </c>
       <c r="G44" t="n">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="H44" t="n">
-        <v>2.18</v>
+        <v>2.28</v>
       </c>
       <c r="I44" t="n">
         <v>2.38</v>
@@ -11540,10 +11540,10 @@
         <v>3.1</v>
       </c>
       <c r="K44" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L44" t="n">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="M44" t="n">
         <v>1.1</v>
@@ -11555,10 +11555,10 @@
         <v>1.42</v>
       </c>
       <c r="P44" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="Q44" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="R44" t="n">
         <v>1.25</v>
@@ -11570,13 +11570,13 @@
         <v>1.89</v>
       </c>
       <c r="U44" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="V44" t="n">
         <v>1.73</v>
       </c>
       <c r="W44" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="X44" t="n">
         <v>11.5</v>
@@ -11600,49 +11600,49 @@
         <v>12</v>
       </c>
       <c r="AE44" t="n">
-        <v>30</v>
+        <v>500</v>
       </c>
       <c r="AF44" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AG44" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AH44" t="n">
         <v>20</v>
       </c>
       <c r="AI44" t="n">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="AJ44" t="n">
-        <v>80</v>
+        <v>900</v>
       </c>
       <c r="AK44" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AL44" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AM44" t="n">
-        <v>150</v>
+        <v>500</v>
       </c>
       <c r="AN44" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AO44" t="n">
         <v>28</v>
       </c>
       <c r="AP44" t="n">
-        <v>3.5</v>
+        <v>9.4</v>
       </c>
       <c r="AQ44" t="n">
-        <v>3.25</v>
+        <v>7.4</v>
       </c>
       <c r="AR44" t="n">
-        <v>3.8</v>
+        <v>12.5</v>
       </c>
       <c r="AS44" t="n">
-        <v>22</v>
+        <v>7.8</v>
       </c>
       <c r="AT44" t="n">
         <v>9.800000000000001</v>
@@ -11654,7 +11654,7 @@
         <v>10</v>
       </c>
       <c r="AW44" t="n">
-        <v>4.3</v>
+        <v>7.4</v>
       </c>
       <c r="AX44" t="n">
         <v>20</v>
@@ -11666,22 +11666,22 @@
         <v>16.5</v>
       </c>
       <c r="BA44" t="n">
-        <v>4.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB44" t="n">
-        <v>4.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC44" t="n">
-        <v>5.1</v>
+        <v>8.4</v>
       </c>
       <c r="BD44" t="n">
-        <v>5.1</v>
+        <v>8.6</v>
       </c>
       <c r="BE44" t="n">
-        <v>4.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF44" t="n">
-        <v>5.1</v>
+        <v>8.6</v>
       </c>
       <c r="BG44" t="n">
         <v>20</v>
@@ -11696,13 +11696,13 @@
         <v>12</v>
       </c>
       <c r="BK44" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BL44" t="n">
         <v>180</v>
       </c>
       <c r="BM44" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BN44" t="n">
         <v>7.4</v>
@@ -11714,13 +11714,13 @@
         <v>36</v>
       </c>
       <c r="BQ44" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BR44" t="n">
         <v>55</v>
       </c>
       <c r="BS44" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BT44" t="n">
         <v>5.8</v>
@@ -11732,23 +11732,23 @@
         <v>22</v>
       </c>
       <c r="BW44" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BX44" t="n">
         <v>42</v>
       </c>
       <c r="BY44" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BZ44" t="n">
         <v>42</v>
       </c>
       <c r="CA44" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-07-18 16:34:23</t>
+          <t>2026-07-18 18:49:17</t>
         </is>
       </c>
     </row>
@@ -11779,220 +11779,220 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="G45" t="n">
-        <v>2.98</v>
+        <v>2.26</v>
       </c>
       <c r="H45" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="I45" t="n">
-        <v>36</v>
+        <v>4.7</v>
       </c>
       <c r="J45" t="n">
-        <v>2.52</v>
+        <v>3.25</v>
       </c>
       <c r="K45" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="L45" t="n">
         <v>1.37</v>
       </c>
       <c r="M45" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N45" t="n">
-        <v>1.77</v>
+        <v>3.35</v>
       </c>
       <c r="O45" t="n">
         <v>1.3</v>
       </c>
       <c r="P45" t="n">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="Q45" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="R45" t="n">
-        <v>1.07</v>
+        <v>1.31</v>
       </c>
       <c r="S45" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="T45" t="n">
-        <v>1.44</v>
+        <v>1.73</v>
       </c>
       <c r="U45" t="n">
         <v>1.99</v>
       </c>
       <c r="V45" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="W45" t="n">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="X45" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="Y45" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="Z45" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AA45" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AB45" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AC45" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AD45" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AE45" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AF45" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AG45" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH45" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI45" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ45" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AK45" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AL45" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AM45" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN45" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="AO45" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AP45" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AQ45" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AR45" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AS45" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="AT45" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="AU45" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="AV45" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AW45" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AX45" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AY45" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="AZ45" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BA45" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BB45" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BC45" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BD45" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BE45" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BF45" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BG45" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BH45" t="n">
-        <v>1000</v>
+        <v>3.8</v>
       </c>
       <c r="BI45" t="n">
-        <v>1.01</v>
+        <v>2.8</v>
       </c>
       <c r="BJ45" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK45" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BL45" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="BM45" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BN45" t="n">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="BO45" t="n">
-        <v>1.01</v>
+        <v>2.9</v>
       </c>
       <c r="BP45" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="BQ45" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BR45" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BS45" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BT45" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU45" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="BV45" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BW45" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BX45" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BY45" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BZ45" t="n">
         <v>0</v>
@@ -12002,7 +12002,7 @@
       </c>
       <c r="CB45" t="inlineStr">
         <is>
-          <t>2026-07-18 16:34:23</t>
+          <t>2026-07-18 18:49:17</t>
         </is>
       </c>
     </row>
@@ -12033,7 +12033,7 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="G46" t="n">
         <v>1.73</v>
@@ -12051,7 +12051,7 @@
         <v>4.8</v>
       </c>
       <c r="L46" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="M46" t="n">
         <v>1.05</v>
@@ -12060,13 +12060,13 @@
         <v>4.3</v>
       </c>
       <c r="O46" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="P46" t="n">
         <v>2.14</v>
       </c>
       <c r="Q46" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="R46" t="n">
         <v>1.45</v>
@@ -12093,10 +12093,10 @@
         <v>24</v>
       </c>
       <c r="Z46" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AA46" t="n">
-        <v>180</v>
+        <v>700</v>
       </c>
       <c r="AB46" t="n">
         <v>10.5</v>
@@ -12108,7 +12108,7 @@
         <v>24</v>
       </c>
       <c r="AE46" t="n">
-        <v>95</v>
+        <v>700</v>
       </c>
       <c r="AF46" t="n">
         <v>11.5</v>
@@ -12129,28 +12129,28 @@
         <v>17.5</v>
       </c>
       <c r="AL46" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AM46" t="n">
-        <v>120</v>
+        <v>500</v>
       </c>
       <c r="AN46" t="n">
         <v>8.6</v>
       </c>
       <c r="AO46" t="n">
-        <v>100</v>
+        <v>700</v>
       </c>
       <c r="AP46" t="n">
         <v>14</v>
       </c>
       <c r="AQ46" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AR46" t="n">
-        <v>1.01</v>
+        <v>34</v>
       </c>
       <c r="AS46" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AT46" t="n">
         <v>7.2</v>
@@ -12162,19 +12162,19 @@
         <v>16.5</v>
       </c>
       <c r="AW46" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AX46" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AY46" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AZ46" t="n">
         <v>14.5</v>
       </c>
       <c r="BA46" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BB46" t="n">
         <v>11.5</v>
@@ -12183,70 +12183,70 @@
         <v>12</v>
       </c>
       <c r="BD46" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BE46" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BF46" t="n">
         <v>6.2</v>
       </c>
       <c r="BG46" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BH46" t="n">
         <v>4.6</v>
       </c>
       <c r="BI46" t="n">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="BJ46" t="n">
         <v>12</v>
       </c>
       <c r="BK46" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="BL46" t="n">
         <v>140</v>
       </c>
       <c r="BM46" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BN46" t="n">
         <v>5.1</v>
       </c>
       <c r="BO46" t="n">
-        <v>1.01</v>
+        <v>2.44</v>
       </c>
       <c r="BP46" t="n">
         <v>12.5</v>
       </c>
       <c r="BQ46" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="BR46" t="n">
         <v>28</v>
       </c>
       <c r="BS46" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BT46" t="n">
         <v>11.5</v>
       </c>
       <c r="BU46" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="BV46" t="n">
         <v>60</v>
       </c>
       <c r="BW46" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BX46" t="n">
         <v>60</v>
       </c>
       <c r="BY46" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BZ46" t="n">
         <v>0</v>
@@ -12256,7 +12256,7 @@
       </c>
       <c r="CB46" t="inlineStr">
         <is>
-          <t>2026-07-18 16:34:23</t>
+          <t>2026-07-18 18:49:17</t>
         </is>
       </c>
     </row>
@@ -12290,7 +12290,7 @@
         <v>1.94</v>
       </c>
       <c r="G47" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="H47" t="n">
         <v>4.2</v>
@@ -12335,118 +12335,118 @@
         <v>1.88</v>
       </c>
       <c r="V47" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="W47" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="X47" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Y47" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="Z47" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA47" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB47" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AC47" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD47" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AE47" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF47" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AG47" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AH47" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI47" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ47" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK47" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AL47" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM47" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN47" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AO47" t="n">
         <v>1000</v>
       </c>
       <c r="AP47" t="n">
-        <v>1.01</v>
+        <v>2.5</v>
       </c>
       <c r="AQ47" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR47" t="n">
-        <v>1.01</v>
+        <v>2.38</v>
       </c>
       <c r="AS47" t="n">
-        <v>1.01</v>
+        <v>2.5</v>
       </c>
       <c r="AT47" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AU47" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="AV47" t="n">
-        <v>1.01</v>
+        <v>2.3</v>
       </c>
       <c r="AW47" t="n">
-        <v>1.01</v>
+        <v>2.46</v>
       </c>
       <c r="AX47" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AY47" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AZ47" t="n">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="BA47" t="n">
-        <v>1.01</v>
+        <v>2.46</v>
       </c>
       <c r="BB47" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BC47" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BD47" t="n">
-        <v>1.01</v>
+        <v>2.42</v>
       </c>
       <c r="BE47" t="n">
-        <v>1.01</v>
+        <v>2.5</v>
       </c>
       <c r="BF47" t="n">
-        <v>1.01</v>
+        <v>2.3</v>
       </c>
       <c r="BG47" t="n">
-        <v>1.01</v>
+        <v>2.52</v>
       </c>
       <c r="BH47" t="n">
         <v>3.4</v>
@@ -12458,49 +12458,49 @@
         <v>12.5</v>
       </c>
       <c r="BK47" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BL47" t="n">
         <v>190</v>
       </c>
       <c r="BM47" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BN47" t="n">
         <v>5.1</v>
       </c>
       <c r="BO47" t="n">
-        <v>1.01</v>
+        <v>2.76</v>
       </c>
       <c r="BP47" t="n">
         <v>17.5</v>
       </c>
       <c r="BQ47" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BR47" t="n">
         <v>38</v>
       </c>
       <c r="BS47" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BT47" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BU47" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="BV47" t="n">
         <v>50</v>
       </c>
       <c r="BW47" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BX47" t="n">
         <v>65</v>
       </c>
       <c r="BY47" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BZ47" t="n">
         <v>0</v>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="CB47" t="inlineStr">
         <is>
-          <t>2026-07-18 16:34:23</t>
+          <t>2026-07-18 18:49:17</t>
         </is>
       </c>
     </row>
@@ -12541,19 +12541,19 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="G48" t="n">
         <v>1000</v>
       </c>
       <c r="H48" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="I48" t="n">
         <v>1000</v>
       </c>
       <c r="J48" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="K48" t="n">
         <v>1000</v>
@@ -12589,10 +12589,10 @@
         <v>1.11</v>
       </c>
       <c r="V48" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="W48" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X48" t="n">
         <v>1000</v>
@@ -12706,65 +12706,65 @@
         <v>1000</v>
       </c>
       <c r="BI48" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ48" t="n">
         <v>1000</v>
       </c>
       <c r="BK48" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL48" t="n">
         <v>1000</v>
       </c>
       <c r="BM48" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN48" t="n">
         <v>1000</v>
       </c>
       <c r="BO48" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP48" t="n">
         <v>1000</v>
       </c>
       <c r="BQ48" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR48" t="n">
         <v>1000</v>
       </c>
       <c r="BS48" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT48" t="n">
         <v>1000</v>
       </c>
       <c r="BU48" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV48" t="n">
         <v>1000</v>
       </c>
       <c r="BW48" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX48" t="n">
         <v>1000</v>
       </c>
       <c r="BY48" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ48" t="n">
         <v>1000</v>
       </c>
       <c r="CA48" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB48" t="inlineStr">
         <is>
-          <t>2026-07-18 16:34:23</t>
+          <t>2026-07-18 18:49:17</t>
         </is>
       </c>
     </row>
@@ -12795,31 +12795,31 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="G49" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="H49" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="I49" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="J49" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="K49" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="L49" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="M49" t="n">
         <v>1.12</v>
       </c>
       <c r="N49" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="O49" t="n">
         <v>1.5</v>
@@ -12843,34 +12843,34 @@
         <v>1.79</v>
       </c>
       <c r="V49" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="W49" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="X49" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="Y49" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Z49" t="n">
         <v>28</v>
       </c>
       <c r="AA49" t="n">
-        <v>110</v>
+        <v>900</v>
       </c>
       <c r="AB49" t="n">
         <v>7.6</v>
       </c>
       <c r="AC49" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD49" t="n">
         <v>17.5</v>
       </c>
       <c r="AE49" t="n">
-        <v>65</v>
+        <v>500</v>
       </c>
       <c r="AF49" t="n">
         <v>14</v>
@@ -12882,25 +12882,25 @@
         <v>24</v>
       </c>
       <c r="AI49" t="n">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="AJ49" t="n">
-        <v>34</v>
+        <v>900</v>
       </c>
       <c r="AK49" t="n">
-        <v>34</v>
+        <v>500</v>
       </c>
       <c r="AL49" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AM49" t="n">
-        <v>210</v>
+        <v>500</v>
       </c>
       <c r="AN49" t="n">
-        <v>34</v>
+        <v>500</v>
       </c>
       <c r="AO49" t="n">
-        <v>110</v>
+        <v>500</v>
       </c>
       <c r="AP49" t="n">
         <v>7.8</v>
@@ -12909,10 +12909,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AR49" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AS49" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT49" t="n">
         <v>6.4</v>
@@ -12924,7 +12924,7 @@
         <v>14.5</v>
       </c>
       <c r="AW49" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX49" t="n">
         <v>11.5</v>
@@ -12936,25 +12936,25 @@
         <v>19</v>
       </c>
       <c r="BA49" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BB49" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BC49" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BD49" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BE49" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BF49" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BG49" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH49" t="n">
         <v>3.2</v>
@@ -12966,13 +12966,13 @@
         <v>13.5</v>
       </c>
       <c r="BK49" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BL49" t="n">
         <v>240</v>
       </c>
       <c r="BM49" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BN49" t="n">
         <v>5.8</v>
@@ -12984,41 +12984,41 @@
         <v>24</v>
       </c>
       <c r="BQ49" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BR49" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BS49" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BT49" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BU49" t="n">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="BV49" t="n">
         <v>46</v>
       </c>
       <c r="BW49" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BX49" t="n">
         <v>70</v>
       </c>
       <c r="BY49" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BZ49" t="n">
         <v>55</v>
       </c>
       <c r="CA49" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="CB49" t="inlineStr">
         <is>
-          <t>2026-07-18 16:34:23</t>
+          <t>2026-07-18 18:49:17</t>
         </is>
       </c>
     </row>
@@ -13049,22 +13049,22 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>1.86</v>
+        <v>1.94</v>
       </c>
       <c r="G50" t="n">
-        <v>2.48</v>
+        <v>2.34</v>
       </c>
       <c r="H50" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="I50" t="n">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="J50" t="n">
-        <v>2.8</v>
+        <v>2.96</v>
       </c>
       <c r="K50" t="n">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="L50" t="n">
         <v>1.46</v>
@@ -13085,130 +13085,130 @@
         <v>2.18</v>
       </c>
       <c r="R50" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="S50" t="n">
-        <v>3.9</v>
+        <v>3.45</v>
       </c>
       <c r="T50" t="n">
-        <v>1.9</v>
+        <v>1.81</v>
       </c>
       <c r="U50" t="n">
         <v>1.78</v>
       </c>
       <c r="V50" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="W50" t="n">
-        <v>1.68</v>
+        <v>1.74</v>
       </c>
       <c r="X50" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Y50" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Z50" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA50" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB50" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AC50" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AD50" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AE50" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF50" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AG50" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH50" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI50" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ50" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AK50" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AL50" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM50" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN50" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AO50" t="n">
         <v>1000</v>
       </c>
       <c r="AP50" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="AQ50" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="AR50" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AS50" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AT50" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="AU50" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="AV50" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AW50" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AX50" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AY50" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="AZ50" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BA50" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BB50" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BC50" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BD50" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BE50" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BF50" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BG50" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BH50" t="n">
         <v>3.4</v>
@@ -13220,59 +13220,59 @@
         <v>13</v>
       </c>
       <c r="BK50" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BL50" t="n">
         <v>210</v>
       </c>
       <c r="BM50" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BN50" t="n">
         <v>5.5</v>
       </c>
       <c r="BO50" t="n">
-        <v>1.01</v>
+        <v>2.62</v>
       </c>
       <c r="BP50" t="n">
         <v>20</v>
       </c>
       <c r="BQ50" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BR50" t="n">
         <v>44</v>
       </c>
       <c r="BS50" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BT50" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BU50" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="BV50" t="n">
         <v>50</v>
       </c>
       <c r="BW50" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BX50" t="n">
         <v>70</v>
       </c>
       <c r="BY50" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BZ50" t="n">
         <v>44</v>
       </c>
       <c r="CA50" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="CB50" t="inlineStr">
         <is>
-          <t>2026-07-18 16:34:23</t>
+          <t>2026-07-18 18:49:17</t>
         </is>
       </c>
     </row>
@@ -13393,7 +13393,7 @@
         <v>80</v>
       </c>
       <c r="AJ51" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AK51" t="n">
         <v>55</v>
@@ -13402,7 +13402,7 @@
         <v>80</v>
       </c>
       <c r="AM51" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="AN51" t="n">
         <v>60</v>
@@ -13420,7 +13420,7 @@
         <v>14</v>
       </c>
       <c r="AS51" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AT51" t="n">
         <v>6.8</v>
@@ -13432,7 +13432,7 @@
         <v>10.5</v>
       </c>
       <c r="AW51" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AX51" t="n">
         <v>14</v>
@@ -13444,25 +13444,25 @@
         <v>16.5</v>
       </c>
       <c r="BA51" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BB51" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BC51" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BD51" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BE51" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BF51" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BG51" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BH51" t="n">
         <v>3</v>
@@ -13474,13 +13474,13 @@
         <v>12.5</v>
       </c>
       <c r="BK51" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BL51" t="n">
         <v>230</v>
       </c>
       <c r="BM51" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BN51" t="n">
         <v>6.6</v>
@@ -13492,13 +13492,13 @@
         <v>32</v>
       </c>
       <c r="BQ51" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BR51" t="n">
         <v>60</v>
       </c>
       <c r="BS51" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BT51" t="n">
         <v>6.6</v>
@@ -13510,23 +13510,23 @@
         <v>32</v>
       </c>
       <c r="BW51" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BX51" t="n">
         <v>60</v>
       </c>
       <c r="BY51" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BZ51" t="n">
         <v>60</v>
       </c>
       <c r="CA51" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="CB51" t="inlineStr">
         <is>
-          <t>2026-07-18 16:34:23</t>
+          <t>2026-07-18 18:49:17</t>
         </is>
       </c>
     </row>
@@ -13557,31 +13557,31 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="G52" t="n">
-        <v>2.44</v>
+        <v>2.6</v>
       </c>
       <c r="H52" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="I52" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="J52" t="n">
-        <v>2.96</v>
+        <v>2.88</v>
       </c>
       <c r="K52" t="n">
         <v>3.55</v>
       </c>
       <c r="L52" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="M52" t="n">
         <v>1.11</v>
       </c>
       <c r="N52" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="O52" t="n">
         <v>1.46</v>
@@ -13590,7 +13590,7 @@
         <v>1.56</v>
       </c>
       <c r="Q52" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="R52" t="n">
         <v>1.2</v>
@@ -13599,43 +13599,43 @@
         <v>4.7</v>
       </c>
       <c r="T52" t="n">
-        <v>1.99</v>
+        <v>1.94</v>
       </c>
       <c r="U52" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="V52" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="W52" t="n">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="X52" t="n">
         <v>10</v>
       </c>
       <c r="Y52" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="Z52" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="AA52" t="n">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="AB52" t="n">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="AC52" t="n">
         <v>7.8</v>
       </c>
       <c r="AD52" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AE52" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="AF52" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AG52" t="n">
         <v>12.5</v>
@@ -13644,25 +13644,25 @@
         <v>24</v>
       </c>
       <c r="AI52" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="AJ52" t="n">
+        <v>38</v>
+      </c>
+      <c r="AK52" t="n">
         <v>34</v>
       </c>
-      <c r="AK52" t="n">
-        <v>46</v>
-      </c>
       <c r="AL52" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="AM52" t="n">
         <v>200</v>
       </c>
       <c r="AN52" t="n">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="AO52" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="AP52" t="n">
         <v>7</v>
@@ -13671,7 +13671,7 @@
         <v>8</v>
       </c>
       <c r="AR52" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AS52" t="n">
         <v>1.01</v>
@@ -13683,7 +13683,7 @@
         <v>5.5</v>
       </c>
       <c r="AV52" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AW52" t="n">
         <v>1.01</v>
@@ -13692,7 +13692,7 @@
         <v>10</v>
       </c>
       <c r="AY52" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AZ52" t="n">
         <v>15.5</v>
@@ -13701,7 +13701,7 @@
         <v>1.01</v>
       </c>
       <c r="BB52" t="n">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="BC52" t="n">
         <v>1.01</v>
@@ -13713,7 +13713,7 @@
         <v>1.01</v>
       </c>
       <c r="BF52" t="n">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="BG52" t="n">
         <v>1.01</v>
@@ -13722,31 +13722,31 @@
         <v>3.25</v>
       </c>
       <c r="BI52" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="BJ52" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BK52" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="BL52" t="n">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="BM52" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BN52" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BO52" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="BP52" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BQ52" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BR52" t="n">
         <v>48</v>
@@ -13755,19 +13755,19 @@
         <v>4.5</v>
       </c>
       <c r="BT52" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BU52" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="BV52" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="BW52" t="n">
         <v>4.5</v>
       </c>
       <c r="BX52" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="BY52" t="n">
         <v>4.6</v>
@@ -13776,11 +13776,11 @@
         <v>55</v>
       </c>
       <c r="CA52" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="CB52" t="inlineStr">
         <is>
-          <t>2026-07-18 16:34:23</t>
+          <t>2026-07-18 18:49:17</t>
         </is>
       </c>
     </row>
@@ -13817,7 +13817,7 @@
         <v>1.5</v>
       </c>
       <c r="H53" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="I53" t="n">
         <v>10.5</v>
@@ -13865,7 +13865,7 @@
         <v>3</v>
       </c>
       <c r="X53" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Y53" t="n">
         <v>29</v>
@@ -13877,7 +13877,7 @@
         <v>400</v>
       </c>
       <c r="AB53" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC53" t="n">
         <v>12</v>
@@ -13922,13 +13922,13 @@
         <v>15</v>
       </c>
       <c r="AQ53" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AR53" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AS53" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AT53" t="n">
         <v>6.8</v>
@@ -13937,10 +13937,10 @@
         <v>9.4</v>
       </c>
       <c r="AV53" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AW53" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AX53" t="n">
         <v>7.2</v>
@@ -13949,10 +13949,10 @@
         <v>8.6</v>
       </c>
       <c r="AZ53" t="n">
-        <v>5.2</v>
+        <v>19</v>
       </c>
       <c r="BA53" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BB53" t="n">
         <v>10</v>
@@ -13961,16 +13961,16 @@
         <v>13.5</v>
       </c>
       <c r="BD53" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="BE53" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BF53" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="BG53" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BH53" t="n">
         <v>4.4</v>
@@ -13982,13 +13982,13 @@
         <v>14</v>
       </c>
       <c r="BK53" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BL53" t="n">
         <v>200</v>
       </c>
       <c r="BM53" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BN53" t="n">
         <v>4.5</v>
@@ -14000,41 +14000,41 @@
         <v>10.5</v>
       </c>
       <c r="BQ53" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="BR53" t="n">
         <v>32</v>
       </c>
       <c r="BS53" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BT53" t="n">
         <v>14.5</v>
       </c>
       <c r="BU53" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BV53" t="n">
         <v>100</v>
       </c>
       <c r="BW53" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BX53" t="n">
         <v>95</v>
       </c>
       <c r="BY53" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BZ53" t="n">
         <v>19</v>
       </c>
       <c r="CA53" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="CB53" t="inlineStr">
         <is>
-          <t>2026-07-18 16:34:23</t>
+          <t>2026-07-18 18:49:17</t>
         </is>
       </c>
     </row>
@@ -14065,10 +14065,10 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="G54" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="H54" t="n">
         <v>10</v>
@@ -14077,10 +14077,10 @@
         <v>14</v>
       </c>
       <c r="J54" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="K54" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="L54" t="n">
         <v>1.35</v>
@@ -14095,10 +14095,10 @@
         <v>1.27</v>
       </c>
       <c r="P54" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="Q54" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="R54" t="n">
         <v>1.39</v>
@@ -14113,10 +14113,10 @@
         <v>1.72</v>
       </c>
       <c r="V54" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="W54" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="X54" t="n">
         <v>20</v>
@@ -14131,7 +14131,7 @@
         <v>530</v>
       </c>
       <c r="AB54" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="AC54" t="n">
         <v>13.5</v>
@@ -14149,7 +14149,7 @@
         <v>12</v>
       </c>
       <c r="AH54" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AI54" t="n">
         <v>190</v>
@@ -14176,13 +14176,13 @@
         <v>15</v>
       </c>
       <c r="AQ54" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="AR54" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="AS54" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="AT54" t="n">
         <v>6.6</v>
@@ -14191,10 +14191,10 @@
         <v>10</v>
       </c>
       <c r="AV54" t="n">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="AW54" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="AX54" t="n">
         <v>6.8</v>
@@ -14203,10 +14203,10 @@
         <v>9</v>
       </c>
       <c r="AZ54" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="BA54" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="BB54" t="n">
         <v>9.6</v>
@@ -14215,80 +14215,80 @@
         <v>13.5</v>
       </c>
       <c r="BD54" t="n">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="BE54" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="BF54" t="n">
         <v>5.3</v>
       </c>
       <c r="BG54" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BH54" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BI54" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="BJ54" t="n">
         <v>14.5</v>
       </c>
       <c r="BK54" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BL54" t="n">
         <v>220</v>
       </c>
       <c r="BM54" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BN54" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BO54" t="n">
         <v>3</v>
       </c>
       <c r="BP54" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BQ54" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="BR54" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BS54" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BT54" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BU54" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BV54" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="BW54" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BX54" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="BY54" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BZ54" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="CA54" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="CB54" t="inlineStr">
         <is>
-          <t>2026-07-18 16:34:23</t>
+          <t>2026-07-18 18:49:17</t>
         </is>
       </c>
     </row>
@@ -14325,13 +14325,13 @@
         <v>1.5</v>
       </c>
       <c r="H55" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="I55" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="J55" t="n">
-        <v>1.1</v>
+        <v>4.6</v>
       </c>
       <c r="K55" t="n">
         <v>6.8</v>
@@ -14343,7 +14343,7 @@
         <v>1.01</v>
       </c>
       <c r="N55" t="n">
-        <v>5.7</v>
+        <v>1.1</v>
       </c>
       <c r="O55" t="n">
         <v>1.14</v>
@@ -14367,10 +14367,10 @@
         <v>2.2</v>
       </c>
       <c r="V55" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="W55" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="X55" t="n">
         <v>40</v>
@@ -14400,19 +14400,19 @@
         <v>13.5</v>
       </c>
       <c r="AG55" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH55" t="n">
         <v>24</v>
       </c>
       <c r="AI55" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AJ55" t="n">
         <v>16</v>
       </c>
       <c r="AK55" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AL55" t="n">
         <v>32</v>
@@ -14427,112 +14427,112 @@
         <v>85</v>
       </c>
       <c r="AP55" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AQ55" t="n">
+        <v>5</v>
+      </c>
+      <c r="AR55" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AS55" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AT55" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AU55" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AV55" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AW55" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AX55" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY55" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AZ55" t="n">
         <v>4.6</v>
       </c>
-      <c r="AQ55" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AR55" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AS55" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AT55" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AU55" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AV55" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AW55" t="n">
-        <v>5</v>
-      </c>
-      <c r="AX55" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AY55" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AZ55" t="n">
-        <v>4.3</v>
-      </c>
       <c r="BA55" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BB55" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="BC55" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BD55" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="BE55" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="BF55" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="BG55" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="BH55" t="n">
         <v>5.7</v>
       </c>
       <c r="BI55" t="n">
-        <v>1.01</v>
+        <v>2.9</v>
       </c>
       <c r="BJ55" t="n">
         <v>11.5</v>
       </c>
       <c r="BK55" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BL55" t="n">
         <v>100</v>
       </c>
       <c r="BM55" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BN55" t="n">
         <v>5</v>
       </c>
       <c r="BO55" t="n">
-        <v>1.01</v>
+        <v>2.72</v>
       </c>
       <c r="BP55" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BQ55" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="BR55" t="n">
         <v>21</v>
       </c>
       <c r="BS55" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BT55" t="n">
         <v>13</v>
       </c>
       <c r="BU55" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BV55" t="n">
         <v>60</v>
       </c>
       <c r="BW55" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BX55" t="n">
         <v>55</v>
       </c>
       <c r="BY55" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BZ55" t="n">
         <v>0</v>
@@ -14542,7 +14542,7 @@
       </c>
       <c r="CB55" t="inlineStr">
         <is>
-          <t>2026-07-18 16:34:23</t>
+          <t>2026-07-18 18:49:17</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-19.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-19.xlsx
@@ -857,19 +857,19 @@
         </is>
       </c>
       <c r="F2" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="G2" t="n">
         <v>3.7</v>
       </c>
-      <c r="G2" t="n">
-        <v>3.85</v>
-      </c>
       <c r="H2" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="I2" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="J2" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K2" t="n">
         <v>3.8</v>
@@ -881,115 +881,115 @@
         <v>1.07</v>
       </c>
       <c r="N2" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="O2" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="P2" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.99</v>
+        <v>1.89</v>
       </c>
       <c r="R2" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="S2" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="T2" t="n">
-        <v>1.77</v>
+        <v>1.72</v>
       </c>
       <c r="U2" t="n">
-        <v>2.12</v>
+        <v>2.28</v>
       </c>
       <c r="V2" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="W2" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="X2" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Z2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA2" t="n">
         <v>28</v>
       </c>
       <c r="AB2" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AC2" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD2" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AF2" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AG2" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH2" t="n">
         <v>16.5</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>18</v>
       </c>
       <c r="AI2" t="n">
         <v>36</v>
       </c>
       <c r="AJ2" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AK2" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AL2" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="AM2" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AN2" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="AO2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AP2" t="n">
+        <v>14</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>27</v>
+      </c>
+      <c r="AT2" t="n">
         <v>13</v>
       </c>
-      <c r="AQ2" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>11</v>
-      </c>
-      <c r="AS2" t="n">
+      <c r="AU2" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AW2" t="n">
         <v>21</v>
       </c>
-      <c r="AT2" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>18.5</v>
-      </c>
       <c r="AX2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AY2" t="n">
         <v>13.5</v>
@@ -1001,22 +1001,22 @@
         <v>30</v>
       </c>
       <c r="BB2" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BC2" t="n">
         <v>36</v>
       </c>
       <c r="BD2" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="BE2" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="BF2" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BG2" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BH2" t="n">
         <v>4.1</v>
@@ -1040,7 +1040,7 @@
         <v>7.2</v>
       </c>
       <c r="BO2" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BP2" t="n">
         <v>32</v>
@@ -1058,7 +1058,7 @@
         <v>5.1</v>
       </c>
       <c r="BU2" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BV2" t="n">
         <v>16</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-18 18:49:17</t>
+          <t>2026-07-18 21:03:51</t>
         </is>
       </c>
     </row>
@@ -1111,10 +1111,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="G3" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="H3" t="n">
         <v>6.4</v>
@@ -1123,7 +1123,7 @@
         <v>6.8</v>
       </c>
       <c r="J3" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="K3" t="n">
         <v>4</v>
@@ -1135,16 +1135,16 @@
         <v>1.09</v>
       </c>
       <c r="N3" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="O3" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="P3" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="R3" t="n">
         <v>1.28</v>
@@ -1153,22 +1153,22 @@
         <v>4.2</v>
       </c>
       <c r="T3" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="U3" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="V3" t="n">
         <v>1.17</v>
       </c>
       <c r="W3" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="X3" t="n">
         <v>12</v>
       </c>
       <c r="Y3" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="Z3" t="n">
         <v>60</v>
@@ -1189,7 +1189,7 @@
         <v>460</v>
       </c>
       <c r="AF3" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AG3" t="n">
         <v>10.5</v>
@@ -1225,22 +1225,22 @@
         <v>15.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="AS3" t="n">
         <v>46</v>
       </c>
       <c r="AT3" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AU3" t="n">
         <v>8</v>
       </c>
       <c r="AV3" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AW3" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AX3" t="n">
         <v>8</v>
@@ -1264,7 +1264,7 @@
         <v>38</v>
       </c>
       <c r="BE3" t="n">
-        <v>95</v>
+        <v>70</v>
       </c>
       <c r="BF3" t="n">
         <v>11</v>
@@ -1282,13 +1282,13 @@
         <v>12.5</v>
       </c>
       <c r="BK3" t="n">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="BL3" t="n">
         <v>240</v>
       </c>
       <c r="BM3" t="n">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BN3" t="n">
         <v>4.7</v>
@@ -1300,41 +1300,41 @@
         <v>12.5</v>
       </c>
       <c r="BQ3" t="n">
-        <v>8.800000000000001</v>
+        <v>4.2</v>
       </c>
       <c r="BR3" t="n">
         <v>34</v>
       </c>
       <c r="BS3" t="n">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="BT3" t="n">
         <v>10.5</v>
       </c>
       <c r="BU3" t="n">
-        <v>1.04</v>
+        <v>3.95</v>
       </c>
       <c r="BV3" t="n">
         <v>85</v>
       </c>
       <c r="BW3" t="n">
-        <v>1.04</v>
+        <v>5.8</v>
       </c>
       <c r="BX3" t="n">
         <v>95</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.04</v>
+        <v>5.9</v>
       </c>
       <c r="BZ3" t="n">
         <v>28</v>
       </c>
       <c r="CA3" t="n">
-        <v>1.04</v>
+        <v>5.1</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-18 18:49:17</t>
+          <t>2026-07-18 21:03:51</t>
         </is>
       </c>
     </row>
@@ -1368,28 +1368,28 @@
         <v>5.5</v>
       </c>
       <c r="G4" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="H4" t="n">
         <v>1.78</v>
       </c>
       <c r="I4" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="J4" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K4" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L4" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="M4" t="n">
         <v>1.09</v>
       </c>
       <c r="N4" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="O4" t="n">
         <v>1.43</v>
@@ -1410,7 +1410,7 @@
         <v>2.1</v>
       </c>
       <c r="U4" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="V4" t="n">
         <v>2.2</v>
@@ -1443,13 +1443,13 @@
         <v>22</v>
       </c>
       <c r="AF4" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AG4" t="n">
         <v>25</v>
       </c>
       <c r="AH4" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AI4" t="n">
         <v>48</v>
@@ -1467,7 +1467,7 @@
         <v>200</v>
       </c>
       <c r="AN4" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AO4" t="n">
         <v>15.5</v>
@@ -1488,7 +1488,7 @@
         <v>13</v>
       </c>
       <c r="AU4" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV4" t="n">
         <v>9.199999999999999</v>
@@ -1497,7 +1497,7 @@
         <v>19.5</v>
       </c>
       <c r="AX4" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="AY4" t="n">
         <v>19</v>
@@ -1506,22 +1506,22 @@
         <v>20</v>
       </c>
       <c r="BA4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BB4" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BC4" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BD4" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BE4" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BF4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BG4" t="n">
         <v>13.5</v>
@@ -1536,59 +1536,59 @@
         <v>13</v>
       </c>
       <c r="BK4" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="BL4" t="n">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="BM4" t="n">
-        <v>6</v>
+        <v>7.8</v>
       </c>
       <c r="BN4" t="n">
         <v>10.5</v>
       </c>
       <c r="BO4" t="n">
-        <v>3.95</v>
+        <v>4.6</v>
       </c>
       <c r="BP4" t="n">
         <v>60</v>
       </c>
       <c r="BQ4" t="n">
-        <v>5.7</v>
+        <v>7.2</v>
       </c>
       <c r="BR4" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="BS4" t="n">
-        <v>5.8</v>
+        <v>7.4</v>
       </c>
       <c r="BT4" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="BU4" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="BV4" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BW4" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="BX4" t="n">
         <v>34</v>
       </c>
       <c r="BY4" t="n">
-        <v>5.3</v>
+        <v>6.6</v>
       </c>
       <c r="BZ4" t="n">
         <v>30</v>
       </c>
       <c r="CA4" t="n">
-        <v>5.2</v>
+        <v>6.4</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-18 18:49:17</t>
+          <t>2026-07-18 21:03:51</t>
         </is>
       </c>
     </row>
@@ -1625,10 +1625,10 @@
         <v>1.86</v>
       </c>
       <c r="H5" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="I5" t="n">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="J5" t="n">
         <v>3.85</v>
@@ -1637,37 +1637,37 @@
         <v>4.1</v>
       </c>
       <c r="L5" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="M5" t="n">
         <v>1.07</v>
       </c>
       <c r="N5" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="O5" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="P5" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="Q5" t="n">
         <v>1.92</v>
       </c>
-      <c r="Q5" t="n">
-        <v>1.94</v>
-      </c>
       <c r="R5" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="S5" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="T5" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="U5" t="n">
-        <v>1.98</v>
+        <v>1.9</v>
       </c>
       <c r="V5" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="W5" t="n">
         <v>2.16</v>
@@ -1679,19 +1679,19 @@
         <v>18</v>
       </c>
       <c r="Z5" t="n">
-        <v>100</v>
+        <v>48</v>
       </c>
       <c r="AA5" t="n">
         <v>700</v>
       </c>
       <c r="AB5" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC5" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AD5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE5" t="n">
         <v>400</v>
@@ -1703,10 +1703,10 @@
         <v>11</v>
       </c>
       <c r="AH5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI5" t="n">
-        <v>700</v>
+        <v>320</v>
       </c>
       <c r="AJ5" t="n">
         <v>20</v>
@@ -1715,13 +1715,13 @@
         <v>20</v>
       </c>
       <c r="AL5" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AM5" t="n">
         <v>580</v>
       </c>
       <c r="AN5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AO5" t="n">
         <v>700</v>
@@ -1730,70 +1730,70 @@
         <v>11</v>
       </c>
       <c r="AQ5" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AR5" t="n">
-        <v>6.8</v>
+        <v>29</v>
       </c>
       <c r="AS5" t="n">
-        <v>7.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT5" t="n">
         <v>6.8</v>
       </c>
       <c r="AU5" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="AV5" t="n">
         <v>15</v>
       </c>
       <c r="AW5" t="n">
-        <v>7.4</v>
+        <v>44</v>
       </c>
       <c r="AX5" t="n">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="AY5" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="AZ5" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BA5" t="n">
-        <v>7.4</v>
+        <v>44</v>
       </c>
       <c r="BB5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BC5" t="n">
         <v>15</v>
       </c>
       <c r="BD5" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="BE5" t="n">
-        <v>7.6</v>
+        <v>20</v>
       </c>
       <c r="BF5" t="n">
         <v>9.6</v>
       </c>
       <c r="BG5" t="n">
-        <v>7.4</v>
+        <v>44</v>
       </c>
       <c r="BH5" t="n">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.82</v>
+        <v>2.9</v>
       </c>
       <c r="BJ5" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BK5" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BL5" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="BM5" t="n">
         <v>5.6</v>
@@ -1802,13 +1802,13 @@
         <v>5</v>
       </c>
       <c r="BO5" t="n">
-        <v>3.55</v>
+        <v>3.85</v>
       </c>
       <c r="BP5" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BQ5" t="n">
-        <v>9.800000000000001</v>
+        <v>4.1</v>
       </c>
       <c r="BR5" t="n">
         <v>32</v>
@@ -1817,13 +1817,13 @@
         <v>4.9</v>
       </c>
       <c r="BT5" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BU5" t="n">
         <v>3.65</v>
       </c>
       <c r="BV5" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BW5" t="n">
         <v>5.2</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-18 18:49:17</t>
+          <t>2026-07-18 21:03:51</t>
         </is>
       </c>
     </row>
@@ -1873,13 +1873,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="G6" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="H6" t="n">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
       <c r="I6" t="n">
         <v>2.82</v>
@@ -1891,7 +1891,7 @@
         <v>3.7</v>
       </c>
       <c r="L6" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="M6" t="n">
         <v>1.07</v>
@@ -1903,19 +1903,19 @@
         <v>1.33</v>
       </c>
       <c r="P6" t="n">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="R6" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="S6" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="T6" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="U6" t="n">
         <v>2.16</v>
@@ -1927,7 +1927,7 @@
         <v>1.5</v>
       </c>
       <c r="X6" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="Y6" t="n">
         <v>11.5</v>
@@ -1948,61 +1948,61 @@
         <v>12.5</v>
       </c>
       <c r="AE6" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AF6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AG6" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH6" t="n">
         <v>17.5</v>
       </c>
       <c r="AI6" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="AJ6" t="n">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="AK6" t="n">
         <v>34</v>
       </c>
       <c r="AL6" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AM6" t="n">
         <v>110</v>
       </c>
       <c r="AN6" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AO6" t="n">
         <v>26</v>
       </c>
       <c r="AP6" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AQ6" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="AR6" t="n">
         <v>13.5</v>
       </c>
       <c r="AS6" t="n">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="AT6" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU6" t="n">
         <v>6.8</v>
       </c>
       <c r="AV6" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>7.6</v>
+        <v>21</v>
       </c>
       <c r="AX6" t="n">
         <v>15</v>
@@ -2011,25 +2011,25 @@
         <v>10</v>
       </c>
       <c r="AZ6" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="BB6" t="n">
-        <v>8.199999999999999</v>
+        <v>34</v>
       </c>
       <c r="BC6" t="n">
-        <v>7.6</v>
+        <v>23</v>
       </c>
       <c r="BD6" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="BE6" t="n">
-        <v>9</v>
+        <v>60</v>
       </c>
       <c r="BF6" t="n">
-        <v>7.6</v>
+        <v>19</v>
       </c>
       <c r="BG6" t="n">
         <v>19</v>
@@ -2038,19 +2038,19 @@
         <v>3.75</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="BJ6" t="n">
         <v>11</v>
       </c>
       <c r="BK6" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="BL6" t="n">
         <v>140</v>
       </c>
       <c r="BM6" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BN6" t="n">
         <v>6.8</v>
@@ -2062,13 +2062,13 @@
         <v>26</v>
       </c>
       <c r="BQ6" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BR6" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BS6" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BT6" t="n">
         <v>6.4</v>
@@ -2080,13 +2080,13 @@
         <v>24</v>
       </c>
       <c r="BW6" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BX6" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BY6" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BZ6" t="n">
         <v>0</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-18 18:49:17</t>
+          <t>2026-07-18 21:03:51</t>
         </is>
       </c>
     </row>
@@ -2127,58 +2127,58 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.96</v>
+        <v>3.1</v>
       </c>
       <c r="G7" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="H7" t="n">
         <v>2.44</v>
       </c>
       <c r="I7" t="n">
-        <v>2.68</v>
+        <v>2.62</v>
       </c>
       <c r="J7" t="n">
         <v>3.3</v>
       </c>
       <c r="K7" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N7" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S7" t="n">
         <v>3.65</v>
       </c>
-      <c r="L7" t="n">
+      <c r="T7" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="W7" t="n">
         <v>1.42</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N7" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="O7" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="P7" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>2</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S7" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="U7" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.43</v>
       </c>
       <c r="X7" t="n">
         <v>16</v>
@@ -2187,13 +2187,13 @@
         <v>12.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AA7" t="n">
         <v>46</v>
       </c>
       <c r="AB7" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AC7" t="n">
         <v>8</v>
@@ -2208,7 +2208,7 @@
         <v>26</v>
       </c>
       <c r="AG7" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AH7" t="n">
         <v>21</v>
@@ -2217,7 +2217,7 @@
         <v>55</v>
       </c>
       <c r="AJ7" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AK7" t="n">
         <v>44</v>
@@ -2232,28 +2232,28 @@
         <v>44</v>
       </c>
       <c r="AO7" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AP7" t="n">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="AQ7" t="n">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="AR7" t="n">
         <v>12</v>
       </c>
       <c r="AS7" t="n">
-        <v>4.3</v>
+        <v>25</v>
       </c>
       <c r="AT7" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AU7" t="n">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="AV7" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AW7" t="n">
         <v>20</v>
@@ -2265,25 +2265,25 @@
         <v>10</v>
       </c>
       <c r="AZ7" t="n">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="BA7" t="n">
-        <v>4.4</v>
+        <v>29</v>
       </c>
       <c r="BB7" t="n">
-        <v>4.4</v>
+        <v>36</v>
       </c>
       <c r="BC7" t="n">
-        <v>4.3</v>
+        <v>25</v>
       </c>
       <c r="BD7" t="n">
-        <v>4.4</v>
+        <v>32</v>
       </c>
       <c r="BE7" t="n">
-        <v>4.6</v>
+        <v>65</v>
       </c>
       <c r="BF7" t="n">
-        <v>4.3</v>
+        <v>23</v>
       </c>
       <c r="BG7" t="n">
         <v>17.5</v>
@@ -2292,19 +2292,19 @@
         <v>3.8</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="BJ7" t="n">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="BK7" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="BL7" t="n">
         <v>150</v>
       </c>
       <c r="BM7" t="n">
-        <v>5.5</v>
+        <v>4.7</v>
       </c>
       <c r="BN7" t="n">
         <v>7.4</v>
@@ -2313,16 +2313,16 @@
         <v>4.7</v>
       </c>
       <c r="BP7" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="BR7" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="BS7" t="n">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="BT7" t="n">
         <v>6.4</v>
@@ -2334,13 +2334,13 @@
         <v>24</v>
       </c>
       <c r="BW7" t="n">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="BX7" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="BY7" t="n">
-        <v>4.9</v>
+        <v>4.3</v>
       </c>
       <c r="BZ7" t="n">
         <v>0</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-18 18:49:17</t>
+          <t>2026-07-18 21:03:51</t>
         </is>
       </c>
     </row>
@@ -2381,19 +2381,19 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="G8" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="H8" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="I8" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J8" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="K8" t="n">
         <v>5.6</v>
@@ -2405,34 +2405,34 @@
         <v>1.05</v>
       </c>
       <c r="N8" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="O8" t="n">
         <v>1.24</v>
       </c>
       <c r="P8" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="Q8" t="n">
         <v>1.71</v>
       </c>
       <c r="R8" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="S8" t="n">
         <v>2.86</v>
       </c>
       <c r="T8" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="U8" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="V8" t="n">
         <v>1.11</v>
       </c>
       <c r="W8" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="X8" t="n">
         <v>21</v>
@@ -2456,7 +2456,7 @@
         <v>34</v>
       </c>
       <c r="AE8" t="n">
-        <v>170</v>
+        <v>200</v>
       </c>
       <c r="AF8" t="n">
         <v>9</v>
@@ -2471,7 +2471,7 @@
         <v>470</v>
       </c>
       <c r="AJ8" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AK8" t="n">
         <v>16</v>
@@ -2486,55 +2486,55 @@
         <v>6.8</v>
       </c>
       <c r="AO8" t="n">
-        <v>220</v>
+        <v>240</v>
       </c>
       <c r="AP8" t="n">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="AQ8" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AR8" t="n">
-        <v>7.4</v>
+        <v>50</v>
       </c>
       <c r="AS8" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT8" t="n">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="AU8" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>23</v>
+      </c>
+      <c r="AW8" t="n">
         <v>8.6</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>7.8</v>
       </c>
       <c r="AX8" t="n">
         <v>7.4</v>
       </c>
       <c r="AY8" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ8" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BA8" t="n">
-        <v>7.8</v>
+        <v>29</v>
       </c>
       <c r="BB8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BC8" t="n">
         <v>11</v>
       </c>
       <c r="BD8" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="BE8" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BF8" t="n">
         <v>5.6</v>
@@ -2552,7 +2552,7 @@
         <v>14</v>
       </c>
       <c r="BK8" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="BL8" t="n">
         <v>180</v>
@@ -2573,7 +2573,7 @@
         <v>3.25</v>
       </c>
       <c r="BR8" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BS8" t="n">
         <v>4</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-18 18:49:17</t>
+          <t>2026-07-18 21:03:51</t>
         </is>
       </c>
     </row>
@@ -2635,103 +2635,103 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.34</v>
+        <v>2.08</v>
       </c>
       <c r="G9" t="n">
-        <v>2.88</v>
+        <v>2.46</v>
       </c>
       <c r="H9" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="I9" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="J9" t="n">
-        <v>2.64</v>
+        <v>2.76</v>
       </c>
       <c r="K9" t="n">
         <v>3.3</v>
       </c>
       <c r="L9" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="M9" t="n">
         <v>1.13</v>
       </c>
       <c r="N9" t="n">
-        <v>2.24</v>
+        <v>2.32</v>
       </c>
       <c r="O9" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="P9" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.72</v>
+        <v>2.66</v>
       </c>
       <c r="R9" t="n">
         <v>1.18</v>
       </c>
       <c r="S9" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="T9" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="U9" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="V9" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="W9" t="n">
-        <v>1.53</v>
+        <v>1.68</v>
       </c>
       <c r="X9" t="n">
-        <v>9.6</v>
+        <v>8.6</v>
       </c>
       <c r="Y9" t="n">
         <v>13</v>
       </c>
       <c r="Z9" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="AA9" t="n">
         <v>900</v>
       </c>
       <c r="AB9" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AC9" t="n">
         <v>8</v>
       </c>
-      <c r="AC9" t="n">
-        <v>8.6</v>
-      </c>
       <c r="AD9" t="n">
-        <v>18.5</v>
+        <v>23</v>
       </c>
       <c r="AE9" t="n">
-        <v>160</v>
+        <v>500</v>
       </c>
       <c r="AF9" t="n">
-        <v>16.5</v>
+        <v>13.5</v>
       </c>
       <c r="AG9" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AI9" t="n">
-        <v>540</v>
+        <v>500</v>
       </c>
       <c r="AJ9" t="n">
-        <v>110</v>
+        <v>36</v>
       </c>
       <c r="AK9" t="n">
-        <v>100</v>
+        <v>38</v>
       </c>
       <c r="AL9" t="n">
-        <v>85</v>
+        <v>190</v>
       </c>
       <c r="AM9" t="n">
         <v>500</v>
@@ -2740,125 +2740,125 @@
         <v>75</v>
       </c>
       <c r="AO9" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP9" t="n">
-        <v>3.85</v>
+        <v>6.4</v>
       </c>
       <c r="AQ9" t="n">
+        <v>8</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>6</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>15</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>16</v>
+      </c>
+      <c r="BD9" t="n">
         <v>5.8</v>
       </c>
-      <c r="AR9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>4.6</v>
-      </c>
       <c r="BE9" t="n">
-        <v>4.8</v>
+        <v>6.2</v>
       </c>
       <c r="BF9" t="n">
-        <v>4.5</v>
+        <v>6.2</v>
       </c>
       <c r="BG9" t="n">
-        <v>4.7</v>
+        <v>6</v>
       </c>
       <c r="BH9" t="n">
-        <v>2.9</v>
+        <v>2.98</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="BJ9" t="n">
         <v>14.5</v>
       </c>
       <c r="BK9" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="BL9" t="n">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="BM9" t="n">
         <v>5</v>
       </c>
       <c r="BN9" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="BO9" t="n">
-        <v>3.9</v>
+        <v>3.65</v>
       </c>
       <c r="BP9" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BR9" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="BS9" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BT9" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU9" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="BV9" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="BW9" t="n">
         <v>4.6</v>
       </c>
       <c r="BX9" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="BY9" t="n">
         <v>4.8</v>
       </c>
       <c r="BZ9" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="CA9" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-18 18:49:17</t>
+          <t>2026-07-18 21:03:51</t>
         </is>
       </c>
     </row>
@@ -2895,7 +2895,7 @@
         <v>3.4</v>
       </c>
       <c r="H10" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="I10" t="n">
         <v>3.15</v>
@@ -2922,7 +2922,7 @@
         <v>1.52</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="R10" t="n">
         <v>1.19</v>
@@ -2952,7 +2952,7 @@
         <v>19</v>
       </c>
       <c r="AA10" t="n">
-        <v>55</v>
+        <v>220</v>
       </c>
       <c r="AB10" t="n">
         <v>9.800000000000001</v>
@@ -2979,22 +2979,22 @@
         <v>500</v>
       </c>
       <c r="AJ10" t="n">
-        <v>65</v>
+        <v>220</v>
       </c>
       <c r="AK10" t="n">
-        <v>50</v>
+        <v>290</v>
       </c>
       <c r="AL10" t="n">
-        <v>160</v>
+        <v>500</v>
       </c>
       <c r="AM10" t="n">
         <v>500</v>
       </c>
       <c r="AN10" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AO10" t="n">
-        <v>390</v>
+        <v>600</v>
       </c>
       <c r="AP10" t="n">
         <v>4.3</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-18 18:49:17</t>
+          <t>2026-07-18 21:03:51</t>
         </is>
       </c>
     </row>
@@ -3143,19 +3143,19 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="G11" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="H11" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="I11" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="J11" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="K11" t="n">
         <v>5</v>
@@ -3173,7 +3173,7 @@
         <v>1.17</v>
       </c>
       <c r="P11" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="Q11" t="n">
         <v>1.51</v>
@@ -3185,22 +3185,22 @@
         <v>2.26</v>
       </c>
       <c r="T11" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="U11" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="V11" t="n">
         <v>1.2</v>
       </c>
       <c r="W11" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="X11" t="n">
         <v>500</v>
       </c>
       <c r="Y11" t="n">
-        <v>950</v>
+        <v>500</v>
       </c>
       <c r="Z11" t="n">
         <v>500</v>
@@ -3224,13 +3224,13 @@
         <v>14</v>
       </c>
       <c r="AG11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AH11" t="n">
         <v>25</v>
       </c>
       <c r="AI11" t="n">
-        <v>700</v>
+        <v>120</v>
       </c>
       <c r="AJ11" t="n">
         <v>16.5</v>
@@ -3254,13 +3254,13 @@
         <v>21</v>
       </c>
       <c r="AQ11" t="n">
-        <v>14.5</v>
+        <v>28</v>
       </c>
       <c r="AR11" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AS11" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AT11" t="n">
         <v>11.5</v>
@@ -3272,7 +3272,7 @@
         <v>11.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="AX11" t="n">
         <v>11</v>
@@ -3281,7 +3281,7 @@
         <v>9.4</v>
       </c>
       <c r="AZ11" t="n">
-        <v>9</v>
+        <v>14.5</v>
       </c>
       <c r="BA11" t="n">
         <v>38</v>
@@ -3296,10 +3296,10 @@
         <v>13</v>
       </c>
       <c r="BE11" t="n">
-        <v>9.199999999999999</v>
+        <v>48</v>
       </c>
       <c r="BF11" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BG11" t="n">
         <v>34</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-18 18:49:17</t>
+          <t>2026-07-18 21:03:51</t>
         </is>
       </c>
     </row>
@@ -3397,230 +3397,230 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.28</v>
+        <v>2.12</v>
       </c>
       <c r="G12" t="n">
-        <v>2.8</v>
+        <v>2.38</v>
       </c>
       <c r="H12" t="n">
+        <v>4</v>
+      </c>
+      <c r="I12" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="K12" t="n">
         <v>3.3</v>
       </c>
-      <c r="I12" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J12" t="n">
+      <c r="L12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N12" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="Q12" t="n">
         <v>2.66</v>
-      </c>
-      <c r="K12" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="M12" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="N12" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="O12" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="P12" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>2.78</v>
       </c>
       <c r="R12" t="n">
         <v>1.17</v>
       </c>
       <c r="S12" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="T12" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="U12" t="n">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="V12" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="W12" t="n">
-        <v>1.55</v>
+        <v>1.72</v>
       </c>
       <c r="X12" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="Y12" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="Z12" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="AA12" t="n">
         <v>900</v>
       </c>
       <c r="AB12" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AC12" t="n">
         <v>7.8</v>
       </c>
-      <c r="AC12" t="n">
-        <v>7.6</v>
-      </c>
       <c r="AD12" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AE12" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="AF12" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AG12" t="n">
-        <v>15.5</v>
+        <v>13</v>
       </c>
       <c r="AH12" t="n">
+        <v>28</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>130</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>32</v>
+      </c>
+      <c r="AK12" t="n">
         <v>36</v>
       </c>
-      <c r="AI12" t="n">
-        <v>260</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>46</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>44</v>
-      </c>
       <c r="AL12" t="n">
-        <v>80</v>
+        <v>170</v>
       </c>
       <c r="AM12" t="n">
         <v>500</v>
       </c>
       <c r="AN12" t="n">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="AO12" t="n">
-        <v>120</v>
+        <v>600</v>
       </c>
       <c r="AP12" t="n">
-        <v>3.3</v>
+        <v>6.8</v>
       </c>
       <c r="AQ12" t="n">
-        <v>3.65</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR12" t="n">
-        <v>4.4</v>
+        <v>24</v>
       </c>
       <c r="AS12" t="n">
-        <v>5</v>
+        <v>6.6</v>
       </c>
       <c r="AT12" t="n">
-        <v>3.15</v>
+        <v>5.6</v>
       </c>
       <c r="AU12" t="n">
-        <v>3.1</v>
+        <v>6</v>
       </c>
       <c r="AV12" t="n">
-        <v>4.3</v>
+        <v>15.5</v>
       </c>
       <c r="AW12" t="n">
-        <v>4.9</v>
+        <v>6.6</v>
       </c>
       <c r="AX12" t="n">
-        <v>3.95</v>
+        <v>10</v>
       </c>
       <c r="AY12" t="n">
-        <v>3.95</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ12" t="n">
-        <v>4.5</v>
+        <v>20</v>
       </c>
       <c r="BA12" t="n">
-        <v>5</v>
+        <v>6.6</v>
       </c>
       <c r="BB12" t="n">
-        <v>4.7</v>
+        <v>5.8</v>
       </c>
       <c r="BC12" t="n">
-        <v>4.7</v>
+        <v>5.9</v>
       </c>
       <c r="BD12" t="n">
-        <v>4.9</v>
+        <v>6.4</v>
       </c>
       <c r="BE12" t="n">
-        <v>5.2</v>
+        <v>6.8</v>
       </c>
       <c r="BF12" t="n">
-        <v>4.8</v>
+        <v>5.9</v>
       </c>
       <c r="BG12" t="n">
-        <v>5</v>
+        <v>6.8</v>
       </c>
       <c r="BH12" t="n">
-        <v>1000</v>
+        <v>2.98</v>
       </c>
       <c r="BI12" t="n">
-        <v>1.04</v>
+        <v>2.16</v>
       </c>
       <c r="BJ12" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BK12" t="n">
         <v>1.04</v>
       </c>
       <c r="BL12" t="n">
-        <v>1000</v>
+        <v>290</v>
       </c>
       <c r="BM12" t="n">
         <v>1.04</v>
       </c>
       <c r="BN12" t="n">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.04</v>
+        <v>3.6</v>
       </c>
       <c r="BP12" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BQ12" t="n">
         <v>1.04</v>
       </c>
       <c r="BR12" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BS12" t="n">
         <v>1.04</v>
       </c>
       <c r="BT12" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BU12" t="n">
-        <v>1.04</v>
+        <v>5.6</v>
       </c>
       <c r="BV12" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BW12" t="n">
         <v>1.04</v>
       </c>
       <c r="BX12" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="BY12" t="n">
         <v>1.04</v>
       </c>
       <c r="BZ12" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="CA12" t="n">
         <v>1.04</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-18 18:49:17</t>
+          <t>2026-07-18 21:03:51</t>
         </is>
       </c>
     </row>
@@ -3666,7 +3666,7 @@
         <v>2.76</v>
       </c>
       <c r="K13" t="n">
-        <v>3.65</v>
+        <v>3.35</v>
       </c>
       <c r="L13" t="n">
         <v>1.52</v>
@@ -3681,13 +3681,13 @@
         <v>1.5</v>
       </c>
       <c r="P13" t="n">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="Q13" t="n">
         <v>2.32</v>
       </c>
       <c r="R13" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -3696,13 +3696,13 @@
         <v>2</v>
       </c>
       <c r="U13" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="V13" t="n">
         <v>1.59</v>
       </c>
       <c r="W13" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="X13" t="n">
         <v>10.5</v>
@@ -3753,13 +3753,13 @@
         <v>500</v>
       </c>
       <c r="AN13" t="n">
-        <v>110</v>
+        <v>600</v>
       </c>
       <c r="AO13" t="n">
         <v>40</v>
       </c>
       <c r="AP13" t="n">
-        <v>6.6</v>
+        <v>4.9</v>
       </c>
       <c r="AQ13" t="n">
         <v>4.2</v>
@@ -3768,7 +3768,7 @@
         <v>5.1</v>
       </c>
       <c r="AS13" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AT13" t="n">
         <v>7</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-18 18:49:17</t>
+          <t>2026-07-18 21:03:51</t>
         </is>
       </c>
     </row>
@@ -3905,31 +3905,31 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="G14" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="H14" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="I14" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="J14" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="K14" t="n">
         <v>3.95</v>
       </c>
       <c r="L14" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="M14" t="n">
         <v>1.09</v>
       </c>
       <c r="N14" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="O14" t="n">
         <v>1.4</v>
@@ -3944,19 +3944,19 @@
         <v>1.24</v>
       </c>
       <c r="S14" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="T14" t="n">
         <v>1.98</v>
       </c>
       <c r="U14" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="V14" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W14" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="X14" t="n">
         <v>12</v>
@@ -4010,7 +4010,7 @@
         <v>18.5</v>
       </c>
       <c r="AO14" t="n">
-        <v>150</v>
+        <v>600</v>
       </c>
       <c r="AP14" t="n">
         <v>4.9</v>
@@ -4040,7 +4040,7 @@
         <v>5.6</v>
       </c>
       <c r="AY14" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="AZ14" t="n">
         <v>5.8</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-18 18:49:17</t>
+          <t>2026-07-18 21:03:51</t>
         </is>
       </c>
     </row>
@@ -4159,25 +4159,25 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.34</v>
+        <v>2.42</v>
       </c>
       <c r="G15" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="H15" t="n">
         <v>3.25</v>
       </c>
       <c r="I15" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="J15" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="K15" t="n">
         <v>3.2</v>
       </c>
       <c r="L15" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="M15" t="n">
         <v>1.12</v>
@@ -4189,7 +4189,7 @@
         <v>1.51</v>
       </c>
       <c r="P15" t="n">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="Q15" t="n">
         <v>2.5</v>
@@ -4198,19 +4198,19 @@
         <v>1.19</v>
       </c>
       <c r="S15" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="T15" t="n">
         <v>2.06</v>
       </c>
       <c r="U15" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="V15" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W15" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="X15" t="n">
         <v>9.199999999999999</v>
@@ -4225,13 +4225,13 @@
         <v>500</v>
       </c>
       <c r="AB15" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AC15" t="n">
         <v>7.4</v>
       </c>
       <c r="AD15" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AE15" t="n">
         <v>60</v>
@@ -4267,58 +4267,58 @@
         <v>90</v>
       </c>
       <c r="AP15" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AQ15" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AR15" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AS15" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AW15" t="n">
         <v>7</v>
       </c>
-      <c r="AT15" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AW15" t="n">
+      <c r="AX15" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BF15" t="n">
         <v>6.8</v>
       </c>
-      <c r="AX15" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>7</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>7</v>
-      </c>
-      <c r="BE15" t="n">
+      <c r="BG15" t="n">
         <v>7.4</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BG15" t="n">
-        <v>7</v>
       </c>
       <c r="BH15" t="n">
         <v>3</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-18 18:49:17</t>
+          <t>2026-07-18 21:03:51</t>
         </is>
       </c>
     </row>
@@ -4419,13 +4419,13 @@
         <v>3.3</v>
       </c>
       <c r="H16" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="I16" t="n">
         <v>2.8</v>
       </c>
       <c r="J16" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="K16" t="n">
         <v>3.6</v>
@@ -4443,7 +4443,7 @@
         <v>1.35</v>
       </c>
       <c r="P16" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="Q16" t="n">
         <v>2.02</v>
@@ -4455,7 +4455,7 @@
         <v>3.6</v>
       </c>
       <c r="T16" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="U16" t="n">
         <v>2.06</v>
@@ -4500,7 +4500,7 @@
         <v>18.5</v>
       </c>
       <c r="AI16" t="n">
-        <v>46</v>
+        <v>100</v>
       </c>
       <c r="AJ16" t="n">
         <v>55</v>
@@ -4563,7 +4563,7 @@
         <v>30</v>
       </c>
       <c r="BD16" t="n">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="BE16" t="n">
         <v>8.800000000000001</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-18 18:49:17</t>
+          <t>2026-07-18 21:03:51</t>
         </is>
       </c>
     </row>
@@ -4667,22 +4667,22 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.88</v>
+        <v>1.98</v>
       </c>
       <c r="G17" t="n">
-        <v>1.98</v>
+        <v>2.08</v>
       </c>
       <c r="H17" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I17" t="n">
         <v>4.1</v>
       </c>
-      <c r="I17" t="n">
-        <v>4.5</v>
-      </c>
       <c r="J17" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="K17" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L17" t="n">
         <v>1.37</v>
@@ -4697,7 +4697,7 @@
         <v>1.25</v>
       </c>
       <c r="P17" t="n">
-        <v>2.16</v>
+        <v>2.24</v>
       </c>
       <c r="Q17" t="n">
         <v>1.74</v>
@@ -4712,52 +4712,52 @@
         <v>1.67</v>
       </c>
       <c r="U17" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="V17" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="W17" t="n">
-        <v>2.02</v>
+        <v>1.92</v>
       </c>
       <c r="X17" t="n">
         <v>19.5</v>
       </c>
       <c r="Y17" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="Z17" t="n">
         <v>48</v>
       </c>
       <c r="AA17" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AB17" t="n">
         <v>11.5</v>
       </c>
       <c r="AC17" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AD17" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AE17" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="AF17" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AG17" t="n">
         <v>11</v>
       </c>
       <c r="AH17" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AI17" t="n">
         <v>120</v>
       </c>
       <c r="AJ17" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AK17" t="n">
         <v>19.5</v>
@@ -4769,10 +4769,10 @@
         <v>320</v>
       </c>
       <c r="AN17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AO17" t="n">
-        <v>120</v>
+        <v>55</v>
       </c>
       <c r="AP17" t="n">
         <v>16</v>
@@ -4781,10 +4781,10 @@
         <v>15.5</v>
       </c>
       <c r="AR17" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AS17" t="n">
-        <v>9.199999999999999</v>
+        <v>28</v>
       </c>
       <c r="AT17" t="n">
         <v>9.199999999999999</v>
@@ -4796,7 +4796,7 @@
         <v>14.5</v>
       </c>
       <c r="AW17" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="AX17" t="n">
         <v>11</v>
@@ -4808,7 +4808,7 @@
         <v>14.5</v>
       </c>
       <c r="BA17" t="n">
-        <v>8.6</v>
+        <v>30</v>
       </c>
       <c r="BB17" t="n">
         <v>18</v>
@@ -4817,16 +4817,16 @@
         <v>15.5</v>
       </c>
       <c r="BD17" t="n">
-        <v>14.5</v>
+        <v>25</v>
       </c>
       <c r="BE17" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF17" t="n">
         <v>7.8</v>
       </c>
       <c r="BG17" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH17" t="n">
         <v>4.5</v>
@@ -4835,62 +4835,62 @@
         <v>3.05</v>
       </c>
       <c r="BJ17" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BK17" t="n">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="BL17" t="n">
         <v>120</v>
       </c>
       <c r="BM17" t="n">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="BN17" t="n">
-        <v>5</v>
+        <v>5.9</v>
       </c>
       <c r="BO17" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="BP17" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="BQ17" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="BR17" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BS17" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BT17" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BU17" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BV17" t="n">
+        <v>32</v>
+      </c>
+      <c r="BW17" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BX17" t="n">
+        <v>44</v>
+      </c>
+      <c r="BY17" t="n">
         <v>4.5</v>
       </c>
-      <c r="BT17" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BU17" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BV17" t="n">
-        <v>40</v>
-      </c>
-      <c r="BW17" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BX17" t="n">
-        <v>48</v>
-      </c>
-      <c r="BY17" t="n">
-        <v>4.8</v>
-      </c>
       <c r="BZ17" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="CA17" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-18 18:49:17</t>
+          <t>2026-07-18 21:03:51</t>
         </is>
       </c>
     </row>
@@ -4927,7 +4927,7 @@
         <v>2.96</v>
       </c>
       <c r="H18" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="I18" t="n">
         <v>2.72</v>
@@ -4990,7 +4990,7 @@
         <v>14.5</v>
       </c>
       <c r="AC18" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD18" t="n">
         <v>13</v>
@@ -5038,7 +5038,7 @@
         <v>15.5</v>
       </c>
       <c r="AS18" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="AT18" t="n">
         <v>11.5</v>
@@ -5071,16 +5071,16 @@
         <v>13</v>
       </c>
       <c r="BD18" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BE18" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF18" t="n">
         <v>15</v>
       </c>
       <c r="BG18" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BH18" t="n">
         <v>4.5</v>
@@ -5092,13 +5092,13 @@
         <v>11</v>
       </c>
       <c r="BK18" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BL18" t="n">
         <v>110</v>
       </c>
       <c r="BM18" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BN18" t="n">
         <v>7.4</v>
@@ -5110,7 +5110,7 @@
         <v>22</v>
       </c>
       <c r="BQ18" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BR18" t="n">
         <v>36</v>
@@ -5125,16 +5125,16 @@
         <v>5</v>
       </c>
       <c r="BV18" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BW18" t="n">
-        <v>3.95</v>
+        <v>13</v>
       </c>
       <c r="BX18" t="n">
         <v>34</v>
       </c>
       <c r="BY18" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BZ18" t="n">
         <v>25</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-18 18:49:17</t>
+          <t>2026-07-18 21:03:51</t>
         </is>
       </c>
     </row>
@@ -5175,7 +5175,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="G19" t="n">
         <v>3.15</v>
@@ -5193,7 +5193,7 @@
         <v>3.1</v>
       </c>
       <c r="L19" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="M19" t="n">
         <v>1.13</v>
@@ -5202,16 +5202,16 @@
         <v>2.56</v>
       </c>
       <c r="O19" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="P19" t="n">
-        <v>1.56</v>
+        <v>1.51</v>
       </c>
       <c r="Q19" t="n">
         <v>2.62</v>
       </c>
       <c r="R19" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="S19" t="n">
         <v>5.4</v>
@@ -5286,7 +5286,7 @@
         <v>6.6</v>
       </c>
       <c r="AQ19" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AR19" t="n">
         <v>14</v>
@@ -5301,7 +5301,7 @@
         <v>6</v>
       </c>
       <c r="AV19" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AW19" t="n">
         <v>7.8</v>
@@ -5310,10 +5310,10 @@
         <v>14</v>
       </c>
       <c r="AY19" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AZ19" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="BA19" t="n">
         <v>8</v>
@@ -5340,7 +5340,7 @@
         <v>2.96</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="BJ19" t="n">
         <v>13</v>
@@ -5376,7 +5376,7 @@
         <v>6.6</v>
       </c>
       <c r="BU19" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="BV19" t="n">
         <v>32</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-18 18:49:17</t>
+          <t>2026-07-18 21:03:51</t>
         </is>
       </c>
     </row>
@@ -5432,16 +5432,16 @@
         <v>3.85</v>
       </c>
       <c r="G20" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="H20" t="n">
         <v>2.24</v>
       </c>
       <c r="I20" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="J20" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="K20" t="n">
         <v>3.2</v>
@@ -5453,7 +5453,7 @@
         <v>1.13</v>
       </c>
       <c r="N20" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="O20" t="n">
         <v>1.54</v>
@@ -5462,10 +5462,10 @@
         <v>1.49</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="R20" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="S20" t="n">
         <v>5.5</v>
@@ -5474,22 +5474,22 @@
         <v>2.12</v>
       </c>
       <c r="U20" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="V20" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="W20" t="n">
         <v>1.3</v>
       </c>
       <c r="X20" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="Y20" t="n">
-        <v>8.4</v>
+        <v>7.2</v>
       </c>
       <c r="Z20" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AA20" t="n">
         <v>40</v>
@@ -5501,7 +5501,7 @@
         <v>8.6</v>
       </c>
       <c r="AD20" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AE20" t="n">
         <v>36</v>
@@ -5516,25 +5516,25 @@
         <v>30</v>
       </c>
       <c r="AI20" t="n">
-        <v>70</v>
+        <v>460</v>
       </c>
       <c r="AJ20" t="n">
-        <v>130</v>
+        <v>900</v>
       </c>
       <c r="AK20" t="n">
         <v>200</v>
       </c>
       <c r="AL20" t="n">
-        <v>260</v>
+        <v>540</v>
       </c>
       <c r="AM20" t="n">
         <v>500</v>
       </c>
       <c r="AN20" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AO20" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AP20" t="n">
         <v>7</v>
@@ -5570,22 +5570,22 @@
         <v>18</v>
       </c>
       <c r="BA20" t="n">
-        <v>4.5</v>
+        <v>5.9</v>
       </c>
       <c r="BB20" t="n">
-        <v>4.7</v>
+        <v>6</v>
       </c>
       <c r="BC20" t="n">
-        <v>4.6</v>
+        <v>6</v>
       </c>
       <c r="BD20" t="n">
-        <v>4.6</v>
+        <v>6</v>
       </c>
       <c r="BE20" t="n">
-        <v>4.7</v>
+        <v>6.2</v>
       </c>
       <c r="BF20" t="n">
-        <v>4.7</v>
+        <v>6.2</v>
       </c>
       <c r="BG20" t="n">
         <v>5.5</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-18 18:49:17</t>
+          <t>2026-07-18 21:03:51</t>
         </is>
       </c>
     </row>
@@ -5683,25 +5683,25 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="G21" t="n">
-        <v>2.18</v>
+        <v>2.28</v>
       </c>
       <c r="H21" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="I21" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="J21" t="n">
         <v>3.5</v>
       </c>
       <c r="K21" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L21" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="M21" t="n">
         <v>1.07</v>
@@ -5710,31 +5710,31 @@
         <v>3.7</v>
       </c>
       <c r="O21" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="P21" t="n">
         <v>1.91</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="R21" t="n">
         <v>1.36</v>
       </c>
       <c r="S21" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="T21" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="U21" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="V21" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W21" t="n">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="X21" t="n">
         <v>14</v>
@@ -5746,10 +5746,10 @@
         <v>28</v>
       </c>
       <c r="AA21" t="n">
-        <v>900</v>
+        <v>75</v>
       </c>
       <c r="AB21" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AC21" t="n">
         <v>8</v>
@@ -5758,155 +5758,155 @@
         <v>16</v>
       </c>
       <c r="AE21" t="n">
-        <v>60</v>
+        <v>110</v>
       </c>
       <c r="AF21" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AG21" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AH21" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="AI21" t="n">
         <v>60</v>
       </c>
       <c r="AJ21" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="AK21" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AL21" t="n">
-        <v>38</v>
+        <v>95</v>
       </c>
       <c r="AM21" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AN21" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AO21" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AP21" t="n">
         <v>12</v>
       </c>
       <c r="AQ21" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AR21" t="n">
-        <v>24</v>
+        <v>19.5</v>
       </c>
       <c r="AS21" t="n">
-        <v>14</v>
+        <v>60</v>
       </c>
       <c r="AT21" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AU21" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AV21" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AW21" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AX21" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AY21" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ21" t="n">
         <v>16</v>
       </c>
       <c r="BA21" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BB21" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BC21" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BD21" t="n">
         <v>32</v>
       </c>
       <c r="BE21" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BF21" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="BG21" t="n">
         <v>32</v>
       </c>
       <c r="BH21" t="n">
-        <v>3.45</v>
+        <v>3.9</v>
       </c>
       <c r="BI21" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="BJ21" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="BK21" t="n">
-        <v>5.5</v>
+        <v>3.85</v>
       </c>
       <c r="BL21" t="n">
         <v>140</v>
       </c>
       <c r="BM21" t="n">
-        <v>11.5</v>
+        <v>5.7</v>
       </c>
       <c r="BN21" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="BO21" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BP21" t="n">
         <v>17</v>
       </c>
       <c r="BQ21" t="n">
-        <v>7.2</v>
+        <v>4.4</v>
       </c>
       <c r="BR21" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BS21" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="BT21" t="n">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="BU21" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BV21" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="BW21" t="n">
-        <v>9</v>
+        <v>5.1</v>
       </c>
       <c r="BX21" t="n">
         <v>50</v>
       </c>
       <c r="BY21" t="n">
-        <v>10</v>
+        <v>5.3</v>
       </c>
       <c r="BZ21" t="n">
         <v>29</v>
       </c>
       <c r="CA21" t="n">
-        <v>8.6</v>
+        <v>4.9</v>
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-07-18 18:49:17</t>
+          <t>2026-07-18 21:03:51</t>
         </is>
       </c>
     </row>
@@ -5946,13 +5946,13 @@
         <v>2.12</v>
       </c>
       <c r="I22" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="J22" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K22" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L22" t="n">
         <v>1.5</v>
@@ -5976,7 +5976,7 @@
         <v>1.23</v>
       </c>
       <c r="S22" t="n">
-        <v>3.95</v>
+        <v>4.5</v>
       </c>
       <c r="T22" t="n">
         <v>1.96</v>
@@ -5991,10 +5991,10 @@
         <v>1.29</v>
       </c>
       <c r="X22" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="Y22" t="n">
-        <v>9.199999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z22" t="n">
         <v>16</v>
@@ -6006,7 +6006,7 @@
         <v>14.5</v>
       </c>
       <c r="AC22" t="n">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="AD22" t="n">
         <v>14</v>
@@ -6015,88 +6015,88 @@
         <v>29</v>
       </c>
       <c r="AF22" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AG22" t="n">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="AH22" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AI22" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AJ22" t="n">
         <v>900</v>
       </c>
       <c r="AK22" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AL22" t="n">
+        <v>370</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN22" t="n">
         <v>95</v>
       </c>
-      <c r="AM22" t="n">
-        <v>500</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>100</v>
-      </c>
       <c r="AO22" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AP22" t="n">
-        <v>7.6</v>
+        <v>5.8</v>
       </c>
       <c r="AQ22" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="AR22" t="n">
+        <v>11</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV22" t="n">
         <v>9.6</v>
       </c>
-      <c r="AS22" t="n">
-        <v>4</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AU22" t="n">
+      <c r="AW22" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BG22" t="n">
         <v>5.6</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>20</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>20</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BD22" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BE22" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BF22" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BG22" t="n">
-        <v>4</v>
       </c>
       <c r="BH22" t="n">
         <v>1000</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-07-18 18:49:17</t>
+          <t>2026-07-18 21:03:51</t>
         </is>
       </c>
     </row>
@@ -6206,10 +6206,10 @@
         <v>4.2</v>
       </c>
       <c r="K23" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L23" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="M23" t="n">
         <v>1.04</v>
@@ -6224,19 +6224,19 @@
         <v>2.34</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="R23" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="S23" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="T23" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="U23" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="V23" t="n">
         <v>2.34</v>
@@ -6245,19 +6245,19 @@
         <v>1.22</v>
       </c>
       <c r="X23" t="n">
-        <v>950</v>
+        <v>500</v>
       </c>
       <c r="Y23" t="n">
         <v>11</v>
       </c>
       <c r="Z23" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AA23" t="n">
         <v>17.5</v>
       </c>
       <c r="AB23" t="n">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="AC23" t="n">
         <v>10.5</v>
@@ -6269,19 +6269,19 @@
         <v>17</v>
       </c>
       <c r="AF23" t="n">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="AG23" t="n">
         <v>950</v>
       </c>
       <c r="AH23" t="n">
-        <v>19.5</v>
+        <v>25</v>
       </c>
       <c r="AI23" t="n">
         <v>500</v>
       </c>
       <c r="AJ23" t="n">
-        <v>700</v>
+        <v>900</v>
       </c>
       <c r="AK23" t="n">
         <v>75</v>
@@ -6290,25 +6290,25 @@
         <v>70</v>
       </c>
       <c r="AM23" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN23" t="n">
         <v>700</v>
       </c>
       <c r="AO23" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AP23" t="n">
         <v>16.5</v>
       </c>
       <c r="AQ23" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AR23" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AS23" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="AT23" t="n">
         <v>17.5</v>
@@ -6317,58 +6317,58 @@
         <v>9</v>
       </c>
       <c r="AV23" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AW23" t="n">
         <v>12</v>
       </c>
       <c r="AX23" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AY23" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AZ23" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="BA23" t="n">
         <v>21</v>
       </c>
       <c r="BB23" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BC23" t="n">
         <v>46</v>
       </c>
       <c r="BD23" t="n">
-        <v>8.6</v>
+        <v>44</v>
       </c>
       <c r="BE23" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BF23" t="n">
-        <v>8.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG23" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BH23" t="n">
         <v>4.7</v>
       </c>
       <c r="BI23" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="BJ23" t="n">
         <v>11</v>
       </c>
       <c r="BK23" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BL23" t="n">
         <v>120</v>
       </c>
       <c r="BM23" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BN23" t="n">
         <v>10.5</v>
@@ -6386,7 +6386,7 @@
         <v>50</v>
       </c>
       <c r="BS23" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BT23" t="n">
         <v>5.1</v>
@@ -6398,7 +6398,7 @@
         <v>12</v>
       </c>
       <c r="BW23" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BX23" t="n">
         <v>25</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-07-18 18:49:17</t>
+          <t>2026-07-18 21:03:51</t>
         </is>
       </c>
     </row>
@@ -6445,13 +6445,13 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="G24" t="n">
         <v>2.56</v>
       </c>
       <c r="H24" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="I24" t="n">
         <v>2.98</v>
@@ -6475,13 +6475,13 @@
         <v>1.14</v>
       </c>
       <c r="P24" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="Q24" t="n">
         <v>1.44</v>
       </c>
       <c r="R24" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="S24" t="n">
         <v>2.08</v>
@@ -6490,7 +6490,7 @@
         <v>1.44</v>
       </c>
       <c r="U24" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="V24" t="n">
         <v>1.51</v>
@@ -6502,7 +6502,7 @@
         <v>40</v>
       </c>
       <c r="Y24" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="Z24" t="n">
         <v>32</v>
@@ -6547,10 +6547,10 @@
         <v>55</v>
       </c>
       <c r="AN24" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AO24" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AP24" t="n">
         <v>2.5</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-07-18 18:49:17</t>
+          <t>2026-07-18 21:03:51</t>
         </is>
       </c>
     </row>
@@ -6699,7 +6699,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="G25" t="n">
         <v>4.3</v>
@@ -6717,7 +6717,7 @@
         <v>4.2</v>
       </c>
       <c r="L25" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="M25" t="n">
         <v>1.05</v>
@@ -6753,7 +6753,7 @@
         <v>1.3</v>
       </c>
       <c r="X25" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="Y25" t="n">
         <v>11.5</v>
@@ -6762,7 +6762,7 @@
         <v>14</v>
       </c>
       <c r="AA25" t="n">
-        <v>900</v>
+        <v>38</v>
       </c>
       <c r="AB25" t="n">
         <v>17.5</v>
@@ -6777,7 +6777,7 @@
         <v>21</v>
       </c>
       <c r="AF25" t="n">
-        <v>36</v>
+        <v>100</v>
       </c>
       <c r="AG25" t="n">
         <v>17</v>
@@ -6795,10 +6795,10 @@
         <v>48</v>
       </c>
       <c r="AL25" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="AM25" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN25" t="n">
         <v>500</v>
@@ -6831,7 +6831,7 @@
         <v>15</v>
       </c>
       <c r="AX25" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="AY25" t="n">
         <v>12</v>
@@ -6840,16 +6840,16 @@
         <v>13</v>
       </c>
       <c r="BA25" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.01</v>
+        <v>28</v>
       </c>
       <c r="BC25" t="n">
-        <v>1.01</v>
+        <v>34</v>
       </c>
       <c r="BD25" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="BE25" t="n">
         <v>1.01</v>
@@ -6900,13 +6900,13 @@
         <v>5.4</v>
       </c>
       <c r="BU25" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BV25" t="n">
         <v>15</v>
       </c>
       <c r="BW25" t="n">
-        <v>4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX25" t="n">
         <v>29</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-07-18 18:49:17</t>
+          <t>2026-07-18 21:03:51</t>
         </is>
       </c>
     </row>
@@ -6953,16 +6953,16 @@
         </is>
       </c>
       <c r="F26" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="G26" t="n">
         <v>3.8</v>
-      </c>
-      <c r="G26" t="n">
-        <v>3.85</v>
       </c>
       <c r="H26" t="n">
         <v>2.06</v>
       </c>
       <c r="I26" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="J26" t="n">
         <v>3.95</v>
@@ -6971,37 +6971,37 @@
         <v>4</v>
       </c>
       <c r="L26" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="M26" t="n">
         <v>1.04</v>
       </c>
       <c r="N26" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="O26" t="n">
         <v>1.22</v>
       </c>
       <c r="P26" t="n">
-        <v>2.34</v>
+        <v>2.44</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="R26" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="S26" t="n">
-        <v>2.72</v>
+        <v>2.64</v>
       </c>
       <c r="T26" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="U26" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="V26" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="W26" t="n">
         <v>1.35</v>
@@ -7013,22 +7013,22 @@
         <v>13</v>
       </c>
       <c r="Z26" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA26" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AB26" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AC26" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AD26" t="n">
         <v>10.5</v>
       </c>
       <c r="AE26" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AF26" t="n">
         <v>32</v>
@@ -7040,28 +7040,28 @@
         <v>16</v>
       </c>
       <c r="AI26" t="n">
+        <v>28</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>150</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>80</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>90</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>65</v>
+      </c>
+      <c r="AN26" t="n">
         <v>29</v>
       </c>
-      <c r="AJ26" t="n">
-        <v>490</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>85</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>42</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>70</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>32</v>
-      </c>
       <c r="AO26" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AP26" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AQ26" t="n">
         <v>11.5</v>
@@ -7076,7 +7076,7 @@
         <v>17</v>
       </c>
       <c r="AU26" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="AV26" t="n">
         <v>9.800000000000001</v>
@@ -7091,13 +7091,13 @@
         <v>14</v>
       </c>
       <c r="AZ26" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BA26" t="n">
         <v>25</v>
       </c>
       <c r="BB26" t="n">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="BC26" t="n">
         <v>34</v>
@@ -7106,31 +7106,31 @@
         <v>36</v>
       </c>
       <c r="BE26" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BF26" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="BG26" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BH26" t="n">
         <v>4.5</v>
       </c>
       <c r="BI26" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="BJ26" t="n">
         <v>9</v>
       </c>
       <c r="BK26" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BL26" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="BM26" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BN26" t="n">
         <v>7.2</v>
@@ -7142,13 +7142,13 @@
         <v>32</v>
       </c>
       <c r="BQ26" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR26" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="BS26" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT26" t="n">
         <v>5.1</v>
@@ -7160,23 +7160,23 @@
         <v>14</v>
       </c>
       <c r="BW26" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BX26" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BY26" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BZ26" t="n">
         <v>18</v>
       </c>
       <c r="CA26" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-07-18 18:49:17</t>
+          <t>2026-07-18 21:03:51</t>
         </is>
       </c>
     </row>
@@ -7213,10 +7213,10 @@
         <v>1.31</v>
       </c>
       <c r="H27" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="I27" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="J27" t="n">
         <v>6.6</v>
@@ -7237,19 +7237,19 @@
         <v>1.18</v>
       </c>
       <c r="P27" t="n">
-        <v>2.74</v>
+        <v>2.66</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="R27" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="S27" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="T27" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="U27" t="n">
         <v>1.9</v>
@@ -7270,10 +7270,10 @@
         <v>130</v>
       </c>
       <c r="AA27" t="n">
-        <v>520</v>
+        <v>540</v>
       </c>
       <c r="AB27" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC27" t="n">
         <v>15</v>
@@ -7285,7 +7285,7 @@
         <v>200</v>
       </c>
       <c r="AF27" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AG27" t="n">
         <v>11</v>
@@ -7294,7 +7294,7 @@
         <v>32</v>
       </c>
       <c r="AI27" t="n">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AJ27" t="n">
         <v>10.5</v>
@@ -7306,7 +7306,7 @@
         <v>36</v>
       </c>
       <c r="AM27" t="n">
-        <v>160</v>
+        <v>380</v>
       </c>
       <c r="AN27" t="n">
         <v>4.3</v>
@@ -7315,7 +7315,7 @@
         <v>1000</v>
       </c>
       <c r="AP27" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AQ27" t="n">
         <v>38</v>
@@ -7324,13 +7324,13 @@
         <v>40</v>
       </c>
       <c r="AS27" t="n">
-        <v>55</v>
+        <v>100</v>
       </c>
       <c r="AT27" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU27" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AV27" t="n">
         <v>38</v>
@@ -7339,10 +7339,10 @@
         <v>46</v>
       </c>
       <c r="AX27" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AY27" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ27" t="n">
         <v>26</v>
@@ -7351,19 +7351,19 @@
         <v>42</v>
       </c>
       <c r="BB27" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BC27" t="n">
         <v>12</v>
       </c>
       <c r="BD27" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BE27" t="n">
-        <v>44</v>
+        <v>70</v>
       </c>
       <c r="BF27" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BG27" t="n">
         <v>48</v>
@@ -7384,13 +7384,13 @@
         <v>170</v>
       </c>
       <c r="BM27" t="n">
-        <v>1.04</v>
+        <v>7.2</v>
       </c>
       <c r="BN27" t="n">
         <v>4</v>
       </c>
       <c r="BO27" t="n">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="BP27" t="n">
         <v>7.4</v>
@@ -7402,35 +7402,35 @@
         <v>23</v>
       </c>
       <c r="BS27" t="n">
-        <v>1.04</v>
+        <v>17</v>
       </c>
       <c r="BT27" t="n">
         <v>15.5</v>
       </c>
       <c r="BU27" t="n">
-        <v>1.04</v>
+        <v>5.1</v>
       </c>
       <c r="BV27" t="n">
         <v>120</v>
       </c>
       <c r="BW27" t="n">
-        <v>1.04</v>
+        <v>7</v>
       </c>
       <c r="BX27" t="n">
         <v>95</v>
       </c>
       <c r="BY27" t="n">
-        <v>1.04</v>
+        <v>7</v>
       </c>
       <c r="BZ27" t="n">
         <v>11.5</v>
       </c>
       <c r="CA27" t="n">
-        <v>7.8</v>
+        <v>4.5</v>
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-07-18 18:49:17</t>
+          <t>2026-07-18 21:03:51</t>
         </is>
       </c>
     </row>
@@ -7464,19 +7464,19 @@
         <v>5.4</v>
       </c>
       <c r="G28" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="H28" t="n">
         <v>1.64</v>
       </c>
       <c r="I28" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="J28" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="K28" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="L28" t="n">
         <v>1.27</v>
@@ -7485,103 +7485,103 @@
         <v>1.03</v>
       </c>
       <c r="N28" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="O28" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="P28" t="n">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="R28" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="S28" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="T28" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="U28" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="V28" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="W28" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="X28" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="Y28" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Z28" t="n">
         <v>13</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>12.5</v>
       </c>
       <c r="AA28" t="n">
         <v>17.5</v>
       </c>
       <c r="AB28" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AC28" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AD28" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AE28" t="n">
         <v>15</v>
       </c>
       <c r="AF28" t="n">
-        <v>180</v>
+        <v>110</v>
       </c>
       <c r="AG28" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AH28" t="n">
         <v>17.5</v>
       </c>
       <c r="AI28" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AJ28" t="n">
         <v>690</v>
       </c>
       <c r="AK28" t="n">
-        <v>390</v>
+        <v>120</v>
       </c>
       <c r="AL28" t="n">
-        <v>220</v>
+        <v>55</v>
       </c>
       <c r="AM28" t="n">
-        <v>490</v>
+        <v>65</v>
       </c>
       <c r="AN28" t="n">
         <v>46</v>
       </c>
       <c r="AO28" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AP28" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AQ28" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AR28" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AS28" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AT28" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AU28" t="n">
         <v>10</v>
@@ -7590,19 +7590,19 @@
         <v>9.4</v>
       </c>
       <c r="AW28" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AX28" t="n">
         <v>44</v>
       </c>
       <c r="AY28" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AZ28" t="n">
         <v>15.5</v>
       </c>
       <c r="BA28" t="n">
-        <v>22</v>
+        <v>17.5</v>
       </c>
       <c r="BB28" t="n">
         <v>42</v>
@@ -7614,61 +7614,61 @@
         <v>46</v>
       </c>
       <c r="BE28" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="BF28" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="BG28" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="BH28" t="n">
         <v>5.4</v>
       </c>
       <c r="BI28" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="BJ28" t="n">
         <v>11</v>
       </c>
       <c r="BK28" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="BL28" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="BM28" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BN28" t="n">
         <v>11</v>
       </c>
       <c r="BO28" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="BP28" t="n">
         <v>46</v>
       </c>
       <c r="BQ28" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BR28" t="n">
         <v>46</v>
       </c>
       <c r="BS28" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BT28" t="n">
         <v>5.5</v>
       </c>
       <c r="BU28" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="BV28" t="n">
         <v>12</v>
       </c>
       <c r="BW28" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BX28" t="n">
         <v>24</v>
@@ -7677,14 +7677,14 @@
         <v>4</v>
       </c>
       <c r="BZ28" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="CA28" t="n">
         <v>3.65</v>
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-07-18 18:49:17</t>
+          <t>2026-07-18 21:03:51</t>
         </is>
       </c>
     </row>
@@ -7736,7 +7736,7 @@
         <v>1.24</v>
       </c>
       <c r="M29" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N29" t="n">
         <v>4.2</v>
@@ -7745,7 +7745,7 @@
         <v>1.19</v>
       </c>
       <c r="P29" t="n">
-        <v>2.4</v>
+        <v>2.56</v>
       </c>
       <c r="Q29" t="n">
         <v>1.51</v>
@@ -7760,7 +7760,7 @@
         <v>1.52</v>
       </c>
       <c r="U29" t="n">
-        <v>1.11</v>
+        <v>2.56</v>
       </c>
       <c r="V29" t="n">
         <v>1.92</v>
@@ -7769,7 +7769,7 @@
         <v>1.32</v>
       </c>
       <c r="X29" t="n">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="Y29" t="n">
         <v>15.5</v>
@@ -7793,7 +7793,7 @@
         <v>19</v>
       </c>
       <c r="AF29" t="n">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="AG29" t="n">
         <v>17</v>
@@ -7802,22 +7802,22 @@
         <v>16.5</v>
       </c>
       <c r="AI29" t="n">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="AJ29" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AK29" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="AL29" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="AM29" t="n">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="AN29" t="n">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="AO29" t="n">
         <v>9</v>
@@ -7838,10 +7838,10 @@
         <v>6.4</v>
       </c>
       <c r="AU29" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AV29" t="n">
-        <v>5.1</v>
+        <v>6.2</v>
       </c>
       <c r="AW29" t="n">
         <v>6</v>
@@ -7853,7 +7853,7 @@
         <v>5.8</v>
       </c>
       <c r="AZ29" t="n">
-        <v>5.8</v>
+        <v>7.6</v>
       </c>
       <c r="BA29" t="n">
         <v>6.6</v>
@@ -7874,61 +7874,61 @@
         <v>6.6</v>
       </c>
       <c r="BG29" t="n">
-        <v>4.4</v>
+        <v>5.9</v>
       </c>
       <c r="BH29" t="n">
         <v>5.2</v>
       </c>
       <c r="BI29" t="n">
-        <v>2.8</v>
+        <v>2.72</v>
       </c>
       <c r="BJ29" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK29" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="BL29" t="n">
         <v>85</v>
       </c>
       <c r="BM29" t="n">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="BN29" t="n">
         <v>8.6</v>
       </c>
       <c r="BO29" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="BP29" t="n">
         <v>30</v>
       </c>
       <c r="BQ29" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="BR29" t="n">
         <v>34</v>
       </c>
       <c r="BS29" t="n">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="BT29" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BU29" t="n">
         <v>4.2</v>
       </c>
       <c r="BV29" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BW29" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="BX29" t="n">
         <v>24</v>
       </c>
       <c r="BY29" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="BZ29" t="n">
         <v>0</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-07-18 18:49:17</t>
+          <t>2026-07-18 21:03:51</t>
         </is>
       </c>
     </row>
@@ -7975,7 +7975,7 @@
         <v>6.2</v>
       </c>
       <c r="H30" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="I30" t="n">
         <v>1.67</v>
@@ -7987,13 +7987,13 @@
         <v>4.5</v>
       </c>
       <c r="L30" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="M30" t="n">
         <v>1.05</v>
       </c>
       <c r="N30" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="O30" t="n">
         <v>1.26</v>
@@ -8005,10 +8005,10 @@
         <v>1.76</v>
       </c>
       <c r="R30" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="S30" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="T30" t="n">
         <v>1.81</v>
@@ -8032,7 +8032,7 @@
         <v>11</v>
       </c>
       <c r="AA30" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AB30" t="n">
         <v>30</v>
@@ -8041,7 +8041,7 @@
         <v>10</v>
       </c>
       <c r="AD30" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AE30" t="n">
         <v>17</v>
@@ -8056,7 +8056,7 @@
         <v>21</v>
       </c>
       <c r="AI30" t="n">
-        <v>65</v>
+        <v>34</v>
       </c>
       <c r="AJ30" t="n">
         <v>690</v>
@@ -8089,7 +8089,7 @@
         <v>14</v>
       </c>
       <c r="AT30" t="n">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="AU30" t="n">
         <v>8.800000000000001</v>
@@ -8104,13 +8104,13 @@
         <v>40</v>
       </c>
       <c r="AY30" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AZ30" t="n">
         <v>17</v>
       </c>
       <c r="BA30" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="BB30" t="n">
         <v>44</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-07-18 18:49:17</t>
+          <t>2026-07-18 21:03:51</t>
         </is>
       </c>
     </row>
@@ -8229,10 +8229,10 @@
         <v>3.15</v>
       </c>
       <c r="H31" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="I31" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="J31" t="n">
         <v>3.05</v>
@@ -8280,16 +8280,16 @@
         <v>13</v>
       </c>
       <c r="Y31" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Z31" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AA31" t="n">
         <v>48</v>
       </c>
       <c r="AB31" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC31" t="n">
         <v>8.199999999999999</v>
@@ -8301,7 +8301,7 @@
         <v>38</v>
       </c>
       <c r="AF31" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AG31" t="n">
         <v>14</v>
@@ -8310,7 +8310,7 @@
         <v>20</v>
       </c>
       <c r="AI31" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AJ31" t="n">
         <v>55</v>
@@ -8319,10 +8319,10 @@
         <v>40</v>
       </c>
       <c r="AL31" t="n">
-        <v>65</v>
+        <v>500</v>
       </c>
       <c r="AM31" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN31" t="n">
         <v>40</v>
@@ -8334,55 +8334,55 @@
         <v>8.6</v>
       </c>
       <c r="AQ31" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="AR31" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AS31" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW31" t="n">
         <v>6.2</v>
       </c>
-      <c r="AT31" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AU31" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AV31" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AW31" t="n">
-        <v>6</v>
-      </c>
       <c r="AX31" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AY31" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AZ31" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="BA31" t="n">
-        <v>38</v>
+        <v>6.6</v>
       </c>
       <c r="BB31" t="n">
         <v>36</v>
       </c>
       <c r="BC31" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BD31" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BE31" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BF31" t="n">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="BG31" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BH31" t="n">
         <v>3.35</v>
@@ -8424,7 +8424,7 @@
         <v>6.4</v>
       </c>
       <c r="BU31" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="BV31" t="n">
         <v>27</v>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-07-18 18:49:17</t>
+          <t>2026-07-18 21:03:51</t>
         </is>
       </c>
     </row>
@@ -8477,19 +8477,19 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="G32" t="n">
         <v>1000</v>
       </c>
       <c r="H32" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="I32" t="n">
         <v>1000</v>
       </c>
       <c r="J32" t="n">
-        <v>3.1</v>
+        <v>2</v>
       </c>
       <c r="K32" t="n">
         <v>1000</v>
@@ -8525,10 +8525,10 @@
         <v>1.11</v>
       </c>
       <c r="V32" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="W32" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="X32" t="n">
         <v>1000</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-07-18 18:49:17</t>
+          <t>2026-07-18 21:03:51</t>
         </is>
       </c>
     </row>
@@ -8731,22 +8731,22 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="G33" t="n">
         <v>6.6</v>
       </c>
       <c r="H33" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="I33" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="J33" t="n">
         <v>3.5</v>
       </c>
       <c r="K33" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="L33" t="n">
         <v>1.59</v>
@@ -8755,19 +8755,19 @@
         <v>1.13</v>
       </c>
       <c r="N33" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="O33" t="n">
         <v>1.59</v>
       </c>
       <c r="P33" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="Q33" t="n">
         <v>2.74</v>
       </c>
       <c r="R33" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="S33" t="n">
         <v>6</v>
@@ -8797,7 +8797,7 @@
         <v>24</v>
       </c>
       <c r="AB33" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AC33" t="n">
         <v>11</v>
@@ -8845,7 +8845,7 @@
         <v>4.4</v>
       </c>
       <c r="AR33" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="AS33" t="n">
         <v>17.5</v>
@@ -8863,31 +8863,31 @@
         <v>18.5</v>
       </c>
       <c r="AX33" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="AY33" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AZ33" t="n">
         <v>4.5</v>
       </c>
       <c r="BA33" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BB33" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BC33" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BD33" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BE33" t="n">
         <v>5</v>
       </c>
-      <c r="BC33" t="n">
-        <v>5</v>
-      </c>
-      <c r="BD33" t="n">
-        <v>5</v>
-      </c>
-      <c r="BE33" t="n">
-        <v>5.1</v>
-      </c>
       <c r="BF33" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="BG33" t="n">
         <v>18</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-07-18 18:49:17</t>
+          <t>2026-07-18 21:03:51</t>
         </is>
       </c>
     </row>
@@ -8991,10 +8991,10 @@
         <v>4</v>
       </c>
       <c r="H34" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="I34" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="J34" t="n">
         <v>3.75</v>
@@ -9009,19 +9009,19 @@
         <v>1.05</v>
       </c>
       <c r="N34" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="O34" t="n">
         <v>1.23</v>
       </c>
       <c r="P34" t="n">
-        <v>2.24</v>
+        <v>2.32</v>
       </c>
       <c r="Q34" t="n">
         <v>1.68</v>
       </c>
       <c r="R34" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="S34" t="n">
         <v>2.74</v>
@@ -9030,7 +9030,7 @@
         <v>1.62</v>
       </c>
       <c r="U34" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="V34" t="n">
         <v>1.86</v>
@@ -9084,7 +9084,7 @@
         <v>50</v>
       </c>
       <c r="AM34" t="n">
-        <v>500</v>
+        <v>75</v>
       </c>
       <c r="AN34" t="n">
         <v>34</v>
@@ -9102,7 +9102,7 @@
         <v>11</v>
       </c>
       <c r="AS34" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AT34" t="n">
         <v>12.5</v>
@@ -9111,7 +9111,7 @@
         <v>7.8</v>
       </c>
       <c r="AV34" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW34" t="n">
         <v>15</v>
@@ -9135,7 +9135,7 @@
         <v>7</v>
       </c>
       <c r="BD34" t="n">
-        <v>7.2</v>
+        <v>34</v>
       </c>
       <c r="BE34" t="n">
         <v>7.6</v>
@@ -9150,37 +9150,37 @@
         <v>4.4</v>
       </c>
       <c r="BI34" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="BJ34" t="n">
         <v>9.4</v>
       </c>
       <c r="BK34" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="BL34" t="n">
         <v>110</v>
       </c>
       <c r="BM34" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BN34" t="n">
         <v>7.4</v>
       </c>
       <c r="BO34" t="n">
-        <v>5.9</v>
+        <v>4</v>
       </c>
       <c r="BP34" t="n">
         <v>28</v>
       </c>
       <c r="BQ34" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BR34" t="n">
         <v>34</v>
       </c>
       <c r="BS34" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BT34" t="n">
         <v>5.3</v>
@@ -9192,13 +9192,13 @@
         <v>14.5</v>
       </c>
       <c r="BW34" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BX34" t="n">
         <v>26</v>
       </c>
       <c r="BY34" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BZ34" t="n">
         <v>0</v>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-07-18 18:49:17</t>
+          <t>2026-07-18 21:03:51</t>
         </is>
       </c>
     </row>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-07-18 18:49:17</t>
+          <t>2026-07-18 21:03:51</t>
         </is>
       </c>
     </row>
@@ -9496,7 +9496,7 @@
         <v>1.57</v>
       </c>
       <c r="G36" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="H36" t="n">
         <v>6.2</v>
@@ -9523,7 +9523,7 @@
         <v>1.38</v>
       </c>
       <c r="P36" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="Q36" t="n">
         <v>2</v>
@@ -9538,13 +9538,13 @@
         <v>1.99</v>
       </c>
       <c r="U36" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="V36" t="n">
         <v>1.15</v>
       </c>
       <c r="W36" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="X36" t="n">
         <v>15.5</v>
@@ -9583,7 +9583,7 @@
         <v>700</v>
       </c>
       <c r="AJ36" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AK36" t="n">
         <v>20</v>
@@ -9607,49 +9607,49 @@
         <v>16.5</v>
       </c>
       <c r="AR36" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AS36" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AT36" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="AU36" t="n">
         <v>7.8</v>
       </c>
       <c r="AV36" t="n">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="AW36" t="n">
         <v>7.6</v>
       </c>
       <c r="AX36" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AY36" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="AZ36" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="BA36" t="n">
         <v>7.6</v>
       </c>
       <c r="BB36" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BC36" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="BD36" t="n">
-        <v>6.8</v>
+        <v>28</v>
       </c>
       <c r="BE36" t="n">
         <v>7.8</v>
       </c>
       <c r="BF36" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="BG36" t="n">
         <v>7.8</v>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-07-18 18:49:17</t>
+          <t>2026-07-18 21:03:51</t>
         </is>
       </c>
     </row>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-07-18 18:49:17</t>
+          <t>2026-07-18 21:03:51</t>
         </is>
       </c>
     </row>
@@ -10001,13 +10001,13 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="G38" t="n">
         <v>2.08</v>
       </c>
       <c r="H38" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="I38" t="n">
         <v>4.4</v>
@@ -10019,7 +10019,7 @@
         <v>4.3</v>
       </c>
       <c r="L38" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="M38" t="n">
         <v>1.05</v>
@@ -10067,16 +10067,16 @@
         <v>900</v>
       </c>
       <c r="AB38" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AC38" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AD38" t="n">
         <v>17.5</v>
       </c>
       <c r="AE38" t="n">
-        <v>500</v>
+        <v>48</v>
       </c>
       <c r="AF38" t="n">
         <v>14.5</v>
@@ -10097,7 +10097,7 @@
         <v>21</v>
       </c>
       <c r="AL38" t="n">
-        <v>34</v>
+        <v>500</v>
       </c>
       <c r="AM38" t="n">
         <v>500</v>
@@ -10127,19 +10127,19 @@
         <v>7.8</v>
       </c>
       <c r="AV38" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AW38" t="n">
         <v>36</v>
       </c>
       <c r="AX38" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AY38" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AZ38" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="BA38" t="n">
         <v>1.01</v>
@@ -10160,7 +10160,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BG38" t="n">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="BH38" t="n">
         <v>4.3</v>
@@ -10184,7 +10184,7 @@
         <v>5.6</v>
       </c>
       <c r="BO38" t="n">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="BP38" t="n">
         <v>15.5</v>
@@ -10224,7 +10224,7 @@
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-07-18 18:49:17</t>
+          <t>2026-07-18 21:03:51</t>
         </is>
       </c>
     </row>
@@ -10264,7 +10264,7 @@
         <v>6.2</v>
       </c>
       <c r="I39" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="J39" t="n">
         <v>3.8</v>
@@ -10273,7 +10273,7 @@
         <v>4.2</v>
       </c>
       <c r="L39" t="n">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="M39" t="n">
         <v>1.07</v>
@@ -10288,7 +10288,7 @@
         <v>1.9</v>
       </c>
       <c r="Q39" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="R39" t="n">
         <v>1.35</v>
@@ -10324,7 +10324,7 @@
         <v>8.4</v>
       </c>
       <c r="AC39" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AD39" t="n">
         <v>34</v>
@@ -10366,13 +10366,13 @@
         <v>10.5</v>
       </c>
       <c r="AQ39" t="n">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="AR39" t="n">
         <v>40</v>
       </c>
       <c r="AS39" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AT39" t="n">
         <v>7</v>
@@ -10384,7 +10384,7 @@
         <v>21</v>
       </c>
       <c r="AW39" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AX39" t="n">
         <v>7.6</v>
@@ -10396,25 +10396,25 @@
         <v>19</v>
       </c>
       <c r="BA39" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BB39" t="n">
         <v>11.5</v>
       </c>
       <c r="BC39" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="BD39" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BE39" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF39" t="n">
         <v>7.4</v>
       </c>
       <c r="BG39" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH39" t="n">
         <v>4</v>
@@ -10426,13 +10426,13 @@
         <v>11.5</v>
       </c>
       <c r="BK39" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BL39" t="n">
         <v>180</v>
       </c>
       <c r="BM39" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BN39" t="n">
         <v>4.2</v>
@@ -10450,10 +10450,10 @@
         <v>34</v>
       </c>
       <c r="BS39" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BT39" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BU39" t="n">
         <v>4.5</v>
@@ -10462,23 +10462,23 @@
         <v>65</v>
       </c>
       <c r="BW39" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BX39" t="n">
         <v>70</v>
       </c>
       <c r="BY39" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BZ39" t="n">
         <v>21</v>
       </c>
       <c r="CA39" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-07-18 18:49:17</t>
+          <t>2026-07-18 21:03:51</t>
         </is>
       </c>
     </row>
@@ -10524,10 +10524,10 @@
         <v>4.7</v>
       </c>
       <c r="K40" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="L40" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="M40" t="n">
         <v>1.01</v>
@@ -10539,7 +10539,7 @@
         <v>1.19</v>
       </c>
       <c r="P40" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="Q40" t="n">
         <v>1.48</v>
@@ -10557,10 +10557,10 @@
         <v>2.36</v>
       </c>
       <c r="V40" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="W40" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="X40" t="n">
         <v>38</v>
@@ -10605,31 +10605,31 @@
         <v>65</v>
       </c>
       <c r="AL40" t="n">
-        <v>700</v>
+        <v>55</v>
       </c>
       <c r="AM40" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN40" t="n">
         <v>60</v>
       </c>
       <c r="AO40" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="AP40" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="AQ40" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AR40" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AS40" t="n">
         <v>13.5</v>
       </c>
       <c r="AT40" t="n">
-        <v>5.8</v>
+        <v>13</v>
       </c>
       <c r="AU40" t="n">
         <v>10</v>
@@ -10641,7 +10641,7 @@
         <v>12.5</v>
       </c>
       <c r="AX40" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AY40" t="n">
         <v>19</v>
@@ -10653,7 +10653,7 @@
         <v>18.5</v>
       </c>
       <c r="BB40" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BC40" t="n">
         <v>42</v>
@@ -10662,10 +10662,10 @@
         <v>38</v>
       </c>
       <c r="BE40" t="n">
+        <v>28</v>
+      </c>
+      <c r="BF40" t="n">
         <v>6.4</v>
-      </c>
-      <c r="BF40" t="n">
-        <v>6.2</v>
       </c>
       <c r="BG40" t="n">
         <v>5.1</v>
@@ -10674,7 +10674,7 @@
         <v>5.6</v>
       </c>
       <c r="BI40" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BJ40" t="n">
         <v>11</v>
@@ -10732,7 +10732,7 @@
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-07-18 18:49:17</t>
+          <t>2026-07-18 21:03:51</t>
         </is>
       </c>
     </row>
@@ -10805,10 +10805,10 @@
         <v>3.85</v>
       </c>
       <c r="T41" t="n">
-        <v>1.89</v>
+        <v>1.78</v>
       </c>
       <c r="U41" t="n">
-        <v>1.93</v>
+        <v>2.08</v>
       </c>
       <c r="V41" t="n">
         <v>1.26</v>
@@ -10856,7 +10856,7 @@
         <v>28</v>
       </c>
       <c r="AK41" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AL41" t="n">
         <v>48</v>
@@ -10877,10 +10877,10 @@
         <v>11</v>
       </c>
       <c r="AR41" t="n">
-        <v>22</v>
+        <v>4.7</v>
       </c>
       <c r="AS41" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AT41" t="n">
         <v>6.4</v>
@@ -10892,7 +10892,7 @@
         <v>13.5</v>
       </c>
       <c r="AW41" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AX41" t="n">
         <v>9.199999999999999</v>
@@ -10904,7 +10904,7 @@
         <v>15</v>
       </c>
       <c r="BA41" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BB41" t="n">
         <v>18</v>
@@ -10916,13 +10916,13 @@
         <v>28</v>
       </c>
       <c r="BE41" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BF41" t="n">
         <v>13</v>
       </c>
       <c r="BG41" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BH41" t="n">
         <v>3.55</v>
@@ -10986,7 +10986,7 @@
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-07-18 18:49:17</t>
+          <t>2026-07-18 21:03:51</t>
         </is>
       </c>
     </row>
@@ -11023,16 +11023,16 @@
         <v>3.05</v>
       </c>
       <c r="H42" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="I42" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="J42" t="n">
         <v>2.82</v>
       </c>
       <c r="K42" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="L42" t="n">
         <v>1.56</v>
@@ -11065,7 +11065,7 @@
         <v>1.77</v>
       </c>
       <c r="V42" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W42" t="n">
         <v>1.5</v>
@@ -11113,7 +11113,7 @@
         <v>46</v>
       </c>
       <c r="AL42" t="n">
-        <v>75</v>
+        <v>500</v>
       </c>
       <c r="AM42" t="n">
         <v>500</v>
@@ -11125,10 +11125,10 @@
         <v>65</v>
       </c>
       <c r="AP42" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="AQ42" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AR42" t="n">
         <v>16</v>
@@ -11240,7 +11240,7 @@
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-07-18 18:49:17</t>
+          <t>2026-07-18 21:03:51</t>
         </is>
       </c>
     </row>
@@ -11346,7 +11346,7 @@
         <v>12</v>
       </c>
       <c r="AE43" t="n">
-        <v>32</v>
+        <v>65</v>
       </c>
       <c r="AF43" t="n">
         <v>34</v>
@@ -11388,7 +11388,7 @@
         <v>10.5</v>
       </c>
       <c r="AS43" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AT43" t="n">
         <v>10.5</v>
@@ -11403,7 +11403,7 @@
         <v>5.1</v>
       </c>
       <c r="AX43" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AY43" t="n">
         <v>14.5</v>
@@ -11412,25 +11412,25 @@
         <v>17.5</v>
       </c>
       <c r="BA43" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BB43" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BC43" t="n">
         <v>5.8</v>
       </c>
-      <c r="BC43" t="n">
-        <v>5.6</v>
-      </c>
       <c r="BD43" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BE43" t="n">
+        <v>6</v>
+      </c>
+      <c r="BF43" t="n">
         <v>5.9</v>
       </c>
-      <c r="BF43" t="n">
-        <v>5.8</v>
-      </c>
       <c r="BG43" t="n">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="BH43" t="n">
         <v>3.3</v>
@@ -11442,13 +11442,13 @@
         <v>12</v>
       </c>
       <c r="BK43" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BL43" t="n">
         <v>190</v>
       </c>
       <c r="BM43" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BN43" t="n">
         <v>8.199999999999999</v>
@@ -11460,13 +11460,13 @@
         <v>44</v>
       </c>
       <c r="BQ43" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BR43" t="n">
         <v>65</v>
       </c>
       <c r="BS43" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="BT43" t="n">
         <v>5.4</v>
@@ -11478,7 +11478,7 @@
         <v>19.5</v>
       </c>
       <c r="BW43" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BX43" t="n">
         <v>42</v>
@@ -11494,7 +11494,7 @@
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-07-18 18:49:17</t>
+          <t>2026-07-18 21:03:51</t>
         </is>
       </c>
     </row>
@@ -11537,13 +11537,13 @@
         <v>2.38</v>
       </c>
       <c r="J44" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K44" t="n">
         <v>3.45</v>
       </c>
       <c r="L44" t="n">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="M44" t="n">
         <v>1.1</v>
@@ -11588,7 +11588,7 @@
         <v>15</v>
       </c>
       <c r="AA44" t="n">
-        <v>36</v>
+        <v>900</v>
       </c>
       <c r="AB44" t="n">
         <v>12</v>
@@ -11603,7 +11603,7 @@
         <v>500</v>
       </c>
       <c r="AF44" t="n">
-        <v>25</v>
+        <v>500</v>
       </c>
       <c r="AG44" t="n">
         <v>16</v>
@@ -11642,7 +11642,7 @@
         <v>12.5</v>
       </c>
       <c r="AS44" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AT44" t="n">
         <v>9.800000000000001</v>
@@ -11684,7 +11684,7 @@
         <v>8.6</v>
       </c>
       <c r="BG44" t="n">
-        <v>20</v>
+        <v>7.2</v>
       </c>
       <c r="BH44" t="n">
         <v>3.35</v>
@@ -11748,7 +11748,7 @@
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-07-18 18:49:17</t>
+          <t>2026-07-18 21:03:51</t>
         </is>
       </c>
     </row>
@@ -11779,13 +11779,13 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="G45" t="n">
         <v>2.26</v>
       </c>
       <c r="H45" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="I45" t="n">
         <v>4.7</v>
@@ -11803,7 +11803,7 @@
         <v>1.06</v>
       </c>
       <c r="N45" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="O45" t="n">
         <v>1.3</v>
@@ -11812,22 +11812,22 @@
         <v>1.81</v>
       </c>
       <c r="Q45" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="R45" t="n">
         <v>1.31</v>
       </c>
       <c r="S45" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="T45" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="U45" t="n">
         <v>1.99</v>
       </c>
       <c r="V45" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="W45" t="n">
         <v>1.79</v>
@@ -11848,7 +11848,7 @@
         <v>10.5</v>
       </c>
       <c r="AC45" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AD45" t="n">
         <v>19.5</v>
@@ -11905,22 +11905,22 @@
         <v>3.5</v>
       </c>
       <c r="AV45" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AW45" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AX45" t="n">
         <v>4</v>
       </c>
       <c r="AY45" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="AZ45" t="n">
         <v>4.4</v>
       </c>
       <c r="BA45" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BB45" t="n">
         <v>4.6</v>
@@ -11929,16 +11929,16 @@
         <v>4.5</v>
       </c>
       <c r="BD45" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BE45" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BF45" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BG45" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BH45" t="n">
         <v>3.8</v>
@@ -11962,7 +11962,7 @@
         <v>5.2</v>
       </c>
       <c r="BO45" t="n">
-        <v>2.9</v>
+        <v>3.85</v>
       </c>
       <c r="BP45" t="n">
         <v>16</v>
@@ -12002,7 +12002,7 @@
       </c>
       <c r="CB45" t="inlineStr">
         <is>
-          <t>2026-07-18 18:49:17</t>
+          <t>2026-07-18 21:03:51</t>
         </is>
       </c>
     </row>
@@ -12039,19 +12039,19 @@
         <v>1.73</v>
       </c>
       <c r="H46" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="I46" t="n">
         <v>6.8</v>
       </c>
       <c r="J46" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K46" t="n">
         <v>4.8</v>
       </c>
       <c r="L46" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="M46" t="n">
         <v>1.05</v>
@@ -12060,13 +12060,13 @@
         <v>4.3</v>
       </c>
       <c r="O46" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P46" t="n">
         <v>2.14</v>
       </c>
       <c r="Q46" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="R46" t="n">
         <v>1.45</v>
@@ -12114,7 +12114,7 @@
         <v>11.5</v>
       </c>
       <c r="AG46" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH46" t="n">
         <v>21</v>
@@ -12150,7 +12150,7 @@
         <v>34</v>
       </c>
       <c r="AS46" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AT46" t="n">
         <v>7.2</v>
@@ -12162,7 +12162,7 @@
         <v>16.5</v>
       </c>
       <c r="AW46" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AX46" t="n">
         <v>9</v>
@@ -12174,7 +12174,7 @@
         <v>14.5</v>
       </c>
       <c r="BA46" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BB46" t="n">
         <v>11.5</v>
@@ -12183,16 +12183,16 @@
         <v>12</v>
       </c>
       <c r="BD46" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BE46" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BF46" t="n">
         <v>6.2</v>
       </c>
       <c r="BG46" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BH46" t="n">
         <v>4.6</v>
@@ -12256,7 +12256,7 @@
       </c>
       <c r="CB46" t="inlineStr">
         <is>
-          <t>2026-07-18 18:49:17</t>
+          <t>2026-07-18 21:03:51</t>
         </is>
       </c>
     </row>
@@ -12287,16 +12287,16 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="G47" t="n">
         <v>2.12</v>
       </c>
       <c r="H47" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="I47" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J47" t="n">
         <v>3.2</v>
@@ -12341,10 +12341,10 @@
         <v>1.89</v>
       </c>
       <c r="X47" t="n">
-        <v>950</v>
+        <v>13</v>
       </c>
       <c r="Y47" t="n">
-        <v>19</v>
+        <v>14.5</v>
       </c>
       <c r="Z47" t="n">
         <v>500</v>
@@ -12353,31 +12353,31 @@
         <v>900</v>
       </c>
       <c r="AB47" t="n">
-        <v>10.5</v>
+        <v>8</v>
       </c>
       <c r="AC47" t="n">
-        <v>10.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD47" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="AE47" t="n">
         <v>500</v>
       </c>
       <c r="AF47" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AG47" t="n">
-        <v>15</v>
+        <v>11.5</v>
       </c>
       <c r="AH47" t="n">
-        <v>950</v>
+        <v>22</v>
       </c>
       <c r="AI47" t="n">
         <v>500</v>
       </c>
       <c r="AJ47" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AK47" t="n">
         <v>65</v>
@@ -12389,64 +12389,64 @@
         <v>500</v>
       </c>
       <c r="AN47" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="AO47" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AP47" t="n">
-        <v>2.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ47" t="n">
-        <v>8.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="AR47" t="n">
-        <v>2.38</v>
+        <v>7</v>
       </c>
       <c r="AS47" t="n">
-        <v>2.5</v>
+        <v>8</v>
       </c>
       <c r="AT47" t="n">
-        <v>5.1</v>
+        <v>6.6</v>
       </c>
       <c r="AU47" t="n">
-        <v>5.3</v>
+        <v>6.6</v>
       </c>
       <c r="AV47" t="n">
-        <v>2.3</v>
+        <v>16</v>
       </c>
       <c r="AW47" t="n">
-        <v>2.46</v>
+        <v>7.8</v>
       </c>
       <c r="AX47" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AY47" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ47" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BA47" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BB47" t="n">
+        <v>20</v>
+      </c>
+      <c r="BC47" t="n">
+        <v>20</v>
+      </c>
+      <c r="BD47" t="n">
         <v>7.4</v>
       </c>
-      <c r="AY47" t="n">
-        <v>7</v>
-      </c>
-      <c r="AZ47" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="BA47" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="BB47" t="n">
-        <v>15</v>
-      </c>
-      <c r="BC47" t="n">
-        <v>15</v>
-      </c>
-      <c r="BD47" t="n">
-        <v>2.42</v>
-      </c>
       <c r="BE47" t="n">
-        <v>2.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF47" t="n">
-        <v>2.3</v>
+        <v>16</v>
       </c>
       <c r="BG47" t="n">
-        <v>2.52</v>
+        <v>8</v>
       </c>
       <c r="BH47" t="n">
         <v>3.4</v>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="CB47" t="inlineStr">
         <is>
-          <t>2026-07-18 18:49:17</t>
+          <t>2026-07-18 21:03:51</t>
         </is>
       </c>
     </row>
@@ -12541,19 +12541,19 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="G48" t="n">
         <v>1000</v>
       </c>
       <c r="H48" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="I48" t="n">
         <v>1000</v>
       </c>
       <c r="J48" t="n">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="K48" t="n">
         <v>1000</v>
@@ -12764,7 +12764,7 @@
       </c>
       <c r="CB48" t="inlineStr">
         <is>
-          <t>2026-07-18 18:49:17</t>
+          <t>2026-07-18 21:03:51</t>
         </is>
       </c>
     </row>
@@ -12813,7 +12813,7 @@
         <v>3.25</v>
       </c>
       <c r="L49" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="M49" t="n">
         <v>1.12</v>
@@ -12837,7 +12837,7 @@
         <v>5.1</v>
       </c>
       <c r="T49" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="U49" t="n">
         <v>1.79</v>
@@ -12873,7 +12873,7 @@
         <v>500</v>
       </c>
       <c r="AF49" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AG49" t="n">
         <v>12.5</v>
@@ -12909,10 +12909,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AR49" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AS49" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AT49" t="n">
         <v>6.4</v>
@@ -12924,7 +12924,7 @@
         <v>14.5</v>
       </c>
       <c r="AW49" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AX49" t="n">
         <v>11.5</v>
@@ -12936,25 +12936,25 @@
         <v>19</v>
       </c>
       <c r="BA49" t="n">
+        <v>10</v>
+      </c>
+      <c r="BB49" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BC49" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BD49" t="n">
         <v>9.6</v>
       </c>
-      <c r="BB49" t="n">
-        <v>8</v>
-      </c>
-      <c r="BC49" t="n">
-        <v>8</v>
-      </c>
-      <c r="BD49" t="n">
-        <v>9</v>
-      </c>
       <c r="BE49" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BF49" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BG49" t="n">
         <v>10</v>
-      </c>
-      <c r="BF49" t="n">
-        <v>8</v>
-      </c>
-      <c r="BG49" t="n">
-        <v>9.800000000000001</v>
       </c>
       <c r="BH49" t="n">
         <v>3.2</v>
@@ -12966,13 +12966,13 @@
         <v>13.5</v>
       </c>
       <c r="BK49" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="BL49" t="n">
         <v>240</v>
       </c>
       <c r="BM49" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BN49" t="n">
         <v>5.8</v>
@@ -12987,7 +12987,7 @@
         <v>4.1</v>
       </c>
       <c r="BR49" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BS49" t="n">
         <v>4.5</v>
@@ -13002,7 +13002,7 @@
         <v>46</v>
       </c>
       <c r="BW49" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BX49" t="n">
         <v>70</v>
@@ -13014,11 +13014,11 @@
         <v>55</v>
       </c>
       <c r="CA49" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="CB49" t="inlineStr">
         <is>
-          <t>2026-07-18 18:49:17</t>
+          <t>2026-07-18 21:03:51</t>
         </is>
       </c>
     </row>
@@ -13049,64 +13049,64 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>1.94</v>
+        <v>1.77</v>
       </c>
       <c r="G50" t="n">
-        <v>2.34</v>
+        <v>2.14</v>
       </c>
       <c r="H50" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="I50" t="n">
-        <v>5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J50" t="n">
-        <v>2.96</v>
+        <v>3.1</v>
       </c>
       <c r="K50" t="n">
         <v>3.65</v>
       </c>
       <c r="L50" t="n">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="M50" t="n">
         <v>1.09</v>
       </c>
       <c r="N50" t="n">
-        <v>2.58</v>
+        <v>2.24</v>
       </c>
       <c r="O50" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="P50" t="n">
-        <v>1.59</v>
+        <v>1.45</v>
       </c>
       <c r="Q50" t="n">
-        <v>2.18</v>
+        <v>2.28</v>
       </c>
       <c r="R50" t="n">
         <v>1.18</v>
       </c>
       <c r="S50" t="n">
-        <v>3.45</v>
+        <v>4.7</v>
       </c>
       <c r="T50" t="n">
-        <v>1.81</v>
+        <v>1.6</v>
       </c>
       <c r="U50" t="n">
-        <v>1.78</v>
+        <v>1.49</v>
       </c>
       <c r="V50" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="W50" t="n">
-        <v>1.74</v>
+        <v>1.87</v>
       </c>
       <c r="X50" t="n">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="Y50" t="n">
-        <v>14</v>
+        <v>970</v>
       </c>
       <c r="Z50" t="n">
         <v>500</v>
@@ -13115,34 +13115,34 @@
         <v>900</v>
       </c>
       <c r="AB50" t="n">
-        <v>8.4</v>
+        <v>970</v>
       </c>
       <c r="AC50" t="n">
-        <v>8.4</v>
+        <v>970</v>
       </c>
       <c r="AD50" t="n">
-        <v>20</v>
+        <v>500</v>
       </c>
       <c r="AE50" t="n">
         <v>500</v>
       </c>
       <c r="AF50" t="n">
-        <v>17</v>
+        <v>970</v>
       </c>
       <c r="AG50" t="n">
-        <v>12.5</v>
+        <v>970</v>
       </c>
       <c r="AH50" t="n">
-        <v>24</v>
+        <v>500</v>
       </c>
       <c r="AI50" t="n">
         <v>500</v>
       </c>
       <c r="AJ50" t="n">
-        <v>30</v>
+        <v>900</v>
       </c>
       <c r="AK50" t="n">
-        <v>30</v>
+        <v>500</v>
       </c>
       <c r="AL50" t="n">
         <v>500</v>
@@ -13151,128 +13151,128 @@
         <v>500</v>
       </c>
       <c r="AN50" t="n">
-        <v>26</v>
+        <v>500</v>
       </c>
       <c r="AO50" t="n">
         <v>1000</v>
       </c>
       <c r="AP50" t="n">
-        <v>3.55</v>
+        <v>1.1</v>
       </c>
       <c r="AQ50" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AR50" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AS50" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AT50" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AU50" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AV50" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AW50" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AX50" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AY50" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AZ50" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BA50" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="BB50" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="BC50" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="BD50" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BE50" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BF50" t="n">
         <v>3.75</v>
       </c>
-      <c r="AR50" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AS50" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AT50" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AU50" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AV50" t="n">
-        <v>4</v>
-      </c>
-      <c r="AW50" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AX50" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AY50" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AZ50" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BA50" t="n">
-        <v>5</v>
-      </c>
-      <c r="BB50" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BC50" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BD50" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BE50" t="n">
-        <v>5</v>
-      </c>
-      <c r="BF50" t="n">
-        <v>4.2</v>
-      </c>
       <c r="BG50" t="n">
-        <v>5.1</v>
+        <v>1.1</v>
       </c>
       <c r="BH50" t="n">
-        <v>3.4</v>
+        <v>1000</v>
       </c>
       <c r="BI50" t="n">
-        <v>2.4</v>
+        <v>1.04</v>
       </c>
       <c r="BJ50" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="BK50" t="n">
-        <v>3.6</v>
+        <v>1.04</v>
       </c>
       <c r="BL50" t="n">
-        <v>210</v>
+        <v>1000</v>
       </c>
       <c r="BM50" t="n">
-        <v>4.9</v>
+        <v>1.04</v>
       </c>
       <c r="BN50" t="n">
-        <v>5.5</v>
+        <v>1000</v>
       </c>
       <c r="BO50" t="n">
-        <v>2.62</v>
+        <v>1.04</v>
       </c>
       <c r="BP50" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="BQ50" t="n">
-        <v>4</v>
+        <v>1.04</v>
       </c>
       <c r="BR50" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BS50" t="n">
-        <v>4.5</v>
+        <v>1.04</v>
       </c>
       <c r="BT50" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BU50" t="n">
-        <v>3.15</v>
+        <v>1.04</v>
       </c>
       <c r="BV50" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BW50" t="n">
-        <v>4.5</v>
+        <v>1.04</v>
       </c>
       <c r="BX50" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="BY50" t="n">
-        <v>4.6</v>
+        <v>1.04</v>
       </c>
       <c r="BZ50" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="CA50" t="n">
-        <v>4.5</v>
+        <v>1.04</v>
       </c>
       <c r="CB50" t="inlineStr">
         <is>
-          <t>2026-07-18 18:49:17</t>
+          <t>2026-07-18 21:03:51</t>
         </is>
       </c>
     </row>
@@ -13303,55 +13303,55 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="G51" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="H51" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="I51" t="n">
         <v>3.3</v>
-      </c>
-      <c r="H51" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="I51" t="n">
-        <v>3.35</v>
       </c>
       <c r="J51" t="n">
         <v>2.88</v>
       </c>
       <c r="K51" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="L51" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="M51" t="n">
         <v>1.12</v>
       </c>
       <c r="N51" t="n">
-        <v>2.5</v>
+        <v>2.64</v>
       </c>
       <c r="O51" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="P51" t="n">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="Q51" t="n">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="R51" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="S51" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="T51" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="U51" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="V51" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W51" t="n">
         <v>1.44</v>
@@ -13411,7 +13411,7 @@
         <v>60</v>
       </c>
       <c r="AP51" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AQ51" t="n">
         <v>6.8</v>
@@ -13526,7 +13526,7 @@
       </c>
       <c r="CB51" t="inlineStr">
         <is>
-          <t>2026-07-18 18:49:17</t>
+          <t>2026-07-18 21:03:51</t>
         </is>
       </c>
     </row>
@@ -13557,31 +13557,31 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="G52" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="H52" t="n">
         <v>3.4</v>
       </c>
       <c r="I52" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="J52" t="n">
-        <v>2.88</v>
+        <v>3.05</v>
       </c>
       <c r="K52" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L52" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="M52" t="n">
         <v>1.11</v>
       </c>
       <c r="N52" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="O52" t="n">
         <v>1.46</v>
@@ -13590,7 +13590,7 @@
         <v>1.56</v>
       </c>
       <c r="Q52" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="R52" t="n">
         <v>1.2</v>
@@ -13599,16 +13599,16 @@
         <v>4.7</v>
       </c>
       <c r="T52" t="n">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="U52" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="V52" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W52" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="X52" t="n">
         <v>10</v>
@@ -13617,22 +13617,22 @@
         <v>11.5</v>
       </c>
       <c r="Z52" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AA52" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AB52" t="n">
-        <v>9.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC52" t="n">
         <v>7.8</v>
       </c>
       <c r="AD52" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="AE52" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="AF52" t="n">
         <v>15</v>
@@ -13641,49 +13641,49 @@
         <v>12.5</v>
       </c>
       <c r="AH52" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI52" t="n">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="AJ52" t="n">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="AK52" t="n">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="AL52" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="AM52" t="n">
         <v>200</v>
       </c>
       <c r="AN52" t="n">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="AO52" t="n">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="AP52" t="n">
         <v>7</v>
       </c>
       <c r="AQ52" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AR52" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AS52" t="n">
         <v>1.01</v>
       </c>
       <c r="AT52" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="AU52" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AV52" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AW52" t="n">
         <v>1.01</v>
@@ -13692,7 +13692,7 @@
         <v>10</v>
       </c>
       <c r="AY52" t="n">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ52" t="n">
         <v>15.5</v>
@@ -13722,7 +13722,7 @@
         <v>3.25</v>
       </c>
       <c r="BI52" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="BJ52" t="n">
         <v>13</v>
@@ -13731,7 +13731,7 @@
         <v>3.6</v>
       </c>
       <c r="BL52" t="n">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="BM52" t="n">
         <v>4.9</v>
@@ -13749,7 +13749,7 @@
         <v>4.1</v>
       </c>
       <c r="BR52" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BS52" t="n">
         <v>4.5</v>
@@ -13761,7 +13761,7 @@
         <v>5.1</v>
       </c>
       <c r="BV52" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BW52" t="n">
         <v>4.5</v>
@@ -13780,7 +13780,7 @@
       </c>
       <c r="CB52" t="inlineStr">
         <is>
-          <t>2026-07-18 18:49:17</t>
+          <t>2026-07-18 21:03:51</t>
         </is>
       </c>
     </row>
@@ -13811,22 +13811,22 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="G53" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="H53" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="I53" t="n">
         <v>10.5</v>
       </c>
       <c r="J53" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="K53" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="L53" t="n">
         <v>1.3</v>
@@ -13835,13 +13835,13 @@
         <v>1.05</v>
       </c>
       <c r="N53" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="O53" t="n">
         <v>1.27</v>
       </c>
       <c r="P53" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="Q53" t="n">
         <v>1.8</v>
@@ -13907,7 +13907,7 @@
         <v>17</v>
       </c>
       <c r="AL53" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="AM53" t="n">
         <v>200</v>
@@ -13922,13 +13922,13 @@
         <v>15</v>
       </c>
       <c r="AQ53" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AR53" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AS53" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AT53" t="n">
         <v>6.8</v>
@@ -13937,10 +13937,10 @@
         <v>9.4</v>
       </c>
       <c r="AV53" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="AW53" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AX53" t="n">
         <v>7.2</v>
@@ -13949,10 +13949,10 @@
         <v>8.6</v>
       </c>
       <c r="AZ53" t="n">
-        <v>19</v>
+        <v>5.5</v>
       </c>
       <c r="BA53" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BB53" t="n">
         <v>10</v>
@@ -13961,16 +13961,16 @@
         <v>13.5</v>
       </c>
       <c r="BD53" t="n">
-        <v>27</v>
+        <v>5.9</v>
       </c>
       <c r="BE53" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BF53" t="n">
         <v>6</v>
       </c>
       <c r="BG53" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BH53" t="n">
         <v>4.4</v>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="CB53" t="inlineStr">
         <is>
-          <t>2026-07-18 18:49:17</t>
+          <t>2026-07-18 21:03:51</t>
         </is>
       </c>
     </row>
@@ -14068,7 +14068,7 @@
         <v>1.38</v>
       </c>
       <c r="G54" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="H54" t="n">
         <v>10</v>
@@ -14077,7 +14077,7 @@
         <v>14</v>
       </c>
       <c r="J54" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="K54" t="n">
         <v>5.5</v>
@@ -14095,10 +14095,10 @@
         <v>1.27</v>
       </c>
       <c r="P54" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="Q54" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="R54" t="n">
         <v>1.39</v>
@@ -14110,13 +14110,13 @@
         <v>2.14</v>
       </c>
       <c r="U54" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="V54" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="W54" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="X54" t="n">
         <v>20</v>
@@ -14221,7 +14221,7 @@
         <v>6.2</v>
       </c>
       <c r="BF54" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="BG54" t="n">
         <v>6.2</v>
@@ -14288,7 +14288,7 @@
       </c>
       <c r="CB54" t="inlineStr">
         <is>
-          <t>2026-07-18 18:49:17</t>
+          <t>2026-07-18 21:03:51</t>
         </is>
       </c>
     </row>
@@ -14325,13 +14325,13 @@
         <v>1.5</v>
       </c>
       <c r="H55" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="I55" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="J55" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="K55" t="n">
         <v>6.8</v>
@@ -14343,7 +14343,7 @@
         <v>1.01</v>
       </c>
       <c r="N55" t="n">
-        <v>1.1</v>
+        <v>5.7</v>
       </c>
       <c r="O55" t="n">
         <v>1.14</v>
@@ -14367,10 +14367,10 @@
         <v>2.2</v>
       </c>
       <c r="V55" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="W55" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="X55" t="n">
         <v>40</v>
@@ -14397,28 +14397,28 @@
         <v>100</v>
       </c>
       <c r="AF55" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AG55" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AH55" t="n">
         <v>24</v>
       </c>
       <c r="AI55" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AJ55" t="n">
         <v>16</v>
       </c>
       <c r="AK55" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AL55" t="n">
         <v>32</v>
       </c>
       <c r="AM55" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AN55" t="n">
         <v>5.2</v>
@@ -14427,85 +14427,85 @@
         <v>85</v>
       </c>
       <c r="AP55" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="AQ55" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="AR55" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AS55" t="n">
         <v>5.3</v>
       </c>
-      <c r="AS55" t="n">
-        <v>5.5</v>
-      </c>
       <c r="AT55" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AU55" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="AV55" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="AW55" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="AX55" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="AY55" t="n">
         <v>3.8</v>
       </c>
       <c r="AZ55" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="BA55" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BB55" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="BC55" t="n">
         <v>4.1</v>
       </c>
       <c r="BD55" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="BE55" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="BF55" t="n">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="BG55" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="BH55" t="n">
         <v>5.7</v>
       </c>
       <c r="BI55" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="BJ55" t="n">
         <v>11.5</v>
       </c>
       <c r="BK55" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="BL55" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="BM55" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="BN55" t="n">
         <v>5</v>
       </c>
       <c r="BO55" t="n">
-        <v>2.72</v>
+        <v>2.66</v>
       </c>
       <c r="BP55" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BQ55" t="n">
         <v>3.55</v>
@@ -14514,25 +14514,25 @@
         <v>21</v>
       </c>
       <c r="BS55" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BT55" t="n">
         <v>13</v>
       </c>
       <c r="BU55" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BV55" t="n">
         <v>60</v>
       </c>
       <c r="BW55" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="BX55" t="n">
         <v>55</v>
       </c>
       <c r="BY55" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BZ55" t="n">
         <v>0</v>
@@ -14542,7 +14542,7 @@
       </c>
       <c r="CB55" t="inlineStr">
         <is>
-          <t>2026-07-18 18:49:17</t>
+          <t>2026-07-18 21:03:51</t>
         </is>
       </c>
     </row>
